--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/Stocks/Data/Stocks/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16DC897A-35A7-7446-9715-8E9F09EC1C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44681635-F8EA-D747-8184-ECF65A9077C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="1" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -1099,20 +1099,19 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sheet1"/>
+      <sheetName val="1. List_AutomaticData"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="6">
           <cell r="C6">
-            <v>175.2</v>
+            <v>201.68</v>
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1525,7 +1524,7 @@
       </c>
       <c r="C3" s="34">
         <f>[1]Sheet1!$C$6</f>
-        <v>175.2</v>
+        <v>201.68</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.2">
@@ -1545,7 +1544,7 @@
       </c>
       <c r="C9" s="88">
         <f>C3*'Statement Q'!J133</f>
-        <v>4257360</v>
+        <v>4900824</v>
       </c>
     </row>
   </sheetData>

--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44681635-F8EA-D747-8184-ECF65A9077C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6BF44BC-AB1A-EC48-9AE5-1C9F4B84A391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="1" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -45,6 +45,7 @@
   <authors>
     <author>tc={29FC7FD2-5F9A-5C4F-BF8E-3E5CCBBE01EB}</author>
     <author>tc={99CB6D0C-F252-AD47-9174-81F4A7883F6D}</author>
+    <author>tc={20862E9D-9DF4-6C49-AC66-E72F2C0DA1C7}</author>
     <author>tc={2BBFC279-0AE8-CC41-8651-7C9F770A0136}</author>
   </authors>
   <commentList>
@@ -64,7 +65,15 @@
     The company had $31M in convertible debt that has been subtracted</t>
       </text>
     </comment>
-    <comment ref="B140" authorId="2" shapeId="0" xr:uid="{2BBFC279-0AE8-CC41-8651-7C9F770A0136}">
+    <comment ref="B139" authorId="2" shapeId="0" xr:uid="{20862E9D-9DF4-6C49-AC66-E72F2C0DA1C7}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Actual number</t>
+      </text>
+    </comment>
+    <comment ref="B140" authorId="3" shapeId="0" xr:uid="{2BBFC279-0AE8-CC41-8651-7C9F770A0136}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -634,7 +643,7 @@
     <numFmt numFmtId="164" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="165" formatCode="0.000_);[Red]\(0.000\)"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -714,6 +723,12 @@
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="12">
@@ -1099,6 +1114,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sheet1"/>
       <sheetName val="1. List_AutomaticData"/>
@@ -1446,6 +1464,9 @@
   <threadedComment ref="D121" dT="2025-12-22T13:50:10.75" personId="{C1312E89-78DF-2C41-9F37-0481EBE70D1D}" id="{99CB6D0C-F252-AD47-9174-81F4A7883F6D}">
     <text>The company had $31M in convertible debt that has been subtracted</text>
   </threadedComment>
+  <threadedComment ref="B139" dT="2026-04-18T21:58:38.68" personId="{C1312E89-78DF-2C41-9F37-0481EBE70D1D}" id="{20862E9D-9DF4-6C49-AC66-E72F2C0DA1C7}">
+    <text>Actual number</text>
+  </threadedComment>
   <threadedComment ref="B140" dT="2025-12-21T17:36:44.92" personId="{C1312E89-78DF-2C41-9F37-0481EBE70D1D}" id="{2BBFC279-0AE8-CC41-8651-7C9F770A0136}">
     <text>Total stock split factor. in this case they split first 4:1 and then 10:1 so older values will be 4*10</text>
   </threadedComment>
@@ -1662,7 +1683,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:16" s="50" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" s="50" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7"/>
       <c r="B5" s="17" t="s">
         <v>7</v>
@@ -1701,7 +1722,7 @@
         <v>215938</v>
       </c>
     </row>
-    <row r="6" spans="1:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B6" s="9" t="s">
         <v>8</v>
       </c>
@@ -1739,7 +1760,7 @@
         <v>62475</v>
       </c>
     </row>
-    <row r="7" spans="1:16" s="50" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" s="50" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7"/>
       <c r="B7" s="17" t="s">
         <v>9</v>
@@ -1789,7 +1810,7 @@
         <v>153463</v>
       </c>
     </row>
-    <row r="8" spans="1:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B8" s="9" t="s">
         <v>10</v>
       </c>
@@ -1830,7 +1851,7 @@
       <c r="O8" s="27"/>
       <c r="P8" s="27"/>
     </row>
-    <row r="9" spans="1:16" s="8" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" s="8" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B9" s="12" t="s">
         <v>11</v>
       </c>
@@ -1870,7 +1891,7 @@
       <c r="N9" s="27"/>
       <c r="O9" s="27"/>
     </row>
-    <row r="10" spans="1:16" s="8" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" s="8" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B10" s="12" t="s">
         <v>131</v>
       </c>
@@ -1910,7 +1931,7 @@
       <c r="N10" s="27"/>
       <c r="O10" s="27"/>
     </row>
-    <row r="11" spans="1:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B11" s="12" t="s">
         <v>121</v>
       </c>
@@ -1950,7 +1971,7 @@
       <c r="N11" s="27"/>
       <c r="O11" s="27"/>
     </row>
-    <row r="12" spans="1:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B12" s="12" t="s">
         <v>12</v>
       </c>
@@ -1999,7 +2020,7 @@
         <v>23076</v>
       </c>
     </row>
-    <row r="13" spans="1:16" s="50" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" s="50" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7"/>
       <c r="B13" s="17" t="s">
         <v>13</v>
@@ -2040,7 +2061,7 @@
       <c r="N13" s="48"/>
       <c r="O13" s="48"/>
     </row>
-    <row r="14" spans="1:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B14" s="12" t="s">
         <v>113</v>
       </c>
@@ -2080,7 +2101,7 @@
       <c r="N14" s="27"/>
       <c r="O14" s="27"/>
     </row>
-    <row r="15" spans="1:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B15" s="12" t="s">
         <v>122</v>
       </c>
@@ -2120,7 +2141,7 @@
       <c r="N15" s="27"/>
       <c r="O15" s="27"/>
     </row>
-    <row r="16" spans="1:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B16" s="12" t="s">
         <v>123</v>
       </c>
@@ -2160,7 +2181,7 @@
       <c r="N16" s="27"/>
       <c r="O16" s="27"/>
     </row>
-    <row r="17" spans="1:16" s="50" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" s="50" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A17" s="7"/>
       <c r="B17" s="17" t="s">
         <v>14</v>
@@ -2201,7 +2222,7 @@
       <c r="N17" s="48"/>
       <c r="O17" s="48"/>
     </row>
-    <row r="18" spans="1:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B18" s="12" t="s">
         <v>83</v>
       </c>
@@ -2241,7 +2262,7 @@
       <c r="N18" s="27"/>
       <c r="O18" s="27"/>
     </row>
-    <row r="19" spans="1:16" s="18" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A19" s="7"/>
       <c r="B19" s="17" t="s">
         <v>15</v>
@@ -2283,7 +2304,7 @@
       <c r="O19" s="48"/>
       <c r="P19" s="50"/>
     </row>
-    <row r="20" spans="1:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B20" s="12" t="s">
         <v>16</v>
       </c>
@@ -2323,7 +2344,7 @@
       <c r="N20" s="27"/>
       <c r="O20" s="27"/>
     </row>
-    <row r="21" spans="1:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B21" s="12" t="s">
         <v>127</v>
       </c>
@@ -2374,7 +2395,7 @@
       <c r="N21" s="27"/>
       <c r="O21" s="27"/>
     </row>
-    <row r="22" spans="1:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B22" s="12" t="s">
         <v>17</v>
       </c>
@@ -2414,7 +2435,7 @@
       <c r="N22" s="27"/>
       <c r="O22" s="27"/>
     </row>
-    <row r="23" spans="1:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B23" s="12" t="s">
         <v>128</v>
       </c>
@@ -2465,7 +2486,7 @@
       <c r="N23" s="27"/>
       <c r="O23" s="27"/>
     </row>
-    <row r="24" spans="1:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B24" s="12" t="s">
         <v>18</v>
       </c>
@@ -2505,7 +2526,7 @@
       <c r="N24" s="30"/>
       <c r="O24" s="30"/>
     </row>
-    <row r="25" spans="1:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B25" s="12" t="s">
         <v>129</v>
       </c>
@@ -2556,7 +2577,7 @@
       <c r="N25" s="30"/>
       <c r="O25" s="30"/>
     </row>
-    <row r="26" spans="1:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B26" s="12" t="s">
         <v>19</v>
       </c>
@@ -2596,7 +2617,7 @@
       <c r="N26" s="30"/>
       <c r="O26" s="30"/>
     </row>
-    <row r="27" spans="1:16" s="16" customFormat="1" ht="17" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" s="16" customFormat="1" ht="17" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="10" t="s">
         <v>130</v>
@@ -2648,7 +2669,7 @@
       <c r="N27" s="31"/>
       <c r="O27" s="31"/>
     </row>
-    <row r="28" spans="1:16" s="16" customFormat="1" ht="17" collapsed="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" s="16" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="6"/>
       <c r="F28" s="6"/>

--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6BF44BC-AB1A-EC48-9AE5-1C9F4B84A391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FF5FFC0-98B4-AF42-9674-ECDBD3171A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="1" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -643,7 +643,7 @@
     <numFmt numFmtId="164" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="165" formatCode="0.000_);[Red]\(0.000\)"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -723,12 +723,6 @@
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="12">
@@ -1125,7 +1119,7 @@
       <sheetData sheetId="0">
         <row r="6">
           <cell r="C6">
-            <v>201.68</v>
+            <v>224.36</v>
           </cell>
         </row>
       </sheetData>
@@ -1545,7 +1539,7 @@
       </c>
       <c r="C3" s="34">
         <f>[1]Sheet1!$C$6</f>
-        <v>201.68</v>
+        <v>224.36</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.2">
@@ -1565,7 +1559,7 @@
       </c>
       <c r="C9" s="88">
         <f>C3*'Statement Q'!J133</f>
-        <v>4900824</v>
+        <v>5451948</v>
       </c>
     </row>
   </sheetData>

--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72D3CB17-DB87-284C-ACBB-6E10E12ADBE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4630369-20F5-1A49-987C-1B2E0E2DE78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -150,7 +150,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="389">
   <si>
     <t>Ticker</t>
   </si>
@@ -956,9 +956,6 @@
     <t>Dividend yield</t>
   </si>
   <si>
-    <t>FCF/Sales</t>
-  </si>
-  <si>
     <t>Earnings yields</t>
   </si>
   <si>
@@ -1314,6 +1311,12 @@
   </si>
   <si>
     <t>Edge Growth Rate</t>
+  </si>
+  <si>
+    <t>FCFF/Sales (FCFF Margin)</t>
+  </si>
+  <si>
+    <t>FCFE/Sales (FCFE Margin)</t>
   </si>
 </sst>
 </file>
@@ -1917,7 +1920,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="248">
+  <cellXfs count="249">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2219,6 +2222,14 @@
     <xf numFmtId="10" fontId="0" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="10" fontId="9" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2231,12 +2242,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2246,10 +2251,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2259,6 +2264,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2272,13 +2283,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="9" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -11664,7 +11668,7 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>236.54</v>
-    <v>138.83000000000001</v>
+    <v>140.85499999999999</v>
     <v>2.2010999999999998</v>
     <v>-13.56</v>
     <v>-6.2013999999999993E-2</v>
@@ -12524,18 +12528,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="228" t="s">
+      <c r="B2" s="232" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="229"/>
-      <c r="E2" s="228" t="s">
-        <v>288</v>
-      </c>
-      <c r="F2" s="229"/>
-      <c r="H2" s="228" t="s">
-        <v>329</v>
-      </c>
-      <c r="I2" s="229"/>
+      <c r="C2" s="233"/>
+      <c r="E2" s="232" t="s">
+        <v>287</v>
+      </c>
+      <c r="F2" s="233"/>
+      <c r="H2" s="232" t="s">
+        <v>328</v>
+      </c>
+      <c r="I2" s="233"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="189" t="s">
@@ -12690,7 +12694,7 @@
         <v>-6.2013999999999993E-2</v>
       </c>
       <c r="E9" s="189" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F9" s="196">
         <f ca="1">Statement!AC173</f>
@@ -12706,7 +12710,7 @@
         <v>-5.071E-3</v>
       </c>
       <c r="E10" s="189" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F10" s="196">
         <f ca="1">Statement!AC175</f>
@@ -12722,7 +12726,7 @@
         <v>236.54</v>
       </c>
       <c r="E11" s="190" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F11" s="197">
         <f ca="1">Statement!AC174</f>
@@ -12735,7 +12739,7 @@
       </c>
       <c r="C12" s="213" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>138.83000000000001</v>
+        <v>140.85499999999999</v>
       </c>
       <c r="E12" s="189" t="s">
         <v>94</v>
@@ -12779,32 +12783,32 @@
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.2">
       <c r="E15" s="189" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F15" s="196">
-        <f ca="1">Statement!AC186</f>
+        <f ca="1">Statement!AC187</f>
         <v>1.4463920490363455E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
       <c r="E16" s="190" t="s">
+        <v>295</v>
+      </c>
+      <c r="F16" s="195">
+        <f>Statement!AC186</f>
+        <v>2.9794214876033056</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B17" s="234" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" s="234"/>
+      <c r="E17" s="188" t="s">
         <v>296</v>
       </c>
-      <c r="F16" s="195">
-        <f>Statement!AC185</f>
-        <v>2.9794214876033056</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="230" t="s">
-        <v>83</v>
-      </c>
-      <c r="C17" s="230"/>
-      <c r="E17" s="188" t="s">
-        <v>297</v>
-      </c>
       <c r="F17" s="198">
-        <f>Statement!AC181</f>
+        <f>Statement!AC182</f>
         <v>3.9374614276897757E-2</v>
       </c>
     </row>
@@ -12813,10 +12817,10 @@
         <v>12</v>
       </c>
       <c r="C18" s="69" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E18" s="189" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F18" s="194">
         <f>Statement!AC155</f>
@@ -12844,10 +12848,10 @@
         <v>84</v>
       </c>
       <c r="C20" s="69" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E20" s="190" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F20" s="195">
         <f>Statement!AC158</f>
@@ -12868,18 +12872,18 @@
         <v>87</v>
       </c>
       <c r="C22" s="69" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="230" t="s">
+      <c r="B25" s="234" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="230"/>
-      <c r="E25" s="228" t="s">
-        <v>344</v>
-      </c>
-      <c r="F25" s="229"/>
+      <c r="C25" s="234"/>
+      <c r="E25" s="232" t="s">
+        <v>343</v>
+      </c>
+      <c r="F25" s="233"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="188" t="s">
@@ -12904,7 +12908,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="E27" s="190" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F27" s="225">
         <f ca="1">F26/1000</f>
@@ -12912,72 +12916,72 @@
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B31" s="227" t="s">
-        <v>339</v>
-      </c>
-      <c r="C31" s="227"/>
-      <c r="D31" s="227"/>
-      <c r="E31" s="227"/>
-      <c r="F31" s="227"/>
-      <c r="G31" s="227"/>
-      <c r="H31" s="227"/>
+      <c r="B31" s="231" t="s">
+        <v>338</v>
+      </c>
+      <c r="C31" s="231"/>
+      <c r="D31" s="231"/>
+      <c r="E31" s="231"/>
+      <c r="F31" s="231"/>
+      <c r="G31" s="231"/>
+      <c r="H31" s="231"/>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="16" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
+        <v>340</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="231"/>
+      <c r="C37" s="231"/>
+      <c r="D37" s="231"/>
+      <c r="E37" s="231"/>
+      <c r="F37" s="231"/>
+      <c r="G37" s="231"/>
+      <c r="H37" s="231"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B40" s="231" t="s">
         <v>341</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="227"/>
-      <c r="C37" s="227"/>
-      <c r="D37" s="227"/>
-      <c r="E37" s="227"/>
-      <c r="F37" s="227"/>
-      <c r="G37" s="227"/>
-      <c r="H37" s="227"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B40" s="227" t="s">
-        <v>342</v>
-      </c>
-      <c r="C40" s="227"/>
-      <c r="D40" s="227"/>
-      <c r="E40" s="227"/>
-      <c r="F40" s="227"/>
-      <c r="G40" s="227"/>
-      <c r="H40" s="227"/>
+      <c r="C40" s="231"/>
+      <c r="D40" s="231"/>
+      <c r="E40" s="231"/>
+      <c r="F40" s="231"/>
+      <c r="G40" s="231"/>
+      <c r="H40" s="231"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="41" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C42" s="41" t="s">
+        <v>329</v>
+      </c>
+      <c r="D42" s="41" t="s">
         <v>330</v>
       </c>
-      <c r="D42" s="41" t="s">
-        <v>331</v>
-      </c>
       <c r="E42" s="222"/>
     </row>
     <row r="47" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="227"/>
-      <c r="C47" s="227"/>
-      <c r="D47" s="227"/>
-      <c r="E47" s="227"/>
-      <c r="F47" s="227"/>
-      <c r="G47" s="227"/>
-      <c r="H47" s="227"/>
+      <c r="B47" s="231"/>
+      <c r="C47" s="231"/>
+      <c r="D47" s="231"/>
+      <c r="E47" s="231"/>
+      <c r="F47" s="231"/>
+      <c r="G47" s="231"/>
+      <c r="H47" s="231"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -13060,36 +13064,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="227" t="s">
+      <c r="C2" s="231" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="227"/>
-      <c r="E2" s="227"/>
-      <c r="F2" s="227"/>
-      <c r="G2" s="236"/>
-      <c r="H2" s="237" t="s">
+      <c r="D2" s="231"/>
+      <c r="E2" s="231"/>
+      <c r="F2" s="231"/>
+      <c r="G2" s="243"/>
+      <c r="H2" s="244" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="227"/>
-      <c r="J2" s="227"/>
-      <c r="K2" s="227"/>
-      <c r="L2" s="227"/>
+      <c r="I2" s="231"/>
+      <c r="J2" s="231"/>
+      <c r="K2" s="231"/>
+      <c r="L2" s="231"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="227" t="s">
+      <c r="S2" s="231" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="227"/>
-      <c r="U2" s="227"/>
-      <c r="V2" s="227"/>
-      <c r="W2" s="227"/>
-      <c r="X2" s="227"/>
-      <c r="Y2" s="227"/>
-      <c r="Z2" s="227"/>
-      <c r="AA2" s="227" t="s">
+      <c r="T2" s="231"/>
+      <c r="U2" s="231"/>
+      <c r="V2" s="231"/>
+      <c r="W2" s="231"/>
+      <c r="X2" s="231"/>
+      <c r="Y2" s="231"/>
+      <c r="Z2" s="231"/>
+      <c r="AA2" s="231" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="227"/>
-      <c r="AC2" s="227"/>
+      <c r="AB2" s="231"/>
+      <c r="AC2" s="231"/>
       <c r="AE2" s="85" t="s">
         <v>107</v>
       </c>
@@ -13100,32 +13104,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="238" t="s">
+      <c r="C4" s="240" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="238"/>
-      <c r="E4" s="238"/>
-      <c r="F4" s="238"/>
-      <c r="G4" s="238"/>
-      <c r="H4" s="238"/>
-      <c r="I4" s="238"/>
-      <c r="J4" s="238"/>
-      <c r="K4" s="238"/>
-      <c r="L4" s="238"/>
+      <c r="D4" s="240"/>
+      <c r="E4" s="240"/>
+      <c r="F4" s="240"/>
+      <c r="G4" s="240"/>
+      <c r="H4" s="240"/>
+      <c r="I4" s="240"/>
+      <c r="J4" s="240"/>
+      <c r="K4" s="240"/>
+      <c r="L4" s="240"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="239" t="s">
+      <c r="S4" s="241" t="s">
         <v>108</v>
       </c>
-      <c r="T4" s="240"/>
-      <c r="U4" s="240"/>
-      <c r="V4" s="240"/>
-      <c r="W4" s="240"/>
-      <c r="X4" s="240"/>
-      <c r="Y4" s="240"/>
-      <c r="Z4" s="240"/>
-      <c r="AA4" s="240"/>
-      <c r="AB4" s="240"/>
-      <c r="AC4" s="240"/>
+      <c r="T4" s="242"/>
+      <c r="U4" s="242"/>
+      <c r="V4" s="242"/>
+      <c r="W4" s="242"/>
+      <c r="X4" s="242"/>
+      <c r="Y4" s="242"/>
+      <c r="Z4" s="242"/>
+      <c r="AA4" s="242"/>
+      <c r="AB4" s="242"/>
+      <c r="AC4" s="242"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -13223,7 +13227,7 @@
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B6" s="247" t="str">
+      <c r="B6" s="229" t="str">
         <f>Statement!B103</f>
         <v>HyperScale</v>
       </c>
@@ -13248,33 +13252,33 @@
         <v>105636</v>
       </c>
       <c r="H6" s="64">
-        <f>G6+G6*H14</f>
+        <f t="shared" ref="H6:L7" si="1">G6+G6*H14</f>
         <v>179581.2</v>
       </c>
       <c r="I6" s="64">
-        <f>H6+H6*I14</f>
+        <f t="shared" si="1"/>
         <v>296308.98000000004</v>
       </c>
       <c r="J6" s="64">
-        <f>I6+I6*J14</f>
+        <f t="shared" si="1"/>
         <v>459278.91900000011</v>
       </c>
       <c r="K6" s="64">
-        <f>J6+J6*K14</f>
+        <f t="shared" si="1"/>
         <v>665954.43255000014</v>
       </c>
       <c r="L6" s="64">
-        <f>K6+K6*L14</f>
+        <f t="shared" si="1"/>
         <v>899038.4839425002</v>
       </c>
       <c r="N6" s="90" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="O6" s="5"/>
       <c r="Q6" s="90" t="s">
-        <v>385</v>
-      </c>
-      <c r="R6" s="247" t="str">
+        <v>384</v>
+      </c>
+      <c r="R6" s="229" t="str">
         <f>B6</f>
         <v>HyperScale</v>
       </c>
@@ -13322,7 +13326,7 @@
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B7" s="247" t="str">
+      <c r="B7" s="229" t="str">
         <f>Statement!B104</f>
         <v>AI Clouds</v>
       </c>
@@ -13347,34 +13351,34 @@
         <v>88101</v>
       </c>
       <c r="H7" s="64">
-        <f>G7+G7*H15</f>
+        <f t="shared" si="1"/>
         <v>118936.35</v>
       </c>
       <c r="I7" s="64">
-        <f>H7+H7*I15</f>
+        <f t="shared" si="1"/>
         <v>158185.3455</v>
       </c>
       <c r="J7" s="64">
-        <f>I7+I7*J15</f>
+        <f t="shared" si="1"/>
         <v>205640.94915</v>
       </c>
       <c r="K7" s="64">
-        <f>J7+J7*K15</f>
+        <f t="shared" si="1"/>
         <v>246769.13897999999</v>
       </c>
       <c r="L7" s="64">
-        <f>K7+K7*L15</f>
+        <f t="shared" si="1"/>
         <v>276381.4356576</v>
       </c>
       <c r="N7" s="90" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="O7" s="5"/>
       <c r="Q7" s="90" t="s">
-        <v>386</v>
-      </c>
-      <c r="R7" s="247" t="str">
-        <f t="shared" ref="R7:R9" si="1">B7</f>
+        <v>385</v>
+      </c>
+      <c r="R7" s="229" t="str">
+        <f t="shared" ref="R7:R9" si="2">B7</f>
         <v>AI Clouds</v>
       </c>
       <c r="S7" s="88">
@@ -13416,7 +13420,7 @@
       <c r="AB7" s="64"/>
       <c r="AC7" s="64"/>
       <c r="AE7" s="64">
-        <f t="shared" ref="AE7:AE9" si="2">SUM(X7:AA7)</f>
+        <f t="shared" ref="AE7:AE9" si="3">SUM(X7:AA7)</f>
         <v>130856.86</v>
       </c>
     </row>
@@ -13469,7 +13473,7 @@
       <c r="O8" s="5"/>
       <c r="Q8" s="90"/>
       <c r="R8" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Data Center</v>
       </c>
       <c r="S8" s="88">
@@ -13511,7 +13515,7 @@
       <c r="AB8" s="64"/>
       <c r="AC8" s="64"/>
       <c r="AE8" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>274535.76</v>
       </c>
     </row>
@@ -13561,14 +13565,14 @@
         <v>81428.411531250007</v>
       </c>
       <c r="N9" s="90" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O9" s="5"/>
       <c r="Q9" s="90" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="R9" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Edge Computing</v>
       </c>
       <c r="S9" s="88">
@@ -13610,7 +13614,7 @@
       <c r="AB9" s="64"/>
       <c r="AC9" s="64"/>
       <c r="AE9" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>24915.21</v>
       </c>
     </row>
@@ -13710,76 +13714,76 @@
       <c r="Q11" s="91"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C12" s="238" t="s">
+      <c r="C12" s="240" t="s">
         <v>114</v>
       </c>
-      <c r="D12" s="238"/>
-      <c r="E12" s="238"/>
-      <c r="F12" s="238"/>
-      <c r="G12" s="238"/>
-      <c r="H12" s="238"/>
-      <c r="I12" s="238"/>
-      <c r="J12" s="238"/>
-      <c r="K12" s="238"/>
-      <c r="L12" s="238"/>
+      <c r="D12" s="240"/>
+      <c r="E12" s="240"/>
+      <c r="F12" s="240"/>
+      <c r="G12" s="240"/>
+      <c r="H12" s="240"/>
+      <c r="I12" s="240"/>
+      <c r="J12" s="240"/>
+      <c r="K12" s="240"/>
+      <c r="L12" s="240"/>
       <c r="O12" s="5"/>
       <c r="Q12" s="91"/>
-      <c r="S12" s="239" t="s">
+      <c r="S12" s="241" t="s">
         <v>114</v>
       </c>
-      <c r="T12" s="240"/>
-      <c r="U12" s="240"/>
-      <c r="V12" s="240"/>
-      <c r="W12" s="240"/>
-      <c r="X12" s="240"/>
-      <c r="Y12" s="240"/>
-      <c r="Z12" s="240"/>
-      <c r="AA12" s="240"/>
-      <c r="AB12" s="240"/>
-      <c r="AC12" s="240"/>
+      <c r="T12" s="242"/>
+      <c r="U12" s="242"/>
+      <c r="V12" s="242"/>
+      <c r="W12" s="242"/>
+      <c r="X12" s="242"/>
+      <c r="Y12" s="242"/>
+      <c r="Z12" s="242"/>
+      <c r="AA12" s="242"/>
+      <c r="AB12" s="242"/>
+      <c r="AC12" s="242"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B13" s="16" t="s">
         <v>115</v>
       </c>
       <c r="C13" s="12">
-        <f t="shared" ref="C13:L13" si="3">C5</f>
+        <f t="shared" ref="C13:L13" si="4">C5</f>
         <v>2022</v>
       </c>
       <c r="D13" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2023</v>
       </c>
       <c r="E13" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2024</v>
       </c>
       <c r="F13" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2025</v>
       </c>
       <c r="G13" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2026</v>
       </c>
       <c r="H13" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2027</v>
       </c>
       <c r="I13" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2028</v>
       </c>
       <c r="J13" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2029</v>
       </c>
       <c r="K13" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2030</v>
       </c>
       <c r="L13" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2031</v>
       </c>
       <c r="O13" s="5"/>
@@ -13788,70 +13792,70 @@
         <v>115</v>
       </c>
       <c r="S13" s="12" t="str">
-        <f t="shared" ref="S13:AC13" si="4">S5</f>
+        <f t="shared" ref="S13:AC13" si="5">S5</f>
         <v>Q2 2025</v>
       </c>
       <c r="T13" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Q3 2025</v>
       </c>
       <c r="U13" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Q4 2025</v>
       </c>
       <c r="V13" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Q1 2026</v>
       </c>
       <c r="W13" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Q2 2026</v>
       </c>
       <c r="X13" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Q3 2026</v>
       </c>
       <c r="Y13" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Q4 2026</v>
       </c>
       <c r="Z13" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Q1 2027</v>
       </c>
       <c r="AA13" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>FQ1</v>
       </c>
       <c r="AB13" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>FQ2</v>
       </c>
       <c r="AC13" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>FQ3</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B14" s="247" t="str">
+      <c r="B14" s="229" t="str">
         <f>B6</f>
         <v>HyperScale</v>
       </c>
       <c r="C14" s="47"/>
       <c r="D14" s="95" t="e">
-        <f t="shared" ref="D14:G14" si="5">D6/C6-1</f>
+        <f t="shared" ref="D14:G14" si="6">D6/C6-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E14" s="95" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F14" s="95" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G14" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.96364041936203426</v>
       </c>
       <c r="H14" s="106">
@@ -13871,37 +13875,37 @@
       </c>
       <c r="O14" s="5"/>
       <c r="Q14" s="91"/>
-      <c r="R14" s="247" t="str">
+      <c r="R14" s="229" t="str">
         <f>R6</f>
         <v>HyperScale</v>
       </c>
       <c r="S14" s="47"/>
       <c r="T14" s="95">
-        <f>T6/S6-1</f>
+        <f t="shared" ref="T14:Z16" si="7">T6/S6-1</f>
         <v>0.26059122575786109</v>
       </c>
       <c r="U14" s="95">
-        <f>U6/T6-1</f>
+        <f t="shared" si="7"/>
         <v>0.42598954443614634</v>
       </c>
       <c r="V14" s="95">
-        <f>V6/U6-1</f>
+        <f t="shared" si="7"/>
         <v>-7.8296847177123707E-2</v>
       </c>
       <c r="W14" s="95">
-        <f>W6/V6-1</f>
+        <f t="shared" si="7"/>
         <v>0.35706574237172561</v>
       </c>
       <c r="X14" s="95">
-        <f>X6/W6-1</f>
+        <f t="shared" si="7"/>
         <v>0.2703596700582005</v>
       </c>
       <c r="Y14" s="95">
-        <f>Y6/X6-1</f>
+        <f t="shared" si="7"/>
         <v>0.11450230718523402</v>
       </c>
       <c r="Z14" s="96">
-        <f>Z6/Y6-1</f>
+        <f t="shared" si="7"/>
         <v>0.11992074288756127</v>
       </c>
       <c r="AA14" s="106">
@@ -13911,25 +13915,25 @@
       <c r="AC14" s="95"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B15" s="247" t="str">
+      <c r="B15" s="229" t="str">
         <f>B7</f>
         <v>AI Clouds</v>
       </c>
       <c r="C15" s="47"/>
       <c r="D15" s="95" t="e">
-        <f t="shared" ref="D15:G15" si="6">D7/C7-1</f>
+        <f t="shared" ref="D15:G15" si="8">D7/C7-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E15" s="95" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F15" s="95" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G15" s="96">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.43510343704186361</v>
       </c>
       <c r="H15" s="106">
@@ -13949,37 +13953,37 @@
       </c>
       <c r="O15" s="5"/>
       <c r="Q15" s="91"/>
-      <c r="R15" s="247" t="str">
+      <c r="R15" s="229" t="str">
         <f>R7</f>
         <v>AI Clouds</v>
       </c>
       <c r="S15" s="47"/>
       <c r="T15" s="95">
-        <f>T7/S7-1</f>
+        <f t="shared" si="7"/>
         <v>0.11060702875399353</v>
       </c>
       <c r="U15" s="95">
-        <f>U7/T7-1</f>
+        <f t="shared" si="7"/>
         <v>-5.1493009608192808E-2</v>
       </c>
       <c r="V15" s="95">
-        <f>V7/U7-1</f>
+        <f t="shared" si="7"/>
         <v>0.304925391241053</v>
       </c>
       <c r="W15" s="95">
-        <f>W7/V7-1</f>
+        <f t="shared" si="7"/>
         <v>-0.19987914284386188</v>
       </c>
       <c r="X15" s="95">
-        <f>X7/W7-1</f>
+        <f t="shared" si="7"/>
         <v>0.21274618021263003</v>
       </c>
       <c r="Y15" s="95">
-        <f>Y7/X7-1</f>
+        <f t="shared" si="7"/>
         <v>0.36526946107784442</v>
       </c>
       <c r="Z15" s="96">
-        <f>Z7/Y7-1</f>
+        <f t="shared" si="7"/>
         <v>0.31147368421052635</v>
       </c>
       <c r="AA15" s="106">
@@ -13995,39 +13999,39 @@
       </c>
       <c r="C16" s="47"/>
       <c r="D16" s="95" t="e">
-        <f t="shared" ref="D16:L17" si="7">D8/C8-1</f>
+        <f t="shared" ref="D16:L17" si="9">D8/C8-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E16" s="95" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F16" s="95" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G16" s="96">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.68194919521469632</v>
       </c>
       <c r="H16" s="95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.54083912727047512</v>
       </c>
       <c r="I16" s="95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.52250454119029177</v>
       </c>
       <c r="J16" s="95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.46298827255655151</v>
       </c>
       <c r="K16" s="95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.37268205576329327</v>
       </c>
       <c r="L16" s="95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.28781589110243067</v>
       </c>
       <c r="O16" s="5"/>
@@ -14038,31 +14042,31 @@
       </c>
       <c r="S16" s="47"/>
       <c r="T16" s="95">
-        <f>T8/S8-1</f>
+        <f t="shared" si="7"/>
         <v>0.17124695493300846</v>
       </c>
       <c r="U16" s="95">
-        <f>U8/T8-1</f>
+        <f t="shared" si="7"/>
         <v>0.15628351369796234</v>
       </c>
       <c r="V16" s="95">
-        <f>V8/U8-1</f>
+        <f t="shared" si="7"/>
         <v>9.9269252388982654E-2</v>
       </c>
       <c r="W16" s="95">
-        <f>W8/V8-1</f>
+        <f t="shared" si="7"/>
         <v>5.0726119860912355E-2</v>
       </c>
       <c r="X16" s="95">
-        <f>X8/W8-1</f>
+        <f t="shared" si="7"/>
         <v>0.24622834339108435</v>
       </c>
       <c r="Y16" s="95">
-        <f>Y8/X8-1</f>
+        <f t="shared" si="7"/>
         <v>0.21671385336327242</v>
       </c>
       <c r="Z16" s="96">
-        <f>Z8/Y8-1</f>
+        <f t="shared" si="7"/>
         <v>0.20752960811374654</v>
       </c>
       <c r="AA16" s="95">
@@ -14079,19 +14083,19 @@
       </c>
       <c r="C17" s="47"/>
       <c r="D17" s="95" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E17" s="95" t="e">
-        <f t="shared" ref="E17" si="8">E9/D9-1</f>
+        <f t="shared" ref="E17" si="10">E9/D9-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F17" s="95" t="e">
-        <f t="shared" ref="F17" si="9">F9/E9-1</f>
+        <f t="shared" ref="F17" si="11">F9/E9-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G17" s="96">
-        <f t="shared" ref="G17" si="10">G9/F9-1</f>
+        <f t="shared" ref="G17" si="12">G9/F9-1</f>
         <v>0.45000326562602044</v>
       </c>
       <c r="H17" s="106">
@@ -14121,23 +14125,23 @@
         <v>0.14410828025477707</v>
       </c>
       <c r="U17" s="95">
-        <f t="shared" ref="U17:Y17" si="11">U9/T9-1</f>
+        <f t="shared" ref="U17:Y17" si="13">U9/T9-1</f>
         <v>-0.12990025516121551</v>
       </c>
       <c r="V17" s="95">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.31964809384164217</v>
       </c>
       <c r="W17" s="95">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.14080808080808072</v>
       </c>
       <c r="X17" s="95">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>2.5500265627766971E-2</v>
       </c>
       <c r="Y17" s="95">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>3.7989984458641768E-3</v>
       </c>
       <c r="Z17" s="96">
@@ -14157,39 +14161,39 @@
       </c>
       <c r="C18" s="47"/>
       <c r="D18" s="103">
-        <f t="shared" ref="D18:L18" si="12">D10/C10-1</f>
+        <f t="shared" ref="D18:L18" si="14">D10/C10-1</f>
         <v>2.2293230289069932E-3</v>
       </c>
       <c r="E18" s="103">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1.2585452658115224</v>
       </c>
       <c r="F18" s="103">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1.1420340763599355</v>
       </c>
       <c r="G18" s="104">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.65473535790094783</v>
       </c>
       <c r="H18" s="103">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.52121859052135355</v>
       </c>
       <c r="I18" s="103">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.51132721836262962</v>
       </c>
       <c r="J18" s="103">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.45343859941501496</v>
       </c>
       <c r="K18" s="103">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.3630510140948322</v>
       </c>
       <c r="L18" s="103">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.27789411511450002</v>
       </c>
       <c r="O18" s="5"/>
@@ -14200,35 +14204,35 @@
       </c>
       <c r="S18" s="47"/>
       <c r="T18" s="103">
-        <f t="shared" ref="T18:AA18" si="13">T10/S10-1</f>
+        <f t="shared" ref="T18:AA18" si="15">T10/S10-1</f>
         <v>0.16784287616511318</v>
       </c>
       <c r="U18" s="103">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.12111624194743742</v>
       </c>
       <c r="V18" s="103">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.12028679667437903</v>
       </c>
       <c r="W18" s="103">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>6.0846080522899637E-2</v>
       </c>
       <c r="X18" s="103">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.21956228740132211</v>
       </c>
       <c r="Y18" s="103">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.1950847279233765</v>
       </c>
       <c r="Z18" s="104">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.1979831784754944</v>
       </c>
       <c r="AA18" s="103">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.13585701157875407</v>
       </c>
       <c r="AB18" s="103"/>
@@ -14285,35 +14289,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="227" t="s">
+      <c r="C2" s="231" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="227"/>
-      <c r="E2" s="227"/>
-      <c r="F2" s="227"/>
-      <c r="G2" s="236"/>
-      <c r="H2" s="237" t="s">
+      <c r="D2" s="231"/>
+      <c r="E2" s="231"/>
+      <c r="F2" s="231"/>
+      <c r="G2" s="243"/>
+      <c r="H2" s="244" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="227"/>
-      <c r="J2" s="227"/>
-      <c r="K2" s="227"/>
-      <c r="L2" s="227"/>
-      <c r="P2" s="227" t="s">
+      <c r="I2" s="231"/>
+      <c r="J2" s="231"/>
+      <c r="K2" s="231"/>
+      <c r="L2" s="231"/>
+      <c r="P2" s="231" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="227"/>
-      <c r="R2" s="227"/>
-      <c r="S2" s="227"/>
-      <c r="T2" s="227"/>
-      <c r="U2" s="227"/>
-      <c r="V2" s="227"/>
-      <c r="W2" s="227"/>
-      <c r="X2" s="227" t="s">
+      <c r="Q2" s="231"/>
+      <c r="R2" s="231"/>
+      <c r="S2" s="231"/>
+      <c r="T2" s="231"/>
+      <c r="U2" s="231"/>
+      <c r="V2" s="231"/>
+      <c r="W2" s="231"/>
+      <c r="X2" s="231" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="227"/>
-      <c r="Z2" s="227"/>
+      <c r="Y2" s="231"/>
+      <c r="Z2" s="231"/>
       <c r="AB2" s="85" t="s">
         <v>107</v>
       </c>
@@ -14322,31 +14326,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="238" t="s">
+      <c r="C4" s="240" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="238"/>
-      <c r="E4" s="238"/>
-      <c r="F4" s="238"/>
-      <c r="G4" s="238"/>
-      <c r="H4" s="238"/>
-      <c r="I4" s="238"/>
-      <c r="J4" s="238"/>
-      <c r="K4" s="238"/>
-      <c r="L4" s="238"/>
-      <c r="P4" s="240" t="s">
+      <c r="D4" s="240"/>
+      <c r="E4" s="240"/>
+      <c r="F4" s="240"/>
+      <c r="G4" s="240"/>
+      <c r="H4" s="240"/>
+      <c r="I4" s="240"/>
+      <c r="J4" s="240"/>
+      <c r="K4" s="240"/>
+      <c r="L4" s="240"/>
+      <c r="P4" s="242" t="s">
         <v>108</v>
       </c>
-      <c r="Q4" s="240"/>
-      <c r="R4" s="240"/>
-      <c r="S4" s="240"/>
-      <c r="T4" s="240"/>
-      <c r="U4" s="240"/>
-      <c r="V4" s="240"/>
-      <c r="W4" s="240"/>
-      <c r="X4" s="240"/>
-      <c r="Y4" s="240"/>
-      <c r="Z4" s="240"/>
+      <c r="Q4" s="242"/>
+      <c r="R4" s="242"/>
+      <c r="S4" s="242"/>
+      <c r="T4" s="242"/>
+      <c r="U4" s="242"/>
+      <c r="V4" s="242"/>
+      <c r="W4" s="242"/>
+      <c r="X4" s="242"/>
+      <c r="Y4" s="242"/>
+      <c r="Z4" s="242"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -14541,32 +14545,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="238" t="s">
+      <c r="C9" s="240" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="238"/>
-      <c r="E9" s="238"/>
-      <c r="F9" s="238"/>
-      <c r="G9" s="238"/>
-      <c r="H9" s="238"/>
-      <c r="I9" s="238"/>
-      <c r="J9" s="238"/>
-      <c r="K9" s="238"/>
-      <c r="L9" s="238"/>
+      <c r="D9" s="240"/>
+      <c r="E9" s="240"/>
+      <c r="F9" s="240"/>
+      <c r="G9" s="240"/>
+      <c r="H9" s="240"/>
+      <c r="I9" s="240"/>
+      <c r="J9" s="240"/>
+      <c r="K9" s="240"/>
+      <c r="L9" s="240"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="240" t="s">
+      <c r="P9" s="242" t="s">
         <v>118</v>
       </c>
-      <c r="Q9" s="240"/>
-      <c r="R9" s="240"/>
-      <c r="S9" s="240"/>
-      <c r="T9" s="240"/>
-      <c r="U9" s="240"/>
-      <c r="V9" s="240"/>
-      <c r="W9" s="240"/>
-      <c r="X9" s="240"/>
-      <c r="Y9" s="240"/>
-      <c r="Z9" s="240"/>
+      <c r="Q9" s="242"/>
+      <c r="R9" s="242"/>
+      <c r="S9" s="242"/>
+      <c r="T9" s="242"/>
+      <c r="U9" s="242"/>
+      <c r="V9" s="242"/>
+      <c r="W9" s="242"/>
+      <c r="X9" s="242"/>
+      <c r="Y9" s="242"/>
+      <c r="Z9" s="242"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -15042,121 +15046,121 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="238" t="s">
+      <c r="C17" s="240" t="s">
         <v>120</v>
       </c>
-      <c r="D17" s="238"/>
-      <c r="E17" s="238"/>
-      <c r="F17" s="238"/>
-      <c r="G17" s="238"/>
-      <c r="H17" s="238"/>
-      <c r="I17" s="238"/>
-      <c r="J17" s="238"/>
-      <c r="K17" s="238"/>
-      <c r="L17" s="238"/>
-      <c r="P17" s="240" t="s">
+      <c r="D17" s="240"/>
+      <c r="E17" s="240"/>
+      <c r="F17" s="240"/>
+      <c r="G17" s="240"/>
+      <c r="H17" s="240"/>
+      <c r="I17" s="240"/>
+      <c r="J17" s="240"/>
+      <c r="K17" s="240"/>
+      <c r="L17" s="240"/>
+      <c r="P17" s="242" t="s">
         <v>120</v>
       </c>
-      <c r="Q17" s="240"/>
-      <c r="R17" s="240"/>
-      <c r="S17" s="240"/>
-      <c r="T17" s="240"/>
-      <c r="U17" s="240"/>
-      <c r="V17" s="240"/>
-      <c r="W17" s="240"/>
-      <c r="X17" s="240"/>
-      <c r="Y17" s="240"/>
-      <c r="Z17" s="240"/>
+      <c r="Q17" s="242"/>
+      <c r="R17" s="242"/>
+      <c r="S17" s="242"/>
+      <c r="T17" s="242"/>
+      <c r="U17" s="242"/>
+      <c r="V17" s="242"/>
+      <c r="W17" s="242"/>
+      <c r="X17" s="242"/>
+      <c r="Y17" s="242"/>
+      <c r="Z17" s="242"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="16" t="s">
         <v>121</v>
       </c>
       <c r="C18" s="12">
-        <f>C5</f>
+        <f t="shared" ref="C18:L18" si="6">C5</f>
         <v>2022</v>
       </c>
       <c r="D18" s="12">
-        <f>D5</f>
+        <f t="shared" si="6"/>
         <v>2023</v>
       </c>
       <c r="E18" s="12">
-        <f>E5</f>
+        <f t="shared" si="6"/>
         <v>2024</v>
       </c>
       <c r="F18" s="12">
-        <f>F5</f>
+        <f t="shared" si="6"/>
         <v>2025</v>
       </c>
       <c r="G18" s="12">
-        <f>G5</f>
+        <f t="shared" si="6"/>
         <v>2026</v>
       </c>
       <c r="H18" s="12">
-        <f>H5</f>
+        <f t="shared" si="6"/>
         <v>2027</v>
       </c>
       <c r="I18" s="12">
-        <f>I5</f>
+        <f t="shared" si="6"/>
         <v>2028</v>
       </c>
       <c r="J18" s="12">
-        <f>J5</f>
+        <f t="shared" si="6"/>
         <v>2029</v>
       </c>
       <c r="K18" s="12">
-        <f>K5</f>
+        <f t="shared" si="6"/>
         <v>2030</v>
       </c>
       <c r="L18" s="12">
-        <f>L5</f>
+        <f t="shared" si="6"/>
         <v>2031</v>
       </c>
       <c r="O18" s="16" t="s">
         <v>121</v>
       </c>
       <c r="P18" s="12" t="str">
-        <f>P5</f>
+        <f t="shared" ref="P18:Z18" si="7">P5</f>
         <v>Q2 2025</v>
       </c>
       <c r="Q18" s="12" t="str">
-        <f>Q5</f>
+        <f t="shared" si="7"/>
         <v>Q3 2025</v>
       </c>
       <c r="R18" s="12" t="str">
-        <f>R5</f>
+        <f t="shared" si="7"/>
         <v>Q4 2025</v>
       </c>
       <c r="S18" s="12" t="str">
-        <f>S5</f>
+        <f t="shared" si="7"/>
         <v>Q1 2026</v>
       </c>
       <c r="T18" s="12" t="str">
-        <f>T5</f>
+        <f t="shared" si="7"/>
         <v>Q2 2026</v>
       </c>
       <c r="U18" s="12" t="str">
-        <f>U5</f>
+        <f t="shared" si="7"/>
         <v>Q3 2026</v>
       </c>
       <c r="V18" s="12" t="str">
-        <f>V5</f>
+        <f t="shared" si="7"/>
         <v>Q4 2026</v>
       </c>
       <c r="W18" s="12" t="str">
-        <f>W5</f>
+        <f t="shared" si="7"/>
         <v>Q1 2027</v>
       </c>
       <c r="X18" s="12" t="str">
-        <f>X5</f>
+        <f t="shared" si="7"/>
         <v>FQ1</v>
       </c>
       <c r="Y18" s="12" t="str">
-        <f>Y5</f>
+        <f t="shared" si="7"/>
         <v>FQ2</v>
       </c>
       <c r="Z18" s="12" t="str">
-        <f>Z5</f>
+        <f t="shared" si="7"/>
         <v>FQ3</v>
       </c>
     </row>
@@ -15166,23 +15170,23 @@
         <v>COGS</v>
       </c>
       <c r="C19" s="103">
-        <f>C11/C$6</f>
+        <f t="shared" ref="C19:G21" si="8">C11/C$6</f>
         <v>0.35070966783086871</v>
       </c>
       <c r="D19" s="103">
-        <f>D11/D$6</f>
+        <f t="shared" si="8"/>
         <v>0.43071105509008673</v>
       </c>
       <c r="E19" s="103">
-        <f>E11/E$6</f>
+        <f t="shared" si="8"/>
         <v>0.27282426709563046</v>
       </c>
       <c r="F19" s="103">
-        <f>F11/F$6</f>
+        <f t="shared" si="8"/>
         <v>0.25011302941830083</v>
       </c>
       <c r="G19" s="104">
-        <f>G11/G$6</f>
+        <f t="shared" si="8"/>
         <v>0.28931915642452927</v>
       </c>
       <c r="H19" s="97">
@@ -15205,35 +15209,35 @@
         <v>COGS</v>
       </c>
       <c r="P19" s="103">
-        <f>P11/P$6</f>
+        <f t="shared" ref="P19:W21" si="9">P11/P$6</f>
         <v>0.24853528628495339</v>
       </c>
       <c r="Q19" s="103">
-        <f>Q11/Q$6</f>
+        <f t="shared" si="9"/>
         <v>0.25443247249301637</v>
       </c>
       <c r="R19" s="103">
-        <f>R11/R$6</f>
+        <f t="shared" si="9"/>
         <v>0.26971091505428291</v>
       </c>
       <c r="S19" s="103">
-        <f>S11/S$6</f>
+        <f t="shared" si="9"/>
         <v>0.39476192637646951</v>
       </c>
       <c r="T19" s="103">
-        <f>T11/T$6</f>
+        <f t="shared" si="9"/>
         <v>0.27576321588259206</v>
       </c>
       <c r="U19" s="103">
-        <f>U11/U$6</f>
+        <f t="shared" si="9"/>
         <v>0.2658842928814511</v>
       </c>
       <c r="V19" s="103">
-        <f>V11/V$6</f>
+        <f t="shared" si="9"/>
         <v>0.25003302655334891</v>
       </c>
       <c r="W19" s="104">
-        <f>W11/W$6</f>
+        <f t="shared" si="9"/>
         <v>0.25066470624272497</v>
       </c>
       <c r="X19" s="97">
@@ -15248,23 +15252,23 @@
         <v>R&amp;D</v>
       </c>
       <c r="C20" s="95">
-        <f>C12/C$6</f>
+        <f t="shared" si="8"/>
         <v>0.19573456193802483</v>
       </c>
       <c r="D20" s="95">
-        <f>D12/D$6</f>
+        <f t="shared" si="8"/>
         <v>0.27207681471046191</v>
       </c>
       <c r="E20" s="95">
-        <f>E12/E$6</f>
+        <f t="shared" si="8"/>
         <v>0.14239519385443683</v>
       </c>
       <c r="F20" s="95">
-        <f>F12/F$6</f>
+        <f t="shared" si="8"/>
         <v>9.8960129351632606E-2</v>
       </c>
       <c r="G20" s="96">
-        <f>G12/G$6</f>
+        <f t="shared" si="8"/>
         <v>8.5658846520760584E-2</v>
       </c>
       <c r="H20" s="97">
@@ -15287,35 +15291,35 @@
         <v>R&amp;D</v>
       </c>
       <c r="P20" s="95">
-        <f>P12/P$6</f>
+        <f t="shared" si="9"/>
         <v>0.10286284953395473</v>
       </c>
       <c r="Q20" s="95">
-        <f>Q12/Q$6</f>
+        <f t="shared" si="9"/>
         <v>9.6630750812382413E-2</v>
       </c>
       <c r="R20" s="95">
-        <f>R12/R$6</f>
+        <f t="shared" si="9"/>
         <v>9.4429330553507412E-2</v>
       </c>
       <c r="S20" s="95">
-        <f>S12/S$6</f>
+        <f t="shared" si="9"/>
         <v>9.0531523761971766E-2</v>
       </c>
       <c r="T20" s="95">
-        <f>T12/T$6</f>
+        <f t="shared" si="9"/>
         <v>9.1799841687525405E-2</v>
       </c>
       <c r="U20" s="95">
-        <f>U12/U$6</f>
+        <f t="shared" si="9"/>
         <v>8.2535171736308463E-2</v>
       </c>
       <c r="V20" s="95">
-        <f>V12/V$6</f>
+        <f t="shared" si="9"/>
         <v>8.0907716470709115E-2</v>
       </c>
       <c r="W20" s="96">
-        <f>W12/W$6</f>
+        <f t="shared" si="9"/>
         <v>7.7448998345892306E-2</v>
       </c>
       <c r="X20" s="97">
@@ -15330,23 +15334,23 @@
         <v>SG&amp;A</v>
       </c>
       <c r="C21" s="95">
-        <f>C13/C$6</f>
+        <f t="shared" si="8"/>
         <v>8.0478561343538674E-2</v>
       </c>
       <c r="D21" s="95">
-        <f>D13/D$6</f>
+        <f t="shared" si="8"/>
         <v>9.0457477570994288E-2</v>
       </c>
       <c r="E21" s="95">
-        <f>E13/E$6</f>
+        <f t="shared" si="8"/>
         <v>4.3563901382095135E-2</v>
       </c>
       <c r="F21" s="95">
-        <f>F13/F$6</f>
+        <f t="shared" si="8"/>
         <v>2.6751572833091947E-2</v>
       </c>
       <c r="G21" s="96">
-        <f>G13/G$6</f>
+        <f t="shared" si="8"/>
         <v>2.1205160740582946E-2</v>
       </c>
       <c r="H21" s="97">
@@ -15369,35 +15373,35 @@
         <v>SG&amp;A</v>
       </c>
       <c r="P21" s="95">
-        <f>P13/P$6</f>
+        <f t="shared" si="9"/>
         <v>2.8029294274300932E-2</v>
       </c>
       <c r="Q21" s="95">
-        <f>Q13/Q$6</f>
+        <f t="shared" si="9"/>
         <v>2.5568667692833932E-2</v>
       </c>
       <c r="R21" s="95">
-        <f>R13/R$6</f>
+        <f t="shared" si="9"/>
         <v>2.478960616307747E-2</v>
       </c>
       <c r="S21" s="95">
-        <f>S13/S$6</f>
+        <f t="shared" si="9"/>
         <v>2.3625800009078116E-2</v>
       </c>
       <c r="T21" s="95">
-        <f>T13/T$6</f>
+        <f t="shared" si="9"/>
         <v>2.4003594121044861E-2</v>
       </c>
       <c r="U21" s="95">
-        <f>U13/U$6</f>
+        <f t="shared" si="9"/>
         <v>1.9892642879696873E-2</v>
       </c>
       <c r="V21" s="95">
-        <f>V13/V$6</f>
+        <f t="shared" si="9"/>
         <v>1.88177961747912E-2</v>
       </c>
       <c r="W21" s="96">
-        <f>W13/W$6</f>
+        <f t="shared" si="9"/>
         <v>1.5928444526128776E-2</v>
       </c>
       <c r="X21" s="97">
@@ -15408,7 +15412,7 @@
     </row>
     <row r="22" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B22" s="16" t="str">
-        <f t="shared" ref="B22" si="6">B14</f>
+        <f t="shared" ref="B22" si="10">B14</f>
         <v>OpEx</v>
       </c>
       <c r="C22" s="103">
@@ -15416,79 +15420,79 @@
         <v>0.2762131232815635</v>
       </c>
       <c r="D22" s="103">
-        <f t="shared" ref="D22:L22" si="7">D14/D$6</f>
+        <f t="shared" ref="D22:L22" si="11">D14/D$6</f>
         <v>0.41269370504930675</v>
       </c>
       <c r="E22" s="103">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.18595909523653195</v>
       </c>
       <c r="F22" s="103">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.12571170218472455</v>
       </c>
       <c r="G22" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.10686400726134353</v>
       </c>
       <c r="H22" s="103">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.12300000000000003</v>
       </c>
       <c r="I22" s="103">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.12300000000000001</v>
       </c>
       <c r="J22" s="103">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.12300000000000001</v>
       </c>
       <c r="K22" s="103">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.123</v>
       </c>
       <c r="L22" s="103">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.12300000000000001</v>
       </c>
       <c r="O22" s="16" t="str">
-        <f t="shared" ref="O22" si="8">O14</f>
+        <f t="shared" ref="O22" si="12">O14</f>
         <v>OpEx</v>
       </c>
       <c r="P22" s="103">
-        <f t="shared" ref="P22:V22" si="9">P14/P$6</f>
+        <f t="shared" ref="P22:V22" si="13">P14/P$6</f>
         <v>0.13089214380825565</v>
       </c>
       <c r="Q22" s="103">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0.12219941850521635</v>
       </c>
       <c r="R22" s="103">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0.11921893671658489</v>
       </c>
       <c r="S22" s="103">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0.11415732377104988</v>
       </c>
       <c r="T22" s="103">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0.11580343580857026</v>
       </c>
       <c r="U22" s="103">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0.10242781461600534</v>
       </c>
       <c r="V22" s="103">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>9.9725512645500322E-2</v>
       </c>
       <c r="W22" s="104">
-        <f t="shared" ref="W22:X22" si="10">W14/W$6</f>
+        <f t="shared" ref="W22:X22" si="14">W14/W$6</f>
         <v>9.3377442872021071E-2</v>
       </c>
       <c r="X22" s="103">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>9.0999999999999998E-2</v>
       </c>
       <c r="Y22" s="16"/>
@@ -15544,60 +15548,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="227" t="s">
+      <c r="C3" s="231" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="227"/>
-      <c r="E3" s="227"/>
-      <c r="F3" s="227"/>
-      <c r="G3" s="236"/>
-      <c r="H3" s="237" t="s">
+      <c r="D3" s="231"/>
+      <c r="E3" s="231"/>
+      <c r="F3" s="231"/>
+      <c r="G3" s="243"/>
+      <c r="H3" s="244" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="227"/>
-      <c r="J3" s="227"/>
-      <c r="K3" s="227"/>
-      <c r="L3" s="227"/>
-      <c r="P3" s="241"/>
-      <c r="Q3" s="241"/>
-      <c r="R3" s="241"/>
-      <c r="S3" s="241"/>
-      <c r="T3" s="241"/>
-      <c r="U3" s="241"/>
-      <c r="V3" s="241"/>
-      <c r="W3" s="241"/>
-      <c r="X3" s="241"/>
-      <c r="Y3" s="241"/>
-      <c r="Z3" s="241"/>
+      <c r="I3" s="231"/>
+      <c r="J3" s="231"/>
+      <c r="K3" s="231"/>
+      <c r="L3" s="231"/>
+      <c r="P3" s="245"/>
+      <c r="Q3" s="245"/>
+      <c r="R3" s="245"/>
+      <c r="S3" s="245"/>
+      <c r="T3" s="245"/>
+      <c r="U3" s="245"/>
+      <c r="V3" s="245"/>
+      <c r="W3" s="245"/>
+      <c r="X3" s="245"/>
+      <c r="Y3" s="245"/>
+      <c r="Z3" s="245"/>
       <c r="AB3" s="110"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="238" t="s">
+      <c r="C5" s="240" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="238"/>
-      <c r="E5" s="238"/>
-      <c r="F5" s="238"/>
-      <c r="G5" s="238"/>
-      <c r="H5" s="238"/>
-      <c r="I5" s="238"/>
-      <c r="J5" s="238"/>
-      <c r="K5" s="238"/>
-      <c r="L5" s="238"/>
-      <c r="P5" s="241"/>
-      <c r="Q5" s="241"/>
-      <c r="R5" s="241"/>
-      <c r="S5" s="241"/>
-      <c r="T5" s="241"/>
-      <c r="U5" s="241"/>
-      <c r="V5" s="241"/>
-      <c r="W5" s="241"/>
-      <c r="X5" s="241"/>
-      <c r="Y5" s="241"/>
-      <c r="Z5" s="241"/>
+      <c r="D5" s="240"/>
+      <c r="E5" s="240"/>
+      <c r="F5" s="240"/>
+      <c r="G5" s="240"/>
+      <c r="H5" s="240"/>
+      <c r="I5" s="240"/>
+      <c r="J5" s="240"/>
+      <c r="K5" s="240"/>
+      <c r="L5" s="240"/>
+      <c r="P5" s="245"/>
+      <c r="Q5" s="245"/>
+      <c r="R5" s="245"/>
+      <c r="S5" s="245"/>
+      <c r="T5" s="245"/>
+      <c r="U5" s="245"/>
+      <c r="V5" s="245"/>
+      <c r="W5" s="245"/>
+      <c r="X5" s="245"/>
+      <c r="Y5" s="245"/>
+      <c r="Z5" s="245"/>
       <c r="AB5" s="111"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -15783,30 +15787,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="238" t="s">
+      <c r="C11" s="240" t="s">
         <v>124</v>
       </c>
-      <c r="D11" s="238"/>
-      <c r="E11" s="238"/>
-      <c r="F11" s="238"/>
-      <c r="G11" s="238"/>
-      <c r="H11" s="238"/>
-      <c r="I11" s="238"/>
-      <c r="J11" s="238"/>
-      <c r="K11" s="238"/>
-      <c r="L11" s="238"/>
+      <c r="D11" s="240"/>
+      <c r="E11" s="240"/>
+      <c r="F11" s="240"/>
+      <c r="G11" s="240"/>
+      <c r="H11" s="240"/>
+      <c r="I11" s="240"/>
+      <c r="J11" s="240"/>
+      <c r="K11" s="240"/>
+      <c r="L11" s="240"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="241"/>
-      <c r="Q11" s="241"/>
-      <c r="R11" s="241"/>
-      <c r="S11" s="241"/>
-      <c r="T11" s="241"/>
-      <c r="U11" s="241"/>
-      <c r="V11" s="241"/>
-      <c r="W11" s="241"/>
-      <c r="X11" s="241"/>
-      <c r="Y11" s="241"/>
-      <c r="Z11" s="241"/>
+      <c r="P11" s="245"/>
+      <c r="Q11" s="245"/>
+      <c r="R11" s="245"/>
+      <c r="S11" s="245"/>
+      <c r="T11" s="245"/>
+      <c r="U11" s="245"/>
+      <c r="V11" s="245"/>
+      <c r="W11" s="245"/>
+      <c r="X11" s="245"/>
+      <c r="Y11" s="245"/>
+      <c r="Z11" s="245"/>
       <c r="AB11" s="111"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -16048,18 +16052,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="238" t="s">
+      <c r="C18" s="240" t="s">
         <v>129</v>
       </c>
-      <c r="D18" s="238"/>
-      <c r="E18" s="238"/>
-      <c r="F18" s="238"/>
-      <c r="G18" s="238"/>
-      <c r="H18" s="238"/>
-      <c r="I18" s="238"/>
-      <c r="J18" s="238"/>
-      <c r="K18" s="238"/>
-      <c r="L18" s="238"/>
+      <c r="D18" s="240"/>
+      <c r="E18" s="240"/>
+      <c r="F18" s="240"/>
+      <c r="G18" s="240"/>
+      <c r="H18" s="240"/>
+      <c r="I18" s="240"/>
+      <c r="J18" s="240"/>
+      <c r="K18" s="240"/>
+      <c r="L18" s="240"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -16272,23 +16276,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="241"/>
-      <c r="C25" s="241"/>
+      <c r="B25" s="245"/>
+      <c r="C25" s="245"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="110"/>
-      <c r="C26" s="238" t="s">
+      <c r="C26" s="240" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="238"/>
-      <c r="E26" s="238"/>
-      <c r="F26" s="238"/>
-      <c r="G26" s="238"/>
-      <c r="H26" s="238"/>
-      <c r="I26" s="238"/>
-      <c r="J26" s="238"/>
-      <c r="K26" s="238"/>
-      <c r="L26" s="238"/>
+      <c r="D26" s="240"/>
+      <c r="E26" s="240"/>
+      <c r="F26" s="240"/>
+      <c r="G26" s="240"/>
+      <c r="H26" s="240"/>
+      <c r="I26" s="240"/>
+      <c r="J26" s="240"/>
+      <c r="K26" s="240"/>
+      <c r="L26" s="240"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -16480,18 +16484,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="110"/>
-      <c r="C33" s="238" t="s">
+      <c r="C33" s="240" t="s">
         <v>139</v>
       </c>
-      <c r="D33" s="238"/>
-      <c r="E33" s="238"/>
-      <c r="F33" s="238"/>
-      <c r="G33" s="238"/>
-      <c r="H33" s="238"/>
-      <c r="I33" s="238"/>
-      <c r="J33" s="238"/>
-      <c r="K33" s="238"/>
-      <c r="L33" s="238"/>
+      <c r="D33" s="240"/>
+      <c r="E33" s="240"/>
+      <c r="F33" s="240"/>
+      <c r="G33" s="240"/>
+      <c r="H33" s="240"/>
+      <c r="I33" s="240"/>
+      <c r="J33" s="240"/>
+      <c r="K33" s="240"/>
+      <c r="L33" s="240"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -16675,18 +16679,18 @@
       <c r="C39" s="126"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="238" t="s">
+      <c r="C40" s="240" t="s">
         <v>142</v>
       </c>
-      <c r="D40" s="238"/>
-      <c r="E40" s="238"/>
-      <c r="F40" s="238"/>
-      <c r="G40" s="238"/>
-      <c r="H40" s="238"/>
-      <c r="I40" s="238"/>
-      <c r="J40" s="238"/>
-      <c r="K40" s="238"/>
-      <c r="L40" s="238"/>
+      <c r="D40" s="240"/>
+      <c r="E40" s="240"/>
+      <c r="F40" s="240"/>
+      <c r="G40" s="240"/>
+      <c r="H40" s="240"/>
+      <c r="I40" s="240"/>
+      <c r="J40" s="240"/>
+      <c r="K40" s="240"/>
+      <c r="L40" s="240"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -16950,12 +16954,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -16963,6 +16961,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -17000,60 +17004,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="227" t="s">
+      <c r="C2" s="231" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="227"/>
-      <c r="E2" s="227"/>
-      <c r="F2" s="227"/>
-      <c r="G2" s="236"/>
-      <c r="H2" s="237" t="s">
+      <c r="D2" s="231"/>
+      <c r="E2" s="231"/>
+      <c r="F2" s="231"/>
+      <c r="G2" s="243"/>
+      <c r="H2" s="244" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="227"/>
-      <c r="J2" s="227"/>
-      <c r="K2" s="227"/>
-      <c r="L2" s="227"/>
-      <c r="S2" s="241"/>
-      <c r="T2" s="241"/>
-      <c r="U2" s="241"/>
-      <c r="V2" s="241"/>
-      <c r="W2" s="241"/>
-      <c r="X2" s="241"/>
-      <c r="Y2" s="241"/>
-      <c r="Z2" s="241"/>
-      <c r="AA2" s="241"/>
-      <c r="AB2" s="241"/>
-      <c r="AC2" s="241"/>
+      <c r="I2" s="231"/>
+      <c r="J2" s="231"/>
+      <c r="K2" s="231"/>
+      <c r="L2" s="231"/>
+      <c r="S2" s="245"/>
+      <c r="T2" s="245"/>
+      <c r="U2" s="245"/>
+      <c r="V2" s="245"/>
+      <c r="W2" s="245"/>
+      <c r="X2" s="245"/>
+      <c r="Y2" s="245"/>
+      <c r="Z2" s="245"/>
+      <c r="AA2" s="245"/>
+      <c r="AB2" s="245"/>
+      <c r="AC2" s="245"/>
       <c r="AE2" s="110"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="238" t="s">
+      <c r="C4" s="240" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="238"/>
-      <c r="E4" s="238"/>
-      <c r="F4" s="238"/>
-      <c r="G4" s="238"/>
-      <c r="H4" s="238"/>
-      <c r="I4" s="238"/>
-      <c r="J4" s="238"/>
-      <c r="K4" s="238"/>
-      <c r="L4" s="238"/>
-      <c r="S4" s="241"/>
-      <c r="T4" s="241"/>
-      <c r="U4" s="241"/>
-      <c r="V4" s="241"/>
-      <c r="W4" s="241"/>
-      <c r="X4" s="241"/>
-      <c r="Y4" s="241"/>
-      <c r="Z4" s="241"/>
-      <c r="AA4" s="241"/>
-      <c r="AB4" s="241"/>
-      <c r="AC4" s="241"/>
+      <c r="D4" s="240"/>
+      <c r="E4" s="240"/>
+      <c r="F4" s="240"/>
+      <c r="G4" s="240"/>
+      <c r="H4" s="240"/>
+      <c r="I4" s="240"/>
+      <c r="J4" s="240"/>
+      <c r="K4" s="240"/>
+      <c r="L4" s="240"/>
+      <c r="S4" s="245"/>
+      <c r="T4" s="245"/>
+      <c r="U4" s="245"/>
+      <c r="V4" s="245"/>
+      <c r="W4" s="245"/>
+      <c r="X4" s="245"/>
+      <c r="Y4" s="245"/>
+      <c r="Z4" s="245"/>
+      <c r="AA4" s="245"/>
+      <c r="AB4" s="245"/>
+      <c r="AC4" s="245"/>
       <c r="AE4" s="111"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -17416,18 +17420,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="238" t="s">
+      <c r="C13" s="240" t="s">
         <v>150</v>
       </c>
-      <c r="D13" s="238"/>
-      <c r="E13" s="238"/>
-      <c r="F13" s="238"/>
-      <c r="G13" s="238"/>
-      <c r="H13" s="238"/>
-      <c r="I13" s="238"/>
-      <c r="J13" s="238"/>
-      <c r="K13" s="238"/>
-      <c r="L13" s="238"/>
+      <c r="D13" s="240"/>
+      <c r="E13" s="240"/>
+      <c r="F13" s="240"/>
+      <c r="G13" s="240"/>
+      <c r="H13" s="240"/>
+      <c r="I13" s="240"/>
+      <c r="J13" s="240"/>
+      <c r="K13" s="240"/>
+      <c r="L13" s="240"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -17520,18 +17524,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="238" t="s">
+      <c r="C18" s="240" t="s">
         <v>151</v>
       </c>
-      <c r="D18" s="238"/>
-      <c r="E18" s="238"/>
-      <c r="F18" s="238"/>
-      <c r="G18" s="238"/>
-      <c r="H18" s="238"/>
-      <c r="I18" s="238"/>
-      <c r="J18" s="238"/>
-      <c r="K18" s="238"/>
-      <c r="L18" s="238"/>
+      <c r="D18" s="240"/>
+      <c r="E18" s="240"/>
+      <c r="F18" s="240"/>
+      <c r="G18" s="240"/>
+      <c r="H18" s="240"/>
+      <c r="I18" s="240"/>
+      <c r="J18" s="240"/>
+      <c r="K18" s="240"/>
+      <c r="L18" s="240"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17723,18 +17727,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="238" t="s">
+      <c r="C25" s="240" t="s">
         <v>154</v>
       </c>
-      <c r="D25" s="238"/>
-      <c r="E25" s="238"/>
-      <c r="F25" s="238"/>
-      <c r="G25" s="238"/>
-      <c r="H25" s="238"/>
-      <c r="I25" s="238"/>
-      <c r="J25" s="238"/>
-      <c r="K25" s="238"/>
-      <c r="L25" s="238"/>
+      <c r="D25" s="240"/>
+      <c r="E25" s="240"/>
+      <c r="F25" s="240"/>
+      <c r="G25" s="240"/>
+      <c r="H25" s="240"/>
+      <c r="I25" s="240"/>
+      <c r="J25" s="240"/>
+      <c r="K25" s="240"/>
+      <c r="L25" s="240"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -17872,22 +17876,22 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="238" t="s">
+      <c r="C31" s="240" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="238"/>
-      <c r="E31" s="238"/>
-      <c r="F31" s="238"/>
-      <c r="G31" s="238"/>
-      <c r="H31" s="238"/>
-      <c r="I31" s="238"/>
-      <c r="J31" s="238"/>
-      <c r="K31" s="238"/>
-      <c r="L31" s="238"/>
+      <c r="D31" s="240"/>
+      <c r="E31" s="240"/>
+      <c r="F31" s="240"/>
+      <c r="G31" s="240"/>
+      <c r="H31" s="240"/>
+      <c r="I31" s="240"/>
+      <c r="J31" s="240"/>
+      <c r="K31" s="240"/>
+      <c r="L31" s="240"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C32" s="12">
         <f>C5</f>
@@ -18022,16 +18026,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -18094,10 +18098,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="227" t="s">
+      <c r="B4" s="231" t="s">
         <v>159</v>
       </c>
-      <c r="C4" s="227"/>
+      <c r="C4" s="231"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -18182,10 +18186,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="227" t="s">
+      <c r="B15" s="231" t="s">
         <v>166</v>
       </c>
-      <c r="C15" s="227"/>
+      <c r="C15" s="231"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -18282,60 +18286,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="227" t="s">
+      <c r="C3" s="231" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="227"/>
-      <c r="E3" s="227"/>
-      <c r="F3" s="227"/>
-      <c r="G3" s="236"/>
-      <c r="H3" s="237" t="s">
+      <c r="D3" s="231"/>
+      <c r="E3" s="231"/>
+      <c r="F3" s="231"/>
+      <c r="G3" s="243"/>
+      <c r="H3" s="244" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="227"/>
-      <c r="J3" s="227"/>
-      <c r="K3" s="227"/>
-      <c r="L3" s="227"/>
-      <c r="P3" s="241"/>
-      <c r="Q3" s="241"/>
-      <c r="R3" s="241"/>
-      <c r="S3" s="241"/>
-      <c r="T3" s="241"/>
-      <c r="U3" s="241"/>
-      <c r="V3" s="241"/>
-      <c r="W3" s="241"/>
-      <c r="X3" s="241"/>
-      <c r="Y3" s="241"/>
-      <c r="Z3" s="241"/>
+      <c r="I3" s="231"/>
+      <c r="J3" s="231"/>
+      <c r="K3" s="231"/>
+      <c r="L3" s="231"/>
+      <c r="P3" s="245"/>
+      <c r="Q3" s="245"/>
+      <c r="R3" s="245"/>
+      <c r="S3" s="245"/>
+      <c r="T3" s="245"/>
+      <c r="U3" s="245"/>
+      <c r="V3" s="245"/>
+      <c r="W3" s="245"/>
+      <c r="X3" s="245"/>
+      <c r="Y3" s="245"/>
+      <c r="Z3" s="245"/>
       <c r="AB3" s="110"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="238" t="s">
+      <c r="C5" s="240" t="s">
         <v>173</v>
       </c>
-      <c r="D5" s="238"/>
-      <c r="E5" s="238"/>
-      <c r="F5" s="238"/>
-      <c r="G5" s="238"/>
-      <c r="H5" s="238"/>
-      <c r="I5" s="238"/>
-      <c r="J5" s="238"/>
-      <c r="K5" s="238"/>
-      <c r="L5" s="238"/>
-      <c r="P5" s="241"/>
-      <c r="Q5" s="241"/>
-      <c r="R5" s="241"/>
-      <c r="S5" s="241"/>
-      <c r="T5" s="241"/>
-      <c r="U5" s="241"/>
-      <c r="V5" s="241"/>
-      <c r="W5" s="241"/>
-      <c r="X5" s="241"/>
-      <c r="Y5" s="241"/>
-      <c r="Z5" s="241"/>
+      <c r="D5" s="240"/>
+      <c r="E5" s="240"/>
+      <c r="F5" s="240"/>
+      <c r="G5" s="240"/>
+      <c r="H5" s="240"/>
+      <c r="I5" s="240"/>
+      <c r="J5" s="240"/>
+      <c r="K5" s="240"/>
+      <c r="L5" s="240"/>
+      <c r="P5" s="245"/>
+      <c r="Q5" s="245"/>
+      <c r="R5" s="245"/>
+      <c r="S5" s="245"/>
+      <c r="T5" s="245"/>
+      <c r="U5" s="245"/>
+      <c r="V5" s="245"/>
+      <c r="W5" s="245"/>
+      <c r="X5" s="245"/>
+      <c r="Y5" s="245"/>
+      <c r="Z5" s="245"/>
       <c r="AB5" s="111"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -18533,7 +18537,7 @@
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C10" s="139"/>
       <c r="D10" s="139"/>
@@ -18581,10 +18585,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="227" t="s">
+      <c r="B13" s="231" t="s">
         <v>177</v>
       </c>
-      <c r="C13" s="227"/>
+      <c r="C13" s="231"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -18604,10 +18608,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="227" t="s">
+      <c r="B18" s="231" t="s">
         <v>179</v>
       </c>
-      <c r="C18" s="227"/>
+      <c r="C18" s="231"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -18721,37 +18725,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="227" t="s">
+      <c r="C2" s="231" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="227"/>
-      <c r="E2" s="227"/>
-      <c r="F2" s="227"/>
-      <c r="G2" s="236"/>
-      <c r="H2" s="237" t="s">
+      <c r="D2" s="231"/>
+      <c r="E2" s="231"/>
+      <c r="F2" s="231"/>
+      <c r="G2" s="243"/>
+      <c r="H2" s="244" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="227"/>
-      <c r="J2" s="227"/>
-      <c r="K2" s="227"/>
-      <c r="L2" s="227"/>
+      <c r="I2" s="231"/>
+      <c r="J2" s="231"/>
+      <c r="K2" s="231"/>
+      <c r="L2" s="231"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="238" t="s">
+      <c r="C4" s="240" t="s">
         <v>187</v>
       </c>
-      <c r="D4" s="238"/>
-      <c r="E4" s="238"/>
-      <c r="F4" s="238"/>
-      <c r="G4" s="238"/>
-      <c r="H4" s="238"/>
-      <c r="I4" s="238"/>
-      <c r="J4" s="238"/>
-      <c r="K4" s="238"/>
-      <c r="L4" s="238"/>
+      <c r="D4" s="240"/>
+      <c r="E4" s="240"/>
+      <c r="F4" s="240"/>
+      <c r="G4" s="240"/>
+      <c r="H4" s="240"/>
+      <c r="I4" s="240"/>
+      <c r="J4" s="240"/>
+      <c r="K4" s="240"/>
+      <c r="L4" s="240"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -18940,18 +18944,18 @@
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="238" t="s">
+      <c r="C10" s="240" t="s">
         <v>114</v>
       </c>
-      <c r="D10" s="238"/>
-      <c r="E10" s="238"/>
-      <c r="F10" s="238"/>
-      <c r="G10" s="238"/>
-      <c r="H10" s="238"/>
-      <c r="I10" s="238"/>
-      <c r="J10" s="238"/>
-      <c r="K10" s="238"/>
-      <c r="L10" s="238"/>
+      <c r="D10" s="240"/>
+      <c r="E10" s="240"/>
+      <c r="F10" s="240"/>
+      <c r="G10" s="240"/>
+      <c r="H10" s="240"/>
+      <c r="I10" s="240"/>
+      <c r="J10" s="240"/>
+      <c r="K10" s="240"/>
+      <c r="L10" s="240"/>
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -19145,18 +19149,18 @@
       <c r="N15" s="91"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="238" t="s">
+      <c r="C16" s="240" t="s">
         <v>189</v>
       </c>
-      <c r="D16" s="238"/>
-      <c r="E16" s="238"/>
-      <c r="F16" s="238"/>
-      <c r="G16" s="238"/>
-      <c r="H16" s="238"/>
-      <c r="I16" s="238"/>
-      <c r="J16" s="238"/>
-      <c r="K16" s="238"/>
-      <c r="L16" s="238"/>
+      <c r="D16" s="240"/>
+      <c r="E16" s="240"/>
+      <c r="F16" s="240"/>
+      <c r="G16" s="240"/>
+      <c r="H16" s="240"/>
+      <c r="I16" s="240"/>
+      <c r="J16" s="240"/>
+      <c r="K16" s="240"/>
+      <c r="L16" s="240"/>
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -19290,18 +19294,18 @@
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="238" t="s">
+      <c r="C21" s="240" t="s">
         <v>192</v>
       </c>
-      <c r="D21" s="238"/>
-      <c r="E21" s="238"/>
-      <c r="F21" s="238"/>
-      <c r="G21" s="238"/>
-      <c r="H21" s="238"/>
-      <c r="I21" s="238"/>
-      <c r="J21" s="238"/>
-      <c r="K21" s="238"/>
-      <c r="L21" s="238"/>
+      <c r="D21" s="240"/>
+      <c r="E21" s="240"/>
+      <c r="F21" s="240"/>
+      <c r="G21" s="240"/>
+      <c r="H21" s="240"/>
+      <c r="I21" s="240"/>
+      <c r="J21" s="240"/>
+      <c r="K21" s="240"/>
+      <c r="L21" s="240"/>
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -19385,18 +19389,18 @@
       <c r="N25" s="91"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="238" t="s">
+      <c r="C26" s="240" t="s">
         <v>193</v>
       </c>
-      <c r="D26" s="238"/>
-      <c r="E26" s="238"/>
-      <c r="F26" s="238"/>
-      <c r="G26" s="238"/>
-      <c r="H26" s="238"/>
-      <c r="I26" s="238"/>
-      <c r="J26" s="238"/>
-      <c r="K26" s="238"/>
-      <c r="L26" s="238"/>
+      <c r="D26" s="240"/>
+      <c r="E26" s="240"/>
+      <c r="F26" s="240"/>
+      <c r="G26" s="240"/>
+      <c r="H26" s="240"/>
+      <c r="I26" s="240"/>
+      <c r="J26" s="240"/>
+      <c r="K26" s="240"/>
+      <c r="L26" s="240"/>
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -19630,7 +19634,7 @@
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C34" s="151">
         <f>C32/C8</f>
@@ -19666,10 +19670,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="227" t="s">
+      <c r="B37" s="231" t="s">
         <v>198</v>
       </c>
-      <c r="C37" s="227"/>
+      <c r="C37" s="231"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -19735,10 +19739,10 @@
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="227" t="s">
+      <c r="B46" s="231" t="s">
         <v>203</v>
       </c>
-      <c r="C46" s="227"/>
+      <c r="C46" s="231"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
@@ -19794,10 +19798,10 @@
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="227" t="s">
-        <v>323</v>
-      </c>
-      <c r="C54" s="227"/>
+      <c r="B54" s="231" t="s">
+        <v>322</v>
+      </c>
+      <c r="C54" s="231"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
@@ -19910,10 +19914,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="227" t="s">
+      <c r="B4" s="231" t="s">
         <v>209</v>
       </c>
-      <c r="C4" s="227"/>
+      <c r="C4" s="231"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -19945,7 +19949,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C8" s="134">
         <f ca="1">Multiples!C61</f>
@@ -20041,60 +20045,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="227" t="s">
+      <c r="C3" s="231" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="227"/>
-      <c r="E3" s="227"/>
-      <c r="F3" s="227"/>
-      <c r="G3" s="236"/>
-      <c r="H3" s="237" t="s">
+      <c r="D3" s="231"/>
+      <c r="E3" s="231"/>
+      <c r="F3" s="231"/>
+      <c r="G3" s="243"/>
+      <c r="H3" s="244" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="227"/>
-      <c r="J3" s="227"/>
-      <c r="K3" s="227"/>
-      <c r="L3" s="227"/>
-      <c r="P3" s="241"/>
-      <c r="Q3" s="241"/>
-      <c r="R3" s="241"/>
-      <c r="S3" s="241"/>
-      <c r="T3" s="241"/>
-      <c r="U3" s="241"/>
-      <c r="V3" s="241"/>
-      <c r="W3" s="241"/>
-      <c r="X3" s="241"/>
-      <c r="Y3" s="241"/>
-      <c r="Z3" s="241"/>
+      <c r="I3" s="231"/>
+      <c r="J3" s="231"/>
+      <c r="K3" s="231"/>
+      <c r="L3" s="231"/>
+      <c r="P3" s="245"/>
+      <c r="Q3" s="245"/>
+      <c r="R3" s="245"/>
+      <c r="S3" s="245"/>
+      <c r="T3" s="245"/>
+      <c r="U3" s="245"/>
+      <c r="V3" s="245"/>
+      <c r="W3" s="245"/>
+      <c r="X3" s="245"/>
+      <c r="Y3" s="245"/>
+      <c r="Z3" s="245"/>
       <c r="AB3" s="110"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="238" t="s">
+      <c r="C5" s="240" t="s">
         <v>173</v>
       </c>
-      <c r="D5" s="238"/>
-      <c r="E5" s="238"/>
-      <c r="F5" s="238"/>
-      <c r="G5" s="238"/>
-      <c r="H5" s="238"/>
-      <c r="I5" s="238"/>
-      <c r="J5" s="238"/>
-      <c r="K5" s="238"/>
-      <c r="L5" s="238"/>
-      <c r="P5" s="241"/>
-      <c r="Q5" s="241"/>
-      <c r="R5" s="241"/>
-      <c r="S5" s="241"/>
-      <c r="T5" s="241"/>
-      <c r="U5" s="241"/>
-      <c r="V5" s="241"/>
-      <c r="W5" s="241"/>
-      <c r="X5" s="241"/>
-      <c r="Y5" s="241"/>
-      <c r="Z5" s="241"/>
+      <c r="D5" s="240"/>
+      <c r="E5" s="240"/>
+      <c r="F5" s="240"/>
+      <c r="G5" s="240"/>
+      <c r="H5" s="240"/>
+      <c r="I5" s="240"/>
+      <c r="J5" s="240"/>
+      <c r="K5" s="240"/>
+      <c r="L5" s="240"/>
+      <c r="P5" s="245"/>
+      <c r="Q5" s="245"/>
+      <c r="R5" s="245"/>
+      <c r="S5" s="245"/>
+      <c r="T5" s="245"/>
+      <c r="U5" s="245"/>
+      <c r="V5" s="245"/>
+      <c r="W5" s="245"/>
+      <c r="X5" s="245"/>
+      <c r="Y5" s="245"/>
+      <c r="Z5" s="245"/>
       <c r="AB5" s="111"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -20274,7 +20278,7 @@
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C10" s="139"/>
       <c r="D10" s="139"/>
@@ -20323,10 +20327,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="242" t="s">
+      <c r="B14" s="246" t="s">
         <v>217</v>
       </c>
-      <c r="C14" s="243"/>
+      <c r="C14" s="247"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="157" t="s">
@@ -20348,25 +20352,25 @@
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B17" s="159" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C17" s="160">
         <v>0.56000000000000005</v>
       </c>
-      <c r="E17" s="244" t="s">
+      <c r="E17" s="248" t="s">
         <v>220</v>
       </c>
-      <c r="F17" s="244"/>
-      <c r="G17" s="244"/>
-      <c r="H17" s="244"/>
-      <c r="I17" s="244"/>
+      <c r="F17" s="248"/>
+      <c r="G17" s="248"/>
+      <c r="H17" s="248"/>
+      <c r="I17" s="248"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="242" t="s">
+      <c r="B19" s="246" t="s">
         <v>177</v>
       </c>
-      <c r="C19" s="243"/>
+      <c r="C19" s="247"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="161" t="s">
@@ -20432,10 +20436,10 @@
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="242" t="s">
+      <c r="B28" s="246" t="s">
         <v>179</v>
       </c>
-      <c r="C28" s="243"/>
+      <c r="C28" s="247"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="161" t="s">
@@ -20510,18 +20514,18 @@
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="238" t="s">
+      <c r="C39" s="240" t="s">
         <v>223</v>
       </c>
-      <c r="D39" s="238"/>
-      <c r="E39" s="238"/>
-      <c r="F39" s="238"/>
-      <c r="G39" s="238"/>
-      <c r="H39" s="238"/>
-      <c r="I39" s="238"/>
-      <c r="J39" s="238"/>
-      <c r="K39" s="238"/>
-      <c r="L39" s="238"/>
+      <c r="D39" s="240"/>
+      <c r="E39" s="240"/>
+      <c r="F39" s="240"/>
+      <c r="G39" s="240"/>
+      <c r="H39" s="240"/>
+      <c r="I39" s="240"/>
+      <c r="J39" s="240"/>
+      <c r="K39" s="240"/>
+      <c r="L39" s="240"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -20657,7 +20661,7 @@
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B43" s="123" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C43" s="95">
         <f>C41/C42</f>
@@ -20742,7 +20746,7 @@
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B45" s="123" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C45" s="95">
         <f>C41/C44</f>
@@ -20782,7 +20786,7 @@
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B46" s="123" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C46" s="139"/>
       <c r="D46" s="95">
@@ -20953,17 +20957,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -20973,7 +20977,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0548B83C-60BF-4548-84AB-1D4A73B251A4}">
-  <dimension ref="A1:AE200"/>
+  <dimension ref="A1:AE201"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.6640625" style="1" customWidth="1"/>
@@ -21010,45 +21014,45 @@
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
       <c r="M2" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O2" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="P2" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="Q2" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="R2" s="7"/>
       <c r="S2" s="7"/>
       <c r="T2" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="U2" s="10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="V2" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="W2" s="10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="X2" s="10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Y2" s="10" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Z2" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AA2" s="10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AB2" s="7"/>
       <c r="AD2" s="7"/>
@@ -21077,28 +21081,28 @@
       <c r="R3" s="11"/>
       <c r="S3" s="11"/>
       <c r="T3" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="U3" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="V3" s="10" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="W3" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="X3" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="Y3" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="Z3" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="X3" s="10" t="s">
-        <v>365</v>
-      </c>
-      <c r="Y3" s="10" t="s">
-        <v>361</v>
-      </c>
-      <c r="Z3" s="10" t="s">
-        <v>358</v>
-      </c>
       <c r="AA3" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AB3" s="11"/>
       <c r="AC3" s="59" t="s">
@@ -21407,7 +21411,7 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B9" s="20" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C9" s="21"/>
       <c r="D9" s="21"/>
@@ -21880,7 +21884,7 @@
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B16" s="23" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C16" s="21"/>
       <c r="D16" s="21"/>
@@ -23556,7 +23560,7 @@
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B43" s="20" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C43" s="21"/>
       <c r="D43" s="21"/>
@@ -23672,7 +23676,7 @@
     </row>
     <row r="45" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B45" s="20" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C45" s="21"/>
       <c r="D45" s="21"/>
@@ -23730,7 +23734,7 @@
     </row>
     <row r="46" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C46" s="21"/>
       <c r="D46" s="21"/>
@@ -24594,7 +24598,7 @@
     </row>
     <row r="62" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B62" s="20" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C62" s="62"/>
       <c r="D62" s="62"/>
@@ -24652,7 +24656,7 @@
     </row>
     <row r="63" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B63" s="20" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C63" s="62"/>
       <c r="D63" s="62"/>
@@ -25000,97 +25004,97 @@
         <v>65</v>
       </c>
       <c r="C69" s="42">
-        <f>C35-(C41+C116)</f>
+        <f t="shared" ref="C69:Q69" si="26">C35-(C41+C116)</f>
         <v>0</v>
       </c>
       <c r="D69" s="42">
-        <f>D35-(D41+D116)</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="E69" s="42">
-        <f>E35-(E41+E116)</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="F69" s="42">
-        <f>F35-(F41+F116)</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="G69" s="42">
-        <f>G35-(G41+G116)</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H69" s="42">
-        <f>H35-(H41+H116)</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="I69" s="42">
-        <f>I35-(I41+I116)</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="J69" s="42">
-        <f>J35-(J41+J116)</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="K69" s="42">
-        <f>K35-(K41+K116)</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="L69" s="42">
-        <f>L35-(L41+L116)</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M69" s="42">
-        <f>M35-(M41+M116)</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="N69" s="42">
-        <f>N35-(N41+N116)</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="O69" s="42">
-        <f>O35-(O41+O116)</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="P69" s="42">
-        <f>P35-(P41+P116)</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="Q69" s="42">
-        <f>Q35-(Q41+Q116)</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="R69" s="1"/>
       <c r="S69" s="1"/>
       <c r="T69" s="42">
-        <f>T35-(T41+T116)</f>
+        <f t="shared" ref="T69:AA69" si="27">T35-(T41+T116)</f>
         <v>0</v>
       </c>
       <c r="U69" s="42">
-        <f>U35-(U41+U116)</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="V69" s="42">
-        <f>V35-(V41+V116)</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="W69" s="42">
-        <f>W35-(W41+W116)</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="X69" s="42">
-        <f>X35-(X41+X116)</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="Y69" s="42">
-        <f>Y35-(Y41+Y116)</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="Z69" s="42">
-        <f>Z35-(Z41+Z116)</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AA69" s="42">
-        <f>AA35-(AA41+AA116)</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AB69" s="16"/>
@@ -25195,55 +25199,55 @@
       <c r="K73" s="25"/>
       <c r="L73" s="25"/>
       <c r="M73" s="25">
-        <f t="shared" ref="M73:Q73" si="26">M72*M83</f>
+        <f t="shared" ref="M73:Q73" si="28">M72*M83</f>
         <v>25100</v>
       </c>
       <c r="N73" s="25">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>24700</v>
       </c>
       <c r="O73" s="25">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>25000</v>
       </c>
       <c r="P73" s="25">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>24400</v>
       </c>
       <c r="Q73" s="25">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>24300</v>
       </c>
       <c r="T73" s="25">
-        <f t="shared" ref="T73" si="27">T72*T83</f>
+        <f t="shared" ref="T73" si="29">T72*T83</f>
         <v>24530</v>
       </c>
       <c r="U73" s="25">
-        <f t="shared" ref="U73" si="28">U72*U83</f>
+        <f t="shared" ref="U73" si="30">U72*U83</f>
         <v>24490</v>
       </c>
       <c r="V73" s="25">
-        <f t="shared" ref="V73" si="29">V72*V83</f>
+        <f t="shared" ref="V73" si="31">V72*V83</f>
         <v>24400</v>
       </c>
       <c r="W73" s="25">
-        <f t="shared" ref="W73" si="30">W72*W83</f>
+        <f t="shared" ref="W73" si="32">W72*W83</f>
         <v>24400</v>
       </c>
       <c r="X73" s="25">
-        <f t="shared" ref="X73" si="31">X72*X83</f>
+        <f t="shared" ref="X73" si="33">X72*X83</f>
         <v>24300</v>
       </c>
       <c r="Y73" s="25">
-        <f t="shared" ref="Y73" si="32">Y72*Y83</f>
+        <f t="shared" ref="Y73" si="34">Y72*Y83</f>
         <v>24300</v>
       </c>
       <c r="Z73" s="25">
-        <f t="shared" ref="Z73:AA73" si="33">Z72*Z83</f>
+        <f t="shared" ref="Z73:AA73" si="35">Z72*Z83</f>
         <v>24300</v>
       </c>
       <c r="AA73" s="25">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>24200</v>
       </c>
       <c r="AC73" s="24">
@@ -25324,19 +25328,19 @@
       <c r="K75" s="25"/>
       <c r="L75" s="25"/>
       <c r="M75" s="25">
-        <f t="shared" ref="M75:P75" si="34">M74*M83</f>
+        <f t="shared" ref="M75:P75" si="36">M74*M83</f>
         <v>390</v>
       </c>
       <c r="N75" s="25">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>200</v>
       </c>
       <c r="O75" s="25">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>250</v>
       </c>
       <c r="P75" s="25">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>249</v>
       </c>
       <c r="Q75" s="25">
@@ -25344,35 +25348,35 @@
         <v>155</v>
       </c>
       <c r="T75" s="25">
-        <f t="shared" ref="T75:Z75" si="35">T74*T83</f>
+        <f t="shared" ref="T75:Z75" si="37">T74*T83</f>
         <v>270</v>
       </c>
       <c r="U75" s="25">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>241</v>
       </c>
       <c r="V75" s="25">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>249</v>
       </c>
       <c r="W75" s="25">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>170</v>
       </c>
       <c r="X75" s="25">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>166</v>
       </c>
       <c r="Y75" s="25">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>156</v>
       </c>
       <c r="Z75" s="25">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>155</v>
       </c>
       <c r="AA75" s="25">
-        <f t="shared" ref="AA75" si="36">AA74*AA83</f>
+        <f t="shared" ref="AA75" si="38">AA74*AA83</f>
         <v>105</v>
       </c>
       <c r="AC75" s="24">
@@ -25395,19 +25399,19 @@
       <c r="K76" s="25"/>
       <c r="L76" s="25"/>
       <c r="M76" s="25">
-        <f t="shared" ref="M76:P76" si="37">M73+M75</f>
+        <f t="shared" ref="M76:P76" si="39">M73+M75</f>
         <v>25490</v>
       </c>
       <c r="N76" s="25">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>24900</v>
       </c>
       <c r="O76" s="25">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>25250</v>
       </c>
       <c r="P76" s="25">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>24649</v>
       </c>
       <c r="Q76" s="25">
@@ -25415,35 +25419,35 @@
         <v>24455</v>
       </c>
       <c r="T76" s="25">
-        <f t="shared" ref="T76:Z76" si="38">T73+T75</f>
+        <f t="shared" ref="T76:Z76" si="40">T73+T75</f>
         <v>24800</v>
       </c>
       <c r="U76" s="25">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>24731</v>
       </c>
       <c r="V76" s="25">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>24649</v>
       </c>
       <c r="W76" s="25">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>24570</v>
       </c>
       <c r="X76" s="25">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>24466</v>
       </c>
       <c r="Y76" s="25">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>24456</v>
       </c>
       <c r="Z76" s="25">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>24455</v>
       </c>
       <c r="AA76" s="25">
-        <f t="shared" ref="AA76" si="39">AA73+AA75</f>
+        <f t="shared" ref="AA76" si="41">AA73+AA75</f>
         <v>24305</v>
       </c>
       <c r="AC76" s="24">
@@ -25453,7 +25457,7 @@
     </row>
     <row r="77" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B77" s="20" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C77" s="25"/>
       <c r="D77" s="25"/>
@@ -25495,7 +25499,7 @@
     </row>
     <row r="78" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B78" s="20" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C78" s="25"/>
       <c r="D78" s="25"/>
@@ -25508,19 +25512,19 @@
       <c r="K78" s="25"/>
       <c r="L78" s="25"/>
       <c r="M78" s="25">
-        <f t="shared" ref="M78:P78" si="40">M77*M83</f>
+        <f t="shared" ref="M78:P78" si="42">M77*M83</f>
         <v>1010</v>
       </c>
       <c r="N78" s="25">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>990</v>
       </c>
       <c r="O78" s="25">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>1040</v>
       </c>
       <c r="P78" s="25">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>1020</v>
       </c>
       <c r="Q78" s="25">
@@ -25613,55 +25617,55 @@
       <c r="K80" s="45"/>
       <c r="L80" s="45"/>
       <c r="M80" s="45">
-        <f t="shared" ref="M80:Q80" si="41">M79/M83</f>
+        <f t="shared" ref="M80:Q80" si="43">M79/M83</f>
         <v>1.6E-2</v>
       </c>
       <c r="N80" s="45">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>1.6E-2</v>
       </c>
       <c r="O80" s="45">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>1.6E-2</v>
       </c>
       <c r="P80" s="45">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="Q80" s="45">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0.04</v>
       </c>
       <c r="T80" s="45">
-        <f t="shared" ref="T80" si="42">T79/T83</f>
+        <f t="shared" ref="T80" si="44">T79/T83</f>
         <v>0.01</v>
       </c>
       <c r="U80" s="45">
-        <f t="shared" ref="U80" si="43">U79/U83</f>
+        <f t="shared" ref="U80" si="45">U79/U83</f>
         <v>0.01</v>
       </c>
       <c r="V80" s="45">
-        <f t="shared" ref="V80" si="44">V79/V83</f>
+        <f t="shared" ref="V80" si="46">V79/V83</f>
         <v>0.01</v>
       </c>
       <c r="W80" s="45">
-        <f t="shared" ref="W80" si="45">W79/W83</f>
+        <f t="shared" ref="W80" si="47">W79/W83</f>
         <v>0.01</v>
       </c>
       <c r="X80" s="45">
-        <f t="shared" ref="X80" si="46">X79/X83</f>
+        <f t="shared" ref="X80" si="48">X79/X83</f>
         <v>0.01</v>
       </c>
       <c r="Y80" s="45">
-        <f t="shared" ref="Y80" si="47">Y79/Y83</f>
+        <f t="shared" ref="Y80" si="49">Y79/Y83</f>
         <v>0.01</v>
       </c>
       <c r="Z80" s="45">
-        <f t="shared" ref="Z80:AA80" si="48">Z79/Z83</f>
+        <f t="shared" ref="Z80:AA80" si="50">Z79/Z83</f>
         <v>0.01</v>
       </c>
       <c r="AA80" s="45">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0.01</v>
       </c>
       <c r="AC80" s="72">
@@ -25674,95 +25678,95 @@
         <v>71</v>
       </c>
       <c r="C81" s="46">
-        <f t="shared" ref="C81:Q81" si="49">IF(AND(C14&gt;0,C15&lt;0),-(C15)/C14,0)</f>
+        <f t="shared" ref="C81:Q81" si="51">IF(AND(C14&gt;0,C15&lt;0),-(C15)/C14,0)</f>
         <v>0</v>
       </c>
       <c r="D81" s="46">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="E81" s="46">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="F81" s="46">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="G81" s="46">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="H81" s="46">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="I81" s="46">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="J81" s="46">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="K81" s="46">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="L81" s="46">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="M81" s="46">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>1.9012171813700834E-2</v>
       </c>
       <c r="N81" s="46">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="O81" s="46">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0.1199952687917677</v>
       </c>
       <c r="P81" s="46">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0.13264941803727417</v>
       </c>
       <c r="Q81" s="46">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0.15117002474372571</v>
       </c>
       <c r="T81" s="46">
-        <f t="shared" ref="T81:AA81" si="50">IF(AND(T14&gt;0,T15&lt;0),-(T15)/T14,0)</f>
+        <f t="shared" ref="T81:AA81" si="52">IF(AND(T14&gt;0,T15&lt;0),-(T15)/T14,0)</f>
         <v>0.1360986780472572</v>
       </c>
       <c r="U81" s="46">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0.13474637031726117</v>
       </c>
       <c r="V81" s="46">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0.1239639925447119</v>
       </c>
       <c r="W81" s="46">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0.1430853491556367</v>
       </c>
       <c r="X81" s="46">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0.15330385182336731</v>
       </c>
       <c r="Y81" s="46">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0.15884647827920709</v>
       </c>
       <c r="Z81" s="46">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0.14756830763735937</v>
       </c>
       <c r="AA81" s="46">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0.16568673733602277</v>
       </c>
       <c r="AC81" s="46">
@@ -25899,63 +25903,63 @@
       <c r="K87" s="48"/>
       <c r="L87" s="48"/>
       <c r="M87" s="48">
-        <f t="shared" ref="M87:Q91" si="51">IF(L5=0,
+        <f t="shared" ref="M87:Q91" si="53">IF(L5=0,
 IF(M5=0,0,IF(M5&gt;0,1,-1)),
 (M5-L5)/ABS(L5)
 )</f>
         <v>1</v>
       </c>
       <c r="N87" s="48">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>2.2293230289068887E-3</v>
       </c>
       <c r="O87" s="48">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>1.2585452658115222</v>
       </c>
       <c r="P87" s="48">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>1.1420340763599357</v>
       </c>
       <c r="Q87" s="48">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0.65473535790094795</v>
       </c>
       <c r="R87" s="1"/>
       <c r="S87" s="1"/>
       <c r="T87" s="48">
-        <f t="shared" ref="T87:AA91" si="52">IF(S5=0,
+        <f t="shared" ref="T87:AA91" si="54">IF(S5=0,
 IF(T5=0,0,IF(T5&gt;0,1,-1)),
 (T5-S5)/ABS(S5)
 )</f>
         <v>1</v>
       </c>
       <c r="U87" s="48">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>0.16784287616511318</v>
       </c>
       <c r="V87" s="48">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>0.12111624194743743</v>
       </c>
       <c r="W87" s="48">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>0.12028679667437898</v>
       </c>
       <c r="X87" s="48">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>6.0846080522899554E-2</v>
       </c>
       <c r="Y87" s="48">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>0.21956228740132211</v>
       </c>
       <c r="Z87" s="48">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>0.1950847279233765</v>
       </c>
       <c r="AA87" s="48">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>0.19798317847549429</v>
       </c>
       <c r="AB87" s="1"/>
@@ -25978,55 +25982,55 @@
       <c r="K88" s="50"/>
       <c r="L88" s="50"/>
       <c r="M88" s="50">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>1</v>
       </c>
       <c r="N88" s="50">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0.23085072571246953</v>
       </c>
       <c r="O88" s="50">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0.43062489240833191</v>
       </c>
       <c r="P88" s="50">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0.9637205944287347</v>
       </c>
       <c r="Q88" s="50">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0.91412114341738415</v>
       </c>
       <c r="T88" s="50">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>1</v>
       </c>
       <c r="U88" s="50">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>0.1955531743905706</v>
       </c>
       <c r="V88" s="50">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>0.18843827022182388</v>
       </c>
       <c r="W88" s="50">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>0.63970588235294112</v>
       </c>
       <c r="X88" s="50">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>-0.25893986432103022</v>
       </c>
       <c r="Y88" s="50">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>0.17587276958882855</v>
       </c>
       <c r="Z88" s="50">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>0.12383717094411822</v>
       </c>
       <c r="AA88" s="50">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>0.20100974521545145</v>
       </c>
       <c r="AC88" s="68"/>
@@ -26047,57 +26051,57 @@
       <c r="K89" s="48"/>
       <c r="L89" s="48"/>
       <c r="M89" s="48">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>1</v>
       </c>
       <c r="N89" s="48">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>-0.12125894134477826</v>
       </c>
       <c r="O89" s="48">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>1.8849309716071894</v>
       </c>
       <c r="P89" s="48">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>1.208934335568046</v>
       </c>
       <c r="Q89" s="48">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0.56822130025138462</v>
       </c>
       <c r="R89" s="1"/>
       <c r="S89" s="1"/>
       <c r="T89" s="48">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>1</v>
       </c>
       <c r="U89" s="48">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>0.1586781252768672</v>
       </c>
       <c r="V89" s="48">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>9.8141917724422698E-2</v>
       </c>
       <c r="W89" s="48">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>-7.1545451380426839E-2</v>
       </c>
       <c r="X89" s="48">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>0.26942402879856009</v>
       </c>
       <c r="Y89" s="48">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>0.23619767819691018</v>
       </c>
       <c r="Z89" s="48">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>0.22088938803794594</v>
       </c>
       <c r="AA89" s="48">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>0.19697414518622902</v>
       </c>
       <c r="AB89" s="1"/>
@@ -26120,62 +26124,62 @@
       <c r="K90" s="50"/>
       <c r="L90" s="50"/>
       <c r="M90" s="50">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>1</v>
       </c>
       <c r="N90" s="50">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0.3931283219438117</v>
       </c>
       <c r="O90" s="50">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0.18204115002043875</v>
       </c>
       <c r="P90" s="50">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0.4886455331412104</v>
       </c>
       <c r="Q90" s="50">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0.43232151153786585</v>
       </c>
       <c r="T90" s="50">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>1</v>
       </c>
       <c r="U90" s="50">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>9.7087378640776698E-2</v>
       </c>
       <c r="V90" s="50">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>9.5575221238938052E-2</v>
       </c>
       <c r="W90" s="50">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>7.4044157242864839E-2</v>
       </c>
       <c r="X90" s="50">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>7.5708197543243927E-2</v>
       </c>
       <c r="Y90" s="50">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>9.6481006758331392E-2</v>
       </c>
       <c r="Z90" s="50">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>0.17151965993623805</v>
       </c>
       <c r="AA90" s="50">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>0.14677068214804065</v>
       </c>
       <c r="AC90" s="68"/>
     </row>
     <row r="91" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B91" s="20" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C91" s="49"/>
       <c r="D91" s="50"/>
@@ -26188,55 +26192,55 @@
       <c r="K91" s="50"/>
       <c r="L91" s="50"/>
       <c r="M91" s="50">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>1</v>
       </c>
       <c r="N91" s="50">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0.1265004616805171</v>
       </c>
       <c r="O91" s="50">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>8.7704918032786891E-2</v>
       </c>
       <c r="P91" s="50">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0.31537302185380556</v>
       </c>
       <c r="Q91" s="50">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0.31165855055857922</v>
       </c>
       <c r="T91" s="50">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>1</v>
       </c>
       <c r="U91" s="50">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>6.5320665083135387E-2</v>
       </c>
       <c r="V91" s="50">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>8.6956521739130432E-2</v>
       </c>
       <c r="W91" s="50">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>6.7692307692307691E-2</v>
       </c>
       <c r="X91" s="50">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>7.7809798270893377E-2</v>
       </c>
       <c r="Y91" s="50">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>1.06951871657754E-2</v>
       </c>
       <c r="Z91" s="50">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>0.13051146384479717</v>
       </c>
       <c r="AA91" s="50">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>1.4040561622464899E-2</v>
       </c>
       <c r="AC91" s="68"/>
@@ -26256,94 +26260,61 @@
       <c r="K92" s="50"/>
       <c r="L92" s="50"/>
       <c r="M92" s="50">
-        <f>IF(L10=0,
+        <f t="shared" ref="M92:Q93" si="55">IF(L10=0,
 IF(M10=0,0,IF(M10&gt;0,1,-1)),
 (M10-L10)/ABS(L10)
 )</f>
         <v>1</v>
       </c>
       <c r="N92" s="50">
-        <f>IF(M10=0,
-IF(N10=0,0,IF(N10&gt;0,1,-1)),
-(N10-M10)/ABS(M10)
-)</f>
+        <f t="shared" si="55"/>
         <v>0.49744417541027708</v>
       </c>
       <c r="O92" s="50">
-        <f>IF(N10=0,
-IF(O10=0,0,IF(O10&gt;0,1,-1)),
-(O10-N10)/ABS(N10)
-)</f>
+        <f t="shared" si="55"/>
         <v>1.7696730147323033E-2</v>
       </c>
       <c r="P92" s="50">
-        <f>IF(O10=0,
-IF(P10=0,0,IF(P10&gt;0,1,-1)),
-(P10-O10)/ABS(O10)
-)</f>
+        <f t="shared" si="55"/>
         <v>0.44805366757878012</v>
       </c>
       <c r="Q92" s="50">
-        <f>IF(P10=0,
-IF(Q10=0,0,IF(Q10&gt;0,1,-1)),
-(Q10-P10)/ABS(P10)
-)</f>
+        <f t="shared" si="55"/>
         <v>0.40664431575739102</v>
       </c>
       <c r="T92" s="50">
-        <f>IF(S10=0,
+        <f t="shared" ref="T92:AA93" si="56">IF(S10=0,
 IF(T10=0,0,IF(T10&gt;0,1,-1)),
 (T10-S10)/ABS(S10)
 )</f>
         <v>1</v>
       </c>
       <c r="U92" s="50">
-        <f>IF(T10=0,
-IF(U10=0,0,IF(U10&gt;0,1,-1)),
-(U10-T10)/ABS(T10)
-)</f>
+        <f t="shared" si="56"/>
         <v>9.028484231943032E-2</v>
       </c>
       <c r="V92" s="50">
-        <f>IF(U10=0,
-IF(V10=0,0,IF(V10&gt;0,1,-1)),
-(V10-U10)/ABS(U10)
-)</f>
+        <f t="shared" si="56"/>
         <v>9.3771868439468165E-2</v>
       </c>
       <c r="W92" s="50">
-        <f>IF(V10=0,
-IF(W10=0,0,IF(W10&gt;0,1,-1)),
-(W10-V10)/ABS(V10)
-)</f>
+        <f t="shared" si="56"/>
         <v>7.2723395180208997E-2</v>
       </c>
       <c r="X92" s="50">
-        <f>IF(W10=0,
-IF(X10=0,0,IF(X10&gt;0,1,-1)),
-(X10-W10)/ABS(W10)
-)</f>
+        <f t="shared" si="56"/>
         <v>7.6143141153081517E-2</v>
       </c>
       <c r="Y92" s="50">
-        <f>IF(X10=0,
-IF(Y10=0,0,IF(Y10&gt;0,1,-1)),
-(Y10-X10)/ABS(X10)
-)</f>
+        <f t="shared" si="56"/>
         <v>7.8699427304636985E-2</v>
       </c>
       <c r="Z92" s="50">
-        <f>IF(Y10=0,
-IF(Z10=0,0,IF(Z10&gt;0,1,-1)),
-(Z10-Y10)/ABS(Y10)
-)</f>
+        <f t="shared" si="56"/>
         <v>0.16355540332248672</v>
       </c>
       <c r="AA92" s="50">
-        <f>IF(Z10=0,
-IF(AA10=0,0,IF(AA10&gt;0,1,-1)),
-(AA10-Z10)/ABS(Z10)
-)</f>
+        <f t="shared" si="56"/>
         <v>0.12172505151604357</v>
       </c>
       <c r="AC92" s="68"/>
@@ -26364,96 +26335,57 @@
       <c r="K93" s="48"/>
       <c r="L93" s="48"/>
       <c r="M93" s="48">
-        <f>IF(L11=0,
-IF(M11=0,0,IF(M11&gt;0,1,-1)),
-(M11-L11)/ABS(L11)
-)</f>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="N93" s="48">
-        <f>IF(M11=0,
-IF(N11=0,0,IF(N11&gt;0,1,-1)),
-(N11-M11)/ABS(M11)
-)</f>
+        <f t="shared" si="55"/>
         <v>-0.57932476844935765</v>
       </c>
       <c r="O93" s="48">
-        <f>IF(N11=0,
-IF(O11=0,0,IF(O11&gt;0,1,-1)),
-(O11-N11)/ABS(N11)
-)</f>
+        <f t="shared" si="55"/>
         <v>6.8058712121212119</v>
       </c>
       <c r="P93" s="48">
-        <f>IF(O11=0,
-IF(P11=0,0,IF(P11&gt;0,1,-1)),
-(P11-O11)/ABS(O11)
-)</f>
+        <f t="shared" si="55"/>
         <v>1.470368797767803</v>
       </c>
       <c r="Q93" s="48">
-        <f>IF(P11=0,
-IF(Q11=0,0,IF(Q11&gt;0,1,-1)),
-(Q11-P11)/ABS(P11)
-)</f>
+        <f t="shared" si="55"/>
         <v>0.60076363055995485</v>
       </c>
       <c r="R93" s="1"/>
       <c r="S93" s="1"/>
       <c r="T93" s="48">
-        <f>IF(S11=0,
-IF(T11=0,0,IF(T11&gt;0,1,-1)),
-(T11-S11)/ABS(S11)
-)</f>
+        <f t="shared" si="56"/>
         <v>1</v>
       </c>
       <c r="U93" s="48">
-        <f>IF(T11=0,
-IF(U11=0,0,IF(U11&gt;0,1,-1)),
-(U11-T11)/ABS(T11)
-)</f>
+        <f t="shared" si="56"/>
         <v>0.17310374423345135</v>
       </c>
       <c r="V93" s="48">
-        <f>IF(U11=0,
-IF(V11=0,0,IF(V11&gt;0,1,-1)),
-(V11-U11)/ABS(U11)
-)</f>
+        <f t="shared" si="56"/>
         <v>9.8998582468334165E-2</v>
       </c>
       <c r="W93" s="48">
-        <f>IF(V11=0,
-IF(W11=0,0,IF(W11&gt;0,1,-1)),
-(W11-V11)/ABS(V11)
-)</f>
+        <f t="shared" si="56"/>
         <v>-9.9692102854289755E-2</v>
       </c>
       <c r="X93" s="48">
-        <f>IF(W11=0,
-IF(X11=0,0,IF(X11&gt;0,1,-1)),
-(X11-W11)/ABS(W11)
-)</f>
+        <f t="shared" si="56"/>
         <v>0.31435437655975601</v>
       </c>
       <c r="Y93" s="48">
-        <f>IF(X11=0,
-IF(Y11=0,0,IF(Y11&gt;0,1,-1)),
-(Y11-X11)/ABS(X11)
-)</f>
+        <f t="shared" si="56"/>
         <v>0.2661744022503516</v>
       </c>
       <c r="Z93" s="48">
-        <f>IF(Y11=0,
-IF(Z11=0,0,IF(Z11&gt;0,1,-1)),
-(Z11-Y11)/ABS(Y11)
-)</f>
+        <f t="shared" si="56"/>
         <v>0.23018605942793668</v>
       </c>
       <c r="AA93" s="48">
-        <f>IF(Z11=0,
-IF(AA11=0,0,IF(AA11&gt;0,1,-1)),
-(AA11-Z11)/ABS(Z11)
-)</f>
+        <f t="shared" si="56"/>
         <v>0.20851486489537011</v>
       </c>
       <c r="AB93" s="1"/>
@@ -26514,59 +26446,38 @@
       <c r="R94" s="1"/>
       <c r="S94" s="1"/>
       <c r="T94" s="52">
-        <f>IF(S14=0,
+        <f t="shared" ref="T94:AA94" si="57">IF(S14=0,
 IF(T14=0,0,IF(T14&gt;0,1,-1)),
 (T14-S14)/ABS(S14)
 )</f>
         <v>1</v>
       </c>
       <c r="U94" s="52">
-        <f>IF(T14=0,
-IF(U14=0,0,IF(U14&gt;0,1,-1)),
-(U14-T14)/ABS(T14)
-)</f>
+        <f t="shared" si="57"/>
         <v>0.16144477984802749</v>
       </c>
       <c r="V94" s="52">
-        <f>IF(U14=0,
-IF(V14=0,0,IF(V14&gt;0,1,-1)),
-(V14-U14)/ABS(U14)
-)</f>
+        <f t="shared" si="57"/>
         <v>0.12999641512815918</v>
       </c>
       <c r="W94" s="52">
-        <f>IF(V14=0,
-IF(W14=0,0,IF(W14&gt;0,1,-1)),
-(W14-V14)/ABS(V14)
-)</f>
+        <f t="shared" si="57"/>
         <v>-0.13114169012967442</v>
       </c>
       <c r="X94" s="52">
-        <f>IF(W14=0,
-IF(X14=0,0,IF(X14&gt;0,1,-1)),
-(X14-W14)/ABS(W14)
-)</f>
+        <f t="shared" si="57"/>
         <v>0.42428115015974444</v>
       </c>
       <c r="Y94" s="52">
-        <f>IF(X14=0,
-IF(Y14=0,0,IF(Y14&gt;0,1,-1)),
-(Y14-X14)/ABS(X14)
-)</f>
+        <f t="shared" si="57"/>
         <v>0.21566365442543101</v>
       </c>
       <c r="Z94" s="52">
-        <f>IF(Y14=0,
-IF(Z14=0,0,IF(Z14&gt;0,1,-1)),
-(Z14-Y14)/ABS(Y14)
-)</f>
+        <f t="shared" si="57"/>
         <v>0.32847427245887811</v>
       </c>
       <c r="AA94" s="52">
-        <f>IF(Z14=0,
-IF(AA14=0,0,IF(AA14&gt;0,1,-1)),
-(AA14-Z14)/ABS(Z14)
-)</f>
+        <f t="shared" si="57"/>
         <v>0.38704684802666828</v>
       </c>
       <c r="AB94" s="1"/>
@@ -26627,59 +26538,38 @@
       <c r="R95" s="1"/>
       <c r="S95" s="1"/>
       <c r="T95" s="52">
-        <f>IF(S17=0,
+        <f t="shared" ref="T95:AA95" si="58">IF(S17=0,
 IF(T17=0,0,IF(T17&gt;0,1,-1)),
 (T17-S17)/ABS(S17)
 )</f>
         <v>1</v>
       </c>
       <c r="U95" s="52">
-        <f>IF(T17=0,
-IF(U17=0,0,IF(U17&gt;0,1,-1)),
-(U17-T17)/ABS(T17)
-)</f>
+        <f t="shared" si="58"/>
         <v>0.16326284715946743</v>
       </c>
       <c r="V95" s="52">
-        <f>IF(U17=0,
-IF(V17=0,0,IF(V17&gt;0,1,-1)),
-(V17-U17)/ABS(U17)
-)</f>
+        <f t="shared" si="58"/>
         <v>0.14407789113884717</v>
       </c>
       <c r="W95" s="52">
-        <f>IF(V17=0,
-IF(W17=0,0,IF(W17&gt;0,1,-1)),
-(W17-V17)/ABS(V17)
-)</f>
+        <f t="shared" si="58"/>
         <v>-0.15010637816305283</v>
       </c>
       <c r="X95" s="52">
-        <f>IF(W17=0,
-IF(X17=0,0,IF(X17&gt;0,1,-1)),
-(X17-W17)/ABS(W17)
-)</f>
+        <f t="shared" si="58"/>
         <v>0.40729693741677764</v>
       </c>
       <c r="Y95" s="52">
-        <f>IF(X17=0,
-IF(Y17=0,0,IF(Y17&gt;0,1,-1)),
-(Y17-X17)/ABS(X17)
-)</f>
+        <f t="shared" si="58"/>
         <v>0.20770569979562487</v>
       </c>
       <c r="Z95" s="52">
-        <f>IF(Y17=0,
-IF(Z17=0,0,IF(Z17&gt;0,1,-1)),
-(Z17-Y17)/ABS(Y17)
-)</f>
+        <f t="shared" si="58"/>
         <v>0.34628643058602321</v>
       </c>
       <c r="AA95" s="52">
-        <f>IF(Z17=0,
-IF(AA17=0,0,IF(AA17&gt;0,1,-1)),
-(AA17-Z17)/ABS(Z17)
-)</f>
+        <f t="shared" si="58"/>
         <v>0.35756517690875234</v>
       </c>
       <c r="AB95" s="1"/>
@@ -26736,35 +26626,35 @@
         <v>0.71068084357547079</v>
       </c>
       <c r="T98" s="50">
-        <f>T7/T5</f>
+        <f t="shared" ref="T98:AA98" si="59">T7/T5</f>
         <v>0.75146471371504664</v>
       </c>
       <c r="U98" s="50">
-        <f>U7/U5</f>
+        <f t="shared" si="59"/>
         <v>0.74556752750698363</v>
       </c>
       <c r="V98" s="50">
-        <f>V7/V5</f>
+        <f t="shared" si="59"/>
         <v>0.73028908494571709</v>
       </c>
       <c r="W98" s="50">
-        <f>W7/W5</f>
+        <f t="shared" si="59"/>
         <v>0.60523807362353044</v>
       </c>
       <c r="X98" s="50">
-        <f>X7/X5</f>
+        <f t="shared" si="59"/>
         <v>0.72423678411740799</v>
       </c>
       <c r="Y98" s="50">
-        <f>Y7/Y5</f>
+        <f t="shared" si="59"/>
         <v>0.7341157071185489</v>
       </c>
       <c r="Z98" s="50">
-        <f>Z7/Z5</f>
+        <f t="shared" si="59"/>
         <v>0.74996697344665109</v>
       </c>
       <c r="AA98" s="50">
-        <f>AA7/AA5</f>
+        <f t="shared" si="59"/>
         <v>0.74933529375727503</v>
       </c>
       <c r="AC98" s="50">
@@ -26807,35 +26697,35 @@
         <v>0.60381683631412719</v>
       </c>
       <c r="T99" s="50">
-        <f>T11/T5</f>
+        <f t="shared" ref="T99:AA99" si="60">T11/T5</f>
         <v>0.62057256990679099</v>
       </c>
       <c r="U99" s="50">
-        <f>U11/U5</f>
+        <f t="shared" si="60"/>
         <v>0.62336810900176731</v>
       </c>
       <c r="V99" s="50">
-        <f>V11/V5</f>
+        <f t="shared" si="60"/>
         <v>0.61107014822913219</v>
       </c>
       <c r="W99" s="50">
-        <f>W11/W5</f>
+        <f t="shared" si="60"/>
         <v>0.49108074985248057</v>
       </c>
       <c r="X99" s="50">
-        <f>X11/X5</f>
+        <f t="shared" si="60"/>
         <v>0.60843334830883766</v>
       </c>
       <c r="Y99" s="50">
-        <f>Y11/Y5</f>
+        <f t="shared" si="60"/>
         <v>0.63168789250254365</v>
       </c>
       <c r="Z99" s="50">
-        <f>Z11/Z5</f>
+        <f t="shared" si="60"/>
         <v>0.65024146080115075</v>
       </c>
       <c r="AA99" s="50">
-        <f>AA11/AA5</f>
+        <f t="shared" si="60"/>
         <v>0.65595785088525393</v>
       </c>
       <c r="AC99" s="50">
@@ -26881,35 +26771,35 @@
       <c r="R100" s="1"/>
       <c r="S100" s="1"/>
       <c r="T100" s="55">
-        <f>T115/T5</f>
+        <f t="shared" ref="T100:AA100" si="61">T115/T5</f>
         <v>0.55256324900133158</v>
       </c>
       <c r="U100" s="55">
-        <f>U115/U5</f>
+        <f t="shared" si="61"/>
         <v>0.55039621458297705</v>
       </c>
       <c r="V100" s="55">
-        <f>V115/V5</f>
+        <f t="shared" si="61"/>
         <v>0.56166891256260965</v>
       </c>
       <c r="W100" s="55">
-        <f>W115/W5</f>
+        <f t="shared" si="61"/>
         <v>0.42610412600426673</v>
       </c>
       <c r="X100" s="55">
-        <f>X115/X5</f>
+        <f t="shared" si="61"/>
         <v>0.56526110861519374</v>
       </c>
       <c r="Y100" s="55">
-        <f>Y115/Y5</f>
+        <f t="shared" si="61"/>
         <v>0.55976563870469775</v>
       </c>
       <c r="Z100" s="55">
-        <f>Z115/Z5</f>
+        <f t="shared" si="61"/>
         <v>0.63058699194152101</v>
       </c>
       <c r="AA100" s="55">
-        <f>AA115/AA5</f>
+        <f t="shared" si="61"/>
         <v>0.71458677939104331</v>
       </c>
       <c r="AB100" s="1"/>
@@ -26935,8 +26825,8 @@
       <c r="AE102" s="1"/>
     </row>
     <row r="103" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B103" s="246" t="s">
-        <v>374</v>
+      <c r="B103" s="228" t="s">
+        <v>373</v>
       </c>
       <c r="C103" s="62"/>
       <c r="D103" s="62"/>
@@ -26993,8 +26883,8 @@
       </c>
     </row>
     <row r="104" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B104" s="246" t="s">
-        <v>375</v>
+      <c r="B104" s="228" t="s">
+        <v>374</v>
       </c>
       <c r="C104" s="62"/>
       <c r="D104" s="62"/>
@@ -27046,13 +26936,13 @@
         <v>37377</v>
       </c>
       <c r="AC104" s="62">
-        <f t="shared" ref="AC104:AC106" si="53">SUM(X104:AA104)</f>
+        <f t="shared" ref="AC104:AC106" si="62">SUM(X104:AA104)</f>
         <v>103965</v>
       </c>
     </row>
     <row r="105" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B105" s="20" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C105" s="62"/>
       <c r="D105" s="62"/>
@@ -27104,13 +26994,13 @@
         <v>75246</v>
       </c>
       <c r="AC105" s="62">
-        <f t="shared" si="53"/>
+        <f t="shared" si="62"/>
         <v>229871</v>
       </c>
     </row>
     <row r="106" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B106" s="20" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C106" s="21"/>
       <c r="D106" s="21"/>
@@ -27164,7 +27054,7 @@
         <v>6369</v>
       </c>
       <c r="AC106" s="62">
-        <f t="shared" si="53"/>
+        <f t="shared" si="62"/>
         <v>23620</v>
       </c>
     </row>
@@ -27200,95 +27090,95 @@
         <v>71</v>
       </c>
       <c r="C110" s="81">
-        <f>IF(AND(C81&gt;=0,C11&gt;=0),C81,0)</f>
+        <f t="shared" ref="C110:Q110" si="63">IF(AND(C81&gt;=0,C11&gt;=0),C81,0)</f>
         <v>0</v>
       </c>
       <c r="D110" s="81">
-        <f>IF(AND(D81&gt;=0,D11&gt;=0),D81,0)</f>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="E110" s="81">
-        <f>IF(AND(E81&gt;=0,E11&gt;=0),E81,0)</f>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="F110" s="81">
-        <f>IF(AND(F81&gt;=0,F11&gt;=0),F81,0)</f>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="G110" s="81">
-        <f>IF(AND(G81&gt;=0,G11&gt;=0),G81,0)</f>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="H110" s="81">
-        <f>IF(AND(H81&gt;=0,H11&gt;=0),H81,0)</f>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="I110" s="81">
-        <f>IF(AND(I81&gt;=0,I11&gt;=0),I81,0)</f>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="J110" s="81">
-        <f>IF(AND(J81&gt;=0,J11&gt;=0),J81,0)</f>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="K110" s="81">
-        <f>IF(AND(K81&gt;=0,K11&gt;=0),K81,0)</f>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="L110" s="81">
-        <f>IF(AND(L81&gt;=0,L11&gt;=0),L81,0)</f>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="M110" s="81">
-        <f>IF(AND(M81&gt;=0,M11&gt;=0),M81,0)</f>
+        <f t="shared" si="63"/>
         <v>1.9012171813700834E-2</v>
       </c>
       <c r="N110" s="81">
-        <f>IF(AND(N81&gt;=0,N11&gt;=0),N81,0)</f>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="O110" s="81">
-        <f>IF(AND(O81&gt;=0,O11&gt;=0),O81,0)</f>
+        <f t="shared" si="63"/>
         <v>0.1199952687917677</v>
       </c>
       <c r="P110" s="81">
-        <f>IF(AND(P81&gt;=0,P11&gt;=0),P81,0)</f>
+        <f t="shared" si="63"/>
         <v>0.13264941803727417</v>
       </c>
       <c r="Q110" s="81">
-        <f>IF(AND(Q81&gt;=0,Q11&gt;=0),Q81,0)</f>
+        <f t="shared" si="63"/>
         <v>0.15117002474372571</v>
       </c>
       <c r="T110" s="81">
-        <f>IF(AND(T81&gt;=0,T11&gt;=0),T81,0)</f>
+        <f t="shared" ref="T110:AA110" si="64">IF(AND(T81&gt;=0,T11&gt;=0),T81,0)</f>
         <v>0.1360986780472572</v>
       </c>
       <c r="U110" s="81">
-        <f>IF(AND(U81&gt;=0,U11&gt;=0),U81,0)</f>
+        <f t="shared" si="64"/>
         <v>0.13474637031726117</v>
       </c>
       <c r="V110" s="81">
-        <f>IF(AND(V81&gt;=0,V11&gt;=0),V81,0)</f>
+        <f t="shared" si="64"/>
         <v>0.1239639925447119</v>
       </c>
       <c r="W110" s="81">
-        <f>IF(AND(W81&gt;=0,W11&gt;=0),W81,0)</f>
+        <f t="shared" si="64"/>
         <v>0.1430853491556367</v>
       </c>
       <c r="X110" s="81">
-        <f>IF(AND(X81&gt;=0,X11&gt;=0),X81,0)</f>
+        <f t="shared" si="64"/>
         <v>0.15330385182336731</v>
       </c>
       <c r="Y110" s="81">
-        <f>IF(AND(Y81&gt;=0,Y11&gt;=0),Y81,0)</f>
+        <f t="shared" si="64"/>
         <v>0.15884647827920709</v>
       </c>
       <c r="Z110" s="81">
-        <f>IF(AND(Z81&gt;=0,Z11&gt;=0),Z81,0)</f>
+        <f t="shared" si="64"/>
         <v>0.14756830763735937</v>
       </c>
       <c r="AA110" s="81">
-        <f>IF(AND(AA81&gt;=0,AA11&gt;=0),AA81,0)</f>
+        <f t="shared" si="64"/>
         <v>0.16568673733602277</v>
       </c>
       <c r="AC110" s="81">
@@ -27331,35 +27221,35 @@
         <v>62556</v>
       </c>
       <c r="T111" s="25">
-        <f>T28</f>
+        <f t="shared" ref="T111:AA111" si="65">T28</f>
         <v>34800</v>
       </c>
       <c r="U111" s="25">
-        <f>U28</f>
+        <f t="shared" si="65"/>
         <v>38487</v>
       </c>
       <c r="V111" s="25">
-        <f>V28</f>
+        <f t="shared" si="65"/>
         <v>43210</v>
       </c>
       <c r="W111" s="25">
-        <f>W28</f>
+        <f t="shared" si="65"/>
         <v>53691</v>
       </c>
       <c r="X111" s="25">
-        <f>X28</f>
+        <f t="shared" si="65"/>
         <v>56791</v>
       </c>
       <c r="Y111" s="25">
-        <f>Y28</f>
+        <f t="shared" si="65"/>
         <v>60608</v>
       </c>
       <c r="Z111" s="25">
-        <f>Z28</f>
+        <f t="shared" si="65"/>
         <v>62556</v>
       </c>
       <c r="AA111" s="25">
-        <f>AA28</f>
+        <f t="shared" si="65"/>
         <v>80572</v>
       </c>
       <c r="AC111" s="25">
@@ -27422,35 +27312,35 @@
         <v>8468</v>
       </c>
       <c r="T112" s="25">
-        <f>T37+T39</f>
+        <f t="shared" ref="T112:AA112" si="66">T37+T39</f>
         <v>8461</v>
       </c>
       <c r="U112" s="25">
-        <f>U37+U39</f>
+        <f t="shared" si="66"/>
         <v>8462</v>
       </c>
       <c r="V112" s="25">
-        <f>V37+V39</f>
+        <f t="shared" si="66"/>
         <v>8463</v>
       </c>
       <c r="W112" s="25">
-        <f>W37+W39</f>
+        <f t="shared" si="66"/>
         <v>8464</v>
       </c>
       <c r="X112" s="25">
-        <f>X37+X39</f>
+        <f t="shared" si="66"/>
         <v>8466</v>
       </c>
       <c r="Y112" s="25">
-        <f>Y37+Y39</f>
+        <f t="shared" si="66"/>
         <v>8467</v>
       </c>
       <c r="Z112" s="25">
-        <f>Z37+Z39</f>
+        <f t="shared" si="66"/>
         <v>8568</v>
       </c>
       <c r="AA112" s="25">
-        <f>AA37+AA39</f>
+        <f t="shared" si="66"/>
         <v>8470</v>
       </c>
       <c r="AC112" s="25">
@@ -27507,7 +27397,7 @@
     </row>
     <row r="114" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B114" s="20" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C114" s="25"/>
       <c r="D114" s="25"/>
@@ -27540,35 +27430,35 @@
         <v>-6042</v>
       </c>
       <c r="T114" s="127">
-        <f>T58+T59</f>
+        <f t="shared" ref="T114:AA114" si="67">T58+T59</f>
         <v>-977</v>
       </c>
       <c r="U114" s="127">
-        <f>U58+U59</f>
+        <f t="shared" si="67"/>
         <v>-813</v>
       </c>
       <c r="V114" s="127">
-        <f>V58+V59</f>
+        <f t="shared" si="67"/>
         <v>-1077</v>
       </c>
       <c r="W114" s="127">
-        <f>W58+W59</f>
+        <f t="shared" si="67"/>
         <v>-1227</v>
       </c>
       <c r="X114" s="127">
-        <f>X58+X59</f>
+        <f t="shared" si="67"/>
         <v>-1894</v>
       </c>
       <c r="Y114" s="127">
-        <f>Y58+Y59</f>
+        <f t="shared" si="67"/>
         <v>-1637</v>
       </c>
       <c r="Z114" s="127">
-        <f>Z58+Z59</f>
+        <f t="shared" si="67"/>
         <v>-1284</v>
       </c>
       <c r="AA114" s="127">
-        <f>AA58+AA59</f>
+        <f t="shared" si="67"/>
         <v>-1757</v>
       </c>
       <c r="AC114" s="127">
@@ -27578,7 +27468,7 @@
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B115" s="20" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C115" s="25"/>
       <c r="D115" s="25"/>
@@ -27611,35 +27501,35 @@
         <v>120067</v>
       </c>
       <c r="T115" s="127">
-        <f>T16+T17</f>
+        <f t="shared" ref="T115:AA115" si="68">T16+T17</f>
         <v>16599</v>
       </c>
       <c r="U115" s="127">
-        <f>U16+U17</f>
+        <f t="shared" si="68"/>
         <v>19309</v>
       </c>
       <c r="V115" s="127">
-        <f>V16+V17</f>
+        <f t="shared" si="68"/>
         <v>22091</v>
       </c>
       <c r="W115" s="127">
-        <f>W16+W17</f>
+        <f t="shared" si="68"/>
         <v>18775</v>
       </c>
       <c r="X115" s="127">
-        <f>X16+X17</f>
+        <f t="shared" si="68"/>
         <v>26422</v>
       </c>
       <c r="Y115" s="127">
-        <f>Y16+Y17</f>
+        <f t="shared" si="68"/>
         <v>31910</v>
       </c>
       <c r="Z115" s="127">
-        <f>Z16+Z17</f>
+        <f t="shared" si="68"/>
         <v>42960</v>
       </c>
       <c r="AA115" s="127">
-        <f>AA16+AA17</f>
+        <f t="shared" si="68"/>
         <v>58321</v>
       </c>
       <c r="AC115" s="127">
@@ -27649,7 +27539,7 @@
     </row>
     <row r="116" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B116" s="20" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C116" s="25"/>
       <c r="D116" s="25"/>
@@ -27682,35 +27572,35 @@
         <v>157293</v>
       </c>
       <c r="T116" s="127">
-        <f>T47+T46</f>
+        <f t="shared" ref="T116:AA116" si="69">T47+T46</f>
         <v>58157</v>
       </c>
       <c r="U116" s="127">
-        <f>U47+U46</f>
+        <f t="shared" si="69"/>
         <v>65899</v>
       </c>
       <c r="V116" s="127">
-        <f>V47+V46</f>
+        <f t="shared" si="69"/>
         <v>79327</v>
       </c>
       <c r="W116" s="127">
-        <f>W47+W46</f>
+        <f t="shared" si="69"/>
         <v>83843</v>
       </c>
       <c r="X116" s="127">
-        <f>X47+X46</f>
+        <f t="shared" si="69"/>
         <v>100131</v>
       </c>
       <c r="Y116" s="127">
-        <f>Y47+Y46</f>
+        <f t="shared" si="69"/>
         <v>118897</v>
       </c>
       <c r="Z116" s="127">
-        <f>Z47+Z46</f>
+        <f t="shared" si="69"/>
         <v>157293</v>
       </c>
       <c r="AA116" s="127">
-        <f>AA47+AA46</f>
+        <f t="shared" si="69"/>
         <v>195474</v>
       </c>
       <c r="AC116" s="127">
@@ -27787,7 +27677,7 @@
     </row>
     <row r="121" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B121" s="20" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C121" s="26"/>
       <c r="D121" s="26"/>
@@ -27943,19 +27833,19 @@
         <v>94</v>
       </c>
       <c r="M127" s="76">
-        <f t="shared" ref="M127:P127" si="54">M125*M126</f>
+        <f t="shared" ref="M127:P127" si="70">M125*M126</f>
         <v>0.22069839545567699</v>
       </c>
       <c r="N127" s="76">
-        <f t="shared" si="54"/>
+        <f t="shared" si="70"/>
         <v>0.10606575688407557</v>
       </c>
       <c r="O127" s="76">
-        <f t="shared" si="54"/>
+        <f t="shared" si="70"/>
         <v>0.45277507302823755</v>
       </c>
       <c r="P127" s="76">
-        <f t="shared" si="54"/>
+        <f t="shared" si="70"/>
         <v>0.65304074336251472</v>
       </c>
       <c r="Q127" s="76">
@@ -28017,19 +27907,19 @@
         <v>96</v>
       </c>
       <c r="M129" s="76">
-        <f t="shared" ref="M129:P129" si="55">M127*M128</f>
+        <f t="shared" ref="M129:P129" si="71">M127*M128</f>
         <v>0.36645122501127303</v>
       </c>
       <c r="N129" s="76">
-        <f t="shared" si="55"/>
+        <f t="shared" si="71"/>
         <v>0.19763811592235647</v>
       </c>
       <c r="O129" s="76">
-        <f t="shared" si="55"/>
+        <f t="shared" si="71"/>
         <v>0.69244729861789756</v>
       </c>
       <c r="P129" s="76">
-        <f t="shared" si="55"/>
+        <f t="shared" si="71"/>
         <v>0.91872880608115781</v>
       </c>
       <c r="Q129" s="76">
@@ -28205,35 +28095,35 @@
       <c r="P138" s="49"/>
       <c r="Q138" s="49"/>
       <c r="T138" s="25">
-        <f>U5</f>
+        <f t="shared" ref="T138:AA138" si="72">U5</f>
         <v>35082</v>
       </c>
       <c r="U138" s="25">
-        <f>V5</f>
+        <f t="shared" si="72"/>
         <v>39331</v>
       </c>
       <c r="V138" s="25">
-        <f>W5</f>
+        <f t="shared" si="72"/>
         <v>44062</v>
       </c>
       <c r="W138" s="25">
-        <f>X5</f>
+        <f t="shared" si="72"/>
         <v>46743</v>
       </c>
       <c r="X138" s="25">
-        <f>Y5</f>
+        <f t="shared" si="72"/>
         <v>57006</v>
       </c>
       <c r="Y138" s="25">
-        <f>Z5</f>
+        <f t="shared" si="72"/>
         <v>68127</v>
       </c>
       <c r="Z138" s="25">
-        <f>AA5</f>
+        <f t="shared" si="72"/>
         <v>81615</v>
       </c>
       <c r="AA138" s="25">
-        <f>AB5</f>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AC138" s="49"/>
@@ -28258,42 +28148,42 @@
       <c r="P139" s="49"/>
       <c r="Q139" s="49"/>
       <c r="T139" s="175" t="str">
-        <f>IF(T138&gt;T137, "BEAT", IF(T138&lt;T136, "MISSED", "MET"))</f>
+        <f t="shared" ref="T139:AA139" si="73">IF(T138&gt;T137, "BEAT", IF(T138&lt;T136, "MISSED", "MET"))</f>
         <v>BEAT</v>
       </c>
       <c r="U139" s="175" t="str">
-        <f>IF(U138&gt;U137, "BEAT", IF(U138&lt;U136, "MISSED", "MET"))</f>
+        <f t="shared" si="73"/>
         <v>BEAT</v>
       </c>
       <c r="V139" s="175" t="str">
-        <f>IF(V138&gt;V137, "BEAT", IF(V138&lt;V136, "MISSED", "MET"))</f>
+        <f t="shared" si="73"/>
         <v>BEAT</v>
       </c>
       <c r="W139" s="175" t="str">
-        <f>IF(W138&gt;W137, "BEAT", IF(W138&lt;W136, "MISSED", "MET"))</f>
+        <f t="shared" si="73"/>
         <v>BEAT</v>
       </c>
       <c r="X139" s="175" t="str">
-        <f>IF(X138&gt;X137, "BEAT", IF(X138&lt;X136, "MISSED", "MET"))</f>
+        <f t="shared" si="73"/>
         <v>BEAT</v>
       </c>
       <c r="Y139" s="175" t="str">
-        <f>IF(Y138&gt;Y137, "BEAT", IF(Y138&lt;Y136, "MISSED", "MET"))</f>
+        <f t="shared" si="73"/>
         <v>BEAT</v>
       </c>
       <c r="Z139" s="175" t="str">
-        <f>IF(Z138&gt;Z137, "BEAT", IF(Z138&lt;Z136, "MISSED", "MET"))</f>
+        <f t="shared" si="73"/>
         <v>BEAT</v>
       </c>
       <c r="AA139" s="175" t="str">
-        <f>IF(AA138&gt;AA137, "BEAT", IF(AA138&lt;AA136, "MISSED", "MET"))</f>
+        <f t="shared" si="73"/>
         <v>MISSED</v>
       </c>
       <c r="AC139" s="49"/>
     </row>
     <row r="140" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B140" s="20" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C140" s="49"/>
       <c r="D140" s="49"/>
@@ -28310,35 +28200,35 @@
       <c r="O140" s="49"/>
       <c r="P140" s="49"/>
       <c r="Q140" s="49"/>
-      <c r="T140" s="245">
+      <c r="T140" s="227">
         <v>0.73899999999999999</v>
       </c>
-      <c r="U140" s="245">
+      <c r="U140" s="227">
         <v>0.72499999999999998</v>
       </c>
-      <c r="V140" s="245">
+      <c r="V140" s="227">
         <v>0.70099999999999996</v>
       </c>
-      <c r="W140" s="245">
+      <c r="W140" s="227">
         <v>0.71299999999999997</v>
       </c>
-      <c r="X140" s="245">
+      <c r="X140" s="227">
         <v>0.72799999999999998</v>
       </c>
-      <c r="Y140" s="245">
+      <c r="Y140" s="227">
         <v>0.74299999999999999</v>
       </c>
-      <c r="Z140" s="245">
+      <c r="Z140" s="227">
         <v>0.745</v>
       </c>
-      <c r="AA140" s="245">
+      <c r="AA140" s="227">
         <v>0.745</v>
       </c>
       <c r="AC140" s="49"/>
     </row>
     <row r="141" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B141" s="20" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C141" s="49"/>
       <c r="D141" s="49"/>
@@ -28355,35 +28245,35 @@
       <c r="O141" s="49"/>
       <c r="P141" s="49"/>
       <c r="Q141" s="49"/>
-      <c r="T141" s="245">
+      <c r="T141" s="227">
         <v>0.749</v>
       </c>
-      <c r="U141" s="245">
+      <c r="U141" s="227">
         <v>0.73499999999999999</v>
       </c>
-      <c r="V141" s="245">
+      <c r="V141" s="227">
         <v>0.71099999999999997</v>
       </c>
-      <c r="W141" s="245">
+      <c r="W141" s="227">
         <v>0.72299999999999998</v>
       </c>
-      <c r="X141" s="245">
+      <c r="X141" s="227">
         <v>0.73799999999999999</v>
       </c>
-      <c r="Y141" s="245">
+      <c r="Y141" s="227">
         <v>0.754</v>
       </c>
-      <c r="Z141" s="245">
+      <c r="Z141" s="227">
         <v>0.754</v>
       </c>
-      <c r="AA141" s="245">
+      <c r="AA141" s="227">
         <v>0.754</v>
       </c>
       <c r="AC141" s="49"/>
     </row>
     <row r="142" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B142" s="20" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C142" s="49"/>
       <c r="D142" s="49"/>
@@ -28401,31 +28291,31 @@
       <c r="P142" s="49"/>
       <c r="Q142" s="49"/>
       <c r="T142" s="81">
-        <f t="shared" ref="T142:AA142" si="56">U98</f>
+        <f t="shared" ref="T142:Z142" si="74">U98</f>
         <v>0.74556752750698363</v>
       </c>
       <c r="U142" s="81">
-        <f t="shared" si="56"/>
+        <f t="shared" si="74"/>
         <v>0.73028908494571709</v>
       </c>
       <c r="V142" s="81">
-        <f t="shared" si="56"/>
+        <f t="shared" si="74"/>
         <v>0.60523807362353044</v>
       </c>
       <c r="W142" s="81">
-        <f t="shared" si="56"/>
+        <f t="shared" si="74"/>
         <v>0.72423678411740799</v>
       </c>
       <c r="X142" s="81">
-        <f t="shared" si="56"/>
+        <f t="shared" si="74"/>
         <v>0.7341157071185489</v>
       </c>
       <c r="Y142" s="81">
-        <f t="shared" si="56"/>
+        <f t="shared" si="74"/>
         <v>0.74996697344665109</v>
       </c>
       <c r="Z142" s="81">
-        <f t="shared" si="56"/>
+        <f t="shared" si="74"/>
         <v>0.74933529375727503</v>
       </c>
       <c r="AA142" s="81">
@@ -28454,42 +28344,42 @@
       <c r="P143" s="49"/>
       <c r="Q143" s="49"/>
       <c r="T143" s="175" t="str">
-        <f>IF(T142&gt;T141, "BEAT", IF(T142&lt;T140, "MISSED", "MET"))</f>
+        <f t="shared" ref="T143:AA143" si="75">IF(T142&gt;T141, "BEAT", IF(T142&lt;T140, "MISSED", "MET"))</f>
         <v>MET</v>
       </c>
       <c r="U143" s="175" t="str">
-        <f>IF(U142&gt;U141, "BEAT", IF(U142&lt;U140, "MISSED", "MET"))</f>
+        <f t="shared" si="75"/>
         <v>MET</v>
       </c>
       <c r="V143" s="175" t="str">
-        <f>IF(V142&gt;V141, "BEAT", IF(V142&lt;V140, "MISSED", "MET"))</f>
+        <f t="shared" si="75"/>
         <v>MISSED</v>
       </c>
       <c r="W143" s="175" t="str">
-        <f>IF(W142&gt;W141, "BEAT", IF(W142&lt;W140, "MISSED", "MET"))</f>
+        <f t="shared" si="75"/>
         <v>BEAT</v>
       </c>
       <c r="X143" s="175" t="str">
-        <f>IF(X142&gt;X141, "BEAT", IF(X142&lt;X140, "MISSED", "MET"))</f>
+        <f t="shared" si="75"/>
         <v>MET</v>
       </c>
       <c r="Y143" s="175" t="str">
-        <f>IF(Y142&gt;Y141, "BEAT", IF(Y142&lt;Y140, "MISSED", "MET"))</f>
+        <f t="shared" si="75"/>
         <v>MET</v>
       </c>
       <c r="Z143" s="175" t="str">
-        <f>IF(Z142&gt;Z141, "BEAT", IF(Z142&lt;Z140, "MISSED", "MET"))</f>
+        <f t="shared" si="75"/>
         <v>MET</v>
       </c>
       <c r="AA143" s="175" t="str">
-        <f>IF(AA142&gt;AA141, "BEAT", IF(AA142&lt;AA140, "MISSED", "MET"))</f>
+        <f t="shared" si="75"/>
         <v>MISSED</v>
       </c>
       <c r="AC143" s="49"/>
     </row>
     <row r="144" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B144" s="20" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C144" s="49"/>
       <c r="D144" s="49"/>
@@ -28534,7 +28424,7 @@
     </row>
     <row r="145" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B145" s="20" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C145" s="49"/>
       <c r="D145" s="49"/>
@@ -28579,7 +28469,7 @@
     </row>
     <row r="146" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B146" s="20" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C146" s="49"/>
       <c r="D146" s="49"/>
@@ -28597,31 +28487,31 @@
       <c r="P146" s="49"/>
       <c r="Q146" s="49"/>
       <c r="T146" s="25">
-        <f t="shared" ref="T146:AA146" si="57">U10</f>
+        <f t="shared" ref="T146:Z146" si="76">U10</f>
         <v>4287</v>
       </c>
       <c r="U146" s="25">
-        <f t="shared" si="57"/>
+        <f t="shared" si="76"/>
         <v>4689</v>
       </c>
       <c r="V146" s="25">
-        <f t="shared" si="57"/>
+        <f t="shared" si="76"/>
         <v>5030</v>
       </c>
       <c r="W146" s="25">
-        <f t="shared" si="57"/>
+        <f t="shared" si="76"/>
         <v>5413</v>
       </c>
       <c r="X146" s="25">
-        <f t="shared" si="57"/>
+        <f t="shared" si="76"/>
         <v>5839</v>
       </c>
       <c r="Y146" s="25">
-        <f t="shared" si="57"/>
+        <f t="shared" si="76"/>
         <v>6794</v>
       </c>
       <c r="Z146" s="25">
-        <f t="shared" si="57"/>
+        <f t="shared" si="76"/>
         <v>7621</v>
       </c>
       <c r="AA146" s="25">
@@ -28650,35 +28540,35 @@
       <c r="P147" s="49"/>
       <c r="Q147" s="49"/>
       <c r="T147" s="175" t="str">
-        <f>IF(T146&gt;T145, "BEAT", IF(T146&lt;T144, "MISSED", "MET"))</f>
+        <f t="shared" ref="T147:AA147" si="77">IF(T146&gt;T145, "BEAT", IF(T146&lt;T144, "MISSED", "MET"))</f>
         <v>MISSED</v>
       </c>
       <c r="U147" s="175" t="str">
-        <f>IF(U146&gt;U145, "BEAT", IF(U146&lt;U144, "MISSED", "MET"))</f>
+        <f t="shared" si="77"/>
         <v>MISSED</v>
       </c>
       <c r="V147" s="175" t="str">
-        <f>IF(V146&gt;V145, "BEAT", IF(V146&lt;V144, "MISSED", "MET"))</f>
+        <f t="shared" si="77"/>
         <v>MISSED</v>
       </c>
       <c r="W147" s="175" t="str">
-        <f>IF(W146&gt;W145, "BEAT", IF(W146&lt;W144, "MISSED", "MET"))</f>
+        <f t="shared" si="77"/>
         <v>MISSED</v>
       </c>
       <c r="X147" s="175" t="str">
-        <f>IF(X146&gt;X145, "BEAT", IF(X146&lt;X144, "MISSED", "MET"))</f>
+        <f t="shared" si="77"/>
         <v>MISSED</v>
       </c>
       <c r="Y147" s="175" t="str">
-        <f>IF(Y146&gt;Y145, "BEAT", IF(Y146&lt;Y144, "MISSED", "MET"))</f>
+        <f t="shared" si="77"/>
         <v>BEAT</v>
       </c>
       <c r="Z147" s="175" t="str">
-        <f>IF(Z146&gt;Z145, "BEAT", IF(Z146&lt;Z144, "MISSED", "MET"))</f>
+        <f t="shared" si="77"/>
         <v>MISSED</v>
       </c>
       <c r="AA147" s="175" t="str">
-        <f>IF(AA146&gt;AA145, "BEAT", IF(AA146&lt;AA144, "MISSED", "MET"))</f>
+        <f t="shared" si="77"/>
         <v>MISSED</v>
       </c>
       <c r="AC147" s="49"/>
@@ -28767,55 +28657,55 @@
         <v>131</v>
       </c>
       <c r="M152" s="119">
-        <f>M29/M5*365</f>
+        <f t="shared" ref="M152:Q153" si="78">M29/M5*365</f>
         <v>63.061975180203611</v>
       </c>
       <c r="N152" s="119">
-        <f>N29/N5*365</f>
+        <f t="shared" si="78"/>
         <v>51.785237636242307</v>
       </c>
       <c r="O152" s="119">
-        <f>O29/O5*365</f>
+        <f t="shared" si="78"/>
         <v>59.906683956534586</v>
       </c>
       <c r="P152" s="119">
-        <f>P29/P5*365</f>
+        <f t="shared" si="78"/>
         <v>64.512785734537957</v>
       </c>
       <c r="Q152" s="119">
-        <f>Q29/Q5*365</f>
+        <f t="shared" si="78"/>
         <v>65.01907955061175</v>
       </c>
       <c r="T152" s="119">
-        <f>T29/T5*90</f>
+        <f t="shared" ref="T152:AA152" si="79">T29/T5*90</f>
         <v>42.339547270306255</v>
       </c>
       <c r="U152" s="119">
-        <f>U29/U5*90</f>
+        <f t="shared" si="79"/>
         <v>45.389943560800411</v>
       </c>
       <c r="V152" s="119">
-        <f>V29/V5*90</f>
+        <f t="shared" si="79"/>
         <v>52.778978413973704</v>
       </c>
       <c r="W152" s="119">
-        <f>W29/W5*90</f>
+        <f t="shared" si="79"/>
         <v>45.206300213335751</v>
       </c>
       <c r="X152" s="119">
-        <f>X29/X5*90</f>
+        <f t="shared" si="79"/>
         <v>53.542134651177712</v>
       </c>
       <c r="Y152" s="119">
-        <f>Y29/Y5*90</f>
+        <f t="shared" si="79"/>
         <v>52.71708241237765</v>
       </c>
       <c r="Z152" s="119">
-        <f>Z29/Z5*90</f>
+        <f t="shared" si="79"/>
         <v>50.815976044739969</v>
       </c>
       <c r="AA152" s="119">
-        <f>AA29/AA5*90</f>
+        <f t="shared" si="79"/>
         <v>44.892482999448632</v>
       </c>
       <c r="AC152" s="119">
@@ -28828,55 +28718,55 @@
         <v>132</v>
       </c>
       <c r="M153" s="119">
-        <f>M30/M6*365</f>
+        <f t="shared" si="78"/>
         <v>100.73365822650703</v>
       </c>
       <c r="N153" s="119">
-        <f>N30/N6*365</f>
+        <f t="shared" si="78"/>
         <v>162.079101394388</v>
       </c>
       <c r="O153" s="119">
-        <f>O30/O6*365</f>
+        <f t="shared" si="78"/>
         <v>115.99362252572048</v>
       </c>
       <c r="P153" s="119">
-        <f>P30/P6*365</f>
+        <f t="shared" si="78"/>
         <v>112.72404179049603</v>
       </c>
       <c r="Q153" s="119">
-        <f>Q30/Q6*365</f>
+        <f t="shared" si="78"/>
         <v>125.043537414966</v>
       </c>
       <c r="T153" s="119">
-        <f>T30/T6*365</f>
+        <f t="shared" ref="T153:AA153" si="80">T30/T6*365</f>
         <v>326.32935976426467</v>
       </c>
       <c r="U153" s="119">
-        <f>U30/U6*365</f>
+        <f t="shared" si="80"/>
         <v>312.98565987004258</v>
       </c>
       <c r="V153" s="119">
-        <f>V30/V6*365</f>
+        <f t="shared" si="80"/>
         <v>346.83257918552033</v>
       </c>
       <c r="W153" s="119">
-        <f>W30/W6*365</f>
+        <f t="shared" si="80"/>
         <v>237.81447625618031</v>
       </c>
       <c r="X153" s="119">
-        <f>X30/X6*365</f>
+        <f t="shared" si="80"/>
         <v>423.67183863460048</v>
       </c>
       <c r="Y153" s="119">
-        <f>Y30/Y6*365</f>
+        <f t="shared" si="80"/>
         <v>476.42409447779909</v>
       </c>
       <c r="Z153" s="119">
-        <f>Z30/Z6*365</f>
+        <f t="shared" si="80"/>
         <v>458.61776447105791</v>
       </c>
       <c r="AA153" s="119">
-        <f>AA30/AA6*365</f>
+        <f t="shared" si="80"/>
         <v>460.25540131000093</v>
       </c>
       <c r="AC153" s="119">
@@ -28909,35 +28799,35 @@
         <v>57.325010004001605</v>
       </c>
       <c r="T154" s="119">
-        <f>T36/T6*90</f>
+        <f t="shared" ref="T154:AA154" si="81">T36/T6*90</f>
         <v>44.361103669970532</v>
       </c>
       <c r="U154" s="119">
-        <f>U36/U6*90</f>
+        <f t="shared" si="81"/>
         <v>53.973784449921581</v>
       </c>
       <c r="V154" s="119">
-        <f>V36/V6*90</f>
+        <f t="shared" si="81"/>
         <v>53.53506787330317</v>
       </c>
       <c r="W154" s="119">
-        <f>W36/W6*90</f>
+        <f t="shared" si="81"/>
         <v>37.932045532942396</v>
       </c>
       <c r="X154" s="119">
-        <f>X36/X6*90</f>
+        <f t="shared" si="81"/>
         <v>63.286268425135759</v>
       </c>
       <c r="Y154" s="119">
-        <f>Y36/Y6*90</f>
+        <f t="shared" si="81"/>
         <v>51.208022695784123</v>
       </c>
       <c r="Z154" s="119">
-        <f>Z36/Z6*90</f>
+        <f t="shared" si="81"/>
         <v>51.842197957027118</v>
       </c>
       <c r="AA154" s="119">
-        <f>AA36/AA6*90</f>
+        <f t="shared" si="81"/>
         <v>57.617069117215763</v>
       </c>
       <c r="AC154" s="119">
@@ -28954,55 +28844,55 @@
         <v>94.848181346110991</v>
       </c>
       <c r="N155" s="119">
-        <f t="shared" ref="N155:Q155" si="58">N152+N153-N154</f>
+        <f t="shared" ref="N155:Q155" si="82">N152+N153-N154</f>
         <v>176.38413589756092</v>
       </c>
       <c r="O155" s="119">
-        <f t="shared" si="58"/>
+        <f t="shared" si="82"/>
         <v>116.62980530904048</v>
       </c>
       <c r="P155" s="119">
-        <f t="shared" si="58"/>
+        <f t="shared" si="82"/>
         <v>106.67247199943577</v>
       </c>
       <c r="Q155" s="119">
-        <f t="shared" si="58"/>
+        <f t="shared" si="82"/>
         <v>132.73760696157615</v>
       </c>
       <c r="T155" s="119">
-        <f t="shared" ref="T155" si="59">T152+T153-T154</f>
+        <f t="shared" ref="T155" si="83">T152+T153-T154</f>
         <v>324.30780336460037</v>
       </c>
       <c r="U155" s="119">
-        <f t="shared" ref="U155" si="60">U152+U153-U154</f>
+        <f t="shared" ref="U155" si="84">U152+U153-U154</f>
         <v>304.40181898092141</v>
       </c>
       <c r="V155" s="119">
-        <f t="shared" ref="V155" si="61">V152+V153-V154</f>
+        <f t="shared" ref="V155" si="85">V152+V153-V154</f>
         <v>346.07648972619091</v>
       </c>
       <c r="W155" s="119">
-        <f t="shared" ref="W155" si="62">W152+W153-W154</f>
+        <f t="shared" ref="W155" si="86">W152+W153-W154</f>
         <v>245.08873093657368</v>
       </c>
       <c r="X155" s="119">
-        <f t="shared" ref="X155" si="63">X152+X153-X154</f>
+        <f t="shared" ref="X155" si="87">X152+X153-X154</f>
         <v>413.92770486064245</v>
       </c>
       <c r="Y155" s="119">
-        <f t="shared" ref="Y155" si="64">Y152+Y153-Y154</f>
+        <f t="shared" ref="Y155" si="88">Y152+Y153-Y154</f>
         <v>477.93315419439267</v>
       </c>
       <c r="Z155" s="119">
-        <f t="shared" ref="Z155:AA155" si="65">Z152+Z153-Z154</f>
+        <f t="shared" ref="Z155:AA155" si="89">Z152+Z153-Z154</f>
         <v>457.59154255877075</v>
       </c>
       <c r="AA155" s="119">
-        <f t="shared" si="65"/>
+        <f t="shared" si="89"/>
         <v>447.53081519223383</v>
       </c>
       <c r="AC155" s="119">
-        <f t="shared" ref="AC155" si="66">AC152+AC153-AC154</f>
+        <f t="shared" ref="AC155" si="90">AC152+AC153-AC154</f>
         <v>129.34693643390989</v>
       </c>
     </row>
@@ -29031,35 +28921,35 @@
         <v>5.3835835033981171E-2</v>
       </c>
       <c r="T156" s="119">
-        <f>T112/T47</f>
+        <f t="shared" ref="T156:AA156" si="91">T112/T47</f>
         <v>0.14548549615695444</v>
       </c>
       <c r="U156" s="119">
-        <f>U112/U47</f>
+        <f t="shared" si="91"/>
         <v>0.12840862532056632</v>
       </c>
       <c r="V156" s="119">
-        <f>V112/V47</f>
+        <f t="shared" si="91"/>
         <v>0.10668498745698186</v>
       </c>
       <c r="W156" s="119">
-        <f>W112/W47</f>
+        <f t="shared" si="91"/>
         <v>0.10095058621471083</v>
       </c>
       <c r="X156" s="119">
-        <f>X112/X47</f>
+        <f t="shared" si="91"/>
         <v>8.4549240494951619E-2</v>
       </c>
       <c r="Y156" s="119">
-        <f>Y112/Y47</f>
+        <f t="shared" si="91"/>
         <v>7.1212898559257179E-2</v>
       </c>
       <c r="Z156" s="119">
-        <f>Z112/Z47</f>
+        <f t="shared" si="91"/>
         <v>5.4471591234193512E-2</v>
       </c>
       <c r="AA156" s="119">
-        <f>AA112/AA47</f>
+        <f t="shared" si="91"/>
         <v>4.3330570817602339E-2</v>
       </c>
       <c r="AC156" s="119">
@@ -29092,35 +28982,35 @@
         <v>-0.34386781357085183</v>
       </c>
       <c r="T157" s="183">
-        <f>(T112-T111)/T47</f>
+        <f t="shared" ref="T157:AA157" si="92">(T112-T111)/T47</f>
         <v>-0.45289475041697475</v>
       </c>
       <c r="U157" s="183">
-        <f>(U112-U111)/U47</f>
+        <f t="shared" si="92"/>
         <v>-0.45562148135783548</v>
       </c>
       <c r="V157" s="183">
-        <f>(V112-V111)/V47</f>
+        <f t="shared" si="92"/>
         <v>-0.43802236312982967</v>
       </c>
       <c r="W157" s="183">
-        <f>(W112-W111)/W47</f>
+        <f t="shared" si="92"/>
         <v>-0.53942487744951872</v>
       </c>
       <c r="X157" s="183">
-        <f>(X112-X111)/X47</f>
+        <f t="shared" si="92"/>
         <v>-0.48261777072035633</v>
       </c>
       <c r="Y157" s="183">
-        <f>(Y112-Y111)/Y47</f>
+        <f t="shared" si="92"/>
         <v>-0.43853923984625348</v>
       </c>
       <c r="Z157" s="183">
-        <f>(Z112-Z111)/Z47</f>
+        <f t="shared" si="92"/>
         <v>-0.3432320573706395</v>
       </c>
       <c r="AA157" s="183">
-        <f>(AA112-AA111)/AA47</f>
+        <f t="shared" si="92"/>
         <v>-0.36885723932594616</v>
       </c>
       <c r="AC157" s="183">
@@ -29153,35 +29043,35 @@
         <v>3.1409383453036099</v>
       </c>
       <c r="T158" s="119">
-        <f>(T111+T29)/T38</f>
+        <f t="shared" ref="T158:AA158" si="93">(T111+T29)/T38</f>
         <v>3.5028992769704344</v>
       </c>
       <c r="U158" s="119">
-        <f>(U111+U29)/U38</f>
+        <f t="shared" si="93"/>
         <v>3.4091874506948239</v>
       </c>
       <c r="V158" s="119">
-        <f>(V111+V29)/V38</f>
+        <f t="shared" si="93"/>
         <v>3.672355516152269</v>
       </c>
       <c r="W158" s="119">
-        <f>(W111+W29)/W38</f>
+        <f t="shared" si="93"/>
         <v>2.8567176550372992</v>
       </c>
       <c r="X158" s="119">
-        <f>(X111+X29)/X38</f>
+        <f t="shared" si="93"/>
         <v>3.4876118233911861</v>
       </c>
       <c r="Y158" s="119">
-        <f>(Y111+Y29)/Y38</f>
+        <f t="shared" si="93"/>
         <v>3.6049472674976029</v>
       </c>
       <c r="Z158" s="119">
-        <f>(Z111+Z29)/Z38</f>
+        <f t="shared" si="93"/>
         <v>3.1409383453036099</v>
       </c>
       <c r="AA158" s="119">
-        <f>(AA111+AA29)/AA38</f>
+        <f t="shared" si="93"/>
         <v>2.7636951964269438</v>
       </c>
       <c r="AC158" s="119">
@@ -29214,35 +29104,35 @@
         <v>3.9052638124553058</v>
       </c>
       <c r="T159" s="119">
-        <f>T31/T38</f>
+        <f t="shared" ref="T159:AA159" si="94">T31/T38</f>
         <v>4.2689526809363594</v>
       </c>
       <c r="U159" s="119">
-        <f>U31/U38</f>
+        <f t="shared" si="94"/>
         <v>4.1046179986649678</v>
       </c>
       <c r="V159" s="119">
-        <f>V31/V38</f>
+        <f t="shared" si="94"/>
         <v>4.4398514988640772</v>
       </c>
       <c r="W159" s="119">
-        <f>W31/W38</f>
+        <f t="shared" si="94"/>
         <v>3.3884032853590536</v>
       </c>
       <c r="X159" s="119">
-        <f>X31/X38</f>
+        <f t="shared" si="94"/>
         <v>4.2140000824504265</v>
       </c>
       <c r="Y159" s="119">
-        <f>Y31/Y38</f>
+        <f t="shared" si="94"/>
         <v>4.4675743048897409</v>
       </c>
       <c r="Z159" s="119">
-        <f>Z31/Z38</f>
+        <f t="shared" si="94"/>
         <v>3.9052638124553058</v>
       </c>
       <c r="AA159" s="119">
-        <f>AA31/AA38</f>
+        <f t="shared" si="94"/>
         <v>3.440775681341719</v>
       </c>
       <c r="AC159" s="119">
@@ -29275,35 +29165,35 @@
         <v>N/A</v>
       </c>
       <c r="T160" s="185" t="str">
-        <f>IF(T12&gt;=0,"N/A",IF(T11&lt;=0,"N/A",T11/-T12))</f>
+        <f t="shared" ref="T160:AA160" si="95">IF(T12&gt;=0,"N/A",IF(T11&lt;=0,"N/A",T11/-T12))</f>
         <v>N/A</v>
       </c>
       <c r="U160" s="185" t="str">
-        <f>IF(U12&gt;=0,"N/A",IF(U11&lt;=0,"N/A",U11/-U12))</f>
+        <f t="shared" si="95"/>
         <v>N/A</v>
       </c>
       <c r="V160" s="185" t="str">
-        <f>IF(V12&gt;=0,"N/A",IF(V11&lt;=0,"N/A",V11/-V12))</f>
+        <f t="shared" si="95"/>
         <v>N/A</v>
       </c>
       <c r="W160" s="185" t="str">
-        <f>IF(W12&gt;=0,"N/A",IF(W11&lt;=0,"N/A",W11/-W12))</f>
+        <f t="shared" si="95"/>
         <v>N/A</v>
       </c>
       <c r="X160" s="185" t="str">
-        <f>IF(X12&gt;=0,"N/A",IF(X11&lt;=0,"N/A",X11/-X12))</f>
+        <f t="shared" si="95"/>
         <v>N/A</v>
       </c>
       <c r="Y160" s="185" t="str">
-        <f>IF(Y12&gt;=0,"N/A",IF(Y11&lt;=0,"N/A",Y11/-Y12))</f>
+        <f t="shared" si="95"/>
         <v>N/A</v>
       </c>
       <c r="Z160" s="185" t="str">
-        <f>IF(Z12&gt;=0,"N/A",IF(Z11&lt;=0,"N/A",Z11/-Z12))</f>
+        <f t="shared" si="95"/>
         <v>N/A</v>
       </c>
       <c r="AA160" s="185" t="str">
-        <f>IF(AA12&gt;=0,"N/A",IF(AA11&lt;=0,"N/A",AA11/-AA12))</f>
+        <f t="shared" si="95"/>
         <v>N/A</v>
       </c>
       <c r="AC160" s="185" t="str">
@@ -29595,35 +29485,35 @@
         <v>90290</v>
       </c>
       <c r="T168" s="64">
-        <f>T57-T52+T114+T63</f>
+        <f t="shared" ref="T168:AA168" si="96">T57-T52+T114+T63</f>
         <v>12358</v>
       </c>
       <c r="U168" s="64">
-        <f>U57-U52+U114+U63</f>
+        <f t="shared" si="96"/>
         <v>15564</v>
       </c>
       <c r="V168" s="64">
-        <f>V57-V52+V114+V63</f>
+        <f t="shared" si="96"/>
         <v>14230</v>
       </c>
       <c r="W168" s="64">
-        <f>W57-W52+W114+W63</f>
+        <f t="shared" si="96"/>
         <v>24713</v>
       </c>
       <c r="X168" s="64">
-        <f>X57-X52+X114+X63</f>
+        <f t="shared" si="96"/>
         <v>11847</v>
       </c>
       <c r="Y168" s="64">
-        <f>Y57-Y52+Y114+Y63</f>
+        <f t="shared" si="96"/>
         <v>20458</v>
       </c>
       <c r="Z168" s="64">
-        <f>Z57-Z52+Z114+Z63</f>
+        <f t="shared" si="96"/>
         <v>33273</v>
       </c>
       <c r="AA168" s="64">
-        <f>AA57-AA52+AA114+AA63</f>
+        <f t="shared" si="96"/>
         <v>46659</v>
       </c>
       <c r="AC168" s="64">
@@ -29677,19 +29567,19 @@
         <v>95.00515665796344</v>
       </c>
       <c r="N170" s="72">
-        <f t="shared" ref="N170:Q170" si="67">N164/N168</f>
+        <f t="shared" ref="N170:Q170" si="97">N164/N168</f>
         <v>461.29572338489538</v>
       </c>
       <c r="O170" s="72">
-        <f t="shared" si="67"/>
+        <f t="shared" si="97"/>
         <v>65.653012099522826</v>
       </c>
       <c r="P170" s="72">
-        <f t="shared" si="67"/>
+        <f t="shared" si="97"/>
         <v>62.645954451493331</v>
       </c>
       <c r="Q170" s="72">
-        <f t="shared" si="67"/>
+        <f t="shared" si="97"/>
         <v>50.830322848598954</v>
       </c>
       <c r="T170" s="49"/>
@@ -29701,7 +29591,7 @@
       <c r="Z170" s="49"/>
       <c r="AA170" s="49"/>
       <c r="AC170" s="72">
-        <f t="shared" ref="AC170:AC171" ca="1" si="68">AC164/AC168</f>
+        <f t="shared" ref="AC170:AC171" ca="1" si="98">AC164/AC168</f>
         <v>44.414546896299797</v>
       </c>
     </row>
@@ -29714,19 +29604,19 @@
         <v>85.552901846404438</v>
       </c>
       <c r="N171" s="72">
-        <f t="shared" ref="N171:Q171" si="69">N165/N169</f>
+        <f t="shared" ref="N171:Q171" si="99">N165/N169</f>
         <v>292.02604166666669</v>
       </c>
       <c r="O171" s="72">
-        <f t="shared" si="69"/>
+        <f t="shared" si="99"/>
         <v>59.253144937486333</v>
       </c>
       <c r="P171" s="72">
-        <f t="shared" si="69"/>
+        <f t="shared" si="99"/>
         <v>58.114897258120507</v>
       </c>
       <c r="Q171" s="72">
-        <f t="shared" si="69"/>
+        <f t="shared" si="99"/>
         <v>49.56625962229554</v>
       </c>
       <c r="T171" s="49"/>
@@ -29738,7 +29628,7 @@
       <c r="Z171" s="49"/>
       <c r="AA171" s="49"/>
       <c r="AC171" s="72">
-        <f t="shared" ca="1" si="68"/>
+        <f t="shared" ca="1" si="98"/>
         <v>38.739993479789511</v>
       </c>
     </row>
@@ -29751,19 +29641,19 @@
         <v>1.0525744445642981E-2</v>
       </c>
       <c r="N172" s="74">
-        <f t="shared" ref="N172:Q172" si="70">N168/N164</f>
+        <f t="shared" ref="N172:Q172" si="100">N168/N164</f>
         <v>2.1678067870696933E-3</v>
       </c>
       <c r="O172" s="74">
-        <f t="shared" si="70"/>
+        <f t="shared" si="100"/>
         <v>1.5231593616513875E-2</v>
       </c>
       <c r="P172" s="74">
-        <f t="shared" si="70"/>
+        <f t="shared" si="100"/>
         <v>1.5962722712993357E-2</v>
       </c>
       <c r="Q172" s="74">
-        <f t="shared" si="70"/>
+        <f t="shared" si="100"/>
         <v>1.9673296252289359E-2</v>
       </c>
       <c r="T172" s="49"/>
@@ -29775,7 +29665,7 @@
       <c r="Z172" s="49"/>
       <c r="AA172" s="49"/>
       <c r="AC172" s="74">
-        <f t="shared" ref="AC172" ca="1" si="71">AC168/AC164</f>
+        <f t="shared" ref="AC172" ca="1" si="101">AC168/AC164</f>
         <v>2.2515145822264611E-2</v>
       </c>
     </row>
@@ -29855,7 +29745,7 @@
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B175" s="20" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="M175" s="156">
         <f>-M61/M164</f>
@@ -29892,7 +29782,7 @@
     </row>
     <row r="176" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B176" s="20" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="M176" s="156">
         <f>-(M61+M62)/M164</f>
@@ -29929,25 +29819,25 @@
     </row>
     <row r="177" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B177" s="20" t="s">
-        <v>268</v>
-      </c>
-      <c r="M177" s="72">
+        <v>387</v>
+      </c>
+      <c r="M177" s="230">
         <f>M169/M5</f>
         <v>0.24838741111758303</v>
       </c>
-      <c r="N177" s="72">
+      <c r="N177" s="230">
         <f>N169/N5</f>
         <v>6.4061689033884484E-2</v>
       </c>
-      <c r="O177" s="72">
+      <c r="O177" s="230">
         <f>O169/O5</f>
         <v>0.42238462291779383</v>
       </c>
-      <c r="P177" s="72">
+      <c r="P177" s="230">
         <f>P169/P5</f>
         <v>0.45896309457389761</v>
       </c>
-      <c r="Q177" s="72">
+      <c r="Q177" s="230">
         <f>Q169/Q5</f>
         <v>0.42373919358213857</v>
       </c>
@@ -29959,34 +29849,34 @@
       <c r="Y177" s="49"/>
       <c r="Z177" s="49"/>
       <c r="AA177" s="49"/>
-      <c r="AC177" s="72">
+      <c r="AC177" s="156">
         <f>AC169/AC5</f>
         <v>0.50027836962176253</v>
       </c>
     </row>
     <row r="178" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B178" s="20" t="s">
-        <v>271</v>
-      </c>
-      <c r="M178" s="156">
-        <f>-M62/M168</f>
-        <v>6.5110966057441252E-2</v>
-      </c>
-      <c r="N178" s="156">
-        <f>-N62/N168</f>
-        <v>0.36214740673339402</v>
-      </c>
-      <c r="O178" s="156">
-        <f>-O62/O168</f>
-        <v>1.6828561690524879E-2</v>
-      </c>
-      <c r="P178" s="156">
-        <f>-P62/P168</f>
-        <v>1.4862071423479934E-2</v>
-      </c>
-      <c r="Q178" s="156">
-        <f>-Q62/Q168</f>
-        <v>1.0787462620445233E-2</v>
+        <v>388</v>
+      </c>
+      <c r="M178" s="230">
+        <f>M168/M5</f>
+        <v>0.22768819201902354</v>
+      </c>
+      <c r="N178" s="230">
+        <f t="shared" ref="N178:Q178" si="102">N168/N5</f>
+        <v>4.0742937643656857E-2</v>
+      </c>
+      <c r="O178" s="230">
+        <f t="shared" si="102"/>
+        <v>0.38527953776960705</v>
+      </c>
+      <c r="P178" s="230">
+        <f t="shared" si="102"/>
+        <v>0.43001754829612943</v>
+      </c>
+      <c r="Q178" s="230">
+        <f t="shared" si="102"/>
+        <v>0.41812927784827125</v>
       </c>
       <c r="T178" s="49"/>
       <c r="U178" s="49"/>
@@ -29997,33 +29887,33 @@
       <c r="Z178" s="49"/>
       <c r="AA178" s="49"/>
       <c r="AC178" s="156">
-        <f>-AC62/AC168</f>
-        <v>8.6691554478469674E-3</v>
+        <f t="shared" ref="AC178" si="103">AC168/AC5</f>
+        <v>0.4427652263788458</v>
       </c>
     </row>
     <row r="179" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B179" s="20" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="M179" s="156">
-        <f>-M61/M168</f>
-        <v>0</v>
+        <f>-M62/M168</f>
+        <v>6.5110966057441252E-2</v>
       </c>
       <c r="N179" s="156">
-        <f>-N61/N168</f>
-        <v>9.1346678798908094</v>
+        <f>-N62/N168</f>
+        <v>0.36214740673339402</v>
       </c>
       <c r="O179" s="156">
-        <f>-O61/O168</f>
-        <v>0.40614349011588274</v>
+        <f>-O62/O168</f>
+        <v>1.6828561690524879E-2</v>
       </c>
       <c r="P179" s="156">
-        <f>-P61/P168</f>
-        <v>0.60064865635469389</v>
+        <f>-P62/P168</f>
+        <v>1.4862071423479934E-2</v>
       </c>
       <c r="Q179" s="156">
-        <f>-Q61/Q168</f>
-        <v>0.44396943183076754</v>
+        <f>-Q62/Q168</f>
+        <v>1.0787462620445233E-2</v>
       </c>
       <c r="T179" s="49"/>
       <c r="U179" s="49"/>
@@ -30034,33 +29924,33 @@
       <c r="Z179" s="49"/>
       <c r="AA179" s="49"/>
       <c r="AC179" s="156">
-        <f>-AC61/AC168</f>
-        <v>0.40364585653572349</v>
+        <f>-AC62/AC168</f>
+        <v>8.6691554478469674E-3</v>
       </c>
     </row>
     <row r="180" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B180" s="20" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="M180" s="156">
-        <f>(-M62-M61)/M168</f>
-        <v>6.5110966057441252E-2</v>
+        <f>-M61/M168</f>
+        <v>0</v>
       </c>
       <c r="N180" s="156">
-        <f>(-N62-N61)/N168</f>
-        <v>9.4968152866242033</v>
+        <f>-N61/N168</f>
+        <v>9.1346678798908094</v>
       </c>
       <c r="O180" s="156">
-        <f>(-O62-O61)/O168</f>
-        <v>0.42297205180640762</v>
+        <f>-O61/O168</f>
+        <v>0.40614349011588274</v>
       </c>
       <c r="P180" s="156">
-        <f>(-P62-P61)/P168</f>
-        <v>0.61551072777817373</v>
+        <f>-P61/P168</f>
+        <v>0.60064865635469389</v>
       </c>
       <c r="Q180" s="156">
-        <f>(-Q62-Q61)/Q168</f>
-        <v>0.45475689445121276</v>
+        <f>-Q61/Q168</f>
+        <v>0.44396943183076754</v>
       </c>
       <c r="T180" s="49"/>
       <c r="U180" s="49"/>
@@ -30071,33 +29961,33 @@
       <c r="Z180" s="49"/>
       <c r="AA180" s="49"/>
       <c r="AC180" s="156">
-        <f>(-AC62-AC61)/AC168</f>
-        <v>0.41231501198357046</v>
+        <f>-AC61/AC168</f>
+        <v>0.40364585653572349</v>
       </c>
     </row>
     <row r="181" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B181" s="20" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="M181" s="156">
-        <f>M78/M76</f>
-        <v>3.9623381718320909E-2</v>
+        <f>(-M62-M61)/M168</f>
+        <v>6.5110966057441252E-2</v>
       </c>
       <c r="N181" s="156">
-        <f>N78/N76</f>
-        <v>3.9759036144578312E-2</v>
+        <f>(-N62-N61)/N168</f>
+        <v>9.4968152866242033</v>
       </c>
       <c r="O181" s="156">
-        <f>O78/O76</f>
-        <v>4.118811881188119E-2</v>
+        <f>(-O62-O61)/O168</f>
+        <v>0.42297205180640762</v>
       </c>
       <c r="P181" s="156">
-        <f>P78/P76</f>
-        <v>4.1380989086778369E-2</v>
+        <f>(-P62-P61)/P168</f>
+        <v>0.61551072777817373</v>
       </c>
       <c r="Q181" s="156">
-        <f>Q78/Q76</f>
-        <v>3.9133101615211614E-2</v>
+        <f>(-Q62-Q61)/Q168</f>
+        <v>0.45475689445121276</v>
       </c>
       <c r="T181" s="49"/>
       <c r="U181" s="49"/>
@@ -30108,877 +29998,914 @@
       <c r="Z181" s="49"/>
       <c r="AA181" s="49"/>
       <c r="AC181" s="156">
+        <f>(-AC62-AC61)/AC168</f>
+        <v>0.41231501198357046</v>
+      </c>
+    </row>
+    <row r="182" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B182" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="M182" s="156">
+        <f>M78/M76</f>
+        <v>3.9623381718320909E-2</v>
+      </c>
+      <c r="N182" s="156">
+        <f>N78/N76</f>
+        <v>3.9759036144578312E-2</v>
+      </c>
+      <c r="O182" s="156">
+        <f>O78/O76</f>
+        <v>4.118811881188119E-2</v>
+      </c>
+      <c r="P182" s="156">
+        <f>P78/P76</f>
+        <v>4.1380989086778369E-2</v>
+      </c>
+      <c r="Q182" s="156">
+        <f>Q78/Q76</f>
+        <v>3.9133101615211614E-2</v>
+      </c>
+      <c r="T182" s="49"/>
+      <c r="U182" s="49"/>
+      <c r="V182" s="49"/>
+      <c r="W182" s="49"/>
+      <c r="X182" s="49"/>
+      <c r="Y182" s="49"/>
+      <c r="Z182" s="49"/>
+      <c r="AA182" s="49"/>
+      <c r="AC182" s="156">
         <f>AC78/AC76</f>
         <v>3.9374614276897757E-2</v>
       </c>
     </row>
-    <row r="182" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B182" s="20" t="s">
-        <v>279</v>
-      </c>
-      <c r="M182" s="72">
+    <row r="183" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B183" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="M183" s="72">
         <f>M111/M73</f>
         <v>0.84494023904382465</v>
       </c>
-      <c r="N182" s="72">
+      <c r="N183" s="72">
         <f>N111/N73</f>
         <v>0.53829959514170045</v>
       </c>
-      <c r="O182" s="72">
+      <c r="O183" s="72">
         <f>O111/O73</f>
         <v>1.0393600000000001</v>
       </c>
-      <c r="P182" s="72">
+      <c r="P183" s="72">
         <f>P111/P73</f>
         <v>1.7709016393442623</v>
       </c>
-      <c r="Q182" s="72">
+      <c r="Q183" s="72">
         <f>Q111/Q73</f>
         <v>2.5743209876543212</v>
       </c>
-      <c r="T182" s="72">
-        <f>T111/T73</f>
+      <c r="T183" s="72">
+        <f t="shared" ref="T183:AA183" si="104">T111/T73</f>
         <v>1.4186710150835711</v>
       </c>
-      <c r="U182" s="72">
-        <f>U111/U73</f>
+      <c r="U183" s="72">
+        <f t="shared" si="104"/>
         <v>1.5715394038383013</v>
       </c>
-      <c r="V182" s="72">
-        <f>V111/V73</f>
+      <c r="V183" s="72">
+        <f t="shared" si="104"/>
         <v>1.7709016393442623</v>
       </c>
-      <c r="W182" s="72">
-        <f>W111/W73</f>
+      <c r="W183" s="72">
+        <f t="shared" si="104"/>
         <v>2.2004508196721311</v>
       </c>
-      <c r="X182" s="72">
-        <f>X111/X73</f>
+      <c r="X183" s="72">
+        <f t="shared" si="104"/>
         <v>2.3370781893004113</v>
       </c>
-      <c r="Y182" s="72">
-        <f>Y111/Y73</f>
+      <c r="Y183" s="72">
+        <f t="shared" si="104"/>
         <v>2.494156378600823</v>
       </c>
-      <c r="Z182" s="72">
-        <f>Z111/Z73</f>
+      <c r="Z183" s="72">
+        <f t="shared" si="104"/>
         <v>2.5743209876543212</v>
       </c>
-      <c r="AA182" s="72">
-        <f>AA111/AA73</f>
+      <c r="AA183" s="72">
+        <f t="shared" si="104"/>
         <v>3.3294214876033057</v>
       </c>
-      <c r="AC182" s="72">
+      <c r="AC183" s="72">
         <f>AC111/AC73</f>
         <v>3.3294214876033057</v>
       </c>
     </row>
-    <row r="183" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B183" s="20" t="s">
-        <v>281</v>
-      </c>
-      <c r="M183" s="156">
+    <row r="184" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B184" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="M184" s="156">
         <f>M52/M57</f>
         <v>0.22002635046113306</v>
       </c>
-      <c r="N183" s="156">
+      <c r="N184" s="156">
         <f>N52/N57</f>
         <v>0.48023400106364122</v>
       </c>
-      <c r="O183" s="156">
+      <c r="O184" s="156">
         <f>O52/O57</f>
         <v>0.1263438946244215</v>
       </c>
-      <c r="P183" s="156">
+      <c r="P184" s="156">
         <f>P52/P57</f>
         <v>7.3912839956934887E-2</v>
       </c>
-      <c r="Q183" s="156">
+      <c r="Q184" s="156">
         <f>Q52/Q57</f>
         <v>6.217021359450145E-2</v>
       </c>
-      <c r="T183" s="156">
-        <f>T52/T57</f>
+      <c r="T184" s="156">
+        <f t="shared" ref="T184:AA184" si="105">T52/T57</f>
         <v>7.9646628476775491E-2</v>
       </c>
-      <c r="U183" s="156">
-        <f>U52/U57</f>
+      <c r="U184" s="156">
+        <f t="shared" si="105"/>
         <v>7.1019343127800783E-2</v>
       </c>
-      <c r="V183" s="156">
-        <f>V52/V57</f>
+      <c r="V184" s="156">
+        <f t="shared" si="105"/>
         <v>7.944431080105846E-2</v>
       </c>
-      <c r="W183" s="156">
-        <f>W52/W57</f>
+      <c r="W184" s="156">
+        <f t="shared" si="105"/>
         <v>5.3768147661778655E-2</v>
       </c>
-      <c r="X183" s="156">
-        <f>X52/X57</f>
+      <c r="X184" s="156">
+        <f t="shared" si="105"/>
         <v>0.10569476082004556</v>
       </c>
-      <c r="Y183" s="156">
-        <f>Y52/Y57</f>
+      <c r="Y184" s="156">
+        <f t="shared" si="105"/>
         <v>6.9684210526315793E-2</v>
       </c>
-      <c r="Z183" s="156">
-        <f>Z52/Z57</f>
+      <c r="Z184" s="156">
+        <f t="shared" si="105"/>
         <v>4.5122962144238742E-2</v>
       </c>
-      <c r="AA183" s="156">
-        <f>AA52/AA57</f>
+      <c r="AA184" s="156">
+        <f t="shared" si="105"/>
         <v>3.829651994279358E-2</v>
       </c>
-      <c r="AC183" s="156">
+      <c r="AC184" s="156">
         <f>AC52/AC57</f>
         <v>5.4437361220542942E-2</v>
       </c>
     </row>
-    <row r="184" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B184" s="20" t="s">
-        <v>282</v>
-      </c>
-      <c r="M184" s="156">
+    <row r="185" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B185" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="M185" s="156">
         <f>M52/M5</f>
         <v>7.4459389165490081E-2</v>
       </c>
-      <c r="N184" s="156">
+      <c r="N185" s="156">
         <f>N52/N5</f>
         <v>0.10043004374582931</v>
       </c>
-      <c r="O184" s="156">
+      <c r="O185" s="156">
         <f>O52/O5</f>
         <v>5.8254817635665278E-2</v>
       </c>
-      <c r="P184" s="156">
+      <c r="P185" s="156">
         <f>P52/P5</f>
         <v>3.629968505023104E-2</v>
       </c>
-      <c r="Q184" s="156">
+      <c r="Q185" s="156">
         <f>Q52/Q5</f>
         <v>2.9573303448211987E-2</v>
       </c>
-      <c r="T184" s="156">
-        <f>T52/T5</f>
+      <c r="T185" s="156">
+        <f t="shared" ref="T185:AA185" si="106">T52/T5</f>
         <v>3.8415446071904127E-2</v>
       </c>
-      <c r="U184" s="156">
-        <f>U52/U5</f>
+      <c r="U185" s="156">
+        <f t="shared" si="106"/>
         <v>3.5687817114189613E-2</v>
       </c>
-      <c r="V184" s="156">
-        <f>V52/V5</f>
+      <c r="V185" s="156">
+        <f t="shared" si="106"/>
         <v>3.3586738196333683E-2</v>
       </c>
-      <c r="W184" s="156">
-        <f>W52/W5</f>
+      <c r="W185" s="156">
+        <f t="shared" si="106"/>
         <v>3.3452861876446825E-2</v>
       </c>
-      <c r="X184" s="156">
-        <f>X52/X5</f>
+      <c r="X185" s="156">
+        <f t="shared" si="106"/>
         <v>3.4743170100335882E-2</v>
       </c>
-      <c r="Y184" s="156">
-        <f>Y52/Y5</f>
+      <c r="Y185" s="156">
+        <f t="shared" si="106"/>
         <v>2.9032031715959722E-2</v>
       </c>
-      <c r="Z184" s="156">
-        <f>Z52/Z5</f>
+      <c r="Z185" s="156">
+        <f t="shared" si="106"/>
         <v>2.3969938497218429E-2</v>
       </c>
-      <c r="AA184" s="156">
-        <f>AA52/AA5</f>
+      <c r="AA185" s="156">
+        <f t="shared" si="106"/>
         <v>2.3623108497212521E-2</v>
       </c>
-      <c r="AC184" s="156">
+      <c r="AC185" s="156">
         <f>AC52/AC5</f>
         <v>2.6983206504372935E-2</v>
       </c>
     </row>
-    <row r="185" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B185" s="20" t="s">
-        <v>287</v>
-      </c>
-      <c r="M185" s="72">
+    <row r="186" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B186" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="M186" s="72">
         <f>(M111-M112)/M73</f>
         <v>0.40884462151394424</v>
       </c>
-      <c r="N185" s="72">
+      <c r="N186" s="72">
         <f>(N111-N112)/N73</f>
         <v>9.4858299595141707E-2</v>
       </c>
-      <c r="O185" s="72">
+      <c r="O186" s="72">
         <f>(O111-O112)/O73</f>
         <v>0.65100000000000002</v>
       </c>
-      <c r="P185" s="72">
+      <c r="P186" s="72">
         <f>(P111-P112)/P73</f>
         <v>1.4240573770491802</v>
       </c>
-      <c r="Q185" s="72">
+      <c r="Q186" s="72">
         <f>(Q111-Q112)/Q73</f>
         <v>2.2258436213991768</v>
       </c>
-      <c r="T185" s="72">
-        <f>(T111-T112)/T73</f>
+      <c r="T186" s="72">
+        <f t="shared" ref="T186:AA186" si="107">(T111-T112)/T73</f>
         <v>1.0737464329392581</v>
       </c>
-      <c r="U185" s="72">
-        <f>(U111-U112)/U73</f>
+      <c r="U186" s="72">
+        <f t="shared" si="107"/>
         <v>1.2260106165781952</v>
       </c>
-      <c r="V185" s="72">
-        <f>(V111-V112)/V73</f>
+      <c r="V186" s="72">
+        <f t="shared" si="107"/>
         <v>1.4240573770491802</v>
       </c>
-      <c r="W185" s="72">
-        <f>(W111-W112)/W73</f>
+      <c r="W186" s="72">
+        <f t="shared" si="107"/>
         <v>1.8535655737704917</v>
       </c>
-      <c r="X185" s="72">
-        <f>(X111-X112)/X73</f>
+      <c r="X186" s="72">
+        <f t="shared" si="107"/>
         <v>1.9886831275720165</v>
       </c>
-      <c r="Y185" s="72">
-        <f>(Y111-Y112)/Y73</f>
+      <c r="Y186" s="72">
+        <f t="shared" si="107"/>
         <v>2.1457201646090533</v>
       </c>
-      <c r="Z185" s="72">
-        <f>(Z111-Z112)/Z73</f>
+      <c r="Z186" s="72">
+        <f t="shared" si="107"/>
         <v>2.2217283950617284</v>
       </c>
-      <c r="AA185" s="72">
-        <f>(AA111-AA112)/AA73</f>
+      <c r="AA186" s="72">
+        <f t="shared" si="107"/>
         <v>2.9794214876033056</v>
       </c>
-      <c r="AC185" s="72">
+      <c r="AC186" s="72">
         <f>(AC111-AC112)/AC73</f>
         <v>2.9794214876033056</v>
       </c>
     </row>
-    <row r="186" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B186" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="M186" s="156">
+    <row r="187" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B187" s="20" t="s">
+        <v>291</v>
+      </c>
+      <c r="M187" s="156">
         <f>(M111-M112)/M164</f>
         <v>1.7626499592230463E-2</v>
       </c>
-      <c r="N186" s="156">
+      <c r="N187" s="156">
         <f>(N111-N112)/N164</f>
         <v>4.6216299382204652E-3</v>
       </c>
-      <c r="O186" s="156">
+      <c r="O187" s="156">
         <f>(O111-O112)/O164</f>
         <v>1.0561272414313365E-2</v>
       </c>
-      <c r="P186" s="156">
+      <c r="P187" s="156">
         <f>(P111-P112)/P164</f>
         <v>9.8841101665902813E-3</v>
       </c>
-      <c r="Q186" s="156">
+      <c r="Q187" s="156">
         <f>(Q111-Q112)/Q164</f>
         <v>1.1785239203608671E-2</v>
       </c>
-      <c r="T186" s="49"/>
-      <c r="U186" s="49"/>
-      <c r="V186" s="49"/>
-      <c r="W186" s="49"/>
-      <c r="X186" s="49"/>
-      <c r="Y186" s="49"/>
-      <c r="Z186" s="49"/>
-      <c r="AA186" s="49"/>
-      <c r="AC186" s="156">
+      <c r="T187" s="49"/>
+      <c r="U187" s="49"/>
+      <c r="V187" s="49"/>
+      <c r="W187" s="49"/>
+      <c r="X187" s="49"/>
+      <c r="Y187" s="49"/>
+      <c r="Z187" s="49"/>
+      <c r="AA187" s="49"/>
+      <c r="AC187" s="156">
         <f ca="1">(AC111-AC112)/AC164</f>
         <v>1.4463920490363455E-2</v>
       </c>
     </row>
-    <row r="187" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B187" s="20" t="s">
-        <v>301</v>
-      </c>
-      <c r="M187" s="156">
+    <row r="188" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B188" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="M188" s="156">
         <f>-M114/M5</f>
         <v>3.6263654603552055E-2</v>
       </c>
-      <c r="N187" s="156">
+      <c r="N188" s="156">
         <f>-N114/N5</f>
         <v>6.7954326388373995E-2</v>
       </c>
-      <c r="O187" s="156">
+      <c r="O188" s="156">
         <f>-O114/O5</f>
         <v>1.7547027346442992E-2</v>
       </c>
-      <c r="P187" s="156">
+      <c r="P188" s="156">
         <f>-P114/P5</f>
         <v>2.4797504923484832E-2</v>
       </c>
-      <c r="Q187" s="156">
+      <c r="Q188" s="156">
         <f>-Q114/Q5</f>
         <v>2.7980253591308617E-2</v>
       </c>
-      <c r="T187" s="156">
-        <f>-T114/T5</f>
+      <c r="T188" s="156">
+        <f t="shared" ref="T188:AA188" si="108">-T114/T5</f>
         <v>3.2523302263648468E-2</v>
       </c>
-      <c r="U187" s="156">
-        <f>-U114/U5</f>
+      <c r="U188" s="156">
+        <f t="shared" si="108"/>
         <v>2.3174277407217378E-2</v>
       </c>
-      <c r="V187" s="156">
-        <f>-V114/V5</f>
+      <c r="V188" s="156">
+        <f t="shared" si="108"/>
         <v>2.7382980346291729E-2</v>
       </c>
-      <c r="W187" s="156">
-        <f>-W114/W5</f>
+      <c r="W188" s="156">
+        <f t="shared" si="108"/>
         <v>2.7847124506377378E-2</v>
       </c>
-      <c r="X187" s="156">
-        <f>-X114/X5</f>
+      <c r="X188" s="156">
+        <f t="shared" si="108"/>
         <v>4.05194360652932E-2</v>
       </c>
-      <c r="Y187" s="156">
-        <f>-Y114/Y5</f>
+      <c r="Y188" s="156">
+        <f t="shared" si="108"/>
         <v>2.871627547977406E-2</v>
       </c>
-      <c r="Z187" s="156">
-        <f>-Z114/Z5</f>
+      <c r="Z188" s="156">
+        <f t="shared" si="108"/>
         <v>1.8847153111101324E-2</v>
       </c>
-      <c r="AA187" s="156">
-        <f>-AA114/AA5</f>
+      <c r="AA188" s="156">
+        <f t="shared" si="108"/>
         <v>2.1527905409544815E-2</v>
       </c>
-      <c r="AC187" s="156">
+      <c r="AC188" s="156">
         <f>-AC114/AC5</f>
         <v>2.5925969758295166E-2</v>
       </c>
     </row>
-    <row r="188" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B188" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="M188" s="156">
+    <row r="189" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B189" s="20" t="s">
+        <v>301</v>
+      </c>
+      <c r="M189" s="156">
         <f>-(M114/M57)</f>
         <v>0.10715854194115064</v>
       </c>
-      <c r="N188" s="156">
+      <c r="N189" s="156">
         <f>-(N114/N57)</f>
         <v>0.32494238610175502</v>
       </c>
-      <c r="O188" s="156">
+      <c r="O189" s="156">
         <f>-(O114/O57)</f>
         <v>3.8056247775008899E-2</v>
       </c>
-      <c r="P188" s="156">
+      <c r="P189" s="156">
         <f>-(P114/P57)</f>
         <v>5.0492284167329808E-2</v>
       </c>
-      <c r="Q188" s="156">
+      <c r="Q189" s="156">
         <f>-(Q114/Q57)</f>
         <v>5.8821238731283712E-2</v>
       </c>
-      <c r="T188" s="156">
-        <f>-(T114/T57)</f>
+      <c r="T189" s="156">
+        <f t="shared" ref="T189:AA189" si="109">-(T114/T57)</f>
         <v>6.7430464490302988E-2</v>
       </c>
-      <c r="U188" s="156">
-        <f>-(U114/U57)</f>
+      <c r="U189" s="156">
+        <f t="shared" si="109"/>
         <v>4.6117193261103862E-2</v>
       </c>
-      <c r="V188" s="156">
-        <f>-(V114/V57)</f>
+      <c r="V189" s="156">
+        <f t="shared" si="109"/>
         <v>6.4770267019485211E-2</v>
       </c>
-      <c r="W188" s="156">
-        <f>-(W114/W57)</f>
+      <c r="W189" s="156">
+        <f t="shared" si="109"/>
         <v>4.4758152768658348E-2</v>
       </c>
-      <c r="X188" s="156">
-        <f>-(X114/X57)</f>
+      <c r="X189" s="156">
+        <f t="shared" si="109"/>
         <v>0.12326716563618614</v>
       </c>
-      <c r="Y188" s="156">
-        <f>-(Y114/Y57)</f>
+      <c r="Y189" s="156">
+        <f t="shared" si="109"/>
         <v>6.8926315789473683E-2</v>
       </c>
-      <c r="Z188" s="156">
-        <f>-(Z114/Z57)</f>
+      <c r="Z189" s="156">
+        <f t="shared" si="109"/>
         <v>3.5479414202818457E-2</v>
       </c>
-      <c r="AA188" s="156">
-        <f>-(AA114/AA57)</f>
+      <c r="AA189" s="156">
+        <f t="shared" si="109"/>
         <v>3.4899888765294769E-2</v>
       </c>
-      <c r="AC188" s="156">
+      <c r="AC189" s="156">
         <f>-(AC114/AC57)</f>
         <v>5.2304435371550904E-2</v>
       </c>
     </row>
-    <row r="189" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B189" s="20" t="s">
-        <v>303</v>
-      </c>
-      <c r="M189" s="156">
+    <row r="190" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B190" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="M190" s="156">
         <f>-M114/M51</f>
         <v>0.83134582623509368</v>
       </c>
-      <c r="N189" s="156">
+      <c r="N190" s="156">
         <f>-N114/N51</f>
         <v>1.1871761658031088</v>
       </c>
-      <c r="O189" s="156">
+      <c r="O190" s="156">
         <f>-O114/O51</f>
         <v>0.70888594164456231</v>
       </c>
-      <c r="P189" s="156">
+      <c r="P190" s="156">
         <f>-P114/P51</f>
         <v>1.7360515021459229</v>
       </c>
-      <c r="Q189" s="156">
+      <c r="Q190" s="156">
         <f>-Q114/Q51</f>
         <v>2.1252198381990857</v>
       </c>
-      <c r="T189" s="156">
-        <f>-T114/T51</f>
+      <c r="T190" s="156">
+        <f t="shared" ref="T190:AA190" si="110">-T114/T51</f>
         <v>2.25635103926097</v>
       </c>
-      <c r="U189" s="156">
-        <f>-U114/U51</f>
+      <c r="U190" s="156">
+        <f t="shared" si="110"/>
         <v>1.7008368200836821</v>
       </c>
-      <c r="V189" s="156">
-        <f>-V114/V51</f>
+      <c r="V190" s="156">
+        <f t="shared" si="110"/>
         <v>1.9834254143646408</v>
       </c>
-      <c r="W189" s="156">
-        <f>-W114/W51</f>
+      <c r="W190" s="156">
+        <f t="shared" si="110"/>
         <v>2.0081833060556464</v>
       </c>
-      <c r="X189" s="156">
-        <f>-X114/X51</f>
+      <c r="X190" s="156">
+        <f t="shared" si="110"/>
         <v>2.8353293413173652</v>
       </c>
-      <c r="Y189" s="156">
-        <f>-Y114/Y51</f>
+      <c r="Y190" s="156">
+        <f t="shared" si="110"/>
         <v>2.1768617021276597</v>
       </c>
-      <c r="Z189" s="156">
-        <f>-Z114/Z51</f>
+      <c r="Z190" s="156">
+        <f t="shared" si="110"/>
         <v>1.5832305795314427</v>
       </c>
-      <c r="AA189" s="156">
-        <f>-AA114/AA51</f>
+      <c r="AA190" s="156">
+        <f t="shared" si="110"/>
         <v>1.7622868605817452</v>
       </c>
-      <c r="AC189" s="156">
+      <c r="AC190" s="156">
         <f>-AC114/AC51</f>
         <v>2.0359355638166048</v>
       </c>
     </row>
-    <row r="191" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B191" s="1"/>
-    </row>
-    <row r="192" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B192" s="14" t="s">
-        <v>312</v>
-      </c>
-      <c r="C192" s="174"/>
-      <c r="D192" s="174"/>
-      <c r="E192" s="174"/>
-      <c r="F192" s="174"/>
-      <c r="G192" s="174"/>
-      <c r="H192" s="174"/>
-      <c r="I192" s="174"/>
-      <c r="J192" s="174"/>
-      <c r="K192" s="174"/>
-      <c r="L192" s="174"/>
-      <c r="M192" s="174"/>
-      <c r="N192" s="174"/>
-      <c r="O192" s="174"/>
-      <c r="P192" s="174"/>
-      <c r="Q192" s="174"/>
-      <c r="T192" s="174"/>
-      <c r="U192" s="174"/>
-      <c r="V192" s="174"/>
-      <c r="W192" s="174"/>
-      <c r="X192" s="174"/>
-      <c r="Y192" s="174"/>
-      <c r="Z192" s="174"/>
-      <c r="AA192" s="174"/>
-      <c r="AC192" s="174"/>
-    </row>
-    <row r="193" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B193" s="246" t="s">
-        <v>374</v>
-      </c>
-      <c r="C193" s="81"/>
-      <c r="D193" s="81"/>
-      <c r="E193" s="81"/>
-      <c r="F193" s="81"/>
-      <c r="G193" s="81"/>
-      <c r="H193" s="81"/>
-      <c r="I193" s="81"/>
-      <c r="J193" s="81"/>
-      <c r="K193" s="81"/>
-      <c r="L193" s="81"/>
-      <c r="M193" s="81">
+    <row r="192" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B192" s="1"/>
+    </row>
+    <row r="193" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B193" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="C193" s="174"/>
+      <c r="D193" s="174"/>
+      <c r="E193" s="174"/>
+      <c r="F193" s="174"/>
+      <c r="G193" s="174"/>
+      <c r="H193" s="174"/>
+      <c r="I193" s="174"/>
+      <c r="J193" s="174"/>
+      <c r="K193" s="174"/>
+      <c r="L193" s="174"/>
+      <c r="M193" s="174"/>
+      <c r="N193" s="174"/>
+      <c r="O193" s="174"/>
+      <c r="P193" s="174"/>
+      <c r="Q193" s="174"/>
+      <c r="T193" s="174"/>
+      <c r="U193" s="174"/>
+      <c r="V193" s="174"/>
+      <c r="W193" s="174"/>
+      <c r="X193" s="174"/>
+      <c r="Y193" s="174"/>
+      <c r="Z193" s="174"/>
+      <c r="AA193" s="174"/>
+      <c r="AC193" s="174"/>
+    </row>
+    <row r="194" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B194" s="228" t="s">
+        <v>373</v>
+      </c>
+      <c r="C194" s="81"/>
+      <c r="D194" s="81"/>
+      <c r="E194" s="81"/>
+      <c r="F194" s="81"/>
+      <c r="G194" s="81"/>
+      <c r="H194" s="81"/>
+      <c r="I194" s="81"/>
+      <c r="J194" s="81"/>
+      <c r="K194" s="81"/>
+      <c r="L194" s="81"/>
+      <c r="M194" s="81">
         <f>IF(L103=0,
 IF(M103=0,0,IF(M103&gt;0,1,-1)),
 (M103-L103)/ABS(L103)
 )</f>
         <v>0</v>
       </c>
-      <c r="N193" s="81">
-        <f t="shared" ref="N193:Q193" si="72">IF(M103=0,
+      <c r="N194" s="81">
+        <f t="shared" ref="N194:Q194" si="111">IF(M103=0,
 IF(N103=0,0,IF(N103&gt;0,1,-1)),
 (N103-M103)/ABS(M103)
 )</f>
         <v>0</v>
       </c>
-      <c r="O193" s="81">
-        <f t="shared" si="72"/>
-        <v>0</v>
-      </c>
-      <c r="P193" s="81">
-        <f t="shared" si="72"/>
+      <c r="O194" s="81">
+        <f t="shared" si="111"/>
+        <v>0</v>
+      </c>
+      <c r="P194" s="81">
+        <f t="shared" si="111"/>
         <v>1</v>
       </c>
-      <c r="Q193" s="81">
-        <f t="shared" si="72"/>
+      <c r="Q194" s="81">
+        <f t="shared" si="111"/>
         <v>0.96364041936203437</v>
       </c>
-      <c r="T193" s="81">
-        <f t="shared" ref="T193:T196" si="73">IF(S103=0,
+      <c r="T194" s="81">
+        <f t="shared" ref="T194:T197" si="112">IF(S103=0,
 IF(T103=0,0,IF(T103&gt;0,1,-1)),
 (T103-S103)/ABS(S103)
 )</f>
         <v>1</v>
       </c>
-      <c r="U193" s="81">
-        <f t="shared" ref="U193:U196" si="74">IF(T103=0,
+      <c r="U194" s="81">
+        <f t="shared" ref="U194:U197" si="113">IF(T103=0,
 IF(U103=0,0,IF(U103&gt;0,1,-1)),
 (U103-T103)/ABS(T103)
 )</f>
         <v>0.26059122575786103</v>
       </c>
-      <c r="V193" s="81">
-        <f t="shared" ref="V193:V196" si="75">IF(U103=0,
+      <c r="V194" s="81">
+        <f t="shared" ref="V194:V197" si="114">IF(U103=0,
 IF(V103=0,0,IF(V103&gt;0,1,-1)),
 (V103-U103)/ABS(U103)
 )</f>
         <v>0.42598954443614639</v>
       </c>
-      <c r="W193" s="81">
-        <f t="shared" ref="W193:W196" si="76">IF(V103=0,
+      <c r="W194" s="81">
+        <f t="shared" ref="W194:W197" si="115">IF(V103=0,
 IF(W103=0,0,IF(W103&gt;0,1,-1)),
 (W103-V103)/ABS(V103)
 )</f>
         <v>-7.8296847177123707E-2</v>
       </c>
-      <c r="X193" s="81">
-        <f t="shared" ref="X193:X196" si="77">IF(W103=0,
+      <c r="X194" s="81">
+        <f t="shared" ref="X194:X197" si="116">IF(W103=0,
 IF(X103=0,0,IF(X103&gt;0,1,-1)),
 (X103-W103)/ABS(W103)
 )</f>
         <v>0.35706574237172567</v>
       </c>
-      <c r="Y193" s="81">
-        <f t="shared" ref="Y193:Y196" si="78">IF(X103=0,
+      <c r="Y194" s="81">
+        <f t="shared" ref="Y194:Y197" si="117">IF(X103=0,
 IF(Y103=0,0,IF(Y103&gt;0,1,-1)),
 (Y103-X103)/ABS(X103)
 )</f>
         <v>0.27035967005820039</v>
       </c>
-      <c r="Z193" s="81">
-        <f t="shared" ref="Z193:Z196" si="79">IF(Y103=0,
+      <c r="Z194" s="81">
+        <f t="shared" ref="Z194:Z197" si="118">IF(Y103=0,
 IF(Z103=0,0,IF(Z103&gt;0,1,-1)),
 (Z103-Y103)/ABS(Y103)
 )</f>
         <v>0.11450230718523402</v>
       </c>
-      <c r="AA193" s="81">
-        <f t="shared" ref="AA193:AA196" si="80">IF(Z103=0,
+      <c r="AA194" s="81">
+        <f t="shared" ref="AA194:AA197" si="119">IF(Z103=0,
 IF(AA103=0,0,IF(AA103&gt;0,1,-1)),
 (AA103-Z103)/ABS(Z103)
 )</f>
         <v>0.11992074288756137</v>
       </c>
-      <c r="AC193" s="49"/>
-    </row>
-    <row r="194" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B194" s="246" t="s">
-        <v>375</v>
-      </c>
-      <c r="M194" s="81">
-        <f t="shared" ref="M194:Q194" si="81">IF(L104=0,
+      <c r="AC194" s="49"/>
+    </row>
+    <row r="195" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B195" s="228" t="s">
+        <v>374</v>
+      </c>
+      <c r="M195" s="81">
+        <f t="shared" ref="M195:Q195" si="120">IF(L104=0,
 IF(M104=0,0,IF(M104&gt;0,1,-1)),
 (M104-L104)/ABS(L104)
 )</f>
         <v>0</v>
       </c>
-      <c r="N194" s="81">
-        <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="O194" s="81">
-        <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="P194" s="81">
-        <f t="shared" si="81"/>
+      <c r="N195" s="81">
+        <f t="shared" si="120"/>
+        <v>0</v>
+      </c>
+      <c r="O195" s="81">
+        <f t="shared" si="120"/>
+        <v>0</v>
+      </c>
+      <c r="P195" s="81">
+        <f t="shared" si="120"/>
         <v>1</v>
       </c>
-      <c r="Q194" s="81">
-        <f t="shared" si="81"/>
+      <c r="Q195" s="81">
+        <f t="shared" si="120"/>
         <v>0.43510343704186349</v>
       </c>
-      <c r="T194" s="81">
-        <f t="shared" si="73"/>
+      <c r="T195" s="81">
+        <f t="shared" si="112"/>
         <v>1</v>
       </c>
-      <c r="U194" s="81">
-        <f t="shared" si="74"/>
+      <c r="U195" s="81">
+        <f t="shared" si="113"/>
         <v>0.11060702875399361</v>
       </c>
-      <c r="V194" s="81">
-        <f t="shared" si="75"/>
+      <c r="V195" s="81">
+        <f t="shared" si="114"/>
         <v>-5.1493009608192856E-2</v>
       </c>
-      <c r="W194" s="81">
-        <f t="shared" si="76"/>
+      <c r="W195" s="81">
+        <f t="shared" si="115"/>
         <v>0.304925391241053</v>
       </c>
-      <c r="X194" s="81">
-        <f t="shared" si="77"/>
+      <c r="X195" s="81">
+        <f t="shared" si="116"/>
         <v>-0.19987914284386185</v>
       </c>
-      <c r="Y194" s="81">
-        <f t="shared" si="78"/>
+      <c r="Y195" s="81">
+        <f t="shared" si="117"/>
         <v>0.21274618021262998</v>
       </c>
-      <c r="Z194" s="81">
-        <f t="shared" si="79"/>
+      <c r="Z195" s="81">
+        <f t="shared" si="118"/>
         <v>0.3652694610778443</v>
       </c>
-      <c r="AA194" s="81">
-        <f t="shared" si="80"/>
+      <c r="AA195" s="81">
+        <f t="shared" si="119"/>
         <v>0.31147368421052629</v>
       </c>
-      <c r="AC194" s="49"/>
-    </row>
-    <row r="195" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B195" s="20" t="s">
-        <v>376</v>
-      </c>
-      <c r="M195" s="81">
-        <f t="shared" ref="M195:Q196" si="82">IF(L105=0,
+      <c r="AC195" s="49"/>
+    </row>
+    <row r="196" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B196" s="20" t="s">
+        <v>375</v>
+      </c>
+      <c r="M196" s="81">
+        <f t="shared" ref="M196:Q197" si="121">IF(L105=0,
 IF(M105=0,0,IF(M105&gt;0,1,-1)),
 (M105-L105)/ABS(L105)
 )</f>
         <v>0</v>
       </c>
-      <c r="N195" s="81">
-        <f t="shared" si="82"/>
-        <v>0</v>
-      </c>
-      <c r="O195" s="81">
-        <f t="shared" si="82"/>
-        <v>0</v>
-      </c>
-      <c r="P195" s="81">
-        <f t="shared" si="82"/>
+      <c r="N196" s="81">
+        <f t="shared" si="121"/>
+        <v>0</v>
+      </c>
+      <c r="O196" s="81">
+        <f t="shared" si="121"/>
+        <v>0</v>
+      </c>
+      <c r="P196" s="81">
+        <f t="shared" si="121"/>
         <v>1</v>
       </c>
-      <c r="Q195" s="81">
-        <f t="shared" si="82"/>
+      <c r="Q196" s="81">
+        <f t="shared" si="121"/>
         <v>0.68194919521469621</v>
       </c>
-      <c r="T195" s="81">
-        <f t="shared" si="73"/>
+      <c r="T196" s="81">
+        <f t="shared" si="112"/>
         <v>1</v>
       </c>
-      <c r="U195" s="81">
-        <f t="shared" si="74"/>
+      <c r="U196" s="81">
+        <f t="shared" si="113"/>
         <v>0.17124695493300854</v>
       </c>
-      <c r="V195" s="81">
-        <f t="shared" si="75"/>
+      <c r="V196" s="81">
+        <f t="shared" si="114"/>
         <v>0.15628351369796237</v>
       </c>
-      <c r="W195" s="81">
-        <f t="shared" si="76"/>
+      <c r="W196" s="81">
+        <f t="shared" si="115"/>
         <v>9.9269252388982571E-2</v>
       </c>
-      <c r="X195" s="81">
-        <f t="shared" si="77"/>
+      <c r="X196" s="81">
+        <f t="shared" si="116"/>
         <v>5.0726119860912251E-2</v>
       </c>
-      <c r="Y195" s="81">
-        <f t="shared" si="78"/>
+      <c r="Y196" s="81">
+        <f t="shared" si="117"/>
         <v>0.24622834339108429</v>
       </c>
-      <c r="Z195" s="81">
-        <f t="shared" si="79"/>
+      <c r="Z196" s="81">
+        <f t="shared" si="118"/>
         <v>0.21671385336327248</v>
       </c>
-      <c r="AA195" s="81">
-        <f t="shared" si="80"/>
+      <c r="AA196" s="81">
+        <f t="shared" si="119"/>
         <v>0.20752960811374652</v>
       </c>
-      <c r="AC195" s="49"/>
-    </row>
-    <row r="196" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B196" s="20" t="s">
-        <v>377</v>
-      </c>
-      <c r="M196" s="81">
-        <f t="shared" si="82"/>
-        <v>0</v>
-      </c>
-      <c r="N196" s="81">
-        <f t="shared" ref="N196" si="83">IF(M106=0,
+      <c r="AC196" s="49"/>
+    </row>
+    <row r="197" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B197" s="20" t="s">
+        <v>376</v>
+      </c>
+      <c r="M197" s="81">
+        <f t="shared" si="121"/>
+        <v>0</v>
+      </c>
+      <c r="N197" s="81">
+        <f t="shared" ref="N197" si="122">IF(M106=0,
 IF(N106=0,0,IF(N106&gt;0,1,-1)),
 (N106-M106)/ABS(M106)
 )</f>
         <v>0</v>
       </c>
-      <c r="O196" s="81">
-        <f t="shared" ref="O196" si="84">IF(N106=0,
+      <c r="O197" s="81">
+        <f t="shared" ref="O197" si="123">IF(N106=0,
 IF(O106=0,0,IF(O106&gt;0,1,-1)),
 (O106-N106)/ABS(N106)
 )</f>
         <v>0</v>
       </c>
-      <c r="P196" s="81">
-        <f t="shared" ref="P196" si="85">IF(O106=0,
+      <c r="P197" s="81">
+        <f t="shared" ref="P197" si="124">IF(O106=0,
 IF(P106=0,0,IF(P106&gt;0,1,-1)),
 (P106-O106)/ABS(O106)
 )</f>
         <v>1</v>
       </c>
-      <c r="Q196" s="81">
-        <f t="shared" ref="Q196" si="86">IF(P106=0,
+      <c r="Q197" s="81">
+        <f t="shared" ref="Q197" si="125">IF(P106=0,
 IF(Q106=0,0,IF(Q106&gt;0,1,-1)),
 (Q106-P106)/ABS(P106)
 )</f>
         <v>0.4500032656260205</v>
       </c>
-      <c r="T196" s="81">
-        <f t="shared" si="73"/>
+      <c r="T197" s="81">
+        <f t="shared" si="112"/>
         <v>1</v>
       </c>
-      <c r="U196" s="81">
-        <f t="shared" si="74"/>
+      <c r="U197" s="81">
+        <f t="shared" si="113"/>
         <v>0.14410828025477707</v>
       </c>
-      <c r="V196" s="81">
-        <f t="shared" si="75"/>
+      <c r="V197" s="81">
+        <f t="shared" si="114"/>
         <v>-0.12990025516121551</v>
       </c>
-      <c r="W196" s="81">
-        <f t="shared" si="76"/>
+      <c r="W197" s="81">
+        <f t="shared" si="115"/>
         <v>0.31964809384164222</v>
       </c>
-      <c r="X196" s="81">
-        <f t="shared" si="77"/>
+      <c r="X197" s="81">
+        <f t="shared" si="116"/>
         <v>0.1408080808080808</v>
       </c>
-      <c r="Y196" s="81">
-        <f t="shared" si="78"/>
+      <c r="Y197" s="81">
+        <f t="shared" si="117"/>
         <v>2.5500265627766958E-2</v>
       </c>
-      <c r="Z196" s="81">
-        <f t="shared" si="79"/>
+      <c r="Z197" s="81">
+        <f t="shared" si="118"/>
         <v>3.7989984458642722E-3</v>
       </c>
-      <c r="AA196" s="81">
-        <f t="shared" si="80"/>
+      <c r="AA197" s="81">
+        <f t="shared" si="119"/>
         <v>9.5647686220540165E-2</v>
       </c>
-      <c r="AC196" s="49"/>
-    </row>
-    <row r="198" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B198" s="1"/>
-    </row>
-    <row r="199" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B199" s="14" t="s">
-        <v>313</v>
-      </c>
-      <c r="C199" s="174"/>
-      <c r="D199" s="174"/>
-      <c r="E199" s="174"/>
-      <c r="F199" s="174"/>
-      <c r="G199" s="174"/>
-      <c r="H199" s="174"/>
-      <c r="I199" s="174"/>
-      <c r="J199" s="174"/>
-      <c r="K199" s="174"/>
-      <c r="L199" s="174"/>
-      <c r="M199" s="174"/>
-      <c r="N199" s="174"/>
-      <c r="O199" s="174"/>
-      <c r="P199" s="174"/>
-      <c r="Q199" s="174"/>
-      <c r="T199" s="174"/>
-      <c r="U199" s="174"/>
-      <c r="V199" s="174"/>
-      <c r="W199" s="174"/>
-      <c r="X199" s="174"/>
-      <c r="Y199" s="174"/>
-      <c r="Z199" s="174"/>
-      <c r="AA199" s="174"/>
-      <c r="AC199" s="174"/>
-    </row>
-    <row r="200" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B200" s="20" t="s">
-        <v>285</v>
-      </c>
-      <c r="C200" s="81"/>
-      <c r="D200" s="81"/>
-      <c r="E200" s="81"/>
-      <c r="F200" s="81"/>
-      <c r="G200" s="81"/>
-      <c r="H200" s="81"/>
-      <c r="I200" s="81"/>
-      <c r="J200" s="81"/>
-      <c r="K200" s="81"/>
-      <c r="L200" s="81"/>
-      <c r="M200" s="81">
+      <c r="AC197" s="49"/>
+    </row>
+    <row r="199" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B199" s="1"/>
+    </row>
+    <row r="200" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B200" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="C200" s="174"/>
+      <c r="D200" s="174"/>
+      <c r="E200" s="174"/>
+      <c r="F200" s="174"/>
+      <c r="G200" s="174"/>
+      <c r="H200" s="174"/>
+      <c r="I200" s="174"/>
+      <c r="J200" s="174"/>
+      <c r="K200" s="174"/>
+      <c r="L200" s="174"/>
+      <c r="M200" s="174"/>
+      <c r="N200" s="174"/>
+      <c r="O200" s="174"/>
+      <c r="P200" s="174"/>
+      <c r="Q200" s="174"/>
+      <c r="T200" s="174"/>
+      <c r="U200" s="174"/>
+      <c r="V200" s="174"/>
+      <c r="W200" s="174"/>
+      <c r="X200" s="174"/>
+      <c r="Y200" s="174"/>
+      <c r="Z200" s="174"/>
+      <c r="AA200" s="174"/>
+      <c r="AC200" s="174"/>
+    </row>
+    <row r="201" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B201" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="C201" s="81"/>
+      <c r="D201" s="81"/>
+      <c r="E201" s="81"/>
+      <c r="F201" s="81"/>
+      <c r="G201" s="81"/>
+      <c r="H201" s="81"/>
+      <c r="I201" s="81"/>
+      <c r="J201" s="81"/>
+      <c r="K201" s="81"/>
+      <c r="L201" s="81"/>
+      <c r="M201" s="81">
         <f>IF(L62=0,
 IF(M62=0,0,IF(M62&gt;0,1,-1)),
 (M62-L62)/L62
 )</f>
         <v>-1</v>
       </c>
-      <c r="N200" s="81">
-        <f t="shared" ref="N200:Q200" si="87">IF(M62=0,
+      <c r="N201" s="81">
+        <f t="shared" ref="N201:Q201" si="126">IF(M62=0,
 IF(N62=0,0,IF(N62&gt;0,1,-1)),
 (N62-M62)/M62
 )</f>
         <v>-2.5062656641604009E-3</v>
       </c>
-      <c r="O200" s="81">
-        <f t="shared" si="87"/>
+      <c r="O201" s="81">
+        <f t="shared" si="126"/>
         <v>-7.537688442211055E-3</v>
       </c>
-      <c r="P200" s="81">
-        <f t="shared" si="87"/>
+      <c r="P201" s="81">
+        <f t="shared" si="126"/>
         <v>1.1113924050632911</v>
       </c>
-      <c r="Q200" s="81">
-        <f t="shared" si="87"/>
+      <c r="Q201" s="81">
+        <f t="shared" si="126"/>
         <v>0.16786570743405277</v>
       </c>
-      <c r="T200" s="49"/>
-      <c r="U200" s="49"/>
-      <c r="V200" s="49"/>
-      <c r="W200" s="49"/>
-      <c r="X200" s="49"/>
-      <c r="Y200" s="49"/>
-      <c r="Z200" s="49"/>
-      <c r="AA200" s="49"/>
-      <c r="AC200" s="49"/>
+      <c r="T201" s="49"/>
+      <c r="U201" s="49"/>
+      <c r="V201" s="49"/>
+      <c r="W201" s="49"/>
+      <c r="X201" s="49"/>
+      <c r="Y201" s="49"/>
+      <c r="Z201" s="49"/>
+      <c r="AA201" s="49"/>
+      <c r="AC201" s="49"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -31027,19 +30954,19 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B1" s="82" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="227" t="s">
+      <c r="B4" s="231" t="s">
         <v>233</v>
       </c>
-      <c r="C4" s="227"/>
-      <c r="E4" s="227" t="s">
+      <c r="C4" s="231"/>
+      <c r="E4" s="231" t="s">
         <v>240</v>
       </c>
-      <c r="F4" s="227"/>
-      <c r="G4" s="227"/>
+      <c r="F4" s="231"/>
+      <c r="G4" s="231"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -31176,14 +31103,14 @@
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="227" t="s">
+      <c r="B15" s="231" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="227"/>
-      <c r="E15" s="227" t="s">
+      <c r="C15" s="231"/>
+      <c r="E15" s="231" t="s">
         <v>246</v>
       </c>
-      <c r="F15" s="227"/>
+      <c r="F15" s="231"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -31234,14 +31161,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="227" t="s">
+      <c r="B21" s="231" t="s">
         <v>245</v>
       </c>
-      <c r="C21" s="227"/>
-      <c r="E21" s="227" t="s">
+      <c r="C21" s="231"/>
+      <c r="E21" s="231" t="s">
         <v>249</v>
       </c>
-      <c r="F21" s="227"/>
+      <c r="F21" s="231"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -31310,14 +31237,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="227" t="s">
+      <c r="B29" s="231" t="s">
         <v>250</v>
       </c>
-      <c r="C29" s="227"/>
-      <c r="E29" s="227" t="s">
+      <c r="C29" s="231"/>
+      <c r="E29" s="231" t="s">
         <v>256</v>
       </c>
-      <c r="F29" s="227"/>
+      <c r="F29" s="231"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -31393,14 +31320,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="227" t="s">
-        <v>269</v>
-      </c>
-      <c r="C37" s="227"/>
-      <c r="E37" s="227" t="s">
-        <v>272</v>
-      </c>
-      <c r="F37" s="227"/>
+      <c r="B37" s="231" t="s">
+        <v>268</v>
+      </c>
+      <c r="C37" s="231"/>
+      <c r="E37" s="231" t="s">
+        <v>271</v>
+      </c>
+      <c r="F37" s="231"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -31411,26 +31338,26 @@
         <v>3.1838127742564601E-2</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F38" s="179">
-        <f>Statement!AC178</f>
+        <f>Statement!AC179</f>
         <v>8.6691554478469674E-3</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B39" s="54" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C39" s="219">
         <f ca="1">Statement!AC172</f>
         <v>2.2515145822264611E-2</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F39" s="179">
-        <f>Statement!AC179</f>
+        <f>Statement!AC180</f>
         <v>0.40364585653572349</v>
       </c>
     </row>
@@ -31443,16 +31370,16 @@
         <v>1.9502681618722574E-4</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F40" s="179">
-        <f>Statement!AC180</f>
+        <f>Statement!AC181</f>
         <v>0.41231501198357046</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B41" s="20" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C41" s="179">
         <f ca="1">Statement!AC175</f>
@@ -31461,7 +31388,7 @@
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B42" s="20" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C42" s="179">
         <f ca="1">Statement!AC176</f>
@@ -31469,97 +31396,97 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="227" t="s">
-        <v>280</v>
-      </c>
-      <c r="C45" s="227"/>
-      <c r="E45" s="227" t="s">
-        <v>286</v>
-      </c>
-      <c r="F45" s="227"/>
+      <c r="B45" s="231" t="s">
+        <v>279</v>
+      </c>
+      <c r="C45" s="231"/>
+      <c r="E45" s="231" t="s">
+        <v>285</v>
+      </c>
+      <c r="F45" s="231"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="C46" s="179">
+        <f>Statement!AC182</f>
+        <v>3.9374614276897757E-2</v>
+      </c>
+      <c r="E46" s="20" t="s">
         <v>278</v>
       </c>
-      <c r="C46" s="179">
-        <f>Statement!AC181</f>
-        <v>3.9374614276897757E-2</v>
-      </c>
-      <c r="E46" s="20" t="s">
-        <v>279</v>
-      </c>
       <c r="F46" s="178">
-        <f>Statement!AC182</f>
+        <f>Statement!AC183</f>
         <v>3.3294214876033057</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E47" s="20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F47" s="178">
-        <f>Statement!AC185</f>
+        <f>Statement!AC186</f>
         <v>2.9794214876033056</v>
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E48" s="20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F48" s="179">
-        <f ca="1">Statement!AC186</f>
+        <f ca="1">Statement!AC187</f>
         <v>1.4463920490363455E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="227" t="s">
-        <v>283</v>
-      </c>
-      <c r="C51" s="227"/>
-      <c r="E51" s="227" t="s">
-        <v>304</v>
-      </c>
-      <c r="F51" s="227"/>
+      <c r="B51" s="231" t="s">
+        <v>282</v>
+      </c>
+      <c r="C51" s="231"/>
+      <c r="E51" s="231" t="s">
+        <v>303</v>
+      </c>
+      <c r="F51" s="231"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C52" s="179">
-        <f>Statement!AC183</f>
+        <f>Statement!AC184</f>
         <v>5.4437361220542942E-2</v>
       </c>
       <c r="E52" s="20" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F52" s="179">
-        <f>Statement!AC187</f>
+        <f>Statement!AC188</f>
         <v>2.5925969758295166E-2</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B53" s="20" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C53" s="179">
-        <f>Statement!AC184</f>
+        <f>Statement!AC185</f>
         <v>2.6983206504372935E-2</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F53" s="179">
-        <f>Statement!AC188</f>
+        <f>Statement!AC189</f>
         <v>5.2304435371550904E-2</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E54" s="20" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F54" s="179">
-        <f>Statement!AC189</f>
+        <f>Statement!AC190</f>
         <v>2.0359355638166048</v>
       </c>
     </row>
@@ -32249,7 +32176,7 @@
     </row>
     <row r="32" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B32" s="14" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
@@ -32630,7 +32557,7 @@
     </row>
     <row r="50" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B50" s="14" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C50" s="14"/>
       <c r="D50" s="14"/>
@@ -32670,7 +32597,7 @@
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C52" s="179">
         <f>Statement!M172</f>
@@ -32728,7 +32655,7 @@
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B54" s="20" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C54" s="179">
         <f>Statement!M175</f>
@@ -32757,7 +32684,7 @@
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B55" s="20" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C55" s="179">
         <f>Statement!M176</f>
@@ -32786,7 +32713,7 @@
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B57" s="14" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C57" s="14"/>
       <c r="D57" s="14"/>
@@ -32797,94 +32724,94 @@
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B58" s="20" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C58" s="179">
-        <f>Statement!M178</f>
+        <f>Statement!M179</f>
         <v>6.5110966057441252E-2</v>
       </c>
       <c r="D58" s="179">
-        <f>Statement!N178</f>
+        <f>Statement!N179</f>
         <v>0.36214740673339402</v>
       </c>
       <c r="E58" s="179">
-        <f>Statement!O178</f>
+        <f>Statement!O179</f>
         <v>1.6828561690524879E-2</v>
       </c>
       <c r="F58" s="179">
-        <f>Statement!P178</f>
+        <f>Statement!P179</f>
         <v>1.4862071423479934E-2</v>
       </c>
       <c r="G58" s="179">
-        <f>Statement!Q178</f>
+        <f>Statement!Q179</f>
         <v>1.0787462620445233E-2</v>
       </c>
       <c r="I58" s="179">
-        <f>Statement!AC178</f>
+        <f>Statement!AC179</f>
         <v>8.6691554478469674E-3</v>
       </c>
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B59" s="20" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C59" s="179">
-        <f>Statement!M179</f>
+        <f>Statement!M180</f>
         <v>0</v>
       </c>
       <c r="D59" s="179">
-        <f>Statement!N179</f>
+        <f>Statement!N180</f>
         <v>9.1346678798908094</v>
       </c>
       <c r="E59" s="179">
-        <f>Statement!O179</f>
+        <f>Statement!O180</f>
         <v>0.40614349011588274</v>
       </c>
       <c r="F59" s="179">
-        <f>Statement!P179</f>
+        <f>Statement!P180</f>
         <v>0.60064865635469389</v>
       </c>
       <c r="G59" s="179">
-        <f>Statement!Q179</f>
+        <f>Statement!Q180</f>
         <v>0.44396943183076754</v>
       </c>
       <c r="I59" s="179">
-        <f>Statement!AC179</f>
+        <f>Statement!AC180</f>
         <v>0.40364585653572349</v>
       </c>
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B60" s="20" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C60" s="179">
-        <f>Statement!M180</f>
+        <f>Statement!M181</f>
         <v>6.5110966057441252E-2</v>
       </c>
       <c r="D60" s="179">
-        <f>Statement!N180</f>
+        <f>Statement!N181</f>
         <v>9.4968152866242033</v>
       </c>
       <c r="E60" s="179">
-        <f>Statement!O180</f>
+        <f>Statement!O181</f>
         <v>0.42297205180640762</v>
       </c>
       <c r="F60" s="179">
-        <f>Statement!P180</f>
+        <f>Statement!P181</f>
         <v>0.61551072777817373</v>
       </c>
       <c r="G60" s="179">
-        <f>Statement!Q180</f>
+        <f>Statement!Q181</f>
         <v>0.45475689445121276</v>
       </c>
       <c r="I60" s="179">
-        <f>Statement!AC180</f>
+        <f>Statement!AC181</f>
         <v>0.41231501198357046</v>
       </c>
     </row>
     <row r="62" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B62" s="14" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C62" s="14"/>
       <c r="D62" s="14"/>
@@ -32895,36 +32822,36 @@
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B63" s="20" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C63" s="179">
-        <f>Statement!M181</f>
+        <f>Statement!M182</f>
         <v>3.9623381718320909E-2</v>
       </c>
       <c r="D63" s="179">
-        <f>Statement!N181</f>
+        <f>Statement!N182</f>
         <v>3.9759036144578312E-2</v>
       </c>
       <c r="E63" s="179">
-        <f>Statement!O181</f>
+        <f>Statement!O182</f>
         <v>4.118811881188119E-2</v>
       </c>
       <c r="F63" s="179">
-        <f>Statement!P181</f>
+        <f>Statement!P182</f>
         <v>4.1380989086778369E-2</v>
       </c>
       <c r="G63" s="179">
-        <f>Statement!Q181</f>
+        <f>Statement!Q182</f>
         <v>3.9133101615211614E-2</v>
       </c>
       <c r="I63" s="179">
-        <f>Statement!AC181</f>
+        <f>Statement!AC182</f>
         <v>3.9374614276897757E-2</v>
       </c>
     </row>
     <row r="65" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B65" s="14" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C65" s="14"/>
       <c r="D65" s="14"/>
@@ -32935,94 +32862,94 @@
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B66" s="20" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C66" s="178">
-        <f>Statement!M182</f>
+        <f>Statement!M183</f>
         <v>0.84494023904382465</v>
       </c>
       <c r="D66" s="178">
-        <f>Statement!N182</f>
+        <f>Statement!N183</f>
         <v>0.53829959514170045</v>
       </c>
       <c r="E66" s="178">
-        <f>Statement!O182</f>
+        <f>Statement!O183</f>
         <v>1.0393600000000001</v>
       </c>
       <c r="F66" s="178">
-        <f>Statement!P182</f>
+        <f>Statement!P183</f>
         <v>1.7709016393442623</v>
       </c>
       <c r="G66" s="178">
-        <f>Statement!Q182</f>
+        <f>Statement!Q183</f>
         <v>2.5743209876543212</v>
       </c>
       <c r="I66" s="178">
-        <f>Statement!AC182</f>
+        <f>Statement!AC183</f>
         <v>3.3294214876033057</v>
       </c>
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B67" s="20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C67" s="178">
-        <f>Statement!M185</f>
+        <f>Statement!M186</f>
         <v>0.40884462151394424</v>
       </c>
       <c r="D67" s="178">
-        <f>Statement!N185</f>
+        <f>Statement!N186</f>
         <v>9.4858299595141707E-2</v>
       </c>
       <c r="E67" s="178">
-        <f>Statement!O185</f>
+        <f>Statement!O186</f>
         <v>0.65100000000000002</v>
       </c>
       <c r="F67" s="178">
-        <f>Statement!P185</f>
+        <f>Statement!P186</f>
         <v>1.4240573770491802</v>
       </c>
       <c r="G67" s="178">
-        <f>Statement!Q185</f>
+        <f>Statement!Q186</f>
         <v>2.2258436213991768</v>
       </c>
       <c r="I67" s="178">
-        <f>Statement!AC185</f>
+        <f>Statement!AC186</f>
         <v>2.9794214876033056</v>
       </c>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B68" s="20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C68" s="200">
-        <f>Statement!M186</f>
+        <f>Statement!M187</f>
         <v>1.7626499592230463E-2</v>
       </c>
       <c r="D68" s="200">
-        <f>Statement!N186</f>
+        <f>Statement!N187</f>
         <v>4.6216299382204652E-3</v>
       </c>
       <c r="E68" s="200">
-        <f>Statement!O186</f>
+        <f>Statement!O187</f>
         <v>1.0561272414313365E-2</v>
       </c>
       <c r="F68" s="200">
-        <f>Statement!P186</f>
+        <f>Statement!P187</f>
         <v>9.8841101665902813E-3</v>
       </c>
       <c r="G68" s="200">
-        <f>Statement!Q186</f>
+        <f>Statement!Q187</f>
         <v>1.1785239203608671E-2</v>
       </c>
       <c r="I68" s="200">
-        <f ca="1">Statement!AC186</f>
+        <f ca="1">Statement!AC187</f>
         <v>1.4463920490363455E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B70" s="14" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C70" s="14"/>
       <c r="D70" s="14"/>
@@ -33033,65 +32960,65 @@
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B71" s="20" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C71" s="179">
-        <f>Statement!M183</f>
+        <f>Statement!M184</f>
         <v>0.22002635046113306</v>
       </c>
       <c r="D71" s="179">
-        <f>Statement!N183</f>
+        <f>Statement!N184</f>
         <v>0.48023400106364122</v>
       </c>
       <c r="E71" s="179">
-        <f>Statement!O183</f>
+        <f>Statement!O184</f>
         <v>0.1263438946244215</v>
       </c>
       <c r="F71" s="179">
-        <f>Statement!P183</f>
+        <f>Statement!P184</f>
         <v>7.3912839956934887E-2</v>
       </c>
       <c r="G71" s="179">
-        <f>Statement!Q183</f>
+        <f>Statement!Q184</f>
         <v>6.217021359450145E-2</v>
       </c>
       <c r="I71" s="179">
-        <f>Statement!AC183</f>
+        <f>Statement!AC184</f>
         <v>5.4437361220542942E-2</v>
       </c>
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B72" s="20" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C72" s="179">
-        <f>Statement!M184</f>
+        <f>Statement!M185</f>
         <v>7.4459389165490081E-2</v>
       </c>
       <c r="D72" s="179">
-        <f>Statement!N184</f>
+        <f>Statement!N185</f>
         <v>0.10043004374582931</v>
       </c>
       <c r="E72" s="179">
-        <f>Statement!O184</f>
+        <f>Statement!O185</f>
         <v>5.8254817635665278E-2</v>
       </c>
       <c r="F72" s="179">
-        <f>Statement!P184</f>
+        <f>Statement!P185</f>
         <v>3.629968505023104E-2</v>
       </c>
       <c r="G72" s="179">
-        <f>Statement!Q184</f>
+        <f>Statement!Q185</f>
         <v>2.9573303448211987E-2</v>
       </c>
       <c r="I72" s="179">
-        <f>Statement!AC184</f>
+        <f>Statement!AC185</f>
         <v>2.6983206504372935E-2</v>
       </c>
     </row>
     <row r="74" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B74" s="14" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C74" s="14"/>
       <c r="D74" s="14"/>
@@ -33102,88 +33029,88 @@
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B75" s="20" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C75" s="179">
-        <f>Statement!M187</f>
+        <f>Statement!M188</f>
         <v>3.6263654603552055E-2</v>
       </c>
       <c r="D75" s="179">
-        <f>Statement!N187</f>
+        <f>Statement!N188</f>
         <v>6.7954326388373995E-2</v>
       </c>
       <c r="E75" s="179">
-        <f>Statement!O187</f>
+        <f>Statement!O188</f>
         <v>1.7547027346442992E-2</v>
       </c>
       <c r="F75" s="179">
-        <f>Statement!P187</f>
+        <f>Statement!P188</f>
         <v>2.4797504923484832E-2</v>
       </c>
       <c r="G75" s="179">
-        <f>Statement!Q187</f>
+        <f>Statement!Q188</f>
         <v>2.7980253591308617E-2</v>
       </c>
       <c r="I75" s="179">
-        <f>Statement!AC187</f>
+        <f>Statement!AC188</f>
         <v>2.5925969758295166E-2</v>
       </c>
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B76" s="20" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C76" s="179">
-        <f>Statement!M188</f>
+        <f>Statement!M189</f>
         <v>0.10715854194115064</v>
       </c>
       <c r="D76" s="179">
-        <f>Statement!N188</f>
+        <f>Statement!N189</f>
         <v>0.32494238610175502</v>
       </c>
       <c r="E76" s="179">
-        <f>Statement!O188</f>
+        <f>Statement!O189</f>
         <v>3.8056247775008899E-2</v>
       </c>
       <c r="F76" s="179">
-        <f>Statement!P188</f>
+        <f>Statement!P189</f>
         <v>5.0492284167329808E-2</v>
       </c>
       <c r="G76" s="179">
-        <f>Statement!Q188</f>
+        <f>Statement!Q189</f>
         <v>5.8821238731283712E-2</v>
       </c>
       <c r="I76" s="179">
-        <f>Statement!AC188</f>
+        <f>Statement!AC189</f>
         <v>5.2304435371550904E-2</v>
       </c>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B77" s="20" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C77" s="179">
-        <f>Statement!M189</f>
+        <f>Statement!M190</f>
         <v>0.83134582623509368</v>
       </c>
       <c r="D77" s="179">
-        <f>Statement!N189</f>
+        <f>Statement!N190</f>
         <v>1.1871761658031088</v>
       </c>
       <c r="E77" s="179">
-        <f>Statement!O189</f>
+        <f>Statement!O190</f>
         <v>0.70888594164456231</v>
       </c>
       <c r="F77" s="179">
-        <f>Statement!P189</f>
+        <f>Statement!P190</f>
         <v>1.7360515021459229</v>
       </c>
       <c r="G77" s="179">
-        <f>Statement!Q189</f>
+        <f>Statement!Q190</f>
         <v>2.1252198381990857</v>
       </c>
       <c r="I77" s="179">
-        <f>Statement!AC189</f>
+        <f>Statement!AC190</f>
         <v>2.0359355638166048</v>
       </c>
     </row>
@@ -33304,7 +33231,7 @@
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B84" s="20" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C84" s="179">
         <f>Statement!M93</f>
@@ -33330,7 +33257,7 @@
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B85" s="20" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C85" s="179">
         <f>Statement!M95</f>
@@ -33356,7 +33283,7 @@
     </row>
     <row r="88" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B88" s="14" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C88" s="14"/>
       <c r="D88" s="14"/>
@@ -33366,112 +33293,112 @@
       <c r="I88" s="14"/>
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B89" s="246" t="s">
-        <v>374</v>
+      <c r="B89" s="228" t="s">
+        <v>373</v>
       </c>
       <c r="C89" s="179">
-        <f>Statement!M193</f>
+        <f>Statement!M194</f>
         <v>0</v>
       </c>
       <c r="D89" s="179">
-        <f>Statement!N193</f>
+        <f>Statement!N194</f>
         <v>0</v>
       </c>
       <c r="E89" s="179">
-        <f>Statement!O193</f>
+        <f>Statement!O194</f>
         <v>0</v>
       </c>
       <c r="F89" s="179">
-        <f>Statement!P193</f>
-        <v>1</v>
-      </c>
-      <c r="G89" s="179">
-        <f>Statement!Q193</f>
-        <v>0.96364041936203437</v>
-      </c>
-      <c r="I89" s="201"/>
-    </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B90" s="246" t="s">
-        <v>375</v>
-      </c>
-      <c r="C90" s="179">
-        <f>Statement!M194</f>
-        <v>0</v>
-      </c>
-      <c r="D90" s="179">
-        <f>Statement!N194</f>
-        <v>0</v>
-      </c>
-      <c r="E90" s="179">
-        <f>Statement!O194</f>
-        <v>0</v>
-      </c>
-      <c r="F90" s="179">
         <f>Statement!P194</f>
         <v>1</v>
       </c>
+      <c r="G89" s="179">
+        <f>Statement!Q194</f>
+        <v>0.96364041936203437</v>
+      </c>
+      <c r="I89" s="201"/>
+    </row>
+    <row r="90" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B90" s="228" t="s">
+        <v>374</v>
+      </c>
+      <c r="C90" s="179">
+        <f>Statement!M195</f>
+        <v>0</v>
+      </c>
+      <c r="D90" s="179">
+        <f>Statement!N195</f>
+        <v>0</v>
+      </c>
+      <c r="E90" s="179">
+        <f>Statement!O195</f>
+        <v>0</v>
+      </c>
+      <c r="F90" s="179">
+        <f>Statement!P195</f>
+        <v>1</v>
+      </c>
       <c r="G90" s="179">
-        <f>Statement!Q194</f>
+        <f>Statement!Q195</f>
         <v>0.43510343704186349</v>
       </c>
       <c r="I90" s="201"/>
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B91" s="20" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C91" s="179">
-        <f>Statement!M195</f>
+        <f>Statement!M196</f>
         <v>0</v>
       </c>
       <c r="D91" s="179">
-        <f>Statement!N195</f>
+        <f>Statement!N196</f>
         <v>0</v>
       </c>
       <c r="E91" s="179">
-        <f>Statement!O195</f>
+        <f>Statement!O196</f>
         <v>0</v>
       </c>
       <c r="F91" s="179">
-        <f>Statement!P195</f>
+        <f>Statement!P196</f>
         <v>1</v>
       </c>
       <c r="G91" s="179">
-        <f>Statement!Q195</f>
+        <f>Statement!Q196</f>
         <v>0.68194919521469621</v>
       </c>
       <c r="I91" s="201"/>
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B92" s="20" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C92" s="179">
-        <f>Statement!M196</f>
+        <f>Statement!M197</f>
         <v>0</v>
       </c>
       <c r="D92" s="179">
-        <f>Statement!N196</f>
+        <f>Statement!N197</f>
         <v>0</v>
       </c>
       <c r="E92" s="179">
-        <f>Statement!O196</f>
+        <f>Statement!O197</f>
         <v>0</v>
       </c>
       <c r="F92" s="179">
-        <f>Statement!P196</f>
+        <f>Statement!P197</f>
         <v>1</v>
       </c>
       <c r="G92" s="179">
-        <f>Statement!Q196</f>
+        <f>Statement!Q197</f>
         <v>0.4500032656260205</v>
       </c>
       <c r="I92" s="201"/>
     </row>
     <row r="94" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B94" s="14" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C94" s="14"/>
       <c r="D94" s="14"/>
@@ -33482,26 +33409,26 @@
     </row>
     <row r="95" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B95" s="20" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C95" s="179">
-        <f>Statement!M199</f>
+        <f>Statement!M200</f>
         <v>0</v>
       </c>
       <c r="D95" s="179">
-        <f>Statement!N200</f>
+        <f>Statement!N201</f>
         <v>-2.5062656641604009E-3</v>
       </c>
       <c r="E95" s="179">
-        <f>Statement!O200</f>
+        <f>Statement!O201</f>
         <v>-7.537688442211055E-3</v>
       </c>
       <c r="F95" s="179">
-        <f>Statement!P200</f>
+        <f>Statement!P201</f>
         <v>1.1113924050632911</v>
       </c>
       <c r="G95" s="179">
-        <f>Statement!Q200</f>
+        <f>Statement!Q201</f>
         <v>0.16786570743405277</v>
       </c>
       <c r="I95" s="201"/>
@@ -33529,14 +33456,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="233" t="s">
+      <c r="C3" s="235" t="s">
+        <v>313</v>
+      </c>
+      <c r="D3" s="236"/>
+      <c r="F3" s="237" t="s">
         <v>314</v>
       </c>
-      <c r="D3" s="234"/>
-      <c r="F3" s="235" t="s">
-        <v>315</v>
-      </c>
-      <c r="G3" s="234"/>
+      <c r="G3" s="236"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -33559,7 +33486,7 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C5" s="10" t="str">
         <f>Statement!Z3</f>
@@ -33601,21 +33528,21 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B7" s="210" t="s">
-        <v>316</v>
-      </c>
-      <c r="C7" s="231">
+        <v>315</v>
+      </c>
+      <c r="C7" s="238">
         <f>Statement!AA87</f>
         <v>0.19798317847549429</v>
       </c>
-      <c r="D7" s="232"/>
-      <c r="F7" s="231">
+      <c r="D7" s="239"/>
+      <c r="F7" s="238">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.85227633788752211</v>
       </c>
-      <c r="G7" s="232"/>
+      <c r="G7" s="239"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="211" t="s">
@@ -33640,21 +33567,21 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B9" s="210" t="s">
-        <v>316</v>
-      </c>
-      <c r="C9" s="231">
+        <v>315</v>
+      </c>
+      <c r="C9" s="238">
         <f>Statement!AA88</f>
         <v>0.20100974521545145</v>
       </c>
-      <c r="D9" s="232"/>
-      <c r="F9" s="231">
+      <c r="D9" s="239"/>
+      <c r="F9" s="238">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.17615269633206854</v>
       </c>
-      <c r="G9" s="232"/>
+      <c r="G9" s="239"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="211" t="s">
@@ -33679,21 +33606,21 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B11" s="210" t="s">
-        <v>316</v>
-      </c>
-      <c r="C11" s="231">
+        <v>315</v>
+      </c>
+      <c r="C11" s="238">
         <f>Statement!AA89</f>
         <v>0.19697414518622902</v>
       </c>
-      <c r="D11" s="232"/>
-      <c r="F11" s="231">
+      <c r="D11" s="239"/>
+      <c r="F11" s="238">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.293272836358182</v>
       </c>
-      <c r="G11" s="232"/>
+      <c r="G11" s="239"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="211" t="s">
@@ -33718,25 +33645,25 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B13" s="210" t="s">
-        <v>316</v>
-      </c>
-      <c r="C13" s="231">
+        <v>315</v>
+      </c>
+      <c r="C13" s="238">
         <f>Statement!AA92</f>
         <v>0.12172505151604357</v>
       </c>
-      <c r="D13" s="232"/>
-      <c r="F13" s="231">
+      <c r="D13" s="239"/>
+      <c r="F13" s="238">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.51510934393638175</v>
       </c>
-      <c r="G13" s="232"/>
+      <c r="G13" s="239"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="211" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C14" s="204">
         <f>Statement!Z11</f>
@@ -33757,21 +33684,21 @@
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B15" s="210" t="s">
-        <v>316</v>
-      </c>
-      <c r="C15" s="231">
+        <v>315</v>
+      </c>
+      <c r="C15" s="238">
         <f>Statement!AA93</f>
         <v>0.20851486489537011</v>
       </c>
-      <c r="D15" s="232"/>
-      <c r="F15" s="231">
+      <c r="D15" s="239"/>
+      <c r="F15" s="238">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.4741658193918108</v>
       </c>
-      <c r="G15" s="232"/>
+      <c r="G15" s="239"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="211" t="s">
@@ -33796,25 +33723,25 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B17" s="210" t="s">
-        <v>316</v>
-      </c>
-      <c r="C17" s="231">
+        <v>315</v>
+      </c>
+      <c r="C17" s="238">
         <f>Statement!AA95</f>
         <v>0.35756517690875234</v>
       </c>
-      <c r="D17" s="232"/>
-      <c r="F17" s="231">
+      <c r="D17" s="239"/>
+      <c r="F17" s="238">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>2.1063115845539282</v>
       </c>
-      <c r="G17" s="232"/>
+      <c r="G17" s="239"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="211" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C18" s="204">
         <f>Statement!Z21</f>
@@ -33835,24 +33762,24 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B19" s="210" t="s">
-        <v>316</v>
-      </c>
-      <c r="C19" s="231">
+        <v>315</v>
+      </c>
+      <c r="C19" s="238">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-1.6781270464963983E-3</v>
       </c>
-      <c r="D19" s="232"/>
-      <c r="F19" s="231">
+      <c r="D19" s="239"/>
+      <c r="F19" s="238">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-8.9390922758116297E-3</v>
       </c>
-      <c r="G19" s="232"/>
+      <c r="G19" s="239"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="211" t="s">
@@ -33877,28 +33804,28 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B21" s="210" t="s">
-        <v>316</v>
-      </c>
-      <c r="C21" s="231">
+        <v>315</v>
+      </c>
+      <c r="C21" s="238">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.35795454545454553</v>
       </c>
-      <c r="D21" s="232"/>
-      <c r="F21" s="231">
+      <c r="D21" s="239"/>
+      <c r="F21" s="238">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>2.1447368421052633</v>
       </c>
-      <c r="G21" s="232"/>
+      <c r="G21" s="239"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C23" s="10" t="str">
         <f>C5</f>
@@ -33918,8 +33845,8 @@
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B24" s="246" t="s">
-        <v>374</v>
+      <c r="B24" s="228" t="s">
+        <v>373</v>
       </c>
       <c r="C24" s="204">
         <f>Statement!Z103</f>
@@ -33940,28 +33867,28 @@
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B25" s="210" t="s">
-        <v>316</v>
-      </c>
-      <c r="C25" s="231">
+        <v>315</v>
+      </c>
+      <c r="C25" s="238">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.11992074288756137</v>
       </c>
-      <c r="D25" s="232"/>
-      <c r="F25" s="231">
+      <c r="D25" s="239"/>
+      <c r="F25" s="238">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>1.1517699869310756</v>
       </c>
-      <c r="G25" s="232"/>
+      <c r="G25" s="239"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B26" s="246" t="s">
-        <v>375</v>
+      <c r="B26" s="228" t="s">
+        <v>374</v>
       </c>
       <c r="C26" s="204">
         <f>Statement!Z104</f>
@@ -33982,28 +33909,28 @@
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B27" s="210" t="s">
-        <v>316</v>
-      </c>
-      <c r="C27" s="231">
+        <v>315</v>
+      </c>
+      <c r="C27" s="238">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.31147368421052629</v>
       </c>
-      <c r="D27" s="232"/>
-      <c r="F27" s="231">
+      <c r="D27" s="239"/>
+      <c r="F27" s="238">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.73741458652907543</v>
       </c>
-      <c r="G27" s="232"/>
+      <c r="G27" s="239"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C28" s="204">
         <f>Statement!Z105</f>
@@ -34024,28 +33951,28 @@
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B29" s="210" t="s">
-        <v>316</v>
-      </c>
-      <c r="C29" s="231">
+        <v>315</v>
+      </c>
+      <c r="C29" s="238">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.20752960811374652</v>
       </c>
-      <c r="D29" s="232"/>
-      <c r="F29" s="231">
+      <c r="D29" s="239"/>
+      <c r="F29" s="238">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.92385968500715898</v>
       </c>
-      <c r="G29" s="232"/>
+      <c r="G29" s="239"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C30" s="204">
         <f>Statement!Z106</f>
@@ -34066,53 +33993,53 @@
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="210" t="s">
-        <v>316</v>
-      </c>
-      <c r="C31" s="231">
+        <v>315</v>
+      </c>
+      <c r="C31" s="238">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>9.5647686220540165E-2</v>
       </c>
-      <c r="D31" s="232"/>
-      <c r="F31" s="231">
+      <c r="D31" s="239"/>
+      <c r="F31" s="238">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.28666666666666668</v>
       </c>
-      <c r="G31" s="232"/>
+      <c r="G31" s="239"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="F31:G31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -34579,7 +34506,7 @@
     </row>
     <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B65" s="20" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C65" s="64">
         <f>Statement!H103</f>
@@ -34624,7 +34551,7 @@
     </row>
     <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B66" s="20" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C66" s="64">
         <f>Statement!H104</f>
@@ -34669,7 +34596,7 @@
     </row>
     <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B67" s="20" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C67" s="64">
         <f>Statement!H106</f>
@@ -35157,7 +35084,7 @@
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B63" s="20" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C63" s="64">
         <f>Statement!T103</f>
@@ -35194,7 +35121,7 @@
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B64" s="20" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C64" s="64">
         <f>Statement!T104</f>
@@ -35231,7 +35158,7 @@
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B65" s="20" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C65" s="64">
         <f>Statement!T106</f>

--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4630369-20F5-1A49-987C-1B2E0E2DE78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66665DB5-8957-3F46-990A-01708A302A17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -150,7 +150,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="391">
   <si>
     <t>Ticker</t>
   </si>
@@ -773,9 +773,6 @@
     <t>Year 5 UFCF</t>
   </si>
   <si>
-    <t>Applied EV/UFCF ratio</t>
-  </si>
-  <si>
     <t>AVG target price</t>
   </si>
   <si>
@@ -833,9 +830,6 @@
     <t>EBIT margin</t>
   </si>
   <si>
-    <t>WACC set manually</t>
-  </si>
-  <si>
     <t>Company guidance next Quarter</t>
   </si>
   <si>
@@ -1317,6 +1311,18 @@
   </si>
   <si>
     <t>FCFE/Sales (FCFE Margin)</t>
+  </si>
+  <si>
+    <t>PV of EV</t>
+  </si>
+  <si>
+    <t>Applied EV/FCFF ratio</t>
+  </si>
+  <si>
+    <t>Discount rate</t>
+  </si>
+  <si>
+    <t>Manual WACC</t>
   </si>
 </sst>
 </file>
@@ -2102,7 +2108,6 @@
     <xf numFmtId="4" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="12" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="10" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="10" fillId="11" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2128,7 +2133,6 @@
     <xf numFmtId="10" fontId="10" fillId="3" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="10" fillId="3" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="10" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="10" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2230,8 +2234,31 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="12" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="37" fontId="16" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2257,32 +2284,11 @@
     <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12511,7 +12517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825B172E-7ADE-4B4A-B533-F037BCFCDCB0}">
-  <dimension ref="B1:I47"/>
+  <dimension ref="B1:I49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -12528,338 +12534,338 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="232" t="s">
+      <c r="B2" s="239" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="233"/>
-      <c r="E2" s="232" t="s">
-        <v>287</v>
-      </c>
-      <c r="F2" s="233"/>
-      <c r="H2" s="232" t="s">
-        <v>328</v>
-      </c>
-      <c r="I2" s="233"/>
+      <c r="C2" s="240"/>
+      <c r="E2" s="239" t="s">
+        <v>285</v>
+      </c>
+      <c r="F2" s="240"/>
+      <c r="H2" s="239" t="s">
+        <v>326</v>
+      </c>
+      <c r="I2" s="240"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B3" s="189" t="s">
+      <c r="B3" s="187" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="221" t="e" vm="1">
+      <c r="C3" s="219" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
       <c r="D3" s="2"/>
-      <c r="E3" s="189" t="s">
-        <v>239</v>
-      </c>
-      <c r="F3" s="191">
+      <c r="E3" s="187" t="s">
+        <v>237</v>
+      </c>
+      <c r="F3" s="189">
         <f ca="1">Statement!AC164</f>
         <v>4984955.5</v>
       </c>
-      <c r="H3" s="189" t="str">
+      <c r="H3" s="187" t="str">
         <f>'AVG target price'!B5</f>
         <v>DCF price</v>
       </c>
-      <c r="I3" s="215">
+      <c r="I3" s="213">
         <f ca="1">'AVG target price'!C5</f>
         <v>129.85601384240837</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B4" s="189" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="193" t="str" cm="1">
+      <c r="B4" s="187" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="191" t="str" cm="1">
         <f t="array" aca="1" ref="C4" ca="1">_FV(C3,"Ticker symbol",TRUE)</f>
         <v>NVDA</v>
       </c>
-      <c r="E4" s="190" t="s">
+      <c r="E4" s="188" t="s">
         <v>181</v>
       </c>
-      <c r="F4" s="192">
+      <c r="F4" s="190">
         <f ca="1">Statement!AC165</f>
         <v>4912853.5</v>
       </c>
-      <c r="H4" s="189" t="str">
+      <c r="H4" s="187" t="str">
         <f>'AVG target price'!B6</f>
         <v>EV/EBIT price</v>
       </c>
-      <c r="I4" s="215">
+      <c r="I4" s="213">
         <f ca="1">'AVG target price'!C6</f>
-        <v>338.66542684737175</v>
+        <v>327.56000020556689</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B5" s="189" t="s">
+      <c r="B5" s="187" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="212" cm="1">
+      <c r="C5" s="210" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
         <v>205.1</v>
       </c>
-      <c r="E5" s="189" t="s">
-        <v>243</v>
-      </c>
-      <c r="F5" s="193">
+      <c r="E5" s="187" t="s">
+        <v>241</v>
+      </c>
+      <c r="F5" s="191">
         <f>Statement!AC25</f>
         <v>6.5299999999999994</v>
       </c>
-      <c r="H5" s="189" t="str">
+      <c r="H5" s="187" t="str">
         <f>'AVG target price'!B7</f>
         <v>PS price</v>
       </c>
-      <c r="I5" s="215">
-        <f ca="1">'AVG target price'!C7</f>
-        <v>273.49146395013889</v>
+      <c r="I5" s="213">
+        <f>'AVG target price'!C7</f>
+        <v>304.38678708173404</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B6" s="189" t="s">
+      <c r="B6" s="187" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="212" cm="1">
+      <c r="C6" s="210" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
         <v>204.06</v>
       </c>
-      <c r="E6" s="189" t="s">
-        <v>237</v>
-      </c>
-      <c r="F6" s="194">
+      <c r="E6" s="187" t="s">
+        <v>235</v>
+      </c>
+      <c r="F6" s="192">
         <f ca="1">Statement!AC161</f>
         <v>31.408882082695254</v>
       </c>
-      <c r="H6" s="189" t="str">
+      <c r="H6" s="187" t="str">
         <f>'AVG target price'!B8</f>
         <v>EV/FCFF price</v>
       </c>
-      <c r="I6" s="215">
+      <c r="I6" s="213">
         <f ca="1">'AVG target price'!C8</f>
-        <v>325.39805413086026</v>
+        <v>314.77042066082009</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B7" s="189" t="s">
+      <c r="B7" s="187" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
         <v>-13.56</v>
       </c>
-      <c r="E7" s="190" t="s">
+      <c r="E7" s="188" t="s">
         <v>194</v>
       </c>
-      <c r="F7" s="195">
+      <c r="F7" s="193">
         <f ca="1">Statement!AC162</f>
         <v>19.790223124292382</v>
       </c>
-      <c r="H7" s="188" t="str">
+      <c r="H7" s="186" t="str">
         <f>'AVG target price'!B9</f>
         <v>AVG price</v>
       </c>
-      <c r="I7" s="216">
+      <c r="I7" s="214">
         <f ca="1">'AVG target price'!C9</f>
-        <v>266.85273969269485</v>
+        <v>269.14330544763237</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B8" s="189" t="s">
+      <c r="B8" s="187" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
         <v>-1.04</v>
       </c>
-      <c r="E8" s="189" t="s">
-        <v>265</v>
-      </c>
-      <c r="F8" s="196">
+      <c r="E8" s="187" t="s">
+        <v>263</v>
+      </c>
+      <c r="F8" s="194">
         <f ca="1">Statement!AC172</f>
         <v>2.2515145822264611E-2</v>
       </c>
-      <c r="H8" s="188" t="str">
+      <c r="H8" s="186" t="str">
         <f>'AVG target price'!B11</f>
         <v>Upside/Downside</v>
       </c>
-      <c r="I8" s="217">
+      <c r="I8" s="215">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.30108600532761998</v>
+        <v>0.31225404898894382</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B9" s="189" t="s">
+      <c r="B9" s="187" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
         <v>-6.2013999999999993E-2</v>
       </c>
-      <c r="E9" s="189" t="s">
-        <v>288</v>
-      </c>
-      <c r="F9" s="196">
+      <c r="E9" s="187" t="s">
+        <v>286</v>
+      </c>
+      <c r="F9" s="194">
         <f ca="1">Statement!AC173</f>
         <v>3.1838127742564601E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B10" s="189" t="s">
+      <c r="B10" s="187" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
         <v>-5.071E-3</v>
       </c>
-      <c r="E10" s="189" t="s">
-        <v>293</v>
-      </c>
-      <c r="F10" s="196">
+      <c r="E10" s="187" t="s">
+        <v>291</v>
+      </c>
+      <c r="F10" s="194">
         <f ca="1">Statement!AC175</f>
         <v>9.0881453204547154E-3</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B11" s="189" t="s">
+      <c r="B11" s="187" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="213" cm="1">
+      <c r="C11" s="211" cm="1">
         <f t="array" aca="1" ref="C11" ca="1">_FV(C3,"52 week high",TRUE)</f>
         <v>236.54</v>
       </c>
-      <c r="E11" s="190" t="s">
-        <v>289</v>
-      </c>
-      <c r="F11" s="197">
+      <c r="E11" s="188" t="s">
+        <v>287</v>
+      </c>
+      <c r="F11" s="195">
         <f ca="1">Statement!AC174</f>
         <v>1.9502681618722574E-4</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B12" s="189" t="s">
+      <c r="B12" s="187" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="213" cm="1">
+      <c r="C12" s="211" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
         <v>140.85499999999999</v>
       </c>
-      <c r="E12" s="189" t="s">
+      <c r="E12" s="187" t="s">
         <v>94</v>
       </c>
-      <c r="F12" s="196">
+      <c r="F12" s="194">
         <f>Statement!AC127</f>
         <v>0.61514063066049007</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B13" s="189" t="s">
+      <c r="B13" s="187" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="213" cm="1">
+      <c r="C13" s="211" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
         <v>2.2010999999999998</v>
       </c>
-      <c r="E13" s="189" t="s">
+      <c r="E13" s="187" t="s">
         <v>96</v>
       </c>
-      <c r="F13" s="196">
+      <c r="F13" s="194">
         <f>Statement!AC129</f>
         <v>0.81654337661274645</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B14" s="190" t="s">
+      <c r="B14" s="188" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="214" cm="1">
+      <c r="C14" s="212" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
         <v>171448900</v>
       </c>
-      <c r="E14" s="190" t="s">
+      <c r="E14" s="188" t="s">
         <v>97</v>
       </c>
-      <c r="F14" s="197">
+      <c r="F14" s="195">
         <f>Statement!AC151</f>
         <v>1.1082908941558067</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="E15" s="189" t="s">
-        <v>290</v>
-      </c>
-      <c r="F15" s="196">
+      <c r="E15" s="187" t="s">
+        <v>288</v>
+      </c>
+      <c r="F15" s="194">
         <f ca="1">Statement!AC187</f>
         <v>1.4463920490363455E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="E16" s="190" t="s">
-        <v>295</v>
-      </c>
-      <c r="F16" s="195">
+      <c r="E16" s="188" t="s">
+        <v>293</v>
+      </c>
+      <c r="F16" s="193">
         <f>Statement!AC186</f>
         <v>2.9794214876033056</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="234" t="s">
+      <c r="B17" s="241" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="234"/>
-      <c r="E17" s="188" t="s">
-        <v>296</v>
-      </c>
-      <c r="F17" s="198">
+      <c r="C17" s="241"/>
+      <c r="E17" s="186" t="s">
+        <v>294</v>
+      </c>
+      <c r="F17" s="196">
         <f>Statement!AC182</f>
         <v>3.9374614276897757E-2</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B18" s="188" t="s">
+      <c r="B18" s="186" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="69" t="s">
-        <v>346</v>
-      </c>
-      <c r="E18" s="189" t="s">
-        <v>297</v>
-      </c>
-      <c r="F18" s="194">
+        <v>344</v>
+      </c>
+      <c r="E18" s="187" t="s">
+        <v>295</v>
+      </c>
+      <c r="F18" s="192">
         <f>Statement!AC155</f>
         <v>129.34693643390989</v>
       </c>
       <c r="I18" s="50"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="188" t="s">
+      <c r="B19" s="186" t="s">
         <v>13</v>
       </c>
       <c r="C19" s="70">
         <v>1000000</v>
       </c>
-      <c r="E19" s="189" t="s">
-        <v>258</v>
-      </c>
-      <c r="F19" s="194">
+      <c r="E19" s="187" t="s">
+        <v>256</v>
+      </c>
+      <c r="F19" s="192">
         <f>Statement!AC157</f>
         <v>-0.36885723932594616</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B20" s="188" t="s">
+      <c r="B20" s="186" t="s">
         <v>84</v>
       </c>
       <c r="C20" s="69" t="s">
-        <v>353</v>
-      </c>
-      <c r="E20" s="190" t="s">
-        <v>298</v>
-      </c>
-      <c r="F20" s="195">
+        <v>351</v>
+      </c>
+      <c r="E20" s="188" t="s">
+        <v>296</v>
+      </c>
+      <c r="F20" s="193">
         <f>Statement!AC158</f>
         <v>2.7636951964269438</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B21" s="188" t="s">
+      <c r="B21" s="186" t="s">
         <v>85</v>
       </c>
       <c r="C21" s="69" t="s">
@@ -12868,127 +12874,143 @@
       <c r="I21" s="50"/>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B22" s="188" t="s">
+      <c r="B22" s="186" t="s">
         <v>87</v>
       </c>
       <c r="C22" s="69" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="234" t="s">
+      <c r="B25" s="241" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="234"/>
-      <c r="E25" s="232" t="s">
-        <v>343</v>
-      </c>
-      <c r="F25" s="233"/>
+      <c r="C25" s="241"/>
+      <c r="E25" s="239" t="s">
+        <v>341</v>
+      </c>
+      <c r="F25" s="240"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B26" s="188" t="s">
+      <c r="B26" s="186" t="s">
         <v>100</v>
       </c>
-      <c r="C26" s="173">
+      <c r="C26" s="171">
         <v>0.21</v>
       </c>
-      <c r="E26" s="189" t="e" vm="2">
+      <c r="E26" s="187" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="F26" s="224" cm="1">
+      <c r="F26" s="222" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
         <v>45.36</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B27" s="188" t="s">
+      <c r="B27" s="186" t="s">
         <v>165</v>
       </c>
-      <c r="C27" s="226">
+      <c r="C27" s="224">
         <v>5.0999999999999997E-2</v>
       </c>
-      <c r="E27" s="190" t="s">
-        <v>344</v>
-      </c>
-      <c r="F27" s="225">
+      <c r="E27" s="188" t="s">
+        <v>342</v>
+      </c>
+      <c r="F27" s="223">
         <f ca="1">F26/1000</f>
         <v>4.5359999999999998E-2</v>
       </c>
     </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B31" s="231" t="s">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B28" s="186" t="s">
+        <v>390</v>
+      </c>
+      <c r="C28" s="224">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B29" s="186" t="s">
+        <v>389</v>
+      </c>
+      <c r="C29" s="224">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B33" s="231" t="s">
+        <v>336</v>
+      </c>
+      <c r="C33" s="231"/>
+      <c r="D33" s="231"/>
+      <c r="E33" s="231"/>
+      <c r="F33" s="231"/>
+      <c r="G33" s="231"/>
+      <c r="H33" s="231"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B35" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B36" s="16" t="s">
         <v>338</v>
       </c>
-      <c r="C31" s="231"/>
-      <c r="D31" s="231"/>
-      <c r="E31" s="231"/>
-      <c r="F31" s="231"/>
-      <c r="G31" s="231"/>
-      <c r="H31" s="231"/>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="16" t="s">
+      <c r="C36" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="231"/>
+      <c r="C39" s="231"/>
+      <c r="D39" s="231"/>
+      <c r="E39" s="231"/>
+      <c r="F39" s="231"/>
+      <c r="G39" s="231"/>
+      <c r="H39" s="231"/>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B42" s="231" t="s">
         <v>339</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B34" s="16" t="s">
+      <c r="C42" s="231"/>
+      <c r="D42" s="231"/>
+      <c r="E42" s="231"/>
+      <c r="F42" s="231"/>
+      <c r="G42" s="231"/>
+      <c r="H42" s="231"/>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B44" s="41" t="s">
         <v>340</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="231"/>
-      <c r="C37" s="231"/>
-      <c r="D37" s="231"/>
-      <c r="E37" s="231"/>
-      <c r="F37" s="231"/>
-      <c r="G37" s="231"/>
-      <c r="H37" s="231"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B40" s="231" t="s">
-        <v>341</v>
-      </c>
-      <c r="C40" s="231"/>
-      <c r="D40" s="231"/>
-      <c r="E40" s="231"/>
-      <c r="F40" s="231"/>
-      <c r="G40" s="231"/>
-      <c r="H40" s="231"/>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="41" t="s">
-        <v>342</v>
-      </c>
-      <c r="C42" s="41" t="s">
-        <v>329</v>
-      </c>
-      <c r="D42" s="41" t="s">
-        <v>330</v>
-      </c>
-      <c r="E42" s="222"/>
-    </row>
-    <row r="47" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="231"/>
-      <c r="C47" s="231"/>
-      <c r="D47" s="231"/>
-      <c r="E47" s="231"/>
-      <c r="F47" s="231"/>
-      <c r="G47" s="231"/>
-      <c r="H47" s="231"/>
+      <c r="C44" s="41" t="s">
+        <v>327</v>
+      </c>
+      <c r="D44" s="41" t="s">
+        <v>328</v>
+      </c>
+      <c r="E44" s="220"/>
+    </row>
+    <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B49" s="231"/>
+      <c r="C49" s="231"/>
+      <c r="D49" s="231"/>
+      <c r="E49" s="231"/>
+      <c r="F49" s="231"/>
+      <c r="G49" s="231"/>
+      <c r="H49" s="231"/>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="B31:H31"/>
-    <mergeCell ref="B37:H37"/>
-    <mergeCell ref="B40:H40"/>
-    <mergeCell ref="B47:H47"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B49:H49"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
@@ -13070,8 +13092,8 @@
       <c r="D2" s="231"/>
       <c r="E2" s="231"/>
       <c r="F2" s="231"/>
-      <c r="G2" s="243"/>
-      <c r="H2" s="244" t="s">
+      <c r="G2" s="232"/>
+      <c r="H2" s="233" t="s">
         <v>106</v>
       </c>
       <c r="I2" s="231"/>
@@ -13104,32 +13126,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="240" t="s">
+      <c r="C4" s="235" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="240"/>
-      <c r="E4" s="240"/>
-      <c r="F4" s="240"/>
-      <c r="G4" s="240"/>
-      <c r="H4" s="240"/>
-      <c r="I4" s="240"/>
-      <c r="J4" s="240"/>
-      <c r="K4" s="240"/>
-      <c r="L4" s="240"/>
+      <c r="D4" s="235"/>
+      <c r="E4" s="235"/>
+      <c r="F4" s="235"/>
+      <c r="G4" s="235"/>
+      <c r="H4" s="235"/>
+      <c r="I4" s="235"/>
+      <c r="J4" s="235"/>
+      <c r="K4" s="235"/>
+      <c r="L4" s="235"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="241" t="s">
+      <c r="S4" s="247" t="s">
         <v>108</v>
       </c>
-      <c r="T4" s="242"/>
-      <c r="U4" s="242"/>
-      <c r="V4" s="242"/>
-      <c r="W4" s="242"/>
-      <c r="X4" s="242"/>
-      <c r="Y4" s="242"/>
-      <c r="Z4" s="242"/>
-      <c r="AA4" s="242"/>
-      <c r="AB4" s="242"/>
-      <c r="AC4" s="242"/>
+      <c r="T4" s="248"/>
+      <c r="U4" s="248"/>
+      <c r="V4" s="248"/>
+      <c r="W4" s="248"/>
+      <c r="X4" s="248"/>
+      <c r="Y4" s="248"/>
+      <c r="Z4" s="248"/>
+      <c r="AA4" s="248"/>
+      <c r="AB4" s="248"/>
+      <c r="AC4" s="248"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -13227,7 +13249,7 @@
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B6" s="229" t="str">
+      <c r="B6" s="227" t="str">
         <f>Statement!B103</f>
         <v>HyperScale</v>
       </c>
@@ -13272,13 +13294,13 @@
         <v>899038.4839425002</v>
       </c>
       <c r="N6" s="90" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="O6" s="5"/>
       <c r="Q6" s="90" t="s">
-        <v>384</v>
-      </c>
-      <c r="R6" s="229" t="str">
+        <v>382</v>
+      </c>
+      <c r="R6" s="227" t="str">
         <f>B6</f>
         <v>HyperScale</v>
       </c>
@@ -13326,7 +13348,7 @@
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B7" s="229" t="str">
+      <c r="B7" s="227" t="str">
         <f>Statement!B104</f>
         <v>AI Clouds</v>
       </c>
@@ -13371,13 +13393,13 @@
         <v>276381.4356576</v>
       </c>
       <c r="N7" s="90" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="O7" s="5"/>
       <c r="Q7" s="90" t="s">
-        <v>385</v>
-      </c>
-      <c r="R7" s="229" t="str">
+        <v>383</v>
+      </c>
+      <c r="R7" s="227" t="str">
         <f t="shared" ref="R7:R9" si="2">B7</f>
         <v>AI Clouds</v>
       </c>
@@ -13565,11 +13587,11 @@
         <v>81428.411531250007</v>
       </c>
       <c r="N9" s="90" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="O9" s="5"/>
       <c r="Q9" s="90" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="R9" s="1" t="str">
         <f t="shared" si="2"/>
@@ -13714,33 +13736,33 @@
       <c r="Q11" s="91"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C12" s="240" t="s">
+      <c r="C12" s="235" t="s">
         <v>114</v>
       </c>
-      <c r="D12" s="240"/>
-      <c r="E12" s="240"/>
-      <c r="F12" s="240"/>
-      <c r="G12" s="240"/>
-      <c r="H12" s="240"/>
-      <c r="I12" s="240"/>
-      <c r="J12" s="240"/>
-      <c r="K12" s="240"/>
-      <c r="L12" s="240"/>
+      <c r="D12" s="235"/>
+      <c r="E12" s="235"/>
+      <c r="F12" s="235"/>
+      <c r="G12" s="235"/>
+      <c r="H12" s="235"/>
+      <c r="I12" s="235"/>
+      <c r="J12" s="235"/>
+      <c r="K12" s="235"/>
+      <c r="L12" s="235"/>
       <c r="O12" s="5"/>
       <c r="Q12" s="91"/>
-      <c r="S12" s="241" t="s">
+      <c r="S12" s="247" t="s">
         <v>114</v>
       </c>
-      <c r="T12" s="242"/>
-      <c r="U12" s="242"/>
-      <c r="V12" s="242"/>
-      <c r="W12" s="242"/>
-      <c r="X12" s="242"/>
-      <c r="Y12" s="242"/>
-      <c r="Z12" s="242"/>
-      <c r="AA12" s="242"/>
-      <c r="AB12" s="242"/>
-      <c r="AC12" s="242"/>
+      <c r="T12" s="248"/>
+      <c r="U12" s="248"/>
+      <c r="V12" s="248"/>
+      <c r="W12" s="248"/>
+      <c r="X12" s="248"/>
+      <c r="Y12" s="248"/>
+      <c r="Z12" s="248"/>
+      <c r="AA12" s="248"/>
+      <c r="AB12" s="248"/>
+      <c r="AC12" s="248"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B13" s="16" t="s">
@@ -13837,7 +13859,7 @@
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B14" s="229" t="str">
+      <c r="B14" s="227" t="str">
         <f>B6</f>
         <v>HyperScale</v>
       </c>
@@ -13875,7 +13897,7 @@
       </c>
       <c r="O14" s="5"/>
       <c r="Q14" s="91"/>
-      <c r="R14" s="229" t="str">
+      <c r="R14" s="227" t="str">
         <f>R6</f>
         <v>HyperScale</v>
       </c>
@@ -13915,7 +13937,7 @@
       <c r="AC14" s="95"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B15" s="229" t="str">
+      <c r="B15" s="227" t="str">
         <f>B7</f>
         <v>AI Clouds</v>
       </c>
@@ -13953,7 +13975,7 @@
       </c>
       <c r="O15" s="5"/>
       <c r="Q15" s="91"/>
-      <c r="R15" s="229" t="str">
+      <c r="R15" s="227" t="str">
         <f>R7</f>
         <v>AI Clouds</v>
       </c>
@@ -14295,8 +14317,8 @@
       <c r="D2" s="231"/>
       <c r="E2" s="231"/>
       <c r="F2" s="231"/>
-      <c r="G2" s="243"/>
-      <c r="H2" s="244" t="s">
+      <c r="G2" s="232"/>
+      <c r="H2" s="233" t="s">
         <v>106</v>
       </c>
       <c r="I2" s="231"/>
@@ -14326,31 +14348,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="240" t="s">
+      <c r="C4" s="235" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="240"/>
-      <c r="E4" s="240"/>
-      <c r="F4" s="240"/>
-      <c r="G4" s="240"/>
-      <c r="H4" s="240"/>
-      <c r="I4" s="240"/>
-      <c r="J4" s="240"/>
-      <c r="K4" s="240"/>
-      <c r="L4" s="240"/>
-      <c r="P4" s="242" t="s">
+      <c r="D4" s="235"/>
+      <c r="E4" s="235"/>
+      <c r="F4" s="235"/>
+      <c r="G4" s="235"/>
+      <c r="H4" s="235"/>
+      <c r="I4" s="235"/>
+      <c r="J4" s="235"/>
+      <c r="K4" s="235"/>
+      <c r="L4" s="235"/>
+      <c r="P4" s="248" t="s">
         <v>108</v>
       </c>
-      <c r="Q4" s="242"/>
-      <c r="R4" s="242"/>
-      <c r="S4" s="242"/>
-      <c r="T4" s="242"/>
-      <c r="U4" s="242"/>
-      <c r="V4" s="242"/>
-      <c r="W4" s="242"/>
-      <c r="X4" s="242"/>
-      <c r="Y4" s="242"/>
-      <c r="Z4" s="242"/>
+      <c r="Q4" s="248"/>
+      <c r="R4" s="248"/>
+      <c r="S4" s="248"/>
+      <c r="T4" s="248"/>
+      <c r="U4" s="248"/>
+      <c r="V4" s="248"/>
+      <c r="W4" s="248"/>
+      <c r="X4" s="248"/>
+      <c r="Y4" s="248"/>
+      <c r="Z4" s="248"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -14545,32 +14567,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="240" t="s">
+      <c r="C9" s="235" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="240"/>
-      <c r="E9" s="240"/>
-      <c r="F9" s="240"/>
-      <c r="G9" s="240"/>
-      <c r="H9" s="240"/>
-      <c r="I9" s="240"/>
-      <c r="J9" s="240"/>
-      <c r="K9" s="240"/>
-      <c r="L9" s="240"/>
+      <c r="D9" s="235"/>
+      <c r="E9" s="235"/>
+      <c r="F9" s="235"/>
+      <c r="G9" s="235"/>
+      <c r="H9" s="235"/>
+      <c r="I9" s="235"/>
+      <c r="J9" s="235"/>
+      <c r="K9" s="235"/>
+      <c r="L9" s="235"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="242" t="s">
+      <c r="P9" s="248" t="s">
         <v>118</v>
       </c>
-      <c r="Q9" s="242"/>
-      <c r="R9" s="242"/>
-      <c r="S9" s="242"/>
-      <c r="T9" s="242"/>
-      <c r="U9" s="242"/>
-      <c r="V9" s="242"/>
-      <c r="W9" s="242"/>
-      <c r="X9" s="242"/>
-      <c r="Y9" s="242"/>
-      <c r="Z9" s="242"/>
+      <c r="Q9" s="248"/>
+      <c r="R9" s="248"/>
+      <c r="S9" s="248"/>
+      <c r="T9" s="248"/>
+      <c r="U9" s="248"/>
+      <c r="V9" s="248"/>
+      <c r="W9" s="248"/>
+      <c r="X9" s="248"/>
+      <c r="Y9" s="248"/>
+      <c r="Z9" s="248"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -15046,31 +15068,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="240" t="s">
+      <c r="C17" s="235" t="s">
         <v>120</v>
       </c>
-      <c r="D17" s="240"/>
-      <c r="E17" s="240"/>
-      <c r="F17" s="240"/>
-      <c r="G17" s="240"/>
-      <c r="H17" s="240"/>
-      <c r="I17" s="240"/>
-      <c r="J17" s="240"/>
-      <c r="K17" s="240"/>
-      <c r="L17" s="240"/>
-      <c r="P17" s="242" t="s">
+      <c r="D17" s="235"/>
+      <c r="E17" s="235"/>
+      <c r="F17" s="235"/>
+      <c r="G17" s="235"/>
+      <c r="H17" s="235"/>
+      <c r="I17" s="235"/>
+      <c r="J17" s="235"/>
+      <c r="K17" s="235"/>
+      <c r="L17" s="235"/>
+      <c r="P17" s="248" t="s">
         <v>120</v>
       </c>
-      <c r="Q17" s="242"/>
-      <c r="R17" s="242"/>
-      <c r="S17" s="242"/>
-      <c r="T17" s="242"/>
-      <c r="U17" s="242"/>
-      <c r="V17" s="242"/>
-      <c r="W17" s="242"/>
-      <c r="X17" s="242"/>
-      <c r="Y17" s="242"/>
-      <c r="Z17" s="242"/>
+      <c r="Q17" s="248"/>
+      <c r="R17" s="248"/>
+      <c r="S17" s="248"/>
+      <c r="T17" s="248"/>
+      <c r="U17" s="248"/>
+      <c r="V17" s="248"/>
+      <c r="W17" s="248"/>
+      <c r="X17" s="248"/>
+      <c r="Y17" s="248"/>
+      <c r="Z17" s="248"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="16" t="s">
@@ -15554,54 +15576,54 @@
       <c r="D3" s="231"/>
       <c r="E3" s="231"/>
       <c r="F3" s="231"/>
-      <c r="G3" s="243"/>
-      <c r="H3" s="244" t="s">
+      <c r="G3" s="232"/>
+      <c r="H3" s="233" t="s">
         <v>106</v>
       </c>
       <c r="I3" s="231"/>
       <c r="J3" s="231"/>
       <c r="K3" s="231"/>
       <c r="L3" s="231"/>
-      <c r="P3" s="245"/>
-      <c r="Q3" s="245"/>
-      <c r="R3" s="245"/>
-      <c r="S3" s="245"/>
-      <c r="T3" s="245"/>
-      <c r="U3" s="245"/>
-      <c r="V3" s="245"/>
-      <c r="W3" s="245"/>
-      <c r="X3" s="245"/>
-      <c r="Y3" s="245"/>
-      <c r="Z3" s="245"/>
+      <c r="P3" s="234"/>
+      <c r="Q3" s="234"/>
+      <c r="R3" s="234"/>
+      <c r="S3" s="234"/>
+      <c r="T3" s="234"/>
+      <c r="U3" s="234"/>
+      <c r="V3" s="234"/>
+      <c r="W3" s="234"/>
+      <c r="X3" s="234"/>
+      <c r="Y3" s="234"/>
+      <c r="Z3" s="234"/>
       <c r="AB3" s="110"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="240" t="s">
+      <c r="C5" s="235" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="240"/>
-      <c r="E5" s="240"/>
-      <c r="F5" s="240"/>
-      <c r="G5" s="240"/>
-      <c r="H5" s="240"/>
-      <c r="I5" s="240"/>
-      <c r="J5" s="240"/>
-      <c r="K5" s="240"/>
-      <c r="L5" s="240"/>
-      <c r="P5" s="245"/>
-      <c r="Q5" s="245"/>
-      <c r="R5" s="245"/>
-      <c r="S5" s="245"/>
-      <c r="T5" s="245"/>
-      <c r="U5" s="245"/>
-      <c r="V5" s="245"/>
-      <c r="W5" s="245"/>
-      <c r="X5" s="245"/>
-      <c r="Y5" s="245"/>
-      <c r="Z5" s="245"/>
+      <c r="D5" s="235"/>
+      <c r="E5" s="235"/>
+      <c r="F5" s="235"/>
+      <c r="G5" s="235"/>
+      <c r="H5" s="235"/>
+      <c r="I5" s="235"/>
+      <c r="J5" s="235"/>
+      <c r="K5" s="235"/>
+      <c r="L5" s="235"/>
+      <c r="P5" s="234"/>
+      <c r="Q5" s="234"/>
+      <c r="R5" s="234"/>
+      <c r="S5" s="234"/>
+      <c r="T5" s="234"/>
+      <c r="U5" s="234"/>
+      <c r="V5" s="234"/>
+      <c r="W5" s="234"/>
+      <c r="X5" s="234"/>
+      <c r="Y5" s="234"/>
+      <c r="Z5" s="234"/>
       <c r="AB5" s="111"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -15787,30 +15809,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="240" t="s">
+      <c r="C11" s="235" t="s">
         <v>124</v>
       </c>
-      <c r="D11" s="240"/>
-      <c r="E11" s="240"/>
-      <c r="F11" s="240"/>
-      <c r="G11" s="240"/>
-      <c r="H11" s="240"/>
-      <c r="I11" s="240"/>
-      <c r="J11" s="240"/>
-      <c r="K11" s="240"/>
-      <c r="L11" s="240"/>
+      <c r="D11" s="235"/>
+      <c r="E11" s="235"/>
+      <c r="F11" s="235"/>
+      <c r="G11" s="235"/>
+      <c r="H11" s="235"/>
+      <c r="I11" s="235"/>
+      <c r="J11" s="235"/>
+      <c r="K11" s="235"/>
+      <c r="L11" s="235"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="245"/>
-      <c r="Q11" s="245"/>
-      <c r="R11" s="245"/>
-      <c r="S11" s="245"/>
-      <c r="T11" s="245"/>
-      <c r="U11" s="245"/>
-      <c r="V11" s="245"/>
-      <c r="W11" s="245"/>
-      <c r="X11" s="245"/>
-      <c r="Y11" s="245"/>
-      <c r="Z11" s="245"/>
+      <c r="P11" s="234"/>
+      <c r="Q11" s="234"/>
+      <c r="R11" s="234"/>
+      <c r="S11" s="234"/>
+      <c r="T11" s="234"/>
+      <c r="U11" s="234"/>
+      <c r="V11" s="234"/>
+      <c r="W11" s="234"/>
+      <c r="X11" s="234"/>
+      <c r="Y11" s="234"/>
+      <c r="Z11" s="234"/>
       <c r="AB11" s="111"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -16052,18 +16074,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="240" t="s">
+      <c r="C18" s="235" t="s">
         <v>129</v>
       </c>
-      <c r="D18" s="240"/>
-      <c r="E18" s="240"/>
-      <c r="F18" s="240"/>
-      <c r="G18" s="240"/>
-      <c r="H18" s="240"/>
-      <c r="I18" s="240"/>
-      <c r="J18" s="240"/>
-      <c r="K18" s="240"/>
-      <c r="L18" s="240"/>
+      <c r="D18" s="235"/>
+      <c r="E18" s="235"/>
+      <c r="F18" s="235"/>
+      <c r="G18" s="235"/>
+      <c r="H18" s="235"/>
+      <c r="I18" s="235"/>
+      <c r="J18" s="235"/>
+      <c r="K18" s="235"/>
+      <c r="L18" s="235"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -16276,23 +16298,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="245"/>
-      <c r="C25" s="245"/>
+      <c r="B25" s="234"/>
+      <c r="C25" s="234"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="110"/>
-      <c r="C26" s="240" t="s">
+      <c r="C26" s="235" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="240"/>
-      <c r="E26" s="240"/>
-      <c r="F26" s="240"/>
-      <c r="G26" s="240"/>
-      <c r="H26" s="240"/>
-      <c r="I26" s="240"/>
-      <c r="J26" s="240"/>
-      <c r="K26" s="240"/>
-      <c r="L26" s="240"/>
+      <c r="D26" s="235"/>
+      <c r="E26" s="235"/>
+      <c r="F26" s="235"/>
+      <c r="G26" s="235"/>
+      <c r="H26" s="235"/>
+      <c r="I26" s="235"/>
+      <c r="J26" s="235"/>
+      <c r="K26" s="235"/>
+      <c r="L26" s="235"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -16484,18 +16506,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="110"/>
-      <c r="C33" s="240" t="s">
+      <c r="C33" s="235" t="s">
         <v>139</v>
       </c>
-      <c r="D33" s="240"/>
-      <c r="E33" s="240"/>
-      <c r="F33" s="240"/>
-      <c r="G33" s="240"/>
-      <c r="H33" s="240"/>
-      <c r="I33" s="240"/>
-      <c r="J33" s="240"/>
-      <c r="K33" s="240"/>
-      <c r="L33" s="240"/>
+      <c r="D33" s="235"/>
+      <c r="E33" s="235"/>
+      <c r="F33" s="235"/>
+      <c r="G33" s="235"/>
+      <c r="H33" s="235"/>
+      <c r="I33" s="235"/>
+      <c r="J33" s="235"/>
+      <c r="K33" s="235"/>
+      <c r="L33" s="235"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -16679,18 +16701,18 @@
       <c r="C39" s="126"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="240" t="s">
+      <c r="C40" s="235" t="s">
         <v>142</v>
       </c>
-      <c r="D40" s="240"/>
-      <c r="E40" s="240"/>
-      <c r="F40" s="240"/>
-      <c r="G40" s="240"/>
-      <c r="H40" s="240"/>
-      <c r="I40" s="240"/>
-      <c r="J40" s="240"/>
-      <c r="K40" s="240"/>
-      <c r="L40" s="240"/>
+      <c r="D40" s="235"/>
+      <c r="E40" s="235"/>
+      <c r="F40" s="235"/>
+      <c r="G40" s="235"/>
+      <c r="H40" s="235"/>
+      <c r="I40" s="235"/>
+      <c r="J40" s="235"/>
+      <c r="K40" s="235"/>
+      <c r="L40" s="235"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -17010,54 +17032,54 @@
       <c r="D2" s="231"/>
       <c r="E2" s="231"/>
       <c r="F2" s="231"/>
-      <c r="G2" s="243"/>
-      <c r="H2" s="244" t="s">
+      <c r="G2" s="232"/>
+      <c r="H2" s="233" t="s">
         <v>106</v>
       </c>
       <c r="I2" s="231"/>
       <c r="J2" s="231"/>
       <c r="K2" s="231"/>
       <c r="L2" s="231"/>
-      <c r="S2" s="245"/>
-      <c r="T2" s="245"/>
-      <c r="U2" s="245"/>
-      <c r="V2" s="245"/>
-      <c r="W2" s="245"/>
-      <c r="X2" s="245"/>
-      <c r="Y2" s="245"/>
-      <c r="Z2" s="245"/>
-      <c r="AA2" s="245"/>
-      <c r="AB2" s="245"/>
-      <c r="AC2" s="245"/>
+      <c r="S2" s="234"/>
+      <c r="T2" s="234"/>
+      <c r="U2" s="234"/>
+      <c r="V2" s="234"/>
+      <c r="W2" s="234"/>
+      <c r="X2" s="234"/>
+      <c r="Y2" s="234"/>
+      <c r="Z2" s="234"/>
+      <c r="AA2" s="234"/>
+      <c r="AB2" s="234"/>
+      <c r="AC2" s="234"/>
       <c r="AE2" s="110"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="240" t="s">
+      <c r="C4" s="235" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="240"/>
-      <c r="E4" s="240"/>
-      <c r="F4" s="240"/>
-      <c r="G4" s="240"/>
-      <c r="H4" s="240"/>
-      <c r="I4" s="240"/>
-      <c r="J4" s="240"/>
-      <c r="K4" s="240"/>
-      <c r="L4" s="240"/>
-      <c r="S4" s="245"/>
-      <c r="T4" s="245"/>
-      <c r="U4" s="245"/>
-      <c r="V4" s="245"/>
-      <c r="W4" s="245"/>
-      <c r="X4" s="245"/>
-      <c r="Y4" s="245"/>
-      <c r="Z4" s="245"/>
-      <c r="AA4" s="245"/>
-      <c r="AB4" s="245"/>
-      <c r="AC4" s="245"/>
+      <c r="D4" s="235"/>
+      <c r="E4" s="235"/>
+      <c r="F4" s="235"/>
+      <c r="G4" s="235"/>
+      <c r="H4" s="235"/>
+      <c r="I4" s="235"/>
+      <c r="J4" s="235"/>
+      <c r="K4" s="235"/>
+      <c r="L4" s="235"/>
+      <c r="S4" s="234"/>
+      <c r="T4" s="234"/>
+      <c r="U4" s="234"/>
+      <c r="V4" s="234"/>
+      <c r="W4" s="234"/>
+      <c r="X4" s="234"/>
+      <c r="Y4" s="234"/>
+      <c r="Z4" s="234"/>
+      <c r="AA4" s="234"/>
+      <c r="AB4" s="234"/>
+      <c r="AC4" s="234"/>
       <c r="AE4" s="111"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -17420,18 +17442,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="240" t="s">
+      <c r="C13" s="235" t="s">
         <v>150</v>
       </c>
-      <c r="D13" s="240"/>
-      <c r="E13" s="240"/>
-      <c r="F13" s="240"/>
-      <c r="G13" s="240"/>
-      <c r="H13" s="240"/>
-      <c r="I13" s="240"/>
-      <c r="J13" s="240"/>
-      <c r="K13" s="240"/>
-      <c r="L13" s="240"/>
+      <c r="D13" s="235"/>
+      <c r="E13" s="235"/>
+      <c r="F13" s="235"/>
+      <c r="G13" s="235"/>
+      <c r="H13" s="235"/>
+      <c r="I13" s="235"/>
+      <c r="J13" s="235"/>
+      <c r="K13" s="235"/>
+      <c r="L13" s="235"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -17524,18 +17546,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="240" t="s">
+      <c r="C18" s="235" t="s">
         <v>151</v>
       </c>
-      <c r="D18" s="240"/>
-      <c r="E18" s="240"/>
-      <c r="F18" s="240"/>
-      <c r="G18" s="240"/>
-      <c r="H18" s="240"/>
-      <c r="I18" s="240"/>
-      <c r="J18" s="240"/>
-      <c r="K18" s="240"/>
-      <c r="L18" s="240"/>
+      <c r="D18" s="235"/>
+      <c r="E18" s="235"/>
+      <c r="F18" s="235"/>
+      <c r="G18" s="235"/>
+      <c r="H18" s="235"/>
+      <c r="I18" s="235"/>
+      <c r="J18" s="235"/>
+      <c r="K18" s="235"/>
+      <c r="L18" s="235"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17727,18 +17749,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="240" t="s">
+      <c r="C25" s="235" t="s">
         <v>154</v>
       </c>
-      <c r="D25" s="240"/>
-      <c r="E25" s="240"/>
-      <c r="F25" s="240"/>
-      <c r="G25" s="240"/>
-      <c r="H25" s="240"/>
-      <c r="I25" s="240"/>
-      <c r="J25" s="240"/>
-      <c r="K25" s="240"/>
-      <c r="L25" s="240"/>
+      <c r="D25" s="235"/>
+      <c r="E25" s="235"/>
+      <c r="F25" s="235"/>
+      <c r="G25" s="235"/>
+      <c r="H25" s="235"/>
+      <c r="I25" s="235"/>
+      <c r="J25" s="235"/>
+      <c r="K25" s="235"/>
+      <c r="L25" s="235"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -17832,7 +17854,7 @@
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B28" s="16" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C28" s="94">
         <f>C27+C20-C21+C22</f>
@@ -17876,22 +17898,22 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="240" t="s">
+      <c r="C31" s="235" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="240"/>
-      <c r="E31" s="240"/>
-      <c r="F31" s="240"/>
-      <c r="G31" s="240"/>
-      <c r="H31" s="240"/>
-      <c r="I31" s="240"/>
-      <c r="J31" s="240"/>
-      <c r="K31" s="240"/>
-      <c r="L31" s="240"/>
+      <c r="D31" s="235"/>
+      <c r="E31" s="235"/>
+      <c r="F31" s="235"/>
+      <c r="G31" s="235"/>
+      <c r="H31" s="235"/>
+      <c r="I31" s="235"/>
+      <c r="J31" s="235"/>
+      <c r="K31" s="235"/>
+      <c r="L31" s="235"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C32" s="12">
         <f>C5</f>
@@ -17958,23 +17980,23 @@
         <f>Statement!Q98</f>
         <v>0.71068084357547079</v>
       </c>
-      <c r="H33" s="220">
+      <c r="H33" s="218">
         <f>H8/H6</f>
         <v>0.74</v>
       </c>
-      <c r="I33" s="220">
+      <c r="I33" s="218">
         <f t="shared" ref="I33:L33" si="9">I8/I6</f>
         <v>0.74</v>
       </c>
-      <c r="J33" s="220">
+      <c r="J33" s="218">
         <f t="shared" si="9"/>
         <v>0.73999999999999988</v>
       </c>
-      <c r="K33" s="220">
+      <c r="K33" s="218">
         <f t="shared" si="9"/>
         <v>0.74</v>
       </c>
-      <c r="L33" s="220">
+      <c r="L33" s="218">
         <f t="shared" si="9"/>
         <v>0.7400000000000001</v>
       </c>
@@ -18003,23 +18025,23 @@
         <f>Statement!Q99</f>
         <v>0.60381683631412719</v>
       </c>
-      <c r="H34" s="220">
+      <c r="H34" s="218">
         <f>H10/H6</f>
         <v>0.61699999999999999</v>
       </c>
-      <c r="I34" s="220">
+      <c r="I34" s="218">
         <f t="shared" ref="I34:L34" si="10">I10/I6</f>
         <v>0.61699999999999999</v>
       </c>
-      <c r="J34" s="220">
+      <c r="J34" s="218">
         <f t="shared" si="10"/>
         <v>0.61699999999999988</v>
       </c>
-      <c r="K34" s="220">
+      <c r="K34" s="218">
         <f t="shared" si="10"/>
         <v>0.61699999999999999</v>
       </c>
-      <c r="L34" s="220">
+      <c r="L34" s="218">
         <f t="shared" si="10"/>
         <v>0.61699999999999999</v>
       </c>
@@ -18067,7 +18089,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9236FE7C-2B1B-7C49-B055-001352253955}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="83" customWidth="1"/>
@@ -18107,7 +18129,7 @@
       <c r="B5" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C5" s="138">
+      <c r="C5" s="137">
         <f>Statement!AC76</f>
         <v>24305</v>
       </c>
@@ -18234,14 +18256,6 @@
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
         <v>0.1442328893416453</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="C21" s="137">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -18292,54 +18306,54 @@
       <c r="D3" s="231"/>
       <c r="E3" s="231"/>
       <c r="F3" s="231"/>
-      <c r="G3" s="243"/>
-      <c r="H3" s="244" t="s">
+      <c r="G3" s="232"/>
+      <c r="H3" s="233" t="s">
         <v>106</v>
       </c>
       <c r="I3" s="231"/>
       <c r="J3" s="231"/>
       <c r="K3" s="231"/>
       <c r="L3" s="231"/>
-      <c r="P3" s="245"/>
-      <c r="Q3" s="245"/>
-      <c r="R3" s="245"/>
-      <c r="S3" s="245"/>
-      <c r="T3" s="245"/>
-      <c r="U3" s="245"/>
-      <c r="V3" s="245"/>
-      <c r="W3" s="245"/>
-      <c r="X3" s="245"/>
-      <c r="Y3" s="245"/>
-      <c r="Z3" s="245"/>
+      <c r="P3" s="234"/>
+      <c r="Q3" s="234"/>
+      <c r="R3" s="234"/>
+      <c r="S3" s="234"/>
+      <c r="T3" s="234"/>
+      <c r="U3" s="234"/>
+      <c r="V3" s="234"/>
+      <c r="W3" s="234"/>
+      <c r="X3" s="234"/>
+      <c r="Y3" s="234"/>
+      <c r="Z3" s="234"/>
       <c r="AB3" s="110"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="240" t="s">
+      <c r="C5" s="235" t="s">
         <v>173</v>
       </c>
-      <c r="D5" s="240"/>
-      <c r="E5" s="240"/>
-      <c r="F5" s="240"/>
-      <c r="G5" s="240"/>
-      <c r="H5" s="240"/>
-      <c r="I5" s="240"/>
-      <c r="J5" s="240"/>
-      <c r="K5" s="240"/>
-      <c r="L5" s="240"/>
-      <c r="P5" s="245"/>
-      <c r="Q5" s="245"/>
-      <c r="R5" s="245"/>
-      <c r="S5" s="245"/>
-      <c r="T5" s="245"/>
-      <c r="U5" s="245"/>
-      <c r="V5" s="245"/>
-      <c r="W5" s="245"/>
-      <c r="X5" s="245"/>
-      <c r="Y5" s="245"/>
-      <c r="Z5" s="245"/>
+      <c r="D5" s="235"/>
+      <c r="E5" s="235"/>
+      <c r="F5" s="235"/>
+      <c r="G5" s="235"/>
+      <c r="H5" s="235"/>
+      <c r="I5" s="235"/>
+      <c r="J5" s="235"/>
+      <c r="K5" s="235"/>
+      <c r="L5" s="235"/>
+      <c r="P5" s="234"/>
+      <c r="Q5" s="234"/>
+      <c r="R5" s="234"/>
+      <c r="S5" s="234"/>
+      <c r="T5" s="234"/>
+      <c r="U5" s="234"/>
+      <c r="V5" s="234"/>
+      <c r="W5" s="234"/>
+      <c r="X5" s="234"/>
+      <c r="Y5" s="234"/>
+      <c r="Z5" s="234"/>
       <c r="AB5" s="111"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -18402,7 +18416,7 @@
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B7" s="39" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C7" s="113">
         <f>'FCF &amp; Other'!C28</f>
@@ -18513,37 +18527,37 @@
       <c r="B9" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C9" s="139"/>
-      <c r="D9" s="139"/>
-      <c r="E9" s="139"/>
-      <c r="F9" s="139"/>
-      <c r="G9" s="140"/>
-      <c r="H9" s="141">
+      <c r="C9" s="138"/>
+      <c r="D9" s="138"/>
+      <c r="E9" s="138"/>
+      <c r="F9" s="138"/>
+      <c r="G9" s="139"/>
+      <c r="H9" s="140">
         <v>1</v>
       </c>
-      <c r="I9" s="141">
+      <c r="I9" s="140">
         <v>2</v>
       </c>
-      <c r="J9" s="141">
+      <c r="J9" s="140">
         <v>3</v>
       </c>
-      <c r="K9" s="141">
+      <c r="K9" s="140">
         <v>4</v>
       </c>
-      <c r="L9" s="141">
+      <c r="L9" s="140">
         <v>5</v>
       </c>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="C10" s="139"/>
-      <c r="D10" s="139"/>
-      <c r="E10" s="139"/>
-      <c r="F10" s="139"/>
-      <c r="G10" s="140"/>
+        <v>318</v>
+      </c>
+      <c r="C10" s="138"/>
+      <c r="D10" s="138"/>
+      <c r="E10" s="138"/>
+      <c r="F10" s="138"/>
+      <c r="G10" s="139"/>
       <c r="H10" s="127">
         <f ca="1">H7/(1+$C$15)^H9</f>
         <v>111460.82065044239</v>
@@ -18570,15 +18584,15 @@
       <c r="B11" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C11" s="139"/>
-      <c r="D11" s="139"/>
-      <c r="E11" s="139"/>
-      <c r="F11" s="139"/>
-      <c r="G11" s="140"/>
-      <c r="H11" s="139"/>
-      <c r="I11" s="139"/>
-      <c r="J11" s="139"/>
-      <c r="K11" s="139"/>
+      <c r="C11" s="138"/>
+      <c r="D11" s="138"/>
+      <c r="E11" s="138"/>
+      <c r="F11" s="138"/>
+      <c r="G11" s="139"/>
+      <c r="H11" s="138"/>
+      <c r="I11" s="138"/>
+      <c r="J11" s="138"/>
+      <c r="K11" s="138"/>
       <c r="L11" s="127">
         <f ca="1">L8/(1+C15)^L9</f>
         <v>2176781.1700300942</v>
@@ -18594,7 +18608,7 @@
       <c r="B14" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="C14" s="142">
+      <c r="C14" s="141">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
@@ -18603,7 +18617,7 @@
         <v>158</v>
       </c>
       <c r="C15" s="136">
-        <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
         <v>0.1442328893416453</v>
       </c>
     </row>
@@ -18644,7 +18658,7 @@
       <c r="B22" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C22" s="24">
+      <c r="C22" s="137">
         <f>Statement!AC111</f>
         <v>80572</v>
       </c>
@@ -18653,7 +18667,7 @@
       <c r="B23" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C23" s="24">
+      <c r="C23" s="137">
         <f>Statement!AC112</f>
         <v>8470</v>
       </c>
@@ -18671,16 +18685,16 @@
       <c r="B25" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C25" s="64">
+      <c r="C25" s="137">
         <f>Statement!AC76</f>
         <v>24305</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B26" s="143" t="s">
+      <c r="B26" s="142" t="s">
         <v>185</v>
       </c>
-      <c r="C26" s="144">
+      <c r="C26" s="143">
         <f ca="1">C24/C25</f>
         <v>129.85601384240837</v>
       </c>
@@ -18731,8 +18745,8 @@
       <c r="D2" s="231"/>
       <c r="E2" s="231"/>
       <c r="F2" s="231"/>
-      <c r="G2" s="243"/>
-      <c r="H2" s="244" t="s">
+      <c r="G2" s="232"/>
+      <c r="H2" s="233" t="s">
         <v>106</v>
       </c>
       <c r="I2" s="231"/>
@@ -18744,18 +18758,18 @@
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="240" t="s">
+      <c r="C4" s="235" t="s">
         <v>187</v>
       </c>
-      <c r="D4" s="240"/>
-      <c r="E4" s="240"/>
-      <c r="F4" s="240"/>
-      <c r="G4" s="240"/>
-      <c r="H4" s="240"/>
-      <c r="I4" s="240"/>
-      <c r="J4" s="240"/>
-      <c r="K4" s="240"/>
-      <c r="L4" s="240"/>
+      <c r="D4" s="235"/>
+      <c r="E4" s="235"/>
+      <c r="F4" s="235"/>
+      <c r="G4" s="235"/>
+      <c r="H4" s="235"/>
+      <c r="I4" s="235"/>
+      <c r="J4" s="235"/>
+      <c r="K4" s="235"/>
+      <c r="L4" s="235"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -18896,7 +18910,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B8" s="16" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C8" s="92">
         <f>'FCF &amp; Other'!C28</f>
@@ -18944,18 +18958,18 @@
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="240" t="s">
+      <c r="C10" s="235" t="s">
         <v>114</v>
       </c>
-      <c r="D10" s="240"/>
-      <c r="E10" s="240"/>
-      <c r="F10" s="240"/>
-      <c r="G10" s="240"/>
-      <c r="H10" s="240"/>
-      <c r="I10" s="240"/>
-      <c r="J10" s="240"/>
-      <c r="K10" s="240"/>
-      <c r="L10" s="240"/>
+      <c r="D10" s="235"/>
+      <c r="E10" s="235"/>
+      <c r="F10" s="235"/>
+      <c r="G10" s="235"/>
+      <c r="H10" s="235"/>
+      <c r="I10" s="235"/>
+      <c r="J10" s="235"/>
+      <c r="K10" s="235"/>
+      <c r="L10" s="235"/>
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -19008,7 +19022,7 @@
       <c r="B12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="139"/>
+      <c r="C12" s="138"/>
       <c r="D12" s="95">
         <f>(D6-C6)/C6</f>
         <v>2.2293230289068887E-3</v>
@@ -19051,7 +19065,7 @@
       <c r="B13" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C13" s="139"/>
+      <c r="C13" s="138"/>
       <c r="D13" s="95">
         <f>IF(C7=0,
 IF(D7=0,0,IF(D7&gt;0,1,-1)),
@@ -19098,9 +19112,9 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C14" s="139"/>
+        <v>260</v>
+      </c>
+      <c r="C14" s="138"/>
       <c r="D14" s="95">
         <f>IF(C8=0,
 IF(D8=0,0,IF(D8&gt;0,1,-1)),
@@ -19149,18 +19163,18 @@
       <c r="N15" s="91"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="240" t="s">
+      <c r="C16" s="235" t="s">
         <v>189</v>
       </c>
-      <c r="D16" s="240"/>
-      <c r="E16" s="240"/>
-      <c r="F16" s="240"/>
-      <c r="G16" s="240"/>
-      <c r="H16" s="240"/>
-      <c r="I16" s="240"/>
-      <c r="J16" s="240"/>
-      <c r="K16" s="240"/>
-      <c r="L16" s="240"/>
+      <c r="D16" s="235"/>
+      <c r="E16" s="235"/>
+      <c r="F16" s="235"/>
+      <c r="G16" s="235"/>
+      <c r="H16" s="235"/>
+      <c r="I16" s="235"/>
+      <c r="J16" s="235"/>
+      <c r="K16" s="235"/>
+      <c r="L16" s="235"/>
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -19230,23 +19244,23 @@
         <f>Statement!Q21</f>
         <v>24514</v>
       </c>
-      <c r="H18" s="145">
+      <c r="H18" s="144">
         <f>G18*(1+H19)</f>
         <v>24146.29</v>
       </c>
-      <c r="I18" s="145">
+      <c r="I18" s="144">
         <f t="shared" ref="I18:L18" si="5">H18*(1+I19)</f>
         <v>23904.827100000002</v>
       </c>
-      <c r="J18" s="145">
+      <c r="J18" s="144">
         <f t="shared" si="5"/>
         <v>23665.778829000003</v>
       </c>
-      <c r="K18" s="145">
+      <c r="K18" s="144">
         <f t="shared" si="5"/>
         <v>23547.449934855002</v>
       </c>
-      <c r="L18" s="145">
+      <c r="L18" s="144">
         <f t="shared" si="5"/>
         <v>23429.712685180726</v>
       </c>
@@ -19256,24 +19270,24 @@
       <c r="B19" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C19" s="139"/>
-      <c r="D19" s="146">
+      <c r="C19" s="138"/>
+      <c r="D19" s="145">
         <f>D18/C18-1</f>
         <v>-1.104536489151875E-2</v>
       </c>
-      <c r="E19" s="146">
+      <c r="E19" s="145">
         <f t="shared" ref="E19:G19" si="6">E18/D18-1</f>
         <v>-5.1854806541683507E-3</v>
       </c>
-      <c r="F19" s="146">
+      <c r="F19" s="145">
         <f t="shared" si="6"/>
         <v>-5.4530874097834525E-3</v>
       </c>
-      <c r="G19" s="147">
+      <c r="G19" s="146">
         <f t="shared" si="6"/>
         <v>-1.169166263505883E-2</v>
       </c>
-      <c r="H19" s="148">
+      <c r="H19" s="147">
         <v>-1.4999999999999999E-2</v>
       </c>
       <c r="I19" s="97">
@@ -19294,18 +19308,18 @@
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="240" t="s">
+      <c r="C21" s="235" t="s">
         <v>192</v>
       </c>
-      <c r="D21" s="240"/>
-      <c r="E21" s="240"/>
-      <c r="F21" s="240"/>
-      <c r="G21" s="240"/>
-      <c r="H21" s="240"/>
-      <c r="I21" s="240"/>
-      <c r="J21" s="240"/>
-      <c r="K21" s="240"/>
-      <c r="L21" s="240"/>
+      <c r="D21" s="235"/>
+      <c r="E21" s="235"/>
+      <c r="F21" s="235"/>
+      <c r="G21" s="235"/>
+      <c r="H21" s="235"/>
+      <c r="I21" s="235"/>
+      <c r="J21" s="235"/>
+      <c r="K21" s="235"/>
+      <c r="L21" s="235"/>
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -19355,31 +19369,31 @@
       <c r="B23" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C23" s="149">
+      <c r="C23" s="148">
         <f>Statement!M120</f>
         <v>228.4</v>
       </c>
-      <c r="D23" s="149">
+      <c r="D23" s="148">
         <f>Statement!N120</f>
         <v>203.6</v>
       </c>
-      <c r="E23" s="149">
+      <c r="E23" s="148">
         <f>Statement!O120</f>
         <v>610.29999999999995</v>
       </c>
-      <c r="F23" s="149">
+      <c r="F23" s="148">
         <f>Statement!P120</f>
         <v>142.62</v>
       </c>
-      <c r="G23" s="150">
+      <c r="G23" s="149">
         <f>Statement!Q120</f>
         <v>187.67</v>
       </c>
-      <c r="H23" s="139"/>
-      <c r="I23" s="139"/>
-      <c r="J23" s="139"/>
-      <c r="K23" s="139"/>
-      <c r="L23" s="139"/>
+      <c r="H23" s="138"/>
+      <c r="I23" s="138"/>
+      <c r="J23" s="138"/>
+      <c r="K23" s="138"/>
+      <c r="L23" s="138"/>
       <c r="N23" s="91"/>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.2">
@@ -19389,18 +19403,18 @@
       <c r="N25" s="91"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="240" t="s">
+      <c r="C26" s="235" t="s">
         <v>193</v>
       </c>
-      <c r="D26" s="240"/>
-      <c r="E26" s="240"/>
-      <c r="F26" s="240"/>
-      <c r="G26" s="240"/>
-      <c r="H26" s="240"/>
-      <c r="I26" s="240"/>
-      <c r="J26" s="240"/>
-      <c r="K26" s="240"/>
-      <c r="L26" s="240"/>
+      <c r="D26" s="235"/>
+      <c r="E26" s="235"/>
+      <c r="F26" s="235"/>
+      <c r="G26" s="235"/>
+      <c r="H26" s="235"/>
+      <c r="I26" s="235"/>
+      <c r="J26" s="235"/>
+      <c r="K26" s="235"/>
+      <c r="L26" s="235"/>
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -19450,62 +19464,62 @@
       <c r="B28" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="C28" s="151">
+      <c r="C28" s="150">
         <f>C23/(C6/C18)</f>
         <v>215.12744296648586</v>
       </c>
-      <c r="D28" s="151">
+      <c r="D28" s="150">
         <f t="shared" ref="D28:G28" si="9">D23/(D6/D18)</f>
         <v>189.2285904945503</v>
       </c>
-      <c r="E28" s="151">
+      <c r="E28" s="150">
         <f t="shared" si="9"/>
         <v>249.84212599717671</v>
       </c>
-      <c r="F28" s="151">
+      <c r="F28" s="150">
         <f t="shared" si="9"/>
         <v>27.108259040437712</v>
       </c>
-      <c r="G28" s="152">
+      <c r="G28" s="151">
         <f t="shared" si="9"/>
         <v>21.304922616677011</v>
       </c>
-      <c r="H28" s="139"/>
-      <c r="I28" s="139"/>
-      <c r="J28" s="139"/>
-      <c r="K28" s="139"/>
-      <c r="L28" s="139"/>
+      <c r="H28" s="138"/>
+      <c r="I28" s="138"/>
+      <c r="J28" s="138"/>
+      <c r="K28" s="138"/>
+      <c r="L28" s="138"/>
       <c r="N28" s="91"/>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B29" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="C29" s="145">
+      <c r="C29" s="144">
         <f>C23*C18</f>
         <v>5789940</v>
       </c>
-      <c r="D29" s="145">
+      <c r="D29" s="144">
         <f t="shared" ref="D29:G29" si="10">D23*D18</f>
         <v>5104252</v>
       </c>
-      <c r="E29" s="145">
+      <c r="E29" s="144">
         <f t="shared" si="10"/>
         <v>15220881.999999998</v>
       </c>
-      <c r="F29" s="145">
+      <c r="F29" s="144">
         <f t="shared" si="10"/>
         <v>3537546.48</v>
       </c>
-      <c r="G29" s="153">
+      <c r="G29" s="152">
         <f t="shared" si="10"/>
         <v>4600542.38</v>
       </c>
-      <c r="H29" s="139"/>
-      <c r="I29" s="139"/>
-      <c r="J29" s="139"/>
-      <c r="K29" s="139"/>
-      <c r="L29" s="139"/>
+      <c r="H29" s="138"/>
+      <c r="I29" s="138"/>
+      <c r="J29" s="138"/>
+      <c r="K29" s="138"/>
+      <c r="L29" s="138"/>
       <c r="N29" s="91"/>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.2">
@@ -19516,151 +19530,151 @@
         <f>Statement!M112</f>
         <v>10946</v>
       </c>
-      <c r="D30" s="154">
+      <c r="D30" s="153">
         <f>Statement!N112</f>
         <v>10953</v>
       </c>
-      <c r="E30" s="154">
+      <c r="E30" s="153">
         <f>Statement!O112</f>
         <v>9709</v>
       </c>
-      <c r="F30" s="154">
+      <c r="F30" s="153">
         <f>Statement!P112</f>
         <v>8463</v>
       </c>
-      <c r="G30" s="155">
+      <c r="G30" s="154">
         <f>Statement!Q112</f>
         <v>8468</v>
       </c>
-      <c r="H30" s="139"/>
-      <c r="I30" s="139"/>
-      <c r="J30" s="139"/>
-      <c r="K30" s="139"/>
-      <c r="L30" s="139"/>
+      <c r="H30" s="138"/>
+      <c r="I30" s="138"/>
+      <c r="J30" s="138"/>
+      <c r="K30" s="138"/>
+      <c r="L30" s="138"/>
       <c r="N30" s="91"/>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B31" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C31" s="154">
+      <c r="C31" s="153">
         <f>Statement!M111</f>
         <v>21208</v>
       </c>
-      <c r="D31" s="154">
+      <c r="D31" s="153">
         <f>Statement!N111</f>
         <v>13296</v>
       </c>
-      <c r="E31" s="154">
+      <c r="E31" s="153">
         <f>Statement!O111</f>
         <v>25984</v>
       </c>
-      <c r="F31" s="154">
+      <c r="F31" s="153">
         <f>Statement!P111</f>
         <v>43210</v>
       </c>
-      <c r="G31" s="155">
+      <c r="G31" s="154">
         <f>Statement!Q111</f>
         <v>62556</v>
       </c>
-      <c r="H31" s="139"/>
-      <c r="I31" s="139"/>
-      <c r="J31" s="139"/>
-      <c r="K31" s="139"/>
-      <c r="L31" s="139"/>
+      <c r="H31" s="138"/>
+      <c r="I31" s="138"/>
+      <c r="J31" s="138"/>
+      <c r="K31" s="138"/>
+      <c r="L31" s="138"/>
       <c r="N31" s="91"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C32" s="145">
+      <c r="C32" s="144">
         <f>C29+C30-C31</f>
         <v>5779678</v>
       </c>
-      <c r="D32" s="145">
+      <c r="D32" s="144">
         <f t="shared" ref="D32:G32" si="11">D29+D30-D31</f>
         <v>5101909</v>
       </c>
-      <c r="E32" s="145">
+      <c r="E32" s="144">
         <f t="shared" si="11"/>
         <v>15204606.999999998</v>
       </c>
-      <c r="F32" s="145">
+      <c r="F32" s="144">
         <f t="shared" si="11"/>
         <v>3502799.48</v>
       </c>
-      <c r="G32" s="153">
+      <c r="G32" s="152">
         <f t="shared" si="11"/>
         <v>4546454.38</v>
       </c>
-      <c r="H32" s="139"/>
-      <c r="I32" s="139"/>
-      <c r="J32" s="139"/>
-      <c r="K32" s="139"/>
-      <c r="L32" s="139"/>
+      <c r="H32" s="138"/>
+      <c r="I32" s="138"/>
+      <c r="J32" s="138"/>
+      <c r="K32" s="138"/>
+      <c r="L32" s="138"/>
       <c r="N32" s="91"/>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B33" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="C33" s="151">
+      <c r="C33" s="150">
         <f>C32/C7</f>
         <v>575.60780798725227</v>
       </c>
-      <c r="D33" s="151">
+      <c r="D33" s="150">
         <f t="shared" ref="D33:G33" si="12">D32/D7</f>
         <v>1207.8383049242425</v>
       </c>
-      <c r="E33" s="151">
+      <c r="E33" s="150">
         <f t="shared" si="12"/>
         <v>461.1369343685551</v>
       </c>
-      <c r="F33" s="151">
+      <c r="F33" s="150">
         <f t="shared" si="12"/>
         <v>43.003934538936562</v>
       </c>
-      <c r="G33" s="152">
+      <c r="G33" s="151">
         <f t="shared" si="12"/>
         <v>34.868923895787155</v>
       </c>
-      <c r="H33" s="139"/>
-      <c r="I33" s="139"/>
-      <c r="J33" s="139"/>
-      <c r="K33" s="139"/>
-      <c r="L33" s="139"/>
+      <c r="H33" s="138"/>
+      <c r="I33" s="138"/>
+      <c r="J33" s="138"/>
+      <c r="K33" s="138"/>
+      <c r="L33" s="138"/>
       <c r="N33" s="91"/>
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
-        <v>321</v>
-      </c>
-      <c r="C34" s="151">
+        <v>319</v>
+      </c>
+      <c r="C34" s="150">
         <f>C32/C8</f>
         <v>864.5613457282559</v>
       </c>
-      <c r="D34" s="151">
+      <c r="D34" s="150">
         <f t="shared" ref="D34:G34" si="13">D32/D8</f>
         <v>2952.4936342592591</v>
       </c>
-      <c r="E34" s="151">
+      <c r="E34" s="150">
         <f t="shared" si="13"/>
         <v>590.8713707411099</v>
       </c>
-      <c r="F34" s="151">
+      <c r="F34" s="150">
         <f t="shared" si="13"/>
         <v>58.483988582757021</v>
       </c>
-      <c r="G34" s="152">
+      <c r="G34" s="151">
         <f t="shared" si="13"/>
         <v>49.687269035572541</v>
       </c>
-      <c r="H34" s="139"/>
-      <c r="I34" s="139"/>
-      <c r="J34" s="139"/>
-      <c r="K34" s="139"/>
-      <c r="L34" s="139"/>
+      <c r="H34" s="138"/>
+      <c r="I34" s="138"/>
+      <c r="J34" s="138"/>
+      <c r="K34" s="138"/>
+      <c r="L34" s="138"/>
       <c r="N34" s="91"/>
     </row>
     <row r="35" spans="2:14" x14ac:dyDescent="0.2">
@@ -19690,7 +19704,7 @@
         <v>158</v>
       </c>
       <c r="C39" s="136">
-        <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
         <v>0.1442328893416453</v>
       </c>
     </row>
@@ -19704,38 +19718,38 @@
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B41" s="1" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C41" s="24">
-        <f>L18</f>
-        <v>23429.712685180726</v>
+        <f>(C38*C40)</f>
+        <v>15509508.406160863</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B42" s="1" t="s">
-        <v>196</v>
+        <v>387</v>
       </c>
       <c r="C42" s="24">
-        <f>(C38*C40)-G30+G31</f>
-        <v>15563596.406160863</v>
+        <f ca="1">C41/(1+C39)^5-G30+G31</f>
+        <v>7961345.8049963033</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C43" s="24">
-        <f>C42/C41</f>
-        <v>664.26748869203266</v>
+        <v>67</v>
+      </c>
+      <c r="C43" s="88">
+        <f>Statement!AC76</f>
+        <v>24305</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B44" s="143" t="s">
+      <c r="B44" s="142" t="s">
         <v>202</v>
       </c>
-      <c r="C44" s="144">
-        <f ca="1">C43/(1+C48)^5</f>
-        <v>338.66542684737175</v>
+      <c r="C44" s="143">
+        <f ca="1">C42/C43</f>
+        <v>327.56000020556689</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -19755,11 +19769,11 @@
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
-        <v>158</v>
+        <v>389</v>
       </c>
       <c r="C48" s="136">
-        <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
-        <v>0.1442328893416453</v>
+        <f>Overview!C29</f>
+        <v>0.12</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -19789,17 +19803,17 @@
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="143" t="s">
+      <c r="B52" s="142" t="s">
         <v>202</v>
       </c>
-      <c r="C52" s="144">
-        <f ca="1">C51/(1+C48)^5</f>
-        <v>273.49146395013889</v>
+      <c r="C52" s="143">
+        <f>C51/(1+C48)^5</f>
+        <v>304.38678708173404</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B54" s="231" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C54" s="231"/>
     </row>
@@ -19817,13 +19831,13 @@
         <v>158</v>
       </c>
       <c r="C56" s="136">
-        <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
         <v>0.1442328893416453</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B57" s="39" t="s">
-        <v>207</v>
+        <v>388</v>
       </c>
       <c r="C57" s="105">
         <v>30</v>
@@ -19831,38 +19845,38 @@
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C58" s="24">
-        <f>L18</f>
-        <v>23429.712685180726</v>
+        <f>(C55*C57)</f>
+        <v>14899797.411294669</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B59" s="1" t="s">
-        <v>196</v>
+        <v>387</v>
       </c>
       <c r="C59" s="24">
-        <f>(C55*C57)-G30+G31</f>
-        <v>14953885.411294669</v>
+        <f ca="1">C58/(1+C56)^5-G30+G31</f>
+        <v>7650495.0741612324</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B60" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C60" s="24">
-        <f>C59/C58</f>
-        <v>638.24450654714985</v>
+        <v>67</v>
+      </c>
+      <c r="C60" s="88">
+        <f>Statement!AC76</f>
+        <v>24305</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B61" s="143" t="s">
+      <c r="B61" s="142" t="s">
         <v>202</v>
       </c>
-      <c r="C61" s="144">
-        <f ca="1">C60/(1+C56)^5</f>
-        <v>325.39805413086026</v>
+      <c r="C61" s="143">
+        <f ca="1">C59/C60</f>
+        <v>314.77042066082009</v>
       </c>
     </row>
   </sheetData>
@@ -19904,7 +19918,7 @@
     <row r="1" spans="1:14" s="83" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4"/>
       <c r="B1" s="82" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
@@ -19915,14 +19929,14 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B4" s="231" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C4" s="231"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C5" s="134">
         <f ca="1">DCF!C26</f>
@@ -19931,43 +19945,43 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C6" s="134">
         <f ca="1">Multiples!C44</f>
-        <v>338.66542684737175</v>
+        <v>327.56000020556689</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C7" s="134">
-        <f ca="1">Multiples!C52</f>
-        <v>273.49146395013889</v>
+        <f>Multiples!C52</f>
+        <v>304.38678708173404</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C8" s="134">
         <f ca="1">Multiples!C61</f>
-        <v>325.39805413086026</v>
+        <v>314.77042066082009</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B9" s="143" t="s">
-        <v>213</v>
-      </c>
-      <c r="C9" s="144">
+      <c r="B9" s="142" t="s">
+        <v>212</v>
+      </c>
+      <c r="C9" s="143">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>266.85273969269485</v>
+        <v>269.14330544763237</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C5</f>
@@ -19976,11 +19990,11 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C11" s="156">
+        <v>214</v>
+      </c>
+      <c r="C11" s="155">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.30108600532761998</v>
+        <v>0.31225404898894382</v>
       </c>
     </row>
   </sheetData>
@@ -20036,7 +20050,7 @@
     <row r="1" spans="1:28" s="83" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4"/>
       <c r="B1" s="82" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:28" s="83" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -20051,54 +20065,54 @@
       <c r="D3" s="231"/>
       <c r="E3" s="231"/>
       <c r="F3" s="231"/>
-      <c r="G3" s="243"/>
-      <c r="H3" s="244" t="s">
+      <c r="G3" s="232"/>
+      <c r="H3" s="233" t="s">
         <v>106</v>
       </c>
       <c r="I3" s="231"/>
       <c r="J3" s="231"/>
       <c r="K3" s="231"/>
       <c r="L3" s="231"/>
-      <c r="P3" s="245"/>
-      <c r="Q3" s="245"/>
-      <c r="R3" s="245"/>
-      <c r="S3" s="245"/>
-      <c r="T3" s="245"/>
-      <c r="U3" s="245"/>
-      <c r="V3" s="245"/>
-      <c r="W3" s="245"/>
-      <c r="X3" s="245"/>
-      <c r="Y3" s="245"/>
-      <c r="Z3" s="245"/>
+      <c r="P3" s="234"/>
+      <c r="Q3" s="234"/>
+      <c r="R3" s="234"/>
+      <c r="S3" s="234"/>
+      <c r="T3" s="234"/>
+      <c r="U3" s="234"/>
+      <c r="V3" s="234"/>
+      <c r="W3" s="234"/>
+      <c r="X3" s="234"/>
+      <c r="Y3" s="234"/>
+      <c r="Z3" s="234"/>
       <c r="AB3" s="110"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="240" t="s">
+      <c r="C5" s="235" t="s">
         <v>173</v>
       </c>
-      <c r="D5" s="240"/>
-      <c r="E5" s="240"/>
-      <c r="F5" s="240"/>
-      <c r="G5" s="240"/>
-      <c r="H5" s="240"/>
-      <c r="I5" s="240"/>
-      <c r="J5" s="240"/>
-      <c r="K5" s="240"/>
-      <c r="L5" s="240"/>
-      <c r="P5" s="245"/>
-      <c r="Q5" s="245"/>
-      <c r="R5" s="245"/>
-      <c r="S5" s="245"/>
-      <c r="T5" s="245"/>
-      <c r="U5" s="245"/>
-      <c r="V5" s="245"/>
-      <c r="W5" s="245"/>
-      <c r="X5" s="245"/>
-      <c r="Y5" s="245"/>
-      <c r="Z5" s="245"/>
+      <c r="D5" s="235"/>
+      <c r="E5" s="235"/>
+      <c r="F5" s="235"/>
+      <c r="G5" s="235"/>
+      <c r="H5" s="235"/>
+      <c r="I5" s="235"/>
+      <c r="J5" s="235"/>
+      <c r="K5" s="235"/>
+      <c r="L5" s="235"/>
+      <c r="P5" s="234"/>
+      <c r="Q5" s="234"/>
+      <c r="R5" s="234"/>
+      <c r="S5" s="234"/>
+      <c r="T5" s="234"/>
+      <c r="U5" s="234"/>
+      <c r="V5" s="234"/>
+      <c r="W5" s="234"/>
+      <c r="X5" s="234"/>
+      <c r="Y5" s="234"/>
+      <c r="Z5" s="234"/>
       <c r="AB5" s="111"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -20161,7 +20175,7 @@
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B7" s="39" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C7" s="113">
         <f>'FCF &amp; Other'!C28</f>
@@ -20222,15 +20236,15 @@
       <c r="B8" s="39" t="s">
         <v>174</v>
       </c>
-      <c r="C8" s="139"/>
-      <c r="D8" s="139"/>
-      <c r="E8" s="139"/>
-      <c r="F8" s="139"/>
-      <c r="G8" s="140"/>
-      <c r="H8" s="139"/>
-      <c r="I8" s="139"/>
-      <c r="J8" s="139"/>
-      <c r="K8" s="139"/>
+      <c r="C8" s="138"/>
+      <c r="D8" s="138"/>
+      <c r="E8" s="138"/>
+      <c r="F8" s="138"/>
+      <c r="G8" s="139"/>
+      <c r="H8" s="138"/>
+      <c r="I8" s="138"/>
+      <c r="J8" s="138"/>
+      <c r="K8" s="138"/>
       <c r="L8" s="127">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
         <v>7267390.5416517593</v>
@@ -20254,37 +20268,37 @@
       <c r="B9" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C9" s="139"/>
-      <c r="D9" s="139"/>
-      <c r="E9" s="139"/>
-      <c r="F9" s="139"/>
-      <c r="G9" s="140"/>
-      <c r="H9" s="141">
+      <c r="C9" s="138"/>
+      <c r="D9" s="138"/>
+      <c r="E9" s="138"/>
+      <c r="F9" s="138"/>
+      <c r="G9" s="139"/>
+      <c r="H9" s="140">
         <v>1</v>
       </c>
-      <c r="I9" s="141">
+      <c r="I9" s="140">
         <v>2</v>
       </c>
-      <c r="J9" s="141">
+      <c r="J9" s="140">
         <v>3</v>
       </c>
-      <c r="K9" s="141">
+      <c r="K9" s="140">
         <v>4</v>
       </c>
-      <c r="L9" s="141">
+      <c r="L9" s="140">
         <v>5</v>
       </c>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="C10" s="139"/>
-      <c r="D10" s="139"/>
-      <c r="E10" s="139"/>
-      <c r="F10" s="139"/>
-      <c r="G10" s="140"/>
+        <v>318</v>
+      </c>
+      <c r="C10" s="138"/>
+      <c r="D10" s="138"/>
+      <c r="E10" s="138"/>
+      <c r="F10" s="138"/>
+      <c r="G10" s="139"/>
       <c r="H10" s="127">
         <f ca="1">H7/(1+$C$21)^H9</f>
         <v>124749.23238464452</v>
@@ -20311,15 +20325,15 @@
       <c r="B11" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C11" s="139"/>
-      <c r="D11" s="139"/>
-      <c r="E11" s="139"/>
-      <c r="F11" s="139"/>
-      <c r="G11" s="140"/>
-      <c r="H11" s="139"/>
-      <c r="I11" s="139"/>
-      <c r="J11" s="139"/>
-      <c r="K11" s="139"/>
+      <c r="C11" s="138"/>
+      <c r="D11" s="138"/>
+      <c r="E11" s="138"/>
+      <c r="F11" s="138"/>
+      <c r="G11" s="139"/>
+      <c r="H11" s="138"/>
+      <c r="I11" s="138"/>
+      <c r="J11" s="138"/>
+      <c r="K11" s="138"/>
       <c r="L11" s="127">
         <f ca="1">L8/(1+C21)^L9</f>
         <v>3705154.868713004</v>
@@ -20327,205 +20341,205 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="246" t="s">
+      <c r="B14" s="236" t="s">
+        <v>216</v>
+      </c>
+      <c r="C14" s="237"/>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B15" s="156" t="s">
         <v>217</v>
       </c>
-      <c r="C14" s="247"/>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B15" s="157" t="s">
-        <v>218</v>
-      </c>
-      <c r="C15" s="158">
+      <c r="C15" s="157">
         <f ca="1">Overview!C5</f>
         <v>205.1</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B16" s="157" t="s">
-        <v>219</v>
-      </c>
-      <c r="C16" s="158">
+      <c r="B16" s="156" t="s">
+        <v>218</v>
+      </c>
+      <c r="C16" s="157">
         <f ca="1">C36</f>
         <v>208.72291756096095</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="159" t="s">
-        <v>324</v>
-      </c>
-      <c r="C17" s="160">
+      <c r="B17" s="158" t="s">
+        <v>322</v>
+      </c>
+      <c r="C17" s="159">
         <v>0.56000000000000005</v>
       </c>
-      <c r="E17" s="248" t="s">
-        <v>220</v>
-      </c>
-      <c r="F17" s="248"/>
-      <c r="G17" s="248"/>
-      <c r="H17" s="248"/>
-      <c r="I17" s="248"/>
+      <c r="E17" s="238" t="s">
+        <v>219</v>
+      </c>
+      <c r="F17" s="238"/>
+      <c r="G17" s="238"/>
+      <c r="H17" s="238"/>
+      <c r="I17" s="238"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="246" t="s">
+      <c r="B19" s="236" t="s">
         <v>177</v>
       </c>
-      <c r="C19" s="247"/>
+      <c r="C19" s="237"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B20" s="161" t="s">
+      <c r="B20" s="160" t="s">
         <v>178</v>
       </c>
-      <c r="C20" s="162">
+      <c r="C20" s="161">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B21" s="161" t="s">
+      <c r="B21" s="160" t="s">
         <v>158</v>
       </c>
-      <c r="C21" s="163">
-        <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
+      <c r="C21" s="229">
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
         <v>0.1442328893416453</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B22" s="161" t="s">
+      <c r="B22" s="160" t="s">
         <v>67</v>
       </c>
-      <c r="C22" s="164">
+      <c r="C22" s="230">
         <f>Statement!AC73</f>
         <v>24200</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B23" s="161" t="s">
-        <v>221</v>
-      </c>
-      <c r="C23" s="164">
+      <c r="B23" s="160" t="s">
+        <v>220</v>
+      </c>
+      <c r="C23" s="162">
         <f ca="1">C15*C22</f>
         <v>4963420</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B24" s="161" t="s">
+      <c r="B24" s="160" t="s">
         <v>171</v>
       </c>
-      <c r="C24" s="164">
+      <c r="C24" s="230">
         <f>Statement!AC111</f>
         <v>80572</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="161" t="s">
+      <c r="B25" s="160" t="s">
         <v>162</v>
       </c>
-      <c r="C25" s="164">
+      <c r="C25" s="230">
         <f>Statement!AC112</f>
         <v>8470</v>
       </c>
     </row>
     <row r="26" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="159" t="s">
-        <v>222</v>
-      </c>
-      <c r="C26" s="165">
+      <c r="B26" s="158" t="s">
+        <v>221</v>
+      </c>
+      <c r="C26" s="163">
         <f ca="1">C23+C25-C24</f>
         <v>4891318</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="246" t="s">
+      <c r="B28" s="236" t="s">
         <v>179</v>
       </c>
-      <c r="C28" s="247"/>
+      <c r="C28" s="237"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B29" s="161" t="s">
+      <c r="B29" s="160" t="s">
         <v>180</v>
       </c>
-      <c r="C29" s="164">
+      <c r="C29" s="162">
         <f ca="1">SUM(H10:L10)</f>
         <v>1273837.7362622512</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B30" s="161" t="s">
+      <c r="B30" s="160" t="s">
         <v>176</v>
       </c>
-      <c r="C30" s="164">
+      <c r="C30" s="162">
         <f ca="1">L11</f>
         <v>3705154.868713004</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B31" s="166" t="s">
+      <c r="B31" s="164" t="s">
         <v>181</v>
       </c>
-      <c r="C31" s="167">
+      <c r="C31" s="165">
         <f ca="1">C29+C30</f>
         <v>4978992.6049752552</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B32" s="161" t="s">
+      <c r="B32" s="160" t="s">
         <v>182</v>
       </c>
-      <c r="C32" s="168">
+      <c r="C32" s="166">
         <f>C24</f>
         <v>80572</v>
       </c>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B33" s="161" t="s">
+      <c r="B33" s="160" t="s">
         <v>183</v>
       </c>
-      <c r="C33" s="168">
+      <c r="C33" s="166">
         <f>C25</f>
         <v>8470</v>
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B34" s="166" t="s">
+      <c r="B34" s="164" t="s">
         <v>184</v>
       </c>
-      <c r="C34" s="167">
+      <c r="C34" s="165">
         <f ca="1">C31+C32-C33</f>
         <v>5051094.6049752552</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B35" s="161" t="s">
+      <c r="B35" s="160" t="s">
         <v>67</v>
       </c>
-      <c r="C35" s="164">
+      <c r="C35" s="162">
         <f>C22</f>
         <v>24200</v>
       </c>
     </row>
     <row r="36" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="169" t="s">
+      <c r="B36" s="167" t="s">
         <v>185</v>
       </c>
-      <c r="C36" s="170">
+      <c r="C36" s="168">
         <f ca="1">C34/C35</f>
         <v>208.72291756096095</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="240" t="s">
-        <v>223</v>
-      </c>
-      <c r="D39" s="240"/>
-      <c r="E39" s="240"/>
-      <c r="F39" s="240"/>
-      <c r="G39" s="240"/>
-      <c r="H39" s="240"/>
-      <c r="I39" s="240"/>
-      <c r="J39" s="240"/>
-      <c r="K39" s="240"/>
-      <c r="L39" s="240"/>
+      <c r="C39" s="235" t="s">
+        <v>222</v>
+      </c>
+      <c r="D39" s="235"/>
+      <c r="E39" s="235"/>
+      <c r="F39" s="235"/>
+      <c r="G39" s="235"/>
+      <c r="H39" s="235"/>
+      <c r="I39" s="235"/>
+      <c r="J39" s="235"/>
+      <c r="K39" s="235"/>
+      <c r="L39" s="235"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -20571,7 +20585,7 @@
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="39" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C41" s="113">
         <f>C7</f>
@@ -20593,23 +20607,23 @@
         <f t="shared" si="2"/>
         <v>91501.393983739836</v>
       </c>
-      <c r="H41" s="145">
+      <c r="H41" s="144">
         <f t="shared" si="2"/>
         <v>142742.17461463416</v>
       </c>
-      <c r="I41" s="145">
+      <c r="I41" s="144">
         <f t="shared" si="2"/>
         <v>222677.7923988293</v>
       </c>
-      <c r="J41" s="145">
+      <c r="J41" s="144">
         <f t="shared" si="2"/>
         <v>347377.35614217375</v>
       </c>
-      <c r="K41" s="145">
+      <c r="K41" s="144">
         <f t="shared" si="2"/>
         <v>541908.67558179109</v>
       </c>
-      <c r="L41" s="145">
+      <c r="L41" s="144">
         <f t="shared" si="2"/>
         <v>845377.53390759416</v>
       </c>
@@ -20638,30 +20652,30 @@
         <f>'FCF &amp; Other'!G10</f>
         <v>130387</v>
       </c>
-      <c r="H42" s="145">
+      <c r="H42" s="144">
         <f>H41/H43</f>
         <v>129765.61328603105</v>
       </c>
-      <c r="I42" s="145">
+      <c r="I42" s="144">
         <f t="shared" ref="I42:L42" si="3">I41/I43</f>
         <v>202434.35672620844</v>
       </c>
-      <c r="J42" s="145">
+      <c r="J42" s="144">
         <f t="shared" si="3"/>
         <v>315797.5964928852</v>
       </c>
-      <c r="K42" s="145">
+      <c r="K42" s="144">
         <f t="shared" si="3"/>
         <v>492644.25052890094</v>
       </c>
-      <c r="L42" s="145">
+      <c r="L42" s="144">
         <f t="shared" si="3"/>
         <v>768525.03082508559</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B43" s="123" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C43" s="95">
         <f>C41/C42</f>
@@ -20683,19 +20697,19 @@
         <f t="shared" si="4"/>
         <v>0.70176776813439867</v>
       </c>
-      <c r="H43" s="171">
+      <c r="H43" s="169">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I43" s="171">
+      <c r="I43" s="169">
         <v>1.1000000000000001</v>
       </c>
-      <c r="J43" s="171">
+      <c r="J43" s="169">
         <v>1.1000000000000001</v>
       </c>
-      <c r="K43" s="171">
+      <c r="K43" s="169">
         <v>1.1000000000000001</v>
       </c>
-      <c r="L43" s="171">
+      <c r="L43" s="169">
         <v>1.1000000000000001</v>
       </c>
     </row>
@@ -20723,30 +20737,30 @@
         <f>Revenue!G10</f>
         <v>215938</v>
       </c>
-      <c r="H44" s="145">
+      <c r="H44" s="144">
         <f>H41/H45</f>
         <v>14274217.461463416</v>
       </c>
-      <c r="I44" s="145">
+      <c r="I44" s="144">
         <f t="shared" ref="I44:L44" si="5">I41/I45</f>
         <v>11133889.619941466</v>
       </c>
-      <c r="J44" s="145">
+      <c r="J44" s="144">
         <f t="shared" si="5"/>
         <v>8270889.4319565175</v>
       </c>
-      <c r="K44" s="145">
+      <c r="K44" s="144">
         <f t="shared" si="5"/>
         <v>7741552.5083113005</v>
       </c>
-      <c r="L44" s="145">
+      <c r="L44" s="144">
         <f t="shared" si="5"/>
         <v>5635850.2260506283</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B45" s="123" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C45" s="95">
         <f>C41/C44</f>
@@ -20768,27 +20782,27 @@
         <f t="shared" si="6"/>
         <v>0.42373919358213857</v>
       </c>
-      <c r="H45" s="171">
+      <c r="H45" s="169">
         <v>0.01</v>
       </c>
-      <c r="I45" s="171">
+      <c r="I45" s="169">
         <v>0.02</v>
       </c>
-      <c r="J45" s="171">
+      <c r="J45" s="169">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="K45" s="171">
+      <c r="K45" s="169">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L45" s="171">
+      <c r="L45" s="169">
         <v>0.15</v>
       </c>
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B46" s="123" t="s">
-        <v>327</v>
-      </c>
-      <c r="C46" s="139"/>
+        <v>325</v>
+      </c>
+      <c r="C46" s="138"/>
       <c r="D46" s="95">
         <f>D41/C41-1</f>
         <v>-0.74151466475841277</v>
@@ -20805,32 +20819,32 @@
         <f t="shared" si="7"/>
         <v>0.5277398867980283</v>
       </c>
-      <c r="H46" s="172">
+      <c r="H46" s="170">
         <f t="shared" si="7"/>
         <v>0.56000000000000028</v>
       </c>
-      <c r="I46" s="172">
+      <c r="I46" s="170">
         <f t="shared" si="7"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="J46" s="172">
+      <c r="J46" s="170">
         <f t="shared" si="7"/>
         <v>0.56000000000000028</v>
       </c>
-      <c r="K46" s="172">
+      <c r="K46" s="170">
         <f t="shared" si="7"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="L46" s="172">
+      <c r="L46" s="170">
         <f t="shared" si="7"/>
         <v>0.56000000000000005</v>
       </c>
     </row>
     <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B47" s="123" t="s">
-        <v>224</v>
-      </c>
-      <c r="C47" s="139"/>
+        <v>223</v>
+      </c>
+      <c r="C47" s="138"/>
       <c r="D47" s="95">
         <f>D42/C42-1</f>
         <v>-0.57932476844935765</v>
@@ -20847,32 +20861,32 @@
         <f t="shared" si="7"/>
         <v>0.60076363055995485</v>
       </c>
-      <c r="H47" s="172">
+      <c r="H47" s="170">
         <f t="shared" si="7"/>
         <v>-4.7657106457619225E-3</v>
       </c>
-      <c r="I47" s="172">
+      <c r="I47" s="170">
         <f t="shared" si="7"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="J47" s="172">
+      <c r="J47" s="170">
         <f t="shared" si="7"/>
         <v>0.56000000000000028</v>
       </c>
-      <c r="K47" s="172">
+      <c r="K47" s="170">
         <f t="shared" si="7"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="L47" s="172">
+      <c r="L47" s="170">
         <f t="shared" si="7"/>
         <v>0.56000000000000028</v>
       </c>
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B48" s="123" t="s">
-        <v>225</v>
-      </c>
-      <c r="C48" s="139"/>
+        <v>224</v>
+      </c>
+      <c r="C48" s="138"/>
       <c r="D48" s="95">
         <f>D44/C44-1</f>
         <v>2.2293230289069932E-3</v>
@@ -20889,30 +20903,30 @@
         <f t="shared" si="8"/>
         <v>0.65473535790094783</v>
       </c>
-      <c r="H48" s="172">
+      <c r="H48" s="170">
         <f t="shared" si="8"/>
         <v>65.103314198813621</v>
       </c>
-      <c r="I48" s="172">
+      <c r="I48" s="170">
         <f t="shared" si="8"/>
         <v>-0.21999999999999997</v>
       </c>
-      <c r="J48" s="172">
+      <c r="J48" s="170">
         <f t="shared" si="8"/>
         <v>-0.25714285714285712</v>
       </c>
-      <c r="K48" s="172">
+      <c r="K48" s="170">
         <f t="shared" si="8"/>
         <v>-6.3999999999999946E-2</v>
       </c>
-      <c r="L48" s="172">
+      <c r="L48" s="170">
         <f t="shared" si="8"/>
         <v>-0.2719999999999998</v>
       </c>
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B49" s="123" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C49" s="95">
         <f>C42/C44</f>
@@ -20934,23 +20948,23 @@
         <f t="shared" si="9"/>
         <v>0.60381683631412719</v>
       </c>
-      <c r="H49" s="172">
+      <c r="H49" s="170">
         <f t="shared" si="9"/>
         <v>9.0909090909090905E-3</v>
       </c>
-      <c r="I49" s="172">
+      <c r="I49" s="170">
         <f t="shared" si="9"/>
         <v>1.8181818181818181E-2</v>
       </c>
-      <c r="J49" s="172">
+      <c r="J49" s="170">
         <f t="shared" si="9"/>
         <v>3.8181818181818178E-2</v>
       </c>
-      <c r="K49" s="172">
+      <c r="K49" s="170">
         <f t="shared" si="9"/>
         <v>6.363636363636363E-2</v>
       </c>
-      <c r="L49" s="172">
+      <c r="L49" s="170">
         <f t="shared" si="9"/>
         <v>0.13636363636363635</v>
       </c>
@@ -21014,45 +21028,45 @@
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
       <c r="M2" s="10" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="O2" s="10" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="P2" s="10" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="Q2" s="10" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="R2" s="7"/>
       <c r="S2" s="7"/>
       <c r="T2" s="10" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="U2" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="V2" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="W2" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="X2" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="V2" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="W2" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="X2" s="10" t="s">
-        <v>363</v>
-      </c>
       <c r="Y2" s="10" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="Z2" s="10" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AA2" s="10" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AB2" s="7"/>
       <c r="AD2" s="7"/>
@@ -21081,28 +21095,28 @@
       <c r="R3" s="11"/>
       <c r="S3" s="11"/>
       <c r="T3" s="10" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="U3" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="V3" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="W3" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="X3" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="V3" s="10" t="s">
+      <c r="Y3" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="W3" s="10" t="s">
-        <v>356</v>
-      </c>
-      <c r="X3" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="Y3" s="10" t="s">
-        <v>360</v>
-      </c>
       <c r="Z3" s="10" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AA3" s="10" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AB3" s="11"/>
       <c r="AC3" s="59" t="s">
@@ -21411,7 +21425,7 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B9" s="20" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C9" s="21"/>
       <c r="D9" s="21"/>
@@ -21884,7 +21898,7 @@
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B16" s="23" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C16" s="21"/>
       <c r="D16" s="21"/>
@@ -23560,7 +23574,7 @@
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B43" s="20" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C43" s="21"/>
       <c r="D43" s="21"/>
@@ -23676,7 +23690,7 @@
     </row>
     <row r="45" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B45" s="20" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C45" s="21"/>
       <c r="D45" s="21"/>
@@ -23734,7 +23748,7 @@
     </row>
     <row r="46" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C46" s="21"/>
       <c r="D46" s="21"/>
@@ -24598,7 +24612,7 @@
     </row>
     <row r="62" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B62" s="20" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C62" s="62"/>
       <c r="D62" s="62"/>
@@ -24656,7 +24670,7 @@
     </row>
     <row r="63" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B63" s="20" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C63" s="62"/>
       <c r="D63" s="62"/>
@@ -25257,7 +25271,7 @@
     </row>
     <row r="74" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B74" s="20" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C74" s="25"/>
       <c r="D74" s="25"/>
@@ -25315,7 +25329,7 @@
     </row>
     <row r="75" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B75" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C75" s="25"/>
       <c r="D75" s="25"/>
@@ -25386,7 +25400,7 @@
     </row>
     <row r="76" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B76" s="20" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C76" s="25"/>
       <c r="D76" s="25"/>
@@ -25457,7 +25471,7 @@
     </row>
     <row r="77" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B77" s="20" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C77" s="25"/>
       <c r="D77" s="25"/>
@@ -25499,7 +25513,7 @@
     </row>
     <row r="78" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B78" s="20" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C78" s="25"/>
       <c r="D78" s="25"/>
@@ -26179,7 +26193,7 @@
     </row>
     <row r="91" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B91" s="20" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C91" s="49"/>
       <c r="D91" s="50"/>
@@ -26825,8 +26839,8 @@
       <c r="AE102" s="1"/>
     </row>
     <row r="103" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B103" s="228" t="s">
-        <v>373</v>
+      <c r="B103" s="226" t="s">
+        <v>371</v>
       </c>
       <c r="C103" s="62"/>
       <c r="D103" s="62"/>
@@ -26883,8 +26897,8 @@
       </c>
     </row>
     <row r="104" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B104" s="228" t="s">
-        <v>374</v>
+      <c r="B104" s="226" t="s">
+        <v>372</v>
       </c>
       <c r="C104" s="62"/>
       <c r="D104" s="62"/>
@@ -26942,7 +26956,7 @@
     </row>
     <row r="105" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B105" s="20" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C105" s="62"/>
       <c r="D105" s="62"/>
@@ -27000,7 +27014,7 @@
     </row>
     <row r="106" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B106" s="20" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C106" s="21"/>
       <c r="D106" s="21"/>
@@ -27397,7 +27411,7 @@
     </row>
     <row r="114" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B114" s="20" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C114" s="25"/>
       <c r="D114" s="25"/>
@@ -27468,7 +27482,7 @@
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B115" s="20" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C115" s="25"/>
       <c r="D115" s="25"/>
@@ -27539,7 +27553,7 @@
     </row>
     <row r="116" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B116" s="20" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C116" s="25"/>
       <c r="D116" s="25"/>
@@ -27677,7 +27691,7 @@
     </row>
     <row r="121" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B121" s="20" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C121" s="26"/>
       <c r="D121" s="26"/>
@@ -27958,36 +27972,36 @@
     </row>
     <row r="135" spans="1:31" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B135" s="14" t="s">
-        <v>228</v>
-      </c>
-      <c r="C135" s="174"/>
-      <c r="D135" s="174"/>
-      <c r="E135" s="174"/>
-      <c r="F135" s="174"/>
-      <c r="G135" s="174"/>
-      <c r="H135" s="174"/>
-      <c r="I135" s="174"/>
-      <c r="J135" s="174"/>
-      <c r="K135" s="174"/>
-      <c r="L135" s="174"/>
-      <c r="M135" s="174"/>
-      <c r="N135" s="174"/>
-      <c r="O135" s="174"/>
-      <c r="P135" s="174"/>
-      <c r="Q135" s="174"/>
-      <c r="T135" s="174"/>
-      <c r="U135" s="174"/>
-      <c r="V135" s="174"/>
-      <c r="W135" s="174"/>
-      <c r="X135" s="174"/>
-      <c r="Y135" s="174"/>
-      <c r="Z135" s="174"/>
-      <c r="AA135" s="174"/>
-      <c r="AC135" s="174"/>
+        <v>226</v>
+      </c>
+      <c r="C135" s="172"/>
+      <c r="D135" s="172"/>
+      <c r="E135" s="172"/>
+      <c r="F135" s="172"/>
+      <c r="G135" s="172"/>
+      <c r="H135" s="172"/>
+      <c r="I135" s="172"/>
+      <c r="J135" s="172"/>
+      <c r="K135" s="172"/>
+      <c r="L135" s="172"/>
+      <c r="M135" s="172"/>
+      <c r="N135" s="172"/>
+      <c r="O135" s="172"/>
+      <c r="P135" s="172"/>
+      <c r="Q135" s="172"/>
+      <c r="T135" s="172"/>
+      <c r="U135" s="172"/>
+      <c r="V135" s="172"/>
+      <c r="W135" s="172"/>
+      <c r="X135" s="172"/>
+      <c r="Y135" s="172"/>
+      <c r="Z135" s="172"/>
+      <c r="AA135" s="172"/>
+      <c r="AC135" s="172"/>
     </row>
     <row r="136" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B136" s="20" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C136" s="49"/>
       <c r="D136" s="49"/>
@@ -28032,7 +28046,7 @@
     </row>
     <row r="137" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B137" s="20" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C137" s="49"/>
       <c r="D137" s="49"/>
@@ -28077,7 +28091,7 @@
     </row>
     <row r="138" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B138" s="20" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C138" s="49"/>
       <c r="D138" s="49"/>
@@ -28147,35 +28161,35 @@
       <c r="O139" s="49"/>
       <c r="P139" s="49"/>
       <c r="Q139" s="49"/>
-      <c r="T139" s="175" t="str">
+      <c r="T139" s="173" t="str">
         <f t="shared" ref="T139:AA139" si="73">IF(T138&gt;T137, "BEAT", IF(T138&lt;T136, "MISSED", "MET"))</f>
         <v>BEAT</v>
       </c>
-      <c r="U139" s="175" t="str">
+      <c r="U139" s="173" t="str">
         <f t="shared" si="73"/>
         <v>BEAT</v>
       </c>
-      <c r="V139" s="175" t="str">
+      <c r="V139" s="173" t="str">
         <f t="shared" si="73"/>
         <v>BEAT</v>
       </c>
-      <c r="W139" s="175" t="str">
+      <c r="W139" s="173" t="str">
         <f t="shared" si="73"/>
         <v>BEAT</v>
       </c>
-      <c r="X139" s="175" t="str">
+      <c r="X139" s="173" t="str">
         <f t="shared" si="73"/>
         <v>BEAT</v>
       </c>
-      <c r="Y139" s="175" t="str">
+      <c r="Y139" s="173" t="str">
         <f t="shared" si="73"/>
         <v>BEAT</v>
       </c>
-      <c r="Z139" s="175" t="str">
+      <c r="Z139" s="173" t="str">
         <f t="shared" si="73"/>
         <v>BEAT</v>
       </c>
-      <c r="AA139" s="175" t="str">
+      <c r="AA139" s="173" t="str">
         <f t="shared" si="73"/>
         <v>MISSED</v>
       </c>
@@ -28183,7 +28197,7 @@
     </row>
     <row r="140" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B140" s="20" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C140" s="49"/>
       <c r="D140" s="49"/>
@@ -28200,35 +28214,35 @@
       <c r="O140" s="49"/>
       <c r="P140" s="49"/>
       <c r="Q140" s="49"/>
-      <c r="T140" s="227">
+      <c r="T140" s="225">
         <v>0.73899999999999999</v>
       </c>
-      <c r="U140" s="227">
+      <c r="U140" s="225">
         <v>0.72499999999999998</v>
       </c>
-      <c r="V140" s="227">
+      <c r="V140" s="225">
         <v>0.70099999999999996</v>
       </c>
-      <c r="W140" s="227">
+      <c r="W140" s="225">
         <v>0.71299999999999997</v>
       </c>
-      <c r="X140" s="227">
+      <c r="X140" s="225">
         <v>0.72799999999999998</v>
       </c>
-      <c r="Y140" s="227">
+      <c r="Y140" s="225">
         <v>0.74299999999999999</v>
       </c>
-      <c r="Z140" s="227">
+      <c r="Z140" s="225">
         <v>0.745</v>
       </c>
-      <c r="AA140" s="227">
+      <c r="AA140" s="225">
         <v>0.745</v>
       </c>
       <c r="AC140" s="49"/>
     </row>
     <row r="141" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B141" s="20" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C141" s="49"/>
       <c r="D141" s="49"/>
@@ -28245,35 +28259,35 @@
       <c r="O141" s="49"/>
       <c r="P141" s="49"/>
       <c r="Q141" s="49"/>
-      <c r="T141" s="227">
+      <c r="T141" s="225">
         <v>0.749</v>
       </c>
-      <c r="U141" s="227">
+      <c r="U141" s="225">
         <v>0.73499999999999999</v>
       </c>
-      <c r="V141" s="227">
+      <c r="V141" s="225">
         <v>0.71099999999999997</v>
       </c>
-      <c r="W141" s="227">
+      <c r="W141" s="225">
         <v>0.72299999999999998</v>
       </c>
-      <c r="X141" s="227">
+      <c r="X141" s="225">
         <v>0.73799999999999999</v>
       </c>
-      <c r="Y141" s="227">
+      <c r="Y141" s="225">
         <v>0.754</v>
       </c>
-      <c r="Z141" s="227">
+      <c r="Z141" s="225">
         <v>0.754</v>
       </c>
-      <c r="AA141" s="227">
+      <c r="AA141" s="225">
         <v>0.754</v>
       </c>
       <c r="AC141" s="49"/>
     </row>
     <row r="142" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B142" s="20" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C142" s="49"/>
       <c r="D142" s="49"/>
@@ -28343,35 +28357,35 @@
       <c r="O143" s="49"/>
       <c r="P143" s="49"/>
       <c r="Q143" s="49"/>
-      <c r="T143" s="175" t="str">
+      <c r="T143" s="173" t="str">
         <f t="shared" ref="T143:AA143" si="75">IF(T142&gt;T141, "BEAT", IF(T142&lt;T140, "MISSED", "MET"))</f>
         <v>MET</v>
       </c>
-      <c r="U143" s="175" t="str">
+      <c r="U143" s="173" t="str">
         <f t="shared" si="75"/>
         <v>MET</v>
       </c>
-      <c r="V143" s="175" t="str">
+      <c r="V143" s="173" t="str">
         <f t="shared" si="75"/>
         <v>MISSED</v>
       </c>
-      <c r="W143" s="175" t="str">
+      <c r="W143" s="173" t="str">
         <f t="shared" si="75"/>
         <v>BEAT</v>
       </c>
-      <c r="X143" s="175" t="str">
+      <c r="X143" s="173" t="str">
         <f t="shared" si="75"/>
         <v>MET</v>
       </c>
-      <c r="Y143" s="175" t="str">
+      <c r="Y143" s="173" t="str">
         <f t="shared" si="75"/>
         <v>MET</v>
       </c>
-      <c r="Z143" s="175" t="str">
+      <c r="Z143" s="173" t="str">
         <f t="shared" si="75"/>
         <v>MET</v>
       </c>
-      <c r="AA143" s="175" t="str">
+      <c r="AA143" s="173" t="str">
         <f t="shared" si="75"/>
         <v>MISSED</v>
       </c>
@@ -28379,7 +28393,7 @@
     </row>
     <row r="144" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B144" s="20" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C144" s="49"/>
       <c r="D144" s="49"/>
@@ -28424,7 +28438,7 @@
     </row>
     <row r="145" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B145" s="20" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C145" s="49"/>
       <c r="D145" s="49"/>
@@ -28469,7 +28483,7 @@
     </row>
     <row r="146" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B146" s="20" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C146" s="49"/>
       <c r="D146" s="49"/>
@@ -28539,35 +28553,35 @@
       <c r="O147" s="49"/>
       <c r="P147" s="49"/>
       <c r="Q147" s="49"/>
-      <c r="T147" s="175" t="str">
+      <c r="T147" s="173" t="str">
         <f t="shared" ref="T147:AA147" si="77">IF(T146&gt;T145, "BEAT", IF(T146&lt;T144, "MISSED", "MET"))</f>
         <v>MISSED</v>
       </c>
-      <c r="U147" s="175" t="str">
+      <c r="U147" s="173" t="str">
         <f t="shared" si="77"/>
         <v>MISSED</v>
       </c>
-      <c r="V147" s="175" t="str">
+      <c r="V147" s="173" t="str">
         <f t="shared" si="77"/>
         <v>MISSED</v>
       </c>
-      <c r="W147" s="175" t="str">
+      <c r="W147" s="173" t="str">
         <f t="shared" si="77"/>
         <v>MISSED</v>
       </c>
-      <c r="X147" s="175" t="str">
+      <c r="X147" s="173" t="str">
         <f t="shared" si="77"/>
         <v>MISSED</v>
       </c>
-      <c r="Y147" s="175" t="str">
+      <c r="Y147" s="173" t="str">
         <f t="shared" si="77"/>
         <v>BEAT</v>
       </c>
-      <c r="Z147" s="175" t="str">
+      <c r="Z147" s="173" t="str">
         <f t="shared" si="77"/>
         <v>MISSED</v>
       </c>
-      <c r="AA147" s="175" t="str">
+      <c r="AA147" s="173" t="str">
         <f t="shared" si="77"/>
         <v>MISSED</v>
       </c>
@@ -28578,32 +28592,32 @@
     </row>
     <row r="150" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B150" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="C150" s="174"/>
-      <c r="D150" s="174"/>
-      <c r="E150" s="174"/>
-      <c r="F150" s="174"/>
-      <c r="G150" s="174"/>
-      <c r="H150" s="174"/>
-      <c r="I150" s="174"/>
-      <c r="J150" s="174"/>
-      <c r="K150" s="174"/>
-      <c r="L150" s="174"/>
-      <c r="M150" s="174"/>
-      <c r="N150" s="174"/>
-      <c r="O150" s="174"/>
-      <c r="P150" s="174"/>
-      <c r="Q150" s="174"/>
-      <c r="T150" s="174"/>
-      <c r="U150" s="174"/>
-      <c r="V150" s="174"/>
-      <c r="W150" s="174"/>
-      <c r="X150" s="174"/>
-      <c r="Y150" s="174"/>
-      <c r="Z150" s="174"/>
-      <c r="AA150" s="174"/>
-      <c r="AC150" s="174"/>
+        <v>246</v>
+      </c>
+      <c r="C150" s="172"/>
+      <c r="D150" s="172"/>
+      <c r="E150" s="172"/>
+      <c r="F150" s="172"/>
+      <c r="G150" s="172"/>
+      <c r="H150" s="172"/>
+      <c r="I150" s="172"/>
+      <c r="J150" s="172"/>
+      <c r="K150" s="172"/>
+      <c r="L150" s="172"/>
+      <c r="M150" s="172"/>
+      <c r="N150" s="172"/>
+      <c r="O150" s="172"/>
+      <c r="P150" s="172"/>
+      <c r="Q150" s="172"/>
+      <c r="T150" s="172"/>
+      <c r="U150" s="172"/>
+      <c r="V150" s="172"/>
+      <c r="W150" s="172"/>
+      <c r="X150" s="172"/>
+      <c r="Y150" s="172"/>
+      <c r="Z150" s="172"/>
+      <c r="AA150" s="172"/>
+      <c r="AC150" s="172"/>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B151" s="20" t="s">
@@ -28898,7 +28912,7 @@
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B156" s="20" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M156" s="119">
         <f>M112/M47</f>
@@ -28959,68 +28973,68 @@
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B157" s="20" t="s">
-        <v>255</v>
-      </c>
-      <c r="M157" s="183">
+        <v>253</v>
+      </c>
+      <c r="M157" s="181">
         <f>(M112-M111)/M47</f>
         <v>-0.38561551179918835</v>
       </c>
-      <c r="N157" s="183">
+      <c r="N157" s="181">
         <f>(N112-N111)/N47</f>
         <v>-0.10601330256549478</v>
       </c>
-      <c r="O157" s="183">
+      <c r="O157" s="181">
         <f>(O112-O111)/O47</f>
         <v>-0.37868211643166272</v>
       </c>
-      <c r="P157" s="183">
+      <c r="P157" s="181">
         <f>(P112-P111)/P47</f>
         <v>-0.43802236312982967</v>
       </c>
-      <c r="Q157" s="183">
+      <c r="Q157" s="181">
         <f>(Q112-Q111)/Q47</f>
         <v>-0.34386781357085183</v>
       </c>
-      <c r="T157" s="183">
+      <c r="T157" s="181">
         <f t="shared" ref="T157:AA157" si="92">(T112-T111)/T47</f>
         <v>-0.45289475041697475</v>
       </c>
-      <c r="U157" s="183">
+      <c r="U157" s="181">
         <f t="shared" si="92"/>
         <v>-0.45562148135783548</v>
       </c>
-      <c r="V157" s="183">
+      <c r="V157" s="181">
         <f t="shared" si="92"/>
         <v>-0.43802236312982967</v>
       </c>
-      <c r="W157" s="183">
+      <c r="W157" s="181">
         <f t="shared" si="92"/>
         <v>-0.53942487744951872</v>
       </c>
-      <c r="X157" s="183">
+      <c r="X157" s="181">
         <f t="shared" si="92"/>
         <v>-0.48261777072035633</v>
       </c>
-      <c r="Y157" s="183">
+      <c r="Y157" s="181">
         <f t="shared" si="92"/>
         <v>-0.43853923984625348</v>
       </c>
-      <c r="Z157" s="183">
+      <c r="Z157" s="181">
         <f t="shared" si="92"/>
         <v>-0.3432320573706395</v>
       </c>
-      <c r="AA157" s="183">
+      <c r="AA157" s="181">
         <f t="shared" si="92"/>
         <v>-0.36885723932594616</v>
       </c>
-      <c r="AC157" s="183">
+      <c r="AC157" s="181">
         <f>(AC112-AC111)/AC47</f>
         <v>-0.36885723932594616</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B158" s="20" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="M158" s="119">
         <f>(M111+M29)/M38</f>
@@ -29081,7 +29095,7 @@
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B159" s="20" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M159" s="119">
         <f>M31/M38</f>
@@ -29142,68 +29156,68 @@
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B160" s="20" t="s">
-        <v>259</v>
-      </c>
-      <c r="M160" s="185">
+        <v>257</v>
+      </c>
+      <c r="M160" s="183">
         <f>IF(M12&gt;=0,"N/A",IF(M11&lt;=0,"N/A",M11/-M12))</f>
         <v>48.507246376811594</v>
       </c>
-      <c r="N160" s="185" t="str">
+      <c r="N160" s="183" t="str">
         <f>IF(N12&gt;=0,"N/A",IF(N11&lt;=0,"N/A",N11/-N12))</f>
         <v>N/A</v>
       </c>
-      <c r="O160" s="185" t="str">
+      <c r="O160" s="183" t="str">
         <f>IF(O12&gt;=0,"N/A",IF(O11&lt;=0,"N/A",O11/-O12))</f>
         <v>N/A</v>
       </c>
-      <c r="P160" s="185" t="str">
+      <c r="P160" s="183" t="str">
         <f>IF(P12&gt;=0,"N/A",IF(P11&lt;=0,"N/A",P11/-P12))</f>
         <v>N/A</v>
       </c>
-      <c r="Q160" s="185" t="str">
+      <c r="Q160" s="183" t="str">
         <f>IF(Q12&gt;=0,"N/A",IF(Q11&lt;=0,"N/A",Q11/-Q12))</f>
         <v>N/A</v>
       </c>
-      <c r="T160" s="185" t="str">
+      <c r="T160" s="183" t="str">
         <f t="shared" ref="T160:AA160" si="95">IF(T12&gt;=0,"N/A",IF(T11&lt;=0,"N/A",T11/-T12))</f>
         <v>N/A</v>
       </c>
-      <c r="U160" s="185" t="str">
+      <c r="U160" s="183" t="str">
         <f t="shared" si="95"/>
         <v>N/A</v>
       </c>
-      <c r="V160" s="185" t="str">
+      <c r="V160" s="183" t="str">
         <f t="shared" si="95"/>
         <v>N/A</v>
       </c>
-      <c r="W160" s="185" t="str">
+      <c r="W160" s="183" t="str">
         <f t="shared" si="95"/>
         <v>N/A</v>
       </c>
-      <c r="X160" s="185" t="str">
+      <c r="X160" s="183" t="str">
         <f t="shared" si="95"/>
         <v>N/A</v>
       </c>
-      <c r="Y160" s="185" t="str">
+      <c r="Y160" s="183" t="str">
         <f t="shared" si="95"/>
         <v>N/A</v>
       </c>
-      <c r="Z160" s="185" t="str">
+      <c r="Z160" s="183" t="str">
         <f t="shared" si="95"/>
         <v>N/A</v>
       </c>
-      <c r="AA160" s="185" t="str">
+      <c r="AA160" s="183" t="str">
         <f t="shared" si="95"/>
         <v>N/A</v>
       </c>
-      <c r="AC160" s="185" t="str">
+      <c r="AC160" s="183" t="str">
         <f>IF(AC12&gt;=0,"N/A",IF(AC11&lt;=0,"N/A",AC11/-AC12))</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B161" s="20" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="M161" s="72">
         <f>M121/Statement!M25</f>
@@ -29277,7 +29291,7 @@
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B163" s="20" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="M163" s="72">
         <f>M121/(Statement!M47/Statement!M73)</f>
@@ -29314,25 +29328,25 @@
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B164" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="M164" s="145">
+        <v>237</v>
+      </c>
+      <c r="M164" s="144">
         <f>Statement!M121*Statement!M76</f>
         <v>582191.6</v>
       </c>
-      <c r="N164" s="145">
+      <c r="N164" s="144">
         <f>Statement!N121*Statement!N76</f>
         <v>506964</v>
       </c>
-      <c r="O164" s="145">
+      <c r="O164" s="144">
         <f>Statement!O121*Statement!O76</f>
         <v>1541007.4999999998</v>
       </c>
-      <c r="P164" s="145">
+      <c r="P164" s="144">
         <f>Statement!P121*Statement!P76</f>
         <v>3515440.38</v>
       </c>
-      <c r="Q164" s="145">
+      <c r="Q164" s="144">
         <f>Statement!Q121*Statement!Q76</f>
         <v>4589469.8499999996</v>
       </c>
@@ -29344,7 +29358,7 @@
       <c r="Y164" s="49"/>
       <c r="Z164" s="49"/>
       <c r="AA164" s="49"/>
-      <c r="AC164" s="145">
+      <c r="AC164" s="144">
         <f ca="1">Statement!AC121*Statement!AC76</f>
         <v>4984955.5</v>
       </c>
@@ -29353,23 +29367,23 @@
       <c r="B165" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="M165" s="145">
+      <c r="M165" s="144">
         <f>M164+M112-M111+M46+M43</f>
         <v>571929.59999999998</v>
       </c>
-      <c r="N165" s="145">
+      <c r="N165" s="144">
         <f>N164+N112-N111+N46+N43</f>
         <v>504621</v>
       </c>
-      <c r="O165" s="145">
+      <c r="O165" s="144">
         <f>O164+O112-O111+O46+O43</f>
         <v>1524732.4999999998</v>
       </c>
-      <c r="P165" s="145">
+      <c r="P165" s="144">
         <f>P164+P112-P111+P46+P43</f>
         <v>3480693.38</v>
       </c>
-      <c r="Q165" s="145">
+      <c r="Q165" s="144">
         <f>Q164+Q112-Q111+Q46+Q43</f>
         <v>4535381.8499999996</v>
       </c>
@@ -29381,32 +29395,32 @@
       <c r="Y165" s="49"/>
       <c r="Z165" s="49"/>
       <c r="AA165" s="49"/>
-      <c r="AC165" s="145">
+      <c r="AC165" s="144">
         <f ca="1">AC164+AC112-AC111+AC46+AC43</f>
         <v>4912853.5</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B166" s="20" t="s">
-        <v>260</v>
-      </c>
-      <c r="M166" s="187">
+        <v>258</v>
+      </c>
+      <c r="M166" s="185">
         <f>M165/M5</f>
         <v>21.250263803225085</v>
       </c>
-      <c r="N166" s="187">
+      <c r="N166" s="185">
         <f>N165/N5</f>
         <v>18.707681471046193</v>
       </c>
-      <c r="O166" s="187">
+      <c r="O166" s="185">
         <f>O165/O5</f>
         <v>25.02761728111355</v>
       </c>
-      <c r="P166" s="187">
+      <c r="P166" s="185">
         <f>P165/P5</f>
         <v>26.672593086431103</v>
       </c>
-      <c r="Q166" s="187">
+      <c r="Q166" s="185">
         <f>Q165/Q5</f>
         <v>21.003166881234428</v>
       </c>
@@ -29418,7 +29432,7 @@
       <c r="Y166" s="49"/>
       <c r="Z166" s="49"/>
       <c r="AA166" s="49"/>
-      <c r="AC166" s="187">
+      <c r="AC166" s="185">
         <f ca="1">AC165/AC5</f>
         <v>19.380780777226803</v>
       </c>
@@ -29427,23 +29441,23 @@
       <c r="B167" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="M167" s="187">
+      <c r="M167" s="185">
         <f>M165/M11</f>
         <v>56.959426351956971</v>
       </c>
-      <c r="N167" s="187">
+      <c r="N167" s="185">
         <f>N165/N11</f>
         <v>119.46519886363636</v>
       </c>
-      <c r="O167" s="187">
+      <c r="O167" s="185">
         <f>O165/O11</f>
         <v>46.243251850054584</v>
       </c>
-      <c r="P167" s="187">
+      <c r="P167" s="185">
         <f>P165/P11</f>
         <v>42.732537536984516</v>
       </c>
-      <c r="Q167" s="187">
+      <c r="Q167" s="185">
         <f>Q165/Q11</f>
         <v>34.784003389908499</v>
       </c>
@@ -29455,14 +29469,14 @@
       <c r="Y167" s="49"/>
       <c r="Z167" s="49"/>
       <c r="AA167" s="49"/>
-      <c r="AC167" s="187">
+      <c r="AC167" s="185">
         <f ca="1">AC165/AC11</f>
         <v>30.272998120590319</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B168" s="20" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="M168" s="64">
         <f>M57-M52+M114+M63</f>
@@ -29523,7 +29537,7 @@
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B169" s="20" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="M169" s="64">
         <f>M113+M51+M114+M53+M55+M56+M54</f>
@@ -29560,7 +29574,7 @@
     </row>
     <row r="170" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B170" s="20" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="M170" s="72">
         <f>M164/M168</f>
@@ -29597,7 +29611,7 @@
     </row>
     <row r="171" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B171" s="20" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="M171" s="72">
         <f>M165/M169</f>
@@ -29634,7 +29648,7 @@
     </row>
     <row r="172" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B172" s="20" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="M172" s="74">
         <f>M168/M164</f>
@@ -29671,7 +29685,7 @@
     </row>
     <row r="173" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B173" s="20" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="M173" s="74">
         <f>M25/M121</f>
@@ -29708,25 +29722,25 @@
     </row>
     <row r="174" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B174" s="20" t="s">
-        <v>267</v>
-      </c>
-      <c r="M174" s="156">
+        <v>265</v>
+      </c>
+      <c r="M174" s="155">
         <f>M80/M121</f>
         <v>7.0052539404553418E-4</v>
       </c>
-      <c r="N174" s="156">
+      <c r="N174" s="155">
         <f>N80/N121</f>
         <v>7.8585461689587434E-4</v>
       </c>
-      <c r="O174" s="156">
+      <c r="O174" s="155">
         <f>O80/O121</f>
         <v>2.6216614779616586E-4</v>
       </c>
-      <c r="P174" s="156">
+      <c r="P174" s="155">
         <f>P80/P121</f>
         <v>2.3839573692329268E-4</v>
       </c>
-      <c r="Q174" s="156">
+      <c r="Q174" s="155">
         <f>Q80/Q121</f>
         <v>2.1314008632173498E-4</v>
       </c>
@@ -29738,32 +29752,32 @@
       <c r="Y174" s="49"/>
       <c r="Z174" s="49"/>
       <c r="AA174" s="49"/>
-      <c r="AC174" s="156">
+      <c r="AC174" s="155">
         <f ca="1">AC80/AC121</f>
         <v>1.9502681618722574E-4</v>
       </c>
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B175" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="M175" s="156">
+        <v>290</v>
+      </c>
+      <c r="M175" s="155">
         <f>-M61/M164</f>
         <v>0</v>
       </c>
-      <c r="N175" s="156">
+      <c r="N175" s="155">
         <f>-N61/N164</f>
         <v>1.9802195027654824E-2</v>
       </c>
-      <c r="O175" s="156">
+      <c r="O175" s="155">
         <f>-O61/O164</f>
         <v>6.1862125914377451E-3</v>
       </c>
-      <c r="P175" s="156">
+      <c r="P175" s="155">
         <f>-P61/P164</f>
         <v>9.5879879493220143E-3</v>
       </c>
-      <c r="Q175" s="156">
+      <c r="Q175" s="155">
         <f>-Q61/Q164</f>
         <v>8.7343421593672754E-3</v>
       </c>
@@ -29775,32 +29789,32 @@
       <c r="Y175" s="49"/>
       <c r="Z175" s="49"/>
       <c r="AA175" s="49"/>
-      <c r="AC175" s="156">
+      <c r="AC175" s="155">
         <f ca="1">-AC61/AC164</f>
         <v>9.0881453204547154E-3</v>
       </c>
     </row>
     <row r="176" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B176" s="20" t="s">
-        <v>294</v>
-      </c>
-      <c r="M176" s="156">
+        <v>292</v>
+      </c>
+      <c r="M176" s="155">
         <f>-(M61+M62)/M164</f>
         <v>6.853413893295609E-4</v>
       </c>
-      <c r="N176" s="156">
+      <c r="N176" s="155">
         <f>-(N61+N62)/N164</f>
         <v>2.0587260633891165E-2</v>
       </c>
-      <c r="O176" s="156">
+      <c r="O176" s="155">
         <f>-(O61+O62)/O164</f>
         <v>6.4425384042582539E-3</v>
       </c>
-      <c r="P176" s="156">
+      <c r="P176" s="155">
         <f>-(P61+P62)/P164</f>
         <v>9.8252270743957263E-3</v>
       </c>
-      <c r="Q176" s="156">
+      <c r="Q176" s="155">
         <f>-(Q61+Q62)/Q164</f>
         <v>8.946567107309792E-3</v>
       </c>
@@ -29812,32 +29826,32 @@
       <c r="Y176" s="49"/>
       <c r="Z176" s="49"/>
       <c r="AA176" s="49"/>
-      <c r="AC176" s="156">
+      <c r="AC176" s="155">
         <f ca="1">-(AC61+AC62)/AC164</f>
         <v>9.2833326195188703E-3</v>
       </c>
     </row>
     <row r="177" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B177" s="20" t="s">
-        <v>387</v>
-      </c>
-      <c r="M177" s="230">
+        <v>385</v>
+      </c>
+      <c r="M177" s="228">
         <f>M169/M5</f>
         <v>0.24838741111758303</v>
       </c>
-      <c r="N177" s="230">
+      <c r="N177" s="228">
         <f>N169/N5</f>
         <v>6.4061689033884484E-2</v>
       </c>
-      <c r="O177" s="230">
+      <c r="O177" s="228">
         <f>O169/O5</f>
         <v>0.42238462291779383</v>
       </c>
-      <c r="P177" s="230">
+      <c r="P177" s="228">
         <f>P169/P5</f>
         <v>0.45896309457389761</v>
       </c>
-      <c r="Q177" s="230">
+      <c r="Q177" s="228">
         <f>Q169/Q5</f>
         <v>0.42373919358213857</v>
       </c>
@@ -29849,32 +29863,32 @@
       <c r="Y177" s="49"/>
       <c r="Z177" s="49"/>
       <c r="AA177" s="49"/>
-      <c r="AC177" s="156">
+      <c r="AC177" s="155">
         <f>AC169/AC5</f>
         <v>0.50027836962176253</v>
       </c>
     </row>
     <row r="178" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B178" s="20" t="s">
-        <v>388</v>
-      </c>
-      <c r="M178" s="230">
+        <v>386</v>
+      </c>
+      <c r="M178" s="228">
         <f>M168/M5</f>
         <v>0.22768819201902354</v>
       </c>
-      <c r="N178" s="230">
+      <c r="N178" s="228">
         <f t="shared" ref="N178:Q178" si="102">N168/N5</f>
         <v>4.0742937643656857E-2</v>
       </c>
-      <c r="O178" s="230">
+      <c r="O178" s="228">
         <f t="shared" si="102"/>
         <v>0.38527953776960705</v>
       </c>
-      <c r="P178" s="230">
+      <c r="P178" s="228">
         <f t="shared" si="102"/>
         <v>0.43001754829612943</v>
       </c>
-      <c r="Q178" s="230">
+      <c r="Q178" s="228">
         <f t="shared" si="102"/>
         <v>0.41812927784827125</v>
       </c>
@@ -29886,32 +29900,32 @@
       <c r="Y178" s="49"/>
       <c r="Z178" s="49"/>
       <c r="AA178" s="49"/>
-      <c r="AC178" s="156">
+      <c r="AC178" s="155">
         <f t="shared" ref="AC178" si="103">AC168/AC5</f>
         <v>0.4427652263788458</v>
       </c>
     </row>
     <row r="179" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B179" s="20" t="s">
-        <v>270</v>
-      </c>
-      <c r="M179" s="156">
+        <v>268</v>
+      </c>
+      <c r="M179" s="155">
         <f>-M62/M168</f>
         <v>6.5110966057441252E-2</v>
       </c>
-      <c r="N179" s="156">
+      <c r="N179" s="155">
         <f>-N62/N168</f>
         <v>0.36214740673339402</v>
       </c>
-      <c r="O179" s="156">
+      <c r="O179" s="155">
         <f>-O62/O168</f>
         <v>1.6828561690524879E-2</v>
       </c>
-      <c r="P179" s="156">
+      <c r="P179" s="155">
         <f>-P62/P168</f>
         <v>1.4862071423479934E-2</v>
       </c>
-      <c r="Q179" s="156">
+      <c r="Q179" s="155">
         <f>-Q62/Q168</f>
         <v>1.0787462620445233E-2</v>
       </c>
@@ -29923,32 +29937,32 @@
       <c r="Y179" s="49"/>
       <c r="Z179" s="49"/>
       <c r="AA179" s="49"/>
-      <c r="AC179" s="156">
+      <c r="AC179" s="155">
         <f>-AC62/AC168</f>
         <v>8.6691554478469674E-3</v>
       </c>
     </row>
     <row r="180" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B180" s="20" t="s">
-        <v>272</v>
-      </c>
-      <c r="M180" s="156">
+        <v>270</v>
+      </c>
+      <c r="M180" s="155">
         <f>-M61/M168</f>
         <v>0</v>
       </c>
-      <c r="N180" s="156">
+      <c r="N180" s="155">
         <f>-N61/N168</f>
         <v>9.1346678798908094</v>
       </c>
-      <c r="O180" s="156">
+      <c r="O180" s="155">
         <f>-O61/O168</f>
         <v>0.40614349011588274</v>
       </c>
-      <c r="P180" s="156">
+      <c r="P180" s="155">
         <f>-P61/P168</f>
         <v>0.60064865635469389</v>
       </c>
-      <c r="Q180" s="156">
+      <c r="Q180" s="155">
         <f>-Q61/Q168</f>
         <v>0.44396943183076754</v>
       </c>
@@ -29960,32 +29974,32 @@
       <c r="Y180" s="49"/>
       <c r="Z180" s="49"/>
       <c r="AA180" s="49"/>
-      <c r="AC180" s="156">
+      <c r="AC180" s="155">
         <f>-AC61/AC168</f>
         <v>0.40364585653572349</v>
       </c>
     </row>
     <row r="181" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B181" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="M181" s="156">
+        <v>281</v>
+      </c>
+      <c r="M181" s="155">
         <f>(-M62-M61)/M168</f>
         <v>6.5110966057441252E-2</v>
       </c>
-      <c r="N181" s="156">
+      <c r="N181" s="155">
         <f>(-N62-N61)/N168</f>
         <v>9.4968152866242033</v>
       </c>
-      <c r="O181" s="156">
+      <c r="O181" s="155">
         <f>(-O62-O61)/O168</f>
         <v>0.42297205180640762</v>
       </c>
-      <c r="P181" s="156">
+      <c r="P181" s="155">
         <f>(-P62-P61)/P168</f>
         <v>0.61551072777817373</v>
       </c>
-      <c r="Q181" s="156">
+      <c r="Q181" s="155">
         <f>(-Q62-Q61)/Q168</f>
         <v>0.45475689445121276</v>
       </c>
@@ -29997,32 +30011,32 @@
       <c r="Y181" s="49"/>
       <c r="Z181" s="49"/>
       <c r="AA181" s="49"/>
-      <c r="AC181" s="156">
+      <c r="AC181" s="155">
         <f>(-AC62-AC61)/AC168</f>
         <v>0.41231501198357046</v>
       </c>
     </row>
     <row r="182" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B182" s="20" t="s">
-        <v>277</v>
-      </c>
-      <c r="M182" s="156">
+        <v>275</v>
+      </c>
+      <c r="M182" s="155">
         <f>M78/M76</f>
         <v>3.9623381718320909E-2</v>
       </c>
-      <c r="N182" s="156">
+      <c r="N182" s="155">
         <f>N78/N76</f>
         <v>3.9759036144578312E-2</v>
       </c>
-      <c r="O182" s="156">
+      <c r="O182" s="155">
         <f>O78/O76</f>
         <v>4.118811881188119E-2</v>
       </c>
-      <c r="P182" s="156">
+      <c r="P182" s="155">
         <f>P78/P76</f>
         <v>4.1380989086778369E-2</v>
       </c>
-      <c r="Q182" s="156">
+      <c r="Q182" s="155">
         <f>Q78/Q76</f>
         <v>3.9133101615211614E-2</v>
       </c>
@@ -30034,14 +30048,14 @@
       <c r="Y182" s="49"/>
       <c r="Z182" s="49"/>
       <c r="AA182" s="49"/>
-      <c r="AC182" s="156">
+      <c r="AC182" s="155">
         <f>AC78/AC76</f>
         <v>3.9374614276897757E-2</v>
       </c>
     </row>
     <row r="183" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B183" s="20" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="M183" s="72">
         <f>M111/M73</f>
@@ -30102,129 +30116,129 @@
     </row>
     <row r="184" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B184" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="M184" s="156">
+        <v>278</v>
+      </c>
+      <c r="M184" s="155">
         <f>M52/M57</f>
         <v>0.22002635046113306</v>
       </c>
-      <c r="N184" s="156">
+      <c r="N184" s="155">
         <f>N52/N57</f>
         <v>0.48023400106364122</v>
       </c>
-      <c r="O184" s="156">
+      <c r="O184" s="155">
         <f>O52/O57</f>
         <v>0.1263438946244215</v>
       </c>
-      <c r="P184" s="156">
+      <c r="P184" s="155">
         <f>P52/P57</f>
         <v>7.3912839956934887E-2</v>
       </c>
-      <c r="Q184" s="156">
+      <c r="Q184" s="155">
         <f>Q52/Q57</f>
         <v>6.217021359450145E-2</v>
       </c>
-      <c r="T184" s="156">
+      <c r="T184" s="155">
         <f t="shared" ref="T184:AA184" si="105">T52/T57</f>
         <v>7.9646628476775491E-2</v>
       </c>
-      <c r="U184" s="156">
+      <c r="U184" s="155">
         <f t="shared" si="105"/>
         <v>7.1019343127800783E-2</v>
       </c>
-      <c r="V184" s="156">
+      <c r="V184" s="155">
         <f t="shared" si="105"/>
         <v>7.944431080105846E-2</v>
       </c>
-      <c r="W184" s="156">
+      <c r="W184" s="155">
         <f t="shared" si="105"/>
         <v>5.3768147661778655E-2</v>
       </c>
-      <c r="X184" s="156">
+      <c r="X184" s="155">
         <f t="shared" si="105"/>
         <v>0.10569476082004556</v>
       </c>
-      <c r="Y184" s="156">
+      <c r="Y184" s="155">
         <f t="shared" si="105"/>
         <v>6.9684210526315793E-2</v>
       </c>
-      <c r="Z184" s="156">
+      <c r="Z184" s="155">
         <f t="shared" si="105"/>
         <v>4.5122962144238742E-2</v>
       </c>
-      <c r="AA184" s="156">
+      <c r="AA184" s="155">
         <f t="shared" si="105"/>
         <v>3.829651994279358E-2</v>
       </c>
-      <c r="AC184" s="156">
+      <c r="AC184" s="155">
         <f>AC52/AC57</f>
         <v>5.4437361220542942E-2</v>
       </c>
     </row>
     <row r="185" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B185" s="20" t="s">
-        <v>281</v>
-      </c>
-      <c r="M185" s="156">
+        <v>279</v>
+      </c>
+      <c r="M185" s="155">
         <f>M52/M5</f>
         <v>7.4459389165490081E-2</v>
       </c>
-      <c r="N185" s="156">
+      <c r="N185" s="155">
         <f>N52/N5</f>
         <v>0.10043004374582931</v>
       </c>
-      <c r="O185" s="156">
+      <c r="O185" s="155">
         <f>O52/O5</f>
         <v>5.8254817635665278E-2</v>
       </c>
-      <c r="P185" s="156">
+      <c r="P185" s="155">
         <f>P52/P5</f>
         <v>3.629968505023104E-2</v>
       </c>
-      <c r="Q185" s="156">
+      <c r="Q185" s="155">
         <f>Q52/Q5</f>
         <v>2.9573303448211987E-2</v>
       </c>
-      <c r="T185" s="156">
+      <c r="T185" s="155">
         <f t="shared" ref="T185:AA185" si="106">T52/T5</f>
         <v>3.8415446071904127E-2</v>
       </c>
-      <c r="U185" s="156">
+      <c r="U185" s="155">
         <f t="shared" si="106"/>
         <v>3.5687817114189613E-2</v>
       </c>
-      <c r="V185" s="156">
+      <c r="V185" s="155">
         <f t="shared" si="106"/>
         <v>3.3586738196333683E-2</v>
       </c>
-      <c r="W185" s="156">
+      <c r="W185" s="155">
         <f t="shared" si="106"/>
         <v>3.3452861876446825E-2</v>
       </c>
-      <c r="X185" s="156">
+      <c r="X185" s="155">
         <f t="shared" si="106"/>
         <v>3.4743170100335882E-2</v>
       </c>
-      <c r="Y185" s="156">
+      <c r="Y185" s="155">
         <f t="shared" si="106"/>
         <v>2.9032031715959722E-2</v>
       </c>
-      <c r="Z185" s="156">
+      <c r="Z185" s="155">
         <f t="shared" si="106"/>
         <v>2.3969938497218429E-2</v>
       </c>
-      <c r="AA185" s="156">
+      <c r="AA185" s="155">
         <f t="shared" si="106"/>
         <v>2.3623108497212521E-2</v>
       </c>
-      <c r="AC185" s="156">
+      <c r="AC185" s="155">
         <f>AC52/AC5</f>
         <v>2.6983206504372935E-2</v>
       </c>
     </row>
     <row r="186" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B186" s="20" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="M186" s="72">
         <f>(M111-M112)/M73</f>
@@ -30285,25 +30299,25 @@
     </row>
     <row r="187" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B187" s="20" t="s">
-        <v>291</v>
-      </c>
-      <c r="M187" s="156">
+        <v>289</v>
+      </c>
+      <c r="M187" s="155">
         <f>(M111-M112)/M164</f>
         <v>1.7626499592230463E-2</v>
       </c>
-      <c r="N187" s="156">
+      <c r="N187" s="155">
         <f>(N111-N112)/N164</f>
         <v>4.6216299382204652E-3</v>
       </c>
-      <c r="O187" s="156">
+      <c r="O187" s="155">
         <f>(O111-O112)/O164</f>
         <v>1.0561272414313365E-2</v>
       </c>
-      <c r="P187" s="156">
+      <c r="P187" s="155">
         <f>(P111-P112)/P164</f>
         <v>9.8841101665902813E-3</v>
       </c>
-      <c r="Q187" s="156">
+      <c r="Q187" s="155">
         <f>(Q111-Q112)/Q164</f>
         <v>1.1785239203608671E-2</v>
       </c>
@@ -30315,190 +30329,190 @@
       <c r="Y187" s="49"/>
       <c r="Z187" s="49"/>
       <c r="AA187" s="49"/>
-      <c r="AC187" s="156">
+      <c r="AC187" s="155">
         <f ca="1">(AC111-AC112)/AC164</f>
         <v>1.4463920490363455E-2</v>
       </c>
     </row>
     <row r="188" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B188" s="20" t="s">
-        <v>300</v>
-      </c>
-      <c r="M188" s="156">
+        <v>298</v>
+      </c>
+      <c r="M188" s="155">
         <f>-M114/M5</f>
         <v>3.6263654603552055E-2</v>
       </c>
-      <c r="N188" s="156">
+      <c r="N188" s="155">
         <f>-N114/N5</f>
         <v>6.7954326388373995E-2</v>
       </c>
-      <c r="O188" s="156">
+      <c r="O188" s="155">
         <f>-O114/O5</f>
         <v>1.7547027346442992E-2</v>
       </c>
-      <c r="P188" s="156">
+      <c r="P188" s="155">
         <f>-P114/P5</f>
         <v>2.4797504923484832E-2</v>
       </c>
-      <c r="Q188" s="156">
+      <c r="Q188" s="155">
         <f>-Q114/Q5</f>
         <v>2.7980253591308617E-2</v>
       </c>
-      <c r="T188" s="156">
+      <c r="T188" s="155">
         <f t="shared" ref="T188:AA188" si="108">-T114/T5</f>
         <v>3.2523302263648468E-2</v>
       </c>
-      <c r="U188" s="156">
+      <c r="U188" s="155">
         <f t="shared" si="108"/>
         <v>2.3174277407217378E-2</v>
       </c>
-      <c r="V188" s="156">
+      <c r="V188" s="155">
         <f t="shared" si="108"/>
         <v>2.7382980346291729E-2</v>
       </c>
-      <c r="W188" s="156">
+      <c r="W188" s="155">
         <f t="shared" si="108"/>
         <v>2.7847124506377378E-2</v>
       </c>
-      <c r="X188" s="156">
+      <c r="X188" s="155">
         <f t="shared" si="108"/>
         <v>4.05194360652932E-2</v>
       </c>
-      <c r="Y188" s="156">
+      <c r="Y188" s="155">
         <f t="shared" si="108"/>
         <v>2.871627547977406E-2</v>
       </c>
-      <c r="Z188" s="156">
+      <c r="Z188" s="155">
         <f t="shared" si="108"/>
         <v>1.8847153111101324E-2</v>
       </c>
-      <c r="AA188" s="156">
+      <c r="AA188" s="155">
         <f t="shared" si="108"/>
         <v>2.1527905409544815E-2</v>
       </c>
-      <c r="AC188" s="156">
+      <c r="AC188" s="155">
         <f>-AC114/AC5</f>
         <v>2.5925969758295166E-2</v>
       </c>
     </row>
     <row r="189" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B189" s="20" t="s">
-        <v>301</v>
-      </c>
-      <c r="M189" s="156">
+        <v>299</v>
+      </c>
+      <c r="M189" s="155">
         <f>-(M114/M57)</f>
         <v>0.10715854194115064</v>
       </c>
-      <c r="N189" s="156">
+      <c r="N189" s="155">
         <f>-(N114/N57)</f>
         <v>0.32494238610175502</v>
       </c>
-      <c r="O189" s="156">
+      <c r="O189" s="155">
         <f>-(O114/O57)</f>
         <v>3.8056247775008899E-2</v>
       </c>
-      <c r="P189" s="156">
+      <c r="P189" s="155">
         <f>-(P114/P57)</f>
         <v>5.0492284167329808E-2</v>
       </c>
-      <c r="Q189" s="156">
+      <c r="Q189" s="155">
         <f>-(Q114/Q57)</f>
         <v>5.8821238731283712E-2</v>
       </c>
-      <c r="T189" s="156">
+      <c r="T189" s="155">
         <f t="shared" ref="T189:AA189" si="109">-(T114/T57)</f>
         <v>6.7430464490302988E-2</v>
       </c>
-      <c r="U189" s="156">
+      <c r="U189" s="155">
         <f t="shared" si="109"/>
         <v>4.6117193261103862E-2</v>
       </c>
-      <c r="V189" s="156">
+      <c r="V189" s="155">
         <f t="shared" si="109"/>
         <v>6.4770267019485211E-2</v>
       </c>
-      <c r="W189" s="156">
+      <c r="W189" s="155">
         <f t="shared" si="109"/>
         <v>4.4758152768658348E-2</v>
       </c>
-      <c r="X189" s="156">
+      <c r="X189" s="155">
         <f t="shared" si="109"/>
         <v>0.12326716563618614</v>
       </c>
-      <c r="Y189" s="156">
+      <c r="Y189" s="155">
         <f t="shared" si="109"/>
         <v>6.8926315789473683E-2</v>
       </c>
-      <c r="Z189" s="156">
+      <c r="Z189" s="155">
         <f t="shared" si="109"/>
         <v>3.5479414202818457E-2</v>
       </c>
-      <c r="AA189" s="156">
+      <c r="AA189" s="155">
         <f t="shared" si="109"/>
         <v>3.4899888765294769E-2</v>
       </c>
-      <c r="AC189" s="156">
+      <c r="AC189" s="155">
         <f>-(AC114/AC57)</f>
         <v>5.2304435371550904E-2</v>
       </c>
     </row>
     <row r="190" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B190" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="M190" s="156">
+        <v>300</v>
+      </c>
+      <c r="M190" s="155">
         <f>-M114/M51</f>
         <v>0.83134582623509368</v>
       </c>
-      <c r="N190" s="156">
+      <c r="N190" s="155">
         <f>-N114/N51</f>
         <v>1.1871761658031088</v>
       </c>
-      <c r="O190" s="156">
+      <c r="O190" s="155">
         <f>-O114/O51</f>
         <v>0.70888594164456231</v>
       </c>
-      <c r="P190" s="156">
+      <c r="P190" s="155">
         <f>-P114/P51</f>
         <v>1.7360515021459229</v>
       </c>
-      <c r="Q190" s="156">
+      <c r="Q190" s="155">
         <f>-Q114/Q51</f>
         <v>2.1252198381990857</v>
       </c>
-      <c r="T190" s="156">
+      <c r="T190" s="155">
         <f t="shared" ref="T190:AA190" si="110">-T114/T51</f>
         <v>2.25635103926097</v>
       </c>
-      <c r="U190" s="156">
+      <c r="U190" s="155">
         <f t="shared" si="110"/>
         <v>1.7008368200836821</v>
       </c>
-      <c r="V190" s="156">
+      <c r="V190" s="155">
         <f t="shared" si="110"/>
         <v>1.9834254143646408</v>
       </c>
-      <c r="W190" s="156">
+      <c r="W190" s="155">
         <f t="shared" si="110"/>
         <v>2.0081833060556464</v>
       </c>
-      <c r="X190" s="156">
+      <c r="X190" s="155">
         <f t="shared" si="110"/>
         <v>2.8353293413173652</v>
       </c>
-      <c r="Y190" s="156">
+      <c r="Y190" s="155">
         <f t="shared" si="110"/>
         <v>2.1768617021276597</v>
       </c>
-      <c r="Z190" s="156">
+      <c r="Z190" s="155">
         <f t="shared" si="110"/>
         <v>1.5832305795314427</v>
       </c>
-      <c r="AA190" s="156">
+      <c r="AA190" s="155">
         <f t="shared" si="110"/>
         <v>1.7622868605817452</v>
       </c>
-      <c r="AC190" s="156">
+      <c r="AC190" s="155">
         <f>-AC114/AC51</f>
         <v>2.0359355638166048</v>
       </c>
@@ -30508,36 +30522,36 @@
     </row>
     <row r="193" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B193" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="C193" s="174"/>
-      <c r="D193" s="174"/>
-      <c r="E193" s="174"/>
-      <c r="F193" s="174"/>
-      <c r="G193" s="174"/>
-      <c r="H193" s="174"/>
-      <c r="I193" s="174"/>
-      <c r="J193" s="174"/>
-      <c r="K193" s="174"/>
-      <c r="L193" s="174"/>
-      <c r="M193" s="174"/>
-      <c r="N193" s="174"/>
-      <c r="O193" s="174"/>
-      <c r="P193" s="174"/>
-      <c r="Q193" s="174"/>
-      <c r="T193" s="174"/>
-      <c r="U193" s="174"/>
-      <c r="V193" s="174"/>
-      <c r="W193" s="174"/>
-      <c r="X193" s="174"/>
-      <c r="Y193" s="174"/>
-      <c r="Z193" s="174"/>
-      <c r="AA193" s="174"/>
-      <c r="AC193" s="174"/>
+        <v>309</v>
+      </c>
+      <c r="C193" s="172"/>
+      <c r="D193" s="172"/>
+      <c r="E193" s="172"/>
+      <c r="F193" s="172"/>
+      <c r="G193" s="172"/>
+      <c r="H193" s="172"/>
+      <c r="I193" s="172"/>
+      <c r="J193" s="172"/>
+      <c r="K193" s="172"/>
+      <c r="L193" s="172"/>
+      <c r="M193" s="172"/>
+      <c r="N193" s="172"/>
+      <c r="O193" s="172"/>
+      <c r="P193" s="172"/>
+      <c r="Q193" s="172"/>
+      <c r="T193" s="172"/>
+      <c r="U193" s="172"/>
+      <c r="V193" s="172"/>
+      <c r="W193" s="172"/>
+      <c r="X193" s="172"/>
+      <c r="Y193" s="172"/>
+      <c r="Z193" s="172"/>
+      <c r="AA193" s="172"/>
+      <c r="AC193" s="172"/>
     </row>
     <row r="194" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B194" s="228" t="s">
-        <v>373</v>
+      <c r="B194" s="226" t="s">
+        <v>371</v>
       </c>
       <c r="C194" s="81"/>
       <c r="D194" s="81"/>
@@ -30634,8 +30648,8 @@
       <c r="AC194" s="49"/>
     </row>
     <row r="195" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B195" s="228" t="s">
-        <v>374</v>
+      <c r="B195" s="226" t="s">
+        <v>372</v>
       </c>
       <c r="M195" s="81">
         <f t="shared" ref="M195:Q195" si="120">IF(L104=0,
@@ -30696,7 +30710,7 @@
     </row>
     <row r="196" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B196" s="20" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="M196" s="81">
         <f t="shared" ref="M196:Q197" si="121">IF(L105=0,
@@ -30757,7 +30771,7 @@
     </row>
     <row r="197" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B197" s="20" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="M197" s="81">
         <f t="shared" si="121"/>
@@ -30830,36 +30844,36 @@
     </row>
     <row r="200" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B200" s="14" t="s">
-        <v>312</v>
-      </c>
-      <c r="C200" s="174"/>
-      <c r="D200" s="174"/>
-      <c r="E200" s="174"/>
-      <c r="F200" s="174"/>
-      <c r="G200" s="174"/>
-      <c r="H200" s="174"/>
-      <c r="I200" s="174"/>
-      <c r="J200" s="174"/>
-      <c r="K200" s="174"/>
-      <c r="L200" s="174"/>
-      <c r="M200" s="174"/>
-      <c r="N200" s="174"/>
-      <c r="O200" s="174"/>
-      <c r="P200" s="174"/>
-      <c r="Q200" s="174"/>
-      <c r="T200" s="174"/>
-      <c r="U200" s="174"/>
-      <c r="V200" s="174"/>
-      <c r="W200" s="174"/>
-      <c r="X200" s="174"/>
-      <c r="Y200" s="174"/>
-      <c r="Z200" s="174"/>
-      <c r="AA200" s="174"/>
-      <c r="AC200" s="174"/>
+        <v>310</v>
+      </c>
+      <c r="C200" s="172"/>
+      <c r="D200" s="172"/>
+      <c r="E200" s="172"/>
+      <c r="F200" s="172"/>
+      <c r="G200" s="172"/>
+      <c r="H200" s="172"/>
+      <c r="I200" s="172"/>
+      <c r="J200" s="172"/>
+      <c r="K200" s="172"/>
+      <c r="L200" s="172"/>
+      <c r="M200" s="172"/>
+      <c r="N200" s="172"/>
+      <c r="O200" s="172"/>
+      <c r="P200" s="172"/>
+      <c r="Q200" s="172"/>
+      <c r="T200" s="172"/>
+      <c r="U200" s="172"/>
+      <c r="V200" s="172"/>
+      <c r="W200" s="172"/>
+      <c r="X200" s="172"/>
+      <c r="Y200" s="172"/>
+      <c r="Z200" s="172"/>
+      <c r="AA200" s="172"/>
+      <c r="AC200" s="172"/>
     </row>
     <row r="201" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B201" s="20" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C201" s="81"/>
       <c r="D201" s="81"/>
@@ -30931,7 +30945,7 @@
   <sheetData>
     <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -30954,16 +30968,16 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B1" s="82" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="231" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C4" s="231"/>
       <c r="E4" s="231" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F4" s="231"/>
       <c r="G4" s="231"/>
@@ -30972,34 +30986,34 @@
       <c r="B5" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="176">
+      <c r="C5" s="174">
         <f ca="1">Overview!C5</f>
         <v>205.1</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="133" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G5" s="133" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B6" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="C6" s="177">
+        <v>237</v>
+      </c>
+      <c r="C6" s="175">
         <f ca="1">Statement!AC164</f>
         <v>4984955.5</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="182">
+      <c r="F6" s="180">
         <f>IF(Statement!M5&lt;=0,"N/A",_xlfn.RRI(4,Statement!M5,Statement!Q5))</f>
         <v>0.68301391480282692</v>
       </c>
-      <c r="G6" s="182" t="str">
+      <c r="G6" s="180" t="str">
         <f>IF(Statement!H5&lt;=0,"N/A",_xlfn.RRI(9,Statement!H5,Statement!Q5))</f>
         <v>N/A</v>
       </c>
@@ -31008,38 +31022,38 @@
       <c r="B7" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="C7" s="177">
+      <c r="C7" s="175">
         <f ca="1">Statement!AC165</f>
         <v>4912853.5</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="182">
+      <c r="F7" s="180">
         <f>IF(OR(Statement!M17&lt;=0, Statement!Q17&lt;=0), "N/A", _xlfn.RRI(4, Statement!M17, Statement!Q17))</f>
         <v>0.87319285132860491</v>
       </c>
-      <c r="G7" s="182" t="str">
+      <c r="G7" s="180" t="str">
         <f>IF(OR(Statement!H17&lt;=0, Statement!Q17&lt;=0), "N/A", _xlfn.RRI(9, Statement!H17, Statement!Q17))</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="C8" s="178">
+        <v>235</v>
+      </c>
+      <c r="C8" s="176">
         <f ca="1">Statement!AC161</f>
         <v>31.408882082695254</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>243</v>
-      </c>
-      <c r="F8" s="182">
+        <v>241</v>
+      </c>
+      <c r="F8" s="180">
         <f>IF(OR(Statement!M25&lt;=0, Statement!Q25&lt;=0), "N/A", _xlfn.RRI(4, Statement!M25, Statement!Q25))</f>
         <v>0.88879070838020025</v>
       </c>
-      <c r="G8" s="182" t="str">
+      <c r="G8" s="180" t="str">
         <f>IF(OR(Statement!H25&lt;=0, Statement!Q25&lt;=0), "N/A", _xlfn.RRI(9, Statement!H25, Statement!Q25))</f>
         <v>N/A</v>
       </c>
@@ -31048,47 +31062,47 @@
       <c r="B9" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="C9" s="178">
+      <c r="C9" s="176">
         <f ca="1">Statement!AC162</f>
         <v>19.790223124292382</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>244</v>
-      </c>
-      <c r="F9" s="182">
+        <v>242</v>
+      </c>
+      <c r="F9" s="180">
         <f>IF(Statement!M80&lt;=0,"N/A",_xlfn.RRI(4,Statement!M80,Statement!Q80))</f>
         <v>0.25743342968293548</v>
       </c>
-      <c r="G9" s="182" t="str">
+      <c r="G9" s="180" t="str">
         <f>IF(Statement!H80&lt;=0,"N/A",_xlfn.RRI(9,Statement!H80,Statement!Q80))</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="20" t="s">
-        <v>238</v>
-      </c>
-      <c r="C10" s="178">
+        <v>236</v>
+      </c>
+      <c r="C10" s="176">
         <f ca="1">Statement!AC163</f>
         <v>25.391714499114975</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="F10" s="182">
+      <c r="F10" s="180">
         <f>IF(Statement!M121&lt;=0,"N/A",_xlfn.RRI(4,Statement!M121,Statement!Q121))</f>
         <v>0.69306911979142294</v>
       </c>
-      <c r="G10" s="182" t="str">
+      <c r="G10" s="180" t="str">
         <f>IF(Statement!H121&lt;=0,"N/A",_xlfn.RRI(9,Statement!H121,Statement!Q121))</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B11" s="20" t="s">
-        <v>260</v>
-      </c>
-      <c r="C11" s="178">
+        <v>258</v>
+      </c>
+      <c r="C11" s="176">
         <f ca="1">Statement!AC166</f>
         <v>19.380780777226803</v>
       </c>
@@ -31097,7 +31111,7 @@
       <c r="B12" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="C12" s="178">
+      <c r="C12" s="176">
         <f ca="1">Statement!AC167</f>
         <v>30.272998120590319</v>
       </c>
@@ -31108,7 +31122,7 @@
       </c>
       <c r="C15" s="231"/>
       <c r="E15" s="231" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F15" s="231"/>
     </row>
@@ -31116,14 +31130,14 @@
       <c r="B16" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="C16" s="179">
+      <c r="C16" s="177">
         <f>Statement!AC98</f>
         <v>0.74145433171197395</v>
       </c>
       <c r="E16" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="177">
+      <c r="F16" s="175">
         <f>Statement!AC17</f>
         <v>159613</v>
       </c>
@@ -31132,14 +31146,14 @@
       <c r="B17" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="C17" s="179">
+      <c r="C17" s="177">
         <f>Statement!AC99</f>
         <v>0.64020024379563767</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>247</v>
-      </c>
-      <c r="F17" s="177">
+        <v>245</v>
+      </c>
+      <c r="F17" s="175">
         <f>Statement!AC57</f>
         <v>125649</v>
       </c>
@@ -31148,25 +31162,25 @@
       <c r="B18" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="C18" s="179">
+      <c r="C18" s="177">
         <f>Statement!AC100</f>
         <v>0.62965943564071303</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>254</v>
-      </c>
-      <c r="F18" s="181">
+        <v>252</v>
+      </c>
+      <c r="F18" s="179">
         <f>IF(OR(F16&lt;=0, F17&lt;=0),"N/A",F16-F17)</f>
         <v>33964</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B21" s="231" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C21" s="231"/>
       <c r="E21" s="231" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F21" s="231"/>
     </row>
@@ -31174,14 +31188,14 @@
       <c r="B22" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="C22" s="179">
+      <c r="C22" s="177">
         <f>Statement!AC125</f>
         <v>0.62965943564071303</v>
       </c>
       <c r="E22" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="F22" s="179">
+      <c r="F22" s="177">
         <f>C24</f>
         <v>0.61514063066049007</v>
       </c>
@@ -31190,14 +31204,14 @@
       <c r="B23" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="C23" s="178">
+      <c r="C23" s="176">
         <f>Statement!AC126</f>
         <v>0.97694181305256023</v>
       </c>
       <c r="E23" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="F23" s="179">
+      <c r="F23" s="177">
         <f>C26</f>
         <v>0.81654337661274645</v>
       </c>
@@ -31206,14 +31220,14 @@
       <c r="B24" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="C24" s="180">
+      <c r="C24" s="178">
         <f>Statement!AC127</f>
         <v>0.61514063066049007</v>
       </c>
       <c r="E24" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="F24" s="179">
+      <c r="F24" s="177">
         <f>Statement!AC151</f>
         <v>1.1082908941558067</v>
       </c>
@@ -31222,7 +31236,7 @@
       <c r="B25" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="C25" s="178">
+      <c r="C25" s="176">
         <f>Statement!AC128</f>
         <v>1.3274092718213164</v>
       </c>
@@ -31231,18 +31245,18 @@
       <c r="B26" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="C26" s="180">
+      <c r="C26" s="178">
         <f>Statement!AC129</f>
         <v>0.81654337661274645</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B29" s="231" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C29" s="231"/>
       <c r="E29" s="231" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F29" s="231"/>
     </row>
@@ -31250,14 +31264,14 @@
       <c r="B30" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="C30" s="178">
+      <c r="C30" s="176">
         <f>Statement!AC152</f>
         <v>58.61805744582648</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>257</v>
-      </c>
-      <c r="F30" s="184">
+        <v>255</v>
+      </c>
+      <c r="F30" s="182">
         <f>Statement!AC156</f>
         <v>4.3330570817602339E-2</v>
       </c>
@@ -31266,14 +31280,14 @@
       <c r="B31" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="C31" s="178">
+      <c r="C31" s="176">
         <f>Statement!AC153</f>
         <v>143.6687315949282</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>258</v>
-      </c>
-      <c r="F31" s="184">
+        <v>256</v>
+      </c>
+      <c r="F31" s="182">
         <f>Statement!AC157</f>
         <v>-0.36885723932594616</v>
       </c>
@@ -31282,14 +31296,14 @@
       <c r="B32" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="C32" s="178">
+      <c r="C32" s="176">
         <f>Statement!AC154</f>
         <v>72.939852606844781</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>253</v>
-      </c>
-      <c r="F32" s="184">
+        <v>251</v>
+      </c>
+      <c r="F32" s="182">
         <f>Statement!AC159</f>
         <v>3.440775681341719</v>
       </c>
@@ -31298,194 +31312,194 @@
       <c r="B33" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="C33" s="178">
+      <c r="C33" s="176">
         <f>Statement!AC155</f>
         <v>129.34693643390989</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>252</v>
-      </c>
-      <c r="F33" s="184">
+        <v>250</v>
+      </c>
+      <c r="F33" s="182">
         <f>Statement!AC158</f>
         <v>2.7636951964269438</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E34" s="20" t="s">
-        <v>259</v>
-      </c>
-      <c r="F34" s="186" t="str">
+        <v>257</v>
+      </c>
+      <c r="F34" s="184" t="str">
         <f>Statement!AC160</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B37" s="231" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C37" s="231"/>
       <c r="E37" s="231" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F37" s="231"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
-        <v>266</v>
-      </c>
-      <c r="C38" s="179">
+        <v>264</v>
+      </c>
+      <c r="C38" s="177">
         <f ca="1">Statement!AC173</f>
         <v>3.1838127742564601E-2</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>270</v>
-      </c>
-      <c r="F38" s="179">
+        <v>268</v>
+      </c>
+      <c r="F38" s="177">
         <f>Statement!AC179</f>
         <v>8.6691554478469674E-3</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B39" s="54" t="s">
-        <v>269</v>
-      </c>
-      <c r="C39" s="219">
+        <v>267</v>
+      </c>
+      <c r="C39" s="217">
         <f ca="1">Statement!AC172</f>
         <v>2.2515145822264611E-2</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>272</v>
-      </c>
-      <c r="F39" s="179">
+        <v>270</v>
+      </c>
+      <c r="F39" s="177">
         <f>Statement!AC180</f>
         <v>0.40364585653572349</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B40" s="20" t="s">
-        <v>267</v>
-      </c>
-      <c r="C40" s="179">
+        <v>265</v>
+      </c>
+      <c r="C40" s="177">
         <f ca="1">Statement!AC174</f>
         <v>1.9502681618722574E-4</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>273</v>
-      </c>
-      <c r="F40" s="179">
+        <v>271</v>
+      </c>
+      <c r="F40" s="177">
         <f>Statement!AC181</f>
         <v>0.41231501198357046</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B41" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="C41" s="179">
+        <v>290</v>
+      </c>
+      <c r="C41" s="177">
         <f ca="1">Statement!AC175</f>
         <v>9.0881453204547154E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B42" s="20" t="s">
-        <v>294</v>
-      </c>
-      <c r="C42" s="179">
+        <v>292</v>
+      </c>
+      <c r="C42" s="177">
         <f ca="1">Statement!AC176</f>
         <v>9.2833326195188703E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B45" s="231" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C45" s="231"/>
       <c r="E45" s="231" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F45" s="231"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
-        <v>277</v>
-      </c>
-      <c r="C46" s="179">
+        <v>275</v>
+      </c>
+      <c r="C46" s="177">
         <f>Statement!AC182</f>
         <v>3.9374614276897757E-2</v>
       </c>
       <c r="E46" s="20" t="s">
-        <v>278</v>
-      </c>
-      <c r="F46" s="178">
+        <v>276</v>
+      </c>
+      <c r="F46" s="176">
         <f>Statement!AC183</f>
         <v>3.3294214876033057</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E47" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="F47" s="178">
+        <v>284</v>
+      </c>
+      <c r="F47" s="176">
         <f>Statement!AC186</f>
         <v>2.9794214876033056</v>
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E48" s="20" t="s">
-        <v>291</v>
-      </c>
-      <c r="F48" s="179">
+        <v>289</v>
+      </c>
+      <c r="F48" s="177">
         <f ca="1">Statement!AC187</f>
         <v>1.4463920490363455E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B51" s="231" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C51" s="231"/>
       <c r="E51" s="231" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F51" s="231"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="C52" s="179">
+        <v>278</v>
+      </c>
+      <c r="C52" s="177">
         <f>Statement!AC184</f>
         <v>5.4437361220542942E-2</v>
       </c>
       <c r="E52" s="20" t="s">
-        <v>304</v>
-      </c>
-      <c r="F52" s="179">
+        <v>302</v>
+      </c>
+      <c r="F52" s="177">
         <f>Statement!AC188</f>
         <v>2.5925969758295166E-2</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B53" s="20" t="s">
-        <v>281</v>
-      </c>
-      <c r="C53" s="179">
+        <v>279</v>
+      </c>
+      <c r="C53" s="177">
         <f>Statement!AC185</f>
         <v>2.6983206504372935E-2</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>301</v>
-      </c>
-      <c r="F53" s="179">
+        <v>299</v>
+      </c>
+      <c r="F53" s="177">
         <f>Statement!AC189</f>
         <v>5.2304435371550904E-2</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E54" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="F54" s="179">
+        <v>300</v>
+      </c>
+      <c r="F54" s="177">
         <f>Statement!AC190</f>
         <v>2.0359355638166048</v>
       </c>
@@ -31581,7 +31595,7 @@
     </row>
     <row r="5" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
@@ -31594,56 +31608,56 @@
       <c r="B6" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="176">
+      <c r="C6" s="174">
         <f>Statement!M120</f>
         <v>228.4</v>
       </c>
-      <c r="D6" s="176">
+      <c r="D6" s="174">
         <f>Statement!N120</f>
         <v>203.6</v>
       </c>
-      <c r="E6" s="176">
+      <c r="E6" s="174">
         <f>Statement!O120</f>
         <v>610.29999999999995</v>
       </c>
-      <c r="F6" s="176">
+      <c r="F6" s="174">
         <f>Statement!P120</f>
         <v>142.62</v>
       </c>
-      <c r="G6" s="176">
+      <c r="G6" s="174">
         <f>Statement!Q120</f>
         <v>187.67</v>
       </c>
-      <c r="I6" s="176">
+      <c r="I6" s="174">
         <f ca="1">Statement!AC120</f>
         <v>205.1</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B7" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="C7" s="177">
+        <v>237</v>
+      </c>
+      <c r="C7" s="175">
         <f>Statement!M164</f>
         <v>582191.6</v>
       </c>
-      <c r="D7" s="177">
+      <c r="D7" s="175">
         <f>Statement!N164</f>
         <v>506964</v>
       </c>
-      <c r="E7" s="177">
+      <c r="E7" s="175">
         <f>Statement!O164</f>
         <v>1541007.4999999998</v>
       </c>
-      <c r="F7" s="177">
+      <c r="F7" s="175">
         <f>Statement!P164</f>
         <v>3515440.38</v>
       </c>
-      <c r="G7" s="177">
+      <c r="G7" s="175">
         <f>Statement!Q164</f>
         <v>4589469.8499999996</v>
       </c>
-      <c r="I7" s="177">
+      <c r="I7" s="175">
         <f ca="1">Statement!AC164</f>
         <v>4984955.5</v>
       </c>
@@ -31652,56 +31666,56 @@
       <c r="B8" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="C8" s="177">
+      <c r="C8" s="175">
         <f>Statement!M165</f>
         <v>571929.59999999998</v>
       </c>
-      <c r="D8" s="177">
+      <c r="D8" s="175">
         <f>Statement!N165</f>
         <v>504621</v>
       </c>
-      <c r="E8" s="177">
+      <c r="E8" s="175">
         <f>Statement!O165</f>
         <v>1524732.4999999998</v>
       </c>
-      <c r="F8" s="177">
+      <c r="F8" s="175">
         <f>Statement!P165</f>
         <v>3480693.38</v>
       </c>
-      <c r="G8" s="177">
+      <c r="G8" s="175">
         <f>Statement!Q165</f>
         <v>4535381.8499999996</v>
       </c>
-      <c r="I8" s="177">
+      <c r="I8" s="175">
         <f ca="1">Statement!AC165</f>
         <v>4912853.5</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B9" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="C9" s="178">
+        <v>235</v>
+      </c>
+      <c r="C9" s="176">
         <f>Statement!M161</f>
         <v>59.324675324675326</v>
       </c>
-      <c r="D9" s="178">
+      <c r="D9" s="176">
         <f>Statement!N161</f>
         <v>117.01149425287356</v>
       </c>
-      <c r="E9" s="178">
+      <c r="E9" s="176">
         <f>Statement!O161</f>
         <v>51.156747694886832</v>
       </c>
-      <c r="F9" s="178">
+      <c r="F9" s="176">
         <f>Statement!P161</f>
         <v>48.510204081632658</v>
       </c>
-      <c r="G9" s="178">
+      <c r="G9" s="176">
         <f>Statement!Q161</f>
         <v>38.299999999999997</v>
       </c>
-      <c r="I9" s="178">
+      <c r="I9" s="176">
         <f ca="1">Statement!AC161</f>
         <v>31.408882082695254</v>
       </c>
@@ -31710,85 +31724,85 @@
       <c r="B10" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="C10" s="178">
+      <c r="C10" s="176">
         <f>Statement!M162</f>
         <v>21.512744296648584</v>
       </c>
-      <c r="D10" s="178">
+      <c r="D10" s="176">
         <f>Statement!N162</f>
         <v>18.922859049455031</v>
       </c>
-      <c r="E10" s="178">
+      <c r="E10" s="176">
         <f>Statement!O162</f>
         <v>24.984212599717669</v>
       </c>
-      <c r="F10" s="178">
+      <c r="F10" s="176">
         <f>Statement!P162</f>
         <v>27.108259040437712</v>
       </c>
-      <c r="G10" s="178">
+      <c r="G10" s="176">
         <f>Statement!Q162</f>
         <v>21.304922616677011</v>
       </c>
-      <c r="I10" s="178">
+      <c r="I10" s="176">
         <f ca="1">Statement!AC162</f>
         <v>19.790223124292382</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B11" s="20" t="s">
-        <v>238</v>
-      </c>
-      <c r="C11" s="178">
+        <v>236</v>
+      </c>
+      <c r="C11" s="176">
         <f>Statement!M163</f>
         <v>21.542311739065084</v>
       </c>
-      <c r="D11" s="178">
+      <c r="D11" s="176">
         <f>Statement!N163</f>
         <v>22.754264512917967</v>
       </c>
-      <c r="E11" s="178">
+      <c r="E11" s="176">
         <f>Statement!O163</f>
         <v>35.500721299269394</v>
       </c>
-      <c r="F11" s="178">
+      <c r="F11" s="176">
         <f>Statement!P163</f>
         <v>43.868140733924143</v>
       </c>
-      <c r="G11" s="178">
+      <c r="G11" s="176">
         <f>Statement!Q163</f>
         <v>28.992904960805632</v>
       </c>
-      <c r="I11" s="178">
+      <c r="I11" s="176">
         <f ca="1">Statement!AC163</f>
         <v>25.391714499114975</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B12" s="20" t="s">
-        <v>260</v>
-      </c>
-      <c r="C12" s="178">
+        <v>258</v>
+      </c>
+      <c r="C12" s="176">
         <f>Statement!M166</f>
         <v>21.250263803225085</v>
       </c>
-      <c r="D12" s="178">
+      <c r="D12" s="176">
         <f>Statement!N166</f>
         <v>18.707681471046193</v>
       </c>
-      <c r="E12" s="178">
+      <c r="E12" s="176">
         <f>Statement!O166</f>
         <v>25.02761728111355</v>
       </c>
-      <c r="F12" s="178">
+      <c r="F12" s="176">
         <f>Statement!P166</f>
         <v>26.672593086431103</v>
       </c>
-      <c r="G12" s="178">
+      <c r="G12" s="176">
         <f>Statement!Q166</f>
         <v>21.003166881234428</v>
       </c>
-      <c r="I12" s="178">
+      <c r="I12" s="176">
         <f ca="1">Statement!AC166</f>
         <v>19.380780777226803</v>
       </c>
@@ -31797,27 +31811,27 @@
       <c r="B13" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="C13" s="178">
+      <c r="C13" s="176">
         <f>Statement!M167</f>
         <v>56.959426351956971</v>
       </c>
-      <c r="D13" s="178">
+      <c r="D13" s="176">
         <f>Statement!N167</f>
         <v>119.46519886363636</v>
       </c>
-      <c r="E13" s="178">
+      <c r="E13" s="176">
         <f>Statement!O167</f>
         <v>46.243251850054584</v>
       </c>
-      <c r="F13" s="178">
+      <c r="F13" s="176">
         <f>Statement!P167</f>
         <v>42.732537536984516</v>
       </c>
-      <c r="G13" s="178">
+      <c r="G13" s="176">
         <f>Statement!Q167</f>
         <v>34.784003389908499</v>
       </c>
-      <c r="I13" s="178">
+      <c r="I13" s="176">
         <f ca="1">Statement!AC167</f>
         <v>30.272998120590319</v>
       </c>
@@ -31837,27 +31851,27 @@
       <c r="B16" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="C16" s="179">
+      <c r="C16" s="177">
         <f>Statement!M98</f>
         <v>0.64929033216913135</v>
       </c>
-      <c r="D16" s="179">
+      <c r="D16" s="177">
         <f>Statement!N98</f>
         <v>0.56928894490991322</v>
       </c>
-      <c r="E16" s="179">
+      <c r="E16" s="177">
         <f>Statement!O98</f>
         <v>0.72717573290436954</v>
       </c>
-      <c r="F16" s="179">
+      <c r="F16" s="177">
         <f>Statement!P98</f>
         <v>0.74988697058169917</v>
       </c>
-      <c r="G16" s="179">
+      <c r="G16" s="177">
         <f>Statement!Q98</f>
         <v>0.71068084357547079</v>
       </c>
-      <c r="I16" s="179">
+      <c r="I16" s="177">
         <f>Statement!AC98</f>
         <v>0.74145433171197395</v>
       </c>
@@ -31866,27 +31880,27 @@
       <c r="B17" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="C17" s="179">
+      <c r="C17" s="177">
         <f>Statement!M99</f>
         <v>0.37307720888756779</v>
       </c>
-      <c r="D17" s="179">
+      <c r="D17" s="177">
         <f>Statement!N99</f>
         <v>0.1565952398606065</v>
       </c>
-      <c r="E17" s="179">
+      <c r="E17" s="177">
         <f>Statement!O99</f>
         <v>0.54121663766783756</v>
       </c>
-      <c r="F17" s="179">
+      <c r="F17" s="177">
         <f>Statement!P99</f>
         <v>0.62417526839697468</v>
       </c>
-      <c r="G17" s="179">
+      <c r="G17" s="177">
         <f>Statement!Q99</f>
         <v>0.60381683631412719</v>
       </c>
-      <c r="I17" s="179">
+      <c r="I17" s="177">
         <f>Statement!AC99</f>
         <v>0.64020024379563767</v>
       </c>
@@ -31895,34 +31909,34 @@
       <c r="B18" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="C18" s="179">
+      <c r="C18" s="177">
         <f>Statement!M100</f>
         <v>0.36233930296499961</v>
       </c>
-      <c r="D18" s="179">
+      <c r="D18" s="177">
         <f>Statement!N100</f>
         <v>0.16193371394676356</v>
       </c>
-      <c r="E18" s="179">
+      <c r="E18" s="177">
         <f>Statement!O100</f>
         <v>0.4884934834706674</v>
       </c>
-      <c r="F18" s="179">
+      <c r="F18" s="177">
         <f>Statement!P100</f>
         <v>0.55848027157712443</v>
       </c>
-      <c r="G18" s="179">
+      <c r="G18" s="177">
         <f>Statement!Q100</f>
         <v>0.55602534060702613</v>
       </c>
-      <c r="I18" s="179">
+      <c r="I18" s="177">
         <f>Statement!AC100</f>
         <v>0.62965943564071303</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B20" s="14" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
@@ -31935,92 +31949,92 @@
       <c r="B21" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="181">
+      <c r="C21" s="179">
         <f>Statement!M17</f>
         <v>9752</v>
       </c>
-      <c r="D21" s="181">
+      <c r="D21" s="179">
         <f>Statement!N17</f>
         <v>4368</v>
       </c>
-      <c r="E21" s="181">
+      <c r="E21" s="179">
         <f>Statement!O17</f>
         <v>29760</v>
       </c>
-      <c r="F21" s="181">
+      <c r="F21" s="179">
         <f>Statement!P17</f>
         <v>72880</v>
       </c>
-      <c r="G21" s="181">
+      <c r="G21" s="179">
         <f>Statement!Q17</f>
         <v>120067</v>
       </c>
-      <c r="I21" s="181">
+      <c r="I21" s="179">
         <f>Statement!AC17</f>
         <v>159613</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
-        <v>247</v>
-      </c>
-      <c r="C22" s="181">
+        <v>245</v>
+      </c>
+      <c r="C22" s="179">
         <f>Statement!M57</f>
         <v>9108</v>
       </c>
-      <c r="D22" s="181">
+      <c r="D22" s="179">
         <f>Statement!N57</f>
         <v>5641</v>
       </c>
-      <c r="E22" s="181">
+      <c r="E22" s="179">
         <f>Statement!O57</f>
         <v>28090</v>
       </c>
-      <c r="F22" s="181">
+      <c r="F22" s="179">
         <f>Statement!P57</f>
         <v>64089</v>
       </c>
-      <c r="G22" s="181">
+      <c r="G22" s="179">
         <f>Statement!Q57</f>
         <v>102718</v>
       </c>
-      <c r="I22" s="181">
+      <c r="I22" s="179">
         <f>Statement!AC57</f>
         <v>125649</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B23" s="20" t="s">
-        <v>254</v>
-      </c>
-      <c r="C23" s="199">
+        <v>252</v>
+      </c>
+      <c r="C23" s="197">
         <f>IF(OR(C21&lt;=0, C22&lt;=0),"N/A",C21-C22)</f>
         <v>644</v>
       </c>
-      <c r="D23" s="199">
+      <c r="D23" s="197">
         <f t="shared" ref="D23:I23" si="0">IF(OR(D21&lt;=0, D22&lt;=0),"N/A",D21-D22)</f>
         <v>-1273</v>
       </c>
-      <c r="E23" s="199">
+      <c r="E23" s="197">
         <f t="shared" si="0"/>
         <v>1670</v>
       </c>
-      <c r="F23" s="199">
+      <c r="F23" s="197">
         <f t="shared" si="0"/>
         <v>8791</v>
       </c>
-      <c r="G23" s="199">
+      <c r="G23" s="197">
         <f t="shared" si="0"/>
         <v>17349</v>
       </c>
-      <c r="I23" s="199">
+      <c r="I23" s="197">
         <f t="shared" si="0"/>
         <v>33964</v>
       </c>
     </row>
     <row r="25" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B25" s="14" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="14"/>
@@ -32033,27 +32047,27 @@
       <c r="B26" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="C26" s="179">
+      <c r="C26" s="177">
         <f>Statement!M125</f>
         <v>0.36233930296499961</v>
       </c>
-      <c r="D26" s="179">
+      <c r="D26" s="177">
         <f>Statement!N125</f>
         <v>0.16193371394676356</v>
       </c>
-      <c r="E26" s="179">
+      <c r="E26" s="177">
         <f>Statement!O125</f>
         <v>0.4884934834706674</v>
       </c>
-      <c r="F26" s="179">
+      <c r="F26" s="177">
         <f>Statement!P125</f>
         <v>0.55848027157712443</v>
       </c>
-      <c r="G26" s="179">
+      <c r="G26" s="177">
         <f>Statement!Q125</f>
         <v>0.55602534060702613</v>
       </c>
-      <c r="I26" s="179">
+      <c r="I26" s="177">
         <f>Statement!AC125</f>
         <v>0.62965943564071303</v>
       </c>
@@ -32062,27 +32076,27 @@
       <c r="B27" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="C27" s="218">
+      <c r="C27" s="216">
         <f>Statement!M126</f>
         <v>0.60909317219996828</v>
       </c>
-      <c r="D27" s="218">
+      <c r="D27" s="216">
         <f>Statement!N126</f>
         <v>0.65499490068476518</v>
       </c>
-      <c r="E27" s="218">
+      <c r="E27" s="216">
         <f>Statement!O126</f>
         <v>0.92688047711781885</v>
       </c>
-      <c r="F27" s="218">
+      <c r="F27" s="216">
         <f>Statement!P126</f>
         <v>1.169317479234057</v>
       </c>
-      <c r="G27" s="218">
+      <c r="G27" s="216">
         <f>Statement!Q126</f>
         <v>1.0441724733200195</v>
       </c>
-      <c r="I27" s="218">
+      <c r="I27" s="216">
         <f>Statement!AC126</f>
         <v>0.97694181305256023</v>
       </c>
@@ -32091,27 +32105,27 @@
       <c r="B28" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="C28" s="180">
+      <c r="C28" s="178">
         <f>Statement!M127</f>
         <v>0.22069839545567699</v>
       </c>
-      <c r="D28" s="180">
+      <c r="D28" s="178">
         <f>Statement!N127</f>
         <v>0.10606575688407557</v>
       </c>
-      <c r="E28" s="180">
+      <c r="E28" s="178">
         <f>Statement!O127</f>
         <v>0.45277507302823755</v>
       </c>
-      <c r="F28" s="180">
+      <c r="F28" s="178">
         <f>Statement!P127</f>
         <v>0.65304074336251472</v>
       </c>
-      <c r="G28" s="180">
+      <c r="G28" s="178">
         <f>Statement!Q127</f>
         <v>0.5805863551302447</v>
       </c>
-      <c r="I28" s="180">
+      <c r="I28" s="178">
         <f>Statement!AC127</f>
         <v>0.61514063066049007</v>
       </c>
@@ -32120,27 +32134,27 @@
       <c r="B29" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="C29" s="218">
+      <c r="C29" s="216">
         <f>Statement!M128</f>
         <v>1.6604163535247256</v>
       </c>
-      <c r="D29" s="218">
+      <c r="D29" s="216">
         <f>Statement!N128</f>
         <v>1.8633545993393965</v>
       </c>
-      <c r="E29" s="218">
+      <c r="E29" s="216">
         <f>Statement!O128</f>
         <v>1.5293405928614641</v>
       </c>
-      <c r="F29" s="218">
+      <c r="F29" s="216">
         <f>Statement!P128</f>
         <v>1.4068476054811099</v>
       </c>
-      <c r="G29" s="218">
+      <c r="G29" s="216">
         <f>Statement!Q128</f>
         <v>1.3147628947251309</v>
       </c>
-      <c r="I29" s="218">
+      <c r="I29" s="216">
         <f>Statement!AC128</f>
         <v>1.3274092718213164</v>
       </c>
@@ -32149,34 +32163,34 @@
       <c r="B30" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="C30" s="180">
+      <c r="C30" s="178">
         <f>Statement!M129</f>
         <v>0.36645122501127303</v>
       </c>
-      <c r="D30" s="180">
+      <c r="D30" s="178">
         <f>Statement!N129</f>
         <v>0.19763811592235647</v>
       </c>
-      <c r="E30" s="180">
+      <c r="E30" s="178">
         <f>Statement!O129</f>
         <v>0.69244729861789756</v>
       </c>
-      <c r="F30" s="180">
+      <c r="F30" s="178">
         <f>Statement!P129</f>
         <v>0.91872880608115781</v>
       </c>
-      <c r="G30" s="180">
+      <c r="G30" s="178">
         <f>Statement!Q129</f>
         <v>0.76333339690895341</v>
       </c>
-      <c r="I30" s="180">
+      <c r="I30" s="178">
         <f>Statement!AC129</f>
         <v>0.81654337661274645</v>
       </c>
     </row>
     <row r="32" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B32" s="14" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
@@ -32189,27 +32203,27 @@
       <c r="B33" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="C33" s="179">
+      <c r="C33" s="177">
         <f>C28</f>
         <v>0.22069839545567699</v>
       </c>
-      <c r="D33" s="179">
+      <c r="D33" s="177">
         <f t="shared" ref="D33:G33" si="1">D28</f>
         <v>0.10606575688407557</v>
       </c>
-      <c r="E33" s="179">
+      <c r="E33" s="177">
         <f t="shared" si="1"/>
         <v>0.45277507302823755</v>
       </c>
-      <c r="F33" s="179">
+      <c r="F33" s="177">
         <f t="shared" si="1"/>
         <v>0.65304074336251472</v>
       </c>
-      <c r="G33" s="179">
+      <c r="G33" s="177">
         <f t="shared" si="1"/>
         <v>0.5805863551302447</v>
       </c>
-      <c r="I33" s="179">
+      <c r="I33" s="177">
         <f>I28</f>
         <v>0.61514063066049007</v>
       </c>
@@ -32218,27 +32232,27 @@
       <c r="B34" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="C34" s="179">
+      <c r="C34" s="177">
         <f>C30</f>
         <v>0.36645122501127303</v>
       </c>
-      <c r="D34" s="179">
+      <c r="D34" s="177">
         <f t="shared" ref="D34:G34" si="2">D30</f>
         <v>0.19763811592235647</v>
       </c>
-      <c r="E34" s="179">
+      <c r="E34" s="177">
         <f t="shared" si="2"/>
         <v>0.69244729861789756</v>
       </c>
-      <c r="F34" s="179">
+      <c r="F34" s="177">
         <f t="shared" si="2"/>
         <v>0.91872880608115781</v>
       </c>
-      <c r="G34" s="179">
+      <c r="G34" s="177">
         <f t="shared" si="2"/>
         <v>0.76333339690895341</v>
       </c>
-      <c r="I34" s="179">
+      <c r="I34" s="177">
         <f>I30</f>
         <v>0.81654337661274645</v>
       </c>
@@ -32247,34 +32261,34 @@
       <c r="B35" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="C35" s="179">
+      <c r="C35" s="177">
         <f>Statement!M151</f>
         <v>0.60245252494303547</v>
       </c>
-      <c r="D35" s="179">
+      <c r="D35" s="177">
         <f>Statement!N151</f>
         <v>0.21378682052839357</v>
       </c>
-      <c r="E35" s="179">
+      <c r="E35" s="177">
         <f>Statement!O151</f>
         <v>1.0866013555554745</v>
       </c>
-      <c r="F35" s="179">
+      <c r="F35" s="177">
         <f>Statement!P151</f>
         <v>1.5847534085376831</v>
       </c>
-      <c r="G35" s="179">
+      <c r="G35" s="177">
         <f>Statement!Q151</f>
         <v>1.0723937210768841</v>
       </c>
-      <c r="I35" s="179">
+      <c r="I35" s="177">
         <f>Statement!AC151</f>
         <v>1.1082908941558067</v>
       </c>
     </row>
     <row r="37" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B37" s="14" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C37" s="14"/>
       <c r="D37" s="14"/>
@@ -32287,27 +32301,27 @@
       <c r="B38" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="C38" s="178">
+      <c r="C38" s="176">
         <f>Statement!M152</f>
         <v>63.061975180203611</v>
       </c>
-      <c r="D38" s="178">
+      <c r="D38" s="176">
         <f>Statement!N152</f>
         <v>51.785237636242307</v>
       </c>
-      <c r="E38" s="178">
+      <c r="E38" s="176">
         <f>Statement!O152</f>
         <v>59.906683956534586</v>
       </c>
-      <c r="F38" s="178">
+      <c r="F38" s="176">
         <f>Statement!P152</f>
         <v>64.512785734537957</v>
       </c>
-      <c r="G38" s="178">
+      <c r="G38" s="176">
         <f>Statement!Q152</f>
         <v>65.01907955061175</v>
       </c>
-      <c r="I38" s="178">
+      <c r="I38" s="176">
         <f>Statement!AC152</f>
         <v>58.61805744582648</v>
       </c>
@@ -32316,27 +32330,27 @@
       <c r="B39" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="C39" s="178">
+      <c r="C39" s="176">
         <f>Statement!M153</f>
         <v>100.73365822650703</v>
       </c>
-      <c r="D39" s="178">
+      <c r="D39" s="176">
         <f>Statement!N153</f>
         <v>162.079101394388</v>
       </c>
-      <c r="E39" s="178">
+      <c r="E39" s="176">
         <f>Statement!O153</f>
         <v>115.99362252572048</v>
       </c>
-      <c r="F39" s="178">
+      <c r="F39" s="176">
         <f>Statement!P153</f>
         <v>112.72404179049603</v>
       </c>
-      <c r="G39" s="178">
+      <c r="G39" s="176">
         <f>Statement!Q153</f>
         <v>125.043537414966</v>
       </c>
-      <c r="I39" s="178">
+      <c r="I39" s="176">
         <f>Statement!AC153</f>
         <v>143.6687315949282</v>
       </c>
@@ -32345,27 +32359,27 @@
       <c r="B40" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="C40" s="178">
+      <c r="C40" s="176">
         <f>Statement!M154</f>
         <v>68.947452060599645</v>
       </c>
-      <c r="D40" s="178">
+      <c r="D40" s="176">
         <f>Statement!N154</f>
         <v>37.480203133069374</v>
       </c>
-      <c r="E40" s="178">
+      <c r="E40" s="176">
         <f>Statement!O154</f>
         <v>59.270501173214605</v>
       </c>
-      <c r="F40" s="178">
+      <c r="F40" s="176">
         <f>Statement!P154</f>
         <v>70.564355525598216</v>
       </c>
-      <c r="G40" s="178">
+      <c r="G40" s="176">
         <f>Statement!Q154</f>
         <v>57.325010004001605</v>
       </c>
-      <c r="I40" s="178">
+      <c r="I40" s="176">
         <f>Statement!AC154</f>
         <v>72.939852606844781</v>
       </c>
@@ -32374,34 +32388,34 @@
       <c r="B41" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="C41" s="178">
+      <c r="C41" s="176">
         <f>Statement!M155</f>
         <v>94.848181346110991</v>
       </c>
-      <c r="D41" s="178">
+      <c r="D41" s="176">
         <f>Statement!N155</f>
         <v>176.38413589756092</v>
       </c>
-      <c r="E41" s="178">
+      <c r="E41" s="176">
         <f>Statement!O155</f>
         <v>116.62980530904048</v>
       </c>
-      <c r="F41" s="178">
+      <c r="F41" s="176">
         <f>Statement!P155</f>
         <v>106.67247199943577</v>
       </c>
-      <c r="G41" s="178">
+      <c r="G41" s="176">
         <f>Statement!Q155</f>
         <v>132.73760696157615</v>
       </c>
-      <c r="I41" s="178">
+      <c r="I41" s="176">
         <f>Statement!AC155</f>
         <v>129.34693643390989</v>
       </c>
     </row>
     <row r="43" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B43" s="14" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C43" s="14"/>
       <c r="D43" s="14"/>
@@ -32412,152 +32426,152 @@
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B44" s="20" t="s">
-        <v>257</v>
-      </c>
-      <c r="C44" s="184">
+        <v>255</v>
+      </c>
+      <c r="C44" s="182">
         <f>Statement!M156</f>
         <v>0.41131820231474525</v>
       </c>
-      <c r="D44" s="184">
+      <c r="D44" s="182">
         <f>Statement!N156</f>
         <v>0.49558843491244742</v>
       </c>
-      <c r="E44" s="184">
+      <c r="E44" s="182">
         <f>Statement!O156</f>
         <v>0.22590627763041557</v>
       </c>
-      <c r="F44" s="184">
+      <c r="F44" s="182">
         <f>Statement!P156</f>
         <v>0.10668498745698186</v>
       </c>
-      <c r="G44" s="184">
+      <c r="G44" s="182">
         <f>Statement!Q156</f>
         <v>5.3835835033981171E-2</v>
       </c>
-      <c r="I44" s="184">
+      <c r="I44" s="182">
         <f>Statement!AC156</f>
         <v>4.3330570817602339E-2</v>
       </c>
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B45" s="20" t="s">
-        <v>258</v>
-      </c>
-      <c r="C45" s="184">
+        <v>256</v>
+      </c>
+      <c r="C45" s="182">
         <f>Statement!M157</f>
         <v>-0.38561551179918835</v>
       </c>
-      <c r="D45" s="184">
+      <c r="D45" s="182">
         <f>Statement!N157</f>
         <v>-0.10601330256549478</v>
       </c>
-      <c r="E45" s="184">
+      <c r="E45" s="182">
         <f>Statement!O157</f>
         <v>-0.37868211643166272</v>
       </c>
-      <c r="F45" s="184">
+      <c r="F45" s="182">
         <f>Statement!P157</f>
         <v>-0.43802236312982967</v>
       </c>
-      <c r="G45" s="184">
+      <c r="G45" s="182">
         <f>Statement!Q157</f>
         <v>-0.34386781357085183</v>
       </c>
-      <c r="I45" s="184">
+      <c r="I45" s="182">
         <f>Statement!AC157</f>
         <v>-0.36885723932594616</v>
       </c>
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
-        <v>252</v>
-      </c>
-      <c r="C46" s="184">
+        <v>250</v>
+      </c>
+      <c r="C46" s="182">
         <f>Statement!M158</f>
         <v>5.9649365628604381</v>
       </c>
-      <c r="D46" s="184">
+      <c r="D46" s="182">
         <f>Statement!N158</f>
         <v>2.6090202651226573</v>
       </c>
-      <c r="E46" s="184">
+      <c r="E46" s="182">
         <f>Statement!O158</f>
         <v>3.3847239206095381</v>
       </c>
-      <c r="F46" s="184">
+      <c r="F46" s="182">
         <f>Statement!P158</f>
         <v>3.672355516152269</v>
       </c>
-      <c r="G46" s="184">
+      <c r="G46" s="182">
         <f>Statement!Q158</f>
         <v>3.1409383453036099</v>
       </c>
-      <c r="I46" s="184">
+      <c r="I46" s="182">
         <f>Statement!AC158</f>
         <v>2.7636951964269438</v>
       </c>
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B47" s="20" t="s">
-        <v>253</v>
-      </c>
-      <c r="C47" s="184">
+        <v>251</v>
+      </c>
+      <c r="C47" s="182">
         <f>Statement!M159</f>
         <v>6.6502883506343711</v>
       </c>
-      <c r="D47" s="184">
+      <c r="D47" s="182">
         <f>Statement!N159</f>
         <v>3.5156178576870332</v>
       </c>
-      <c r="E47" s="184">
+      <c r="E47" s="182">
         <f>Statement!O159</f>
         <v>4.1712915059730973</v>
       </c>
-      <c r="F47" s="184">
+      <c r="F47" s="182">
         <f>Statement!P159</f>
         <v>4.4398514988640772</v>
       </c>
-      <c r="G47" s="184">
+      <c r="G47" s="182">
         <f>Statement!Q159</f>
         <v>3.9052638124553058</v>
       </c>
-      <c r="I47" s="184">
+      <c r="I47" s="182">
         <f>Statement!AC159</f>
         <v>3.440775681341719</v>
       </c>
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B48" s="20" t="s">
-        <v>259</v>
-      </c>
-      <c r="C48" s="186">
+        <v>257</v>
+      </c>
+      <c r="C48" s="184">
         <f>Statement!M160</f>
         <v>48.507246376811594</v>
       </c>
-      <c r="D48" s="186" t="str">
+      <c r="D48" s="184" t="str">
         <f>Statement!N160</f>
         <v>N/A</v>
       </c>
-      <c r="E48" s="186" t="str">
+      <c r="E48" s="184" t="str">
         <f>Statement!O160</f>
         <v>N/A</v>
       </c>
-      <c r="F48" s="186" t="str">
+      <c r="F48" s="184" t="str">
         <f>Statement!P160</f>
         <v>N/A</v>
       </c>
-      <c r="G48" s="186" t="str">
+      <c r="G48" s="184" t="str">
         <f>Statement!Q160</f>
         <v>N/A</v>
       </c>
-      <c r="I48" s="186" t="str">
+      <c r="I48" s="184" t="str">
         <f>Statement!AC160</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="50" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B50" s="14" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C50" s="14"/>
       <c r="D50" s="14"/>
@@ -32568,152 +32582,152 @@
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B51" s="20" t="s">
-        <v>266</v>
-      </c>
-      <c r="C51" s="179">
+        <v>264</v>
+      </c>
+      <c r="C51" s="177">
         <f>Statement!M173</f>
         <v>1.6856392294220666E-2</v>
       </c>
-      <c r="D51" s="179">
+      <c r="D51" s="177">
         <f>Statement!N173</f>
         <v>8.546168958742632E-3</v>
       </c>
-      <c r="E51" s="179">
+      <c r="E51" s="177">
         <f>Statement!O173</f>
         <v>1.9547763395051616E-2</v>
       </c>
-      <c r="F51" s="179">
+      <c r="F51" s="177">
         <f>Statement!P173</f>
         <v>2.061421960454354E-2</v>
       </c>
-      <c r="G51" s="179">
+      <c r="G51" s="177">
         <f>Statement!Q173</f>
         <v>2.6109660574412535E-2</v>
       </c>
-      <c r="I51" s="179">
+      <c r="I51" s="177">
         <f ca="1">Statement!AC173</f>
         <v>3.1838127742564601E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
-        <v>269</v>
-      </c>
-      <c r="C52" s="179">
+        <v>267</v>
+      </c>
+      <c r="C52" s="177">
         <f>Statement!M172</f>
         <v>1.0525744445642981E-2</v>
       </c>
-      <c r="D52" s="179">
+      <c r="D52" s="177">
         <f>Statement!N172</f>
         <v>2.1678067870696933E-3</v>
       </c>
-      <c r="E52" s="179">
+      <c r="E52" s="177">
         <f>Statement!O172</f>
         <v>1.5231593616513875E-2</v>
       </c>
-      <c r="F52" s="179">
+      <c r="F52" s="177">
         <f>Statement!P172</f>
         <v>1.5962722712993357E-2</v>
       </c>
-      <c r="G52" s="179">
+      <c r="G52" s="177">
         <f>Statement!Q172</f>
         <v>1.9673296252289359E-2</v>
       </c>
-      <c r="I52" s="179">
+      <c r="I52" s="177">
         <f ca="1">Statement!AC172</f>
         <v>2.2515145822264611E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B53" s="20" t="s">
-        <v>267</v>
-      </c>
-      <c r="C53" s="179">
+        <v>265</v>
+      </c>
+      <c r="C53" s="177">
         <f>Statement!M174</f>
         <v>7.0052539404553418E-4</v>
       </c>
-      <c r="D53" s="179">
+      <c r="D53" s="177">
         <f>Statement!N174</f>
         <v>7.8585461689587434E-4</v>
       </c>
-      <c r="E53" s="179">
+      <c r="E53" s="177">
         <f>Statement!O174</f>
         <v>2.6216614779616586E-4</v>
       </c>
-      <c r="F53" s="179">
+      <c r="F53" s="177">
         <f>Statement!P174</f>
         <v>2.3839573692329268E-4</v>
       </c>
-      <c r="G53" s="179">
+      <c r="G53" s="177">
         <f>Statement!Q174</f>
         <v>2.1314008632173498E-4</v>
       </c>
-      <c r="I53" s="179">
+      <c r="I53" s="177">
         <f ca="1">Statement!AC174</f>
         <v>1.9502681618722574E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B54" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="C54" s="179">
+        <v>290</v>
+      </c>
+      <c r="C54" s="177">
         <f>Statement!M175</f>
         <v>0</v>
       </c>
-      <c r="D54" s="179">
+      <c r="D54" s="177">
         <f>Statement!N175</f>
         <v>1.9802195027654824E-2</v>
       </c>
-      <c r="E54" s="179">
+      <c r="E54" s="177">
         <f>Statement!O175</f>
         <v>6.1862125914377451E-3</v>
       </c>
-      <c r="F54" s="179">
+      <c r="F54" s="177">
         <f>Statement!P175</f>
         <v>9.5879879493220143E-3</v>
       </c>
-      <c r="G54" s="179">
+      <c r="G54" s="177">
         <f>Statement!Q175</f>
         <v>8.7343421593672754E-3</v>
       </c>
-      <c r="I54" s="179">
+      <c r="I54" s="177">
         <f ca="1">Statement!AC175</f>
         <v>9.0881453204547154E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B55" s="20" t="s">
-        <v>294</v>
-      </c>
-      <c r="C55" s="179">
+        <v>292</v>
+      </c>
+      <c r="C55" s="177">
         <f>Statement!M176</f>
         <v>6.853413893295609E-4</v>
       </c>
-      <c r="D55" s="179">
+      <c r="D55" s="177">
         <f>Statement!N176</f>
         <v>2.0587260633891165E-2</v>
       </c>
-      <c r="E55" s="179">
+      <c r="E55" s="177">
         <f>Statement!O176</f>
         <v>6.4425384042582539E-3</v>
       </c>
-      <c r="F55" s="179">
+      <c r="F55" s="177">
         <f>Statement!P176</f>
         <v>9.8252270743957263E-3</v>
       </c>
-      <c r="G55" s="179">
+      <c r="G55" s="177">
         <f>Statement!Q176</f>
         <v>8.946567107309792E-3</v>
       </c>
-      <c r="I55" s="179">
+      <c r="I55" s="177">
         <f ca="1">Statement!AC176</f>
         <v>9.2833326195188703E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B57" s="14" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C57" s="14"/>
       <c r="D57" s="14"/>
@@ -32724,94 +32738,94 @@
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B58" s="20" t="s">
-        <v>270</v>
-      </c>
-      <c r="C58" s="179">
+        <v>268</v>
+      </c>
+      <c r="C58" s="177">
         <f>Statement!M179</f>
         <v>6.5110966057441252E-2</v>
       </c>
-      <c r="D58" s="179">
+      <c r="D58" s="177">
         <f>Statement!N179</f>
         <v>0.36214740673339402</v>
       </c>
-      <c r="E58" s="179">
+      <c r="E58" s="177">
         <f>Statement!O179</f>
         <v>1.6828561690524879E-2</v>
       </c>
-      <c r="F58" s="179">
+      <c r="F58" s="177">
         <f>Statement!P179</f>
         <v>1.4862071423479934E-2</v>
       </c>
-      <c r="G58" s="179">
+      <c r="G58" s="177">
         <f>Statement!Q179</f>
         <v>1.0787462620445233E-2</v>
       </c>
-      <c r="I58" s="179">
+      <c r="I58" s="177">
         <f>Statement!AC179</f>
         <v>8.6691554478469674E-3</v>
       </c>
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B59" s="20" t="s">
-        <v>272</v>
-      </c>
-      <c r="C59" s="179">
+        <v>270</v>
+      </c>
+      <c r="C59" s="177">
         <f>Statement!M180</f>
         <v>0</v>
       </c>
-      <c r="D59" s="179">
+      <c r="D59" s="177">
         <f>Statement!N180</f>
         <v>9.1346678798908094</v>
       </c>
-      <c r="E59" s="179">
+      <c r="E59" s="177">
         <f>Statement!O180</f>
         <v>0.40614349011588274</v>
       </c>
-      <c r="F59" s="179">
+      <c r="F59" s="177">
         <f>Statement!P180</f>
         <v>0.60064865635469389</v>
       </c>
-      <c r="G59" s="179">
+      <c r="G59" s="177">
         <f>Statement!Q180</f>
         <v>0.44396943183076754</v>
       </c>
-      <c r="I59" s="179">
+      <c r="I59" s="177">
         <f>Statement!AC180</f>
         <v>0.40364585653572349</v>
       </c>
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B60" s="20" t="s">
-        <v>273</v>
-      </c>
-      <c r="C60" s="179">
+        <v>271</v>
+      </c>
+      <c r="C60" s="177">
         <f>Statement!M181</f>
         <v>6.5110966057441252E-2</v>
       </c>
-      <c r="D60" s="179">
+      <c r="D60" s="177">
         <f>Statement!N181</f>
         <v>9.4968152866242033</v>
       </c>
-      <c r="E60" s="179">
+      <c r="E60" s="177">
         <f>Statement!O181</f>
         <v>0.42297205180640762</v>
       </c>
-      <c r="F60" s="179">
+      <c r="F60" s="177">
         <f>Statement!P181</f>
         <v>0.61551072777817373</v>
       </c>
-      <c r="G60" s="179">
+      <c r="G60" s="177">
         <f>Statement!Q181</f>
         <v>0.45475689445121276</v>
       </c>
-      <c r="I60" s="179">
+      <c r="I60" s="177">
         <f>Statement!AC181</f>
         <v>0.41231501198357046</v>
       </c>
     </row>
     <row r="62" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B62" s="14" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C62" s="14"/>
       <c r="D62" s="14"/>
@@ -32822,36 +32836,36 @@
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B63" s="20" t="s">
-        <v>277</v>
-      </c>
-      <c r="C63" s="179">
+        <v>275</v>
+      </c>
+      <c r="C63" s="177">
         <f>Statement!M182</f>
         <v>3.9623381718320909E-2</v>
       </c>
-      <c r="D63" s="179">
+      <c r="D63" s="177">
         <f>Statement!N182</f>
         <v>3.9759036144578312E-2</v>
       </c>
-      <c r="E63" s="179">
+      <c r="E63" s="177">
         <f>Statement!O182</f>
         <v>4.118811881188119E-2</v>
       </c>
-      <c r="F63" s="179">
+      <c r="F63" s="177">
         <f>Statement!P182</f>
         <v>4.1380989086778369E-2</v>
       </c>
-      <c r="G63" s="179">
+      <c r="G63" s="177">
         <f>Statement!Q182</f>
         <v>3.9133101615211614E-2</v>
       </c>
-      <c r="I63" s="179">
+      <c r="I63" s="177">
         <f>Statement!AC182</f>
         <v>3.9374614276897757E-2</v>
       </c>
     </row>
     <row r="65" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B65" s="14" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C65" s="14"/>
       <c r="D65" s="14"/>
@@ -32862,94 +32876,94 @@
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B66" s="20" t="s">
-        <v>278</v>
-      </c>
-      <c r="C66" s="178">
+        <v>276</v>
+      </c>
+      <c r="C66" s="176">
         <f>Statement!M183</f>
         <v>0.84494023904382465</v>
       </c>
-      <c r="D66" s="178">
+      <c r="D66" s="176">
         <f>Statement!N183</f>
         <v>0.53829959514170045</v>
       </c>
-      <c r="E66" s="178">
+      <c r="E66" s="176">
         <f>Statement!O183</f>
         <v>1.0393600000000001</v>
       </c>
-      <c r="F66" s="178">
+      <c r="F66" s="176">
         <f>Statement!P183</f>
         <v>1.7709016393442623</v>
       </c>
-      <c r="G66" s="178">
+      <c r="G66" s="176">
         <f>Statement!Q183</f>
         <v>2.5743209876543212</v>
       </c>
-      <c r="I66" s="178">
+      <c r="I66" s="176">
         <f>Statement!AC183</f>
         <v>3.3294214876033057</v>
       </c>
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B67" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="C67" s="178">
+        <v>284</v>
+      </c>
+      <c r="C67" s="176">
         <f>Statement!M186</f>
         <v>0.40884462151394424</v>
       </c>
-      <c r="D67" s="178">
+      <c r="D67" s="176">
         <f>Statement!N186</f>
         <v>9.4858299595141707E-2</v>
       </c>
-      <c r="E67" s="178">
+      <c r="E67" s="176">
         <f>Statement!O186</f>
         <v>0.65100000000000002</v>
       </c>
-      <c r="F67" s="178">
+      <c r="F67" s="176">
         <f>Statement!P186</f>
         <v>1.4240573770491802</v>
       </c>
-      <c r="G67" s="178">
+      <c r="G67" s="176">
         <f>Statement!Q186</f>
         <v>2.2258436213991768</v>
       </c>
-      <c r="I67" s="178">
+      <c r="I67" s="176">
         <f>Statement!AC186</f>
         <v>2.9794214876033056</v>
       </c>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B68" s="20" t="s">
-        <v>291</v>
-      </c>
-      <c r="C68" s="200">
+        <v>289</v>
+      </c>
+      <c r="C68" s="198">
         <f>Statement!M187</f>
         <v>1.7626499592230463E-2</v>
       </c>
-      <c r="D68" s="200">
+      <c r="D68" s="198">
         <f>Statement!N187</f>
         <v>4.6216299382204652E-3</v>
       </c>
-      <c r="E68" s="200">
+      <c r="E68" s="198">
         <f>Statement!O187</f>
         <v>1.0561272414313365E-2</v>
       </c>
-      <c r="F68" s="200">
+      <c r="F68" s="198">
         <f>Statement!P187</f>
         <v>9.8841101665902813E-3</v>
       </c>
-      <c r="G68" s="200">
+      <c r="G68" s="198">
         <f>Statement!Q187</f>
         <v>1.1785239203608671E-2</v>
       </c>
-      <c r="I68" s="200">
+      <c r="I68" s="198">
         <f ca="1">Statement!AC187</f>
         <v>1.4463920490363455E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B70" s="14" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C70" s="14"/>
       <c r="D70" s="14"/>
@@ -32960,65 +32974,65 @@
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B71" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="C71" s="179">
+        <v>278</v>
+      </c>
+      <c r="C71" s="177">
         <f>Statement!M184</f>
         <v>0.22002635046113306</v>
       </c>
-      <c r="D71" s="179">
+      <c r="D71" s="177">
         <f>Statement!N184</f>
         <v>0.48023400106364122</v>
       </c>
-      <c r="E71" s="179">
+      <c r="E71" s="177">
         <f>Statement!O184</f>
         <v>0.1263438946244215</v>
       </c>
-      <c r="F71" s="179">
+      <c r="F71" s="177">
         <f>Statement!P184</f>
         <v>7.3912839956934887E-2</v>
       </c>
-      <c r="G71" s="179">
+      <c r="G71" s="177">
         <f>Statement!Q184</f>
         <v>6.217021359450145E-2</v>
       </c>
-      <c r="I71" s="179">
+      <c r="I71" s="177">
         <f>Statement!AC184</f>
         <v>5.4437361220542942E-2</v>
       </c>
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B72" s="20" t="s">
-        <v>281</v>
-      </c>
-      <c r="C72" s="179">
+        <v>279</v>
+      </c>
+      <c r="C72" s="177">
         <f>Statement!M185</f>
         <v>7.4459389165490081E-2</v>
       </c>
-      <c r="D72" s="179">
+      <c r="D72" s="177">
         <f>Statement!N185</f>
         <v>0.10043004374582931</v>
       </c>
-      <c r="E72" s="179">
+      <c r="E72" s="177">
         <f>Statement!O185</f>
         <v>5.8254817635665278E-2</v>
       </c>
-      <c r="F72" s="179">
+      <c r="F72" s="177">
         <f>Statement!P185</f>
         <v>3.629968505023104E-2</v>
       </c>
-      <c r="G72" s="179">
+      <c r="G72" s="177">
         <f>Statement!Q185</f>
         <v>2.9573303448211987E-2</v>
       </c>
-      <c r="I72" s="179">
+      <c r="I72" s="177">
         <f>Statement!AC185</f>
         <v>2.6983206504372935E-2</v>
       </c>
     </row>
     <row r="74" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B74" s="14" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C74" s="14"/>
       <c r="D74" s="14"/>
@@ -33029,87 +33043,87 @@
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B75" s="20" t="s">
-        <v>304</v>
-      </c>
-      <c r="C75" s="179">
+        <v>302</v>
+      </c>
+      <c r="C75" s="177">
         <f>Statement!M188</f>
         <v>3.6263654603552055E-2</v>
       </c>
-      <c r="D75" s="179">
+      <c r="D75" s="177">
         <f>Statement!N188</f>
         <v>6.7954326388373995E-2</v>
       </c>
-      <c r="E75" s="179">
+      <c r="E75" s="177">
         <f>Statement!O188</f>
         <v>1.7547027346442992E-2</v>
       </c>
-      <c r="F75" s="179">
+      <c r="F75" s="177">
         <f>Statement!P188</f>
         <v>2.4797504923484832E-2</v>
       </c>
-      <c r="G75" s="179">
+      <c r="G75" s="177">
         <f>Statement!Q188</f>
         <v>2.7980253591308617E-2</v>
       </c>
-      <c r="I75" s="179">
+      <c r="I75" s="177">
         <f>Statement!AC188</f>
         <v>2.5925969758295166E-2</v>
       </c>
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B76" s="20" t="s">
-        <v>301</v>
-      </c>
-      <c r="C76" s="179">
+        <v>299</v>
+      </c>
+      <c r="C76" s="177">
         <f>Statement!M189</f>
         <v>0.10715854194115064</v>
       </c>
-      <c r="D76" s="179">
+      <c r="D76" s="177">
         <f>Statement!N189</f>
         <v>0.32494238610175502</v>
       </c>
-      <c r="E76" s="179">
+      <c r="E76" s="177">
         <f>Statement!O189</f>
         <v>3.8056247775008899E-2</v>
       </c>
-      <c r="F76" s="179">
+      <c r="F76" s="177">
         <f>Statement!P189</f>
         <v>5.0492284167329808E-2</v>
       </c>
-      <c r="G76" s="179">
+      <c r="G76" s="177">
         <f>Statement!Q189</f>
         <v>5.8821238731283712E-2</v>
       </c>
-      <c r="I76" s="179">
+      <c r="I76" s="177">
         <f>Statement!AC189</f>
         <v>5.2304435371550904E-2</v>
       </c>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B77" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="C77" s="179">
+        <v>300</v>
+      </c>
+      <c r="C77" s="177">
         <f>Statement!M190</f>
         <v>0.83134582623509368</v>
       </c>
-      <c r="D77" s="179">
+      <c r="D77" s="177">
         <f>Statement!N190</f>
         <v>1.1871761658031088</v>
       </c>
-      <c r="E77" s="179">
+      <c r="E77" s="177">
         <f>Statement!O190</f>
         <v>0.70888594164456231</v>
       </c>
-      <c r="F77" s="179">
+      <c r="F77" s="177">
         <f>Statement!P190</f>
         <v>1.7360515021459229</v>
       </c>
-      <c r="G77" s="179">
+      <c r="G77" s="177">
         <f>Statement!Q190</f>
         <v>2.1252198381990857</v>
       </c>
-      <c r="I77" s="179">
+      <c r="I77" s="177">
         <f>Statement!AC190</f>
         <v>2.0359355638166048</v>
       </c>
@@ -33129,161 +33143,161 @@
       <c r="B80" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C80" s="179">
+      <c r="C80" s="177">
         <f>Statement!M87</f>
         <v>1</v>
       </c>
-      <c r="D80" s="179">
+      <c r="D80" s="177">
         <f>Statement!N87</f>
         <v>2.2293230289068887E-3</v>
       </c>
-      <c r="E80" s="179">
+      <c r="E80" s="177">
         <f>Statement!O87</f>
         <v>1.2585452658115222</v>
       </c>
-      <c r="F80" s="179">
+      <c r="F80" s="177">
         <f>Statement!P87</f>
         <v>1.1420340763599357</v>
       </c>
-      <c r="G80" s="179">
+      <c r="G80" s="177">
         <f>Statement!Q87</f>
         <v>0.65473535790094795</v>
       </c>
-      <c r="I80" s="201"/>
+      <c r="I80" s="199"/>
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B81" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C81" s="179">
+      <c r="C81" s="177">
         <f>Statement!M88</f>
         <v>1</v>
       </c>
-      <c r="D81" s="179">
+      <c r="D81" s="177">
         <f>Statement!N88</f>
         <v>0.23085072571246953</v>
       </c>
-      <c r="E81" s="179">
+      <c r="E81" s="177">
         <f>Statement!O88</f>
         <v>0.43062489240833191</v>
       </c>
-      <c r="F81" s="179">
+      <c r="F81" s="177">
         <f>Statement!P88</f>
         <v>0.9637205944287347</v>
       </c>
-      <c r="G81" s="179">
+      <c r="G81" s="177">
         <f>Statement!Q88</f>
         <v>0.91412114341738415</v>
       </c>
-      <c r="I81" s="201"/>
+      <c r="I81" s="199"/>
     </row>
     <row r="82" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B82" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="C82" s="179">
+      <c r="C82" s="177">
         <f>Statement!M89</f>
         <v>1</v>
       </c>
-      <c r="D82" s="179">
+      <c r="D82" s="177">
         <f>Statement!N89</f>
         <v>-0.12125894134477826</v>
       </c>
-      <c r="E82" s="179">
+      <c r="E82" s="177">
         <f>Statement!O89</f>
         <v>1.8849309716071894</v>
       </c>
-      <c r="F82" s="179">
+      <c r="F82" s="177">
         <f>Statement!P89</f>
         <v>1.208934335568046</v>
       </c>
-      <c r="G82" s="179">
+      <c r="G82" s="177">
         <f>Statement!Q89</f>
         <v>0.56822130025138462</v>
       </c>
-      <c r="I82" s="201"/>
+      <c r="I82" s="199"/>
     </row>
     <row r="83" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B83" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C83" s="179">
+      <c r="C83" s="177">
         <f>Statement!M92</f>
         <v>1</v>
       </c>
-      <c r="D83" s="179">
+      <c r="D83" s="177">
         <f>Statement!N92</f>
         <v>0.49744417541027708</v>
       </c>
-      <c r="E83" s="179">
+      <c r="E83" s="177">
         <f>Statement!O92</f>
         <v>1.7696730147323033E-2</v>
       </c>
-      <c r="F83" s="179">
+      <c r="F83" s="177">
         <f>Statement!P92</f>
         <v>0.44805366757878012</v>
       </c>
-      <c r="G83" s="179">
+      <c r="G83" s="177">
         <f>Statement!Q92</f>
         <v>0.40664431575739102</v>
       </c>
-      <c r="I83" s="201"/>
+      <c r="I83" s="199"/>
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B84" s="20" t="s">
-        <v>308</v>
-      </c>
-      <c r="C84" s="179">
+        <v>306</v>
+      </c>
+      <c r="C84" s="177">
         <f>Statement!M93</f>
         <v>1</v>
       </c>
-      <c r="D84" s="179">
+      <c r="D84" s="177">
         <f>Statement!N93</f>
         <v>-0.57932476844935765</v>
       </c>
-      <c r="E84" s="179">
+      <c r="E84" s="177">
         <f>Statement!O93</f>
         <v>6.8058712121212119</v>
       </c>
-      <c r="F84" s="179">
+      <c r="F84" s="177">
         <f>Statement!P93</f>
         <v>1.470368797767803</v>
       </c>
-      <c r="G84" s="179">
+      <c r="G84" s="177">
         <f>Statement!Q93</f>
         <v>0.60076363055995485</v>
       </c>
-      <c r="I84" s="201"/>
+      <c r="I84" s="199"/>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B85" s="20" t="s">
-        <v>309</v>
-      </c>
-      <c r="C85" s="179">
+        <v>307</v>
+      </c>
+      <c r="C85" s="177">
         <f>Statement!M95</f>
         <v>1</v>
       </c>
-      <c r="D85" s="179">
+      <c r="D85" s="177">
         <f>Statement!N95</f>
         <v>-0.55209187858900743</v>
       </c>
-      <c r="E85" s="179">
+      <c r="E85" s="177">
         <f>Statement!O95</f>
         <v>5.813186813186813</v>
       </c>
-      <c r="F85" s="179">
+      <c r="F85" s="177">
         <f>Statement!P95</f>
         <v>1.4489247311827957</v>
       </c>
-      <c r="G85" s="179">
+      <c r="G85" s="177">
         <f>Statement!Q95</f>
         <v>0.6474615806805708</v>
       </c>
-      <c r="I85" s="201"/>
+      <c r="I85" s="199"/>
     </row>
     <row r="88" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B88" s="14" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C88" s="14"/>
       <c r="D88" s="14"/>
@@ -33293,112 +33307,112 @@
       <c r="I88" s="14"/>
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B89" s="228" t="s">
-        <v>373</v>
-      </c>
-      <c r="C89" s="179">
+      <c r="B89" s="226" t="s">
+        <v>371</v>
+      </c>
+      <c r="C89" s="177">
         <f>Statement!M194</f>
         <v>0</v>
       </c>
-      <c r="D89" s="179">
+      <c r="D89" s="177">
         <f>Statement!N194</f>
         <v>0</v>
       </c>
-      <c r="E89" s="179">
+      <c r="E89" s="177">
         <f>Statement!O194</f>
         <v>0</v>
       </c>
-      <c r="F89" s="179">
+      <c r="F89" s="177">
         <f>Statement!P194</f>
         <v>1</v>
       </c>
-      <c r="G89" s="179">
+      <c r="G89" s="177">
         <f>Statement!Q194</f>
         <v>0.96364041936203437</v>
       </c>
-      <c r="I89" s="201"/>
+      <c r="I89" s="199"/>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B90" s="228" t="s">
-        <v>374</v>
-      </c>
-      <c r="C90" s="179">
+      <c r="B90" s="226" t="s">
+        <v>372</v>
+      </c>
+      <c r="C90" s="177">
         <f>Statement!M195</f>
         <v>0</v>
       </c>
-      <c r="D90" s="179">
+      <c r="D90" s="177">
         <f>Statement!N195</f>
         <v>0</v>
       </c>
-      <c r="E90" s="179">
+      <c r="E90" s="177">
         <f>Statement!O195</f>
         <v>0</v>
       </c>
-      <c r="F90" s="179">
+      <c r="F90" s="177">
         <f>Statement!P195</f>
         <v>1</v>
       </c>
-      <c r="G90" s="179">
+      <c r="G90" s="177">
         <f>Statement!Q195</f>
         <v>0.43510343704186349</v>
       </c>
-      <c r="I90" s="201"/>
+      <c r="I90" s="199"/>
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B91" s="20" t="s">
-        <v>375</v>
-      </c>
-      <c r="C91" s="179">
+        <v>373</v>
+      </c>
+      <c r="C91" s="177">
         <f>Statement!M196</f>
         <v>0</v>
       </c>
-      <c r="D91" s="179">
+      <c r="D91" s="177">
         <f>Statement!N196</f>
         <v>0</v>
       </c>
-      <c r="E91" s="179">
+      <c r="E91" s="177">
         <f>Statement!O196</f>
         <v>0</v>
       </c>
-      <c r="F91" s="179">
+      <c r="F91" s="177">
         <f>Statement!P196</f>
         <v>1</v>
       </c>
-      <c r="G91" s="179">
+      <c r="G91" s="177">
         <f>Statement!Q196</f>
         <v>0.68194919521469621</v>
       </c>
-      <c r="I91" s="201"/>
+      <c r="I91" s="199"/>
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B92" s="20" t="s">
-        <v>376</v>
-      </c>
-      <c r="C92" s="179">
+        <v>374</v>
+      </c>
+      <c r="C92" s="177">
         <f>Statement!M197</f>
         <v>0</v>
       </c>
-      <c r="D92" s="179">
+      <c r="D92" s="177">
         <f>Statement!N197</f>
         <v>0</v>
       </c>
-      <c r="E92" s="179">
+      <c r="E92" s="177">
         <f>Statement!O197</f>
         <v>0</v>
       </c>
-      <c r="F92" s="179">
+      <c r="F92" s="177">
         <f>Statement!P197</f>
         <v>1</v>
       </c>
-      <c r="G92" s="179">
+      <c r="G92" s="177">
         <f>Statement!Q197</f>
         <v>0.4500032656260205</v>
       </c>
-      <c r="I92" s="201"/>
+      <c r="I92" s="199"/>
     </row>
     <row r="94" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B94" s="14" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C94" s="14"/>
       <c r="D94" s="14"/>
@@ -33409,29 +33423,29 @@
     </row>
     <row r="95" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B95" s="20" t="s">
-        <v>284</v>
-      </c>
-      <c r="C95" s="179">
+        <v>282</v>
+      </c>
+      <c r="C95" s="177">
         <f>Statement!M200</f>
         <v>0</v>
       </c>
-      <c r="D95" s="179">
+      <c r="D95" s="177">
         <f>Statement!N201</f>
         <v>-2.5062656641604009E-3</v>
       </c>
-      <c r="E95" s="179">
+      <c r="E95" s="177">
         <f>Statement!O201</f>
         <v>-7.537688442211055E-3</v>
       </c>
-      <c r="F95" s="179">
+      <c r="F95" s="177">
         <f>Statement!P201</f>
         <v>1.1113924050632911</v>
       </c>
-      <c r="G95" s="179">
+      <c r="G95" s="177">
         <f>Statement!Q201</f>
         <v>0.16786570743405277</v>
       </c>
-      <c r="I95" s="201"/>
+      <c r="I95" s="199"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -33456,14 +33470,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="235" t="s">
-        <v>313</v>
-      </c>
-      <c r="D3" s="236"/>
-      <c r="F3" s="237" t="s">
-        <v>314</v>
-      </c>
-      <c r="G3" s="236"/>
+      <c r="C3" s="242" t="s">
+        <v>311</v>
+      </c>
+      <c r="D3" s="243"/>
+      <c r="F3" s="244" t="s">
+        <v>312</v>
+      </c>
+      <c r="G3" s="243"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -33471,546 +33485,546 @@
         <f>Statement!Z2</f>
         <v>25.01.2026</v>
       </c>
-      <c r="D4" s="207" t="str">
+      <c r="D4" s="205" t="str">
         <f>Statement!AA2</f>
         <v>26.04.2026</v>
       </c>
-      <c r="F4" s="208" t="str">
+      <c r="F4" s="206" t="str">
         <f>Statement!W2</f>
         <v>27.04.2025</v>
       </c>
-      <c r="G4" s="207" t="str">
+      <c r="G4" s="205" t="str">
         <f>Statement!AA2</f>
         <v>26.04.2026</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C5" s="10" t="str">
         <f>Statement!Z3</f>
         <v>Q4 2026</v>
       </c>
-      <c r="D5" s="207" t="str">
+      <c r="D5" s="205" t="str">
         <f>Statement!AA3</f>
         <v>Q1 2027</v>
       </c>
-      <c r="F5" s="208" t="str">
+      <c r="F5" s="206" t="str">
         <f>Statement!W3</f>
         <v>Q1 2026</v>
       </c>
-      <c r="G5" s="207" t="str">
+      <c r="G5" s="205" t="str">
         <f>Statement!AA3</f>
         <v>Q1 2027</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B6" s="209" t="s">
+      <c r="B6" s="207" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="203">
+      <c r="C6" s="201">
         <f>Statement!Z5</f>
         <v>68127</v>
       </c>
-      <c r="D6" s="202">
+      <c r="D6" s="200">
         <f>Statement!AA5</f>
         <v>81615</v>
       </c>
-      <c r="F6" s="203">
+      <c r="F6" s="201">
         <f>Statement!W5</f>
         <v>44062</v>
       </c>
-      <c r="G6" s="202">
+      <c r="G6" s="200">
         <f>Statement!AA5</f>
         <v>81615</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="210" t="s">
-        <v>315</v>
-      </c>
-      <c r="C7" s="238">
+      <c r="B7" s="208" t="s">
+        <v>313</v>
+      </c>
+      <c r="C7" s="245">
         <f>Statement!AA87</f>
         <v>0.19798317847549429</v>
       </c>
-      <c r="D7" s="239"/>
-      <c r="F7" s="238">
+      <c r="D7" s="246"/>
+      <c r="F7" s="245">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.85227633788752211</v>
       </c>
-      <c r="G7" s="239"/>
+      <c r="G7" s="246"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B8" s="211" t="s">
+      <c r="B8" s="209" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="204">
+      <c r="C8" s="202">
         <f>Statement!Z6</f>
         <v>17034</v>
       </c>
-      <c r="D8" s="202">
+      <c r="D8" s="200">
         <f>Statement!AA6</f>
         <v>20458</v>
       </c>
-      <c r="F8" s="204">
+      <c r="F8" s="202">
         <f>Statement!W6</f>
         <v>17394</v>
       </c>
-      <c r="G8" s="202">
+      <c r="G8" s="200">
         <f>Statement!AA6</f>
         <v>20458</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B9" s="210" t="s">
-        <v>315</v>
-      </c>
-      <c r="C9" s="238">
+      <c r="B9" s="208" t="s">
+        <v>313</v>
+      </c>
+      <c r="C9" s="245">
         <f>Statement!AA88</f>
         <v>0.20100974521545145</v>
       </c>
-      <c r="D9" s="239"/>
-      <c r="F9" s="238">
+      <c r="D9" s="246"/>
+      <c r="F9" s="245">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.17615269633206854</v>
       </c>
-      <c r="G9" s="239"/>
+      <c r="G9" s="246"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B10" s="211" t="s">
+      <c r="B10" s="209" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="204">
+      <c r="C10" s="202">
         <f>Statement!Z7</f>
         <v>51093</v>
       </c>
-      <c r="D10" s="202">
+      <c r="D10" s="200">
         <f>Statement!AA7</f>
         <v>61157</v>
       </c>
-      <c r="F10" s="204">
+      <c r="F10" s="202">
         <f>Statement!W7</f>
         <v>26668</v>
       </c>
-      <c r="G10" s="202">
+      <c r="G10" s="200">
         <f>Statement!AA7</f>
         <v>61157</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B11" s="210" t="s">
-        <v>315</v>
-      </c>
-      <c r="C11" s="238">
+      <c r="B11" s="208" t="s">
+        <v>313</v>
+      </c>
+      <c r="C11" s="245">
         <f>Statement!AA89</f>
         <v>0.19697414518622902</v>
       </c>
-      <c r="D11" s="239"/>
-      <c r="F11" s="238">
+      <c r="D11" s="246"/>
+      <c r="F11" s="245">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.293272836358182</v>
       </c>
-      <c r="G11" s="239"/>
+      <c r="G11" s="246"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B12" s="211" t="s">
+      <c r="B12" s="209" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="204">
+      <c r="C12" s="202">
         <f>Statement!Z10</f>
         <v>6794</v>
       </c>
-      <c r="D12" s="202">
+      <c r="D12" s="200">
         <f>Statement!AA10</f>
         <v>7621</v>
       </c>
-      <c r="F12" s="204">
+      <c r="F12" s="202">
         <f>Statement!W10</f>
         <v>5030</v>
       </c>
-      <c r="G12" s="202">
+      <c r="G12" s="200">
         <f>Statement!AA10</f>
         <v>7621</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B13" s="210" t="s">
-        <v>315</v>
-      </c>
-      <c r="C13" s="238">
+      <c r="B13" s="208" t="s">
+        <v>313</v>
+      </c>
+      <c r="C13" s="245">
         <f>Statement!AA92</f>
         <v>0.12172505151604357</v>
       </c>
-      <c r="D13" s="239"/>
-      <c r="F13" s="238">
+      <c r="D13" s="246"/>
+      <c r="F13" s="245">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.51510934393638175</v>
       </c>
-      <c r="G13" s="239"/>
+      <c r="G13" s="246"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B14" s="211" t="s">
-        <v>316</v>
-      </c>
-      <c r="C14" s="204">
+      <c r="B14" s="209" t="s">
+        <v>314</v>
+      </c>
+      <c r="C14" s="202">
         <f>Statement!Z11</f>
         <v>44299</v>
       </c>
-      <c r="D14" s="202">
+      <c r="D14" s="200">
         <f>Statement!AA11</f>
         <v>53536</v>
       </c>
-      <c r="F14" s="204">
+      <c r="F14" s="202">
         <f>Statement!W11</f>
         <v>21638</v>
       </c>
-      <c r="G14" s="202">
+      <c r="G14" s="200">
         <f>Statement!AA11</f>
         <v>53536</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="210" t="s">
-        <v>315</v>
-      </c>
-      <c r="C15" s="238">
+      <c r="B15" s="208" t="s">
+        <v>313</v>
+      </c>
+      <c r="C15" s="245">
         <f>Statement!AA93</f>
         <v>0.20851486489537011</v>
       </c>
-      <c r="D15" s="239"/>
-      <c r="F15" s="238">
+      <c r="D15" s="246"/>
+      <c r="F15" s="245">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.4741658193918108</v>
       </c>
-      <c r="G15" s="239"/>
+      <c r="G15" s="246"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B16" s="211" t="s">
+      <c r="B16" s="209" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="204">
+      <c r="C16" s="202">
         <f>Statement!Z17</f>
         <v>42960</v>
       </c>
-      <c r="D16" s="202">
+      <c r="D16" s="200">
         <f>Statement!AA17</f>
         <v>58321</v>
       </c>
-      <c r="F16" s="204">
+      <c r="F16" s="202">
         <f>Statement!W17</f>
         <v>18775</v>
       </c>
-      <c r="G16" s="202">
+      <c r="G16" s="200">
         <f>Statement!AA17</f>
         <v>58321</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B17" s="210" t="s">
-        <v>315</v>
-      </c>
-      <c r="C17" s="238">
+      <c r="B17" s="208" t="s">
+        <v>313</v>
+      </c>
+      <c r="C17" s="245">
         <f>Statement!AA95</f>
         <v>0.35756517690875234</v>
       </c>
-      <c r="D17" s="239"/>
-      <c r="F17" s="238">
+      <c r="D17" s="246"/>
+      <c r="F17" s="245">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>2.1063115845539282</v>
       </c>
-      <c r="G17" s="239"/>
+      <c r="G17" s="246"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B18" s="211" t="s">
-        <v>317</v>
-      </c>
-      <c r="C18" s="204">
+      <c r="B18" s="209" t="s">
+        <v>315</v>
+      </c>
+      <c r="C18" s="202">
         <f>Statement!Z21</f>
         <v>24432</v>
       </c>
-      <c r="D18" s="202">
+      <c r="D18" s="200">
         <f>Statement!AA21</f>
         <v>24391</v>
       </c>
-      <c r="F18" s="204">
+      <c r="F18" s="202">
         <f>Statement!W21</f>
         <v>24611</v>
       </c>
-      <c r="G18" s="202">
+      <c r="G18" s="200">
         <f>Statement!AA21</f>
         <v>24391</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B19" s="210" t="s">
-        <v>315</v>
-      </c>
-      <c r="C19" s="238">
+      <c r="B19" s="208" t="s">
+        <v>313</v>
+      </c>
+      <c r="C19" s="245">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-1.6781270464963983E-3</v>
       </c>
-      <c r="D19" s="239"/>
-      <c r="F19" s="238">
+      <c r="D19" s="246"/>
+      <c r="F19" s="245">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-8.9390922758116297E-3</v>
       </c>
-      <c r="G19" s="239"/>
+      <c r="G19" s="246"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B20" s="211" t="s">
+      <c r="B20" s="209" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="205">
+      <c r="C20" s="203">
         <f>Statement!Z25</f>
         <v>1.76</v>
       </c>
-      <c r="D20" s="206">
+      <c r="D20" s="204">
         <f>Statement!AA25</f>
         <v>2.39</v>
       </c>
-      <c r="F20" s="205">
+      <c r="F20" s="203">
         <f>Statement!W25</f>
         <v>0.76</v>
       </c>
-      <c r="G20" s="206">
+      <c r="G20" s="204">
         <f>Statement!AA25</f>
         <v>2.39</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B21" s="210" t="s">
-        <v>315</v>
-      </c>
-      <c r="C21" s="238">
+      <c r="B21" s="208" t="s">
+        <v>313</v>
+      </c>
+      <c r="C21" s="245">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.35795454545454553</v>
       </c>
-      <c r="D21" s="239"/>
-      <c r="F21" s="238">
+      <c r="D21" s="246"/>
+      <c r="F21" s="245">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>2.1447368421052633</v>
       </c>
-      <c r="G21" s="239"/>
+      <c r="G21" s="246"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C23" s="10" t="str">
         <f>C5</f>
         <v>Q4 2026</v>
       </c>
-      <c r="D23" s="207" t="str">
+      <c r="D23" s="205" t="str">
         <f>D5</f>
         <v>Q1 2027</v>
       </c>
-      <c r="F23" s="208" t="str">
+      <c r="F23" s="206" t="str">
         <f>F5</f>
         <v>Q1 2026</v>
       </c>
-      <c r="G23" s="207" t="str">
+      <c r="G23" s="205" t="str">
         <f>G5</f>
         <v>Q1 2027</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B24" s="228" t="s">
-        <v>373</v>
-      </c>
-      <c r="C24" s="204">
+      <c r="B24" s="226" t="s">
+        <v>371</v>
+      </c>
+      <c r="C24" s="202">
         <f>Statement!Z103</f>
         <v>33814</v>
       </c>
-      <c r="D24" s="202">
+      <c r="D24" s="200">
         <f>Statement!AA103</f>
         <v>37869</v>
       </c>
-      <c r="F24" s="204">
+      <c r="F24" s="202">
         <f>Statement!W103</f>
         <v>17599</v>
       </c>
-      <c r="G24" s="202">
+      <c r="G24" s="200">
         <f>Statement!AA103</f>
         <v>37869</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B25" s="210" t="s">
-        <v>315</v>
-      </c>
-      <c r="C25" s="238">
+      <c r="B25" s="208" t="s">
+        <v>313</v>
+      </c>
+      <c r="C25" s="245">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.11992074288756137</v>
       </c>
-      <c r="D25" s="239"/>
-      <c r="F25" s="238">
+      <c r="D25" s="246"/>
+      <c r="F25" s="245">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>1.1517699869310756</v>
       </c>
-      <c r="G25" s="239"/>
+      <c r="G25" s="246"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B26" s="228" t="s">
-        <v>374</v>
-      </c>
-      <c r="C26" s="204">
+      <c r="B26" s="226" t="s">
+        <v>372</v>
+      </c>
+      <c r="C26" s="202">
         <f>Statement!Z104</f>
         <v>28500</v>
       </c>
-      <c r="D26" s="202">
+      <c r="D26" s="200">
         <f>Statement!AA104</f>
         <v>37377</v>
       </c>
-      <c r="F26" s="204">
+      <c r="F26" s="202">
         <f>Statement!W104</f>
         <v>21513</v>
       </c>
-      <c r="G26" s="202">
+      <c r="G26" s="200">
         <f>Statement!AA104</f>
         <v>37377</v>
       </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B27" s="210" t="s">
-        <v>315</v>
-      </c>
-      <c r="C27" s="238">
+      <c r="B27" s="208" t="s">
+        <v>313</v>
+      </c>
+      <c r="C27" s="245">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.31147368421052629</v>
       </c>
-      <c r="D27" s="239"/>
-      <c r="F27" s="238">
+      <c r="D27" s="246"/>
+      <c r="F27" s="245">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.73741458652907543</v>
       </c>
-      <c r="G27" s="239"/>
+      <c r="G27" s="246"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
-        <v>375</v>
-      </c>
-      <c r="C28" s="204">
+        <v>373</v>
+      </c>
+      <c r="C28" s="202">
         <f>Statement!Z105</f>
         <v>62314</v>
       </c>
-      <c r="D28" s="202">
+      <c r="D28" s="200">
         <f>Statement!AA105</f>
         <v>75246</v>
       </c>
-      <c r="F28" s="204">
+      <c r="F28" s="202">
         <f>Statement!W105</f>
         <v>39112</v>
       </c>
-      <c r="G28" s="202">
+      <c r="G28" s="200">
         <f>Statement!AA105</f>
         <v>75246</v>
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B29" s="210" t="s">
-        <v>315</v>
-      </c>
-      <c r="C29" s="238">
+      <c r="B29" s="208" t="s">
+        <v>313</v>
+      </c>
+      <c r="C29" s="245">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.20752960811374652</v>
       </c>
-      <c r="D29" s="239"/>
-      <c r="F29" s="238">
+      <c r="D29" s="246"/>
+      <c r="F29" s="245">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.92385968500715898</v>
       </c>
-      <c r="G29" s="239"/>
+      <c r="G29" s="246"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
-        <v>376</v>
-      </c>
-      <c r="C30" s="204">
+        <v>374</v>
+      </c>
+      <c r="C30" s="202">
         <f>Statement!Z106</f>
         <v>5813</v>
       </c>
-      <c r="D30" s="204">
+      <c r="D30" s="202">
         <f>Statement!AA106</f>
         <v>6369</v>
       </c>
-      <c r="F30" s="204">
+      <c r="F30" s="202">
         <f>Statement!W106</f>
         <v>4950</v>
       </c>
-      <c r="G30" s="204">
+      <c r="G30" s="202">
         <f>Statement!AA106</f>
         <v>6369</v>
       </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B31" s="210" t="s">
-        <v>315</v>
-      </c>
-      <c r="C31" s="238">
+      <c r="B31" s="208" t="s">
+        <v>313</v>
+      </c>
+      <c r="C31" s="245">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>9.5647686220540165E-2</v>
       </c>
-      <c r="D31" s="239"/>
-      <c r="F31" s="238">
+      <c r="D31" s="246"/>
+      <c r="F31" s="245">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.28666666666666668</v>
       </c>
-      <c r="G31" s="239"/>
+      <c r="G31" s="246"/>
     </row>
   </sheetData>
   <mergeCells count="26">
@@ -34281,7 +34295,7 @@
     </row>
     <row r="60" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B60" s="20" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C60" s="64">
         <f>Statement!H168</f>
@@ -34326,7 +34340,7 @@
     </row>
     <row r="61" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B61" s="20" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C61" s="64">
         <f>Statement!H169</f>
@@ -34506,7 +34520,7 @@
     </row>
     <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B65" s="20" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C65" s="64">
         <f>Statement!H103</f>
@@ -34551,7 +34565,7 @@
     </row>
     <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B66" s="20" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C66" s="64">
         <f>Statement!H104</f>
@@ -34596,7 +34610,7 @@
     </row>
     <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B67" s="20" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C67" s="64">
         <f>Statement!H106</f>
@@ -34643,43 +34657,43 @@
       <c r="B68" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="C68" s="223">
+      <c r="C68" s="221">
         <f>Statement!H127</f>
         <v>0</v>
       </c>
-      <c r="D68" s="223">
+      <c r="D68" s="221">
         <f>Statement!I127</f>
         <v>0</v>
       </c>
-      <c r="E68" s="223">
+      <c r="E68" s="221">
         <f>Statement!J127</f>
         <v>0</v>
       </c>
-      <c r="F68" s="223">
+      <c r="F68" s="221">
         <f>Statement!K127</f>
         <v>0</v>
       </c>
-      <c r="G68" s="223">
+      <c r="G68" s="221">
         <f>Statement!L127</f>
         <v>0</v>
       </c>
-      <c r="H68" s="223">
+      <c r="H68" s="221">
         <f>Statement!M127</f>
         <v>0.22069839545567699</v>
       </c>
-      <c r="I68" s="223">
+      <c r="I68" s="221">
         <f>Statement!N127</f>
         <v>0.10606575688407557</v>
       </c>
-      <c r="J68" s="223">
+      <c r="J68" s="221">
         <f>Statement!O127</f>
         <v>0.45277507302823755</v>
       </c>
-      <c r="K68" s="223">
+      <c r="K68" s="221">
         <f>Statement!P127</f>
         <v>0.65304074336251472</v>
       </c>
-      <c r="L68" s="223">
+      <c r="L68" s="221">
         <f>Statement!Q127</f>
         <v>0.5805863551302447</v>
       </c>
@@ -34688,43 +34702,43 @@
       <c r="B69" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="C69" s="223">
+      <c r="C69" s="221">
         <f>Statement!H129</f>
         <v>0</v>
       </c>
-      <c r="D69" s="223">
+      <c r="D69" s="221">
         <f>Statement!I129</f>
         <v>0</v>
       </c>
-      <c r="E69" s="223">
+      <c r="E69" s="221">
         <f>Statement!J129</f>
         <v>0</v>
       </c>
-      <c r="F69" s="223">
+      <c r="F69" s="221">
         <f>Statement!K129</f>
         <v>0</v>
       </c>
-      <c r="G69" s="223">
+      <c r="G69" s="221">
         <f>Statement!L129</f>
         <v>0</v>
       </c>
-      <c r="H69" s="223">
+      <c r="H69" s="221">
         <f>Statement!M129</f>
         <v>0.36645122501127303</v>
       </c>
-      <c r="I69" s="223">
+      <c r="I69" s="221">
         <f>Statement!N129</f>
         <v>0.19763811592235647</v>
       </c>
-      <c r="J69" s="223">
+      <c r="J69" s="221">
         <f>Statement!O129</f>
         <v>0.69244729861789756</v>
       </c>
-      <c r="K69" s="223">
+      <c r="K69" s="221">
         <f>Statement!P129</f>
         <v>0.91872880608115781</v>
       </c>
-      <c r="L69" s="223">
+      <c r="L69" s="221">
         <f>Statement!Q129</f>
         <v>0.76333339690895341</v>
       </c>
@@ -34733,43 +34747,43 @@
       <c r="B70" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="C70" s="223">
+      <c r="C70" s="221">
         <f>Statement!H151</f>
         <v>0</v>
       </c>
-      <c r="D70" s="223">
+      <c r="D70" s="221">
         <f>Statement!I151</f>
         <v>0</v>
       </c>
-      <c r="E70" s="223">
+      <c r="E70" s="221">
         <f>Statement!J151</f>
         <v>0</v>
       </c>
-      <c r="F70" s="223">
+      <c r="F70" s="221">
         <f>Statement!K151</f>
         <v>0</v>
       </c>
-      <c r="G70" s="223">
+      <c r="G70" s="221">
         <f>Statement!L151</f>
         <v>0</v>
       </c>
-      <c r="H70" s="223">
+      <c r="H70" s="221">
         <f>Statement!M151</f>
         <v>0.60245252494303547</v>
       </c>
-      <c r="I70" s="223">
+      <c r="I70" s="221">
         <f>Statement!N151</f>
         <v>0.21378682052839357</v>
       </c>
-      <c r="J70" s="223">
+      <c r="J70" s="221">
         <f>Statement!O151</f>
         <v>1.0866013555554745</v>
       </c>
-      <c r="K70" s="223">
+      <c r="K70" s="221">
         <f>Statement!P151</f>
         <v>1.5847534085376831</v>
       </c>
-      <c r="L70" s="223">
+      <c r="L70" s="221">
         <f>Statement!Q151</f>
         <v>1.0723937210768841</v>
       </c>
@@ -35084,7 +35098,7 @@
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B63" s="20" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C63" s="64">
         <f>Statement!T103</f>
@@ -35121,7 +35135,7 @@
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B64" s="20" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C64" s="64">
         <f>Statement!T104</f>
@@ -35158,7 +35172,7 @@
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B65" s="20" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C65" s="64">
         <f>Statement!T106</f>
@@ -35195,7 +35209,7 @@
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B66" s="20" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C66" s="64">
         <f>Statement!T168</f>

--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{409FA6FC-F531-9F43-B4AE-9F84DDA1669F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74BF92DD-37A0-1943-82B4-DD320AE0F36A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="9" activeTab="19" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -117,7 +117,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -128,7 +128,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -138,19 +159,28 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
     </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="396">
   <si>
     <t>Ticker</t>
   </si>
@@ -612,9 +642,6 @@
   </si>
   <si>
     <t>Change in NWC</t>
-  </si>
-  <si>
-    <t>UFCF</t>
   </si>
   <si>
     <t>NOPAT</t>
@@ -11674,7 +11701,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1yv52&amp;q=XNAS%3aNVDA&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -11693,11 +11720,9 @@
     <v>Powered by Refinitiv</v>
     <v>236.54</v>
     <v>140.85499999999999</v>
-    <v>2.1970999999999998</v>
-    <v>-7.77</v>
-    <v>-3.7322000000000001E-2</v>
-    <v>-0.40039999999999998</v>
-    <v>-1.9980000000000002E-3</v>
+    <v>2.1962000000000002</v>
+    <v>0.90500000000000003</v>
+    <v>4.516E-3</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -11705,35 +11730,49 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2788 San Tomas Expressway, SANTA CLARA, CA, 95051 US</v>
-    <v>207.22</v>
+    <v>203.65</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46183.899640010939</v>
+    <v>46184.655324120315</v>
     <v>0</v>
-    <v>199.92</v>
-    <v>4850164000000</v>
+    <v>199.54</v>
+    <v>4872065000000</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
-    <v>204.43</v>
-    <v>30.6922</v>
-    <v>208.19</v>
+    <v>201.58</v>
+    <v>30.8308</v>
     <v>200.42</v>
-    <v>200.0196</v>
+    <v>201.32499999999999</v>
     <v>24200000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>160202862</v>
-    <v>173838363</v>
+    <v>51798653</v>
+    <v>175771962</v>
     <v>1998</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -11747,28 +11786,28 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.24</v>
-    <v>-5.2719999999999998E-3</v>
+    <v>0.14000000000000001</v>
+    <v>3.0919999999999997E-3</v>
     <v>US</v>
-    <v>45.56</v>
+    <v>45.6</v>
     <v>Index</v>
-    <v>3</v>
-    <v>45.2</v>
+    <v>6</v>
+    <v>45.13</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>45.46</v>
-    <v>45.52</v>
+    <v>45.34</v>
     <v>45.28</v>
+    <v>45.42</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>4</v>
+    <v>7</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -11790,8 +11829,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -11812,7 +11849,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -11822,6 +11858,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -11857,7 +11898,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="45">
+    <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -11868,16 +11909,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -11971,19 +12009,13 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="4">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -12055,9 +12087,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -12065,9 +12094,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -12557,11 +12583,11 @@
       </c>
       <c r="C2" s="233"/>
       <c r="E2" s="232" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F2" s="233"/>
       <c r="H2" s="232" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I2" s="233"/>
     </row>
@@ -12574,11 +12600,11 @@
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="187" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F3" s="189">
         <f ca="1">Statement!AC155</f>
-        <v>4871208.0999999996</v>
+        <v>4893204.125</v>
       </c>
       <c r="H3" s="187" t="str">
         <f>'AVG target price'!B5</f>
@@ -12586,7 +12612,7 @@
       </c>
       <c r="I3" s="213">
         <f ca="1">'AVG target price'!C5</f>
-        <v>130.18726406227856</v>
+        <v>130.06128089086198</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -12598,11 +12624,11 @@
         <v>NVDA</v>
       </c>
       <c r="E4" s="188" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F4" s="190">
         <f ca="1">Statement!AC156</f>
-        <v>4799106.0999999996</v>
+        <v>4821102.125</v>
       </c>
       <c r="H4" s="187" t="str">
         <f>'AVG target price'!B6</f>
@@ -12610,7 +12636,7 @@
       </c>
       <c r="I4" s="213">
         <f ca="1">'AVG target price'!C6</f>
-        <v>327.93509371975153</v>
+        <v>327.7925765771455</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -12619,10 +12645,10 @@
       </c>
       <c r="C5" s="210" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>200.42</v>
+        <v>201.32499999999999</v>
       </c>
       <c r="E5" s="187" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F5" s="191">
         <f>Statement!AC25</f>
@@ -12641,16 +12667,16 @@
       <c r="B6" s="187" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="210" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>200.0196</v>
+      <c r="C6" s="210" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="187" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F6" s="192">
         <f ca="1">Statement!AC152</f>
-        <v>30.69218989280245</v>
+        <v>30.830781010719758</v>
       </c>
       <c r="H6" s="187" t="str">
         <f>'AVG target price'!B8</f>
@@ -12658,7 +12684,7 @@
       </c>
       <c r="I6" s="213">
         <f ca="1">'AVG target price'!C8</f>
-        <v>315.13076846974371</v>
+        <v>314.99385397207828</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -12667,14 +12693,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-7.77</v>
+        <v>0.90500000000000003</v>
       </c>
       <c r="E7" s="188" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F7" s="193">
         <f ca="1">Statement!AC153</f>
-        <v>19.338647092007211</v>
+        <v>19.425971089703381</v>
       </c>
       <c r="H7" s="186" t="str">
         <f>'AVG target price'!B9</f>
@@ -12682,23 +12708,23 @@
       </c>
       <c r="I7" s="214">
         <f ca="1">'AVG target price'!C9</f>
-        <v>269.40997833337696</v>
+        <v>269.30862463045497</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="187" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.40039999999999998</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="187" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F8" s="194">
         <f ca="1">Statement!AC163</f>
-        <v>2.3040896158798882E-2</v>
+        <v>2.2937322280623229E-2</v>
       </c>
       <c r="H8" s="186" t="str">
         <f>'AVG target price'!B11</f>
@@ -12706,7 +12732,7 @@
       </c>
       <c r="I8" s="215">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.34422701493552027</v>
+        <v>0.33768098661594431</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -12715,30 +12741,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-3.7322000000000001E-2</v>
+        <v>4.516E-3</v>
       </c>
       <c r="E9" s="187" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F9" s="194">
         <f ca="1">Statement!AC164</f>
-        <v>3.2581578684761997E-2</v>
+        <v>3.2435117347572331E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="187" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.9980000000000002E-3</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="187" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F10" s="194">
         <f ca="1">Statement!AC166</f>
-        <v>9.300362265369037E-3</v>
+        <v>9.2585550985980983E-3</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -12750,11 +12776,11 @@
         <v>236.54</v>
       </c>
       <c r="E11" s="188" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F11" s="195">
         <f ca="1">Statement!AC165</f>
-        <v>1.9958088015168147E-4</v>
+        <v>1.9868372035266362E-4</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -12779,7 +12805,7 @@
       </c>
       <c r="C13" s="211" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.1970999999999998</v>
+        <v>2.1962000000000002</v>
       </c>
       <c r="E13" s="187" t="s">
         <v>96</v>
@@ -12795,7 +12821,7 @@
       </c>
       <c r="C14" s="212" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>173838363</v>
+        <v>175771962</v>
       </c>
       <c r="E14" s="188" t="s">
         <v>97</v>
@@ -12807,16 +12833,16 @@
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.2">
       <c r="E15" s="187" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F15" s="194">
         <f ca="1">Statement!AC178</f>
-        <v>1.4801666962247006E-2</v>
+        <v>1.473513022512626E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
       <c r="E16" s="188" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F16" s="193">
         <f>Statement!AC177</f>
@@ -12829,7 +12855,7 @@
       </c>
       <c r="C17" s="234"/>
       <c r="E17" s="186" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F17" s="196">
         <f>Statement!AC173</f>
@@ -12841,10 +12867,10 @@
         <v>12</v>
       </c>
       <c r="C18" s="69" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E18" s="187" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F18" s="192">
         <f>Statement!AC146</f>
@@ -12860,7 +12886,7 @@
         <v>1000000</v>
       </c>
       <c r="E19" s="187" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F19" s="192">
         <f>Statement!AC148</f>
@@ -12872,10 +12898,10 @@
         <v>84</v>
       </c>
       <c r="C20" s="69" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E20" s="188" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F20" s="193">
         <f>Statement!AC149</f>
@@ -12896,7 +12922,7 @@
         <v>87</v>
       </c>
       <c r="C22" s="69" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
@@ -12905,7 +12931,7 @@
       </c>
       <c r="C25" s="234"/>
       <c r="E25" s="232" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F25" s="233"/>
     </row>
@@ -12916,32 +12942,32 @@
       <c r="C26" s="171">
         <v>0.21</v>
       </c>
-      <c r="E26" s="187" t="e" vm="2">
+      <c r="E26" s="187" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="222" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>45.28</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B27" s="186" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C27" s="224">
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="E27" s="188" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F27" s="223">
         <f ca="1">F26/1000</f>
-        <v>4.5280000000000001E-2</v>
+        <v>4.5420000000000002E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B28" s="186" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C28" s="224">
         <v>0</v>
@@ -12949,7 +12975,7 @@
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="186" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C29" s="224">
         <v>0.12</v>
@@ -12957,7 +12983,7 @@
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="231" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C33" s="231"/>
       <c r="D33" s="231"/>
@@ -12968,18 +12994,18 @@
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="16" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -12993,7 +13019,7 @@
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="231" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C42" s="231"/>
       <c r="D42" s="231"/>
@@ -13004,13 +13030,13 @@
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C44" s="41" t="s">
+        <v>326</v>
+      </c>
+      <c r="D44" s="41" t="s">
         <v>327</v>
-      </c>
-      <c r="D44" s="41" t="s">
-        <v>328</v>
       </c>
       <c r="E44" s="220"/>
     </row>
@@ -13312,11 +13338,11 @@
         <v>899038.4839425002</v>
       </c>
       <c r="N6" s="90" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="O6" s="5"/>
       <c r="Q6" s="90" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="R6" s="227" t="str">
         <f>B6</f>
@@ -13411,11 +13437,11 @@
         <v>276381.4356576</v>
       </c>
       <c r="N7" s="90" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="O7" s="5"/>
       <c r="Q7" s="90" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="R7" s="227" t="str">
         <f t="shared" ref="R7:R9" si="2">B7</f>
@@ -13605,11 +13631,11 @@
         <v>81428.411531250007</v>
       </c>
       <c r="N9" s="90" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="O9" s="5"/>
       <c r="Q9" s="90" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="R9" s="1" t="str">
         <f t="shared" si="2"/>
@@ -17560,7 +17586,7 @@
         <v>0.21</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -17768,7 +17794,7 @@
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C25" s="240" t="s">
-        <v>154</v>
+        <v>259</v>
       </c>
       <c r="D25" s="240"/>
       <c r="E25" s="240"/>
@@ -17827,7 +17853,7 @@
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B27" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C27" s="127">
         <f>C10*(1-C15)</f>
@@ -17872,7 +17898,7 @@
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B28" s="16" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C28" s="94">
         <f>C27+C20-C21+C22</f>
@@ -17931,7 +17957,7 @@
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C32" s="12">
         <f>C5</f>
@@ -18097,7 +18123,7 @@
   <sheetData>
     <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -18129,7 +18155,7 @@
     <row r="1" spans="1:3" s="83" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4"/>
       <c r="B1" s="82" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="83" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -18139,13 +18165,13 @@
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="231" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C4" s="231"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C5" s="137">
         <f>Statement!AC77</f>
@@ -18158,21 +18184,21 @@
       </c>
       <c r="C6" s="134">
         <f ca="1">Overview!C5</f>
-        <v>200.42</v>
+        <v>201.32499999999999</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C7" s="135">
         <f ca="1">C5*C6</f>
-        <v>4871208.0999999996</v>
+        <v>4893204.125</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C8" s="113">
         <f>Statement!AC106</f>
@@ -18181,11 +18207,11 @@
     </row>
     <row r="9" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C9" s="136">
         <f ca="1">Overview!F27</f>
-        <v>4.5280000000000001E-2</v>
+        <v>4.5420000000000002E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18194,12 +18220,12 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C13</f>
-        <v>2.1970999999999998</v>
+        <v>2.1962000000000002</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C11" s="136">
         <f>[1]Sheet1!$C$12</f>
@@ -18217,7 +18243,7 @@
     </row>
     <row r="13" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C13" s="136">
         <f>Overview!C27</f>
@@ -18227,31 +18253,31 @@
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="231" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C15" s="231"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>1.7357702345160843E-3</v>
+        <v>1.7279810497398173E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.9982642297654839</v>
+        <v>0.99827201895026019</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C18" s="46">
         <f>C13*(1-C12)</f>
@@ -18260,20 +18286,20 @@
     </row>
     <row r="19" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14414949999999999</v>
+        <v>0.14424900000000002</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14396922377132826</v>
+        <v>0.14406936081805011</v>
       </c>
     </row>
   </sheetData>
@@ -18309,7 +18335,7 @@
     <row r="1" spans="1:28" s="83" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4"/>
       <c r="B1" s="82" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:28" s="83" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -18350,7 +18376,7 @@
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
       <c r="C5" s="240" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D5" s="240"/>
       <c r="E5" s="240"/>
@@ -18434,7 +18460,7 @@
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B7" s="39" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C7" s="113">
         <f>'FCF &amp; Other'!C28</f>
@@ -18493,7 +18519,7 @@
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B8" s="39" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C8" s="127">
         <v>0</v>
@@ -18524,7 +18550,7 @@
       </c>
       <c r="L8" s="127">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>4279059.7048112862</v>
+        <v>4275461.0258678338</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -18543,7 +18569,7 @@
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C9" s="138"/>
       <c r="D9" s="138"/>
@@ -18569,7 +18595,7 @@
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C10" s="138"/>
       <c r="D10" s="138"/>
@@ -18578,29 +18604,29 @@
       <c r="G10" s="139"/>
       <c r="H10" s="127">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>111486.51048565308</v>
+        <v>111476.75239729614</v>
       </c>
       <c r="I10" s="127">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>140574.93549478284</v>
+        <v>140550.32834539691</v>
       </c>
       <c r="J10" s="127">
         <f t="shared" ca="1" si="0"/>
-        <v>181189.24632581943</v>
+        <v>181141.67359477043</v>
       </c>
       <c r="K10" s="127">
         <f t="shared" ca="1" si="0"/>
-        <v>221222.51287948817</v>
+        <v>221145.07120816314</v>
       </c>
       <c r="L10" s="127">
         <f t="shared" ca="1" si="0"/>
-        <v>253505.51092190403</v>
+        <v>253394.58735971208</v>
       </c>
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C11" s="138"/>
       <c r="D11" s="138"/>
@@ -18613,18 +18639,18 @@
       <c r="K11" s="138"/>
       <c r="L11" s="127">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>2184120.7369260327</v>
+        <v>2181329.0191470617</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B13" s="231" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C13" s="231"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C14" s="141">
         <v>2.5000000000000001E-2</v>
@@ -18632,49 +18658,49 @@
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C15" s="136">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14396922377132826</v>
+        <v>0.14406936081805011</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B18" s="231" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C18" s="231"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>907978.71610764752</v>
+        <v>907708.41290533869</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>2184120.7369260327</v>
+        <v>2181329.0191470617</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B21" s="16" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>3092099.4530336801</v>
+        <v>3089037.4320524004</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C22" s="137">
         <f>Statement!AC105</f>
@@ -18683,7 +18709,7 @@
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C23" s="137">
         <f>Statement!AC106</f>
@@ -18692,11 +18718,11 @@
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B24" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>3164201.4530336801</v>
+        <v>3161139.4320524004</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -18710,11 +18736,11 @@
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B26" s="142" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C26" s="143">
         <f ca="1">C24/C25</f>
-        <v>130.18726406227856</v>
+        <v>130.06128089086198</v>
       </c>
     </row>
   </sheetData>
@@ -18752,7 +18778,7 @@
     <row r="1" spans="1:14" s="83" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4"/>
       <c r="B1" s="82" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
@@ -18777,7 +18803,7 @@
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
       <c r="C4" s="240" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D4" s="240"/>
       <c r="E4" s="240"/>
@@ -18928,7 +18954,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B8" s="16" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C8" s="92">
         <f>'FCF &amp; Other'!C28</f>
@@ -18992,7 +19018,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B11" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C11" s="12">
         <f>C5</f>
@@ -19130,7 +19156,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C14" s="138"/>
       <c r="D14" s="95">
@@ -19182,7 +19208,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C16" s="240" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D16" s="240"/>
       <c r="E16" s="240"/>
@@ -19240,7 +19266,7 @@
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C18" s="100">
         <f>Statement!M21</f>
@@ -19286,7 +19312,7 @@
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C19" s="138"/>
       <c r="D19" s="145">
@@ -19327,7 +19353,7 @@
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C21" s="240" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D21" s="240"/>
       <c r="E21" s="240"/>
@@ -19422,7 +19448,7 @@
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C26" s="240" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D26" s="240"/>
       <c r="E26" s="240"/>
@@ -19480,7 +19506,7 @@
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B28" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C28" s="150">
         <f>C23/(C6/C18)</f>
@@ -19511,7 +19537,7 @@
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B29" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C29" s="144">
         <f>C23*C18</f>
@@ -19542,7 +19568,7 @@
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C30" s="88">
         <f>Statement!M106</f>
@@ -19573,7 +19599,7 @@
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B31" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C31" s="153">
         <f>Statement!M105</f>
@@ -19604,7 +19630,7 @@
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C32" s="144">
         <f>C29+C30-C31</f>
@@ -19635,7 +19661,7 @@
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B33" s="16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C33" s="150">
         <f>C32/C7</f>
@@ -19666,7 +19692,7 @@
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C34" s="150">
         <f>C32/C8</f>
@@ -19703,14 +19729,14 @@
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="231" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C37" s="231"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B38" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C38" s="64">
         <f>L7</f>
@@ -19719,16 +19745,16 @@
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B39" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C39" s="136">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14396922377132826</v>
+        <v>0.14406936081805011</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B40" s="39" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C40" s="105">
         <v>20</v>
@@ -19736,7 +19762,7 @@
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B41" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C41" s="24">
         <f>(C38*C40)</f>
@@ -19745,11 +19771,11 @@
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B42" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>7970462.4528585616</v>
+        <v>7966998.573707521</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -19763,22 +19789,22 @@
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B44" s="142" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C44" s="143">
         <f ca="1">C42/C43</f>
-        <v>327.93509371975153</v>
+        <v>327.7925765771455</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B46" s="231" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C46" s="231"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C47" s="64">
         <f>L6</f>
@@ -19787,7 +19813,7 @@
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C48" s="136">
         <f>Overview!C29</f>
@@ -19796,7 +19822,7 @@
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B49" s="39" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C49" s="105">
         <v>10</v>
@@ -19804,7 +19830,7 @@
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C50" s="24">
         <f>L18</f>
@@ -19813,7 +19839,7 @@
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B51" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C51" s="24">
         <f>(C47*C49)/C50</f>
@@ -19822,7 +19848,7 @@
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B52" s="142" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C52" s="143">
         <f>C51/(1+C48)^5</f>
@@ -19831,13 +19857,13 @@
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B54" s="231" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C54" s="231"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C55" s="64">
         <f>L8</f>
@@ -19846,16 +19872,16 @@
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C56" s="136">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14396922377132826</v>
+        <v>0.14406936081805011</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B57" s="39" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C57" s="105">
         <v>30</v>
@@ -19863,7 +19889,7 @@
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C58" s="24">
         <f>(C55*C57)</f>
@@ -19872,11 +19898,11 @@
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B59" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C59" s="24">
         <f ca="1">C58/(1+C56)^5-G30+G31</f>
-        <v>7659253.3276571212</v>
+        <v>7655925.6207913626</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -19890,11 +19916,11 @@
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="142" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C61" s="143">
         <f ca="1">C59/C60</f>
-        <v>315.13076846974371</v>
+        <v>314.99385397207828</v>
       </c>
     </row>
   </sheetData>
@@ -19936,7 +19962,7 @@
     <row r="1" spans="1:14" s="83" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4"/>
       <c r="B1" s="82" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
@@ -19947,32 +19973,32 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B4" s="231" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C4" s="231"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C5" s="134">
         <f ca="1">DCF!C26</f>
-        <v>130.18726406227856</v>
+        <v>130.06128089086198</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C6" s="134">
         <f ca="1">Multiples!C44</f>
-        <v>327.93509371975153</v>
+        <v>327.7925765771455</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C7" s="134">
         <f>Multiples!C52</f>
@@ -19981,38 +20007,38 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C8" s="134">
         <f ca="1">Multiples!C61</f>
-        <v>315.13076846974371</v>
+        <v>314.99385397207828</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B9" s="142" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C9" s="143">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>269.40997833337696</v>
+        <v>269.30862463045497</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C5</f>
-        <v>200.42</v>
+        <v>201.32499999999999</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C11" s="155">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.34422701493552027</v>
+        <v>0.33768098661594431</v>
       </c>
     </row>
   </sheetData>
@@ -20068,7 +20094,7 @@
     <row r="1" spans="1:28" s="83" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4"/>
       <c r="B1" s="82" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:28" s="83" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -20109,7 +20135,7 @@
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
       <c r="C5" s="240" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D5" s="240"/>
       <c r="E5" s="240"/>
@@ -20193,7 +20219,7 @@
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B7" s="39" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C7" s="113">
         <f>'FCF &amp; Other'!C28</f>
@@ -20211,29 +20237,29 @@
         <f>'FCF &amp; Other'!F28</f>
         <v>59893.306952609913</v>
       </c>
-      <c r="G7" s="113">
+      <c r="G7" s="114">
         <f>'FCF &amp; Other'!G28</f>
         <v>91501.393983739836</v>
       </c>
       <c r="H7" s="127">
         <f>G7*(1+$C$17)</f>
-        <v>142742.17461463416</v>
+        <v>141827.16067479676</v>
       </c>
       <c r="I7" s="127">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>222677.7923988293</v>
+        <v>219832.09904593497</v>
       </c>
       <c r="J7" s="127">
         <f t="shared" si="0"/>
-        <v>347377.35614217375</v>
+        <v>340739.75352119922</v>
       </c>
       <c r="K7" s="127">
         <f t="shared" si="0"/>
-        <v>541908.67558179109</v>
+        <v>528146.61795785883</v>
       </c>
       <c r="L7" s="127">
         <f t="shared" si="0"/>
-        <v>845377.53390759416</v>
+        <v>818627.25783468119</v>
       </c>
       <c r="N7" s="91"/>
       <c r="O7" s="16"/>
@@ -20252,7 +20278,7 @@
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B8" s="39" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C8" s="138"/>
       <c r="D8" s="138"/>
@@ -20265,7 +20291,7 @@
       <c r="K8" s="138"/>
       <c r="L8" s="127">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>7283496.8976582875</v>
+        <v>7047093.6730966922</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20284,7 +20310,7 @@
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C9" s="138"/>
       <c r="D9" s="138"/>
@@ -20310,7 +20336,7 @@
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C10" s="138"/>
       <c r="D10" s="138"/>
@@ -20319,29 +20345,29 @@
       <c r="G10" s="139"/>
       <c r="H10" s="127">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>124777.98497415465</v>
+        <v>123967.27465316029</v>
       </c>
       <c r="I10" s="127">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>170156.37528950794</v>
+        <v>167952.47062206519</v>
       </c>
       <c r="J10" s="127">
         <f t="shared" ca="1" si="1"/>
-        <v>232037.66319564282</v>
+        <v>227544.18427747994</v>
       </c>
       <c r="K10" s="127">
         <f t="shared" ca="1" si="1"/>
-        <v>316423.50778621982</v>
+        <v>308279.81039358105</v>
       </c>
       <c r="L10" s="127">
         <f t="shared" ca="1" si="1"/>
-        <v>431498.20981999981</v>
+        <v>417661.4831887313</v>
       </c>
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C11" s="138"/>
       <c r="D11" s="138"/>
@@ -20354,43 +20380,43 @@
       <c r="K11" s="138"/>
       <c r="L11" s="127">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>3717647.733128198</v>
+        <v>3595408.7376233903</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="246" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C14" s="247"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="156" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C15" s="157">
         <f ca="1">Overview!C5</f>
-        <v>200.42</v>
+        <v>201.32499999999999</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B16" s="156" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C16" s="157">
         <f ca="1">C36</f>
-        <v>209.28278818982326</v>
+        <v>203.0130562296863</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B17" s="158" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C17" s="159">
-        <v>0.56000000000000005</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="E17" s="248" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F17" s="248"/>
       <c r="G17" s="248"/>
@@ -20400,13 +20426,13 @@
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B19" s="246" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C19" s="247"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="160" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C20" s="161">
         <v>2.5000000000000001E-2</v>
@@ -20414,11 +20440,11 @@
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B21" s="160" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C21" s="229">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14396922377132826</v>
+        <v>0.14406936081805011</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -20432,16 +20458,16 @@
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B23" s="160" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C23" s="162">
         <f ca="1">C15*C22</f>
-        <v>4850164</v>
+        <v>4872065</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B24" s="160" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C24" s="230">
         <f>Statement!AC105</f>
@@ -20450,7 +20476,7 @@
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B25" s="160" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C25" s="230">
         <f>Statement!AC106</f>
@@ -20459,50 +20485,50 @@
     </row>
     <row r="26" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B26" s="158" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C26" s="163">
         <f ca="1">C23+C25-C24</f>
-        <v>4778062</v>
+        <v>4799963</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B28" s="246" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C28" s="247"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="160" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C29" s="162">
         <f ca="1">SUM(H10:L10)</f>
-        <v>1274893.741065525</v>
+        <v>1245405.2231350178</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B30" s="160" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C30" s="162">
         <f ca="1">L11</f>
-        <v>3717647.733128198</v>
+        <v>3595408.7376233903</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B31" s="164" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C31" s="165">
         <f ca="1">C29+C30</f>
-        <v>4992541.4741937229</v>
+        <v>4840813.9607584085</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B32" s="160" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C32" s="166">
         <f>C24</f>
@@ -20511,7 +20537,7 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="160" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C33" s="166">
         <f>C25</f>
@@ -20520,11 +20546,11 @@
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="164" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C34" s="165">
         <f ca="1">C31+C32-C33</f>
-        <v>5064643.4741937229</v>
+        <v>4912915.9607584085</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -20538,16 +20564,16 @@
     </row>
     <row r="36" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B36" s="167" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C36" s="168">
         <f ca="1">C34/C35</f>
-        <v>209.28278818982326</v>
+        <v>203.0130562296863</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="240" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D39" s="240"/>
       <c r="E39" s="240"/>
@@ -20603,7 +20629,7 @@
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="39" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C41" s="113">
         <f>C7</f>
@@ -20627,23 +20653,23 @@
       </c>
       <c r="H41" s="144">
         <f t="shared" si="2"/>
-        <v>142742.17461463416</v>
+        <v>141827.16067479676</v>
       </c>
       <c r="I41" s="144">
         <f t="shared" si="2"/>
-        <v>222677.7923988293</v>
+        <v>219832.09904593497</v>
       </c>
       <c r="J41" s="144">
         <f t="shared" si="2"/>
-        <v>347377.35614217375</v>
+        <v>340739.75352119922</v>
       </c>
       <c r="K41" s="144">
         <f t="shared" si="2"/>
-        <v>541908.67558179109</v>
+        <v>528146.61795785883</v>
       </c>
       <c r="L41" s="144">
         <f t="shared" si="2"/>
-        <v>845377.53390759416</v>
+        <v>818627.25783468119</v>
       </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.2">
@@ -20672,28 +20698,28 @@
       </c>
       <c r="H42" s="144">
         <f>H41/H43</f>
-        <v>129765.61328603105</v>
+        <v>128933.7824316334</v>
       </c>
       <c r="I42" s="144">
         <f t="shared" ref="I42:L42" si="3">I41/I43</f>
-        <v>202434.35672620844</v>
+        <v>199847.36276903178</v>
       </c>
       <c r="J42" s="144">
         <f t="shared" si="3"/>
-        <v>315797.5964928852</v>
+        <v>309763.41229199927</v>
       </c>
       <c r="K42" s="144">
         <f t="shared" si="3"/>
-        <v>492644.25052890094</v>
+        <v>480133.28905259888</v>
       </c>
       <c r="L42" s="144">
         <f t="shared" si="3"/>
-        <v>768525.03082508559</v>
+        <v>744206.59803152829</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B43" s="123" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C43" s="95">
         <f>C41/C42</f>
@@ -20757,28 +20783,28 @@
       </c>
       <c r="H44" s="144">
         <f>H41/H45</f>
-        <v>14274217.461463416</v>
+        <v>14182716.067479676</v>
       </c>
       <c r="I44" s="144">
         <f t="shared" ref="I44:L44" si="5">I41/I45</f>
-        <v>11133889.619941466</v>
+        <v>10991604.952296749</v>
       </c>
       <c r="J44" s="144">
         <f t="shared" si="5"/>
-        <v>8270889.4319565175</v>
+        <v>8112851.2743142666</v>
       </c>
       <c r="K44" s="144">
         <f t="shared" si="5"/>
-        <v>7741552.5083113005</v>
+        <v>7544951.6851122687</v>
       </c>
       <c r="L44" s="144">
         <f t="shared" si="5"/>
-        <v>5635850.2260506283</v>
+        <v>5457515.0522312084</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B45" s="123" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C45" s="95">
         <f>C41/C44</f>
@@ -20818,7 +20844,7 @@
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B46" s="123" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C46" s="138"/>
       <c r="D46" s="95">
@@ -20839,28 +20865,28 @@
       </c>
       <c r="H46" s="170">
         <f t="shared" si="7"/>
-        <v>0.56000000000000028</v>
+        <v>0.55000000000000027</v>
       </c>
       <c r="I46" s="170">
         <f t="shared" si="7"/>
-        <v>0.56000000000000005</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="J46" s="170">
         <f t="shared" si="7"/>
-        <v>0.56000000000000028</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="K46" s="170">
         <f t="shared" si="7"/>
-        <v>0.56000000000000005</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L46" s="170">
         <f t="shared" si="7"/>
-        <v>0.56000000000000005</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B47" s="123" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C47" s="138"/>
       <c r="D47" s="95">
@@ -20881,28 +20907,28 @@
       </c>
       <c r="H47" s="170">
         <f t="shared" si="7"/>
-        <v>-4.7657106457619225E-3</v>
+        <v>-1.1145417628801946E-2</v>
       </c>
       <c r="I47" s="170">
         <f t="shared" si="7"/>
-        <v>0.56000000000000005</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="J47" s="170">
         <f t="shared" si="7"/>
-        <v>0.56000000000000028</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="K47" s="170">
         <f t="shared" si="7"/>
-        <v>0.56000000000000005</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L47" s="170">
         <f t="shared" si="7"/>
-        <v>0.56000000000000028</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B48" s="123" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C48" s="138"/>
       <c r="D48" s="95">
@@ -20923,28 +20949,28 @@
       </c>
       <c r="H48" s="170">
         <f t="shared" si="8"/>
-        <v>65.103314198813621</v>
+        <v>64.679575005231484</v>
       </c>
       <c r="I48" s="170">
         <f t="shared" si="8"/>
-        <v>-0.21999999999999997</v>
+        <v>-0.22499999999999998</v>
       </c>
       <c r="J48" s="170">
         <f t="shared" si="8"/>
-        <v>-0.25714285714285712</v>
+        <v>-0.26190476190476197</v>
       </c>
       <c r="K48" s="170">
         <f t="shared" si="8"/>
-        <v>-6.3999999999999946E-2</v>
+        <v>-6.9999999999999951E-2</v>
       </c>
       <c r="L48" s="170">
         <f t="shared" si="8"/>
-        <v>-0.2719999999999998</v>
+        <v>-0.27666666666666662</v>
       </c>
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B49" s="123" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C49" s="95">
         <f>C42/C44</f>
@@ -21046,45 +21072,45 @@
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
       <c r="M2" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O2" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="P2" s="10" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="Q2" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="R2" s="7"/>
       <c r="S2" s="7"/>
       <c r="T2" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="U2" s="10" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="V2" s="10" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="W2" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="X2" s="10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Y2" s="10" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Z2" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AA2" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AB2" s="7"/>
       <c r="AD2" s="7"/>
@@ -21113,28 +21139,28 @@
       <c r="R3" s="11"/>
       <c r="S3" s="11"/>
       <c r="T3" s="10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="U3" s="10" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="V3" s="10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="W3" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="X3" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="Y3" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="Z3" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="X3" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="Y3" s="10" t="s">
-        <v>358</v>
-      </c>
-      <c r="Z3" s="10" t="s">
-        <v>355</v>
-      </c>
       <c r="AA3" s="10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AB3" s="11"/>
       <c r="AC3" s="59" t="s">
@@ -21443,7 +21469,7 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B9" s="20" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C9" s="21"/>
       <c r="D9" s="21"/>
@@ -21916,7 +21942,7 @@
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B16" s="23" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C16" s="21"/>
       <c r="D16" s="21"/>
@@ -22956,7 +22982,7 @@
     </row>
     <row r="33" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B33" s="20" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C33" s="21"/>
       <c r="D33" s="21"/>
@@ -23271,7 +23297,7 @@
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C38" s="21"/>
       <c r="D38" s="21"/>
@@ -23393,7 +23419,7 @@
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B40" s="20" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C40" s="21"/>
       <c r="D40" s="21"/>
@@ -23650,7 +23676,7 @@
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B44" s="20" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C44" s="21"/>
       <c r="D44" s="21"/>
@@ -23766,7 +23792,7 @@
     </row>
     <row r="46" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C46" s="21"/>
       <c r="D46" s="21"/>
@@ -23824,7 +23850,7 @@
     </row>
     <row r="47" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B47" s="20" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C47" s="21"/>
       <c r="D47" s="21"/>
@@ -24688,7 +24714,7 @@
     </row>
     <row r="63" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B63" s="20" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C63" s="62"/>
       <c r="D63" s="62"/>
@@ -24746,7 +24772,7 @@
     </row>
     <row r="64" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B64" s="20" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C64" s="62"/>
       <c r="D64" s="62"/>
@@ -25347,7 +25373,7 @@
     </row>
     <row r="75" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B75" s="20" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C75" s="25"/>
       <c r="D75" s="25"/>
@@ -25405,7 +25431,7 @@
     </row>
     <row r="76" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B76" s="20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C76" s="25"/>
       <c r="D76" s="25"/>
@@ -25476,7 +25502,7 @@
     </row>
     <row r="77" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B77" s="20" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C77" s="25"/>
       <c r="D77" s="25"/>
@@ -25547,7 +25573,7 @@
     </row>
     <row r="78" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B78" s="20" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C78" s="25"/>
       <c r="D78" s="25"/>
@@ -25589,7 +25615,7 @@
     </row>
     <row r="79" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B79" s="20" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C79" s="25"/>
       <c r="D79" s="25"/>
@@ -26269,7 +26295,7 @@
     </row>
     <row r="92" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B92" s="20" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C92" s="49"/>
       <c r="D92" s="50"/>
@@ -27011,7 +27037,7 @@
     </row>
     <row r="105" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B105" s="20" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C105" s="25"/>
       <c r="D105" s="25"/>
@@ -27082,7 +27108,7 @@
     </row>
     <row r="106" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B106" s="20" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C106" s="25">
         <v>0</v>
@@ -27173,7 +27199,7 @@
     </row>
     <row r="107" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B107" s="20" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C107" s="25"/>
       <c r="D107" s="25"/>
@@ -27220,7 +27246,7 @@
     </row>
     <row r="108" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B108" s="20" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C108" s="25"/>
       <c r="D108" s="25"/>
@@ -27291,7 +27317,7 @@
     </row>
     <row r="109" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B109" s="20" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C109" s="25"/>
       <c r="D109" s="25"/>
@@ -27362,7 +27388,7 @@
     </row>
     <row r="110" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B110" s="20" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C110" s="25"/>
       <c r="D110" s="25"/>
@@ -27495,12 +27521,12 @@
       <c r="AA114" s="68"/>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>200.42</v>
+        <v>201.32499999999999</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B115" s="20" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C115" s="26"/>
       <c r="D115" s="26"/>
@@ -27542,7 +27568,7 @@
       <c r="AA115" s="68"/>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>200.42</v>
+        <v>201.32499999999999</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -27767,7 +27793,7 @@
     </row>
     <row r="126" spans="1:31" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B126" s="14" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C126" s="172"/>
       <c r="D126" s="172"/>
@@ -27796,7 +27822,7 @@
     </row>
     <row r="127" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B127" s="20" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C127" s="49"/>
       <c r="D127" s="49"/>
@@ -27841,7 +27867,7 @@
     </row>
     <row r="128" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B128" s="20" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C128" s="49"/>
       <c r="D128" s="49"/>
@@ -27886,7 +27912,7 @@
     </row>
     <row r="129" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B129" s="20" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C129" s="49"/>
       <c r="D129" s="49"/>
@@ -27939,7 +27965,7 @@
     </row>
     <row r="130" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B130" s="20" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C130" s="49"/>
       <c r="D130" s="49"/>
@@ -27992,7 +28018,7 @@
     </row>
     <row r="131" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B131" s="20" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C131" s="49"/>
       <c r="D131" s="49"/>
@@ -28037,7 +28063,7 @@
     </row>
     <row r="132" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B132" s="20" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C132" s="49"/>
       <c r="D132" s="49"/>
@@ -28082,7 +28108,7 @@
     </row>
     <row r="133" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B133" s="20" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C133" s="49"/>
       <c r="D133" s="49"/>
@@ -28135,7 +28161,7 @@
     </row>
     <row r="134" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B134" s="20" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C134" s="49"/>
       <c r="D134" s="49"/>
@@ -28188,7 +28214,7 @@
     </row>
     <row r="135" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B135" s="20" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C135" s="49"/>
       <c r="D135" s="49"/>
@@ -28233,7 +28259,7 @@
     </row>
     <row r="136" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B136" s="20" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C136" s="49"/>
       <c r="D136" s="49"/>
@@ -28278,7 +28304,7 @@
     </row>
     <row r="137" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B137" s="20" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C137" s="49"/>
       <c r="D137" s="49"/>
@@ -28331,7 +28357,7 @@
     </row>
     <row r="138" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B138" s="20" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C138" s="49"/>
       <c r="D138" s="49"/>
@@ -28387,7 +28413,7 @@
     </row>
     <row r="141" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B141" s="14" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C141" s="172"/>
       <c r="D141" s="172"/>
@@ -28707,7 +28733,7 @@
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B147" s="20" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="M147" s="119">
         <f>M106/M48</f>
@@ -28768,7 +28794,7 @@
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B148" s="20" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="M148" s="181">
         <f>(M106-M105)/M48</f>
@@ -28829,7 +28855,7 @@
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B149" s="20" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M149" s="119">
         <f>(M105+M29)/M39</f>
@@ -28890,7 +28916,7 @@
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B150" s="20" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="M150" s="119">
         <f>M31/M39</f>
@@ -28951,7 +28977,7 @@
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B151" s="20" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="M151" s="183">
         <f>IF(M12&gt;=0,"N/A",IF(M11&lt;=0,"N/A",M11/-M12))</f>
@@ -29012,7 +29038,7 @@
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B152" s="20" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="M152" s="72">
         <f>M115/Statement!M25</f>
@@ -29044,12 +29070,12 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>30.69218989280245</v>
+        <v>30.830781010719758</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B153" s="20" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="M153" s="72">
         <f>M115/(Statement!M5/Statement!M21)</f>
@@ -29081,12 +29107,12 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>19.338647092007211</v>
+        <v>19.425971089703381</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B154" s="20" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M154" s="72">
         <f>M115/(Statement!M48/Statement!M74)</f>
@@ -29118,12 +29144,12 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>24.812322866468175</v>
+        <v>24.924363342439406</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B155" s="20" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M155" s="144">
         <f>Statement!M115*Statement!M77</f>
@@ -29155,12 +29181,12 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="144">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>4871208.0999999996</v>
+        <v>4893204.125</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B156" s="20" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="M156" s="144">
         <f>M155+M106-M105+M47+M44</f>
@@ -29192,12 +29218,12 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="144">
         <f ca="1">AC155+AC106-AC105+AC47+AC44</f>
-        <v>4799106.0999999996</v>
+        <v>4821102.125</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B157" s="20" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="M157" s="185">
         <f>M156/M5</f>
@@ -29229,12 +29255,12 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="185">
         <f ca="1">AC156/AC5</f>
-        <v>18.9320571539029</v>
+        <v>19.01882956396874</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B158" s="20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M158" s="185">
         <f>M156/M11</f>
@@ -29266,12 +29292,12 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="185">
         <f ca="1">AC156/AC11</f>
-        <v>29.572086760945247</v>
+        <v>29.707626243953538</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B159" s="20" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="M159" s="64">
         <f>M58-M53+M108+M64</f>
@@ -29332,7 +29358,7 @@
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B160" s="20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M160" s="64">
         <f>M107+M52+M108+M54+M56+M57+M55</f>
@@ -29369,7 +29395,7 @@
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B161" s="20" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="M161" s="72">
         <f>M155/M159</f>
@@ -29401,12 +29427,12 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="72">
         <f t="shared" ref="AC161:AC162" ca="1" si="96">AC155/AC159</f>
-        <v>43.401089658490513</v>
+        <v>43.597068034605343</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B162" s="20" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="M162" s="72">
         <f>M156/M160</f>
@@ -29438,12 +29464,12 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ca="1" si="96"/>
-        <v>37.843045599226201</v>
+        <v>38.016493853907782</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B163" s="20" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="M163" s="74">
         <f>M159/M155</f>
@@ -29475,12 +29501,12 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="74">
         <f t="shared" ref="AC163" ca="1" si="99">AC159/AC155</f>
-        <v>2.3040896158798882E-2</v>
+        <v>2.2937322280623229E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B164" s="20" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="M164" s="74">
         <f>M25/M115</f>
@@ -29512,12 +29538,12 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>3.2581578684761997E-2</v>
+        <v>3.2435117347572331E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B165" s="20" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="M165" s="155">
         <f>M81/M115</f>
@@ -29549,12 +29575,12 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="155">
         <f ca="1">AC81/AC115</f>
-        <v>1.9958088015168147E-4</v>
+        <v>1.9868372035266362E-4</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B166" s="20" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="M166" s="155">
         <f>-M62/M155</f>
@@ -29586,12 +29612,12 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="155">
         <f ca="1">-AC62/AC155</f>
-        <v>9.300362265369037E-3</v>
+        <v>9.2585550985980983E-3</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B167" s="20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="M167" s="155">
         <f>-(M62+M63)/M155</f>
@@ -29623,12 +29649,12 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="155">
         <f ca="1">-(AC62+AC63)/AC155</f>
-        <v>9.5001073758273647E-3</v>
+        <v>9.4574023110061863E-3</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B168" s="20" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="M168" s="228">
         <f>M160/M5</f>
@@ -29665,7 +29691,7 @@
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B169" s="20" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="M169" s="228">
         <f>M159/M5</f>
@@ -29702,7 +29728,7 @@
     </row>
     <row r="170" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B170" s="20" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="M170" s="155">
         <f>-M63/M159</f>
@@ -29739,7 +29765,7 @@
     </row>
     <row r="171" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B171" s="20" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="M171" s="155">
         <f>-M62/M159</f>
@@ -29776,7 +29802,7 @@
     </row>
     <row r="172" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B172" s="20" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M172" s="155">
         <f>(-M63-M62)/M159</f>
@@ -29813,7 +29839,7 @@
     </row>
     <row r="173" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B173" s="20" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="M173" s="155">
         <f>M79/M77</f>
@@ -29850,7 +29876,7 @@
     </row>
     <row r="174" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B174" s="20" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M174" s="72">
         <f>M105/M74</f>
@@ -29911,7 +29937,7 @@
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B175" s="20" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="M175" s="155">
         <f>M53/M58</f>
@@ -29972,7 +29998,7 @@
     </row>
     <row r="176" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B176" s="20" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M176" s="155">
         <f>M53/M5</f>
@@ -30033,7 +30059,7 @@
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B177" s="20" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="M177" s="72">
         <f>(M105-M106)/M74</f>
@@ -30094,7 +30120,7 @@
     </row>
     <row r="178" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B178" s="20" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="M178" s="155">
         <f>(M105-M106)/M155</f>
@@ -30126,12 +30152,12 @@
       <c r="AA178" s="49"/>
       <c r="AC178" s="155">
         <f ca="1">(AC105-AC106)/AC155</f>
-        <v>1.4801666962247006E-2</v>
+        <v>1.473513022512626E-2</v>
       </c>
     </row>
     <row r="179" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B179" s="20" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="M179" s="155">
         <f>-M108/M5</f>
@@ -30192,7 +30218,7 @@
     </row>
     <row r="180" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B180" s="20" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="M180" s="155">
         <f>-(M108/M58)</f>
@@ -30253,7 +30279,7 @@
     </row>
     <row r="181" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B181" s="20" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="M181" s="155">
         <f>-M108/M52</f>
@@ -30314,7 +30340,7 @@
     </row>
     <row r="182" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B182" s="20" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="M182" s="72">
         <f>M36/M5</f>
@@ -30365,7 +30391,7 @@
     </row>
     <row r="186" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B186" s="226" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C186" s="62"/>
       <c r="D186" s="62"/>
@@ -30423,7 +30449,7 @@
     </row>
     <row r="187" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B187" s="226" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C187" s="62"/>
       <c r="D187" s="62"/>
@@ -30481,7 +30507,7 @@
     </row>
     <row r="188" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B188" s="20" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C188" s="62"/>
       <c r="D188" s="62"/>
@@ -30539,7 +30565,7 @@
     </row>
     <row r="189" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B189" s="20" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C189" s="21"/>
       <c r="D189" s="21"/>
@@ -30615,7 +30641,7 @@
     </row>
     <row r="192" spans="1:31" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B192" s="14" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C192" s="172"/>
       <c r="D192" s="172"/>
@@ -30644,7 +30670,7 @@
     </row>
     <row r="193" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B193" s="226" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C193" s="81"/>
       <c r="D193" s="81"/>
@@ -30718,7 +30744,7 @@
     </row>
     <row r="194" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B194" s="226" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="M194" s="81">
         <f t="shared" si="108"/>
@@ -30776,7 +30802,7 @@
     </row>
     <row r="195" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B195" s="20" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="M195" s="81">
         <f t="shared" si="108"/>
@@ -30834,7 +30860,7 @@
     </row>
     <row r="196" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B196" s="20" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="M196" s="81">
         <f t="shared" si="108"/>
@@ -30895,7 +30921,7 @@
     </row>
     <row r="199" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B199" s="14" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C199" s="172"/>
       <c r="D199" s="172"/>
@@ -30924,7 +30950,7 @@
     </row>
     <row r="200" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B200" s="20" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C200" s="81"/>
       <c r="D200" s="81"/>
@@ -30986,7 +31012,7 @@
     </row>
     <row r="203" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B203" s="14" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C203" s="172"/>
       <c r="D203" s="172"/>
@@ -31015,7 +31041,7 @@
     </row>
     <row r="204" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B204" s="20" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="M204" s="144">
         <v>100</v>
@@ -31048,7 +31074,7 @@
     </row>
     <row r="205" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B205" s="20" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="M205" s="144">
         <v>100</v>
@@ -31081,7 +31107,7 @@
     </row>
     <row r="206" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B206" s="20" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="M206" s="144">
         <v>100</v>
@@ -31153,7 +31179,7 @@
   <sheetData>
     <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
@@ -31176,16 +31202,16 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B1" s="82" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="231" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C4" s="231"/>
       <c r="E4" s="231" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F4" s="231"/>
       <c r="G4" s="231"/>
@@ -31196,23 +31222,23 @@
       </c>
       <c r="C5" s="174">
         <f ca="1">Overview!C5</f>
-        <v>200.42</v>
+        <v>201.32499999999999</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="133" t="s">
+        <v>238</v>
+      </c>
+      <c r="G5" s="133" t="s">
         <v>239</v>
-      </c>
-      <c r="G5" s="133" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B6" s="20" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C6" s="175">
         <f ca="1">Statement!AC155</f>
-        <v>4871208.0999999996</v>
+        <v>4893204.125</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -31228,11 +31254,11 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B7" s="20" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C7" s="175">
         <f ca="1">Statement!AC156</f>
-        <v>4799106.0999999996</v>
+        <v>4821102.125</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -31248,14 +31274,14 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="20" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C8" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>30.69218989280245</v>
+        <v>30.830781010719758</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F8" s="180">
         <f>IF(OR(Statement!M25&lt;=0, Statement!Q25&lt;=0), "N/A", _xlfn.RRI(4, Statement!M25, Statement!Q25))</f>
@@ -31268,14 +31294,14 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B9" s="20" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C9" s="176">
         <f ca="1">Statement!AC153</f>
-        <v>19.338647092007211</v>
+        <v>19.425971089703381</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F9" s="180">
         <f>IF(Statement!M81&lt;=0,"N/A",_xlfn.RRI(4,Statement!M81,Statement!Q81))</f>
@@ -31288,11 +31314,11 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="20" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C10" s="176">
         <f ca="1">Statement!AC154</f>
-        <v>24.812322866468175</v>
+        <v>24.924363342439406</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -31308,20 +31334,20 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B11" s="20" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C11" s="176">
         <f ca="1">Statement!AC157</f>
-        <v>18.9320571539029</v>
+        <v>19.01882956396874</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C12" s="176">
         <f ca="1">Statement!AC158</f>
-        <v>29.572086760945247</v>
+        <v>29.707626243953538</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -31330,7 +31356,7 @@
       </c>
       <c r="C15" s="231"/>
       <c r="E15" s="231" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F15" s="231"/>
     </row>
@@ -31359,7 +31385,7 @@
         <v>0.64020024379563767</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F17" s="175">
         <f>Statement!AC58</f>
@@ -31375,7 +31401,7 @@
         <v>0.62965943564071303</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F18" s="179">
         <f>IF(OR(F16&lt;=0, F17&lt;=0),"N/A",F16-F17)</f>
@@ -31384,11 +31410,11 @@
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B21" s="231" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C21" s="231"/>
       <c r="E21" s="231" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F21" s="231"/>
     </row>
@@ -31460,11 +31486,11 @@
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B29" s="231" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C29" s="231"/>
       <c r="E29" s="231" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F29" s="231"/>
     </row>
@@ -31477,7 +31503,7 @@
         <v>58.61805744582648</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F30" s="182">
         <f>Statement!AC147</f>
@@ -31493,7 +31519,7 @@
         <v>143.6687315949282</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F31" s="182">
         <f>Statement!AC148</f>
@@ -31509,7 +31535,7 @@
         <v>72.939852606844781</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F32" s="182">
         <f>Statement!AC150</f>
@@ -31525,7 +31551,7 @@
         <v>129.34693643390989</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F33" s="182">
         <f>Statement!AC149</f>
@@ -31534,7 +31560,7 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E34" s="20" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F34" s="184" t="str">
         <f>Statement!AC151</f>
@@ -31543,24 +31569,24 @@
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B37" s="231" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C37" s="231"/>
       <c r="E37" s="231" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F37" s="231"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C38" s="177">
         <f ca="1">Statement!AC164</f>
-        <v>3.2581578684761997E-2</v>
+        <v>3.2435117347572331E-2</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F38" s="177">
         <f>Statement!AC170</f>
@@ -31569,14 +31595,14 @@
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B39" s="54" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C39" s="217">
         <f ca="1">Statement!AC163</f>
-        <v>2.3040896158798882E-2</v>
+        <v>2.2937322280623229E-2</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F39" s="177">
         <f>Statement!AC171</f>
@@ -31585,14 +31611,14 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B40" s="20" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C40" s="177">
         <f ca="1">Statement!AC165</f>
-        <v>1.9958088015168147E-4</v>
+        <v>1.9868372035266362E-4</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F40" s="177">
         <f>Statement!AC172</f>
@@ -31601,42 +31627,42 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B41" s="20" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C41" s="177">
         <f ca="1">Statement!AC166</f>
-        <v>9.300362265369037E-3</v>
+        <v>9.2585550985980983E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B42" s="20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C42" s="177">
         <f ca="1">Statement!AC167</f>
-        <v>9.5001073758273647E-3</v>
+        <v>9.4574023110061863E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B45" s="231" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C45" s="231"/>
       <c r="E45" s="231" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F45" s="231"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C46" s="177">
         <f>Statement!AC173</f>
         <v>3.9374614276897757E-2</v>
       </c>
       <c r="E46" s="20" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F46" s="176">
         <f>Statement!AC174</f>
@@ -31645,7 +31671,7 @@
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E47" s="20" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F47" s="176">
         <f>Statement!AC177</f>
@@ -31654,33 +31680,33 @@
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E48" s="20" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F48" s="177">
         <f ca="1">Statement!AC178</f>
-        <v>1.4801666962247006E-2</v>
+        <v>1.473513022512626E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B51" s="231" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C51" s="231"/>
       <c r="E51" s="231" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F51" s="231"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C52" s="177">
         <f>Statement!AC175</f>
         <v>5.4437361220542942E-2</v>
       </c>
       <c r="E52" s="20" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F52" s="177">
         <f>Statement!AC179</f>
@@ -31689,14 +31715,14 @@
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B53" s="20" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C53" s="177">
         <f>Statement!AC176</f>
         <v>2.6983206504372935E-2</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F53" s="177">
         <f>Statement!AC180</f>
@@ -31705,7 +31731,7 @@
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E54" s="20" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F54" s="177">
         <f>Statement!AC181</f>
@@ -31803,7 +31829,7 @@
     </row>
     <row r="5" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
@@ -31838,12 +31864,12 @@
       </c>
       <c r="I6" s="174">
         <f ca="1">Statement!AC114</f>
-        <v>200.42</v>
+        <v>201.32499999999999</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B7" s="20" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C7" s="175">
         <f>Statement!M155</f>
@@ -31867,12 +31893,12 @@
       </c>
       <c r="I7" s="175">
         <f ca="1">Statement!AC155</f>
-        <v>4871208.0999999996</v>
+        <v>4893204.125</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="20" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C8" s="175">
         <f>Statement!M156</f>
@@ -31896,12 +31922,12 @@
       </c>
       <c r="I8" s="175">
         <f ca="1">Statement!AC156</f>
-        <v>4799106.0999999996</v>
+        <v>4821102.125</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B9" s="20" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C9" s="176">
         <f>Statement!M152</f>
@@ -31925,12 +31951,12 @@
       </c>
       <c r="I9" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>30.69218989280245</v>
+        <v>30.830781010719758</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="20" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C10" s="176">
         <f>Statement!M153</f>
@@ -31954,12 +31980,12 @@
       </c>
       <c r="I10" s="176">
         <f ca="1">Statement!AC153</f>
-        <v>19.338647092007211</v>
+        <v>19.425971089703381</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B11" s="20" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C11" s="176">
         <f>Statement!M154</f>
@@ -31983,12 +32009,12 @@
       </c>
       <c r="I11" s="176">
         <f ca="1">Statement!AC154</f>
-        <v>24.812322866468175</v>
+        <v>24.924363342439406</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B12" s="20" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C12" s="176">
         <f>Statement!M157</f>
@@ -32012,12 +32038,12 @@
       </c>
       <c r="I12" s="176">
         <f ca="1">Statement!AC157</f>
-        <v>18.9320571539029</v>
+        <v>19.01882956396874</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B13" s="20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C13" s="176">
         <f>Statement!M158</f>
@@ -32041,7 +32067,7 @@
       </c>
       <c r="I13" s="176">
         <f ca="1">Statement!AC158</f>
-        <v>29.572086760945247</v>
+        <v>29.707626243953538</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -32144,7 +32170,7 @@
     </row>
     <row r="20" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B20" s="14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
@@ -32184,7 +32210,7 @@
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C22" s="179">
         <f>Statement!M58</f>
@@ -32213,7 +32239,7 @@
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B23" s="20" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C23" s="197">
         <f>IF(OR(C21&lt;=0, C22&lt;=0),"N/A",C21-C22)</f>
@@ -32242,7 +32268,7 @@
     </row>
     <row r="25" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B25" s="14" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="14"/>
@@ -32398,7 +32424,7 @@
     </row>
     <row r="32" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B32" s="14" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
@@ -32496,7 +32522,7 @@
     </row>
     <row r="37" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B37" s="14" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C37" s="14"/>
       <c r="D37" s="14"/>
@@ -32623,7 +32649,7 @@
     </row>
     <row r="43" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B43" s="14" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C43" s="14"/>
       <c r="D43" s="14"/>
@@ -32634,7 +32660,7 @@
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B44" s="20" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C44" s="182">
         <f>Statement!M147</f>
@@ -32663,7 +32689,7 @@
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B45" s="20" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C45" s="182">
         <f>Statement!M148</f>
@@ -32692,7 +32718,7 @@
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C46" s="182">
         <f>Statement!M149</f>
@@ -32721,7 +32747,7 @@
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B47" s="20" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C47" s="182">
         <f>Statement!M150</f>
@@ -32750,7 +32776,7 @@
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B48" s="20" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C48" s="184">
         <f>Statement!M151</f>
@@ -32779,7 +32805,7 @@
     </row>
     <row r="50" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B50" s="14" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C50" s="14"/>
       <c r="D50" s="14"/>
@@ -32790,7 +32816,7 @@
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B51" s="20" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C51" s="177">
         <f>Statement!M164</f>
@@ -32814,12 +32840,12 @@
       </c>
       <c r="I51" s="177">
         <f ca="1">Statement!AC164</f>
-        <v>3.2581578684761997E-2</v>
+        <v>3.2435117347572331E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C52" s="177">
         <f>Statement!M163</f>
@@ -32843,12 +32869,12 @@
       </c>
       <c r="I52" s="177">
         <f ca="1">Statement!AC163</f>
-        <v>2.3040896158798882E-2</v>
+        <v>2.2937322280623229E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B53" s="20" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C53" s="177">
         <f>Statement!M165</f>
@@ -32872,12 +32898,12 @@
       </c>
       <c r="I53" s="177">
         <f ca="1">Statement!AC165</f>
-        <v>1.9958088015168147E-4</v>
+        <v>1.9868372035266362E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B54" s="20" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C54" s="177">
         <f>Statement!M166</f>
@@ -32901,12 +32927,12 @@
       </c>
       <c r="I54" s="177">
         <f ca="1">Statement!AC166</f>
-        <v>9.300362265369037E-3</v>
+        <v>9.2585550985980983E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B55" s="20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C55" s="177">
         <f>Statement!M167</f>
@@ -32930,12 +32956,12 @@
       </c>
       <c r="I55" s="177">
         <f ca="1">Statement!AC167</f>
-        <v>9.5001073758273647E-3</v>
+        <v>9.4574023110061863E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B57" s="14" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C57" s="14"/>
       <c r="D57" s="14"/>
@@ -32946,7 +32972,7 @@
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B58" s="20" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C58" s="177">
         <f>Statement!M170</f>
@@ -32975,7 +33001,7 @@
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B59" s="20" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C59" s="177">
         <f>Statement!M171</f>
@@ -33004,7 +33030,7 @@
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B60" s="20" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C60" s="177">
         <f>Statement!M172</f>
@@ -33033,7 +33059,7 @@
     </row>
     <row r="62" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B62" s="14" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C62" s="14"/>
       <c r="D62" s="14"/>
@@ -33044,7 +33070,7 @@
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B63" s="20" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C63" s="177">
         <f>Statement!M173</f>
@@ -33073,7 +33099,7 @@
     </row>
     <row r="65" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B65" s="14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C65" s="14"/>
       <c r="D65" s="14"/>
@@ -33084,7 +33110,7 @@
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B66" s="20" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C66" s="176">
         <f>Statement!M174</f>
@@ -33113,7 +33139,7 @@
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B67" s="20" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C67" s="176">
         <f>Statement!M177</f>
@@ -33142,7 +33168,7 @@
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B68" s="20" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C68" s="198">
         <f>Statement!M178</f>
@@ -33166,12 +33192,12 @@
       </c>
       <c r="I68" s="198">
         <f ca="1">Statement!AC178</f>
-        <v>1.4801666962247006E-2</v>
+        <v>1.473513022512626E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B70" s="14" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C70" s="14"/>
       <c r="D70" s="14"/>
@@ -33182,7 +33208,7 @@
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B71" s="20" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C71" s="177">
         <f>Statement!M175</f>
@@ -33211,7 +33237,7 @@
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B72" s="20" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C72" s="177">
         <f>Statement!M176</f>
@@ -33240,7 +33266,7 @@
     </row>
     <row r="74" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B74" s="14" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C74" s="14"/>
       <c r="D74" s="14"/>
@@ -33251,7 +33277,7 @@
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B75" s="20" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C75" s="177">
         <f>Statement!M179</f>
@@ -33280,7 +33306,7 @@
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B76" s="20" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C76" s="177">
         <f>Statement!M180</f>
@@ -33309,7 +33335,7 @@
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B77" s="20" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C77" s="177">
         <f>Statement!M181</f>
@@ -33453,7 +33479,7 @@
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B84" s="20" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C84" s="177">
         <f>Statement!M94</f>
@@ -33479,7 +33505,7 @@
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B85" s="20" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C85" s="177">
         <f>Statement!M96</f>
@@ -33505,7 +33531,7 @@
     </row>
     <row r="88" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B88" s="14" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C88" s="14"/>
       <c r="D88" s="14"/>
@@ -33516,7 +33542,7 @@
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B89" s="226" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C89" s="177">
         <f>Statement!M193</f>
@@ -33542,7 +33568,7 @@
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B90" s="226" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C90" s="177">
         <f>Statement!M194</f>
@@ -33568,7 +33594,7 @@
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B91" s="20" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C91" s="177">
         <f>Statement!M195</f>
@@ -33594,7 +33620,7 @@
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B92" s="20" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C92" s="177">
         <f>Statement!M196</f>
@@ -33620,7 +33646,7 @@
     </row>
     <row r="94" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B94" s="14" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C94" s="14"/>
       <c r="D94" s="14"/>
@@ -33631,7 +33657,7 @@
     </row>
     <row r="95" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B95" s="20" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C95" s="177">
         <f>Statement!M199</f>
@@ -33679,11 +33705,11 @@
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
       <c r="C3" s="237" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D3" s="238"/>
       <c r="F3" s="239" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G3" s="238"/>
     </row>
@@ -33708,7 +33734,7 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C5" s="10" t="str">
         <f>Statement!Z3</f>
@@ -33750,7 +33776,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B7" s="208" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C7" s="235">
         <f>Statement!AA88</f>
@@ -33789,7 +33815,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B9" s="208" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C9" s="235">
         <f>Statement!AA89</f>
@@ -33828,7 +33854,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B11" s="208" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C11" s="235">
         <f>Statement!AA90</f>
@@ -33867,7 +33893,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B13" s="208" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C13" s="235">
         <f>Statement!AA93</f>
@@ -33885,7 +33911,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="209" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C14" s="202">
         <f>Statement!Z11</f>
@@ -33906,7 +33932,7 @@
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B15" s="208" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C15" s="235">
         <f>Statement!AA94</f>
@@ -33945,7 +33971,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B17" s="208" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C17" s="235">
         <f>Statement!AA96</f>
@@ -33963,7 +33989,7 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="209" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C18" s="202">
         <f>Statement!Z21</f>
@@ -33984,7 +34010,7 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B19" s="208" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C19" s="235">
         <f>IF(C18=0,
@@ -34026,7 +34052,7 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B21" s="208" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C21" s="235">
         <f>IF(C20=0,
@@ -34047,7 +34073,7 @@
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C23" s="10" t="str">
         <f>C5</f>
@@ -34068,7 +34094,7 @@
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B24" s="226" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C24" s="202">
         <f>Statement!Z186</f>
@@ -34089,7 +34115,7 @@
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B25" s="208" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C25" s="235">
         <f>IF(C24=0,
@@ -34110,7 +34136,7 @@
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="226" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C26" s="202">
         <f>Statement!Z187</f>
@@ -34131,7 +34157,7 @@
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B27" s="208" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C27" s="235">
         <f>IF(C26=0,
@@ -34152,7 +34178,7 @@
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C28" s="202">
         <f>Statement!Z188</f>
@@ -34173,7 +34199,7 @@
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B29" s="208" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C29" s="235">
         <f>IF(C28=0,
@@ -34194,7 +34220,7 @@
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C30" s="202">
         <f>Statement!Z189</f>
@@ -34215,7 +34241,7 @@
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="208" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C31" s="235">
         <f>IF(C30=0,
@@ -34503,7 +34529,7 @@
     </row>
     <row r="60" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B60" s="20" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C60" s="64">
         <f>Statement!H159</f>
@@ -34548,7 +34574,7 @@
     </row>
     <row r="61" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B61" s="20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C61" s="64">
         <f>Statement!H160</f>
@@ -34728,7 +34754,7 @@
     </row>
     <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B65" s="20" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C65" s="64">
         <f>Statement!H186</f>
@@ -34773,7 +34799,7 @@
     </row>
     <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B66" s="20" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C66" s="64">
         <f>Statement!H187</f>
@@ -34818,7 +34844,7 @@
     </row>
     <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B67" s="20" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C67" s="64">
         <f>Statement!H189</f>
@@ -35306,7 +35332,7 @@
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B63" s="20" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C63" s="64">
         <f>Statement!T186</f>
@@ -35343,7 +35369,7 @@
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B64" s="20" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C64" s="64">
         <f>Statement!T187</f>
@@ -35380,7 +35406,7 @@
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B65" s="20" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C65" s="64">
         <f>Statement!T189</f>
@@ -35417,7 +35443,7 @@
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B66" s="20" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C66" s="64">
         <f>Statement!T159</f>

--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74BF92DD-37A0-1943-82B4-DD320AE0F36A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61AC8C39-E425-DE46-8C76-4807F3696AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="9" activeTab="19" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -117,7 +117,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -128,28 +128,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -159,28 +138,19 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
     </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
-    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="399">
   <si>
     <t>Ticker</t>
   </si>
@@ -1352,9 +1322,6 @@
     <t>Manual WACC</t>
   </si>
   <si>
-    <t>Capital intensity</t>
-  </si>
-  <si>
     <t>Common size growth rates</t>
   </si>
   <si>
@@ -1368,6 +1335,18 @@
   </si>
   <si>
     <t>Marketable securities and investments</t>
+  </si>
+  <si>
+    <t>Debt/EBIT</t>
+  </si>
+  <si>
+    <t>Net Debt/EBIT</t>
+  </si>
+  <si>
+    <t>Sales/Invested Capital</t>
+  </si>
+  <si>
+    <t>Sales/Assets</t>
   </si>
 </sst>
 </file>
@@ -2191,9 +2170,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="2" fontId="10" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2262,7 +2238,6 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="0" fillId="17" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -2281,9 +2256,10 @@
     <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="10" fontId="12" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="16" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2291,6 +2267,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -11701,7 +11680,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1yv52&amp;q=XNAS%3aNVDA&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -11719,10 +11698,12 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>236.54</v>
-    <v>140.85499999999999</v>
-    <v>2.1962000000000002</v>
-    <v>0.90500000000000003</v>
-    <v>4.516E-3</v>
+    <v>142.03</v>
+    <v>2.2052999999999998</v>
+    <v>-2.76</v>
+    <v>-1.3306999999999999E-2</v>
+    <v>0.42799999999999999</v>
+    <v>2.091E-3</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -11730,49 +11711,35 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2788 San Tomas Expressway, SANTA CLARA, CA, 95051 US</v>
-    <v>203.65</v>
+    <v>209.21</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46184.655324120315</v>
+    <v>46190.871673020316</v>
     <v>0</v>
-    <v>199.54</v>
-    <v>4872065000000</v>
+    <v>203.08</v>
+    <v>4952530000000</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
-    <v>201.58</v>
-    <v>30.8308</v>
-    <v>200.42</v>
-    <v>201.32499999999999</v>
+    <v>208.53</v>
+    <v>31.34</v>
+    <v>207.41</v>
+    <v>204.65</v>
+    <v>205.078</v>
     <v>24200000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>51798653</v>
-    <v>175771962</v>
+    <v>126195668</v>
+    <v>171485621</v>
     <v>1998</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -11786,28 +11753,28 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>0.14000000000000001</v>
-    <v>3.0919999999999997E-3</v>
+    <v>-0.41</v>
+    <v>-9.1739999999999999E-3</v>
     <v>US</v>
-    <v>45.6</v>
+    <v>44.59</v>
     <v>Index</v>
-    <v>6</v>
-    <v>45.13</v>
+    <v>3</v>
+    <v>44.2</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>45.34</v>
-    <v>45.28</v>
-    <v>45.42</v>
+    <v>44.43</v>
+    <v>44.69</v>
+    <v>44.28</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -11829,6 +11796,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -11849,6 +11818,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -11858,11 +11828,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -11898,7 +11863,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -11909,13 +11874,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -12009,13 +11977,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -12087,6 +12061,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -12094,6 +12071,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -12561,7 +12541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825B172E-7ADE-4B4A-B533-F037BCFCDCB0}">
-  <dimension ref="B1:I49"/>
+  <dimension ref="B1:I59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -12578,338 +12558,338 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="232" t="s">
+      <c r="B2" s="231" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="233"/>
-      <c r="E2" s="232" t="s">
+      <c r="C2" s="232"/>
+      <c r="E2" s="231" t="s">
         <v>284</v>
       </c>
-      <c r="F2" s="233"/>
-      <c r="H2" s="232" t="s">
+      <c r="F2" s="232"/>
+      <c r="H2" s="231" t="s">
         <v>325</v>
       </c>
-      <c r="I2" s="233"/>
+      <c r="I2" s="232"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B3" s="187" t="s">
+      <c r="B3" s="186" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="219" t="e" vm="1">
+      <c r="C3" s="218" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
       <c r="D3" s="2"/>
-      <c r="E3" s="187" t="s">
+      <c r="E3" s="186" t="s">
         <v>236</v>
       </c>
-      <c r="F3" s="189">
+      <c r="F3" s="188">
         <f ca="1">Statement!AC155</f>
-        <v>4893204.125</v>
-      </c>
-      <c r="H3" s="187" t="str">
+        <v>4974018.25</v>
+      </c>
+      <c r="H3" s="186" t="str">
         <f>'AVG target price'!B5</f>
         <v>DCF price</v>
       </c>
-      <c r="I3" s="213">
-        <f ca="1">'AVG target price'!C5</f>
-        <v>130.06128089086198</v>
+      <c r="I3" s="212">
+        <f>'AVG target price'!C5</f>
+        <v>168.2356845632454</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B4" s="187" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="191" t="str" cm="1">
+      <c r="B4" s="186" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="190" t="str" cm="1">
         <f t="array" aca="1" ref="C4" ca="1">_FV(C3,"Ticker symbol",TRUE)</f>
         <v>NVDA</v>
       </c>
-      <c r="E4" s="188" t="s">
+      <c r="E4" s="187" t="s">
         <v>180</v>
       </c>
-      <c r="F4" s="190">
+      <c r="F4" s="189">
         <f ca="1">Statement!AC156</f>
-        <v>4821102.125</v>
-      </c>
-      <c r="H4" s="187" t="str">
+        <v>4901916.25</v>
+      </c>
+      <c r="H4" s="186" t="str">
         <f>'AVG target price'!B6</f>
         <v>EV/EBIT price</v>
       </c>
-      <c r="I4" s="213">
-        <f ca="1">'AVG target price'!C6</f>
-        <v>327.7925765771455</v>
+      <c r="I4" s="212">
+        <f>'AVG target price'!C6</f>
+        <v>364.31185306105914</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B5" s="187" t="s">
+      <c r="B5" s="186" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="210" cm="1">
+      <c r="C5" s="209" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>201.32499999999999</v>
-      </c>
-      <c r="E5" s="187" t="s">
+        <v>204.65</v>
+      </c>
+      <c r="E5" s="186" t="s">
         <v>240</v>
       </c>
-      <c r="F5" s="191">
+      <c r="F5" s="190">
         <f>Statement!AC25</f>
         <v>6.5299999999999994</v>
       </c>
-      <c r="H5" s="187" t="str">
+      <c r="H5" s="186" t="str">
         <f>'AVG target price'!B7</f>
         <v>PS price</v>
       </c>
-      <c r="I5" s="213">
+      <c r="I5" s="212">
         <f>'AVG target price'!C7</f>
         <v>304.38678708173404</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B6" s="187" t="s">
+      <c r="B6" s="186" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="210" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E6" s="187" t="s">
+      <c r="C6" s="209" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>205.078</v>
+      </c>
+      <c r="E6" s="186" t="s">
         <v>234</v>
       </c>
-      <c r="F6" s="192">
+      <c r="F6" s="191">
         <f ca="1">Statement!AC152</f>
-        <v>30.830781010719758</v>
-      </c>
-      <c r="H6" s="187" t="str">
+        <v>31.339969372128643</v>
+      </c>
+      <c r="H6" s="186" t="str">
         <f>'AVG target price'!B8</f>
         <v>EV/FCFF price</v>
       </c>
-      <c r="I6" s="213">
-        <f ca="1">'AVG target price'!C8</f>
-        <v>314.99385397207828</v>
+      <c r="I6" s="212">
+        <f>'AVG target price'!C8</f>
+        <v>350.07748183234139</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B7" s="187" t="s">
+      <c r="B7" s="186" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>0.90500000000000003</v>
-      </c>
-      <c r="E7" s="188" t="s">
+        <v>-2.76</v>
+      </c>
+      <c r="E7" s="187" t="s">
         <v>193</v>
       </c>
-      <c r="F7" s="193">
+      <c r="F7" s="192">
         <f ca="1">Statement!AC153</f>
-        <v>19.425971089703381</v>
-      </c>
-      <c r="H7" s="186" t="str">
+        <v>19.746802351957271</v>
+      </c>
+      <c r="H7" s="185" t="str">
         <f>'AVG target price'!B9</f>
         <v>AVG price</v>
       </c>
-      <c r="I7" s="214">
-        <f ca="1">'AVG target price'!C9</f>
-        <v>269.30862463045497</v>
+      <c r="I7" s="213">
+        <f>'AVG target price'!C9</f>
+        <v>296.75295163459498</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B8" s="187" t="s">
+      <c r="B8" s="186" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E8" s="187" t="s">
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>0.42799999999999999</v>
+      </c>
+      <c r="E8" s="186" t="s">
         <v>262</v>
       </c>
-      <c r="F8" s="194">
+      <c r="F8" s="193">
         <f ca="1">Statement!AC163</f>
-        <v>2.2937322280623229E-2</v>
-      </c>
-      <c r="H8" s="186" t="str">
+        <v>2.2564653838976163E-2</v>
+      </c>
+      <c r="H8" s="185" t="str">
         <f>'AVG target price'!B11</f>
         <v>Upside/Downside</v>
       </c>
-      <c r="I8" s="215">
+      <c r="I8" s="214">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.33768098661594431</v>
+        <v>0.45005107077740031</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B9" s="187" t="s">
+      <c r="B9" s="186" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>4.516E-3</v>
-      </c>
-      <c r="E9" s="187" t="s">
+        <v>-1.3306999999999999E-2</v>
+      </c>
+      <c r="E9" s="186" t="s">
         <v>285</v>
       </c>
-      <c r="F9" s="194">
+      <c r="F9" s="193">
         <f ca="1">Statement!AC164</f>
-        <v>3.2435117347572331E-2</v>
+        <v>3.1908135841680917E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B10" s="187" t="s">
+      <c r="B10" s="186" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E10" s="187" t="s">
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>2.091E-3</v>
+      </c>
+      <c r="E10" s="186" t="s">
         <v>290</v>
       </c>
-      <c r="F10" s="194">
+      <c r="F10" s="193">
         <f ca="1">Statement!AC166</f>
-        <v>9.2585550985980983E-3</v>
+        <v>9.108129026265635E-3</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B11" s="187" t="s">
+      <c r="B11" s="186" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="211" cm="1">
+      <c r="C11" s="210" cm="1">
         <f t="array" aca="1" ref="C11" ca="1">_FV(C3,"52 week high",TRUE)</f>
         <v>236.54</v>
       </c>
-      <c r="E11" s="188" t="s">
+      <c r="E11" s="187" t="s">
         <v>286</v>
       </c>
-      <c r="F11" s="195">
+      <c r="F11" s="194">
         <f ca="1">Statement!AC165</f>
-        <v>1.9868372035266362E-4</v>
+        <v>1.9545565599804544E-4</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B12" s="187" t="s">
+      <c r="B12" s="186" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="211" cm="1">
+      <c r="C12" s="210" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>140.85499999999999</v>
-      </c>
-      <c r="E12" s="187" t="s">
+        <v>142.03</v>
+      </c>
+      <c r="E12" s="186" t="s">
         <v>94</v>
       </c>
-      <c r="F12" s="194">
+      <c r="F12" s="193">
         <f>Statement!AC121</f>
         <v>0.61514063066049007</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B13" s="187" t="s">
+      <c r="B13" s="186" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="211" cm="1">
+      <c r="C13" s="210" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.1962000000000002</v>
-      </c>
-      <c r="E13" s="187" t="s">
+        <v>2.2052999999999998</v>
+      </c>
+      <c r="E13" s="186" t="s">
         <v>96</v>
       </c>
-      <c r="F13" s="194">
+      <c r="F13" s="193">
         <f>Statement!AC123</f>
         <v>0.81654337661274645</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B14" s="188" t="s">
+      <c r="B14" s="187" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="212" cm="1">
+      <c r="C14" s="211" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>175771962</v>
-      </c>
-      <c r="E14" s="188" t="s">
+        <v>171485621</v>
+      </c>
+      <c r="E14" s="187" t="s">
         <v>97</v>
       </c>
-      <c r="F14" s="195">
+      <c r="F14" s="194">
         <f>Statement!AC142</f>
         <v>1.1082908941558067</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="E15" s="187" t="s">
+      <c r="E15" s="186" t="s">
         <v>287</v>
       </c>
-      <c r="F15" s="194">
+      <c r="F15" s="193">
         <f ca="1">Statement!AC178</f>
-        <v>1.473513022512626E-2</v>
+        <v>1.4495724859875615E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="E16" s="188" t="s">
+      <c r="E16" s="187" t="s">
         <v>292</v>
       </c>
-      <c r="F16" s="193">
+      <c r="F16" s="192">
         <f>Statement!AC177</f>
         <v>2.9794214876033056</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="234" t="s">
+      <c r="B17" s="233" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="234"/>
-      <c r="E17" s="186" t="s">
+      <c r="C17" s="233"/>
+      <c r="E17" s="185" t="s">
         <v>293</v>
       </c>
-      <c r="F17" s="196">
+      <c r="F17" s="195">
         <f>Statement!AC173</f>
         <v>3.9374614276897757E-2</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B18" s="186" t="s">
+      <c r="B18" s="185" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="69" t="s">
         <v>343</v>
       </c>
-      <c r="E18" s="187" t="s">
+      <c r="E18" s="186" t="s">
         <v>294</v>
       </c>
-      <c r="F18" s="192">
+      <c r="F18" s="191">
         <f>Statement!AC146</f>
         <v>129.34693643390989</v>
       </c>
       <c r="I18" s="50"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="186" t="s">
+      <c r="B19" s="185" t="s">
         <v>13</v>
       </c>
       <c r="C19" s="70">
         <v>1000000</v>
       </c>
-      <c r="E19" s="187" t="s">
+      <c r="E19" s="186" t="s">
         <v>255</v>
       </c>
-      <c r="F19" s="192">
+      <c r="F19" s="191">
         <f>Statement!AC148</f>
         <v>-0.36885723932594616</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B20" s="186" t="s">
+      <c r="B20" s="185" t="s">
         <v>84</v>
       </c>
       <c r="C20" s="69" t="s">
         <v>350</v>
       </c>
-      <c r="E20" s="188" t="s">
+      <c r="E20" s="187" t="s">
         <v>295</v>
       </c>
-      <c r="F20" s="193">
+      <c r="F20" s="192">
         <f>Statement!AC149</f>
         <v>2.7636951964269438</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B21" s="186" t="s">
+      <c r="B21" s="185" t="s">
         <v>85</v>
       </c>
       <c r="C21" s="69" t="s">
@@ -12918,7 +12898,7 @@
       <c r="I21" s="50"/>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B22" s="186" t="s">
+      <c r="B22" s="185" t="s">
         <v>87</v>
       </c>
       <c r="C22" s="69" t="s">
@@ -12926,71 +12906,71 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="234" t="s">
+      <c r="B25" s="233" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="234"/>
-      <c r="E25" s="232" t="s">
+      <c r="C25" s="233"/>
+      <c r="E25" s="231" t="s">
         <v>340</v>
       </c>
-      <c r="F25" s="233"/>
+      <c r="F25" s="232"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B26" s="186" t="s">
+      <c r="B26" s="185" t="s">
         <v>100</v>
       </c>
       <c r="C26" s="171">
         <v>0.21</v>
       </c>
-      <c r="E26" s="187" t="e" vm="5">
+      <c r="E26" s="186" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="F26" s="222" cm="1">
+      <c r="F26" s="220" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>45.42</v>
+        <v>44.28</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B27" s="186" t="s">
+      <c r="B27" s="185" t="s">
         <v>164</v>
       </c>
-      <c r="C27" s="224">
+      <c r="C27" s="222">
         <v>5.0999999999999997E-2</v>
       </c>
-      <c r="E27" s="188" t="s">
+      <c r="E27" s="187" t="s">
         <v>341</v>
       </c>
-      <c r="F27" s="223">
+      <c r="F27" s="221">
         <f ca="1">F26/1000</f>
-        <v>4.5420000000000002E-2</v>
+        <v>4.428E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="186" t="s">
+      <c r="B28" s="185" t="s">
         <v>389</v>
       </c>
-      <c r="C28" s="224">
-        <v>0</v>
+      <c r="C28" s="222">
+        <v>0.12</v>
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B29" s="186" t="s">
+      <c r="B29" s="185" t="s">
         <v>388</v>
       </c>
-      <c r="C29" s="224">
+      <c r="C29" s="222">
         <v>0.12</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="231" t="s">
+      <c r="B33" s="234" t="s">
         <v>335</v>
       </c>
-      <c r="C33" s="231"/>
-      <c r="D33" s="231"/>
-      <c r="E33" s="231"/>
-      <c r="F33" s="231"/>
-      <c r="G33" s="231"/>
-      <c r="H33" s="231"/>
+      <c r="C33" s="234"/>
+      <c r="D33" s="234"/>
+      <c r="E33" s="234"/>
+      <c r="F33" s="234"/>
+      <c r="G33" s="234"/>
+      <c r="H33" s="234"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -13009,24 +12989,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="231"/>
-      <c r="C39" s="231"/>
-      <c r="D39" s="231"/>
-      <c r="E39" s="231"/>
-      <c r="F39" s="231"/>
-      <c r="G39" s="231"/>
-      <c r="H39" s="231"/>
+      <c r="B39" s="234"/>
+      <c r="C39" s="234"/>
+      <c r="D39" s="234"/>
+      <c r="E39" s="234"/>
+      <c r="F39" s="234"/>
+      <c r="G39" s="234"/>
+      <c r="H39" s="234"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="231" t="s">
+      <c r="B42" s="234" t="s">
         <v>338</v>
       </c>
-      <c r="C42" s="231"/>
-      <c r="D42" s="231"/>
-      <c r="E42" s="231"/>
-      <c r="F42" s="231"/>
-      <c r="G42" s="231"/>
-      <c r="H42" s="231"/>
+      <c r="C42" s="234"/>
+      <c r="D42" s="234"/>
+      <c r="E42" s="234"/>
+      <c r="F42" s="234"/>
+      <c r="G42" s="234"/>
+      <c r="H42" s="234"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -13035,22 +13015,56 @@
       <c r="C44" s="41" t="s">
         <v>326</v>
       </c>
-      <c r="D44" s="41" t="s">
+      <c r="D44" s="41"/>
+      <c r="E44" s="41" t="s">
         <v>327</v>
       </c>
-      <c r="E44" s="220"/>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="231"/>
-      <c r="C49" s="231"/>
-      <c r="D49" s="231"/>
-      <c r="E49" s="231"/>
-      <c r="F49" s="231"/>
-      <c r="G49" s="231"/>
-      <c r="H49" s="231"/>
+      <c r="B49" s="234"/>
+      <c r="C49" s="234"/>
+      <c r="D49" s="234"/>
+      <c r="E49" s="234"/>
+      <c r="F49" s="234"/>
+      <c r="G49" s="234"/>
+      <c r="H49" s="234"/>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B52" s="234" t="s">
+        <v>101</v>
+      </c>
+      <c r="C52" s="234"/>
+      <c r="D52" s="234"/>
+      <c r="E52" s="234"/>
+      <c r="F52" s="234"/>
+      <c r="G52" s="234"/>
+      <c r="H52" s="234"/>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B54" s="41" t="s">
+        <v>339</v>
+      </c>
+      <c r="C54" s="41" t="s">
+        <v>326</v>
+      </c>
+      <c r="D54" s="41"/>
+      <c r="E54" s="41" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B59" s="234"/>
+      <c r="C59" s="234"/>
+      <c r="D59" s="234"/>
+      <c r="E59" s="234"/>
+      <c r="F59" s="234"/>
+      <c r="G59" s="234"/>
+      <c r="H59" s="234"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B59:H59"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B42:H42"/>
@@ -13130,36 +13144,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="231" t="s">
+      <c r="C2" s="234" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="231"/>
-      <c r="E2" s="231"/>
-      <c r="F2" s="231"/>
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="234"/>
       <c r="G2" s="243"/>
       <c r="H2" s="244" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="231"/>
-      <c r="J2" s="231"/>
-      <c r="K2" s="231"/>
-      <c r="L2" s="231"/>
+      <c r="I2" s="234"/>
+      <c r="J2" s="234"/>
+      <c r="K2" s="234"/>
+      <c r="L2" s="234"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="231" t="s">
+      <c r="S2" s="234" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="231"/>
-      <c r="U2" s="231"/>
-      <c r="V2" s="231"/>
-      <c r="W2" s="231"/>
-      <c r="X2" s="231"/>
-      <c r="Y2" s="231"/>
-      <c r="Z2" s="231"/>
-      <c r="AA2" s="231" t="s">
+      <c r="T2" s="234"/>
+      <c r="U2" s="234"/>
+      <c r="V2" s="234"/>
+      <c r="W2" s="234"/>
+      <c r="X2" s="234"/>
+      <c r="Y2" s="234"/>
+      <c r="Z2" s="234"/>
+      <c r="AA2" s="234" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="231"/>
-      <c r="AC2" s="231"/>
+      <c r="AB2" s="234"/>
+      <c r="AC2" s="234"/>
       <c r="AE2" s="85" t="s">
         <v>107</v>
       </c>
@@ -13293,28 +13307,28 @@
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B6" s="227" t="str">
-        <f>Statement!B186</f>
+      <c r="B6" s="225" t="str">
+        <f>Statement!B189</f>
         <v>HyperScale</v>
       </c>
       <c r="C6" s="88">
-        <f>Statement!M186</f>
+        <f>Statement!M189</f>
         <v>0</v>
       </c>
       <c r="D6" s="88">
-        <f>Statement!N186</f>
+        <f>Statement!N189</f>
         <v>0</v>
       </c>
       <c r="E6" s="88">
-        <f>Statement!O186</f>
+        <f>Statement!O189</f>
         <v>0</v>
       </c>
       <c r="F6" s="88">
-        <f>Statement!P186</f>
+        <f>Statement!P189</f>
         <v>53796</v>
       </c>
       <c r="G6" s="89">
-        <f>Statement!Q186</f>
+        <f>Statement!Q189</f>
         <v>105636</v>
       </c>
       <c r="H6" s="64">
@@ -13344,40 +13358,40 @@
       <c r="Q6" s="90" t="s">
         <v>381</v>
       </c>
-      <c r="R6" s="227" t="str">
+      <c r="R6" s="225" t="str">
         <f>B6</f>
         <v>HyperScale</v>
       </c>
       <c r="S6" s="88">
-        <f>Statement!T186</f>
+        <f>Statement!T189</f>
         <v>10622</v>
       </c>
       <c r="T6" s="88">
-        <f>Statement!U186</f>
+        <f>Statement!U189</f>
         <v>13390</v>
       </c>
       <c r="U6" s="88">
-        <f>Statement!V186</f>
+        <f>Statement!V189</f>
         <v>19094</v>
       </c>
       <c r="V6" s="88">
-        <f>Statement!W186</f>
+        <f>Statement!W189</f>
         <v>17599</v>
       </c>
       <c r="W6" s="88">
-        <f>Statement!X186</f>
+        <f>Statement!X189</f>
         <v>23883</v>
       </c>
       <c r="X6" s="88">
-        <f>Statement!Y186</f>
+        <f>Statement!Y189</f>
         <v>30340</v>
       </c>
       <c r="Y6" s="88">
-        <f>Statement!Z186</f>
+        <f>Statement!Z189</f>
         <v>33814</v>
       </c>
       <c r="Z6" s="89">
-        <f>Statement!AA186</f>
+        <f>Statement!AA189</f>
         <v>37869</v>
       </c>
       <c r="AA6" s="64">
@@ -13392,28 +13406,28 @@
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B7" s="227" t="str">
-        <f>Statement!B187</f>
+      <c r="B7" s="225" t="str">
+        <f>Statement!B190</f>
         <v>AI Clouds</v>
       </c>
       <c r="C7" s="88">
-        <f>Statement!M187</f>
+        <f>Statement!M190</f>
         <v>0</v>
       </c>
       <c r="D7" s="88">
-        <f>Statement!N187</f>
+        <f>Statement!N190</f>
         <v>0</v>
       </c>
       <c r="E7" s="88">
-        <f>Statement!O187</f>
+        <f>Statement!O190</f>
         <v>0</v>
       </c>
       <c r="F7" s="88">
-        <f>Statement!P187</f>
+        <f>Statement!P190</f>
         <v>61390</v>
       </c>
       <c r="G7" s="89">
-        <f>Statement!Q187</f>
+        <f>Statement!Q190</f>
         <v>88101</v>
       </c>
       <c r="H7" s="64">
@@ -13443,40 +13457,40 @@
       <c r="Q7" s="90" t="s">
         <v>382</v>
       </c>
-      <c r="R7" s="227" t="str">
+      <c r="R7" s="225" t="str">
         <f t="shared" ref="R7:R9" si="2">B7</f>
         <v>AI Clouds</v>
       </c>
       <c r="S7" s="88">
-        <f>Statement!T187</f>
+        <f>Statement!T190</f>
         <v>15650</v>
       </c>
       <c r="T7" s="88">
-        <f>Statement!U187</f>
+        <f>Statement!U190</f>
         <v>17381</v>
       </c>
       <c r="U7" s="88">
-        <f>Statement!V187</f>
+        <f>Statement!V190</f>
         <v>16486</v>
       </c>
       <c r="V7" s="88">
-        <f>Statement!W187</f>
+        <f>Statement!W190</f>
         <v>21513</v>
       </c>
       <c r="W7" s="88">
-        <f>Statement!X187</f>
+        <f>Statement!X190</f>
         <v>17213</v>
       </c>
       <c r="X7" s="88">
-        <f>Statement!Y187</f>
+        <f>Statement!Y190</f>
         <v>20875</v>
       </c>
       <c r="Y7" s="88">
-        <f>Statement!Z187</f>
+        <f>Statement!Z190</f>
         <v>28500</v>
       </c>
       <c r="Z7" s="89">
-        <f>Statement!AA187</f>
+        <f>Statement!AA190</f>
         <v>37377</v>
       </c>
       <c r="AA7" s="64">
@@ -13492,27 +13506,27 @@
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="str">
-        <f>Statement!B188</f>
+        <f>Statement!B191</f>
         <v>Data Center</v>
       </c>
       <c r="C8" s="88">
-        <f>Statement!M188</f>
+        <f>Statement!M191</f>
         <v>0</v>
       </c>
       <c r="D8" s="88">
-        <f>Statement!N188</f>
+        <f>Statement!N191</f>
         <v>0</v>
       </c>
       <c r="E8" s="88">
-        <f>Statement!O188</f>
+        <f>Statement!O191</f>
         <v>0</v>
       </c>
       <c r="F8" s="88">
-        <f>Statement!P188</f>
+        <f>Statement!P191</f>
         <v>115186</v>
       </c>
       <c r="G8" s="89">
-        <f>Statement!Q188</f>
+        <f>Statement!Q191</f>
         <v>193737</v>
       </c>
       <c r="H8" s="64">
@@ -13543,35 +13557,35 @@
         <v>Data Center</v>
       </c>
       <c r="S8" s="88">
-        <f>Statement!T188</f>
+        <f>Statement!T191</f>
         <v>26272</v>
       </c>
       <c r="T8" s="88">
-        <f>Statement!U188</f>
+        <f>Statement!U191</f>
         <v>30771</v>
       </c>
       <c r="U8" s="88">
-        <f>Statement!V188</f>
+        <f>Statement!V191</f>
         <v>35580</v>
       </c>
       <c r="V8" s="88">
-        <f>Statement!W188</f>
+        <f>Statement!W191</f>
         <v>39112</v>
       </c>
       <c r="W8" s="88">
-        <f>Statement!X188</f>
+        <f>Statement!X191</f>
         <v>41096</v>
       </c>
       <c r="X8" s="88">
-        <f>Statement!Y188</f>
+        <f>Statement!Y191</f>
         <v>51215</v>
       </c>
       <c r="Y8" s="88">
-        <f>Statement!Z188</f>
+        <f>Statement!Z191</f>
         <v>62314</v>
       </c>
       <c r="Z8" s="89">
-        <f>Statement!AA188</f>
+        <f>Statement!AA191</f>
         <v>75246</v>
       </c>
       <c r="AA8" s="64">
@@ -13587,27 +13601,27 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="str">
-        <f>Statement!B189</f>
+        <f>Statement!B192</f>
         <v>Edge Computing</v>
       </c>
       <c r="C9" s="88">
-        <f>Statement!M189</f>
+        <f>Statement!M192</f>
         <v>0</v>
       </c>
       <c r="D9" s="88">
-        <f>Statement!N189</f>
+        <f>Statement!N192</f>
         <v>0</v>
       </c>
       <c r="E9" s="88">
-        <f>Statement!O189</f>
+        <f>Statement!O192</f>
         <v>0</v>
       </c>
       <c r="F9" s="88">
-        <f>Statement!P189</f>
+        <f>Statement!P192</f>
         <v>15311</v>
       </c>
       <c r="G9" s="89">
-        <f>Statement!Q189</f>
+        <f>Statement!Q192</f>
         <v>22201</v>
       </c>
       <c r="H9" s="64">
@@ -13642,35 +13656,35 @@
         <v>Edge Computing</v>
       </c>
       <c r="S9" s="88">
-        <f>Statement!T189</f>
+        <f>Statement!T192</f>
         <v>3768</v>
       </c>
       <c r="T9" s="88">
-        <f>Statement!U189</f>
+        <f>Statement!U192</f>
         <v>4311</v>
       </c>
       <c r="U9" s="88">
-        <f>Statement!V189</f>
+        <f>Statement!V192</f>
         <v>3751</v>
       </c>
       <c r="V9" s="88">
-        <f>Statement!W189</f>
+        <f>Statement!W192</f>
         <v>4950</v>
       </c>
       <c r="W9" s="88">
-        <f>Statement!X189</f>
+        <f>Statement!X192</f>
         <v>5647</v>
       </c>
       <c r="X9" s="88">
-        <f>Statement!Y189</f>
+        <f>Statement!Y192</f>
         <v>5791</v>
       </c>
       <c r="Y9" s="88">
-        <f>Statement!Z189</f>
+        <f>Statement!Z192</f>
         <v>5813</v>
       </c>
       <c r="Z9" s="89">
-        <f>Statement!AA189</f>
+        <f>Statement!AA192</f>
         <v>6369</v>
       </c>
       <c r="AA9" s="64">
@@ -13903,7 +13917,7 @@
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B14" s="227" t="str">
+      <c r="B14" s="225" t="str">
         <f>B6</f>
         <v>HyperScale</v>
       </c>
@@ -13941,7 +13955,7 @@
       </c>
       <c r="O14" s="5"/>
       <c r="Q14" s="91"/>
-      <c r="R14" s="227" t="str">
+      <c r="R14" s="225" t="str">
         <f>R6</f>
         <v>HyperScale</v>
       </c>
@@ -13981,7 +13995,7 @@
       <c r="AC14" s="95"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B15" s="227" t="str">
+      <c r="B15" s="225" t="str">
         <f>B7</f>
         <v>AI Clouds</v>
       </c>
@@ -14019,7 +14033,7 @@
       </c>
       <c r="O15" s="5"/>
       <c r="Q15" s="91"/>
-      <c r="R15" s="227" t="str">
+      <c r="R15" s="225" t="str">
         <f>R7</f>
         <v>AI Clouds</v>
       </c>
@@ -14355,35 +14369,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="231" t="s">
+      <c r="C2" s="234" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="231"/>
-      <c r="E2" s="231"/>
-      <c r="F2" s="231"/>
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="234"/>
       <c r="G2" s="243"/>
       <c r="H2" s="244" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="231"/>
-      <c r="J2" s="231"/>
-      <c r="K2" s="231"/>
-      <c r="L2" s="231"/>
-      <c r="P2" s="231" t="s">
+      <c r="I2" s="234"/>
+      <c r="J2" s="234"/>
+      <c r="K2" s="234"/>
+      <c r="L2" s="234"/>
+      <c r="P2" s="234" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="231"/>
-      <c r="R2" s="231"/>
-      <c r="S2" s="231"/>
-      <c r="T2" s="231"/>
-      <c r="U2" s="231"/>
-      <c r="V2" s="231"/>
-      <c r="W2" s="231"/>
-      <c r="X2" s="231" t="s">
+      <c r="Q2" s="234"/>
+      <c r="R2" s="234"/>
+      <c r="S2" s="234"/>
+      <c r="T2" s="234"/>
+      <c r="U2" s="234"/>
+      <c r="V2" s="234"/>
+      <c r="W2" s="234"/>
+      <c r="X2" s="234" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="231"/>
-      <c r="Z2" s="231"/>
+      <c r="Y2" s="234"/>
+      <c r="Z2" s="234"/>
       <c r="AB2" s="85" t="s">
         <v>107</v>
       </c>
@@ -15614,20 +15628,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="231" t="s">
+      <c r="C3" s="234" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="231"/>
-      <c r="E3" s="231"/>
-      <c r="F3" s="231"/>
+      <c r="D3" s="234"/>
+      <c r="E3" s="234"/>
+      <c r="F3" s="234"/>
       <c r="G3" s="243"/>
       <c r="H3" s="244" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="231"/>
-      <c r="J3" s="231"/>
-      <c r="K3" s="231"/>
-      <c r="L3" s="231"/>
+      <c r="I3" s="234"/>
+      <c r="J3" s="234"/>
+      <c r="K3" s="234"/>
+      <c r="L3" s="234"/>
       <c r="P3" s="245"/>
       <c r="Q3" s="245"/>
       <c r="R3" s="245"/>
@@ -17070,20 +17084,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="231" t="s">
+      <c r="C2" s="234" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="231"/>
-      <c r="E2" s="231"/>
-      <c r="F2" s="231"/>
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="234"/>
       <c r="G2" s="243"/>
       <c r="H2" s="244" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="231"/>
-      <c r="J2" s="231"/>
-      <c r="K2" s="231"/>
-      <c r="L2" s="231"/>
+      <c r="I2" s="234"/>
+      <c r="J2" s="234"/>
+      <c r="K2" s="234"/>
+      <c r="L2" s="234"/>
       <c r="S2" s="245"/>
       <c r="T2" s="245"/>
       <c r="U2" s="245"/>
@@ -18024,23 +18038,23 @@
         <f>Statement!Q99</f>
         <v>0.71068084357547079</v>
       </c>
-      <c r="H33" s="218">
+      <c r="H33" s="217">
         <f>H8/H6</f>
         <v>0.74</v>
       </c>
-      <c r="I33" s="218">
+      <c r="I33" s="217">
         <f t="shared" ref="I33:L33" si="9">I8/I6</f>
         <v>0.74</v>
       </c>
-      <c r="J33" s="218">
+      <c r="J33" s="217">
         <f t="shared" si="9"/>
         <v>0.73999999999999988</v>
       </c>
-      <c r="K33" s="218">
+      <c r="K33" s="217">
         <f t="shared" si="9"/>
         <v>0.74</v>
       </c>
-      <c r="L33" s="218">
+      <c r="L33" s="217">
         <f t="shared" si="9"/>
         <v>0.7400000000000001</v>
       </c>
@@ -18069,23 +18083,23 @@
         <f>Statement!Q100</f>
         <v>0.60381683631412719</v>
       </c>
-      <c r="H34" s="218">
+      <c r="H34" s="217">
         <f>H10/H6</f>
         <v>0.61699999999999999</v>
       </c>
-      <c r="I34" s="218">
+      <c r="I34" s="217">
         <f t="shared" ref="I34:L34" si="10">I10/I6</f>
         <v>0.61699999999999999</v>
       </c>
-      <c r="J34" s="218">
+      <c r="J34" s="217">
         <f t="shared" si="10"/>
         <v>0.61699999999999988</v>
       </c>
-      <c r="K34" s="218">
+      <c r="K34" s="217">
         <f t="shared" si="10"/>
         <v>0.61699999999999999</v>
       </c>
-      <c r="L34" s="218">
+      <c r="L34" s="217">
         <f t="shared" si="10"/>
         <v>0.61699999999999999</v>
       </c>
@@ -18164,10 +18178,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="231" t="s">
+      <c r="B4" s="234" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="231"/>
+      <c r="C4" s="234"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -18184,7 +18198,7 @@
       </c>
       <c r="C6" s="134">
         <f ca="1">Overview!C5</f>
-        <v>201.32499999999999</v>
+        <v>204.65</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18193,7 +18207,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">C5*C6</f>
-        <v>4893204.125</v>
+        <v>4974018.25</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18211,7 +18225,7 @@
       </c>
       <c r="C9" s="136">
         <f ca="1">Overview!F27</f>
-        <v>4.5420000000000002E-2</v>
+        <v>4.428E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18220,7 +18234,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C13</f>
-        <v>2.1962000000000002</v>
+        <v>2.2052999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18252,10 +18266,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="231" t="s">
+      <c r="B15" s="234" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="231"/>
+      <c r="C15" s="234"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -18263,7 +18277,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>1.7279810497398173E-3</v>
+        <v>1.6999538333080865E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18272,7 +18286,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99827201895026019</v>
+        <v>0.99830004616669188</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18290,7 +18304,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14424900000000002</v>
+        <v>0.14351849999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18299,7 +18313,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14406936081805011</v>
+        <v>0.14334301631571833</v>
       </c>
     </row>
   </sheetData>
@@ -18344,20 +18358,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="231" t="s">
+      <c r="C3" s="234" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="231"/>
-      <c r="E3" s="231"/>
-      <c r="F3" s="231"/>
+      <c r="D3" s="234"/>
+      <c r="E3" s="234"/>
+      <c r="F3" s="234"/>
       <c r="G3" s="243"/>
       <c r="H3" s="244" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="231"/>
-      <c r="J3" s="231"/>
-      <c r="K3" s="231"/>
-      <c r="L3" s="231"/>
+      <c r="I3" s="234"/>
+      <c r="J3" s="234"/>
+      <c r="K3" s="234"/>
+      <c r="L3" s="234"/>
       <c r="P3" s="245"/>
       <c r="Q3" s="245"/>
       <c r="R3" s="245"/>
@@ -18549,8 +18563,8 @@
         <v>0</v>
       </c>
       <c r="L8" s="127">
-        <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>4275461.0258678338</v>
+        <f>L7*(1+C14)/(C15-C14)</f>
+        <v>5358699.0689743981</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -18603,24 +18617,24 @@
       <c r="F10" s="138"/>
       <c r="G10" s="139"/>
       <c r="H10" s="127">
-        <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>111476.75239729614</v>
+        <f>H7/(1+$C$15)^H9</f>
+        <v>113872.44362611305</v>
       </c>
       <c r="I10" s="127">
-        <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>140550.32834539691</v>
+        <f t="shared" ref="I10:L10" si="0">I7/(1+$C$15)^I9</f>
+        <v>146656.23420489239</v>
       </c>
       <c r="J10" s="127">
-        <f t="shared" ca="1" si="0"/>
-        <v>181141.67359477043</v>
+        <f t="shared" si="0"/>
+        <v>193072.92356242973</v>
       </c>
       <c r="K10" s="127">
-        <f t="shared" ca="1" si="0"/>
-        <v>221145.07120816314</v>
+        <f t="shared" si="0"/>
+        <v>240776.77526808169</v>
       </c>
       <c r="L10" s="127">
-        <f t="shared" ca="1" si="0"/>
-        <v>253394.58735971208</v>
+        <f t="shared" si="0"/>
+        <v>281818.17319783528</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -18638,15 +18652,15 @@
       <c r="J11" s="138"/>
       <c r="K11" s="138"/>
       <c r="L11" s="127">
-        <f ca="1">L8/(1+C15)^L9</f>
-        <v>2181329.0191470617</v>
+        <f>L8/(1+C15)^L9</f>
+        <v>3040669.7634503278</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="231" t="s">
+      <c r="B13" s="234" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="231"/>
+      <c r="C13" s="234"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -18661,23 +18675,23 @@
         <v>157</v>
       </c>
       <c r="C15" s="136">
-        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14406936081805011</v>
+        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>0.12</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="231" t="s">
+      <c r="B18" s="234" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="231"/>
+      <c r="C18" s="234"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
         <v>179</v>
       </c>
       <c r="C19" s="64">
-        <f ca="1">SUM(H10:L10)</f>
-        <v>907708.41290533869</v>
+        <f>SUM(H10:L10)</f>
+        <v>976196.54985935218</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -18685,8 +18699,8 @@
         <v>175</v>
       </c>
       <c r="C20" s="64">
-        <f ca="1">L11</f>
-        <v>2181329.0191470617</v>
+        <f>L11</f>
+        <v>3040669.7634503278</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -18694,8 +18708,8 @@
         <v>180</v>
       </c>
       <c r="C21" s="94">
-        <f ca="1">C19+C20</f>
-        <v>3089037.4320524004</v>
+        <f>C19+C20</f>
+        <v>4016866.3133096797</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -18721,8 +18735,8 @@
         <v>183</v>
       </c>
       <c r="C24" s="94">
-        <f ca="1">C21+C22-C23</f>
-        <v>3161139.4320524004</v>
+        <f>C21+C22-C23</f>
+        <v>4088968.3133096797</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -18739,8 +18753,8 @@
         <v>184</v>
       </c>
       <c r="C26" s="143">
-        <f ca="1">C24/C25</f>
-        <v>130.06128089086198</v>
+        <f>C24/C25</f>
+        <v>168.2356845632454</v>
       </c>
     </row>
   </sheetData>
@@ -18783,20 +18797,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="231" t="s">
+      <c r="C2" s="234" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="231"/>
-      <c r="E2" s="231"/>
-      <c r="F2" s="231"/>
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="234"/>
       <c r="G2" s="243"/>
       <c r="H2" s="244" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="231"/>
-      <c r="J2" s="231"/>
-      <c r="K2" s="231"/>
-      <c r="L2" s="231"/>
+      <c r="I2" s="234"/>
+      <c r="J2" s="234"/>
+      <c r="K2" s="234"/>
+      <c r="L2" s="234"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -19728,10 +19742,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="231" t="s">
+      <c r="B37" s="234" t="s">
         <v>197</v>
       </c>
-      <c r="C37" s="231"/>
+      <c r="C37" s="234"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -19748,8 +19762,8 @@
         <v>157</v>
       </c>
       <c r="C39" s="136">
-        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14406936081805011</v>
+        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>0.12</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -19774,8 +19788,8 @@
         <v>386</v>
       </c>
       <c r="C42" s="24">
-        <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>7966998.573707521</v>
+        <f>C41/(1+C39)^5-G30+G31</f>
+        <v>8854599.588649042</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -19792,15 +19806,15 @@
         <v>201</v>
       </c>
       <c r="C44" s="143">
-        <f ca="1">C42/C43</f>
-        <v>327.7925765771455</v>
+        <f>C42/C43</f>
+        <v>364.31185306105914</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="231" t="s">
+      <c r="B46" s="234" t="s">
         <v>202</v>
       </c>
-      <c r="C46" s="231"/>
+      <c r="C46" s="234"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
@@ -19856,10 +19870,10 @@
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="231" t="s">
+      <c r="B54" s="234" t="s">
         <v>319</v>
       </c>
-      <c r="C54" s="231"/>
+      <c r="C54" s="234"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
@@ -19875,8 +19889,8 @@
         <v>157</v>
       </c>
       <c r="C56" s="136">
-        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14406936081805011</v>
+        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>0.12</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -19901,8 +19915,8 @@
         <v>386</v>
       </c>
       <c r="C59" s="24">
-        <f ca="1">C58/(1+C56)^5-G30+G31</f>
-        <v>7655925.6207913626</v>
+        <f>C58/(1+C56)^5-G30+G31</f>
+        <v>8508633.1959350575</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -19919,8 +19933,8 @@
         <v>201</v>
       </c>
       <c r="C61" s="143">
-        <f ca="1">C59/C60</f>
-        <v>314.99385397207828</v>
+        <f>C59/C60</f>
+        <v>350.07748183234139</v>
       </c>
     </row>
   </sheetData>
@@ -19972,10 +19986,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="231" t="s">
+      <c r="B4" s="234" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="231"/>
+      <c r="C4" s="234"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -19983,8 +19997,8 @@
         <v>208</v>
       </c>
       <c r="C5" s="134">
-        <f ca="1">DCF!C26</f>
-        <v>130.06128089086198</v>
+        <f>DCF!C26</f>
+        <v>168.2356845632454</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -19992,8 +20006,8 @@
         <v>209</v>
       </c>
       <c r="C6" s="134">
-        <f ca="1">Multiples!C44</f>
-        <v>327.7925765771455</v>
+        <f>Multiples!C44</f>
+        <v>364.31185306105914</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -20010,8 +20024,8 @@
         <v>320</v>
       </c>
       <c r="C8" s="134">
-        <f ca="1">Multiples!C61</f>
-        <v>314.99385397207828</v>
+        <f>Multiples!C61</f>
+        <v>350.07748183234139</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -20019,8 +20033,8 @@
         <v>211</v>
       </c>
       <c r="C9" s="143">
-        <f ca="1">AVERAGE(C5:C8)</f>
-        <v>269.30862463045497</v>
+        <f>AVERAGE(C5:C8)</f>
+        <v>296.75295163459498</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -20029,7 +20043,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C5</f>
-        <v>201.32499999999999</v>
+        <v>204.65</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -20038,7 +20052,7 @@
       </c>
       <c r="C11" s="155">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.33768098661594431</v>
+        <v>0.45005107077740031</v>
       </c>
     </row>
   </sheetData>
@@ -20103,20 +20117,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="231" t="s">
+      <c r="C3" s="234" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="231"/>
-      <c r="E3" s="231"/>
-      <c r="F3" s="231"/>
+      <c r="D3" s="234"/>
+      <c r="E3" s="234"/>
+      <c r="F3" s="234"/>
       <c r="G3" s="243"/>
       <c r="H3" s="244" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="231"/>
-      <c r="J3" s="231"/>
-      <c r="K3" s="231"/>
-      <c r="L3" s="231"/>
+      <c r="I3" s="234"/>
+      <c r="J3" s="234"/>
+      <c r="K3" s="234"/>
+      <c r="L3" s="234"/>
       <c r="P3" s="245"/>
       <c r="Q3" s="245"/>
       <c r="R3" s="245"/>
@@ -20290,8 +20304,8 @@
       <c r="J8" s="138"/>
       <c r="K8" s="138"/>
       <c r="L8" s="127">
-        <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>7047093.6730966922</v>
+        <f>L7*(1+C20)/(C21-C20)</f>
+        <v>8832557.2555847168</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20344,24 +20358,24 @@
       <c r="F10" s="138"/>
       <c r="G10" s="139"/>
       <c r="H10" s="127">
-        <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>123967.27465316029</v>
+        <f>H7/(1+$C$21)^H9</f>
+        <v>126631.39345963995</v>
       </c>
       <c r="I10" s="127">
-        <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>167952.47062206519</v>
+        <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
+        <v>175248.80344860884</v>
       </c>
       <c r="J10" s="127">
-        <f t="shared" ca="1" si="1"/>
-        <v>227544.18427747994</v>
+        <f t="shared" si="1"/>
+        <v>242531.82620119973</v>
       </c>
       <c r="K10" s="127">
-        <f t="shared" ca="1" si="1"/>
-        <v>308279.81039358105</v>
+        <f t="shared" si="1"/>
+        <v>335646.72376058897</v>
       </c>
       <c r="L10" s="127">
-        <f t="shared" ca="1" si="1"/>
-        <v>417661.4831887313</v>
+        <f t="shared" si="1"/>
+        <v>464511.09091867215</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20379,8 +20393,8 @@
       <c r="J11" s="138"/>
       <c r="K11" s="138"/>
       <c r="L11" s="127">
-        <f ca="1">L8/(1+C21)^L9</f>
-        <v>3595408.7376233903</v>
+        <f>L8/(1+C21)^L9</f>
+        <v>5011830.1914909361</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -20396,7 +20410,7 @@
       </c>
       <c r="C15" s="157">
         <f ca="1">Overview!C5</f>
-        <v>201.32499999999999</v>
+        <v>204.65</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -20404,8 +20418,8 @@
         <v>217</v>
       </c>
       <c r="C16" s="157">
-        <f ca="1">C36</f>
-        <v>203.0130562296863</v>
+        <f>C36</f>
+        <v>265.64057972229938</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -20442,16 +20456,16 @@
       <c r="B21" s="160" t="s">
         <v>157</v>
       </c>
-      <c r="C21" s="229">
-        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14406936081805011</v>
+      <c r="C21" s="227">
+        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>0.12</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B22" s="160" t="s">
         <v>67</v>
       </c>
-      <c r="C22" s="230">
+      <c r="C22" s="228">
         <f>Statement!AC74</f>
         <v>24200</v>
       </c>
@@ -20462,14 +20476,14 @@
       </c>
       <c r="C23" s="162">
         <f ca="1">C15*C22</f>
-        <v>4872065</v>
+        <v>4952530</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B24" s="160" t="s">
         <v>170</v>
       </c>
-      <c r="C24" s="230">
+      <c r="C24" s="228">
         <f>Statement!AC105</f>
         <v>80572</v>
       </c>
@@ -20478,7 +20492,7 @@
       <c r="B25" s="160" t="s">
         <v>161</v>
       </c>
-      <c r="C25" s="230">
+      <c r="C25" s="228">
         <f>Statement!AC106</f>
         <v>8470</v>
       </c>
@@ -20489,7 +20503,7 @@
       </c>
       <c r="C26" s="163">
         <f ca="1">C23+C25-C24</f>
-        <v>4799963</v>
+        <v>4880428</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -20504,8 +20518,8 @@
         <v>179</v>
       </c>
       <c r="C29" s="162">
-        <f ca="1">SUM(H10:L10)</f>
-        <v>1245405.2231350178</v>
+        <f>SUM(H10:L10)</f>
+        <v>1344569.8377887099</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -20513,8 +20527,8 @@
         <v>175</v>
       </c>
       <c r="C30" s="162">
-        <f ca="1">L11</f>
-        <v>3595408.7376233903</v>
+        <f>L11</f>
+        <v>5011830.1914909361</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -20522,8 +20536,8 @@
         <v>180</v>
       </c>
       <c r="C31" s="165">
-        <f ca="1">C29+C30</f>
-        <v>4840813.9607584085</v>
+        <f>C29+C30</f>
+        <v>6356400.0292796455</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -20549,8 +20563,8 @@
         <v>183</v>
       </c>
       <c r="C34" s="165">
-        <f ca="1">C31+C32-C33</f>
-        <v>4912915.9607584085</v>
+        <f>C31+C32-C33</f>
+        <v>6428502.0292796455</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -20567,8 +20581,8 @@
         <v>184</v>
       </c>
       <c r="C36" s="168">
-        <f ca="1">C34/C35</f>
-        <v>203.0130562296863</v>
+        <f>C34/C35</f>
+        <v>265.64057972229938</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -21035,7 +21049,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0548B83C-60BF-4548-84AB-1D4A73B251A4}">
-  <dimension ref="A1:AE211"/>
+  <dimension ref="A1:AE214"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.6640625" style="1" customWidth="1"/>
@@ -22982,7 +22996,7 @@
     </row>
     <row r="33" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B33" s="20" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C33" s="21"/>
       <c r="D33" s="21"/>
@@ -27521,7 +27535,7 @@
       <c r="AA114" s="68"/>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>201.32499999999999</v>
+        <v>204.65</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -27568,7 +27582,7 @@
       <c r="AA115" s="68"/>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>201.32499999999999</v>
+        <v>204.65</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -27982,35 +27996,35 @@
       <c r="O130" s="49"/>
       <c r="P130" s="49"/>
       <c r="Q130" s="49"/>
-      <c r="T130" s="173" t="str">
+      <c r="T130" s="229" t="str">
         <f t="shared" ref="T130:AA130" si="71">IF(T129&gt;T128, "BEAT", IF(T129&lt;T127, "MISSED", "MET"))</f>
         <v>BEAT</v>
       </c>
-      <c r="U130" s="173" t="str">
+      <c r="U130" s="229" t="str">
         <f t="shared" si="71"/>
         <v>BEAT</v>
       </c>
-      <c r="V130" s="173" t="str">
+      <c r="V130" s="229" t="str">
         <f t="shared" si="71"/>
         <v>BEAT</v>
       </c>
-      <c r="W130" s="173" t="str">
+      <c r="W130" s="229" t="str">
         <f t="shared" si="71"/>
         <v>BEAT</v>
       </c>
-      <c r="X130" s="173" t="str">
+      <c r="X130" s="229" t="str">
         <f t="shared" si="71"/>
         <v>BEAT</v>
       </c>
-      <c r="Y130" s="173" t="str">
+      <c r="Y130" s="229" t="str">
         <f t="shared" si="71"/>
         <v>BEAT</v>
       </c>
-      <c r="Z130" s="173" t="str">
+      <c r="Z130" s="229" t="str">
         <f t="shared" si="71"/>
         <v>BEAT</v>
       </c>
-      <c r="AA130" s="173" t="str">
+      <c r="AA130" s="229" t="str">
         <f t="shared" si="71"/>
         <v>MISSED</v>
       </c>
@@ -28035,28 +28049,28 @@
       <c r="O131" s="49"/>
       <c r="P131" s="49"/>
       <c r="Q131" s="49"/>
-      <c r="T131" s="225">
+      <c r="T131" s="223">
         <v>0.73899999999999999</v>
       </c>
-      <c r="U131" s="225">
+      <c r="U131" s="223">
         <v>0.72499999999999998</v>
       </c>
-      <c r="V131" s="225">
+      <c r="V131" s="223">
         <v>0.70099999999999996</v>
       </c>
-      <c r="W131" s="225">
+      <c r="W131" s="223">
         <v>0.71299999999999997</v>
       </c>
-      <c r="X131" s="225">
+      <c r="X131" s="223">
         <v>0.72799999999999998</v>
       </c>
-      <c r="Y131" s="225">
+      <c r="Y131" s="223">
         <v>0.74299999999999999</v>
       </c>
-      <c r="Z131" s="225">
+      <c r="Z131" s="223">
         <v>0.745</v>
       </c>
-      <c r="AA131" s="225">
+      <c r="AA131" s="223">
         <v>0.745</v>
       </c>
       <c r="AC131" s="49"/>
@@ -28080,28 +28094,28 @@
       <c r="O132" s="49"/>
       <c r="P132" s="49"/>
       <c r="Q132" s="49"/>
-      <c r="T132" s="225">
+      <c r="T132" s="223">
         <v>0.749</v>
       </c>
-      <c r="U132" s="225">
+      <c r="U132" s="223">
         <v>0.73499999999999999</v>
       </c>
-      <c r="V132" s="225">
+      <c r="V132" s="223">
         <v>0.71099999999999997</v>
       </c>
-      <c r="W132" s="225">
+      <c r="W132" s="223">
         <v>0.72299999999999998</v>
       </c>
-      <c r="X132" s="225">
+      <c r="X132" s="223">
         <v>0.73799999999999999</v>
       </c>
-      <c r="Y132" s="225">
+      <c r="Y132" s="223">
         <v>0.754</v>
       </c>
-      <c r="Z132" s="225">
+      <c r="Z132" s="223">
         <v>0.754</v>
       </c>
-      <c r="AA132" s="225">
+      <c r="AA132" s="223">
         <v>0.754</v>
       </c>
       <c r="AC132" s="49"/>
@@ -28178,35 +28192,35 @@
       <c r="O134" s="49"/>
       <c r="P134" s="49"/>
       <c r="Q134" s="49"/>
-      <c r="T134" s="173" t="str">
+      <c r="T134" s="229" t="str">
         <f t="shared" ref="T134:AA134" si="73">IF(T133&gt;T132, "BEAT", IF(T133&lt;T131, "MISSED", "MET"))</f>
         <v>MET</v>
       </c>
-      <c r="U134" s="173" t="str">
+      <c r="U134" s="229" t="str">
         <f t="shared" si="73"/>
         <v>MET</v>
       </c>
-      <c r="V134" s="173" t="str">
+      <c r="V134" s="229" t="str">
         <f t="shared" si="73"/>
         <v>MISSED</v>
       </c>
-      <c r="W134" s="173" t="str">
+      <c r="W134" s="229" t="str">
         <f t="shared" si="73"/>
         <v>BEAT</v>
       </c>
-      <c r="X134" s="173" t="str">
+      <c r="X134" s="229" t="str">
         <f t="shared" si="73"/>
         <v>MET</v>
       </c>
-      <c r="Y134" s="173" t="str">
+      <c r="Y134" s="229" t="str">
         <f t="shared" si="73"/>
         <v>MET</v>
       </c>
-      <c r="Z134" s="173" t="str">
+      <c r="Z134" s="229" t="str">
         <f t="shared" si="73"/>
         <v>MET</v>
       </c>
-      <c r="AA134" s="173" t="str">
+      <c r="AA134" s="229" t="str">
         <f t="shared" si="73"/>
         <v>MISSED</v>
       </c>
@@ -28374,35 +28388,35 @@
       <c r="O138" s="49"/>
       <c r="P138" s="49"/>
       <c r="Q138" s="49"/>
-      <c r="T138" s="173" t="str">
+      <c r="T138" s="229" t="str">
         <f t="shared" ref="T138:AA138" si="75">IF(T137&gt;T136, "BEAT", IF(T137&lt;T135, "MISSED", "MET"))</f>
         <v>MISSED</v>
       </c>
-      <c r="U138" s="173" t="str">
+      <c r="U138" s="229" t="str">
         <f t="shared" si="75"/>
         <v>MISSED</v>
       </c>
-      <c r="V138" s="173" t="str">
+      <c r="V138" s="229" t="str">
         <f t="shared" si="75"/>
         <v>MISSED</v>
       </c>
-      <c r="W138" s="173" t="str">
+      <c r="W138" s="229" t="str">
         <f t="shared" si="75"/>
         <v>MISSED</v>
       </c>
-      <c r="X138" s="173" t="str">
+      <c r="X138" s="229" t="str">
         <f t="shared" si="75"/>
         <v>MISSED</v>
       </c>
-      <c r="Y138" s="173" t="str">
+      <c r="Y138" s="229" t="str">
         <f t="shared" si="75"/>
         <v>BEAT</v>
       </c>
-      <c r="Z138" s="173" t="str">
+      <c r="Z138" s="229" t="str">
         <f t="shared" si="75"/>
         <v>MISSED</v>
       </c>
-      <c r="AA138" s="173" t="str">
+      <c r="AA138" s="229" t="str">
         <f t="shared" si="75"/>
         <v>MISSED</v>
       </c>
@@ -28796,59 +28810,59 @@
       <c r="B148" s="20" t="s">
         <v>252</v>
       </c>
-      <c r="M148" s="181">
+      <c r="M148" s="180">
         <f>(M106-M105)/M48</f>
         <v>-0.38561551179918835</v>
       </c>
-      <c r="N148" s="181">
+      <c r="N148" s="180">
         <f>(N106-N105)/N48</f>
         <v>-0.10601330256549478</v>
       </c>
-      <c r="O148" s="181">
+      <c r="O148" s="180">
         <f>(O106-O105)/O48</f>
         <v>-0.37868211643166272</v>
       </c>
-      <c r="P148" s="181">
+      <c r="P148" s="180">
         <f>(P106-P105)/P48</f>
         <v>-0.43802236312982967</v>
       </c>
-      <c r="Q148" s="181">
+      <c r="Q148" s="180">
         <f>(Q106-Q105)/Q48</f>
         <v>-0.34386781357085183</v>
       </c>
-      <c r="T148" s="181">
+      <c r="T148" s="180">
         <f t="shared" ref="T148:AA148" si="90">(T106-T105)/T48</f>
         <v>-0.45289475041697475</v>
       </c>
-      <c r="U148" s="181">
+      <c r="U148" s="180">
         <f t="shared" si="90"/>
         <v>-0.45562148135783548</v>
       </c>
-      <c r="V148" s="181">
+      <c r="V148" s="180">
         <f t="shared" si="90"/>
         <v>-0.43802236312982967</v>
       </c>
-      <c r="W148" s="181">
+      <c r="W148" s="180">
         <f t="shared" si="90"/>
         <v>-0.53942487744951872</v>
       </c>
-      <c r="X148" s="181">
+      <c r="X148" s="180">
         <f t="shared" si="90"/>
         <v>-0.48261777072035633</v>
       </c>
-      <c r="Y148" s="181">
+      <c r="Y148" s="180">
         <f t="shared" si="90"/>
         <v>-0.43853923984625348</v>
       </c>
-      <c r="Z148" s="181">
+      <c r="Z148" s="180">
         <f t="shared" si="90"/>
         <v>-0.3432320573706395</v>
       </c>
-      <c r="AA148" s="181">
+      <c r="AA148" s="180">
         <f t="shared" si="90"/>
         <v>-0.36885723932594616</v>
       </c>
-      <c r="AC148" s="181">
+      <c r="AC148" s="180">
         <f>(AC106-AC105)/AC48</f>
         <v>-0.36885723932594616</v>
       </c>
@@ -28979,59 +28993,59 @@
       <c r="B151" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="M151" s="183">
+      <c r="M151" s="182">
         <f>IF(M12&gt;=0,"N/A",IF(M11&lt;=0,"N/A",M11/-M12))</f>
         <v>48.507246376811594</v>
       </c>
-      <c r="N151" s="183" t="str">
+      <c r="N151" s="182" t="str">
         <f>IF(N12&gt;=0,"N/A",IF(N11&lt;=0,"N/A",N11/-N12))</f>
         <v>N/A</v>
       </c>
-      <c r="O151" s="183" t="str">
+      <c r="O151" s="182" t="str">
         <f>IF(O12&gt;=0,"N/A",IF(O11&lt;=0,"N/A",O11/-O12))</f>
         <v>N/A</v>
       </c>
-      <c r="P151" s="183" t="str">
+      <c r="P151" s="182" t="str">
         <f>IF(P12&gt;=0,"N/A",IF(P11&lt;=0,"N/A",P11/-P12))</f>
         <v>N/A</v>
       </c>
-      <c r="Q151" s="183" t="str">
+      <c r="Q151" s="182" t="str">
         <f>IF(Q12&gt;=0,"N/A",IF(Q11&lt;=0,"N/A",Q11/-Q12))</f>
         <v>N/A</v>
       </c>
-      <c r="T151" s="183" t="str">
+      <c r="T151" s="182" t="str">
         <f t="shared" ref="T151:AA151" si="93">IF(T12&gt;=0,"N/A",IF(T11&lt;=0,"N/A",T11/-T12))</f>
         <v>N/A</v>
       </c>
-      <c r="U151" s="183" t="str">
+      <c r="U151" s="182" t="str">
         <f t="shared" si="93"/>
         <v>N/A</v>
       </c>
-      <c r="V151" s="183" t="str">
+      <c r="V151" s="182" t="str">
         <f t="shared" si="93"/>
         <v>N/A</v>
       </c>
-      <c r="W151" s="183" t="str">
+      <c r="W151" s="182" t="str">
         <f t="shared" si="93"/>
         <v>N/A</v>
       </c>
-      <c r="X151" s="183" t="str">
+      <c r="X151" s="182" t="str">
         <f t="shared" si="93"/>
         <v>N/A</v>
       </c>
-      <c r="Y151" s="183" t="str">
+      <c r="Y151" s="182" t="str">
         <f t="shared" si="93"/>
         <v>N/A</v>
       </c>
-      <c r="Z151" s="183" t="str">
+      <c r="Z151" s="182" t="str">
         <f t="shared" si="93"/>
         <v>N/A</v>
       </c>
-      <c r="AA151" s="183" t="str">
+      <c r="AA151" s="182" t="str">
         <f t="shared" si="93"/>
         <v>N/A</v>
       </c>
-      <c r="AC151" s="183" t="str">
+      <c r="AC151" s="182" t="str">
         <f>IF(AC12&gt;=0,"N/A",IF(AC11&lt;=0,"N/A",AC11/-AC12))</f>
         <v>N/A</v>
       </c>
@@ -29070,7 +29084,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>30.830781010719758</v>
+        <v>31.339969372128643</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -29107,7 +29121,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>19.425971089703381</v>
+        <v>19.746802351957271</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -29144,7 +29158,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>24.924363342439406</v>
+        <v>25.33600376520663</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -29181,7 +29195,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="144">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>4893204.125</v>
+        <v>4974018.25</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -29218,30 +29232,30 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="144">
         <f ca="1">AC155+AC106-AC105+AC47+AC44</f>
-        <v>4821102.125</v>
+        <v>4901916.25</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B157" s="20" t="s">
         <v>257</v>
       </c>
-      <c r="M157" s="185">
+      <c r="M157" s="184">
         <f>M156/M5</f>
         <v>21.250263803225085</v>
       </c>
-      <c r="N157" s="185">
+      <c r="N157" s="184">
         <f>N156/N5</f>
         <v>18.707681471046193</v>
       </c>
-      <c r="O157" s="185">
+      <c r="O157" s="184">
         <f>O156/O5</f>
         <v>25.02761728111355</v>
       </c>
-      <c r="P157" s="185">
+      <c r="P157" s="184">
         <f>P156/P5</f>
         <v>26.672593086431103</v>
       </c>
-      <c r="Q157" s="185">
+      <c r="Q157" s="184">
         <f>Q156/Q5</f>
         <v>21.003166881234428</v>
       </c>
@@ -29253,32 +29267,32 @@
       <c r="Y157" s="49"/>
       <c r="Z157" s="49"/>
       <c r="AA157" s="49"/>
-      <c r="AC157" s="185">
+      <c r="AC157" s="184">
         <f ca="1">AC156/AC5</f>
-        <v>19.01882956396874</v>
+        <v>19.337634274984122</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B158" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="M158" s="185">
+      <c r="M158" s="184">
         <f>M156/M11</f>
         <v>56.959426351956971</v>
       </c>
-      <c r="N158" s="185">
+      <c r="N158" s="184">
         <f>N156/N11</f>
         <v>119.46519886363636</v>
       </c>
-      <c r="O158" s="185">
+      <c r="O158" s="184">
         <f>O156/O11</f>
         <v>46.243251850054584</v>
       </c>
-      <c r="P158" s="185">
+      <c r="P158" s="184">
         <f>P156/P11</f>
         <v>42.732537536984516</v>
       </c>
-      <c r="Q158" s="185">
+      <c r="Q158" s="184">
         <f>Q156/Q11</f>
         <v>34.784003389908499</v>
       </c>
@@ -29290,9 +29304,9 @@
       <c r="Y158" s="49"/>
       <c r="Z158" s="49"/>
       <c r="AA158" s="49"/>
-      <c r="AC158" s="185">
+      <c r="AC158" s="184">
         <f ca="1">AC156/AC11</f>
-        <v>29.707626243953538</v>
+        <v>30.205602797547524</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -29427,7 +29441,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="72">
         <f t="shared" ref="AC161:AC162" ca="1" si="96">AC155/AC159</f>
-        <v>43.597068034605343</v>
+        <v>44.317099084971979</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -29464,7 +29478,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ca="1" si="96"/>
-        <v>38.016493853907782</v>
+        <v>38.653748491273809</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -29501,7 +29515,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="74">
         <f t="shared" ref="AC163" ca="1" si="99">AC159/AC155</f>
-        <v>2.2937322280623229E-2</v>
+        <v>2.2564653838976163E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -29538,7 +29552,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>3.2435117347572331E-2</v>
+        <v>3.1908135841680917E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -29575,7 +29589,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="155">
         <f ca="1">AC81/AC115</f>
-        <v>1.9868372035266362E-4</v>
+        <v>1.9545565599804544E-4</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -29612,7 +29626,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="155">
         <f ca="1">-AC62/AC155</f>
-        <v>9.2585550985980983E-3</v>
+        <v>9.108129026265635E-3</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -29649,30 +29663,30 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="155">
         <f ca="1">-(AC62+AC63)/AC155</f>
-        <v>9.4574023110061863E-3</v>
+        <v>9.3037455180225766E-3</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B168" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="M168" s="228">
+      <c r="M168" s="226">
         <f>M160/M5</f>
         <v>0.24838741111758303</v>
       </c>
-      <c r="N168" s="228">
+      <c r="N168" s="226">
         <f>N160/N5</f>
         <v>6.4061689033884484E-2</v>
       </c>
-      <c r="O168" s="228">
+      <c r="O168" s="226">
         <f>O160/O5</f>
         <v>0.42238462291779383</v>
       </c>
-      <c r="P168" s="228">
+      <c r="P168" s="226">
         <f>P160/P5</f>
         <v>0.45896309457389761</v>
       </c>
-      <c r="Q168" s="228">
+      <c r="Q168" s="226">
         <f>Q160/Q5</f>
         <v>0.42373919358213857</v>
       </c>
@@ -29693,23 +29707,23 @@
       <c r="B169" s="20" t="s">
         <v>385</v>
       </c>
-      <c r="M169" s="228">
+      <c r="M169" s="226">
         <f>M159/M5</f>
         <v>0.22768819201902354</v>
       </c>
-      <c r="N169" s="228">
+      <c r="N169" s="226">
         <f>N159/N5</f>
         <v>4.0742937643656857E-2</v>
       </c>
-      <c r="O169" s="228">
+      <c r="O169" s="226">
         <f>O159/O5</f>
         <v>0.38527953776960705</v>
       </c>
-      <c r="P169" s="228">
+      <c r="P169" s="226">
         <f>P159/P5</f>
         <v>0.43001754829612943</v>
       </c>
-      <c r="Q169" s="228">
+      <c r="Q169" s="226">
         <f>Q159/Q5</f>
         <v>0.41812927784827125</v>
       </c>
@@ -30152,7 +30166,7 @@
       <c r="AA178" s="49"/>
       <c r="AC178" s="155">
         <f ca="1">(AC105-AC106)/AC155</f>
-        <v>1.473513022512626E-2</v>
+        <v>1.4495724859875615E-2</v>
       </c>
     </row>
     <row r="179" spans="1:31" x14ac:dyDescent="0.2">
@@ -30340,27 +30354,27 @@
     </row>
     <row r="182" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B182" s="20" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="M182" s="72">
-        <f>M36/M5</f>
-        <v>1.641784944638478</v>
+        <f>M5/M36</f>
+        <v>0.60909317219996828</v>
       </c>
       <c r="N182" s="72">
-        <f>N36/N5</f>
-        <v>1.5267294431674947</v>
+        <f t="shared" ref="N182:Q182" si="107">N5/N36</f>
+        <v>0.65499490068476518</v>
       </c>
       <c r="O182" s="72">
-        <f>O36/O5</f>
-        <v>1.0788877581169365</v>
+        <f t="shared" si="107"/>
+        <v>0.92688047711781885</v>
       </c>
       <c r="P182" s="72">
-        <f>P36/P5</f>
-        <v>0.85519973639240754</v>
+        <f t="shared" si="107"/>
+        <v>1.169317479234057</v>
       </c>
       <c r="Q182" s="72">
-        <f>Q36/Q5</f>
-        <v>0.95769619057322009</v>
+        <f t="shared" si="107"/>
+        <v>1.0441724733200195</v>
       </c>
       <c r="T182" s="49"/>
       <c r="U182" s="49"/>
@@ -30371,208 +30385,145 @@
       <c r="Z182" s="49"/>
       <c r="AA182" s="49"/>
       <c r="AC182" s="72">
-        <f>AC36/AC5</f>
-        <v>1.0236024158648631</v>
+        <f t="shared" ref="AC182" si="108">AC5/AC36</f>
+        <v>0.97694181305256023</v>
+      </c>
+    </row>
+    <row r="183" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B183" s="20" t="s">
+        <v>395</v>
+      </c>
+      <c r="M183" s="72">
+        <f>IF(AND(M11&gt;0,M106&gt;0),M106/M11,"N/A")</f>
+        <v>1.0901304650931183</v>
+      </c>
+      <c r="N183" s="72">
+        <f t="shared" ref="N183:Q183" si="109">IF(AND(N11&gt;0,N106&gt;0),N106/N11,"N/A")</f>
+        <v>2.5930397727272729</v>
+      </c>
+      <c r="O183" s="72">
+        <f t="shared" si="109"/>
+        <v>0.29446196773019534</v>
+      </c>
+      <c r="P183" s="72">
+        <f t="shared" si="109"/>
+        <v>0.103900408824721</v>
+      </c>
+      <c r="Q183" s="72">
+        <f t="shared" si="109"/>
+        <v>6.4945124897420756E-2</v>
+      </c>
+      <c r="T183" s="49"/>
+      <c r="U183" s="49"/>
+      <c r="V183" s="49"/>
+      <c r="W183" s="49"/>
+      <c r="X183" s="49"/>
+      <c r="Y183" s="49"/>
+      <c r="Z183" s="49"/>
+      <c r="AA183" s="49"/>
+      <c r="AC183" s="72">
+        <f t="shared" ref="AC183" si="110">IF(AND(AC11&gt;0,AC106&gt;0),AC106/AC11,"N/A")</f>
+        <v>5.2192131127337706E-2</v>
       </c>
     </row>
     <row r="184" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B184" s="1"/>
-    </row>
-    <row r="185" spans="1:31" s="15" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="11"/>
-      <c r="B185" s="14" t="s">
+      <c r="B184" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="M184" s="230">
+        <f>IF(AND(M11&gt;0,M106&gt;0),(M106-M105)/M11,"N/A")</f>
+        <v>-1.0220097599840654</v>
+      </c>
+      <c r="N184" s="230">
+        <f t="shared" ref="N184:Q184" si="111">IF(AND(N11&gt;0,N106&gt;0),(N106-N105)/N11,"N/A")</f>
+        <v>-0.5546875</v>
+      </c>
+      <c r="O184" s="230">
+        <f t="shared" si="111"/>
+        <v>-0.49360063083828704</v>
+      </c>
+      <c r="P184" s="230">
+        <f t="shared" si="111"/>
+        <v>-0.42658956698955225</v>
+      </c>
+      <c r="Q184" s="230">
+        <f t="shared" si="111"/>
+        <v>-0.41482663148933557</v>
+      </c>
+      <c r="T184" s="49"/>
+      <c r="U184" s="49"/>
+      <c r="V184" s="49"/>
+      <c r="W184" s="49"/>
+      <c r="X184" s="49"/>
+      <c r="Y184" s="49"/>
+      <c r="Z184" s="49"/>
+      <c r="AA184" s="49"/>
+      <c r="AC184" s="230">
+        <f t="shared" ref="AC184" si="112">IF(AND(AC11&gt;0,AC106&gt;0),(AC106-AC105)/AC11,"N/A")</f>
+        <v>-0.44429244847028376</v>
+      </c>
+    </row>
+    <row r="185" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B185" s="20" t="s">
+        <v>397</v>
+      </c>
+      <c r="M185" s="230">
+        <f>M5/(M106+M110-M105)</f>
+        <v>1.6461162079510703</v>
+      </c>
+      <c r="N185" s="230">
+        <f t="shared" ref="N185:Q185" si="113">N5/(N106+N110-N105)</f>
+        <v>1.3652191517360057</v>
+      </c>
+      <c r="O185" s="230">
+        <f t="shared" si="113"/>
+        <v>2.2814665018911731</v>
+      </c>
+      <c r="P185" s="230">
+        <f t="shared" si="113"/>
+        <v>2.9272543741588155</v>
+      </c>
+      <c r="Q185" s="230">
+        <f t="shared" si="113"/>
+        <v>2.0923211084734268</v>
+      </c>
+      <c r="T185" s="49"/>
+      <c r="U185" s="49"/>
+      <c r="V185" s="49"/>
+      <c r="W185" s="49"/>
+      <c r="X185" s="49"/>
+      <c r="Y185" s="49"/>
+      <c r="Z185" s="49"/>
+      <c r="AA185" s="49"/>
+      <c r="AC185" s="230">
+        <f t="shared" ref="AC185" si="114">AC5/(AC106+AC110-AC105)</f>
+        <v>2.0546882598968974</v>
+      </c>
+    </row>
+    <row r="187" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B187" s="1"/>
+    </row>
+    <row r="188" spans="1:31" s="15" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="11"/>
+      <c r="B188" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="R185" s="1"/>
-      <c r="S185" s="1"/>
-      <c r="AB185" s="1"/>
-      <c r="AD185" s="1"/>
-      <c r="AE185" s="1"/>
-    </row>
-    <row r="186" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B186" s="226" t="s">
+      <c r="R188" s="1"/>
+      <c r="S188" s="1"/>
+      <c r="AB188" s="1"/>
+      <c r="AD188" s="1"/>
+      <c r="AE188" s="1"/>
+    </row>
+    <row r="189" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B189" s="224" t="s">
         <v>370</v>
       </c>
-      <c r="C186" s="62"/>
-      <c r="D186" s="62"/>
-      <c r="E186" s="62"/>
-      <c r="F186" s="62"/>
-      <c r="G186" s="62"/>
-      <c r="H186" s="62"/>
-      <c r="I186" s="62"/>
-      <c r="J186" s="62"/>
-      <c r="K186" s="62"/>
-      <c r="L186" s="62"/>
-      <c r="M186" s="62">
-        <v>0</v>
-      </c>
-      <c r="N186" s="62">
-        <v>0</v>
-      </c>
-      <c r="O186" s="62">
-        <v>0</v>
-      </c>
-      <c r="P186" s="62">
-        <v>53796</v>
-      </c>
-      <c r="Q186" s="62">
-        <v>105636</v>
-      </c>
-      <c r="T186" s="62">
-        <v>10622</v>
-      </c>
-      <c r="U186" s="62">
-        <v>13390</v>
-      </c>
-      <c r="V186" s="62">
-        <v>19094</v>
-      </c>
-      <c r="W186" s="62">
-        <v>17599</v>
-      </c>
-      <c r="X186" s="62">
-        <v>23883</v>
-      </c>
-      <c r="Y186" s="62">
-        <v>30340</v>
-      </c>
-      <c r="Z186" s="62">
-        <v>33814</v>
-      </c>
-      <c r="AA186" s="62">
-        <v>37869</v>
-      </c>
-      <c r="AC186" s="62">
-        <f>SUM(X186:AA186)</f>
-        <v>125906</v>
-      </c>
-    </row>
-    <row r="187" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B187" s="226" t="s">
-        <v>371</v>
-      </c>
-      <c r="C187" s="62"/>
-      <c r="D187" s="62"/>
-      <c r="E187" s="62"/>
-      <c r="F187" s="62"/>
-      <c r="G187" s="62"/>
-      <c r="H187" s="62"/>
-      <c r="I187" s="62"/>
-      <c r="J187" s="62"/>
-      <c r="K187" s="62"/>
-      <c r="L187" s="62"/>
-      <c r="M187" s="62">
-        <v>0</v>
-      </c>
-      <c r="N187" s="62">
-        <v>0</v>
-      </c>
-      <c r="O187" s="62">
-        <v>0</v>
-      </c>
-      <c r="P187" s="62">
-        <v>61390</v>
-      </c>
-      <c r="Q187" s="62">
-        <v>88101</v>
-      </c>
-      <c r="T187" s="62">
-        <v>15650</v>
-      </c>
-      <c r="U187" s="62">
-        <v>17381</v>
-      </c>
-      <c r="V187" s="62">
-        <v>16486</v>
-      </c>
-      <c r="W187" s="62">
-        <v>21513</v>
-      </c>
-      <c r="X187" s="62">
-        <v>17213</v>
-      </c>
-      <c r="Y187" s="62">
-        <v>20875</v>
-      </c>
-      <c r="Z187" s="62">
-        <v>28500</v>
-      </c>
-      <c r="AA187" s="62">
-        <v>37377</v>
-      </c>
-      <c r="AC187" s="62">
-        <f t="shared" ref="AC187:AC189" si="107">SUM(X187:AA187)</f>
-        <v>103965</v>
-      </c>
-    </row>
-    <row r="188" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B188" s="20" t="s">
-        <v>372</v>
-      </c>
-      <c r="C188" s="62"/>
-      <c r="D188" s="62"/>
-      <c r="E188" s="62"/>
-      <c r="F188" s="62"/>
-      <c r="G188" s="62"/>
-      <c r="H188" s="62"/>
-      <c r="I188" s="62"/>
-      <c r="J188" s="62"/>
-      <c r="K188" s="62"/>
-      <c r="L188" s="62"/>
-      <c r="M188" s="62">
-        <v>0</v>
-      </c>
-      <c r="N188" s="62">
-        <v>0</v>
-      </c>
-      <c r="O188" s="62">
-        <v>0</v>
-      </c>
-      <c r="P188" s="62">
-        <v>115186</v>
-      </c>
-      <c r="Q188" s="62">
-        <v>193737</v>
-      </c>
-      <c r="T188" s="62">
-        <v>26272</v>
-      </c>
-      <c r="U188" s="62">
-        <v>30771</v>
-      </c>
-      <c r="V188" s="62">
-        <v>35580</v>
-      </c>
-      <c r="W188" s="62">
-        <v>39112</v>
-      </c>
-      <c r="X188" s="62">
-        <v>41096</v>
-      </c>
-      <c r="Y188" s="62">
-        <v>51215</v>
-      </c>
-      <c r="Z188" s="62">
-        <v>62314</v>
-      </c>
-      <c r="AA188" s="62">
-        <v>75246</v>
-      </c>
-      <c r="AC188" s="62">
-        <f t="shared" si="107"/>
-        <v>229871</v>
-      </c>
-    </row>
-    <row r="189" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B189" s="20" t="s">
-        <v>373</v>
-      </c>
-      <c r="C189" s="21"/>
-      <c r="D189" s="21"/>
-      <c r="E189" s="21"/>
-      <c r="F189" s="21"/>
-      <c r="G189" s="21"/>
-      <c r="H189" s="21"/>
+      <c r="C189" s="62"/>
+      <c r="D189" s="62"/>
+      <c r="E189" s="62"/>
+      <c r="F189" s="62"/>
+      <c r="G189" s="62"/>
+      <c r="H189" s="62"/>
       <c r="I189" s="62"/>
       <c r="J189" s="62"/>
       <c r="K189" s="62"/>
@@ -30587,573 +30538,747 @@
         <v>0</v>
       </c>
       <c r="P189" s="62">
+        <v>53796</v>
+      </c>
+      <c r="Q189" s="62">
+        <v>105636</v>
+      </c>
+      <c r="T189" s="62">
+        <v>10622</v>
+      </c>
+      <c r="U189" s="62">
+        <v>13390</v>
+      </c>
+      <c r="V189" s="62">
+        <v>19094</v>
+      </c>
+      <c r="W189" s="62">
+        <v>17599</v>
+      </c>
+      <c r="X189" s="62">
+        <v>23883</v>
+      </c>
+      <c r="Y189" s="62">
+        <v>30340</v>
+      </c>
+      <c r="Z189" s="62">
+        <v>33814</v>
+      </c>
+      <c r="AA189" s="62">
+        <v>37869</v>
+      </c>
+      <c r="AC189" s="62">
+        <f>SUM(X189:AA189)</f>
+        <v>125906</v>
+      </c>
+    </row>
+    <row r="190" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B190" s="224" t="s">
+        <v>371</v>
+      </c>
+      <c r="C190" s="62"/>
+      <c r="D190" s="62"/>
+      <c r="E190" s="62"/>
+      <c r="F190" s="62"/>
+      <c r="G190" s="62"/>
+      <c r="H190" s="62"/>
+      <c r="I190" s="62"/>
+      <c r="J190" s="62"/>
+      <c r="K190" s="62"/>
+      <c r="L190" s="62"/>
+      <c r="M190" s="62">
+        <v>0</v>
+      </c>
+      <c r="N190" s="62">
+        <v>0</v>
+      </c>
+      <c r="O190" s="62">
+        <v>0</v>
+      </c>
+      <c r="P190" s="62">
+        <v>61390</v>
+      </c>
+      <c r="Q190" s="62">
+        <v>88101</v>
+      </c>
+      <c r="T190" s="62">
+        <v>15650</v>
+      </c>
+      <c r="U190" s="62">
+        <v>17381</v>
+      </c>
+      <c r="V190" s="62">
+        <v>16486</v>
+      </c>
+      <c r="W190" s="62">
+        <v>21513</v>
+      </c>
+      <c r="X190" s="62">
+        <v>17213</v>
+      </c>
+      <c r="Y190" s="62">
+        <v>20875</v>
+      </c>
+      <c r="Z190" s="62">
+        <v>28500</v>
+      </c>
+      <c r="AA190" s="62">
+        <v>37377</v>
+      </c>
+      <c r="AC190" s="62">
+        <f t="shared" ref="AC190:AC192" si="115">SUM(X190:AA190)</f>
+        <v>103965</v>
+      </c>
+    </row>
+    <row r="191" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B191" s="20" t="s">
+        <v>372</v>
+      </c>
+      <c r="C191" s="62"/>
+      <c r="D191" s="62"/>
+      <c r="E191" s="62"/>
+      <c r="F191" s="62"/>
+      <c r="G191" s="62"/>
+      <c r="H191" s="62"/>
+      <c r="I191" s="62"/>
+      <c r="J191" s="62"/>
+      <c r="K191" s="62"/>
+      <c r="L191" s="62"/>
+      <c r="M191" s="62">
+        <v>0</v>
+      </c>
+      <c r="N191" s="62">
+        <v>0</v>
+      </c>
+      <c r="O191" s="62">
+        <v>0</v>
+      </c>
+      <c r="P191" s="62">
+        <v>115186</v>
+      </c>
+      <c r="Q191" s="62">
+        <v>193737</v>
+      </c>
+      <c r="T191" s="62">
+        <v>26272</v>
+      </c>
+      <c r="U191" s="62">
+        <v>30771</v>
+      </c>
+      <c r="V191" s="62">
+        <v>35580</v>
+      </c>
+      <c r="W191" s="62">
+        <v>39112</v>
+      </c>
+      <c r="X191" s="62">
+        <v>41096</v>
+      </c>
+      <c r="Y191" s="62">
+        <v>51215</v>
+      </c>
+      <c r="Z191" s="62">
+        <v>62314</v>
+      </c>
+      <c r="AA191" s="62">
+        <v>75246</v>
+      </c>
+      <c r="AC191" s="62">
+        <f t="shared" si="115"/>
+        <v>229871</v>
+      </c>
+    </row>
+    <row r="192" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B192" s="20" t="s">
+        <v>373</v>
+      </c>
+      <c r="C192" s="21"/>
+      <c r="D192" s="21"/>
+      <c r="E192" s="21"/>
+      <c r="F192" s="21"/>
+      <c r="G192" s="21"/>
+      <c r="H192" s="21"/>
+      <c r="I192" s="62"/>
+      <c r="J192" s="62"/>
+      <c r="K192" s="62"/>
+      <c r="L192" s="62"/>
+      <c r="M192" s="62">
+        <v>0</v>
+      </c>
+      <c r="N192" s="62">
+        <v>0</v>
+      </c>
+      <c r="O192" s="62">
+        <v>0</v>
+      </c>
+      <c r="P192" s="62">
         <v>15311</v>
       </c>
-      <c r="Q189" s="62">
+      <c r="Q192" s="62">
         <v>22201</v>
       </c>
-      <c r="R189" s="62"/>
-      <c r="S189" s="62"/>
-      <c r="T189" s="62">
+      <c r="R192" s="62"/>
+      <c r="S192" s="62"/>
+      <c r="T192" s="62">
         <v>3768</v>
       </c>
-      <c r="U189" s="62">
+      <c r="U192" s="62">
         <v>4311</v>
       </c>
-      <c r="V189" s="62">
+      <c r="V192" s="62">
         <v>3751</v>
       </c>
-      <c r="W189" s="62">
+      <c r="W192" s="62">
         <v>4950</v>
       </c>
-      <c r="X189" s="62">
+      <c r="X192" s="62">
         <v>5647</v>
       </c>
-      <c r="Y189" s="62">
+      <c r="Y192" s="62">
         <v>5791</v>
       </c>
-      <c r="Z189" s="62">
+      <c r="Z192" s="62">
         <v>5813</v>
       </c>
-      <c r="AA189" s="62">
+      <c r="AA192" s="62">
         <v>6369</v>
       </c>
-      <c r="AC189" s="62">
-        <f t="shared" si="107"/>
+      <c r="AC192" s="62">
+        <f t="shared" si="115"/>
         <v>23620</v>
       </c>
     </row>
-    <row r="190" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C190" s="21"/>
-      <c r="D190" s="21"/>
-      <c r="E190" s="21"/>
-      <c r="F190" s="21"/>
-      <c r="G190" s="21"/>
-      <c r="H190" s="21"/>
-      <c r="I190" s="21"/>
-      <c r="J190" s="21"/>
-      <c r="K190" s="21"/>
-      <c r="L190" s="21"/>
-      <c r="M190" s="21"/>
-    </row>
-    <row r="191" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B191" s="1"/>
-    </row>
-    <row r="192" spans="1:31" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B192" s="14" t="s">
+    <row r="193" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="C193" s="21"/>
+      <c r="D193" s="21"/>
+      <c r="E193" s="21"/>
+      <c r="F193" s="21"/>
+      <c r="G193" s="21"/>
+      <c r="H193" s="21"/>
+      <c r="I193" s="21"/>
+      <c r="J193" s="21"/>
+      <c r="K193" s="21"/>
+      <c r="L193" s="21"/>
+      <c r="M193" s="21"/>
+    </row>
+    <row r="194" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B194" s="1"/>
+    </row>
+    <row r="195" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B195" s="14" t="s">
         <v>308</v>
       </c>
-      <c r="C192" s="172"/>
-      <c r="D192" s="172"/>
-      <c r="E192" s="172"/>
-      <c r="F192" s="172"/>
-      <c r="G192" s="172"/>
-      <c r="H192" s="172"/>
-      <c r="I192" s="172"/>
-      <c r="J192" s="172"/>
-      <c r="K192" s="172"/>
-      <c r="L192" s="172"/>
-      <c r="M192" s="172"/>
-      <c r="N192" s="172"/>
-      <c r="O192" s="172"/>
-      <c r="P192" s="172"/>
-      <c r="Q192" s="172"/>
-      <c r="T192" s="172"/>
-      <c r="U192" s="172"/>
-      <c r="V192" s="172"/>
-      <c r="W192" s="172"/>
-      <c r="X192" s="172"/>
-      <c r="Y192" s="172"/>
-      <c r="Z192" s="172"/>
-      <c r="AA192" s="172"/>
-      <c r="AC192" s="172"/>
-    </row>
-    <row r="193" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B193" s="226" t="s">
+      <c r="C195" s="172"/>
+      <c r="D195" s="172"/>
+      <c r="E195" s="172"/>
+      <c r="F195" s="172"/>
+      <c r="G195" s="172"/>
+      <c r="H195" s="172"/>
+      <c r="I195" s="172"/>
+      <c r="J195" s="172"/>
+      <c r="K195" s="172"/>
+      <c r="L195" s="172"/>
+      <c r="M195" s="172"/>
+      <c r="N195" s="172"/>
+      <c r="O195" s="172"/>
+      <c r="P195" s="172"/>
+      <c r="Q195" s="172"/>
+      <c r="T195" s="172"/>
+      <c r="U195" s="172"/>
+      <c r="V195" s="172"/>
+      <c r="W195" s="172"/>
+      <c r="X195" s="172"/>
+      <c r="Y195" s="172"/>
+      <c r="Z195" s="172"/>
+      <c r="AA195" s="172"/>
+      <c r="AC195" s="172"/>
+    </row>
+    <row r="196" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B196" s="224" t="s">
         <v>370</v>
       </c>
-      <c r="C193" s="81"/>
-      <c r="D193" s="81"/>
-      <c r="E193" s="81"/>
-      <c r="F193" s="81"/>
-      <c r="G193" s="81"/>
-      <c r="H193" s="81"/>
-      <c r="I193" s="81"/>
-      <c r="J193" s="81"/>
-      <c r="K193" s="81"/>
-      <c r="L193" s="81"/>
-      <c r="M193" s="81">
-        <f t="shared" ref="M193:Q196" si="108">IF(L186=0,
-IF(M186=0,0,IF(M186&gt;0,1,-1)),
-(M186-L186)/ABS(L186)
+      <c r="C196" s="81"/>
+      <c r="D196" s="81"/>
+      <c r="E196" s="81"/>
+      <c r="F196" s="81"/>
+      <c r="G196" s="81"/>
+      <c r="H196" s="81"/>
+      <c r="I196" s="81"/>
+      <c r="J196" s="81"/>
+      <c r="K196" s="81"/>
+      <c r="L196" s="81"/>
+      <c r="M196" s="81">
+        <f t="shared" ref="M196:Q199" si="116">IF(L189=0,
+IF(M189=0,0,IF(M189&gt;0,1,-1)),
+(M189-L189)/ABS(L189)
 )</f>
         <v>0</v>
       </c>
-      <c r="N193" s="81">
-        <f t="shared" si="108"/>
-        <v>0</v>
-      </c>
-      <c r="O193" s="81">
-        <f t="shared" si="108"/>
-        <v>0</v>
-      </c>
-      <c r="P193" s="81">
-        <f t="shared" si="108"/>
+      <c r="N196" s="81">
+        <f t="shared" si="116"/>
+        <v>0</v>
+      </c>
+      <c r="O196" s="81">
+        <f t="shared" si="116"/>
+        <v>0</v>
+      </c>
+      <c r="P196" s="81">
+        <f t="shared" si="116"/>
         <v>1</v>
       </c>
-      <c r="Q193" s="81">
-        <f t="shared" si="108"/>
+      <c r="Q196" s="81">
+        <f t="shared" si="116"/>
         <v>0.96364041936203437</v>
       </c>
-      <c r="T193" s="81">
-        <f t="shared" ref="T193:AA196" si="109">IF(S186=0,
-IF(T186=0,0,IF(T186&gt;0,1,-1)),
-(T186-S186)/ABS(S186)
+      <c r="T196" s="81">
+        <f t="shared" ref="T196:AA199" si="117">IF(S189=0,
+IF(T189=0,0,IF(T189&gt;0,1,-1)),
+(T189-S189)/ABS(S189)
 )</f>
         <v>1</v>
       </c>
-      <c r="U193" s="81">
-        <f t="shared" si="109"/>
+      <c r="U196" s="81">
+        <f t="shared" si="117"/>
         <v>0.26059122575786103</v>
       </c>
-      <c r="V193" s="81">
-        <f t="shared" si="109"/>
+      <c r="V196" s="81">
+        <f t="shared" si="117"/>
         <v>0.42598954443614639</v>
       </c>
-      <c r="W193" s="81">
-        <f t="shared" si="109"/>
+      <c r="W196" s="81">
+        <f t="shared" si="117"/>
         <v>-7.8296847177123707E-2</v>
       </c>
-      <c r="X193" s="81">
-        <f t="shared" si="109"/>
+      <c r="X196" s="81">
+        <f t="shared" si="117"/>
         <v>0.35706574237172567</v>
       </c>
-      <c r="Y193" s="81">
-        <f t="shared" si="109"/>
+      <c r="Y196" s="81">
+        <f t="shared" si="117"/>
         <v>0.27035967005820039</v>
       </c>
-      <c r="Z193" s="81">
-        <f t="shared" si="109"/>
+      <c r="Z196" s="81">
+        <f t="shared" si="117"/>
         <v>0.11450230718523402</v>
       </c>
-      <c r="AA193" s="81">
-        <f t="shared" si="109"/>
+      <c r="AA196" s="81">
+        <f t="shared" si="117"/>
         <v>0.11992074288756137</v>
       </c>
-      <c r="AC193" s="49"/>
-    </row>
-    <row r="194" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B194" s="226" t="s">
+      <c r="AC196" s="49"/>
+    </row>
+    <row r="197" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B197" s="224" t="s">
         <v>371</v>
       </c>
-      <c r="M194" s="81">
-        <f t="shared" si="108"/>
-        <v>0</v>
-      </c>
-      <c r="N194" s="81">
-        <f t="shared" si="108"/>
-        <v>0</v>
-      </c>
-      <c r="O194" s="81">
-        <f t="shared" si="108"/>
-        <v>0</v>
-      </c>
-      <c r="P194" s="81">
-        <f t="shared" si="108"/>
+      <c r="M197" s="81">
+        <f t="shared" si="116"/>
+        <v>0</v>
+      </c>
+      <c r="N197" s="81">
+        <f t="shared" si="116"/>
+        <v>0</v>
+      </c>
+      <c r="O197" s="81">
+        <f t="shared" si="116"/>
+        <v>0</v>
+      </c>
+      <c r="P197" s="81">
+        <f t="shared" si="116"/>
         <v>1</v>
       </c>
-      <c r="Q194" s="81">
-        <f t="shared" si="108"/>
+      <c r="Q197" s="81">
+        <f t="shared" si="116"/>
         <v>0.43510343704186349</v>
       </c>
-      <c r="T194" s="81">
-        <f t="shared" si="109"/>
+      <c r="T197" s="81">
+        <f t="shared" si="117"/>
         <v>1</v>
       </c>
-      <c r="U194" s="81">
-        <f t="shared" si="109"/>
+      <c r="U197" s="81">
+        <f t="shared" si="117"/>
         <v>0.11060702875399361</v>
       </c>
-      <c r="V194" s="81">
-        <f t="shared" si="109"/>
+      <c r="V197" s="81">
+        <f t="shared" si="117"/>
         <v>-5.1493009608192856E-2</v>
       </c>
-      <c r="W194" s="81">
-        <f t="shared" si="109"/>
+      <c r="W197" s="81">
+        <f t="shared" si="117"/>
         <v>0.304925391241053</v>
       </c>
-      <c r="X194" s="81">
-        <f t="shared" si="109"/>
+      <c r="X197" s="81">
+        <f t="shared" si="117"/>
         <v>-0.19987914284386185</v>
       </c>
-      <c r="Y194" s="81">
-        <f t="shared" si="109"/>
+      <c r="Y197" s="81">
+        <f t="shared" si="117"/>
         <v>0.21274618021262998</v>
       </c>
-      <c r="Z194" s="81">
-        <f t="shared" si="109"/>
+      <c r="Z197" s="81">
+        <f t="shared" si="117"/>
         <v>0.3652694610778443</v>
       </c>
-      <c r="AA194" s="81">
-        <f t="shared" si="109"/>
+      <c r="AA197" s="81">
+        <f t="shared" si="117"/>
         <v>0.31147368421052629</v>
       </c>
-      <c r="AC194" s="49"/>
-    </row>
-    <row r="195" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B195" s="20" t="s">
+      <c r="AC197" s="49"/>
+    </row>
+    <row r="198" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B198" s="20" t="s">
         <v>372</v>
       </c>
-      <c r="M195" s="81">
-        <f t="shared" si="108"/>
-        <v>0</v>
-      </c>
-      <c r="N195" s="81">
-        <f t="shared" si="108"/>
-        <v>0</v>
-      </c>
-      <c r="O195" s="81">
-        <f t="shared" si="108"/>
-        <v>0</v>
-      </c>
-      <c r="P195" s="81">
-        <f t="shared" si="108"/>
+      <c r="M198" s="81">
+        <f t="shared" si="116"/>
+        <v>0</v>
+      </c>
+      <c r="N198" s="81">
+        <f t="shared" si="116"/>
+        <v>0</v>
+      </c>
+      <c r="O198" s="81">
+        <f t="shared" si="116"/>
+        <v>0</v>
+      </c>
+      <c r="P198" s="81">
+        <f t="shared" si="116"/>
         <v>1</v>
       </c>
-      <c r="Q195" s="81">
-        <f t="shared" si="108"/>
+      <c r="Q198" s="81">
+        <f t="shared" si="116"/>
         <v>0.68194919521469621</v>
       </c>
-      <c r="T195" s="81">
-        <f t="shared" si="109"/>
+      <c r="T198" s="81">
+        <f t="shared" si="117"/>
         <v>1</v>
       </c>
-      <c r="U195" s="81">
-        <f t="shared" si="109"/>
+      <c r="U198" s="81">
+        <f t="shared" si="117"/>
         <v>0.17124695493300854</v>
       </c>
-      <c r="V195" s="81">
-        <f t="shared" si="109"/>
+      <c r="V198" s="81">
+        <f t="shared" si="117"/>
         <v>0.15628351369796237</v>
       </c>
-      <c r="W195" s="81">
-        <f t="shared" si="109"/>
+      <c r="W198" s="81">
+        <f t="shared" si="117"/>
         <v>9.9269252388982571E-2</v>
       </c>
-      <c r="X195" s="81">
-        <f t="shared" si="109"/>
+      <c r="X198" s="81">
+        <f t="shared" si="117"/>
         <v>5.0726119860912251E-2</v>
       </c>
-      <c r="Y195" s="81">
-        <f t="shared" si="109"/>
+      <c r="Y198" s="81">
+        <f t="shared" si="117"/>
         <v>0.24622834339108429</v>
       </c>
-      <c r="Z195" s="81">
-        <f t="shared" si="109"/>
+      <c r="Z198" s="81">
+        <f t="shared" si="117"/>
         <v>0.21671385336327248</v>
       </c>
-      <c r="AA195" s="81">
-        <f t="shared" si="109"/>
+      <c r="AA198" s="81">
+        <f t="shared" si="117"/>
         <v>0.20752960811374652</v>
       </c>
-      <c r="AC195" s="49"/>
-    </row>
-    <row r="196" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B196" s="20" t="s">
+      <c r="AC198" s="49"/>
+    </row>
+    <row r="199" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B199" s="20" t="s">
         <v>373</v>
       </c>
-      <c r="M196" s="81">
-        <f t="shared" si="108"/>
-        <v>0</v>
-      </c>
-      <c r="N196" s="81">
-        <f t="shared" si="108"/>
-        <v>0</v>
-      </c>
-      <c r="O196" s="81">
-        <f t="shared" si="108"/>
-        <v>0</v>
-      </c>
-      <c r="P196" s="81">
-        <f t="shared" si="108"/>
+      <c r="M199" s="81">
+        <f t="shared" si="116"/>
+        <v>0</v>
+      </c>
+      <c r="N199" s="81">
+        <f t="shared" si="116"/>
+        <v>0</v>
+      </c>
+      <c r="O199" s="81">
+        <f t="shared" si="116"/>
+        <v>0</v>
+      </c>
+      <c r="P199" s="81">
+        <f t="shared" si="116"/>
         <v>1</v>
       </c>
-      <c r="Q196" s="81">
-        <f t="shared" si="108"/>
+      <c r="Q199" s="81">
+        <f t="shared" si="116"/>
         <v>0.4500032656260205</v>
       </c>
-      <c r="T196" s="81">
-        <f t="shared" si="109"/>
+      <c r="T199" s="81">
+        <f t="shared" si="117"/>
         <v>1</v>
       </c>
-      <c r="U196" s="81">
-        <f t="shared" si="109"/>
+      <c r="U199" s="81">
+        <f t="shared" si="117"/>
         <v>0.14410828025477707</v>
       </c>
-      <c r="V196" s="81">
-        <f t="shared" si="109"/>
+      <c r="V199" s="81">
+        <f t="shared" si="117"/>
         <v>-0.12990025516121551</v>
       </c>
-      <c r="W196" s="81">
-        <f t="shared" si="109"/>
+      <c r="W199" s="81">
+        <f t="shared" si="117"/>
         <v>0.31964809384164222</v>
       </c>
-      <c r="X196" s="81">
-        <f t="shared" si="109"/>
+      <c r="X199" s="81">
+        <f t="shared" si="117"/>
         <v>0.1408080808080808</v>
       </c>
-      <c r="Y196" s="81">
-        <f t="shared" si="109"/>
+      <c r="Y199" s="81">
+        <f t="shared" si="117"/>
         <v>2.5500265627766958E-2</v>
       </c>
-      <c r="Z196" s="81">
-        <f t="shared" si="109"/>
+      <c r="Z199" s="81">
+        <f t="shared" si="117"/>
         <v>3.7989984458642722E-3</v>
       </c>
-      <c r="AA196" s="81">
-        <f t="shared" si="109"/>
+      <c r="AA199" s="81">
+        <f t="shared" si="117"/>
         <v>9.5647686220540165E-2</v>
       </c>
-      <c r="AC196" s="49"/>
-    </row>
-    <row r="198" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B198" s="1"/>
-    </row>
-    <row r="199" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B199" s="14" t="s">
+      <c r="AC199" s="49"/>
+    </row>
+    <row r="201" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B201" s="1"/>
+    </row>
+    <row r="202" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B202" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="C199" s="172"/>
-      <c r="D199" s="172"/>
-      <c r="E199" s="172"/>
-      <c r="F199" s="172"/>
-      <c r="G199" s="172"/>
-      <c r="H199" s="172"/>
-      <c r="I199" s="172"/>
-      <c r="J199" s="172"/>
-      <c r="K199" s="172"/>
-      <c r="L199" s="172"/>
-      <c r="M199" s="172"/>
-      <c r="N199" s="172"/>
-      <c r="O199" s="172"/>
-      <c r="P199" s="172"/>
-      <c r="Q199" s="172"/>
-      <c r="T199" s="172"/>
-      <c r="U199" s="172"/>
-      <c r="V199" s="172"/>
-      <c r="W199" s="172"/>
-      <c r="X199" s="172"/>
-      <c r="Y199" s="172"/>
-      <c r="Z199" s="172"/>
-      <c r="AA199" s="172"/>
-      <c r="AC199" s="172"/>
-    </row>
-    <row r="200" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B200" s="20" t="s">
+      <c r="C202" s="172"/>
+      <c r="D202" s="172"/>
+      <c r="E202" s="172"/>
+      <c r="F202" s="172"/>
+      <c r="G202" s="172"/>
+      <c r="H202" s="172"/>
+      <c r="I202" s="172"/>
+      <c r="J202" s="172"/>
+      <c r="K202" s="172"/>
+      <c r="L202" s="172"/>
+      <c r="M202" s="172"/>
+      <c r="N202" s="172"/>
+      <c r="O202" s="172"/>
+      <c r="P202" s="172"/>
+      <c r="Q202" s="172"/>
+      <c r="T202" s="172"/>
+      <c r="U202" s="172"/>
+      <c r="V202" s="172"/>
+      <c r="W202" s="172"/>
+      <c r="X202" s="172"/>
+      <c r="Y202" s="172"/>
+      <c r="Z202" s="172"/>
+      <c r="AA202" s="172"/>
+      <c r="AC202" s="172"/>
+    </row>
+    <row r="203" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B203" s="20" t="s">
         <v>281</v>
       </c>
-      <c r="C200" s="81"/>
-      <c r="D200" s="81"/>
-      <c r="E200" s="81"/>
-      <c r="F200" s="81"/>
-      <c r="G200" s="81"/>
-      <c r="H200" s="81"/>
-      <c r="I200" s="81"/>
-      <c r="J200" s="81"/>
-      <c r="K200" s="81"/>
-      <c r="L200" s="81"/>
-      <c r="M200" s="81">
+      <c r="C203" s="81"/>
+      <c r="D203" s="81"/>
+      <c r="E203" s="81"/>
+      <c r="F203" s="81"/>
+      <c r="G203" s="81"/>
+      <c r="H203" s="81"/>
+      <c r="I203" s="81"/>
+      <c r="J203" s="81"/>
+      <c r="K203" s="81"/>
+      <c r="L203" s="81"/>
+      <c r="M203" s="81">
         <f>IF(L63=0,
 IF(M63=0,0,IF(M63&gt;0,1,-1)),
 (M63-L63)/L63
 )</f>
         <v>-1</v>
       </c>
-      <c r="N200" s="81">
+      <c r="N203" s="81">
         <f>IF(M63=0,
 IF(N63=0,0,IF(N63&gt;0,1,-1)),
 (N63-M63)/M63
 )</f>
         <v>-2.5062656641604009E-3</v>
       </c>
-      <c r="O200" s="81">
+      <c r="O203" s="81">
         <f>IF(N63=0,
 IF(O63=0,0,IF(O63&gt;0,1,-1)),
 (O63-N63)/N63
 )</f>
         <v>-7.537688442211055E-3</v>
       </c>
-      <c r="P200" s="81">
+      <c r="P203" s="81">
         <f>IF(O63=0,
 IF(P63=0,0,IF(P63&gt;0,1,-1)),
 (P63-O63)/O63
 )</f>
         <v>1.1113924050632911</v>
       </c>
-      <c r="Q200" s="81">
+      <c r="Q203" s="81">
         <f>IF(P63=0,
 IF(Q63=0,0,IF(Q63&gt;0,1,-1)),
 (Q63-P63)/P63
 )</f>
         <v>0.16786570743405277</v>
       </c>
-      <c r="T200" s="49"/>
-      <c r="U200" s="49"/>
-      <c r="V200" s="49"/>
-      <c r="W200" s="49"/>
-      <c r="X200" s="49"/>
-      <c r="Y200" s="49"/>
-      <c r="Z200" s="49"/>
-      <c r="AA200" s="49"/>
-      <c r="AC200" s="49"/>
-    </row>
-    <row r="202" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B202" s="1"/>
-    </row>
-    <row r="203" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B203" s="14" t="s">
+      <c r="T203" s="49"/>
+      <c r="U203" s="49"/>
+      <c r="V203" s="49"/>
+      <c r="W203" s="49"/>
+      <c r="X203" s="49"/>
+      <c r="Y203" s="49"/>
+      <c r="Z203" s="49"/>
+      <c r="AA203" s="49"/>
+      <c r="AC203" s="49"/>
+    </row>
+    <row r="205" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B205" s="1"/>
+    </row>
+    <row r="206" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B206" s="14" t="s">
+        <v>390</v>
+      </c>
+      <c r="C206" s="172"/>
+      <c r="D206" s="172"/>
+      <c r="E206" s="172"/>
+      <c r="F206" s="172"/>
+      <c r="G206" s="172"/>
+      <c r="H206" s="172"/>
+      <c r="I206" s="172"/>
+      <c r="J206" s="172"/>
+      <c r="K206" s="172"/>
+      <c r="L206" s="172"/>
+      <c r="M206" s="172"/>
+      <c r="N206" s="172"/>
+      <c r="O206" s="172"/>
+      <c r="P206" s="172"/>
+      <c r="Q206" s="172"/>
+      <c r="T206" s="172"/>
+      <c r="U206" s="172"/>
+      <c r="V206" s="172"/>
+      <c r="W206" s="172"/>
+      <c r="X206" s="172"/>
+      <c r="Y206" s="172"/>
+      <c r="Z206" s="172"/>
+      <c r="AA206" s="172"/>
+      <c r="AC206" s="172"/>
+    </row>
+    <row r="207" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B207" s="20" t="s">
         <v>391</v>
       </c>
-      <c r="C203" s="172"/>
-      <c r="D203" s="172"/>
-      <c r="E203" s="172"/>
-      <c r="F203" s="172"/>
-      <c r="G203" s="172"/>
-      <c r="H203" s="172"/>
-      <c r="I203" s="172"/>
-      <c r="J203" s="172"/>
-      <c r="K203" s="172"/>
-      <c r="L203" s="172"/>
-      <c r="M203" s="172"/>
-      <c r="N203" s="172"/>
-      <c r="O203" s="172"/>
-      <c r="P203" s="172"/>
-      <c r="Q203" s="172"/>
-      <c r="T203" s="172"/>
-      <c r="U203" s="172"/>
-      <c r="V203" s="172"/>
-      <c r="W203" s="172"/>
-      <c r="X203" s="172"/>
-      <c r="Y203" s="172"/>
-      <c r="Z203" s="172"/>
-      <c r="AA203" s="172"/>
-      <c r="AC203" s="172"/>
-    </row>
-    <row r="204" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B204" s="20" t="s">
-        <v>392</v>
-      </c>
-      <c r="M204" s="144">
+      <c r="M207" s="144">
         <v>100</v>
       </c>
-      <c r="N204" s="144">
+      <c r="N207" s="144">
         <f>100*(1+((N115-$M115)/ABS($M115)))</f>
         <v>89.141856392294216</v>
       </c>
-      <c r="O204" s="144">
-        <f t="shared" ref="O204:Q204" si="110">100*(1+((O115-$M115)/ABS($M115)))</f>
+      <c r="O207" s="144">
+        <f t="shared" ref="O207:Q207" si="118">100*(1+((O115-$M115)/ABS($M115)))</f>
         <v>267.20665499124345</v>
       </c>
-      <c r="P204" s="144">
-        <f t="shared" si="110"/>
+      <c r="P207" s="144">
+        <f t="shared" si="118"/>
         <v>624.43082311733804</v>
       </c>
-      <c r="Q204" s="144">
-        <f t="shared" si="110"/>
+      <c r="Q207" s="144">
+        <f t="shared" si="118"/>
         <v>821.67250437828375</v>
       </c>
-      <c r="T204" s="49"/>
-      <c r="U204" s="49"/>
-      <c r="V204" s="49"/>
-      <c r="W204" s="49"/>
-      <c r="X204" s="49"/>
-      <c r="Y204" s="49"/>
-      <c r="Z204" s="49"/>
-      <c r="AA204" s="49"/>
-      <c r="AC204" s="49"/>
-    </row>
-    <row r="205" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B205" s="20" t="s">
-        <v>393</v>
-      </c>
-      <c r="M205" s="144">
+      <c r="T207" s="49"/>
+      <c r="U207" s="49"/>
+      <c r="V207" s="49"/>
+      <c r="W207" s="49"/>
+      <c r="X207" s="49"/>
+      <c r="Y207" s="49"/>
+      <c r="Z207" s="49"/>
+      <c r="AA207" s="49"/>
+      <c r="AC207" s="49"/>
+    </row>
+    <row r="208" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B208" s="20" t="s">
+        <v>392</v>
+      </c>
+      <c r="M208" s="144">
         <v>100</v>
       </c>
-      <c r="N205" s="144">
+      <c r="N208" s="144">
         <f>100*(1+((N5-$M5)/ABS($M5)))</f>
         <v>100.2229323028907</v>
       </c>
-      <c r="O205" s="144">
-        <f t="shared" ref="O205:Q205" si="111">100*(1+((O5-$M5)/ABS($M5)))</f>
+      <c r="O208" s="144">
+        <f t="shared" ref="O208:Q208" si="119">100*(1+((O5-$M5)/ABS($M5)))</f>
         <v>226.35802927844244</v>
       </c>
-      <c r="P205" s="144">
-        <f t="shared" si="111"/>
+      <c r="P208" s="144">
+        <f t="shared" si="119"/>
         <v>484.86661217210371</v>
       </c>
-      <c r="Q205" s="144">
-        <f t="shared" si="111"/>
+      <c r="Q208" s="144">
+        <f t="shared" si="119"/>
         <v>802.32592702682621</v>
       </c>
-      <c r="T205" s="49"/>
-      <c r="U205" s="49"/>
-      <c r="V205" s="49"/>
-      <c r="W205" s="49"/>
-      <c r="X205" s="49"/>
-      <c r="Y205" s="49"/>
-      <c r="Z205" s="49"/>
-      <c r="AA205" s="49"/>
-      <c r="AC205" s="49"/>
-    </row>
-    <row r="206" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B206" s="20" t="s">
-        <v>394</v>
-      </c>
-      <c r="M206" s="144">
+      <c r="T208" s="49"/>
+      <c r="U208" s="49"/>
+      <c r="V208" s="49"/>
+      <c r="W208" s="49"/>
+      <c r="X208" s="49"/>
+      <c r="Y208" s="49"/>
+      <c r="Z208" s="49"/>
+      <c r="AA208" s="49"/>
+      <c r="AC208" s="49"/>
+    </row>
+    <row r="209" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B209" s="20" t="s">
+        <v>393</v>
+      </c>
+      <c r="M209" s="144">
         <v>100</v>
       </c>
-      <c r="N206" s="144">
+      <c r="N209" s="144">
         <f>100*(1+((N25-$M25)/ABS($M25)))</f>
         <v>45.194805194805184</v>
       </c>
-      <c r="O206" s="144">
-        <f t="shared" ref="O206:Q206" si="112">100*(1+((O25-$M25)/ABS($M25)))</f>
+      <c r="O209" s="144">
+        <f t="shared" ref="O209:Q209" si="120">100*(1+((O25-$M25)/ABS($M25)))</f>
         <v>309.87012987012992</v>
       </c>
-      <c r="P206" s="144">
-        <f t="shared" si="112"/>
+      <c r="P209" s="144">
+        <f t="shared" si="120"/>
         <v>763.63636363636363</v>
       </c>
-      <c r="Q206" s="144">
-        <f t="shared" si="112"/>
+      <c r="Q209" s="144">
+        <f t="shared" si="120"/>
         <v>1272.7272727272727</v>
       </c>
-      <c r="T206" s="49"/>
-      <c r="U206" s="49"/>
-      <c r="V206" s="49"/>
-      <c r="W206" s="49"/>
-      <c r="X206" s="49"/>
-      <c r="Y206" s="49"/>
-      <c r="Z206" s="49"/>
-      <c r="AA206" s="49"/>
-      <c r="AC206" s="49"/>
-    </row>
-    <row r="208" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B208" s="1"/>
-    </row>
-    <row r="209" spans="1:31" s="15" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A209" s="11"/>
-      <c r="B209" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="R209" s="1"/>
-      <c r="S209" s="1"/>
-      <c r="AB209" s="1"/>
-      <c r="AD209" s="1"/>
-      <c r="AE209" s="1"/>
+      <c r="T209" s="49"/>
+      <c r="U209" s="49"/>
+      <c r="V209" s="49"/>
+      <c r="W209" s="49"/>
+      <c r="X209" s="49"/>
+      <c r="Y209" s="49"/>
+      <c r="Z209" s="49"/>
+      <c r="AA209" s="49"/>
+      <c r="AC209" s="49"/>
     </row>
     <row r="211" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B211" s="1"/>
+    </row>
+    <row r="212" spans="1:31" s="15" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A212" s="11"/>
+      <c r="B212" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="R212" s="1"/>
+      <c r="S212" s="1"/>
+      <c r="AB212" s="1"/>
+      <c r="AD212" s="1"/>
+      <c r="AE212" s="1"/>
+    </row>
+    <row r="214" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B214" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -31206,23 +31331,23 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="231" t="s">
+      <c r="B4" s="234" t="s">
         <v>230</v>
       </c>
-      <c r="C4" s="231"/>
-      <c r="E4" s="231" t="s">
+      <c r="C4" s="234"/>
+      <c r="E4" s="234" t="s">
         <v>237</v>
       </c>
-      <c r="F4" s="231"/>
-      <c r="G4" s="231"/>
+      <c r="F4" s="234"/>
+      <c r="G4" s="234"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="174">
+      <c r="C5" s="173">
         <f ca="1">Overview!C5</f>
-        <v>201.32499999999999</v>
+        <v>204.65</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="133" t="s">
@@ -31236,18 +31361,18 @@
       <c r="B6" s="20" t="s">
         <v>236</v>
       </c>
-      <c r="C6" s="175">
+      <c r="C6" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>4893204.125</v>
+        <v>4974018.25</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="180">
+      <c r="F6" s="179">
         <f>IF(Statement!M5&lt;=0,"N/A",_xlfn.RRI(4,Statement!M5,Statement!Q5))</f>
         <v>0.68301391480282692</v>
       </c>
-      <c r="G6" s="180" t="str">
+      <c r="G6" s="179" t="str">
         <f>IF(Statement!H5&lt;=0,"N/A",_xlfn.RRI(9,Statement!H5,Statement!Q5))</f>
         <v>N/A</v>
       </c>
@@ -31256,18 +31381,18 @@
       <c r="B7" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="C7" s="175">
+      <c r="C7" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>4821102.125</v>
+        <v>4901916.25</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="180">
+      <c r="F7" s="179">
         <f>IF(OR(Statement!M17&lt;=0, Statement!Q17&lt;=0), "N/A", _xlfn.RRI(4, Statement!M17, Statement!Q17))</f>
         <v>0.87319285132860491</v>
       </c>
-      <c r="G7" s="180" t="str">
+      <c r="G7" s="179" t="str">
         <f>IF(OR(Statement!H17&lt;=0, Statement!Q17&lt;=0), "N/A", _xlfn.RRI(9, Statement!H17, Statement!Q17))</f>
         <v>N/A</v>
       </c>
@@ -31276,18 +31401,18 @@
       <c r="B8" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="C8" s="176">
+      <c r="C8" s="175">
         <f ca="1">Statement!AC152</f>
-        <v>30.830781010719758</v>
+        <v>31.339969372128643</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="F8" s="180">
+      <c r="F8" s="179">
         <f>IF(OR(Statement!M25&lt;=0, Statement!Q25&lt;=0), "N/A", _xlfn.RRI(4, Statement!M25, Statement!Q25))</f>
         <v>0.88879070838020025</v>
       </c>
-      <c r="G8" s="180" t="str">
+      <c r="G8" s="179" t="str">
         <f>IF(OR(Statement!H25&lt;=0, Statement!Q25&lt;=0), "N/A", _xlfn.RRI(9, Statement!H25, Statement!Q25))</f>
         <v>N/A</v>
       </c>
@@ -31296,18 +31421,18 @@
       <c r="B9" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="C9" s="176">
+      <c r="C9" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>19.425971089703381</v>
+        <v>19.746802351957271</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>241</v>
       </c>
-      <c r="F9" s="180">
+      <c r="F9" s="179">
         <f>IF(Statement!M81&lt;=0,"N/A",_xlfn.RRI(4,Statement!M81,Statement!Q81))</f>
         <v>0.25743342968293548</v>
       </c>
-      <c r="G9" s="180" t="str">
+      <c r="G9" s="179" t="str">
         <f>IF(Statement!H81&lt;=0,"N/A",_xlfn.RRI(9,Statement!H81,Statement!Q81))</f>
         <v>N/A</v>
       </c>
@@ -31316,18 +31441,18 @@
       <c r="B10" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="C10" s="176">
+      <c r="C10" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>24.924363342439406</v>
+        <v>25.33600376520663</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="F10" s="180">
+      <c r="F10" s="179">
         <f>IF(Statement!M115&lt;=0,"N/A",_xlfn.RRI(4,Statement!M115,Statement!Q115))</f>
         <v>0.69306911979142294</v>
       </c>
-      <c r="G10" s="180" t="str">
+      <c r="G10" s="179" t="str">
         <f>IF(Statement!H115&lt;=0,"N/A",_xlfn.RRI(9,Statement!H115,Statement!Q115))</f>
         <v>N/A</v>
       </c>
@@ -31336,42 +31461,42 @@
       <c r="B11" s="20" t="s">
         <v>257</v>
       </c>
-      <c r="C11" s="176">
+      <c r="C11" s="175">
         <f ca="1">Statement!AC157</f>
-        <v>19.01882956396874</v>
+        <v>19.337634274984122</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="C12" s="176">
+      <c r="C12" s="175">
         <f ca="1">Statement!AC158</f>
-        <v>29.707626243953538</v>
+        <v>30.205602797547524</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="231" t="s">
+      <c r="B15" s="234" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="231"/>
-      <c r="E15" s="231" t="s">
+      <c r="C15" s="234"/>
+      <c r="E15" s="234" t="s">
         <v>243</v>
       </c>
-      <c r="F15" s="231"/>
+      <c r="F15" s="234"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="C16" s="177">
+      <c r="C16" s="176">
         <f>Statement!AC99</f>
         <v>0.74145433171197395</v>
       </c>
       <c r="E16" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="175">
+      <c r="F16" s="174">
         <f>Statement!AC17</f>
         <v>159613</v>
       </c>
@@ -31380,14 +31505,14 @@
       <c r="B17" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="C17" s="177">
+      <c r="C17" s="176">
         <f>Statement!AC100</f>
         <v>0.64020024379563767</v>
       </c>
       <c r="E17" s="20" t="s">
         <v>244</v>
       </c>
-      <c r="F17" s="175">
+      <c r="F17" s="174">
         <f>Statement!AC58</f>
         <v>125649</v>
       </c>
@@ -31396,40 +31521,40 @@
       <c r="B18" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="C18" s="177">
+      <c r="C18" s="176">
         <f>Statement!AC101</f>
         <v>0.62965943564071303</v>
       </c>
       <c r="E18" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="F18" s="179">
+      <c r="F18" s="178">
         <f>IF(OR(F16&lt;=0, F17&lt;=0),"N/A",F16-F17)</f>
         <v>33964</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="231" t="s">
+      <c r="B21" s="234" t="s">
         <v>242</v>
       </c>
-      <c r="C21" s="231"/>
-      <c r="E21" s="231" t="s">
+      <c r="C21" s="234"/>
+      <c r="E21" s="234" t="s">
         <v>246</v>
       </c>
-      <c r="F21" s="231"/>
+      <c r="F21" s="234"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="C22" s="177">
+      <c r="C22" s="176">
         <f>Statement!AC119</f>
         <v>0.62965943564071303</v>
       </c>
       <c r="E22" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="F22" s="177">
+      <c r="F22" s="176">
         <f>C24</f>
         <v>0.61514063066049007</v>
       </c>
@@ -31438,14 +31563,14 @@
       <c r="B23" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="C23" s="176">
+      <c r="C23" s="175">
         <f>Statement!AC120</f>
         <v>0.97694181305256023</v>
       </c>
       <c r="E23" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="F23" s="177">
+      <c r="F23" s="176">
         <f>C26</f>
         <v>0.81654337661274645</v>
       </c>
@@ -31454,14 +31579,14 @@
       <c r="B24" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="C24" s="178">
+      <c r="C24" s="177">
         <f>Statement!AC121</f>
         <v>0.61514063066049007</v>
       </c>
       <c r="E24" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="F24" s="177">
+      <c r="F24" s="176">
         <f>Statement!AC142</f>
         <v>1.1082908941558067</v>
       </c>
@@ -31470,7 +31595,7 @@
       <c r="B25" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="C25" s="176">
+      <c r="C25" s="175">
         <f>Statement!AC122</f>
         <v>1.3274092718213164</v>
       </c>
@@ -31479,33 +31604,33 @@
       <c r="B26" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="C26" s="178">
+      <c r="C26" s="177">
         <f>Statement!AC123</f>
         <v>0.81654337661274645</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="231" t="s">
+      <c r="B29" s="234" t="s">
         <v>247</v>
       </c>
-      <c r="C29" s="231"/>
-      <c r="E29" s="231" t="s">
+      <c r="C29" s="234"/>
+      <c r="E29" s="234" t="s">
         <v>253</v>
       </c>
-      <c r="F29" s="231"/>
+      <c r="F29" s="234"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="C30" s="176">
+      <c r="C30" s="175">
         <f>Statement!AC143</f>
         <v>58.61805744582648</v>
       </c>
       <c r="E30" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="F30" s="182">
+      <c r="F30" s="181">
         <f>Statement!AC147</f>
         <v>4.3330570817602339E-2</v>
       </c>
@@ -31514,14 +31639,14 @@
       <c r="B31" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="C31" s="176">
+      <c r="C31" s="175">
         <f>Statement!AC144</f>
         <v>143.6687315949282</v>
       </c>
       <c r="E31" s="20" t="s">
         <v>255</v>
       </c>
-      <c r="F31" s="182">
+      <c r="F31" s="181">
         <f>Statement!AC148</f>
         <v>-0.36885723932594616</v>
       </c>
@@ -31530,14 +31655,14 @@
       <c r="B32" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="C32" s="176">
+      <c r="C32" s="175">
         <f>Statement!AC145</f>
         <v>72.939852606844781</v>
       </c>
       <c r="E32" s="20" t="s">
         <v>250</v>
       </c>
-      <c r="F32" s="182">
+      <c r="F32" s="181">
         <f>Statement!AC150</f>
         <v>3.440775681341719</v>
       </c>
@@ -31546,14 +31671,14 @@
       <c r="B33" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="C33" s="176">
+      <c r="C33" s="175">
         <f>Statement!AC146</f>
         <v>129.34693643390989</v>
       </c>
       <c r="E33" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="F33" s="182">
+      <c r="F33" s="181">
         <f>Statement!AC149</f>
         <v>2.7636951964269438</v>
       </c>
@@ -31562,33 +31687,33 @@
       <c r="E34" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="F34" s="184" t="str">
+      <c r="F34" s="183" t="str">
         <f>Statement!AC151</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="231" t="s">
+      <c r="B37" s="234" t="s">
         <v>265</v>
       </c>
-      <c r="C37" s="231"/>
-      <c r="E37" s="231" t="s">
+      <c r="C37" s="234"/>
+      <c r="E37" s="234" t="s">
         <v>268</v>
       </c>
-      <c r="F37" s="231"/>
+      <c r="F37" s="234"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
         <v>263</v>
       </c>
-      <c r="C38" s="177">
+      <c r="C38" s="176">
         <f ca="1">Statement!AC164</f>
-        <v>3.2435117347572331E-2</v>
+        <v>3.1908135841680917E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="F38" s="177">
+      <c r="F38" s="176">
         <f>Statement!AC170</f>
         <v>8.6691554478469674E-3</v>
       </c>
@@ -31597,14 +31722,14 @@
       <c r="B39" s="54" t="s">
         <v>266</v>
       </c>
-      <c r="C39" s="217">
+      <c r="C39" s="216">
         <f ca="1">Statement!AC163</f>
-        <v>2.2937322280623229E-2</v>
+        <v>2.2564653838976163E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>269</v>
       </c>
-      <c r="F39" s="177">
+      <c r="F39" s="176">
         <f>Statement!AC171</f>
         <v>0.40364585653572349</v>
       </c>
@@ -31613,14 +31738,14 @@
       <c r="B40" s="20" t="s">
         <v>264</v>
       </c>
-      <c r="C40" s="177">
+      <c r="C40" s="176">
         <f ca="1">Statement!AC165</f>
-        <v>1.9868372035266362E-4</v>
+        <v>1.9545565599804544E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>270</v>
       </c>
-      <c r="F40" s="177">
+      <c r="F40" s="176">
         <f>Statement!AC172</f>
         <v>0.41231501198357046</v>
       </c>
@@ -31629,42 +31754,42 @@
       <c r="B41" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="C41" s="177">
+      <c r="C41" s="176">
         <f ca="1">Statement!AC166</f>
-        <v>9.2585550985980983E-3</v>
+        <v>9.108129026265635E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B42" s="20" t="s">
         <v>291</v>
       </c>
-      <c r="C42" s="177">
+      <c r="C42" s="176">
         <f ca="1">Statement!AC167</f>
-        <v>9.4574023110061863E-3</v>
+        <v>9.3037455180225766E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="231" t="s">
+      <c r="B45" s="234" t="s">
         <v>276</v>
       </c>
-      <c r="C45" s="231"/>
-      <c r="E45" s="231" t="s">
+      <c r="C45" s="234"/>
+      <c r="E45" s="234" t="s">
         <v>282</v>
       </c>
-      <c r="F45" s="231"/>
+      <c r="F45" s="234"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
         <v>274</v>
       </c>
-      <c r="C46" s="177">
+      <c r="C46" s="176">
         <f>Statement!AC173</f>
         <v>3.9374614276897757E-2</v>
       </c>
       <c r="E46" s="20" t="s">
         <v>275</v>
       </c>
-      <c r="F46" s="176">
+      <c r="F46" s="175">
         <f>Statement!AC174</f>
         <v>3.3294214876033057</v>
       </c>
@@ -31673,7 +31798,7 @@
       <c r="E47" s="20" t="s">
         <v>283</v>
       </c>
-      <c r="F47" s="176">
+      <c r="F47" s="175">
         <f>Statement!AC177</f>
         <v>2.9794214876033056</v>
       </c>
@@ -31682,33 +31807,33 @@
       <c r="E48" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="F48" s="177">
+      <c r="F48" s="176">
         <f ca="1">Statement!AC178</f>
-        <v>1.473513022512626E-2</v>
+        <v>1.4495724859875615E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="231" t="s">
+      <c r="B51" s="234" t="s">
         <v>279</v>
       </c>
-      <c r="C51" s="231"/>
-      <c r="E51" s="231" t="s">
+      <c r="C51" s="234"/>
+      <c r="E51" s="234" t="s">
         <v>300</v>
       </c>
-      <c r="F51" s="231"/>
+      <c r="F51" s="234"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
         <v>277</v>
       </c>
-      <c r="C52" s="177">
+      <c r="C52" s="176">
         <f>Statement!AC175</f>
         <v>5.4437361220542942E-2</v>
       </c>
       <c r="E52" s="20" t="s">
         <v>301</v>
       </c>
-      <c r="F52" s="177">
+      <c r="F52" s="176">
         <f>Statement!AC179</f>
         <v>2.5925969758295166E-2</v>
       </c>
@@ -31717,14 +31842,14 @@
       <c r="B53" s="20" t="s">
         <v>278</v>
       </c>
-      <c r="C53" s="177">
+      <c r="C53" s="176">
         <f>Statement!AC176</f>
         <v>2.6983206504372935E-2</v>
       </c>
       <c r="E53" s="20" t="s">
         <v>298</v>
       </c>
-      <c r="F53" s="177">
+      <c r="F53" s="176">
         <f>Statement!AC180</f>
         <v>5.2304435371550904E-2</v>
       </c>
@@ -31733,7 +31858,7 @@
       <c r="E54" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="F54" s="177">
+      <c r="F54" s="176">
         <f>Statement!AC181</f>
         <v>2.0359355638166048</v>
       </c>
@@ -31842,232 +31967,232 @@
       <c r="B6" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="174">
+      <c r="C6" s="173">
         <f>Statement!M114</f>
         <v>228.4</v>
       </c>
-      <c r="D6" s="174">
+      <c r="D6" s="173">
         <f>Statement!N114</f>
         <v>203.6</v>
       </c>
-      <c r="E6" s="174">
+      <c r="E6" s="173">
         <f>Statement!O114</f>
         <v>610.29999999999995</v>
       </c>
-      <c r="F6" s="174">
+      <c r="F6" s="173">
         <f>Statement!P114</f>
         <v>142.62</v>
       </c>
-      <c r="G6" s="174">
+      <c r="G6" s="173">
         <f>Statement!Q114</f>
         <v>187.67</v>
       </c>
-      <c r="I6" s="174">
+      <c r="I6" s="173">
         <f ca="1">Statement!AC114</f>
-        <v>201.32499999999999</v>
+        <v>204.65</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B7" s="20" t="s">
         <v>236</v>
       </c>
-      <c r="C7" s="175">
+      <c r="C7" s="174">
         <f>Statement!M155</f>
         <v>582191.6</v>
       </c>
-      <c r="D7" s="175">
+      <c r="D7" s="174">
         <f>Statement!N155</f>
         <v>506964</v>
       </c>
-      <c r="E7" s="175">
+      <c r="E7" s="174">
         <f>Statement!O155</f>
         <v>1541007.4999999998</v>
       </c>
-      <c r="F7" s="175">
+      <c r="F7" s="174">
         <f>Statement!P155</f>
         <v>3515440.38</v>
       </c>
-      <c r="G7" s="175">
+      <c r="G7" s="174">
         <f>Statement!Q155</f>
         <v>4589469.8499999996</v>
       </c>
-      <c r="I7" s="175">
+      <c r="I7" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>4893204.125</v>
+        <v>4974018.25</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="C8" s="175">
+      <c r="C8" s="174">
         <f>Statement!M156</f>
         <v>571929.59999999998</v>
       </c>
-      <c r="D8" s="175">
+      <c r="D8" s="174">
         <f>Statement!N156</f>
         <v>504621</v>
       </c>
-      <c r="E8" s="175">
+      <c r="E8" s="174">
         <f>Statement!O156</f>
         <v>1524732.4999999998</v>
       </c>
-      <c r="F8" s="175">
+      <c r="F8" s="174">
         <f>Statement!P156</f>
         <v>3480693.38</v>
       </c>
-      <c r="G8" s="175">
+      <c r="G8" s="174">
         <f>Statement!Q156</f>
         <v>4535381.8499999996</v>
       </c>
-      <c r="I8" s="175">
+      <c r="I8" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>4821102.125</v>
+        <v>4901916.25</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B9" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="C9" s="176">
+      <c r="C9" s="175">
         <f>Statement!M152</f>
         <v>59.324675324675326</v>
       </c>
-      <c r="D9" s="176">
+      <c r="D9" s="175">
         <f>Statement!N152</f>
         <v>117.01149425287356</v>
       </c>
-      <c r="E9" s="176">
+      <c r="E9" s="175">
         <f>Statement!O152</f>
         <v>51.156747694886832</v>
       </c>
-      <c r="F9" s="176">
+      <c r="F9" s="175">
         <f>Statement!P152</f>
         <v>48.510204081632658</v>
       </c>
-      <c r="G9" s="176">
+      <c r="G9" s="175">
         <f>Statement!Q152</f>
         <v>38.299999999999997</v>
       </c>
-      <c r="I9" s="176">
+      <c r="I9" s="175">
         <f ca="1">Statement!AC152</f>
-        <v>30.830781010719758</v>
+        <v>31.339969372128643</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="C10" s="176">
+      <c r="C10" s="175">
         <f>Statement!M153</f>
         <v>21.512744296648584</v>
       </c>
-      <c r="D10" s="176">
+      <c r="D10" s="175">
         <f>Statement!N153</f>
         <v>18.922859049455031</v>
       </c>
-      <c r="E10" s="176">
+      <c r="E10" s="175">
         <f>Statement!O153</f>
         <v>24.984212599717669</v>
       </c>
-      <c r="F10" s="176">
+      <c r="F10" s="175">
         <f>Statement!P153</f>
         <v>27.108259040437712</v>
       </c>
-      <c r="G10" s="176">
+      <c r="G10" s="175">
         <f>Statement!Q153</f>
         <v>21.304922616677011</v>
       </c>
-      <c r="I10" s="176">
+      <c r="I10" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>19.425971089703381</v>
+        <v>19.746802351957271</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B11" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="C11" s="176">
+      <c r="C11" s="175">
         <f>Statement!M154</f>
         <v>21.542311739065084</v>
       </c>
-      <c r="D11" s="176">
+      <c r="D11" s="175">
         <f>Statement!N154</f>
         <v>22.754264512917967</v>
       </c>
-      <c r="E11" s="176">
+      <c r="E11" s="175">
         <f>Statement!O154</f>
         <v>35.500721299269394</v>
       </c>
-      <c r="F11" s="176">
+      <c r="F11" s="175">
         <f>Statement!P154</f>
         <v>43.868140733924143</v>
       </c>
-      <c r="G11" s="176">
+      <c r="G11" s="175">
         <f>Statement!Q154</f>
         <v>28.992904960805632</v>
       </c>
-      <c r="I11" s="176">
+      <c r="I11" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>24.924363342439406</v>
+        <v>25.33600376520663</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B12" s="20" t="s">
         <v>257</v>
       </c>
-      <c r="C12" s="176">
+      <c r="C12" s="175">
         <f>Statement!M157</f>
         <v>21.250263803225085</v>
       </c>
-      <c r="D12" s="176">
+      <c r="D12" s="175">
         <f>Statement!N157</f>
         <v>18.707681471046193</v>
       </c>
-      <c r="E12" s="176">
+      <c r="E12" s="175">
         <f>Statement!O157</f>
         <v>25.02761728111355</v>
       </c>
-      <c r="F12" s="176">
+      <c r="F12" s="175">
         <f>Statement!P157</f>
         <v>26.672593086431103</v>
       </c>
-      <c r="G12" s="176">
+      <c r="G12" s="175">
         <f>Statement!Q157</f>
         <v>21.003166881234428</v>
       </c>
-      <c r="I12" s="176">
+      <c r="I12" s="175">
         <f ca="1">Statement!AC157</f>
-        <v>19.01882956396874</v>
+        <v>19.337634274984122</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B13" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="C13" s="176">
+      <c r="C13" s="175">
         <f>Statement!M158</f>
         <v>56.959426351956971</v>
       </c>
-      <c r="D13" s="176">
+      <c r="D13" s="175">
         <f>Statement!N158</f>
         <v>119.46519886363636</v>
       </c>
-      <c r="E13" s="176">
+      <c r="E13" s="175">
         <f>Statement!O158</f>
         <v>46.243251850054584</v>
       </c>
-      <c r="F13" s="176">
+      <c r="F13" s="175">
         <f>Statement!P158</f>
         <v>42.732537536984516</v>
       </c>
-      <c r="G13" s="176">
+      <c r="G13" s="175">
         <f>Statement!Q158</f>
         <v>34.784003389908499</v>
       </c>
-      <c r="I13" s="176">
+      <c r="I13" s="175">
         <f ca="1">Statement!AC158</f>
-        <v>29.707626243953538</v>
+        <v>30.205602797547524</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -32085,27 +32210,27 @@
       <c r="B16" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="C16" s="177">
+      <c r="C16" s="176">
         <f>Statement!M99</f>
         <v>0.64929033216913135</v>
       </c>
-      <c r="D16" s="177">
+      <c r="D16" s="176">
         <f>Statement!N99</f>
         <v>0.56928894490991322</v>
       </c>
-      <c r="E16" s="177">
+      <c r="E16" s="176">
         <f>Statement!O99</f>
         <v>0.72717573290436954</v>
       </c>
-      <c r="F16" s="177">
+      <c r="F16" s="176">
         <f>Statement!P99</f>
         <v>0.74988697058169917</v>
       </c>
-      <c r="G16" s="177">
+      <c r="G16" s="176">
         <f>Statement!Q99</f>
         <v>0.71068084357547079</v>
       </c>
-      <c r="I16" s="177">
+      <c r="I16" s="176">
         <f>Statement!AC99</f>
         <v>0.74145433171197395</v>
       </c>
@@ -32114,27 +32239,27 @@
       <c r="B17" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="C17" s="177">
+      <c r="C17" s="176">
         <f>Statement!M100</f>
         <v>0.37307720888756779</v>
       </c>
-      <c r="D17" s="177">
+      <c r="D17" s="176">
         <f>Statement!N100</f>
         <v>0.1565952398606065</v>
       </c>
-      <c r="E17" s="177">
+      <c r="E17" s="176">
         <f>Statement!O100</f>
         <v>0.54121663766783756</v>
       </c>
-      <c r="F17" s="177">
+      <c r="F17" s="176">
         <f>Statement!P100</f>
         <v>0.62417526839697468</v>
       </c>
-      <c r="G17" s="177">
+      <c r="G17" s="176">
         <f>Statement!Q100</f>
         <v>0.60381683631412719</v>
       </c>
-      <c r="I17" s="177">
+      <c r="I17" s="176">
         <f>Statement!AC100</f>
         <v>0.64020024379563767</v>
       </c>
@@ -32143,27 +32268,27 @@
       <c r="B18" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="C18" s="177">
+      <c r="C18" s="176">
         <f>Statement!M101</f>
         <v>0.36233930296499961</v>
       </c>
-      <c r="D18" s="177">
+      <c r="D18" s="176">
         <f>Statement!N101</f>
         <v>0.16193371394676356</v>
       </c>
-      <c r="E18" s="177">
+      <c r="E18" s="176">
         <f>Statement!O101</f>
         <v>0.4884934834706674</v>
       </c>
-      <c r="F18" s="177">
+      <c r="F18" s="176">
         <f>Statement!P101</f>
         <v>0.55848027157712443</v>
       </c>
-      <c r="G18" s="177">
+      <c r="G18" s="176">
         <f>Statement!Q101</f>
         <v>0.55602534060702613</v>
       </c>
-      <c r="I18" s="177">
+      <c r="I18" s="176">
         <f>Statement!AC101</f>
         <v>0.62965943564071303</v>
       </c>
@@ -32183,27 +32308,27 @@
       <c r="B21" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="179">
+      <c r="C21" s="178">
         <f>Statement!M17</f>
         <v>9752</v>
       </c>
-      <c r="D21" s="179">
+      <c r="D21" s="178">
         <f>Statement!N17</f>
         <v>4368</v>
       </c>
-      <c r="E21" s="179">
+      <c r="E21" s="178">
         <f>Statement!O17</f>
         <v>29760</v>
       </c>
-      <c r="F21" s="179">
+      <c r="F21" s="178">
         <f>Statement!P17</f>
         <v>72880</v>
       </c>
-      <c r="G21" s="179">
+      <c r="G21" s="178">
         <f>Statement!Q17</f>
         <v>120067</v>
       </c>
-      <c r="I21" s="179">
+      <c r="I21" s="178">
         <f>Statement!AC17</f>
         <v>159613</v>
       </c>
@@ -32212,27 +32337,27 @@
       <c r="B22" s="20" t="s">
         <v>244</v>
       </c>
-      <c r="C22" s="179">
+      <c r="C22" s="178">
         <f>Statement!M58</f>
         <v>9108</v>
       </c>
-      <c r="D22" s="179">
+      <c r="D22" s="178">
         <f>Statement!N58</f>
         <v>5641</v>
       </c>
-      <c r="E22" s="179">
+      <c r="E22" s="178">
         <f>Statement!O58</f>
         <v>28090</v>
       </c>
-      <c r="F22" s="179">
+      <c r="F22" s="178">
         <f>Statement!P58</f>
         <v>64089</v>
       </c>
-      <c r="G22" s="179">
+      <c r="G22" s="178">
         <f>Statement!Q58</f>
         <v>102718</v>
       </c>
-      <c r="I22" s="179">
+      <c r="I22" s="178">
         <f>Statement!AC58</f>
         <v>125649</v>
       </c>
@@ -32241,27 +32366,27 @@
       <c r="B23" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="C23" s="197">
+      <c r="C23" s="196">
         <f>IF(OR(C21&lt;=0, C22&lt;=0),"N/A",C21-C22)</f>
         <v>644</v>
       </c>
-      <c r="D23" s="197">
+      <c r="D23" s="196">
         <f t="shared" ref="D23:I23" si="0">IF(OR(D21&lt;=0, D22&lt;=0),"N/A",D21-D22)</f>
         <v>-1273</v>
       </c>
-      <c r="E23" s="197">
+      <c r="E23" s="196">
         <f t="shared" si="0"/>
         <v>1670</v>
       </c>
-      <c r="F23" s="197">
+      <c r="F23" s="196">
         <f t="shared" si="0"/>
         <v>8791</v>
       </c>
-      <c r="G23" s="197">
+      <c r="G23" s="196">
         <f t="shared" si="0"/>
         <v>17349</v>
       </c>
-      <c r="I23" s="197">
+      <c r="I23" s="196">
         <f t="shared" si="0"/>
         <v>33964</v>
       </c>
@@ -32281,27 +32406,27 @@
       <c r="B26" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="C26" s="177">
+      <c r="C26" s="176">
         <f>Statement!M119</f>
         <v>0.36233930296499961</v>
       </c>
-      <c r="D26" s="177">
+      <c r="D26" s="176">
         <f>Statement!N119</f>
         <v>0.16193371394676356</v>
       </c>
-      <c r="E26" s="177">
+      <c r="E26" s="176">
         <f>Statement!O119</f>
         <v>0.4884934834706674</v>
       </c>
-      <c r="F26" s="177">
+      <c r="F26" s="176">
         <f>Statement!P119</f>
         <v>0.55848027157712443</v>
       </c>
-      <c r="G26" s="177">
+      <c r="G26" s="176">
         <f>Statement!Q119</f>
         <v>0.55602534060702613</v>
       </c>
-      <c r="I26" s="177">
+      <c r="I26" s="176">
         <f>Statement!AC119</f>
         <v>0.62965943564071303</v>
       </c>
@@ -32310,27 +32435,27 @@
       <c r="B27" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="C27" s="216">
+      <c r="C27" s="215">
         <f>Statement!M120</f>
         <v>0.60909317219996828</v>
       </c>
-      <c r="D27" s="216">
+      <c r="D27" s="215">
         <f>Statement!N120</f>
         <v>0.65499490068476518</v>
       </c>
-      <c r="E27" s="216">
+      <c r="E27" s="215">
         <f>Statement!O120</f>
         <v>0.92688047711781885</v>
       </c>
-      <c r="F27" s="216">
+      <c r="F27" s="215">
         <f>Statement!P120</f>
         <v>1.169317479234057</v>
       </c>
-      <c r="G27" s="216">
+      <c r="G27" s="215">
         <f>Statement!Q120</f>
         <v>1.0441724733200195</v>
       </c>
-      <c r="I27" s="216">
+      <c r="I27" s="215">
         <f>Statement!AC120</f>
         <v>0.97694181305256023</v>
       </c>
@@ -32339,27 +32464,27 @@
       <c r="B28" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="C28" s="178">
+      <c r="C28" s="177">
         <f>Statement!M121</f>
         <v>0.22069839545567699</v>
       </c>
-      <c r="D28" s="178">
+      <c r="D28" s="177">
         <f>Statement!N121</f>
         <v>0.10606575688407557</v>
       </c>
-      <c r="E28" s="178">
+      <c r="E28" s="177">
         <f>Statement!O121</f>
         <v>0.45277507302823755</v>
       </c>
-      <c r="F28" s="178">
+      <c r="F28" s="177">
         <f>Statement!P121</f>
         <v>0.65304074336251472</v>
       </c>
-      <c r="G28" s="178">
+      <c r="G28" s="177">
         <f>Statement!Q121</f>
         <v>0.5805863551302447</v>
       </c>
-      <c r="I28" s="178">
+      <c r="I28" s="177">
         <f>Statement!AC121</f>
         <v>0.61514063066049007</v>
       </c>
@@ -32368,27 +32493,27 @@
       <c r="B29" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="C29" s="216">
+      <c r="C29" s="215">
         <f>Statement!M122</f>
         <v>1.6604163535247256</v>
       </c>
-      <c r="D29" s="216">
+      <c r="D29" s="215">
         <f>Statement!N122</f>
         <v>1.8633545993393965</v>
       </c>
-      <c r="E29" s="216">
+      <c r="E29" s="215">
         <f>Statement!O122</f>
         <v>1.5293405928614641</v>
       </c>
-      <c r="F29" s="216">
+      <c r="F29" s="215">
         <f>Statement!P122</f>
         <v>1.4068476054811099</v>
       </c>
-      <c r="G29" s="216">
+      <c r="G29" s="215">
         <f>Statement!Q122</f>
         <v>1.3147628947251309</v>
       </c>
-      <c r="I29" s="216">
+      <c r="I29" s="215">
         <f>Statement!AC122</f>
         <v>1.3274092718213164</v>
       </c>
@@ -32397,27 +32522,27 @@
       <c r="B30" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="C30" s="178">
+      <c r="C30" s="177">
         <f>Statement!M123</f>
         <v>0.36645122501127303</v>
       </c>
-      <c r="D30" s="178">
+      <c r="D30" s="177">
         <f>Statement!N123</f>
         <v>0.19763811592235647</v>
       </c>
-      <c r="E30" s="178">
+      <c r="E30" s="177">
         <f>Statement!O123</f>
         <v>0.69244729861789756</v>
       </c>
-      <c r="F30" s="178">
+      <c r="F30" s="177">
         <f>Statement!P123</f>
         <v>0.91872880608115781</v>
       </c>
-      <c r="G30" s="178">
+      <c r="G30" s="177">
         <f>Statement!Q123</f>
         <v>0.76333339690895341</v>
       </c>
-      <c r="I30" s="178">
+      <c r="I30" s="177">
         <f>Statement!AC123</f>
         <v>0.81654337661274645</v>
       </c>
@@ -32437,27 +32562,27 @@
       <c r="B33" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="C33" s="177">
+      <c r="C33" s="176">
         <f>C28</f>
         <v>0.22069839545567699</v>
       </c>
-      <c r="D33" s="177">
+      <c r="D33" s="176">
         <f t="shared" ref="D33:G33" si="1">D28</f>
         <v>0.10606575688407557</v>
       </c>
-      <c r="E33" s="177">
+      <c r="E33" s="176">
         <f t="shared" si="1"/>
         <v>0.45277507302823755</v>
       </c>
-      <c r="F33" s="177">
+      <c r="F33" s="176">
         <f t="shared" si="1"/>
         <v>0.65304074336251472</v>
       </c>
-      <c r="G33" s="177">
+      <c r="G33" s="176">
         <f t="shared" si="1"/>
         <v>0.5805863551302447</v>
       </c>
-      <c r="I33" s="177">
+      <c r="I33" s="176">
         <f>I28</f>
         <v>0.61514063066049007</v>
       </c>
@@ -32466,27 +32591,27 @@
       <c r="B34" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="C34" s="177">
+      <c r="C34" s="176">
         <f>C30</f>
         <v>0.36645122501127303</v>
       </c>
-      <c r="D34" s="177">
+      <c r="D34" s="176">
         <f t="shared" ref="D34:G34" si="2">D30</f>
         <v>0.19763811592235647</v>
       </c>
-      <c r="E34" s="177">
+      <c r="E34" s="176">
         <f t="shared" si="2"/>
         <v>0.69244729861789756</v>
       </c>
-      <c r="F34" s="177">
+      <c r="F34" s="176">
         <f t="shared" si="2"/>
         <v>0.91872880608115781</v>
       </c>
-      <c r="G34" s="177">
+      <c r="G34" s="176">
         <f t="shared" si="2"/>
         <v>0.76333339690895341</v>
       </c>
-      <c r="I34" s="177">
+      <c r="I34" s="176">
         <f>I30</f>
         <v>0.81654337661274645</v>
       </c>
@@ -32495,27 +32620,27 @@
       <c r="B35" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="C35" s="177">
+      <c r="C35" s="176">
         <f>Statement!M142</f>
         <v>0.60245252494303547</v>
       </c>
-      <c r="D35" s="177">
+      <c r="D35" s="176">
         <f>Statement!N142</f>
         <v>0.21378682052839357</v>
       </c>
-      <c r="E35" s="177">
+      <c r="E35" s="176">
         <f>Statement!O142</f>
         <v>1.0866013555554745</v>
       </c>
-      <c r="F35" s="177">
+      <c r="F35" s="176">
         <f>Statement!P142</f>
         <v>1.5847534085376831</v>
       </c>
-      <c r="G35" s="177">
+      <c r="G35" s="176">
         <f>Statement!Q142</f>
         <v>1.0723937210768841</v>
       </c>
-      <c r="I35" s="177">
+      <c r="I35" s="176">
         <f>Statement!AC142</f>
         <v>1.1082908941558067</v>
       </c>
@@ -32535,27 +32660,27 @@
       <c r="B38" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="C38" s="176">
+      <c r="C38" s="175">
         <f>Statement!M143</f>
         <v>63.061975180203611</v>
       </c>
-      <c r="D38" s="176">
+      <c r="D38" s="175">
         <f>Statement!N143</f>
         <v>51.785237636242307</v>
       </c>
-      <c r="E38" s="176">
+      <c r="E38" s="175">
         <f>Statement!O143</f>
         <v>59.906683956534586</v>
       </c>
-      <c r="F38" s="176">
+      <c r="F38" s="175">
         <f>Statement!P143</f>
         <v>64.512785734537957</v>
       </c>
-      <c r="G38" s="176">
+      <c r="G38" s="175">
         <f>Statement!Q143</f>
         <v>65.01907955061175</v>
       </c>
-      <c r="I38" s="176">
+      <c r="I38" s="175">
         <f>Statement!AC143</f>
         <v>58.61805744582648</v>
       </c>
@@ -32564,27 +32689,27 @@
       <c r="B39" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="C39" s="176">
+      <c r="C39" s="175">
         <f>Statement!M144</f>
         <v>100.73365822650703</v>
       </c>
-      <c r="D39" s="176">
+      <c r="D39" s="175">
         <f>Statement!N144</f>
         <v>162.079101394388</v>
       </c>
-      <c r="E39" s="176">
+      <c r="E39" s="175">
         <f>Statement!O144</f>
         <v>115.99362252572048</v>
       </c>
-      <c r="F39" s="176">
+      <c r="F39" s="175">
         <f>Statement!P144</f>
         <v>112.72404179049603</v>
       </c>
-      <c r="G39" s="176">
+      <c r="G39" s="175">
         <f>Statement!Q144</f>
         <v>125.043537414966</v>
       </c>
-      <c r="I39" s="176">
+      <c r="I39" s="175">
         <f>Statement!AC144</f>
         <v>143.6687315949282</v>
       </c>
@@ -32593,27 +32718,27 @@
       <c r="B40" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="C40" s="176">
+      <c r="C40" s="175">
         <f>Statement!M145</f>
         <v>68.947452060599645</v>
       </c>
-      <c r="D40" s="176">
+      <c r="D40" s="175">
         <f>Statement!N145</f>
         <v>37.480203133069374</v>
       </c>
-      <c r="E40" s="176">
+      <c r="E40" s="175">
         <f>Statement!O145</f>
         <v>59.270501173214605</v>
       </c>
-      <c r="F40" s="176">
+      <c r="F40" s="175">
         <f>Statement!P145</f>
         <v>70.564355525598216</v>
       </c>
-      <c r="G40" s="176">
+      <c r="G40" s="175">
         <f>Statement!Q145</f>
         <v>57.325010004001605</v>
       </c>
-      <c r="I40" s="176">
+      <c r="I40" s="175">
         <f>Statement!AC145</f>
         <v>72.939852606844781</v>
       </c>
@@ -32622,27 +32747,27 @@
       <c r="B41" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="C41" s="176">
+      <c r="C41" s="175">
         <f>Statement!M146</f>
         <v>94.848181346110991</v>
       </c>
-      <c r="D41" s="176">
+      <c r="D41" s="175">
         <f>Statement!N146</f>
         <v>176.38413589756092</v>
       </c>
-      <c r="E41" s="176">
+      <c r="E41" s="175">
         <f>Statement!O146</f>
         <v>116.62980530904048</v>
       </c>
-      <c r="F41" s="176">
+      <c r="F41" s="175">
         <f>Statement!P146</f>
         <v>106.67247199943577</v>
       </c>
-      <c r="G41" s="176">
+      <c r="G41" s="175">
         <f>Statement!Q146</f>
         <v>132.73760696157615</v>
       </c>
-      <c r="I41" s="176">
+      <c r="I41" s="175">
         <f>Statement!AC146</f>
         <v>129.34693643390989</v>
       </c>
@@ -32662,27 +32787,27 @@
       <c r="B44" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="C44" s="182">
+      <c r="C44" s="181">
         <f>Statement!M147</f>
         <v>0.41131820231474525</v>
       </c>
-      <c r="D44" s="182">
+      <c r="D44" s="181">
         <f>Statement!N147</f>
         <v>0.49558843491244742</v>
       </c>
-      <c r="E44" s="182">
+      <c r="E44" s="181">
         <f>Statement!O147</f>
         <v>0.22590627763041557</v>
       </c>
-      <c r="F44" s="182">
+      <c r="F44" s="181">
         <f>Statement!P147</f>
         <v>0.10668498745698186</v>
       </c>
-      <c r="G44" s="182">
+      <c r="G44" s="181">
         <f>Statement!Q147</f>
         <v>5.3835835033981171E-2</v>
       </c>
-      <c r="I44" s="182">
+      <c r="I44" s="181">
         <f>Statement!AC147</f>
         <v>4.3330570817602339E-2</v>
       </c>
@@ -32691,27 +32816,27 @@
       <c r="B45" s="20" t="s">
         <v>255</v>
       </c>
-      <c r="C45" s="182">
+      <c r="C45" s="181">
         <f>Statement!M148</f>
         <v>-0.38561551179918835</v>
       </c>
-      <c r="D45" s="182">
+      <c r="D45" s="181">
         <f>Statement!N148</f>
         <v>-0.10601330256549478</v>
       </c>
-      <c r="E45" s="182">
+      <c r="E45" s="181">
         <f>Statement!O148</f>
         <v>-0.37868211643166272</v>
       </c>
-      <c r="F45" s="182">
+      <c r="F45" s="181">
         <f>Statement!P148</f>
         <v>-0.43802236312982967</v>
       </c>
-      <c r="G45" s="182">
+      <c r="G45" s="181">
         <f>Statement!Q148</f>
         <v>-0.34386781357085183</v>
       </c>
-      <c r="I45" s="182">
+      <c r="I45" s="181">
         <f>Statement!AC148</f>
         <v>-0.36885723932594616</v>
       </c>
@@ -32720,27 +32845,27 @@
       <c r="B46" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="C46" s="182">
+      <c r="C46" s="181">
         <f>Statement!M149</f>
         <v>5.9649365628604381</v>
       </c>
-      <c r="D46" s="182">
+      <c r="D46" s="181">
         <f>Statement!N149</f>
         <v>2.6090202651226573</v>
       </c>
-      <c r="E46" s="182">
+      <c r="E46" s="181">
         <f>Statement!O149</f>
         <v>3.3847239206095381</v>
       </c>
-      <c r="F46" s="182">
+      <c r="F46" s="181">
         <f>Statement!P149</f>
         <v>3.672355516152269</v>
       </c>
-      <c r="G46" s="182">
+      <c r="G46" s="181">
         <f>Statement!Q149</f>
         <v>3.1409383453036099</v>
       </c>
-      <c r="I46" s="182">
+      <c r="I46" s="181">
         <f>Statement!AC149</f>
         <v>2.7636951964269438</v>
       </c>
@@ -32749,27 +32874,27 @@
       <c r="B47" s="20" t="s">
         <v>250</v>
       </c>
-      <c r="C47" s="182">
+      <c r="C47" s="181">
         <f>Statement!M150</f>
         <v>6.6502883506343711</v>
       </c>
-      <c r="D47" s="182">
+      <c r="D47" s="181">
         <f>Statement!N150</f>
         <v>3.5156178576870332</v>
       </c>
-      <c r="E47" s="182">
+      <c r="E47" s="181">
         <f>Statement!O150</f>
         <v>4.1712915059730973</v>
       </c>
-      <c r="F47" s="182">
+      <c r="F47" s="181">
         <f>Statement!P150</f>
         <v>4.4398514988640772</v>
       </c>
-      <c r="G47" s="182">
+      <c r="G47" s="181">
         <f>Statement!Q150</f>
         <v>3.9052638124553058</v>
       </c>
-      <c r="I47" s="182">
+      <c r="I47" s="181">
         <f>Statement!AC150</f>
         <v>3.440775681341719</v>
       </c>
@@ -32778,27 +32903,27 @@
       <c r="B48" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="C48" s="184">
+      <c r="C48" s="183">
         <f>Statement!M151</f>
         <v>48.507246376811594</v>
       </c>
-      <c r="D48" s="184" t="str">
+      <c r="D48" s="183" t="str">
         <f>Statement!N151</f>
         <v>N/A</v>
       </c>
-      <c r="E48" s="184" t="str">
+      <c r="E48" s="183" t="str">
         <f>Statement!O151</f>
         <v>N/A</v>
       </c>
-      <c r="F48" s="184" t="str">
+      <c r="F48" s="183" t="str">
         <f>Statement!P151</f>
         <v>N/A</v>
       </c>
-      <c r="G48" s="184" t="str">
+      <c r="G48" s="183" t="str">
         <f>Statement!Q151</f>
         <v>N/A</v>
       </c>
-      <c r="I48" s="184" t="str">
+      <c r="I48" s="183" t="str">
         <f>Statement!AC151</f>
         <v>N/A</v>
       </c>
@@ -32818,145 +32943,145 @@
       <c r="B51" s="20" t="s">
         <v>263</v>
       </c>
-      <c r="C51" s="177">
+      <c r="C51" s="176">
         <f>Statement!M164</f>
         <v>1.6856392294220666E-2</v>
       </c>
-      <c r="D51" s="177">
+      <c r="D51" s="176">
         <f>Statement!N164</f>
         <v>8.546168958742632E-3</v>
       </c>
-      <c r="E51" s="177">
+      <c r="E51" s="176">
         <f>Statement!O164</f>
         <v>1.9547763395051616E-2</v>
       </c>
-      <c r="F51" s="177">
+      <c r="F51" s="176">
         <f>Statement!P164</f>
         <v>2.061421960454354E-2</v>
       </c>
-      <c r="G51" s="177">
+      <c r="G51" s="176">
         <f>Statement!Q164</f>
         <v>2.6109660574412535E-2</v>
       </c>
-      <c r="I51" s="177">
+      <c r="I51" s="176">
         <f ca="1">Statement!AC164</f>
-        <v>3.2435117347572331E-2</v>
+        <v>3.1908135841680917E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
         <v>266</v>
       </c>
-      <c r="C52" s="177">
+      <c r="C52" s="176">
         <f>Statement!M163</f>
         <v>1.0525744445642981E-2</v>
       </c>
-      <c r="D52" s="177">
+      <c r="D52" s="176">
         <f>Statement!N163</f>
         <v>2.1678067870696933E-3</v>
       </c>
-      <c r="E52" s="177">
+      <c r="E52" s="176">
         <f>Statement!O163</f>
         <v>1.5231593616513875E-2</v>
       </c>
-      <c r="F52" s="177">
+      <c r="F52" s="176">
         <f>Statement!P163</f>
         <v>1.5962722712993357E-2</v>
       </c>
-      <c r="G52" s="177">
+      <c r="G52" s="176">
         <f>Statement!Q163</f>
         <v>1.9673296252289359E-2</v>
       </c>
-      <c r="I52" s="177">
+      <c r="I52" s="176">
         <f ca="1">Statement!AC163</f>
-        <v>2.2937322280623229E-2</v>
+        <v>2.2564653838976163E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B53" s="20" t="s">
         <v>264</v>
       </c>
-      <c r="C53" s="177">
+      <c r="C53" s="176">
         <f>Statement!M165</f>
         <v>7.0052539404553418E-4</v>
       </c>
-      <c r="D53" s="177">
+      <c r="D53" s="176">
         <f>Statement!N165</f>
         <v>7.8585461689587434E-4</v>
       </c>
-      <c r="E53" s="177">
+      <c r="E53" s="176">
         <f>Statement!O165</f>
         <v>2.6216614779616586E-4</v>
       </c>
-      <c r="F53" s="177">
+      <c r="F53" s="176">
         <f>Statement!P165</f>
         <v>2.3839573692329268E-4</v>
       </c>
-      <c r="G53" s="177">
+      <c r="G53" s="176">
         <f>Statement!Q165</f>
         <v>2.1314008632173498E-4</v>
       </c>
-      <c r="I53" s="177">
+      <c r="I53" s="176">
         <f ca="1">Statement!AC165</f>
-        <v>1.9868372035266362E-4</v>
+        <v>1.9545565599804544E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B54" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="C54" s="177">
+      <c r="C54" s="176">
         <f>Statement!M166</f>
         <v>0</v>
       </c>
-      <c r="D54" s="177">
+      <c r="D54" s="176">
         <f>Statement!N166</f>
         <v>1.9802195027654824E-2</v>
       </c>
-      <c r="E54" s="177">
+      <c r="E54" s="176">
         <f>Statement!O166</f>
         <v>6.1862125914377451E-3</v>
       </c>
-      <c r="F54" s="177">
+      <c r="F54" s="176">
         <f>Statement!P166</f>
         <v>9.5879879493220143E-3</v>
       </c>
-      <c r="G54" s="177">
+      <c r="G54" s="176">
         <f>Statement!Q166</f>
         <v>8.7343421593672754E-3</v>
       </c>
-      <c r="I54" s="177">
+      <c r="I54" s="176">
         <f ca="1">Statement!AC166</f>
-        <v>9.2585550985980983E-3</v>
+        <v>9.108129026265635E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B55" s="20" t="s">
         <v>291</v>
       </c>
-      <c r="C55" s="177">
+      <c r="C55" s="176">
         <f>Statement!M167</f>
         <v>6.853413893295609E-4</v>
       </c>
-      <c r="D55" s="177">
+      <c r="D55" s="176">
         <f>Statement!N167</f>
         <v>2.0587260633891165E-2</v>
       </c>
-      <c r="E55" s="177">
+      <c r="E55" s="176">
         <f>Statement!O167</f>
         <v>6.4425384042582539E-3</v>
       </c>
-      <c r="F55" s="177">
+      <c r="F55" s="176">
         <f>Statement!P167</f>
         <v>9.8252270743957263E-3</v>
       </c>
-      <c r="G55" s="177">
+      <c r="G55" s="176">
         <f>Statement!Q167</f>
         <v>8.946567107309792E-3</v>
       </c>
-      <c r="I55" s="177">
+      <c r="I55" s="176">
         <f ca="1">Statement!AC167</f>
-        <v>9.4574023110061863E-3</v>
+        <v>9.3037455180225766E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -32974,27 +33099,27 @@
       <c r="B58" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="C58" s="177">
+      <c r="C58" s="176">
         <f>Statement!M170</f>
         <v>6.5110966057441252E-2</v>
       </c>
-      <c r="D58" s="177">
+      <c r="D58" s="176">
         <f>Statement!N170</f>
         <v>0.36214740673339402</v>
       </c>
-      <c r="E58" s="177">
+      <c r="E58" s="176">
         <f>Statement!O170</f>
         <v>1.6828561690524879E-2</v>
       </c>
-      <c r="F58" s="177">
+      <c r="F58" s="176">
         <f>Statement!P170</f>
         <v>1.4862071423479934E-2</v>
       </c>
-      <c r="G58" s="177">
+      <c r="G58" s="176">
         <f>Statement!Q170</f>
         <v>1.0787462620445233E-2</v>
       </c>
-      <c r="I58" s="177">
+      <c r="I58" s="176">
         <f>Statement!AC170</f>
         <v>8.6691554478469674E-3</v>
       </c>
@@ -33003,27 +33128,27 @@
       <c r="B59" s="20" t="s">
         <v>269</v>
       </c>
-      <c r="C59" s="177">
+      <c r="C59" s="176">
         <f>Statement!M171</f>
         <v>0</v>
       </c>
-      <c r="D59" s="177">
+      <c r="D59" s="176">
         <f>Statement!N171</f>
         <v>9.1346678798908094</v>
       </c>
-      <c r="E59" s="177">
+      <c r="E59" s="176">
         <f>Statement!O171</f>
         <v>0.40614349011588274</v>
       </c>
-      <c r="F59" s="177">
+      <c r="F59" s="176">
         <f>Statement!P171</f>
         <v>0.60064865635469389</v>
       </c>
-      <c r="G59" s="177">
+      <c r="G59" s="176">
         <f>Statement!Q171</f>
         <v>0.44396943183076754</v>
       </c>
-      <c r="I59" s="177">
+      <c r="I59" s="176">
         <f>Statement!AC171</f>
         <v>0.40364585653572349</v>
       </c>
@@ -33032,27 +33157,27 @@
       <c r="B60" s="20" t="s">
         <v>270</v>
       </c>
-      <c r="C60" s="177">
+      <c r="C60" s="176">
         <f>Statement!M172</f>
         <v>6.5110966057441252E-2</v>
       </c>
-      <c r="D60" s="177">
+      <c r="D60" s="176">
         <f>Statement!N172</f>
         <v>9.4968152866242033</v>
       </c>
-      <c r="E60" s="177">
+      <c r="E60" s="176">
         <f>Statement!O172</f>
         <v>0.42297205180640762</v>
       </c>
-      <c r="F60" s="177">
+      <c r="F60" s="176">
         <f>Statement!P172</f>
         <v>0.61551072777817373</v>
       </c>
-      <c r="G60" s="177">
+      <c r="G60" s="176">
         <f>Statement!Q172</f>
         <v>0.45475689445121276</v>
       </c>
-      <c r="I60" s="177">
+      <c r="I60" s="176">
         <f>Statement!AC172</f>
         <v>0.41231501198357046</v>
       </c>
@@ -33072,27 +33197,27 @@
       <c r="B63" s="20" t="s">
         <v>274</v>
       </c>
-      <c r="C63" s="177">
+      <c r="C63" s="176">
         <f>Statement!M173</f>
         <v>3.9623381718320909E-2</v>
       </c>
-      <c r="D63" s="177">
+      <c r="D63" s="176">
         <f>Statement!N173</f>
         <v>3.9759036144578312E-2</v>
       </c>
-      <c r="E63" s="177">
+      <c r="E63" s="176">
         <f>Statement!O173</f>
         <v>4.118811881188119E-2</v>
       </c>
-      <c r="F63" s="177">
+      <c r="F63" s="176">
         <f>Statement!P173</f>
         <v>4.1380989086778369E-2</v>
       </c>
-      <c r="G63" s="177">
+      <c r="G63" s="176">
         <f>Statement!Q173</f>
         <v>3.9133101615211614E-2</v>
       </c>
-      <c r="I63" s="177">
+      <c r="I63" s="176">
         <f>Statement!AC173</f>
         <v>3.9374614276897757E-2</v>
       </c>
@@ -33112,27 +33237,27 @@
       <c r="B66" s="20" t="s">
         <v>275</v>
       </c>
-      <c r="C66" s="176">
+      <c r="C66" s="175">
         <f>Statement!M174</f>
         <v>0.84494023904382465</v>
       </c>
-      <c r="D66" s="176">
+      <c r="D66" s="175">
         <f>Statement!N174</f>
         <v>0.53829959514170045</v>
       </c>
-      <c r="E66" s="176">
+      <c r="E66" s="175">
         <f>Statement!O174</f>
         <v>1.0393600000000001</v>
       </c>
-      <c r="F66" s="176">
+      <c r="F66" s="175">
         <f>Statement!P174</f>
         <v>1.7709016393442623</v>
       </c>
-      <c r="G66" s="176">
+      <c r="G66" s="175">
         <f>Statement!Q174</f>
         <v>2.5743209876543212</v>
       </c>
-      <c r="I66" s="176">
+      <c r="I66" s="175">
         <f>Statement!AC174</f>
         <v>3.3294214876033057</v>
       </c>
@@ -33141,27 +33266,27 @@
       <c r="B67" s="20" t="s">
         <v>283</v>
       </c>
-      <c r="C67" s="176">
+      <c r="C67" s="175">
         <f>Statement!M177</f>
         <v>0.40884462151394424</v>
       </c>
-      <c r="D67" s="176">
+      <c r="D67" s="175">
         <f>Statement!N177</f>
         <v>9.4858299595141707E-2</v>
       </c>
-      <c r="E67" s="176">
+      <c r="E67" s="175">
         <f>Statement!O177</f>
         <v>0.65100000000000002</v>
       </c>
-      <c r="F67" s="176">
+      <c r="F67" s="175">
         <f>Statement!P177</f>
         <v>1.4240573770491802</v>
       </c>
-      <c r="G67" s="176">
+      <c r="G67" s="175">
         <f>Statement!Q177</f>
         <v>2.2258436213991768</v>
       </c>
-      <c r="I67" s="176">
+      <c r="I67" s="175">
         <f>Statement!AC177</f>
         <v>2.9794214876033056</v>
       </c>
@@ -33170,29 +33295,29 @@
       <c r="B68" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="C68" s="198">
+      <c r="C68" s="197">
         <f>Statement!M178</f>
         <v>1.7626499592230463E-2</v>
       </c>
-      <c r="D68" s="198">
+      <c r="D68" s="197">
         <f>Statement!N178</f>
         <v>4.6216299382204652E-3</v>
       </c>
-      <c r="E68" s="198">
+      <c r="E68" s="197">
         <f>Statement!O178</f>
         <v>1.0561272414313365E-2</v>
       </c>
-      <c r="F68" s="198">
+      <c r="F68" s="197">
         <f>Statement!P178</f>
         <v>9.8841101665902813E-3</v>
       </c>
-      <c r="G68" s="198">
+      <c r="G68" s="197">
         <f>Statement!Q178</f>
         <v>1.1785239203608671E-2</v>
       </c>
-      <c r="I68" s="198">
+      <c r="I68" s="197">
         <f ca="1">Statement!AC178</f>
-        <v>1.473513022512626E-2</v>
+        <v>1.4495724859875615E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -33210,27 +33335,27 @@
       <c r="B71" s="20" t="s">
         <v>277</v>
       </c>
-      <c r="C71" s="177">
+      <c r="C71" s="176">
         <f>Statement!M175</f>
         <v>0.22002635046113306</v>
       </c>
-      <c r="D71" s="177">
+      <c r="D71" s="176">
         <f>Statement!N175</f>
         <v>0.48023400106364122</v>
       </c>
-      <c r="E71" s="177">
+      <c r="E71" s="176">
         <f>Statement!O175</f>
         <v>0.1263438946244215</v>
       </c>
-      <c r="F71" s="177">
+      <c r="F71" s="176">
         <f>Statement!P175</f>
         <v>7.3912839956934887E-2</v>
       </c>
-      <c r="G71" s="177">
+      <c r="G71" s="176">
         <f>Statement!Q175</f>
         <v>6.217021359450145E-2</v>
       </c>
-      <c r="I71" s="177">
+      <c r="I71" s="176">
         <f>Statement!AC175</f>
         <v>5.4437361220542942E-2</v>
       </c>
@@ -33239,27 +33364,27 @@
       <c r="B72" s="20" t="s">
         <v>278</v>
       </c>
-      <c r="C72" s="177">
+      <c r="C72" s="176">
         <f>Statement!M176</f>
         <v>7.4459389165490081E-2</v>
       </c>
-      <c r="D72" s="177">
+      <c r="D72" s="176">
         <f>Statement!N176</f>
         <v>0.10043004374582931</v>
       </c>
-      <c r="E72" s="177">
+      <c r="E72" s="176">
         <f>Statement!O176</f>
         <v>5.8254817635665278E-2</v>
       </c>
-      <c r="F72" s="177">
+      <c r="F72" s="176">
         <f>Statement!P176</f>
         <v>3.629968505023104E-2</v>
       </c>
-      <c r="G72" s="177">
+      <c r="G72" s="176">
         <f>Statement!Q176</f>
         <v>2.9573303448211987E-2</v>
       </c>
-      <c r="I72" s="177">
+      <c r="I72" s="176">
         <f>Statement!AC176</f>
         <v>2.6983206504372935E-2</v>
       </c>
@@ -33279,27 +33404,27 @@
       <c r="B75" s="20" t="s">
         <v>301</v>
       </c>
-      <c r="C75" s="177">
+      <c r="C75" s="176">
         <f>Statement!M179</f>
         <v>3.6263654603552055E-2</v>
       </c>
-      <c r="D75" s="177">
+      <c r="D75" s="176">
         <f>Statement!N179</f>
         <v>6.7954326388373995E-2</v>
       </c>
-      <c r="E75" s="177">
+      <c r="E75" s="176">
         <f>Statement!O179</f>
         <v>1.7547027346442992E-2</v>
       </c>
-      <c r="F75" s="177">
+      <c r="F75" s="176">
         <f>Statement!P179</f>
         <v>2.4797504923484832E-2</v>
       </c>
-      <c r="G75" s="177">
+      <c r="G75" s="176">
         <f>Statement!Q179</f>
         <v>2.7980253591308617E-2</v>
       </c>
-      <c r="I75" s="177">
+      <c r="I75" s="176">
         <f>Statement!AC179</f>
         <v>2.5925969758295166E-2</v>
       </c>
@@ -33308,27 +33433,27 @@
       <c r="B76" s="20" t="s">
         <v>298</v>
       </c>
-      <c r="C76" s="177">
+      <c r="C76" s="176">
         <f>Statement!M180</f>
         <v>0.10715854194115064</v>
       </c>
-      <c r="D76" s="177">
+      <c r="D76" s="176">
         <f>Statement!N180</f>
         <v>0.32494238610175502</v>
       </c>
-      <c r="E76" s="177">
+      <c r="E76" s="176">
         <f>Statement!O180</f>
         <v>3.8056247775008899E-2</v>
       </c>
-      <c r="F76" s="177">
+      <c r="F76" s="176">
         <f>Statement!P180</f>
         <v>5.0492284167329808E-2</v>
       </c>
-      <c r="G76" s="177">
+      <c r="G76" s="176">
         <f>Statement!Q180</f>
         <v>5.8821238731283712E-2</v>
       </c>
-      <c r="I76" s="177">
+      <c r="I76" s="176">
         <f>Statement!AC180</f>
         <v>5.2304435371550904E-2</v>
       </c>
@@ -33337,27 +33462,27 @@
       <c r="B77" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="C77" s="177">
+      <c r="C77" s="176">
         <f>Statement!M181</f>
         <v>0.83134582623509368</v>
       </c>
-      <c r="D77" s="177">
+      <c r="D77" s="176">
         <f>Statement!N181</f>
         <v>1.1871761658031088</v>
       </c>
-      <c r="E77" s="177">
+      <c r="E77" s="176">
         <f>Statement!O181</f>
         <v>0.70888594164456231</v>
       </c>
-      <c r="F77" s="177">
+      <c r="F77" s="176">
         <f>Statement!P181</f>
         <v>1.7360515021459229</v>
       </c>
-      <c r="G77" s="177">
+      <c r="G77" s="176">
         <f>Statement!Q181</f>
         <v>2.1252198381990857</v>
       </c>
-      <c r="I77" s="177">
+      <c r="I77" s="176">
         <f>Statement!AC181</f>
         <v>2.0359355638166048</v>
       </c>
@@ -33377,157 +33502,157 @@
       <c r="B80" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C80" s="177">
+      <c r="C80" s="176">
         <f>Statement!M88</f>
         <v>1</v>
       </c>
-      <c r="D80" s="177">
+      <c r="D80" s="176">
         <f>Statement!N88</f>
         <v>2.2293230289068887E-3</v>
       </c>
-      <c r="E80" s="177">
+      <c r="E80" s="176">
         <f>Statement!O88</f>
         <v>1.2585452658115222</v>
       </c>
-      <c r="F80" s="177">
+      <c r="F80" s="176">
         <f>Statement!P88</f>
         <v>1.1420340763599357</v>
       </c>
-      <c r="G80" s="177">
+      <c r="G80" s="176">
         <f>Statement!Q88</f>
         <v>0.65473535790094795</v>
       </c>
-      <c r="I80" s="199"/>
+      <c r="I80" s="198"/>
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B81" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C81" s="177">
+      <c r="C81" s="176">
         <f>Statement!M89</f>
         <v>1</v>
       </c>
-      <c r="D81" s="177">
+      <c r="D81" s="176">
         <f>Statement!N89</f>
         <v>0.23085072571246953</v>
       </c>
-      <c r="E81" s="177">
+      <c r="E81" s="176">
         <f>Statement!O89</f>
         <v>0.43062489240833191</v>
       </c>
-      <c r="F81" s="177">
+      <c r="F81" s="176">
         <f>Statement!P89</f>
         <v>0.9637205944287347</v>
       </c>
-      <c r="G81" s="177">
+      <c r="G81" s="176">
         <f>Statement!Q89</f>
         <v>0.91412114341738415</v>
       </c>
-      <c r="I81" s="199"/>
+      <c r="I81" s="198"/>
     </row>
     <row r="82" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B82" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="C82" s="177">
+      <c r="C82" s="176">
         <f>Statement!M90</f>
         <v>1</v>
       </c>
-      <c r="D82" s="177">
+      <c r="D82" s="176">
         <f>Statement!N90</f>
         <v>-0.12125894134477826</v>
       </c>
-      <c r="E82" s="177">
+      <c r="E82" s="176">
         <f>Statement!O90</f>
         <v>1.8849309716071894</v>
       </c>
-      <c r="F82" s="177">
+      <c r="F82" s="176">
         <f>Statement!P90</f>
         <v>1.208934335568046</v>
       </c>
-      <c r="G82" s="177">
+      <c r="G82" s="176">
         <f>Statement!Q90</f>
         <v>0.56822130025138462</v>
       </c>
-      <c r="I82" s="199"/>
+      <c r="I82" s="198"/>
     </row>
     <row r="83" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B83" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C83" s="177">
+      <c r="C83" s="176">
         <f>Statement!M93</f>
         <v>1</v>
       </c>
-      <c r="D83" s="177">
+      <c r="D83" s="176">
         <f>Statement!N93</f>
         <v>0.49744417541027708</v>
       </c>
-      <c r="E83" s="177">
+      <c r="E83" s="176">
         <f>Statement!O93</f>
         <v>1.7696730147323033E-2</v>
       </c>
-      <c r="F83" s="177">
+      <c r="F83" s="176">
         <f>Statement!P93</f>
         <v>0.44805366757878012</v>
       </c>
-      <c r="G83" s="177">
+      <c r="G83" s="176">
         <f>Statement!Q93</f>
         <v>0.40664431575739102</v>
       </c>
-      <c r="I83" s="199"/>
+      <c r="I83" s="198"/>
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B84" s="20" t="s">
         <v>305</v>
       </c>
-      <c r="C84" s="177">
+      <c r="C84" s="176">
         <f>Statement!M94</f>
         <v>1</v>
       </c>
-      <c r="D84" s="177">
+      <c r="D84" s="176">
         <f>Statement!N94</f>
         <v>-0.57932476844935765</v>
       </c>
-      <c r="E84" s="177">
+      <c r="E84" s="176">
         <f>Statement!O94</f>
         <v>6.8058712121212119</v>
       </c>
-      <c r="F84" s="177">
+      <c r="F84" s="176">
         <f>Statement!P94</f>
         <v>1.470368797767803</v>
       </c>
-      <c r="G84" s="177">
+      <c r="G84" s="176">
         <f>Statement!Q94</f>
         <v>0.60076363055995485</v>
       </c>
-      <c r="I84" s="199"/>
+      <c r="I84" s="198"/>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B85" s="20" t="s">
         <v>306</v>
       </c>
-      <c r="C85" s="177">
+      <c r="C85" s="176">
         <f>Statement!M96</f>
         <v>1</v>
       </c>
-      <c r="D85" s="177">
+      <c r="D85" s="176">
         <f>Statement!N96</f>
         <v>-0.55209187858900743</v>
       </c>
-      <c r="E85" s="177">
+      <c r="E85" s="176">
         <f>Statement!O96</f>
         <v>5.813186813186813</v>
       </c>
-      <c r="F85" s="177">
+      <c r="F85" s="176">
         <f>Statement!P96</f>
         <v>1.4489247311827957</v>
       </c>
-      <c r="G85" s="177">
+      <c r="G85" s="176">
         <f>Statement!Q96</f>
         <v>0.6474615806805708</v>
       </c>
-      <c r="I85" s="199"/>
+      <c r="I85" s="198"/>
     </row>
     <row r="88" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B88" s="14" t="s">
@@ -33541,108 +33666,108 @@
       <c r="I88" s="14"/>
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B89" s="226" t="s">
+      <c r="B89" s="224" t="s">
         <v>370</v>
       </c>
-      <c r="C89" s="177">
-        <f>Statement!M193</f>
-        <v>0</v>
-      </c>
-      <c r="D89" s="177">
-        <f>Statement!N193</f>
-        <v>0</v>
-      </c>
-      <c r="E89" s="177">
-        <f>Statement!O193</f>
-        <v>0</v>
-      </c>
-      <c r="F89" s="177">
-        <f>Statement!P193</f>
+      <c r="C89" s="176">
+        <f>Statement!M196</f>
+        <v>0</v>
+      </c>
+      <c r="D89" s="176">
+        <f>Statement!N196</f>
+        <v>0</v>
+      </c>
+      <c r="E89" s="176">
+        <f>Statement!O196</f>
+        <v>0</v>
+      </c>
+      <c r="F89" s="176">
+        <f>Statement!P196</f>
         <v>1</v>
       </c>
-      <c r="G89" s="177">
-        <f>Statement!Q193</f>
+      <c r="G89" s="176">
+        <f>Statement!Q196</f>
         <v>0.96364041936203437</v>
       </c>
-      <c r="I89" s="199"/>
+      <c r="I89" s="198"/>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B90" s="226" t="s">
+      <c r="B90" s="224" t="s">
         <v>371</v>
       </c>
-      <c r="C90" s="177">
-        <f>Statement!M194</f>
-        <v>0</v>
-      </c>
-      <c r="D90" s="177">
-        <f>Statement!N194</f>
-        <v>0</v>
-      </c>
-      <c r="E90" s="177">
-        <f>Statement!O194</f>
-        <v>0</v>
-      </c>
-      <c r="F90" s="177">
-        <f>Statement!P194</f>
+      <c r="C90" s="176">
+        <f>Statement!M197</f>
+        <v>0</v>
+      </c>
+      <c r="D90" s="176">
+        <f>Statement!N197</f>
+        <v>0</v>
+      </c>
+      <c r="E90" s="176">
+        <f>Statement!O197</f>
+        <v>0</v>
+      </c>
+      <c r="F90" s="176">
+        <f>Statement!P197</f>
         <v>1</v>
       </c>
-      <c r="G90" s="177">
-        <f>Statement!Q194</f>
+      <c r="G90" s="176">
+        <f>Statement!Q197</f>
         <v>0.43510343704186349</v>
       </c>
-      <c r="I90" s="199"/>
+      <c r="I90" s="198"/>
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B91" s="20" t="s">
         <v>372</v>
       </c>
-      <c r="C91" s="177">
-        <f>Statement!M195</f>
-        <v>0</v>
-      </c>
-      <c r="D91" s="177">
-        <f>Statement!N195</f>
-        <v>0</v>
-      </c>
-      <c r="E91" s="177">
-        <f>Statement!O195</f>
-        <v>0</v>
-      </c>
-      <c r="F91" s="177">
-        <f>Statement!P195</f>
+      <c r="C91" s="176">
+        <f>Statement!M198</f>
+        <v>0</v>
+      </c>
+      <c r="D91" s="176">
+        <f>Statement!N198</f>
+        <v>0</v>
+      </c>
+      <c r="E91" s="176">
+        <f>Statement!O198</f>
+        <v>0</v>
+      </c>
+      <c r="F91" s="176">
+        <f>Statement!P198</f>
         <v>1</v>
       </c>
-      <c r="G91" s="177">
-        <f>Statement!Q195</f>
+      <c r="G91" s="176">
+        <f>Statement!Q198</f>
         <v>0.68194919521469621</v>
       </c>
-      <c r="I91" s="199"/>
+      <c r="I91" s="198"/>
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B92" s="20" t="s">
         <v>373</v>
       </c>
-      <c r="C92" s="177">
-        <f>Statement!M196</f>
-        <v>0</v>
-      </c>
-      <c r="D92" s="177">
-        <f>Statement!N196</f>
-        <v>0</v>
-      </c>
-      <c r="E92" s="177">
-        <f>Statement!O196</f>
-        <v>0</v>
-      </c>
-      <c r="F92" s="177">
-        <f>Statement!P196</f>
+      <c r="C92" s="176">
+        <f>Statement!M199</f>
+        <v>0</v>
+      </c>
+      <c r="D92" s="176">
+        <f>Statement!N199</f>
+        <v>0</v>
+      </c>
+      <c r="E92" s="176">
+        <f>Statement!O199</f>
+        <v>0</v>
+      </c>
+      <c r="F92" s="176">
+        <f>Statement!P199</f>
         <v>1</v>
       </c>
-      <c r="G92" s="177">
-        <f>Statement!Q196</f>
+      <c r="G92" s="176">
+        <f>Statement!Q199</f>
         <v>0.4500032656260205</v>
       </c>
-      <c r="I92" s="199"/>
+      <c r="I92" s="198"/>
     </row>
     <row r="94" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B94" s="14" t="s">
@@ -33659,27 +33784,27 @@
       <c r="B95" s="20" t="s">
         <v>281</v>
       </c>
-      <c r="C95" s="177">
-        <f>Statement!M199</f>
-        <v>0</v>
-      </c>
-      <c r="D95" s="177">
-        <f>Statement!N200</f>
+      <c r="C95" s="176">
+        <f>Statement!M202</f>
+        <v>0</v>
+      </c>
+      <c r="D95" s="176">
+        <f>Statement!N203</f>
         <v>-2.5062656641604009E-3</v>
       </c>
-      <c r="E95" s="177">
-        <f>Statement!O200</f>
+      <c r="E95" s="176">
+        <f>Statement!O203</f>
         <v>-7.537688442211055E-3</v>
       </c>
-      <c r="F95" s="177">
-        <f>Statement!P200</f>
+      <c r="F95" s="176">
+        <f>Statement!P203</f>
         <v>1.1113924050632911</v>
       </c>
-      <c r="G95" s="177">
-        <f>Statement!Q200</f>
+      <c r="G95" s="176">
+        <f>Statement!Q203</f>
         <v>0.16786570743405277</v>
       </c>
-      <c r="I95" s="199"/>
+      <c r="I95" s="198"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -33719,15 +33844,15 @@
         <f>Statement!Z2</f>
         <v>25.01.2026</v>
       </c>
-      <c r="D4" s="205" t="str">
+      <c r="D4" s="204" t="str">
         <f>Statement!AA2</f>
         <v>26.04.2026</v>
       </c>
-      <c r="F4" s="206" t="str">
+      <c r="F4" s="205" t="str">
         <f>Statement!W2</f>
         <v>27.04.2025</v>
       </c>
-      <c r="G4" s="205" t="str">
+      <c r="G4" s="204" t="str">
         <f>Statement!AA2</f>
         <v>26.04.2026</v>
       </c>
@@ -33740,42 +33865,42 @@
         <f>Statement!Z3</f>
         <v>Q4 2026</v>
       </c>
-      <c r="D5" s="205" t="str">
+      <c r="D5" s="204" t="str">
         <f>Statement!AA3</f>
         <v>Q1 2027</v>
       </c>
-      <c r="F5" s="206" t="str">
+      <c r="F5" s="205" t="str">
         <f>Statement!W3</f>
         <v>Q1 2026</v>
       </c>
-      <c r="G5" s="205" t="str">
+      <c r="G5" s="204" t="str">
         <f>Statement!AA3</f>
         <v>Q1 2027</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B6" s="207" t="s">
+      <c r="B6" s="206" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="201">
+      <c r="C6" s="200">
         <f>Statement!Z5</f>
         <v>68127</v>
       </c>
-      <c r="D6" s="200">
+      <c r="D6" s="199">
         <f>Statement!AA5</f>
         <v>81615</v>
       </c>
-      <c r="F6" s="201">
+      <c r="F6" s="200">
         <f>Statement!W5</f>
         <v>44062</v>
       </c>
-      <c r="G6" s="200">
+      <c r="G6" s="199">
         <f>Statement!AA5</f>
         <v>81615</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="208" t="s">
+      <c r="B7" s="207" t="s">
         <v>312</v>
       </c>
       <c r="C7" s="235">
@@ -33793,28 +33918,28 @@
       <c r="G7" s="236"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B8" s="209" t="s">
+      <c r="B8" s="208" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="202">
+      <c r="C8" s="201">
         <f>Statement!Z6</f>
         <v>17034</v>
       </c>
-      <c r="D8" s="200">
+      <c r="D8" s="199">
         <f>Statement!AA6</f>
         <v>20458</v>
       </c>
-      <c r="F8" s="202">
+      <c r="F8" s="201">
         <f>Statement!W6</f>
         <v>17394</v>
       </c>
-      <c r="G8" s="200">
+      <c r="G8" s="199">
         <f>Statement!AA6</f>
         <v>20458</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B9" s="208" t="s">
+      <c r="B9" s="207" t="s">
         <v>312</v>
       </c>
       <c r="C9" s="235">
@@ -33832,28 +33957,28 @@
       <c r="G9" s="236"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B10" s="209" t="s">
+      <c r="B10" s="208" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="202">
+      <c r="C10" s="201">
         <f>Statement!Z7</f>
         <v>51093</v>
       </c>
-      <c r="D10" s="200">
+      <c r="D10" s="199">
         <f>Statement!AA7</f>
         <v>61157</v>
       </c>
-      <c r="F10" s="202">
+      <c r="F10" s="201">
         <f>Statement!W7</f>
         <v>26668</v>
       </c>
-      <c r="G10" s="200">
+      <c r="G10" s="199">
         <f>Statement!AA7</f>
         <v>61157</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B11" s="208" t="s">
+      <c r="B11" s="207" t="s">
         <v>312</v>
       </c>
       <c r="C11" s="235">
@@ -33871,28 +33996,28 @@
       <c r="G11" s="236"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B12" s="209" t="s">
+      <c r="B12" s="208" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="202">
+      <c r="C12" s="201">
         <f>Statement!Z10</f>
         <v>6794</v>
       </c>
-      <c r="D12" s="200">
+      <c r="D12" s="199">
         <f>Statement!AA10</f>
         <v>7621</v>
       </c>
-      <c r="F12" s="202">
+      <c r="F12" s="201">
         <f>Statement!W10</f>
         <v>5030</v>
       </c>
-      <c r="G12" s="200">
+      <c r="G12" s="199">
         <f>Statement!AA10</f>
         <v>7621</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B13" s="208" t="s">
+      <c r="B13" s="207" t="s">
         <v>312</v>
       </c>
       <c r="C13" s="235">
@@ -33910,28 +34035,28 @@
       <c r="G13" s="236"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B14" s="209" t="s">
+      <c r="B14" s="208" t="s">
         <v>313</v>
       </c>
-      <c r="C14" s="202">
+      <c r="C14" s="201">
         <f>Statement!Z11</f>
         <v>44299</v>
       </c>
-      <c r="D14" s="200">
+      <c r="D14" s="199">
         <f>Statement!AA11</f>
         <v>53536</v>
       </c>
-      <c r="F14" s="202">
+      <c r="F14" s="201">
         <f>Statement!W11</f>
         <v>21638</v>
       </c>
-      <c r="G14" s="200">
+      <c r="G14" s="199">
         <f>Statement!AA11</f>
         <v>53536</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="208" t="s">
+      <c r="B15" s="207" t="s">
         <v>312</v>
       </c>
       <c r="C15" s="235">
@@ -33949,28 +34074,28 @@
       <c r="G15" s="236"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B16" s="209" t="s">
+      <c r="B16" s="208" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="202">
+      <c r="C16" s="201">
         <f>Statement!Z17</f>
         <v>42960</v>
       </c>
-      <c r="D16" s="200">
+      <c r="D16" s="199">
         <f>Statement!AA17</f>
         <v>58321</v>
       </c>
-      <c r="F16" s="202">
+      <c r="F16" s="201">
         <f>Statement!W17</f>
         <v>18775</v>
       </c>
-      <c r="G16" s="200">
+      <c r="G16" s="199">
         <f>Statement!AA17</f>
         <v>58321</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B17" s="208" t="s">
+      <c r="B17" s="207" t="s">
         <v>312</v>
       </c>
       <c r="C17" s="235">
@@ -33988,28 +34113,28 @@
       <c r="G17" s="236"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B18" s="209" t="s">
+      <c r="B18" s="208" t="s">
         <v>314</v>
       </c>
-      <c r="C18" s="202">
+      <c r="C18" s="201">
         <f>Statement!Z21</f>
         <v>24432</v>
       </c>
-      <c r="D18" s="200">
+      <c r="D18" s="199">
         <f>Statement!AA21</f>
         <v>24391</v>
       </c>
-      <c r="F18" s="202">
+      <c r="F18" s="201">
         <f>Statement!W21</f>
         <v>24611</v>
       </c>
-      <c r="G18" s="200">
+      <c r="G18" s="199">
         <f>Statement!AA21</f>
         <v>24391</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B19" s="208" t="s">
+      <c r="B19" s="207" t="s">
         <v>312</v>
       </c>
       <c r="C19" s="235">
@@ -34030,28 +34155,28 @@
       <c r="G19" s="236"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B20" s="209" t="s">
+      <c r="B20" s="208" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="203">
+      <c r="C20" s="202">
         <f>Statement!Z25</f>
         <v>1.76</v>
       </c>
-      <c r="D20" s="204">
+      <c r="D20" s="203">
         <f>Statement!AA25</f>
         <v>2.39</v>
       </c>
-      <c r="F20" s="203">
+      <c r="F20" s="202">
         <f>Statement!W25</f>
         <v>0.76</v>
       </c>
-      <c r="G20" s="204">
+      <c r="G20" s="203">
         <f>Statement!AA25</f>
         <v>2.39</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B21" s="208" t="s">
+      <c r="B21" s="207" t="s">
         <v>312</v>
       </c>
       <c r="C21" s="235">
@@ -34079,42 +34204,42 @@
         <f>C5</f>
         <v>Q4 2026</v>
       </c>
-      <c r="D23" s="205" t="str">
+      <c r="D23" s="204" t="str">
         <f>D5</f>
         <v>Q1 2027</v>
       </c>
-      <c r="F23" s="206" t="str">
+      <c r="F23" s="205" t="str">
         <f>F5</f>
         <v>Q1 2026</v>
       </c>
-      <c r="G23" s="205" t="str">
+      <c r="G23" s="204" t="str">
         <f>G5</f>
         <v>Q1 2027</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B24" s="226" t="s">
+      <c r="B24" s="224" t="s">
         <v>370</v>
       </c>
-      <c r="C24" s="202">
-        <f>Statement!Z186</f>
+      <c r="C24" s="201">
+        <f>Statement!Z189</f>
         <v>33814</v>
       </c>
-      <c r="D24" s="200">
-        <f>Statement!AA186</f>
+      <c r="D24" s="199">
+        <f>Statement!AA189</f>
         <v>37869</v>
       </c>
-      <c r="F24" s="202">
-        <f>Statement!W186</f>
+      <c r="F24" s="201">
+        <f>Statement!W189</f>
         <v>17599</v>
       </c>
-      <c r="G24" s="200">
-        <f>Statement!AA186</f>
+      <c r="G24" s="199">
+        <f>Statement!AA189</f>
         <v>37869</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B25" s="208" t="s">
+      <c r="B25" s="207" t="s">
         <v>312</v>
       </c>
       <c r="C25" s="235">
@@ -34135,28 +34260,28 @@
       <c r="G25" s="236"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B26" s="226" t="s">
+      <c r="B26" s="224" t="s">
         <v>371</v>
       </c>
-      <c r="C26" s="202">
-        <f>Statement!Z187</f>
+      <c r="C26" s="201">
+        <f>Statement!Z190</f>
         <v>28500</v>
       </c>
-      <c r="D26" s="200">
-        <f>Statement!AA187</f>
+      <c r="D26" s="199">
+        <f>Statement!AA190</f>
         <v>37377</v>
       </c>
-      <c r="F26" s="202">
-        <f>Statement!W187</f>
+      <c r="F26" s="201">
+        <f>Statement!W190</f>
         <v>21513</v>
       </c>
-      <c r="G26" s="200">
-        <f>Statement!AA187</f>
+      <c r="G26" s="199">
+        <f>Statement!AA190</f>
         <v>37377</v>
       </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B27" s="208" t="s">
+      <c r="B27" s="207" t="s">
         <v>312</v>
       </c>
       <c r="C27" s="235">
@@ -34180,25 +34305,25 @@
       <c r="B28" s="20" t="s">
         <v>372</v>
       </c>
-      <c r="C28" s="202">
-        <f>Statement!Z188</f>
+      <c r="C28" s="201">
+        <f>Statement!Z191</f>
         <v>62314</v>
       </c>
-      <c r="D28" s="200">
-        <f>Statement!AA188</f>
+      <c r="D28" s="199">
+        <f>Statement!AA191</f>
         <v>75246</v>
       </c>
-      <c r="F28" s="202">
-        <f>Statement!W188</f>
+      <c r="F28" s="201">
+        <f>Statement!W191</f>
         <v>39112</v>
       </c>
-      <c r="G28" s="200">
-        <f>Statement!AA188</f>
+      <c r="G28" s="199">
+        <f>Statement!AA191</f>
         <v>75246</v>
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B29" s="208" t="s">
+      <c r="B29" s="207" t="s">
         <v>312</v>
       </c>
       <c r="C29" s="235">
@@ -34222,25 +34347,25 @@
       <c r="B30" s="20" t="s">
         <v>373</v>
       </c>
-      <c r="C30" s="202">
-        <f>Statement!Z189</f>
+      <c r="C30" s="201">
+        <f>Statement!Z192</f>
         <v>5813</v>
       </c>
-      <c r="D30" s="202">
-        <f>Statement!AA189</f>
+      <c r="D30" s="201">
+        <f>Statement!AA192</f>
         <v>6369</v>
       </c>
-      <c r="F30" s="202">
-        <f>Statement!W189</f>
+      <c r="F30" s="201">
+        <f>Statement!W192</f>
         <v>4950</v>
       </c>
-      <c r="G30" s="202">
-        <f>Statement!AA189</f>
+      <c r="G30" s="201">
+        <f>Statement!AA192</f>
         <v>6369</v>
       </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B31" s="208" t="s">
+      <c r="B31" s="207" t="s">
         <v>312</v>
       </c>
       <c r="C31" s="235">
@@ -34757,43 +34882,43 @@
         <v>374</v>
       </c>
       <c r="C65" s="64">
-        <f>Statement!H186</f>
+        <f>Statement!H189</f>
         <v>0</v>
       </c>
       <c r="D65" s="64">
-        <f>Statement!I186</f>
+        <f>Statement!I189</f>
         <v>0</v>
       </c>
       <c r="E65" s="64">
-        <f>Statement!J186</f>
+        <f>Statement!J189</f>
         <v>0</v>
       </c>
       <c r="F65" s="64">
-        <f>Statement!K186</f>
+        <f>Statement!K189</f>
         <v>0</v>
       </c>
       <c r="G65" s="64">
-        <f>Statement!L186</f>
+        <f>Statement!L189</f>
         <v>0</v>
       </c>
       <c r="H65" s="64">
-        <f>Statement!M186</f>
+        <f>Statement!M189</f>
         <v>0</v>
       </c>
       <c r="I65" s="64">
-        <f>Statement!N186</f>
+        <f>Statement!N189</f>
         <v>0</v>
       </c>
       <c r="J65" s="64">
-        <f>Statement!O186</f>
+        <f>Statement!O189</f>
         <v>0</v>
       </c>
       <c r="K65" s="64">
-        <f>Statement!P186</f>
+        <f>Statement!P189</f>
         <v>53796</v>
       </c>
       <c r="L65" s="64">
-        <f>Statement!Q186</f>
+        <f>Statement!Q189</f>
         <v>105636</v>
       </c>
     </row>
@@ -34802,43 +34927,43 @@
         <v>375</v>
       </c>
       <c r="C66" s="64">
-        <f>Statement!H187</f>
+        <f>Statement!H190</f>
         <v>0</v>
       </c>
       <c r="D66" s="64">
-        <f>Statement!I187</f>
+        <f>Statement!I190</f>
         <v>0</v>
       </c>
       <c r="E66" s="64">
-        <f>Statement!J187</f>
+        <f>Statement!J190</f>
         <v>0</v>
       </c>
       <c r="F66" s="64">
-        <f>Statement!K187</f>
+        <f>Statement!K190</f>
         <v>0</v>
       </c>
       <c r="G66" s="64">
-        <f>Statement!L187</f>
+        <f>Statement!L190</f>
         <v>0</v>
       </c>
       <c r="H66" s="64">
-        <f>Statement!M187</f>
+        <f>Statement!M190</f>
         <v>0</v>
       </c>
       <c r="I66" s="64">
-        <f>Statement!N187</f>
+        <f>Statement!N190</f>
         <v>0</v>
       </c>
       <c r="J66" s="64">
-        <f>Statement!O187</f>
+        <f>Statement!O190</f>
         <v>0</v>
       </c>
       <c r="K66" s="64">
-        <f>Statement!P187</f>
+        <f>Statement!P190</f>
         <v>61390</v>
       </c>
       <c r="L66" s="64">
-        <f>Statement!Q187</f>
+        <f>Statement!Q190</f>
         <v>88101</v>
       </c>
     </row>
@@ -34847,43 +34972,43 @@
         <v>376</v>
       </c>
       <c r="C67" s="64">
-        <f>Statement!H189</f>
+        <f>Statement!H192</f>
         <v>0</v>
       </c>
       <c r="D67" s="64">
-        <f>Statement!I189</f>
+        <f>Statement!I192</f>
         <v>0</v>
       </c>
       <c r="E67" s="64">
-        <f>Statement!J189</f>
+        <f>Statement!J192</f>
         <v>0</v>
       </c>
       <c r="F67" s="64">
-        <f>Statement!K189</f>
+        <f>Statement!K192</f>
         <v>0</v>
       </c>
       <c r="G67" s="64">
-        <f>Statement!L189</f>
+        <f>Statement!L192</f>
         <v>0</v>
       </c>
       <c r="H67" s="64">
-        <f>Statement!M189</f>
+        <f>Statement!M192</f>
         <v>0</v>
       </c>
       <c r="I67" s="64">
-        <f>Statement!N189</f>
+        <f>Statement!N192</f>
         <v>0</v>
       </c>
       <c r="J67" s="64">
-        <f>Statement!O189</f>
+        <f>Statement!O192</f>
         <v>0</v>
       </c>
       <c r="K67" s="64">
-        <f>Statement!P189</f>
+        <f>Statement!P192</f>
         <v>15311</v>
       </c>
       <c r="L67" s="64">
-        <f>Statement!Q189</f>
+        <f>Statement!Q192</f>
         <v>22201</v>
       </c>
     </row>
@@ -34891,43 +35016,43 @@
       <c r="B68" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="C68" s="221">
+      <c r="C68" s="219">
         <f>Statement!H121</f>
         <v>0</v>
       </c>
-      <c r="D68" s="221">
+      <c r="D68" s="219">
         <f>Statement!I121</f>
         <v>0</v>
       </c>
-      <c r="E68" s="221">
+      <c r="E68" s="219">
         <f>Statement!J121</f>
         <v>0</v>
       </c>
-      <c r="F68" s="221">
+      <c r="F68" s="219">
         <f>Statement!K121</f>
         <v>0</v>
       </c>
-      <c r="G68" s="221">
+      <c r="G68" s="219">
         <f>Statement!L121</f>
         <v>0</v>
       </c>
-      <c r="H68" s="221">
+      <c r="H68" s="219">
         <f>Statement!M121</f>
         <v>0.22069839545567699</v>
       </c>
-      <c r="I68" s="221">
+      <c r="I68" s="219">
         <f>Statement!N121</f>
         <v>0.10606575688407557</v>
       </c>
-      <c r="J68" s="221">
+      <c r="J68" s="219">
         <f>Statement!O121</f>
         <v>0.45277507302823755</v>
       </c>
-      <c r="K68" s="221">
+      <c r="K68" s="219">
         <f>Statement!P121</f>
         <v>0.65304074336251472</v>
       </c>
-      <c r="L68" s="221">
+      <c r="L68" s="219">
         <f>Statement!Q121</f>
         <v>0.5805863551302447</v>
       </c>
@@ -34936,43 +35061,43 @@
       <c r="B69" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="C69" s="221">
+      <c r="C69" s="219">
         <f>Statement!H123</f>
         <v>0</v>
       </c>
-      <c r="D69" s="221">
+      <c r="D69" s="219">
         <f>Statement!I123</f>
         <v>0</v>
       </c>
-      <c r="E69" s="221">
+      <c r="E69" s="219">
         <f>Statement!J123</f>
         <v>0</v>
       </c>
-      <c r="F69" s="221">
+      <c r="F69" s="219">
         <f>Statement!K123</f>
         <v>0</v>
       </c>
-      <c r="G69" s="221">
+      <c r="G69" s="219">
         <f>Statement!L123</f>
         <v>0</v>
       </c>
-      <c r="H69" s="221">
+      <c r="H69" s="219">
         <f>Statement!M123</f>
         <v>0.36645122501127303</v>
       </c>
-      <c r="I69" s="221">
+      <c r="I69" s="219">
         <f>Statement!N123</f>
         <v>0.19763811592235647</v>
       </c>
-      <c r="J69" s="221">
+      <c r="J69" s="219">
         <f>Statement!O123</f>
         <v>0.69244729861789756</v>
       </c>
-      <c r="K69" s="221">
+      <c r="K69" s="219">
         <f>Statement!P123</f>
         <v>0.91872880608115781</v>
       </c>
-      <c r="L69" s="221">
+      <c r="L69" s="219">
         <f>Statement!Q123</f>
         <v>0.76333339690895341</v>
       </c>
@@ -34981,43 +35106,43 @@
       <c r="B70" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="C70" s="221">
+      <c r="C70" s="219">
         <f>Statement!H142</f>
         <v>0</v>
       </c>
-      <c r="D70" s="221">
+      <c r="D70" s="219">
         <f>Statement!I142</f>
         <v>0</v>
       </c>
-      <c r="E70" s="221">
+      <c r="E70" s="219">
         <f>Statement!J142</f>
         <v>0</v>
       </c>
-      <c r="F70" s="221">
+      <c r="F70" s="219">
         <f>Statement!K142</f>
         <v>0</v>
       </c>
-      <c r="G70" s="221">
+      <c r="G70" s="219">
         <f>Statement!L142</f>
         <v>0</v>
       </c>
-      <c r="H70" s="221">
+      <c r="H70" s="219">
         <f>Statement!M142</f>
         <v>0.60245252494303547</v>
       </c>
-      <c r="I70" s="221">
+      <c r="I70" s="219">
         <f>Statement!N142</f>
         <v>0.21378682052839357</v>
       </c>
-      <c r="J70" s="221">
+      <c r="J70" s="219">
         <f>Statement!O142</f>
         <v>1.0866013555554745</v>
       </c>
-      <c r="K70" s="221">
+      <c r="K70" s="219">
         <f>Statement!P142</f>
         <v>1.5847534085376831</v>
       </c>
-      <c r="L70" s="221">
+      <c r="L70" s="219">
         <f>Statement!Q142</f>
         <v>1.0723937210768841</v>
       </c>
@@ -35335,35 +35460,35 @@
         <v>374</v>
       </c>
       <c r="C63" s="64">
-        <f>Statement!T186</f>
+        <f>Statement!T189</f>
         <v>10622</v>
       </c>
       <c r="D63" s="64">
-        <f>Statement!U186</f>
+        <f>Statement!U189</f>
         <v>13390</v>
       </c>
       <c r="E63" s="64">
-        <f>Statement!V186</f>
+        <f>Statement!V189</f>
         <v>19094</v>
       </c>
       <c r="F63" s="64">
-        <f>Statement!W186</f>
+        <f>Statement!W189</f>
         <v>17599</v>
       </c>
       <c r="G63" s="64">
-        <f>Statement!X186</f>
+        <f>Statement!X189</f>
         <v>23883</v>
       </c>
       <c r="H63" s="64">
-        <f>Statement!Y186</f>
+        <f>Statement!Y189</f>
         <v>30340</v>
       </c>
       <c r="I63" s="64">
-        <f>Statement!Z186</f>
+        <f>Statement!Z189</f>
         <v>33814</v>
       </c>
       <c r="J63" s="64">
-        <f>Statement!AA186</f>
+        <f>Statement!AA189</f>
         <v>37869</v>
       </c>
     </row>
@@ -35372,35 +35497,35 @@
         <v>377</v>
       </c>
       <c r="C64" s="64">
-        <f>Statement!T187</f>
+        <f>Statement!T190</f>
         <v>15650</v>
       </c>
       <c r="D64" s="64">
-        <f>Statement!U187</f>
+        <f>Statement!U190</f>
         <v>17381</v>
       </c>
       <c r="E64" s="64">
-        <f>Statement!V187</f>
+        <f>Statement!V190</f>
         <v>16486</v>
       </c>
       <c r="F64" s="64">
-        <f>Statement!W187</f>
+        <f>Statement!W190</f>
         <v>21513</v>
       </c>
       <c r="G64" s="64">
-        <f>Statement!X187</f>
+        <f>Statement!X190</f>
         <v>17213</v>
       </c>
       <c r="H64" s="64">
-        <f>Statement!Y187</f>
+        <f>Statement!Y190</f>
         <v>20875</v>
       </c>
       <c r="I64" s="64">
-        <f>Statement!Z187</f>
+        <f>Statement!Z190</f>
         <v>28500</v>
       </c>
       <c r="J64" s="64">
-        <f>Statement!AA187</f>
+        <f>Statement!AA190</f>
         <v>37377</v>
       </c>
     </row>
@@ -35409,35 +35534,35 @@
         <v>378</v>
       </c>
       <c r="C65" s="64">
-        <f>Statement!T189</f>
+        <f>Statement!T192</f>
         <v>3768</v>
       </c>
       <c r="D65" s="64">
-        <f>Statement!U189</f>
+        <f>Statement!U192</f>
         <v>4311</v>
       </c>
       <c r="E65" s="64">
-        <f>Statement!V189</f>
+        <f>Statement!V192</f>
         <v>3751</v>
       </c>
       <c r="F65" s="64">
-        <f>Statement!W189</f>
+        <f>Statement!W192</f>
         <v>4950</v>
       </c>
       <c r="G65" s="64">
-        <f>Statement!X189</f>
+        <f>Statement!X192</f>
         <v>5647</v>
       </c>
       <c r="H65" s="64">
-        <f>Statement!Y189</f>
+        <f>Statement!Y192</f>
         <v>5791</v>
       </c>
       <c r="I65" s="64">
-        <f>Statement!Z189</f>
+        <f>Statement!Z192</f>
         <v>5813</v>
       </c>
       <c r="J65" s="64">
-        <f>Statement!AA189</f>
+        <f>Statement!AA192</f>
         <v>6369</v>
       </c>
     </row>

--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61AC8C39-E425-DE46-8C76-4807F3696AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAAE61A3-CD28-AB45-87F2-3A5E8D6EE94B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -150,7 +150,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="399">
   <si>
     <t>Ticker</t>
   </si>
@@ -1950,7 +1950,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="249">
+  <cellXfs count="250">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2260,6 +2260,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2793,6 +2794,301 @@
         </a:p>
       </c:txPr>
     </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>FCFE</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="34925" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Graphs Quarter'!$C$66:$J$66</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0_);\(#,##0\)</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>12358</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15564</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14230</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24713</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11847</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>20458</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>33273</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46659</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2537-A641-96D5-AEFA40A2B2D6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1163393471"/>
+        <c:axId val="1163381375"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1163393471"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1163381375"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1163381375"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0_);\(#,##0\)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1163393471"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -4595,6 +4891,368 @@
     <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Price 5y</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="34925" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Graphs Year'!$H$71:$L$71</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>89.141856392294216</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>267.20665499124345</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>624.43082311733804</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>821.67250437828375</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7480-C44D-8C58-DF1FA4187601}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Revenue 5y</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="34925" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Graphs Year'!$H$72:$L$72</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100.2229323028907</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>226.35802927844244</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>484.86661217210371</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>802.32592702682621</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-7480-C44D-8C58-DF1FA4187601}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>EPS 5y</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="34925" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Graphs Year'!$H$73:$L$73</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45.194805194805184</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>309.87012987012992</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>763.63636363636363</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1272.7272727272727</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-7480-C44D-8C58-DF1FA4187601}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1848442175"/>
+        <c:axId val="1845667903"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1848442175"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1845667903"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1845667903"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1848442175"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -5029,7 +5687,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -5480,7 +6138,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -6030,302 +6688,47 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="95000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:effectLst>
-                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-                    <a:prstClr val="black">
-                      <a:alpha val="40000"/>
-                    </a:prstClr>
-                  </a:outerShdw>
-                </a:effectLst>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>FCFE</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="95000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:effectLst>
-                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="40000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="34925" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:val>
-            <c:numRef>
-              <c:f>'Graphs Quarter'!$C$66:$J$66</c:f>
-              <c:numCache>
-                <c:formatCode>#,##0_);\(#,##0\)</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>12358</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>15564</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>14230</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>24713</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>11847</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>20458</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>33273</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>46659</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2537-A641-96D5-AEFA40A2B2D6}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="1163393471"/>
-        <c:axId val="1163381375"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="1163393471"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="b"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1163381375"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1163381375"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="95000"/>
-                  <a:alpha val="10000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="#,##0_);\(#,##0\)" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="85000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1163393471"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:gradFill flip="none" rotWithShape="1">
-      <a:gsLst>
-        <a:gs pos="0">
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:gs>
-        <a:gs pos="100000">
-          <a:schemeClr val="dk1">
-            <a:lumMod val="85000"/>
-            <a:lumOff val="15000"/>
-          </a:schemeClr>
-        </a:gs>
-      </a:gsLst>
-      <a:path path="circle">
-        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-      </a:path>
-      <a:tileRect/>
-    </a:gradFill>
-    <a:ln>
-      <a:noFill/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/colors10.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -7176,6 +7579,502 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="233">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
@@ -9166,7 +10065,7 @@
 </file>
 
 <file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="209">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="233">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -9188,11 +10087,11 @@
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="lt1">
             <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+            <a:alpha val="10000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -9269,7 +10168,7 @@
     </cs:fillRef>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:dataPoint>
   <cs:dataPoint3D>
@@ -9279,7 +10178,7 @@
     </cs:fillRef>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:dataPoint3D>
   <cs:dataPointLine>
@@ -9289,7 +10188,7 @@
     <cs:fillRef idx="3"/>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="34925" cap="rnd">
@@ -9309,7 +10208,7 @@
     </cs:fillRef>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -9328,7 +10227,7 @@
     <cs:fillRef idx="3"/>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -9365,7 +10264,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -9389,7 +10288,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -9408,7 +10307,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -9426,7 +10325,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:floor>
   <cs:gridlineMajor>
@@ -9434,7 +10333,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -9453,7 +10352,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln>
@@ -9471,7 +10370,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -9490,7 +10389,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -9519,7 +10418,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:plotArea>
   <cs:plotArea3D>
@@ -9527,7 +10426,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -9597,7 +10496,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="19050" cap="rnd">
@@ -9623,7 +10522,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -9655,7 +10554,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
@@ -10654,7 +11553,7 @@
 </file>
 
 <file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="233">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="209">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -10676,11 +11575,11 @@
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="lt1">
             <a:lumMod val="95000"/>
-            <a:alpha val="10000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -10757,7 +11656,7 @@
     </cs:fillRef>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:dataPoint>
   <cs:dataPoint3D>
@@ -10767,7 +11666,7 @@
     </cs:fillRef>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:dataPoint3D>
   <cs:dataPointLine>
@@ -10777,7 +11676,7 @@
     <cs:fillRef idx="3"/>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="34925" cap="rnd">
@@ -10797,7 +11696,7 @@
     </cs:fillRef>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -10816,7 +11715,7 @@
     <cs:fillRef idx="3"/>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -10853,7 +11752,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -10877,7 +11776,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -10896,7 +11795,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -10914,7 +11813,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:floor>
   <cs:gridlineMajor>
@@ -10922,7 +11821,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -10941,7 +11840,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln>
@@ -10959,7 +11858,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -10978,7 +11877,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -11007,7 +11906,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:plotArea>
   <cs:plotArea3D>
@@ -11015,7 +11914,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -11085,7 +11984,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="19050" cap="rnd">
@@ -11111,7 +12010,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -11143,7 +12042,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
@@ -11326,6 +12225,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>733244</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>58149</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>369018</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>5752</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2108E1F9-7682-6B89-9FB4-996EB449B524}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -11699,11 +12634,11 @@
     <v>Powered by Refinitiv</v>
     <v>236.54</v>
     <v>142.03</v>
-    <v>2.2052999999999998</v>
-    <v>-2.76</v>
-    <v>-1.3306999999999999E-2</v>
-    <v>0.42799999999999999</v>
-    <v>2.091E-3</v>
+    <v>2.2023999999999999</v>
+    <v>6.04</v>
+    <v>2.9513999999999999E-2</v>
+    <v>-0.38500000000000001</v>
+    <v>-1.8270000000000001E-3</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -11711,25 +12646,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2788 San Tomas Expressway, SANTA CLARA, CA, 95051 US</v>
-    <v>209.21</v>
+    <v>211.39</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46190.871673020316</v>
+    <v>46191.999989178126</v>
     <v>0</v>
-    <v>203.08</v>
-    <v>4952530000000</v>
+    <v>206.5</v>
+    <v>5098698000000</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
-    <v>208.53</v>
-    <v>31.34</v>
-    <v>207.41</v>
+    <v>207.33</v>
+    <v>31.3401</v>
     <v>204.65</v>
-    <v>205.078</v>
+    <v>210.69</v>
+    <v>210.30500000000001</v>
     <v>24200000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>126195668</v>
-    <v>171485621</v>
+    <v>241272013</v>
+    <v>170253095</v>
     <v>1998</v>
   </rv>
   <rv s="2">
@@ -11753,17 +12688,17 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.41</v>
-    <v>-9.1739999999999999E-3</v>
+    <v>-0.12</v>
+    <v>-2.6889999999999996E-3</v>
     <v>US</v>
-    <v>44.59</v>
+    <v>44.53</v>
     <v>Index</v>
     <v>3</v>
     <v>44.2</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>44.43</v>
-    <v>44.69</v>
-    <v>44.28</v>
+    <v>44.53</v>
+    <v>44.63</v>
+    <v>44.51</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -11985,9 +12920,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -12558,18 +13493,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="231" t="s">
+      <c r="B2" s="232" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="232"/>
-      <c r="E2" s="231" t="s">
+      <c r="C2" s="233"/>
+      <c r="E2" s="232" t="s">
         <v>284</v>
       </c>
-      <c r="F2" s="232"/>
-      <c r="H2" s="231" t="s">
+      <c r="F2" s="233"/>
+      <c r="H2" s="232" t="s">
         <v>325</v>
       </c>
-      <c r="I2" s="232"/>
+      <c r="I2" s="233"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="186" t="s">
@@ -12584,7 +13519,7 @@
       </c>
       <c r="F3" s="188">
         <f ca="1">Statement!AC155</f>
-        <v>4974018.25</v>
+        <v>5120820.45</v>
       </c>
       <c r="H3" s="186" t="str">
         <f>'AVG target price'!B5</f>
@@ -12608,7 +13543,7 @@
       </c>
       <c r="F4" s="189">
         <f ca="1">Statement!AC156</f>
-        <v>4901916.25</v>
+        <v>5048718.45</v>
       </c>
       <c r="H4" s="186" t="str">
         <f>'AVG target price'!B6</f>
@@ -12625,7 +13560,7 @@
       </c>
       <c r="C5" s="209" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>204.65</v>
+        <v>210.69</v>
       </c>
       <c r="E5" s="186" t="s">
         <v>240</v>
@@ -12649,14 +13584,14 @@
       </c>
       <c r="C6" s="209" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>205.078</v>
+        <v>210.30500000000001</v>
       </c>
       <c r="E6" s="186" t="s">
         <v>234</v>
       </c>
       <c r="F6" s="191">
         <f ca="1">Statement!AC152</f>
-        <v>31.339969372128643</v>
+        <v>32.264931087289433</v>
       </c>
       <c r="H6" s="186" t="str">
         <f>'AVG target price'!B8</f>
@@ -12673,14 +13608,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-2.76</v>
+        <v>6.04</v>
       </c>
       <c r="E7" s="187" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="192">
         <f ca="1">Statement!AC153</f>
-        <v>19.746802351957271</v>
+        <v>20.329605607299669</v>
       </c>
       <c r="H7" s="185" t="str">
         <f>'AVG target price'!B9</f>
@@ -12697,14 +13632,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.42799999999999999</v>
+        <v>-0.38500000000000001</v>
       </c>
       <c r="E8" s="186" t="s">
         <v>262</v>
       </c>
       <c r="F8" s="193">
         <f ca="1">Statement!AC163</f>
-        <v>2.2564653838976163E-2</v>
+        <v>2.1917776867181507E-2</v>
       </c>
       <c r="H8" s="185" t="str">
         <f>'AVG target price'!B11</f>
@@ -12712,7 +13647,7 @@
       </c>
       <c r="I8" s="214">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.45005107077740031</v>
+        <v>0.40848142595564563</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -12721,14 +13656,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-1.3306999999999999E-2</v>
+        <v>2.9513999999999999E-2</v>
       </c>
       <c r="E9" s="186" t="s">
         <v>285</v>
       </c>
       <c r="F9" s="193">
         <f ca="1">Statement!AC164</f>
-        <v>3.1908135841680917E-2</v>
+        <v>3.0993402629455595E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -12737,14 +13672,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>2.091E-3</v>
+        <v>-1.8270000000000001E-3</v>
       </c>
       <c r="E10" s="186" t="s">
         <v>290</v>
       </c>
       <c r="F10" s="193">
         <f ca="1">Statement!AC166</f>
-        <v>9.108129026265635E-3</v>
+        <v>8.8470198169123462E-3</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -12760,7 +13695,7 @@
       </c>
       <c r="F11" s="194">
         <f ca="1">Statement!AC165</f>
-        <v>1.9545565599804544E-4</v>
+        <v>1.8985238976695619E-4</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -12785,7 +13720,7 @@
       </c>
       <c r="C13" s="210" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.2052999999999998</v>
+        <v>2.2023999999999999</v>
       </c>
       <c r="E13" s="186" t="s">
         <v>96</v>
@@ -12801,7 +13736,7 @@
       </c>
       <c r="C14" s="211" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>171485621</v>
+        <v>170253095</v>
       </c>
       <c r="E14" s="187" t="s">
         <v>97</v>
@@ -12817,7 +13752,7 @@
       </c>
       <c r="F15" s="193">
         <f ca="1">Statement!AC178</f>
-        <v>1.4495724859875615E-2</v>
+        <v>1.4080165610961813E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -12830,10 +13765,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="233" t="s">
+      <c r="B17" s="234" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="233"/>
+      <c r="C17" s="234"/>
       <c r="E17" s="185" t="s">
         <v>293</v>
       </c>
@@ -12906,14 +13841,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="233" t="s">
+      <c r="B25" s="234" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="233"/>
-      <c r="E25" s="231" t="s">
+      <c r="C25" s="234"/>
+      <c r="E25" s="232" t="s">
         <v>340</v>
       </c>
-      <c r="F25" s="232"/>
+      <c r="F25" s="233"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="185" t="s">
@@ -12927,7 +13862,7 @@
       </c>
       <c r="F26" s="220" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>44.28</v>
+        <v>44.51</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -12942,7 +13877,7 @@
       </c>
       <c r="F27" s="221">
         <f ca="1">F26/1000</f>
-        <v>4.428E-2</v>
+        <v>4.4510000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -12962,15 +13897,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="234" t="s">
+      <c r="B33" s="235" t="s">
         <v>335</v>
       </c>
-      <c r="C33" s="234"/>
-      <c r="D33" s="234"/>
-      <c r="E33" s="234"/>
-      <c r="F33" s="234"/>
-      <c r="G33" s="234"/>
-      <c r="H33" s="234"/>
+      <c r="C33" s="235"/>
+      <c r="D33" s="235"/>
+      <c r="E33" s="235"/>
+      <c r="F33" s="235"/>
+      <c r="G33" s="235"/>
+      <c r="H33" s="235"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -12989,24 +13924,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="234"/>
-      <c r="C39" s="234"/>
-      <c r="D39" s="234"/>
-      <c r="E39" s="234"/>
-      <c r="F39" s="234"/>
-      <c r="G39" s="234"/>
-      <c r="H39" s="234"/>
+      <c r="B39" s="235"/>
+      <c r="C39" s="235"/>
+      <c r="D39" s="235"/>
+      <c r="E39" s="235"/>
+      <c r="F39" s="235"/>
+      <c r="G39" s="235"/>
+      <c r="H39" s="235"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="234" t="s">
+      <c r="B42" s="235" t="s">
         <v>338</v>
       </c>
-      <c r="C42" s="234"/>
-      <c r="D42" s="234"/>
-      <c r="E42" s="234"/>
-      <c r="F42" s="234"/>
-      <c r="G42" s="234"/>
-      <c r="H42" s="234"/>
+      <c r="C42" s="235"/>
+      <c r="D42" s="235"/>
+      <c r="E42" s="235"/>
+      <c r="F42" s="235"/>
+      <c r="G42" s="235"/>
+      <c r="H42" s="235"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -13021,24 +13956,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="234"/>
-      <c r="C49" s="234"/>
-      <c r="D49" s="234"/>
-      <c r="E49" s="234"/>
-      <c r="F49" s="234"/>
-      <c r="G49" s="234"/>
-      <c r="H49" s="234"/>
+      <c r="B49" s="235"/>
+      <c r="C49" s="235"/>
+      <c r="D49" s="235"/>
+      <c r="E49" s="235"/>
+      <c r="F49" s="235"/>
+      <c r="G49" s="235"/>
+      <c r="H49" s="235"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="234" t="s">
+      <c r="B52" s="235" t="s">
         <v>101</v>
       </c>
-      <c r="C52" s="234"/>
-      <c r="D52" s="234"/>
-      <c r="E52" s="234"/>
-      <c r="F52" s="234"/>
-      <c r="G52" s="234"/>
-      <c r="H52" s="234"/>
+      <c r="C52" s="235"/>
+      <c r="D52" s="235"/>
+      <c r="E52" s="235"/>
+      <c r="F52" s="235"/>
+      <c r="G52" s="235"/>
+      <c r="H52" s="235"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -13053,13 +13988,13 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="234"/>
-      <c r="C59" s="234"/>
-      <c r="D59" s="234"/>
-      <c r="E59" s="234"/>
-      <c r="F59" s="234"/>
-      <c r="G59" s="234"/>
-      <c r="H59" s="234"/>
+      <c r="B59" s="235"/>
+      <c r="C59" s="235"/>
+      <c r="D59" s="235"/>
+      <c r="E59" s="235"/>
+      <c r="F59" s="235"/>
+      <c r="G59" s="235"/>
+      <c r="H59" s="235"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -13144,36 +14079,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="234" t="s">
+      <c r="C2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="234"/>
-      <c r="G2" s="243"/>
-      <c r="H2" s="244" t="s">
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="234"/>
-      <c r="J2" s="234"/>
-      <c r="K2" s="234"/>
-      <c r="L2" s="234"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="234" t="s">
+      <c r="S2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="234"/>
-      <c r="U2" s="234"/>
-      <c r="V2" s="234"/>
-      <c r="W2" s="234"/>
-      <c r="X2" s="234"/>
-      <c r="Y2" s="234"/>
-      <c r="Z2" s="234"/>
-      <c r="AA2" s="234" t="s">
+      <c r="T2" s="235"/>
+      <c r="U2" s="235"/>
+      <c r="V2" s="235"/>
+      <c r="W2" s="235"/>
+      <c r="X2" s="235"/>
+      <c r="Y2" s="235"/>
+      <c r="Z2" s="235"/>
+      <c r="AA2" s="235" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="234"/>
-      <c r="AC2" s="234"/>
+      <c r="AB2" s="235"/>
+      <c r="AC2" s="235"/>
       <c r="AE2" s="85" t="s">
         <v>107</v>
       </c>
@@ -13184,32 +14119,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="240" t="s">
+      <c r="C4" s="241" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="240"/>
-      <c r="E4" s="240"/>
-      <c r="F4" s="240"/>
-      <c r="G4" s="240"/>
-      <c r="H4" s="240"/>
-      <c r="I4" s="240"/>
-      <c r="J4" s="240"/>
-      <c r="K4" s="240"/>
-      <c r="L4" s="240"/>
+      <c r="D4" s="241"/>
+      <c r="E4" s="241"/>
+      <c r="F4" s="241"/>
+      <c r="G4" s="241"/>
+      <c r="H4" s="241"/>
+      <c r="I4" s="241"/>
+      <c r="J4" s="241"/>
+      <c r="K4" s="241"/>
+      <c r="L4" s="241"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="241" t="s">
+      <c r="S4" s="242" t="s">
         <v>108</v>
       </c>
-      <c r="T4" s="242"/>
-      <c r="U4" s="242"/>
-      <c r="V4" s="242"/>
-      <c r="W4" s="242"/>
-      <c r="X4" s="242"/>
-      <c r="Y4" s="242"/>
-      <c r="Z4" s="242"/>
-      <c r="AA4" s="242"/>
-      <c r="AB4" s="242"/>
-      <c r="AC4" s="242"/>
+      <c r="T4" s="243"/>
+      <c r="U4" s="243"/>
+      <c r="V4" s="243"/>
+      <c r="W4" s="243"/>
+      <c r="X4" s="243"/>
+      <c r="Y4" s="243"/>
+      <c r="Z4" s="243"/>
+      <c r="AA4" s="243"/>
+      <c r="AB4" s="243"/>
+      <c r="AC4" s="243"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -13794,33 +14729,33 @@
       <c r="Q11" s="91"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C12" s="240" t="s">
+      <c r="C12" s="241" t="s">
         <v>114</v>
       </c>
-      <c r="D12" s="240"/>
-      <c r="E12" s="240"/>
-      <c r="F12" s="240"/>
-      <c r="G12" s="240"/>
-      <c r="H12" s="240"/>
-      <c r="I12" s="240"/>
-      <c r="J12" s="240"/>
-      <c r="K12" s="240"/>
-      <c r="L12" s="240"/>
+      <c r="D12" s="241"/>
+      <c r="E12" s="241"/>
+      <c r="F12" s="241"/>
+      <c r="G12" s="241"/>
+      <c r="H12" s="241"/>
+      <c r="I12" s="241"/>
+      <c r="J12" s="241"/>
+      <c r="K12" s="241"/>
+      <c r="L12" s="241"/>
       <c r="O12" s="5"/>
       <c r="Q12" s="91"/>
-      <c r="S12" s="241" t="s">
+      <c r="S12" s="242" t="s">
         <v>114</v>
       </c>
-      <c r="T12" s="242"/>
-      <c r="U12" s="242"/>
-      <c r="V12" s="242"/>
-      <c r="W12" s="242"/>
-      <c r="X12" s="242"/>
-      <c r="Y12" s="242"/>
-      <c r="Z12" s="242"/>
-      <c r="AA12" s="242"/>
-      <c r="AB12" s="242"/>
-      <c r="AC12" s="242"/>
+      <c r="T12" s="243"/>
+      <c r="U12" s="243"/>
+      <c r="V12" s="243"/>
+      <c r="W12" s="243"/>
+      <c r="X12" s="243"/>
+      <c r="Y12" s="243"/>
+      <c r="Z12" s="243"/>
+      <c r="AA12" s="243"/>
+      <c r="AB12" s="243"/>
+      <c r="AC12" s="243"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B13" s="16" t="s">
@@ -14369,35 +15304,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="234" t="s">
+      <c r="C2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="234"/>
-      <c r="G2" s="243"/>
-      <c r="H2" s="244" t="s">
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="234"/>
-      <c r="J2" s="234"/>
-      <c r="K2" s="234"/>
-      <c r="L2" s="234"/>
-      <c r="P2" s="234" t="s">
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
+      <c r="P2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="234"/>
-      <c r="R2" s="234"/>
-      <c r="S2" s="234"/>
-      <c r="T2" s="234"/>
-      <c r="U2" s="234"/>
-      <c r="V2" s="234"/>
-      <c r="W2" s="234"/>
-      <c r="X2" s="234" t="s">
+      <c r="Q2" s="235"/>
+      <c r="R2" s="235"/>
+      <c r="S2" s="235"/>
+      <c r="T2" s="235"/>
+      <c r="U2" s="235"/>
+      <c r="V2" s="235"/>
+      <c r="W2" s="235"/>
+      <c r="X2" s="235" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="234"/>
-      <c r="Z2" s="234"/>
+      <c r="Y2" s="235"/>
+      <c r="Z2" s="235"/>
       <c r="AB2" s="85" t="s">
         <v>107</v>
       </c>
@@ -14406,31 +15341,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="240" t="s">
+      <c r="C4" s="241" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="240"/>
-      <c r="E4" s="240"/>
-      <c r="F4" s="240"/>
-      <c r="G4" s="240"/>
-      <c r="H4" s="240"/>
-      <c r="I4" s="240"/>
-      <c r="J4" s="240"/>
-      <c r="K4" s="240"/>
-      <c r="L4" s="240"/>
-      <c r="P4" s="242" t="s">
+      <c r="D4" s="241"/>
+      <c r="E4" s="241"/>
+      <c r="F4" s="241"/>
+      <c r="G4" s="241"/>
+      <c r="H4" s="241"/>
+      <c r="I4" s="241"/>
+      <c r="J4" s="241"/>
+      <c r="K4" s="241"/>
+      <c r="L4" s="241"/>
+      <c r="P4" s="243" t="s">
         <v>108</v>
       </c>
-      <c r="Q4" s="242"/>
-      <c r="R4" s="242"/>
-      <c r="S4" s="242"/>
-      <c r="T4" s="242"/>
-      <c r="U4" s="242"/>
-      <c r="V4" s="242"/>
-      <c r="W4" s="242"/>
-      <c r="X4" s="242"/>
-      <c r="Y4" s="242"/>
-      <c r="Z4" s="242"/>
+      <c r="Q4" s="243"/>
+      <c r="R4" s="243"/>
+      <c r="S4" s="243"/>
+      <c r="T4" s="243"/>
+      <c r="U4" s="243"/>
+      <c r="V4" s="243"/>
+      <c r="W4" s="243"/>
+      <c r="X4" s="243"/>
+      <c r="Y4" s="243"/>
+      <c r="Z4" s="243"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -14625,32 +15560,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="240" t="s">
+      <c r="C9" s="241" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="240"/>
-      <c r="E9" s="240"/>
-      <c r="F9" s="240"/>
-      <c r="G9" s="240"/>
-      <c r="H9" s="240"/>
-      <c r="I9" s="240"/>
-      <c r="J9" s="240"/>
-      <c r="K9" s="240"/>
-      <c r="L9" s="240"/>
+      <c r="D9" s="241"/>
+      <c r="E9" s="241"/>
+      <c r="F9" s="241"/>
+      <c r="G9" s="241"/>
+      <c r="H9" s="241"/>
+      <c r="I9" s="241"/>
+      <c r="J9" s="241"/>
+      <c r="K9" s="241"/>
+      <c r="L9" s="241"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="242" t="s">
+      <c r="P9" s="243" t="s">
         <v>118</v>
       </c>
-      <c r="Q9" s="242"/>
-      <c r="R9" s="242"/>
-      <c r="S9" s="242"/>
-      <c r="T9" s="242"/>
-      <c r="U9" s="242"/>
-      <c r="V9" s="242"/>
-      <c r="W9" s="242"/>
-      <c r="X9" s="242"/>
-      <c r="Y9" s="242"/>
-      <c r="Z9" s="242"/>
+      <c r="Q9" s="243"/>
+      <c r="R9" s="243"/>
+      <c r="S9" s="243"/>
+      <c r="T9" s="243"/>
+      <c r="U9" s="243"/>
+      <c r="V9" s="243"/>
+      <c r="W9" s="243"/>
+      <c r="X9" s="243"/>
+      <c r="Y9" s="243"/>
+      <c r="Z9" s="243"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -15126,31 +16061,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="240" t="s">
+      <c r="C17" s="241" t="s">
         <v>120</v>
       </c>
-      <c r="D17" s="240"/>
-      <c r="E17" s="240"/>
-      <c r="F17" s="240"/>
-      <c r="G17" s="240"/>
-      <c r="H17" s="240"/>
-      <c r="I17" s="240"/>
-      <c r="J17" s="240"/>
-      <c r="K17" s="240"/>
-      <c r="L17" s="240"/>
-      <c r="P17" s="242" t="s">
+      <c r="D17" s="241"/>
+      <c r="E17" s="241"/>
+      <c r="F17" s="241"/>
+      <c r="G17" s="241"/>
+      <c r="H17" s="241"/>
+      <c r="I17" s="241"/>
+      <c r="J17" s="241"/>
+      <c r="K17" s="241"/>
+      <c r="L17" s="241"/>
+      <c r="P17" s="243" t="s">
         <v>120</v>
       </c>
-      <c r="Q17" s="242"/>
-      <c r="R17" s="242"/>
-      <c r="S17" s="242"/>
-      <c r="T17" s="242"/>
-      <c r="U17" s="242"/>
-      <c r="V17" s="242"/>
-      <c r="W17" s="242"/>
-      <c r="X17" s="242"/>
-      <c r="Y17" s="242"/>
-      <c r="Z17" s="242"/>
+      <c r="Q17" s="243"/>
+      <c r="R17" s="243"/>
+      <c r="S17" s="243"/>
+      <c r="T17" s="243"/>
+      <c r="U17" s="243"/>
+      <c r="V17" s="243"/>
+      <c r="W17" s="243"/>
+      <c r="X17" s="243"/>
+      <c r="Y17" s="243"/>
+      <c r="Z17" s="243"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="16" t="s">
@@ -15628,60 +16563,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="234" t="s">
+      <c r="C3" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="234"/>
-      <c r="E3" s="234"/>
-      <c r="F3" s="234"/>
-      <c r="G3" s="243"/>
-      <c r="H3" s="244" t="s">
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
+      <c r="G3" s="244"/>
+      <c r="H3" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="234"/>
-      <c r="J3" s="234"/>
-      <c r="K3" s="234"/>
-      <c r="L3" s="234"/>
-      <c r="P3" s="245"/>
-      <c r="Q3" s="245"/>
-      <c r="R3" s="245"/>
-      <c r="S3" s="245"/>
-      <c r="T3" s="245"/>
-      <c r="U3" s="245"/>
-      <c r="V3" s="245"/>
-      <c r="W3" s="245"/>
-      <c r="X3" s="245"/>
-      <c r="Y3" s="245"/>
-      <c r="Z3" s="245"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
+      <c r="P3" s="246"/>
+      <c r="Q3" s="246"/>
+      <c r="R3" s="246"/>
+      <c r="S3" s="246"/>
+      <c r="T3" s="246"/>
+      <c r="U3" s="246"/>
+      <c r="V3" s="246"/>
+      <c r="W3" s="246"/>
+      <c r="X3" s="246"/>
+      <c r="Y3" s="246"/>
+      <c r="Z3" s="246"/>
       <c r="AB3" s="110"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="240" t="s">
+      <c r="C5" s="241" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="240"/>
-      <c r="E5" s="240"/>
-      <c r="F5" s="240"/>
-      <c r="G5" s="240"/>
-      <c r="H5" s="240"/>
-      <c r="I5" s="240"/>
-      <c r="J5" s="240"/>
-      <c r="K5" s="240"/>
-      <c r="L5" s="240"/>
-      <c r="P5" s="245"/>
-      <c r="Q5" s="245"/>
-      <c r="R5" s="245"/>
-      <c r="S5" s="245"/>
-      <c r="T5" s="245"/>
-      <c r="U5" s="245"/>
-      <c r="V5" s="245"/>
-      <c r="W5" s="245"/>
-      <c r="X5" s="245"/>
-      <c r="Y5" s="245"/>
-      <c r="Z5" s="245"/>
+      <c r="D5" s="241"/>
+      <c r="E5" s="241"/>
+      <c r="F5" s="241"/>
+      <c r="G5" s="241"/>
+      <c r="H5" s="241"/>
+      <c r="I5" s="241"/>
+      <c r="J5" s="241"/>
+      <c r="K5" s="241"/>
+      <c r="L5" s="241"/>
+      <c r="P5" s="246"/>
+      <c r="Q5" s="246"/>
+      <c r="R5" s="246"/>
+      <c r="S5" s="246"/>
+      <c r="T5" s="246"/>
+      <c r="U5" s="246"/>
+      <c r="V5" s="246"/>
+      <c r="W5" s="246"/>
+      <c r="X5" s="246"/>
+      <c r="Y5" s="246"/>
+      <c r="Z5" s="246"/>
       <c r="AB5" s="111"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -15867,30 +16802,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="240" t="s">
+      <c r="C11" s="241" t="s">
         <v>124</v>
       </c>
-      <c r="D11" s="240"/>
-      <c r="E11" s="240"/>
-      <c r="F11" s="240"/>
-      <c r="G11" s="240"/>
-      <c r="H11" s="240"/>
-      <c r="I11" s="240"/>
-      <c r="J11" s="240"/>
-      <c r="K11" s="240"/>
-      <c r="L11" s="240"/>
+      <c r="D11" s="241"/>
+      <c r="E11" s="241"/>
+      <c r="F11" s="241"/>
+      <c r="G11" s="241"/>
+      <c r="H11" s="241"/>
+      <c r="I11" s="241"/>
+      <c r="J11" s="241"/>
+      <c r="K11" s="241"/>
+      <c r="L11" s="241"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="245"/>
-      <c r="Q11" s="245"/>
-      <c r="R11" s="245"/>
-      <c r="S11" s="245"/>
-      <c r="T11" s="245"/>
-      <c r="U11" s="245"/>
-      <c r="V11" s="245"/>
-      <c r="W11" s="245"/>
-      <c r="X11" s="245"/>
-      <c r="Y11" s="245"/>
-      <c r="Z11" s="245"/>
+      <c r="P11" s="246"/>
+      <c r="Q11" s="246"/>
+      <c r="R11" s="246"/>
+      <c r="S11" s="246"/>
+      <c r="T11" s="246"/>
+      <c r="U11" s="246"/>
+      <c r="V11" s="246"/>
+      <c r="W11" s="246"/>
+      <c r="X11" s="246"/>
+      <c r="Y11" s="246"/>
+      <c r="Z11" s="246"/>
       <c r="AB11" s="111"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -16132,18 +17067,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="240" t="s">
+      <c r="C18" s="241" t="s">
         <v>129</v>
       </c>
-      <c r="D18" s="240"/>
-      <c r="E18" s="240"/>
-      <c r="F18" s="240"/>
-      <c r="G18" s="240"/>
-      <c r="H18" s="240"/>
-      <c r="I18" s="240"/>
-      <c r="J18" s="240"/>
-      <c r="K18" s="240"/>
-      <c r="L18" s="240"/>
+      <c r="D18" s="241"/>
+      <c r="E18" s="241"/>
+      <c r="F18" s="241"/>
+      <c r="G18" s="241"/>
+      <c r="H18" s="241"/>
+      <c r="I18" s="241"/>
+      <c r="J18" s="241"/>
+      <c r="K18" s="241"/>
+      <c r="L18" s="241"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -16356,23 +17291,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="245"/>
-      <c r="C25" s="245"/>
+      <c r="B25" s="246"/>
+      <c r="C25" s="246"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="110"/>
-      <c r="C26" s="240" t="s">
+      <c r="C26" s="241" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="240"/>
-      <c r="E26" s="240"/>
-      <c r="F26" s="240"/>
-      <c r="G26" s="240"/>
-      <c r="H26" s="240"/>
-      <c r="I26" s="240"/>
-      <c r="J26" s="240"/>
-      <c r="K26" s="240"/>
-      <c r="L26" s="240"/>
+      <c r="D26" s="241"/>
+      <c r="E26" s="241"/>
+      <c r="F26" s="241"/>
+      <c r="G26" s="241"/>
+      <c r="H26" s="241"/>
+      <c r="I26" s="241"/>
+      <c r="J26" s="241"/>
+      <c r="K26" s="241"/>
+      <c r="L26" s="241"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -16564,18 +17499,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="110"/>
-      <c r="C33" s="240" t="s">
+      <c r="C33" s="241" t="s">
         <v>139</v>
       </c>
-      <c r="D33" s="240"/>
-      <c r="E33" s="240"/>
-      <c r="F33" s="240"/>
-      <c r="G33" s="240"/>
-      <c r="H33" s="240"/>
-      <c r="I33" s="240"/>
-      <c r="J33" s="240"/>
-      <c r="K33" s="240"/>
-      <c r="L33" s="240"/>
+      <c r="D33" s="241"/>
+      <c r="E33" s="241"/>
+      <c r="F33" s="241"/>
+      <c r="G33" s="241"/>
+      <c r="H33" s="241"/>
+      <c r="I33" s="241"/>
+      <c r="J33" s="241"/>
+      <c r="K33" s="241"/>
+      <c r="L33" s="241"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -16759,18 +17694,18 @@
       <c r="C39" s="126"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="240" t="s">
+      <c r="C40" s="241" t="s">
         <v>142</v>
       </c>
-      <c r="D40" s="240"/>
-      <c r="E40" s="240"/>
-      <c r="F40" s="240"/>
-      <c r="G40" s="240"/>
-      <c r="H40" s="240"/>
-      <c r="I40" s="240"/>
-      <c r="J40" s="240"/>
-      <c r="K40" s="240"/>
-      <c r="L40" s="240"/>
+      <c r="D40" s="241"/>
+      <c r="E40" s="241"/>
+      <c r="F40" s="241"/>
+      <c r="G40" s="241"/>
+      <c r="H40" s="241"/>
+      <c r="I40" s="241"/>
+      <c r="J40" s="241"/>
+      <c r="K40" s="241"/>
+      <c r="L40" s="241"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -17084,60 +18019,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="234" t="s">
+      <c r="C2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="234"/>
-      <c r="G2" s="243"/>
-      <c r="H2" s="244" t="s">
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="234"/>
-      <c r="J2" s="234"/>
-      <c r="K2" s="234"/>
-      <c r="L2" s="234"/>
-      <c r="S2" s="245"/>
-      <c r="T2" s="245"/>
-      <c r="U2" s="245"/>
-      <c r="V2" s="245"/>
-      <c r="W2" s="245"/>
-      <c r="X2" s="245"/>
-      <c r="Y2" s="245"/>
-      <c r="Z2" s="245"/>
-      <c r="AA2" s="245"/>
-      <c r="AB2" s="245"/>
-      <c r="AC2" s="245"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
+      <c r="S2" s="246"/>
+      <c r="T2" s="246"/>
+      <c r="U2" s="246"/>
+      <c r="V2" s="246"/>
+      <c r="W2" s="246"/>
+      <c r="X2" s="246"/>
+      <c r="Y2" s="246"/>
+      <c r="Z2" s="246"/>
+      <c r="AA2" s="246"/>
+      <c r="AB2" s="246"/>
+      <c r="AC2" s="246"/>
       <c r="AE2" s="110"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="240" t="s">
+      <c r="C4" s="241" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="240"/>
-      <c r="E4" s="240"/>
-      <c r="F4" s="240"/>
-      <c r="G4" s="240"/>
-      <c r="H4" s="240"/>
-      <c r="I4" s="240"/>
-      <c r="J4" s="240"/>
-      <c r="K4" s="240"/>
-      <c r="L4" s="240"/>
-      <c r="S4" s="245"/>
-      <c r="T4" s="245"/>
-      <c r="U4" s="245"/>
-      <c r="V4" s="245"/>
-      <c r="W4" s="245"/>
-      <c r="X4" s="245"/>
-      <c r="Y4" s="245"/>
-      <c r="Z4" s="245"/>
-      <c r="AA4" s="245"/>
-      <c r="AB4" s="245"/>
-      <c r="AC4" s="245"/>
+      <c r="D4" s="241"/>
+      <c r="E4" s="241"/>
+      <c r="F4" s="241"/>
+      <c r="G4" s="241"/>
+      <c r="H4" s="241"/>
+      <c r="I4" s="241"/>
+      <c r="J4" s="241"/>
+      <c r="K4" s="241"/>
+      <c r="L4" s="241"/>
+      <c r="S4" s="246"/>
+      <c r="T4" s="246"/>
+      <c r="U4" s="246"/>
+      <c r="V4" s="246"/>
+      <c r="W4" s="246"/>
+      <c r="X4" s="246"/>
+      <c r="Y4" s="246"/>
+      <c r="Z4" s="246"/>
+      <c r="AA4" s="246"/>
+      <c r="AB4" s="246"/>
+      <c r="AC4" s="246"/>
       <c r="AE4" s="111"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -17500,18 +18435,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="240" t="s">
+      <c r="C13" s="241" t="s">
         <v>150</v>
       </c>
-      <c r="D13" s="240"/>
-      <c r="E13" s="240"/>
-      <c r="F13" s="240"/>
-      <c r="G13" s="240"/>
-      <c r="H13" s="240"/>
-      <c r="I13" s="240"/>
-      <c r="J13" s="240"/>
-      <c r="K13" s="240"/>
-      <c r="L13" s="240"/>
+      <c r="D13" s="241"/>
+      <c r="E13" s="241"/>
+      <c r="F13" s="241"/>
+      <c r="G13" s="241"/>
+      <c r="H13" s="241"/>
+      <c r="I13" s="241"/>
+      <c r="J13" s="241"/>
+      <c r="K13" s="241"/>
+      <c r="L13" s="241"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -17604,18 +18539,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="240" t="s">
+      <c r="C18" s="241" t="s">
         <v>151</v>
       </c>
-      <c r="D18" s="240"/>
-      <c r="E18" s="240"/>
-      <c r="F18" s="240"/>
-      <c r="G18" s="240"/>
-      <c r="H18" s="240"/>
-      <c r="I18" s="240"/>
-      <c r="J18" s="240"/>
-      <c r="K18" s="240"/>
-      <c r="L18" s="240"/>
+      <c r="D18" s="241"/>
+      <c r="E18" s="241"/>
+      <c r="F18" s="241"/>
+      <c r="G18" s="241"/>
+      <c r="H18" s="241"/>
+      <c r="I18" s="241"/>
+      <c r="J18" s="241"/>
+      <c r="K18" s="241"/>
+      <c r="L18" s="241"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17807,18 +18742,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="240" t="s">
+      <c r="C25" s="241" t="s">
         <v>259</v>
       </c>
-      <c r="D25" s="240"/>
-      <c r="E25" s="240"/>
-      <c r="F25" s="240"/>
-      <c r="G25" s="240"/>
-      <c r="H25" s="240"/>
-      <c r="I25" s="240"/>
-      <c r="J25" s="240"/>
-      <c r="K25" s="240"/>
-      <c r="L25" s="240"/>
+      <c r="D25" s="241"/>
+      <c r="E25" s="241"/>
+      <c r="F25" s="241"/>
+      <c r="G25" s="241"/>
+      <c r="H25" s="241"/>
+      <c r="I25" s="241"/>
+      <c r="J25" s="241"/>
+      <c r="K25" s="241"/>
+      <c r="L25" s="241"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -17956,18 +18891,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="240" t="s">
+      <c r="C31" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="240"/>
-      <c r="E31" s="240"/>
-      <c r="F31" s="240"/>
-      <c r="G31" s="240"/>
-      <c r="H31" s="240"/>
-      <c r="I31" s="240"/>
-      <c r="J31" s="240"/>
-      <c r="K31" s="240"/>
-      <c r="L31" s="240"/>
+      <c r="D31" s="241"/>
+      <c r="E31" s="241"/>
+      <c r="F31" s="241"/>
+      <c r="G31" s="241"/>
+      <c r="H31" s="241"/>
+      <c r="I31" s="241"/>
+      <c r="J31" s="241"/>
+      <c r="K31" s="241"/>
+      <c r="L31" s="241"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -18178,10 +19113,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="234" t="s">
+      <c r="B4" s="235" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="234"/>
+      <c r="C4" s="235"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -18198,7 +19133,7 @@
       </c>
       <c r="C6" s="134">
         <f ca="1">Overview!C5</f>
-        <v>204.65</v>
+        <v>210.69</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18207,7 +19142,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">C5*C6</f>
-        <v>4974018.25</v>
+        <v>5120820.45</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18225,7 +19160,7 @@
       </c>
       <c r="C9" s="136">
         <f ca="1">Overview!F27</f>
-        <v>4.428E-2</v>
+        <v>4.4510000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18234,7 +19169,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C13</f>
-        <v>2.2052999999999998</v>
+        <v>2.2023999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18266,10 +19201,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="234" t="s">
+      <c r="B15" s="235" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="234"/>
+      <c r="C15" s="235"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -18277,7 +19212,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>1.6999538333080865E-3</v>
+        <v>1.65130052247285E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18286,7 +19221,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99830004616669188</v>
+        <v>0.99834869947752714</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18304,7 +19239,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14351849999999999</v>
+        <v>0.143618</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18313,7 +19248,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14334301631571833</v>
+        <v>0.14344737441961392</v>
       </c>
     </row>
   </sheetData>
@@ -18358,60 +19293,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="234" t="s">
+      <c r="C3" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="234"/>
-      <c r="E3" s="234"/>
-      <c r="F3" s="234"/>
-      <c r="G3" s="243"/>
-      <c r="H3" s="244" t="s">
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
+      <c r="G3" s="244"/>
+      <c r="H3" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="234"/>
-      <c r="J3" s="234"/>
-      <c r="K3" s="234"/>
-      <c r="L3" s="234"/>
-      <c r="P3" s="245"/>
-      <c r="Q3" s="245"/>
-      <c r="R3" s="245"/>
-      <c r="S3" s="245"/>
-      <c r="T3" s="245"/>
-      <c r="U3" s="245"/>
-      <c r="V3" s="245"/>
-      <c r="W3" s="245"/>
-      <c r="X3" s="245"/>
-      <c r="Y3" s="245"/>
-      <c r="Z3" s="245"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
+      <c r="P3" s="246"/>
+      <c r="Q3" s="246"/>
+      <c r="R3" s="246"/>
+      <c r="S3" s="246"/>
+      <c r="T3" s="246"/>
+      <c r="U3" s="246"/>
+      <c r="V3" s="246"/>
+      <c r="W3" s="246"/>
+      <c r="X3" s="246"/>
+      <c r="Y3" s="246"/>
+      <c r="Z3" s="246"/>
       <c r="AB3" s="110"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="240" t="s">
+      <c r="C5" s="241" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="240"/>
-      <c r="E5" s="240"/>
-      <c r="F5" s="240"/>
-      <c r="G5" s="240"/>
-      <c r="H5" s="240"/>
-      <c r="I5" s="240"/>
-      <c r="J5" s="240"/>
-      <c r="K5" s="240"/>
-      <c r="L5" s="240"/>
-      <c r="P5" s="245"/>
-      <c r="Q5" s="245"/>
-      <c r="R5" s="245"/>
-      <c r="S5" s="245"/>
-      <c r="T5" s="245"/>
-      <c r="U5" s="245"/>
-      <c r="V5" s="245"/>
-      <c r="W5" s="245"/>
-      <c r="X5" s="245"/>
-      <c r="Y5" s="245"/>
-      <c r="Z5" s="245"/>
+      <c r="D5" s="241"/>
+      <c r="E5" s="241"/>
+      <c r="F5" s="241"/>
+      <c r="G5" s="241"/>
+      <c r="H5" s="241"/>
+      <c r="I5" s="241"/>
+      <c r="J5" s="241"/>
+      <c r="K5" s="241"/>
+      <c r="L5" s="241"/>
+      <c r="P5" s="246"/>
+      <c r="Q5" s="246"/>
+      <c r="R5" s="246"/>
+      <c r="S5" s="246"/>
+      <c r="T5" s="246"/>
+      <c r="U5" s="246"/>
+      <c r="V5" s="246"/>
+      <c r="W5" s="246"/>
+      <c r="X5" s="246"/>
+      <c r="Y5" s="246"/>
+      <c r="Z5" s="246"/>
       <c r="AB5" s="111"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -18657,10 +19592,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="234" t="s">
+      <c r="B13" s="235" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="234"/>
+      <c r="C13" s="235"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -18680,10 +19615,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="234" t="s">
+      <c r="B18" s="235" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="234"/>
+      <c r="C18" s="235"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -18797,37 +19732,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="234" t="s">
+      <c r="C2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="234"/>
-      <c r="G2" s="243"/>
-      <c r="H2" s="244" t="s">
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="234"/>
-      <c r="J2" s="234"/>
-      <c r="K2" s="234"/>
-      <c r="L2" s="234"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="240" t="s">
+      <c r="C4" s="241" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="240"/>
-      <c r="E4" s="240"/>
-      <c r="F4" s="240"/>
-      <c r="G4" s="240"/>
-      <c r="H4" s="240"/>
-      <c r="I4" s="240"/>
-      <c r="J4" s="240"/>
-      <c r="K4" s="240"/>
-      <c r="L4" s="240"/>
+      <c r="D4" s="241"/>
+      <c r="E4" s="241"/>
+      <c r="F4" s="241"/>
+      <c r="G4" s="241"/>
+      <c r="H4" s="241"/>
+      <c r="I4" s="241"/>
+      <c r="J4" s="241"/>
+      <c r="K4" s="241"/>
+      <c r="L4" s="241"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -19016,18 +19951,18 @@
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="240" t="s">
+      <c r="C10" s="241" t="s">
         <v>114</v>
       </c>
-      <c r="D10" s="240"/>
-      <c r="E10" s="240"/>
-      <c r="F10" s="240"/>
-      <c r="G10" s="240"/>
-      <c r="H10" s="240"/>
-      <c r="I10" s="240"/>
-      <c r="J10" s="240"/>
-      <c r="K10" s="240"/>
-      <c r="L10" s="240"/>
+      <c r="D10" s="241"/>
+      <c r="E10" s="241"/>
+      <c r="F10" s="241"/>
+      <c r="G10" s="241"/>
+      <c r="H10" s="241"/>
+      <c r="I10" s="241"/>
+      <c r="J10" s="241"/>
+      <c r="K10" s="241"/>
+      <c r="L10" s="241"/>
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -19221,18 +20156,18 @@
       <c r="N15" s="91"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="240" t="s">
+      <c r="C16" s="241" t="s">
         <v>188</v>
       </c>
-      <c r="D16" s="240"/>
-      <c r="E16" s="240"/>
-      <c r="F16" s="240"/>
-      <c r="G16" s="240"/>
-      <c r="H16" s="240"/>
-      <c r="I16" s="240"/>
-      <c r="J16" s="240"/>
-      <c r="K16" s="240"/>
-      <c r="L16" s="240"/>
+      <c r="D16" s="241"/>
+      <c r="E16" s="241"/>
+      <c r="F16" s="241"/>
+      <c r="G16" s="241"/>
+      <c r="H16" s="241"/>
+      <c r="I16" s="241"/>
+      <c r="J16" s="241"/>
+      <c r="K16" s="241"/>
+      <c r="L16" s="241"/>
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -19366,18 +20301,18 @@
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="240" t="s">
+      <c r="C21" s="241" t="s">
         <v>191</v>
       </c>
-      <c r="D21" s="240"/>
-      <c r="E21" s="240"/>
-      <c r="F21" s="240"/>
-      <c r="G21" s="240"/>
-      <c r="H21" s="240"/>
-      <c r="I21" s="240"/>
-      <c r="J21" s="240"/>
-      <c r="K21" s="240"/>
-      <c r="L21" s="240"/>
+      <c r="D21" s="241"/>
+      <c r="E21" s="241"/>
+      <c r="F21" s="241"/>
+      <c r="G21" s="241"/>
+      <c r="H21" s="241"/>
+      <c r="I21" s="241"/>
+      <c r="J21" s="241"/>
+      <c r="K21" s="241"/>
+      <c r="L21" s="241"/>
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -19461,18 +20396,18 @@
       <c r="N25" s="91"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="240" t="s">
+      <c r="C26" s="241" t="s">
         <v>192</v>
       </c>
-      <c r="D26" s="240"/>
-      <c r="E26" s="240"/>
-      <c r="F26" s="240"/>
-      <c r="G26" s="240"/>
-      <c r="H26" s="240"/>
-      <c r="I26" s="240"/>
-      <c r="J26" s="240"/>
-      <c r="K26" s="240"/>
-      <c r="L26" s="240"/>
+      <c r="D26" s="241"/>
+      <c r="E26" s="241"/>
+      <c r="F26" s="241"/>
+      <c r="G26" s="241"/>
+      <c r="H26" s="241"/>
+      <c r="I26" s="241"/>
+      <c r="J26" s="241"/>
+      <c r="K26" s="241"/>
+      <c r="L26" s="241"/>
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -19742,10 +20677,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="234" t="s">
+      <c r="B37" s="235" t="s">
         <v>197</v>
       </c>
-      <c r="C37" s="234"/>
+      <c r="C37" s="235"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -19811,10 +20746,10 @@
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="234" t="s">
+      <c r="B46" s="235" t="s">
         <v>202</v>
       </c>
-      <c r="C46" s="234"/>
+      <c r="C46" s="235"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
@@ -19870,10 +20805,10 @@
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="234" t="s">
+      <c r="B54" s="235" t="s">
         <v>319</v>
       </c>
-      <c r="C54" s="234"/>
+      <c r="C54" s="235"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
@@ -19986,10 +20921,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="234" t="s">
+      <c r="B4" s="235" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="234"/>
+      <c r="C4" s="235"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -20043,7 +20978,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C5</f>
-        <v>204.65</v>
+        <v>210.69</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -20052,7 +20987,7 @@
       </c>
       <c r="C11" s="155">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.45005107077740031</v>
+        <v>0.40848142595564563</v>
       </c>
     </row>
   </sheetData>
@@ -20117,60 +21052,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="234" t="s">
+      <c r="C3" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="234"/>
-      <c r="E3" s="234"/>
-      <c r="F3" s="234"/>
-      <c r="G3" s="243"/>
-      <c r="H3" s="244" t="s">
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
+      <c r="G3" s="244"/>
+      <c r="H3" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="234"/>
-      <c r="J3" s="234"/>
-      <c r="K3" s="234"/>
-      <c r="L3" s="234"/>
-      <c r="P3" s="245"/>
-      <c r="Q3" s="245"/>
-      <c r="R3" s="245"/>
-      <c r="S3" s="245"/>
-      <c r="T3" s="245"/>
-      <c r="U3" s="245"/>
-      <c r="V3" s="245"/>
-      <c r="W3" s="245"/>
-      <c r="X3" s="245"/>
-      <c r="Y3" s="245"/>
-      <c r="Z3" s="245"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
+      <c r="P3" s="246"/>
+      <c r="Q3" s="246"/>
+      <c r="R3" s="246"/>
+      <c r="S3" s="246"/>
+      <c r="T3" s="246"/>
+      <c r="U3" s="246"/>
+      <c r="V3" s="246"/>
+      <c r="W3" s="246"/>
+      <c r="X3" s="246"/>
+      <c r="Y3" s="246"/>
+      <c r="Z3" s="246"/>
       <c r="AB3" s="110"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="240" t="s">
+      <c r="C5" s="241" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="240"/>
-      <c r="E5" s="240"/>
-      <c r="F5" s="240"/>
-      <c r="G5" s="240"/>
-      <c r="H5" s="240"/>
-      <c r="I5" s="240"/>
-      <c r="J5" s="240"/>
-      <c r="K5" s="240"/>
-      <c r="L5" s="240"/>
-      <c r="P5" s="245"/>
-      <c r="Q5" s="245"/>
-      <c r="R5" s="245"/>
-      <c r="S5" s="245"/>
-      <c r="T5" s="245"/>
-      <c r="U5" s="245"/>
-      <c r="V5" s="245"/>
-      <c r="W5" s="245"/>
-      <c r="X5" s="245"/>
-      <c r="Y5" s="245"/>
-      <c r="Z5" s="245"/>
+      <c r="D5" s="241"/>
+      <c r="E5" s="241"/>
+      <c r="F5" s="241"/>
+      <c r="G5" s="241"/>
+      <c r="H5" s="241"/>
+      <c r="I5" s="241"/>
+      <c r="J5" s="241"/>
+      <c r="K5" s="241"/>
+      <c r="L5" s="241"/>
+      <c r="P5" s="246"/>
+      <c r="Q5" s="246"/>
+      <c r="R5" s="246"/>
+      <c r="S5" s="246"/>
+      <c r="T5" s="246"/>
+      <c r="U5" s="246"/>
+      <c r="V5" s="246"/>
+      <c r="W5" s="246"/>
+      <c r="X5" s="246"/>
+      <c r="Y5" s="246"/>
+      <c r="Z5" s="246"/>
       <c r="AB5" s="111"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -20399,10 +21334,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="246" t="s">
+      <c r="B14" s="247" t="s">
         <v>215</v>
       </c>
-      <c r="C14" s="247"/>
+      <c r="C14" s="248"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="156" t="s">
@@ -20410,7 +21345,7 @@
       </c>
       <c r="C15" s="157">
         <f ca="1">Overview!C5</f>
-        <v>204.65</v>
+        <v>210.69</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -20429,20 +21364,20 @@
       <c r="C17" s="159">
         <v>0.55000000000000004</v>
       </c>
-      <c r="E17" s="248" t="s">
+      <c r="E17" s="249" t="s">
         <v>218</v>
       </c>
-      <c r="F17" s="248"/>
-      <c r="G17" s="248"/>
-      <c r="H17" s="248"/>
-      <c r="I17" s="248"/>
+      <c r="F17" s="249"/>
+      <c r="G17" s="249"/>
+      <c r="H17" s="249"/>
+      <c r="I17" s="249"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="246" t="s">
+      <c r="B19" s="247" t="s">
         <v>176</v>
       </c>
-      <c r="C19" s="247"/>
+      <c r="C19" s="248"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="160" t="s">
@@ -20476,7 +21411,7 @@
       </c>
       <c r="C23" s="162">
         <f ca="1">C15*C22</f>
-        <v>4952530</v>
+        <v>5098698</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -20503,15 +21438,15 @@
       </c>
       <c r="C26" s="163">
         <f ca="1">C23+C25-C24</f>
-        <v>4880428</v>
+        <v>5026596</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="246" t="s">
+      <c r="B28" s="247" t="s">
         <v>178</v>
       </c>
-      <c r="C28" s="247"/>
+      <c r="C28" s="248"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="160" t="s">
@@ -20586,18 +21521,18 @@
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="240" t="s">
+      <c r="C39" s="241" t="s">
         <v>221</v>
       </c>
-      <c r="D39" s="240"/>
-      <c r="E39" s="240"/>
-      <c r="F39" s="240"/>
-      <c r="G39" s="240"/>
-      <c r="H39" s="240"/>
-      <c r="I39" s="240"/>
-      <c r="J39" s="240"/>
-      <c r="K39" s="240"/>
-      <c r="L39" s="240"/>
+      <c r="D39" s="241"/>
+      <c r="E39" s="241"/>
+      <c r="F39" s="241"/>
+      <c r="G39" s="241"/>
+      <c r="H39" s="241"/>
+      <c r="I39" s="241"/>
+      <c r="J39" s="241"/>
+      <c r="K39" s="241"/>
+      <c r="L39" s="241"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -22618,6 +23553,8 @@
         <f>Q24/Q$84</f>
         <v>4.9000000000000004</v>
       </c>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
       <c r="T25" s="66">
         <f t="shared" ref="T25:AA25" si="11">T24/T$84</f>
         <v>0.67</v>
@@ -27535,7 +28472,7 @@
       <c r="AA114" s="68"/>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>204.65</v>
+        <v>210.69</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -27582,7 +28519,7 @@
       <c r="AA115" s="68"/>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>204.65</v>
+        <v>210.69</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29084,7 +30021,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>31.339969372128643</v>
+        <v>32.264931087289433</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -29121,7 +30058,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>19.746802351957271</v>
+        <v>20.329605607299669</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -29158,7 +30095,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>25.33600376520663</v>
+        <v>26.083765615887536</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -29195,7 +30132,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="144">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>4974018.25</v>
+        <v>5120820.45</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -29232,7 +30169,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="144">
         <f ca="1">AC155+AC106-AC105+AC47+AC44</f>
-        <v>4901916.25</v>
+        <v>5048718.45</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -29269,7 +30206,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="184">
         <f ca="1">AC156/AC5</f>
-        <v>19.337634274984122</v>
+        <v>19.916756216197026</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -29306,7 +30243,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="184">
         <f ca="1">AC156/AC11</f>
-        <v>30.205602797547524</v>
+        <v>31.110197800166375</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -29441,7 +30378,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="72">
         <f t="shared" ref="AC161:AC162" ca="1" si="96">AC155/AC159</f>
-        <v>44.317099084971979</v>
+        <v>45.625065263683098</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -29478,7 +30415,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ca="1" si="96"/>
-        <v>38.653748491273809</v>
+        <v>39.811347892684566</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -29515,7 +30452,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="74">
         <f t="shared" ref="AC163" ca="1" si="99">AC159/AC155</f>
-        <v>2.2564653838976163E-2</v>
+        <v>2.1917776867181507E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -29552,7 +30489,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>3.1908135841680917E-2</v>
+        <v>3.0993402629455595E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -29589,7 +30526,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="155">
         <f ca="1">AC81/AC115</f>
-        <v>1.9545565599804544E-4</v>
+        <v>1.8985238976695619E-4</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -29626,7 +30563,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="155">
         <f ca="1">-AC62/AC155</f>
-        <v>9.108129026265635E-3</v>
+        <v>8.8470198169123462E-3</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -29663,7 +30600,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="155">
         <f ca="1">-(AC62+AC63)/AC155</f>
-        <v>9.3037455180225766E-3</v>
+        <v>9.0370284316451666E-3</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -30166,7 +31103,7 @@
       <c r="AA178" s="49"/>
       <c r="AC178" s="155">
         <f ca="1">(AC105-AC106)/AC155</f>
-        <v>1.4495724859875615E-2</v>
+        <v>1.4080165610961813E-2</v>
       </c>
     </row>
     <row r="179" spans="1:31" x14ac:dyDescent="0.2">
@@ -31331,15 +32268,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="234" t="s">
+      <c r="B4" s="235" t="s">
         <v>230</v>
       </c>
-      <c r="C4" s="234"/>
-      <c r="E4" s="234" t="s">
+      <c r="C4" s="235"/>
+      <c r="E4" s="235" t="s">
         <v>237</v>
       </c>
-      <c r="F4" s="234"/>
-      <c r="G4" s="234"/>
+      <c r="F4" s="235"/>
+      <c r="G4" s="235"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -31347,7 +32284,7 @@
       </c>
       <c r="C5" s="173">
         <f ca="1">Overview!C5</f>
-        <v>204.65</v>
+        <v>210.69</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="133" t="s">
@@ -31363,7 +32300,7 @@
       </c>
       <c r="C6" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>4974018.25</v>
+        <v>5120820.45</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -31383,7 +32320,7 @@
       </c>
       <c r="C7" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>4901916.25</v>
+        <v>5048718.45</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -31403,7 +32340,7 @@
       </c>
       <c r="C8" s="175">
         <f ca="1">Statement!AC152</f>
-        <v>31.339969372128643</v>
+        <v>32.264931087289433</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>240</v>
@@ -31423,7 +32360,7 @@
       </c>
       <c r="C9" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>19.746802351957271</v>
+        <v>20.329605607299669</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>241</v>
@@ -31443,7 +32380,7 @@
       </c>
       <c r="C10" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>25.33600376520663</v>
+        <v>26.083765615887536</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -31463,7 +32400,7 @@
       </c>
       <c r="C11" s="175">
         <f ca="1">Statement!AC157</f>
-        <v>19.337634274984122</v>
+        <v>19.916756216197026</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -31472,18 +32409,18 @@
       </c>
       <c r="C12" s="175">
         <f ca="1">Statement!AC158</f>
-        <v>30.205602797547524</v>
+        <v>31.110197800166375</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="234" t="s">
+      <c r="B15" s="235" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="234"/>
-      <c r="E15" s="234" t="s">
+      <c r="C15" s="235"/>
+      <c r="E15" s="235" t="s">
         <v>243</v>
       </c>
-      <c r="F15" s="234"/>
+      <c r="F15" s="235"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -31534,14 +32471,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="234" t="s">
+      <c r="B21" s="235" t="s">
         <v>242</v>
       </c>
-      <c r="C21" s="234"/>
-      <c r="E21" s="234" t="s">
+      <c r="C21" s="235"/>
+      <c r="E21" s="235" t="s">
         <v>246</v>
       </c>
-      <c r="F21" s="234"/>
+      <c r="F21" s="235"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -31610,14 +32547,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="234" t="s">
+      <c r="B29" s="235" t="s">
         <v>247</v>
       </c>
-      <c r="C29" s="234"/>
-      <c r="E29" s="234" t="s">
+      <c r="C29" s="235"/>
+      <c r="E29" s="235" t="s">
         <v>253</v>
       </c>
-      <c r="F29" s="234"/>
+      <c r="F29" s="235"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -31693,14 +32630,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="234" t="s">
+      <c r="B37" s="235" t="s">
         <v>265</v>
       </c>
-      <c r="C37" s="234"/>
-      <c r="E37" s="234" t="s">
+      <c r="C37" s="235"/>
+      <c r="E37" s="235" t="s">
         <v>268</v>
       </c>
-      <c r="F37" s="234"/>
+      <c r="F37" s="235"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -31708,7 +32645,7 @@
       </c>
       <c r="C38" s="176">
         <f ca="1">Statement!AC164</f>
-        <v>3.1908135841680917E-2</v>
+        <v>3.0993402629455595E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>267</v>
@@ -31724,7 +32661,7 @@
       </c>
       <c r="C39" s="216">
         <f ca="1">Statement!AC163</f>
-        <v>2.2564653838976163E-2</v>
+        <v>2.1917776867181507E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>269</v>
@@ -31740,7 +32677,7 @@
       </c>
       <c r="C40" s="176">
         <f ca="1">Statement!AC165</f>
-        <v>1.9545565599804544E-4</v>
+        <v>1.8985238976695619E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>270</v>
@@ -31756,7 +32693,7 @@
       </c>
       <c r="C41" s="176">
         <f ca="1">Statement!AC166</f>
-        <v>9.108129026265635E-3</v>
+        <v>8.8470198169123462E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -31765,18 +32702,18 @@
       </c>
       <c r="C42" s="176">
         <f ca="1">Statement!AC167</f>
-        <v>9.3037455180225766E-3</v>
+        <v>9.0370284316451666E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="234" t="s">
+      <c r="B45" s="235" t="s">
         <v>276</v>
       </c>
-      <c r="C45" s="234"/>
-      <c r="E45" s="234" t="s">
+      <c r="C45" s="235"/>
+      <c r="E45" s="235" t="s">
         <v>282</v>
       </c>
-      <c r="F45" s="234"/>
+      <c r="F45" s="235"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -31809,18 +32746,18 @@
       </c>
       <c r="F48" s="176">
         <f ca="1">Statement!AC178</f>
-        <v>1.4495724859875615E-2</v>
+        <v>1.4080165610961813E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="234" t="s">
+      <c r="B51" s="235" t="s">
         <v>279</v>
       </c>
-      <c r="C51" s="234"/>
-      <c r="E51" s="234" t="s">
+      <c r="C51" s="235"/>
+      <c r="E51" s="235" t="s">
         <v>300</v>
       </c>
-      <c r="F51" s="234"/>
+      <c r="F51" s="235"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -31989,7 +32926,7 @@
       </c>
       <c r="I6" s="173">
         <f ca="1">Statement!AC114</f>
-        <v>204.65</v>
+        <v>210.69</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -32018,7 +32955,7 @@
       </c>
       <c r="I7" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>4974018.25</v>
+        <v>5120820.45</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -32047,7 +32984,7 @@
       </c>
       <c r="I8" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>4901916.25</v>
+        <v>5048718.45</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -32076,7 +33013,7 @@
       </c>
       <c r="I9" s="175">
         <f ca="1">Statement!AC152</f>
-        <v>31.339969372128643</v>
+        <v>32.264931087289433</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -32105,7 +33042,7 @@
       </c>
       <c r="I10" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>19.746802351957271</v>
+        <v>20.329605607299669</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -32134,7 +33071,7 @@
       </c>
       <c r="I11" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>25.33600376520663</v>
+        <v>26.083765615887536</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -32163,7 +33100,7 @@
       </c>
       <c r="I12" s="175">
         <f ca="1">Statement!AC157</f>
-        <v>19.337634274984122</v>
+        <v>19.916756216197026</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -32192,7 +33129,7 @@
       </c>
       <c r="I13" s="175">
         <f ca="1">Statement!AC158</f>
-        <v>30.205602797547524</v>
+        <v>31.110197800166375</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -32965,7 +33902,7 @@
       </c>
       <c r="I51" s="176">
         <f ca="1">Statement!AC164</f>
-        <v>3.1908135841680917E-2</v>
+        <v>3.0993402629455595E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -32994,7 +33931,7 @@
       </c>
       <c r="I52" s="176">
         <f ca="1">Statement!AC163</f>
-        <v>2.2564653838976163E-2</v>
+        <v>2.1917776867181507E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -33023,7 +33960,7 @@
       </c>
       <c r="I53" s="176">
         <f ca="1">Statement!AC165</f>
-        <v>1.9545565599804544E-4</v>
+        <v>1.8985238976695619E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -33052,7 +33989,7 @@
       </c>
       <c r="I54" s="176">
         <f ca="1">Statement!AC166</f>
-        <v>9.108129026265635E-3</v>
+        <v>8.8470198169123462E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -33081,7 +34018,7 @@
       </c>
       <c r="I55" s="176">
         <f ca="1">Statement!AC167</f>
-        <v>9.3037455180225766E-3</v>
+        <v>9.0370284316451666E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -33317,7 +34254,7 @@
       </c>
       <c r="I68" s="197">
         <f ca="1">Statement!AC178</f>
-        <v>1.4495724859875615E-2</v>
+        <v>1.4080165610961813E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -33829,14 +34766,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="237" t="s">
+      <c r="C3" s="238" t="s">
         <v>310</v>
       </c>
-      <c r="D3" s="238"/>
-      <c r="F3" s="239" t="s">
+      <c r="D3" s="239"/>
+      <c r="F3" s="240" t="s">
         <v>311</v>
       </c>
-      <c r="G3" s="238"/>
+      <c r="G3" s="239"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -33903,19 +34840,19 @@
       <c r="B7" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C7" s="235">
+      <c r="C7" s="236">
         <f>Statement!AA88</f>
         <v>0.19798317847549429</v>
       </c>
-      <c r="D7" s="236"/>
-      <c r="F7" s="235">
+      <c r="D7" s="237"/>
+      <c r="F7" s="236">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.85227633788752211</v>
       </c>
-      <c r="G7" s="236"/>
+      <c r="G7" s="237"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="208" t="s">
@@ -33942,19 +34879,19 @@
       <c r="B9" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C9" s="235">
+      <c r="C9" s="236">
         <f>Statement!AA89</f>
         <v>0.20100974521545145</v>
       </c>
-      <c r="D9" s="236"/>
-      <c r="F9" s="235">
+      <c r="D9" s="237"/>
+      <c r="F9" s="236">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.17615269633206854</v>
       </c>
-      <c r="G9" s="236"/>
+      <c r="G9" s="237"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="208" t="s">
@@ -33981,19 +34918,19 @@
       <c r="B11" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C11" s="235">
+      <c r="C11" s="236">
         <f>Statement!AA90</f>
         <v>0.19697414518622902</v>
       </c>
-      <c r="D11" s="236"/>
-      <c r="F11" s="235">
+      <c r="D11" s="237"/>
+      <c r="F11" s="236">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.293272836358182</v>
       </c>
-      <c r="G11" s="236"/>
+      <c r="G11" s="237"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="208" t="s">
@@ -34020,19 +34957,19 @@
       <c r="B13" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C13" s="235">
+      <c r="C13" s="236">
         <f>Statement!AA93</f>
         <v>0.12172505151604357</v>
       </c>
-      <c r="D13" s="236"/>
-      <c r="F13" s="235">
+      <c r="D13" s="237"/>
+      <c r="F13" s="236">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.51510934393638175</v>
       </c>
-      <c r="G13" s="236"/>
+      <c r="G13" s="237"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="208" t="s">
@@ -34059,19 +34996,19 @@
       <c r="B15" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C15" s="235">
+      <c r="C15" s="236">
         <f>Statement!AA94</f>
         <v>0.20851486489537011</v>
       </c>
-      <c r="D15" s="236"/>
-      <c r="F15" s="235">
+      <c r="D15" s="237"/>
+      <c r="F15" s="236">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.4741658193918108</v>
       </c>
-      <c r="G15" s="236"/>
+      <c r="G15" s="237"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="208" t="s">
@@ -34098,19 +35035,19 @@
       <c r="B17" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C17" s="235">
+      <c r="C17" s="236">
         <f>Statement!AA96</f>
         <v>0.35756517690875234</v>
       </c>
-      <c r="D17" s="236"/>
-      <c r="F17" s="235">
+      <c r="D17" s="237"/>
+      <c r="F17" s="236">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>2.1063115845539282</v>
       </c>
-      <c r="G17" s="236"/>
+      <c r="G17" s="237"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="208" t="s">
@@ -34137,22 +35074,22 @@
       <c r="B19" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C19" s="235">
+      <c r="C19" s="236">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-1.6781270464963983E-3</v>
       </c>
-      <c r="D19" s="236"/>
-      <c r="F19" s="235">
+      <c r="D19" s="237"/>
+      <c r="F19" s="236">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-8.9390922758116297E-3</v>
       </c>
-      <c r="G19" s="236"/>
+      <c r="G19" s="237"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="208" t="s">
@@ -34179,22 +35116,22 @@
       <c r="B21" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C21" s="235">
+      <c r="C21" s="236">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.35795454545454553</v>
       </c>
-      <c r="D21" s="236"/>
-      <c r="F21" s="235">
+      <c r="D21" s="237"/>
+      <c r="F21" s="236">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>2.1447368421052633</v>
       </c>
-      <c r="G21" s="236"/>
+      <c r="G21" s="237"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -34242,22 +35179,22 @@
       <c r="B25" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C25" s="235">
+      <c r="C25" s="236">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.11992074288756137</v>
       </c>
-      <c r="D25" s="236"/>
-      <c r="F25" s="235">
+      <c r="D25" s="237"/>
+      <c r="F25" s="236">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>1.1517699869310756</v>
       </c>
-      <c r="G25" s="236"/>
+      <c r="G25" s="237"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="224" t="s">
@@ -34284,22 +35221,22 @@
       <c r="B27" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C27" s="235">
+      <c r="C27" s="236">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.31147368421052629</v>
       </c>
-      <c r="D27" s="236"/>
-      <c r="F27" s="235">
+      <c r="D27" s="237"/>
+      <c r="F27" s="236">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.73741458652907543</v>
       </c>
-      <c r="G27" s="236"/>
+      <c r="G27" s="237"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -34326,22 +35263,22 @@
       <c r="B29" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C29" s="235">
+      <c r="C29" s="236">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.20752960811374652</v>
       </c>
-      <c r="D29" s="236"/>
-      <c r="F29" s="235">
+      <c r="D29" s="237"/>
+      <c r="F29" s="236">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.92385968500715898</v>
       </c>
-      <c r="G29" s="236"/>
+      <c r="G29" s="237"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -34368,22 +35305,22 @@
       <c r="B31" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C31" s="235">
+      <c r="C31" s="236">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>9.5647686220540165E-2</v>
       </c>
-      <c r="D31" s="236"/>
-      <c r="F31" s="235">
+      <c r="D31" s="237"/>
+      <c r="F31" s="236">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.28666666666666668</v>
       </c>
-      <c r="G31" s="236"/>
+      <c r="G31" s="237"/>
     </row>
   </sheetData>
   <mergeCells count="26">
@@ -34423,7 +35360,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E59D4CD5-3D15-DF4B-A135-ED758F2E1A8D}">
-  <dimension ref="B55:L70"/>
+  <dimension ref="B55:L73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -35145,6 +36082,141 @@
       <c r="L70" s="219">
         <f>Statement!Q142</f>
         <v>1.0723937210768841</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B71" s="20" t="s">
+        <v>391</v>
+      </c>
+      <c r="C71" s="231">
+        <f>Statement!H207</f>
+        <v>0</v>
+      </c>
+      <c r="D71" s="231">
+        <f>Statement!I207</f>
+        <v>0</v>
+      </c>
+      <c r="E71" s="231">
+        <f>Statement!J207</f>
+        <v>0</v>
+      </c>
+      <c r="F71" s="231">
+        <f>Statement!K207</f>
+        <v>0</v>
+      </c>
+      <c r="G71" s="231">
+        <f>Statement!L207</f>
+        <v>0</v>
+      </c>
+      <c r="H71" s="231">
+        <f>Statement!M207</f>
+        <v>100</v>
+      </c>
+      <c r="I71" s="231">
+        <f>Statement!N207</f>
+        <v>89.141856392294216</v>
+      </c>
+      <c r="J71" s="231">
+        <f>Statement!O207</f>
+        <v>267.20665499124345</v>
+      </c>
+      <c r="K71" s="231">
+        <f>Statement!P207</f>
+        <v>624.43082311733804</v>
+      </c>
+      <c r="L71" s="231">
+        <f>Statement!Q207</f>
+        <v>821.67250437828375</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B72" s="20" t="s">
+        <v>392</v>
+      </c>
+      <c r="C72" s="231">
+        <f>Statement!H208</f>
+        <v>0</v>
+      </c>
+      <c r="D72" s="231">
+        <f>Statement!I208</f>
+        <v>0</v>
+      </c>
+      <c r="E72" s="231">
+        <f>Statement!J208</f>
+        <v>0</v>
+      </c>
+      <c r="F72" s="231">
+        <f>Statement!K208</f>
+        <v>0</v>
+      </c>
+      <c r="G72" s="231">
+        <f>Statement!L208</f>
+        <v>0</v>
+      </c>
+      <c r="H72" s="231">
+        <f>Statement!M208</f>
+        <v>100</v>
+      </c>
+      <c r="I72" s="231">
+        <f>Statement!N208</f>
+        <v>100.2229323028907</v>
+      </c>
+      <c r="J72" s="231">
+        <f>Statement!O208</f>
+        <v>226.35802927844244</v>
+      </c>
+      <c r="K72" s="231">
+        <f>Statement!P208</f>
+        <v>484.86661217210371</v>
+      </c>
+      <c r="L72" s="231">
+        <f>Statement!Q208</f>
+        <v>802.32592702682621</v>
+      </c>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B73" s="20" t="s">
+        <v>393</v>
+      </c>
+      <c r="C73" s="231">
+        <f>Statement!H209</f>
+        <v>0</v>
+      </c>
+      <c r="D73" s="231">
+        <f>Statement!I209</f>
+        <v>0</v>
+      </c>
+      <c r="E73" s="231">
+        <f>Statement!J209</f>
+        <v>0</v>
+      </c>
+      <c r="F73" s="231">
+        <f>Statement!K209</f>
+        <v>0</v>
+      </c>
+      <c r="G73" s="231">
+        <f>Statement!L209</f>
+        <v>0</v>
+      </c>
+      <c r="H73" s="231">
+        <f>Statement!M209</f>
+        <v>100</v>
+      </c>
+      <c r="I73" s="231">
+        <f>Statement!N209</f>
+        <v>45.194805194805184</v>
+      </c>
+      <c r="J73" s="231">
+        <f>Statement!O209</f>
+        <v>309.87012987012992</v>
+      </c>
+      <c r="K73" s="231">
+        <f>Statement!P209</f>
+        <v>763.63636363636363</v>
+      </c>
+      <c r="L73" s="231">
+        <f>Statement!Q209</f>
+        <v>1272.7272727272727</v>
       </c>
     </row>
   </sheetData>

--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAAE61A3-CD28-AB45-87F2-3A5E8D6EE94B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD7E46E1-F746-BF43-B2DD-6B4DBF842FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -4258,43 +4258,11 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
+        <c:delete val="1"/>
         <c:axPos val="b"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:lumMod val="95000"/>
-                <a:alpha val="54000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="85000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
         <c:crossAx val="57930431"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
@@ -6496,43 +6464,11 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
+        <c:delete val="1"/>
         <c:axPos val="b"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:lumMod val="95000"/>
-                <a:alpha val="54000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="85000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
         <c:crossAx val="1156723391"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
@@ -12633,12 +12569,12 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>236.54</v>
-    <v>142.03</v>
-    <v>2.2023999999999999</v>
-    <v>6.04</v>
-    <v>2.9513999999999999E-2</v>
-    <v>-0.38500000000000001</v>
-    <v>-1.8270000000000001E-3</v>
+    <v>149.26</v>
+    <v>2.2078000000000002</v>
+    <v>-3.26</v>
+    <v>-1.6382000000000001E-2</v>
+    <v>-0.23</v>
+    <v>-1.1749999999999998E-3</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -12646,25 +12582,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2788 San Tomas Expressway, SANTA CLARA, CA, 95051 US</v>
-    <v>211.39</v>
+    <v>200.8</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46191.999989178126</v>
+    <v>46198.912182881249</v>
     <v>0</v>
-    <v>206.5</v>
-    <v>5098698000000</v>
+    <v>192.13</v>
+    <v>4736908000000</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
-    <v>207.33</v>
-    <v>31.3401</v>
-    <v>204.65</v>
-    <v>210.69</v>
-    <v>210.30500000000001</v>
+    <v>200.08</v>
+    <v>29.9755</v>
+    <v>199</v>
+    <v>195.74</v>
+    <v>195.51</v>
     <v>24200000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>241272013</v>
-    <v>170253095</v>
+    <v>149444373</v>
+    <v>170660038</v>
     <v>1998</v>
   </rv>
   <rv s="2">
@@ -12688,17 +12624,17 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.12</v>
-    <v>-2.6889999999999996E-3</v>
+    <v>-0.1</v>
+    <v>-2.2720000000000001E-3</v>
     <v>US</v>
-    <v>44.53</v>
+    <v>44.14</v>
     <v>Index</v>
     <v>3</v>
-    <v>44.2</v>
+    <v>43.63</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>44.53</v>
-    <v>44.63</v>
-    <v>44.51</v>
+    <v>44.12</v>
+    <v>44.02</v>
+    <v>43.92</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -12920,9 +12856,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13519,7 +13455,7 @@
       </c>
       <c r="F3" s="188">
         <f ca="1">Statement!AC155</f>
-        <v>5120820.45</v>
+        <v>4757460.7</v>
       </c>
       <c r="H3" s="186" t="str">
         <f>'AVG target price'!B5</f>
@@ -13543,7 +13479,7 @@
       </c>
       <c r="F4" s="189">
         <f ca="1">Statement!AC156</f>
-        <v>5048718.45</v>
+        <v>4685358.7</v>
       </c>
       <c r="H4" s="186" t="str">
         <f>'AVG target price'!B6</f>
@@ -13560,7 +13496,7 @@
       </c>
       <c r="C5" s="209" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>210.69</v>
+        <v>195.74</v>
       </c>
       <c r="E5" s="186" t="s">
         <v>240</v>
@@ -13584,14 +13520,14 @@
       </c>
       <c r="C6" s="209" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>210.30500000000001</v>
+        <v>195.51</v>
       </c>
       <c r="E6" s="186" t="s">
         <v>234</v>
       </c>
       <c r="F6" s="191">
         <f ca="1">Statement!AC152</f>
-        <v>32.264931087289433</v>
+        <v>29.975497702909653</v>
       </c>
       <c r="H6" s="186" t="str">
         <f>'AVG target price'!B8</f>
@@ -13608,14 +13544,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>6.04</v>
+        <v>-3.26</v>
       </c>
       <c r="E7" s="187" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="192">
         <f ca="1">Statement!AC153</f>
-        <v>20.329605607299669</v>
+        <v>18.887071059722043</v>
       </c>
       <c r="H7" s="185" t="str">
         <f>'AVG target price'!B9</f>
@@ -13632,14 +13568,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.38500000000000001</v>
+        <v>-0.23</v>
       </c>
       <c r="E8" s="186" t="s">
         <v>262</v>
       </c>
       <c r="F8" s="193">
         <f ca="1">Statement!AC163</f>
-        <v>2.1917776867181507E-2</v>
+        <v>2.3591787106092121E-2</v>
       </c>
       <c r="H8" s="185" t="str">
         <f>'AVG target price'!B11</f>
@@ -13647,7 +13583,7 @@
       </c>
       <c r="I8" s="214">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.40848142595564563</v>
+        <v>0.51605676731682315</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13656,14 +13592,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>2.9513999999999999E-2</v>
+        <v>-1.6382000000000001E-2</v>
       </c>
       <c r="E9" s="186" t="s">
         <v>285</v>
       </c>
       <c r="F9" s="193">
         <f ca="1">Statement!AC164</f>
-        <v>3.0993402629455595E-2</v>
+        <v>3.3360580361704299E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13672,14 +13608,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.8270000000000001E-3</v>
+        <v>-1.1749999999999998E-3</v>
       </c>
       <c r="E10" s="186" t="s">
         <v>290</v>
       </c>
       <c r="F10" s="193">
         <f ca="1">Statement!AC166</f>
-        <v>8.8470198169123462E-3</v>
+        <v>9.5227271136469928E-3</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13695,7 +13631,7 @@
       </c>
       <c r="F11" s="194">
         <f ca="1">Statement!AC165</f>
-        <v>1.8985238976695619E-4</v>
+        <v>2.0435271278226218E-4</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13704,7 +13640,7 @@
       </c>
       <c r="C12" s="210" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>142.03</v>
+        <v>149.26</v>
       </c>
       <c r="E12" s="186" t="s">
         <v>94</v>
@@ -13720,7 +13656,7 @@
       </c>
       <c r="C13" s="210" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.2023999999999999</v>
+        <v>2.2078000000000002</v>
       </c>
       <c r="E13" s="186" t="s">
         <v>96</v>
@@ -13736,7 +13672,7 @@
       </c>
       <c r="C14" s="211" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>170253095</v>
+        <v>170660038</v>
       </c>
       <c r="E14" s="187" t="s">
         <v>97</v>
@@ -13752,7 +13688,7 @@
       </c>
       <c r="F15" s="193">
         <f ca="1">Statement!AC178</f>
-        <v>1.4080165610961813E-2</v>
+        <v>1.5155563975546871E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13862,7 +13798,7 @@
       </c>
       <c r="F26" s="220" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>44.51</v>
+        <v>43.92</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13877,7 +13813,7 @@
       </c>
       <c r="F27" s="221">
         <f ca="1">F26/1000</f>
-        <v>4.4510000000000001E-2</v>
+        <v>4.3920000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -19133,7 +19069,7 @@
       </c>
       <c r="C6" s="134">
         <f ca="1">Overview!C5</f>
-        <v>210.69</v>
+        <v>195.74</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19142,7 +19078,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">C5*C6</f>
-        <v>5120820.45</v>
+        <v>4757460.7</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19160,7 +19096,7 @@
       </c>
       <c r="C9" s="136">
         <f ca="1">Overview!F27</f>
-        <v>4.4510000000000001E-2</v>
+        <v>4.3920000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19169,7 +19105,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C13</f>
-        <v>2.2023999999999999</v>
+        <v>2.2078000000000002</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19212,7 +19148,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>1.65130052247285E-3</v>
+        <v>1.7771974737274296E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19221,7 +19157,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99834869947752714</v>
+        <v>0.9982228025262726</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19239,7 +19175,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.143618</v>
+        <v>0.14327100000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19248,7 +19184,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14344737441961392</v>
+        <v>0.14308798242695808</v>
       </c>
     </row>
   </sheetData>
@@ -20978,7 +20914,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C5</f>
-        <v>210.69</v>
+        <v>195.74</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -20987,7 +20923,7 @@
       </c>
       <c r="C11" s="155">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.40848142595564563</v>
+        <v>0.51605676731682315</v>
       </c>
     </row>
   </sheetData>
@@ -21345,7 +21281,7 @@
       </c>
       <c r="C15" s="157">
         <f ca="1">Overview!C5</f>
-        <v>210.69</v>
+        <v>195.74</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -21411,7 +21347,7 @@
       </c>
       <c r="C23" s="162">
         <f ca="1">C15*C22</f>
-        <v>5098698</v>
+        <v>4736908</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -21438,7 +21374,7 @@
       </c>
       <c r="C26" s="163">
         <f ca="1">C23+C25-C24</f>
-        <v>5026596</v>
+        <v>4664806</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -28472,7 +28408,7 @@
       <c r="AA114" s="68"/>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>210.69</v>
+        <v>195.74</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -28519,7 +28455,7 @@
       <c r="AA115" s="68"/>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>210.69</v>
+        <v>195.74</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30021,7 +29957,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>32.264931087289433</v>
+        <v>29.975497702909653</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -30058,7 +29994,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>20.329605607299669</v>
+        <v>18.887071059722043</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30095,7 +30031,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>26.083765615887536</v>
+        <v>24.232931233821382</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30132,7 +30068,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="144">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>5120820.45</v>
+        <v>4757460.7</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30169,7 +30105,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="144">
         <f ca="1">AC155+AC106-AC105+AC47+AC44</f>
-        <v>5048718.45</v>
+        <v>4685358.7</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -30206,7 +30142,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="184">
         <f ca="1">AC156/AC5</f>
-        <v>19.916756216197026</v>
+        <v>18.483333530578996</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -30243,7 +30179,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="184">
         <f ca="1">AC156/AC11</f>
-        <v>31.110197800166375</v>
+        <v>28.871175401300182</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -30378,7 +30314,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="72">
         <f t="shared" ref="AC161:AC162" ca="1" si="96">AC155/AC159</f>
-        <v>45.625065263683098</v>
+        <v>42.387632420681236</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -30415,7 +30351,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ca="1" si="96"/>
-        <v>39.811347892684566</v>
+        <v>36.946097718662905</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -30452,7 +30388,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="74">
         <f t="shared" ref="AC163" ca="1" si="99">AC159/AC155</f>
-        <v>2.1917776867181507E-2</v>
+        <v>2.3591787106092121E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -30489,7 +30425,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>3.0993402629455595E-2</v>
+        <v>3.3360580361704299E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -30526,7 +30462,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="155">
         <f ca="1">AC81/AC115</f>
-        <v>1.8985238976695619E-4</v>
+        <v>2.0435271278226218E-4</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -30563,7 +30499,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="155">
         <f ca="1">-AC62/AC155</f>
-        <v>8.8470198169123462E-3</v>
+        <v>9.5227271136469928E-3</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -30600,7 +30536,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="155">
         <f ca="1">-(AC62+AC63)/AC155</f>
-        <v>9.0370284316451666E-3</v>
+        <v>9.7272479833622159E-3</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31103,7 +31039,7 @@
       <c r="AA178" s="49"/>
       <c r="AC178" s="155">
         <f ca="1">(AC105-AC106)/AC155</f>
-        <v>1.4080165610961813E-2</v>
+        <v>1.5155563975546871E-2</v>
       </c>
     </row>
     <row r="179" spans="1:31" x14ac:dyDescent="0.2">
@@ -32284,7 +32220,7 @@
       </c>
       <c r="C5" s="173">
         <f ca="1">Overview!C5</f>
-        <v>210.69</v>
+        <v>195.74</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="133" t="s">
@@ -32300,7 +32236,7 @@
       </c>
       <c r="C6" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>5120820.45</v>
+        <v>4757460.7</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -32320,7 +32256,7 @@
       </c>
       <c r="C7" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>5048718.45</v>
+        <v>4685358.7</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -32340,7 +32276,7 @@
       </c>
       <c r="C8" s="175">
         <f ca="1">Statement!AC152</f>
-        <v>32.264931087289433</v>
+        <v>29.975497702909653</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>240</v>
@@ -32360,7 +32296,7 @@
       </c>
       <c r="C9" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>20.329605607299669</v>
+        <v>18.887071059722043</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>241</v>
@@ -32380,7 +32316,7 @@
       </c>
       <c r="C10" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>26.083765615887536</v>
+        <v>24.232931233821382</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -32400,7 +32336,7 @@
       </c>
       <c r="C11" s="175">
         <f ca="1">Statement!AC157</f>
-        <v>19.916756216197026</v>
+        <v>18.483333530578996</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -32409,7 +32345,7 @@
       </c>
       <c r="C12" s="175">
         <f ca="1">Statement!AC158</f>
-        <v>31.110197800166375</v>
+        <v>28.871175401300182</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -32645,7 +32581,7 @@
       </c>
       <c r="C38" s="176">
         <f ca="1">Statement!AC164</f>
-        <v>3.0993402629455595E-2</v>
+        <v>3.3360580361704299E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>267</v>
@@ -32661,7 +32597,7 @@
       </c>
       <c r="C39" s="216">
         <f ca="1">Statement!AC163</f>
-        <v>2.1917776867181507E-2</v>
+        <v>2.3591787106092121E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>269</v>
@@ -32677,7 +32613,7 @@
       </c>
       <c r="C40" s="176">
         <f ca="1">Statement!AC165</f>
-        <v>1.8985238976695619E-4</v>
+        <v>2.0435271278226218E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>270</v>
@@ -32693,7 +32629,7 @@
       </c>
       <c r="C41" s="176">
         <f ca="1">Statement!AC166</f>
-        <v>8.8470198169123462E-3</v>
+        <v>9.5227271136469928E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -32702,7 +32638,7 @@
       </c>
       <c r="C42" s="176">
         <f ca="1">Statement!AC167</f>
-        <v>9.0370284316451666E-3</v>
+        <v>9.7272479833622159E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -32746,7 +32682,7 @@
       </c>
       <c r="F48" s="176">
         <f ca="1">Statement!AC178</f>
-        <v>1.4080165610961813E-2</v>
+        <v>1.5155563975546871E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -32926,7 +32862,7 @@
       </c>
       <c r="I6" s="173">
         <f ca="1">Statement!AC114</f>
-        <v>210.69</v>
+        <v>195.74</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -32955,7 +32891,7 @@
       </c>
       <c r="I7" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>5120820.45</v>
+        <v>4757460.7</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -32984,7 +32920,7 @@
       </c>
       <c r="I8" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>5048718.45</v>
+        <v>4685358.7</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33013,7 +32949,7 @@
       </c>
       <c r="I9" s="175">
         <f ca="1">Statement!AC152</f>
-        <v>32.264931087289433</v>
+        <v>29.975497702909653</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33042,7 +32978,7 @@
       </c>
       <c r="I10" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>20.329605607299669</v>
+        <v>18.887071059722043</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33071,7 +33007,7 @@
       </c>
       <c r="I11" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>26.083765615887536</v>
+        <v>24.232931233821382</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33100,7 +33036,7 @@
       </c>
       <c r="I12" s="175">
         <f ca="1">Statement!AC157</f>
-        <v>19.916756216197026</v>
+        <v>18.483333530578996</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33129,7 +33065,7 @@
       </c>
       <c r="I13" s="175">
         <f ca="1">Statement!AC158</f>
-        <v>31.110197800166375</v>
+        <v>28.871175401300182</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -33902,7 +33838,7 @@
       </c>
       <c r="I51" s="176">
         <f ca="1">Statement!AC164</f>
-        <v>3.0993402629455595E-2</v>
+        <v>3.3360580361704299E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -33931,7 +33867,7 @@
       </c>
       <c r="I52" s="176">
         <f ca="1">Statement!AC163</f>
-        <v>2.1917776867181507E-2</v>
+        <v>2.3591787106092121E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -33960,7 +33896,7 @@
       </c>
       <c r="I53" s="176">
         <f ca="1">Statement!AC165</f>
-        <v>1.8985238976695619E-4</v>
+        <v>2.0435271278226218E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -33989,7 +33925,7 @@
       </c>
       <c r="I54" s="176">
         <f ca="1">Statement!AC166</f>
-        <v>8.8470198169123462E-3</v>
+        <v>9.5227271136469928E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34018,7 +33954,7 @@
       </c>
       <c r="I55" s="176">
         <f ca="1">Statement!AC167</f>
-        <v>9.0370284316451666E-3</v>
+        <v>9.7272479833622159E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34254,7 +34190,7 @@
       </c>
       <c r="I68" s="197">
         <f ca="1">Statement!AC178</f>
-        <v>1.4080165610961813E-2</v>
+        <v>1.5155563975546871E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">

--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD7E46E1-F746-BF43-B2DD-6B4DBF842FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{273E88C5-7449-0446-9008-592BD9067F14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2261,6 +2261,9 @@
     </xf>
     <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2270,15 +2273,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2286,6 +2280,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12569,12 +12569,12 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>236.54</v>
-    <v>149.26</v>
-    <v>2.2078000000000002</v>
-    <v>-3.26</v>
-    <v>-1.6382000000000001E-2</v>
-    <v>-0.23</v>
-    <v>-1.1749999999999998E-3</v>
+    <v>151.49</v>
+    <v>2.2160000000000002</v>
+    <v>5.12</v>
+    <v>2.6259999999999999E-2</v>
+    <v>-0.84</v>
+    <v>-4.1980000000000003E-3</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -12582,25 +12582,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2788 San Tomas Expressway, SANTA CLARA, CA, 95051 US</v>
-    <v>200.8</v>
+    <v>200.63</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46198.912182881249</v>
+    <v>46203.950696596876</v>
     <v>0</v>
-    <v>192.13</v>
-    <v>4736908000000</v>
+    <v>195.11</v>
+    <v>4842178000000</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
-    <v>200.08</v>
-    <v>29.9755</v>
-    <v>199</v>
-    <v>195.74</v>
-    <v>195.51</v>
+    <v>197.24</v>
+    <v>30.6417</v>
+    <v>194.97</v>
+    <v>200.09</v>
+    <v>199.25</v>
     <v>24200000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>149444373</v>
-    <v>170660038</v>
+    <v>166082238</v>
+    <v>168652596</v>
     <v>1998</v>
   </rv>
   <rv s="2">
@@ -12624,17 +12624,17 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.1</v>
-    <v>-2.2720000000000001E-3</v>
+    <v>0.02</v>
+    <v>4.5750000000000001E-4</v>
     <v>US</v>
-    <v>44.14</v>
+    <v>43.9</v>
     <v>Index</v>
     <v>3</v>
-    <v>43.63</v>
+    <v>43.67</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>44.12</v>
-    <v>44.02</v>
-    <v>43.92</v>
+    <v>43.78</v>
+    <v>43.72</v>
+    <v>43.74</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13429,18 +13429,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="232" t="s">
+      <c r="B2" s="233" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="233"/>
-      <c r="E2" s="232" t="s">
+      <c r="C2" s="234"/>
+      <c r="E2" s="233" t="s">
         <v>284</v>
       </c>
-      <c r="F2" s="233"/>
-      <c r="H2" s="232" t="s">
+      <c r="F2" s="234"/>
+      <c r="H2" s="233" t="s">
         <v>325</v>
       </c>
-      <c r="I2" s="233"/>
+      <c r="I2" s="234"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="186" t="s">
@@ -13455,7 +13455,7 @@
       </c>
       <c r="F3" s="188">
         <f ca="1">Statement!AC155</f>
-        <v>4757460.7</v>
+        <v>4863187.45</v>
       </c>
       <c r="H3" s="186" t="str">
         <f>'AVG target price'!B5</f>
@@ -13479,7 +13479,7 @@
       </c>
       <c r="F4" s="189">
         <f ca="1">Statement!AC156</f>
-        <v>4685358.7</v>
+        <v>4791085.45</v>
       </c>
       <c r="H4" s="186" t="str">
         <f>'AVG target price'!B6</f>
@@ -13496,7 +13496,7 @@
       </c>
       <c r="C5" s="209" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>195.74</v>
+        <v>200.09</v>
       </c>
       <c r="E5" s="186" t="s">
         <v>240</v>
@@ -13520,14 +13520,14 @@
       </c>
       <c r="C6" s="209" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>195.51</v>
+        <v>199.25</v>
       </c>
       <c r="E6" s="186" t="s">
         <v>234</v>
       </c>
       <c r="F6" s="191">
         <f ca="1">Statement!AC152</f>
-        <v>29.975497702909653</v>
+        <v>30.641653905053602</v>
       </c>
       <c r="H6" s="186" t="str">
         <f>'AVG target price'!B8</f>
@@ -13544,14 +13544,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-3.26</v>
+        <v>5.12</v>
       </c>
       <c r="E7" s="187" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="192">
         <f ca="1">Statement!AC153</f>
-        <v>18.887071059722043</v>
+        <v>19.306805192294796</v>
       </c>
       <c r="H7" s="185" t="str">
         <f>'AVG target price'!B9</f>
@@ -13568,14 +13568,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.23</v>
+        <v>-0.84</v>
       </c>
       <c r="E8" s="186" t="s">
         <v>262</v>
       </c>
       <c r="F8" s="193">
         <f ca="1">Statement!AC163</f>
-        <v>2.3591787106092121E-2</v>
+        <v>2.3078896537290578E-2</v>
       </c>
       <c r="H8" s="185" t="str">
         <f>'AVG target price'!B11</f>
@@ -13583,7 +13583,7 @@
       </c>
       <c r="I8" s="214">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.51605676731682315</v>
+        <v>0.48309736435901329</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13592,14 +13592,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-1.6382000000000001E-2</v>
+        <v>2.6259999999999999E-2</v>
       </c>
       <c r="E9" s="186" t="s">
         <v>285</v>
       </c>
       <c r="F9" s="193">
         <f ca="1">Statement!AC164</f>
-        <v>3.3360580361704299E-2</v>
+        <v>3.2635314108651101E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13608,14 +13608,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.1749999999999998E-3</v>
+        <v>-4.1980000000000003E-3</v>
       </c>
       <c r="E10" s="186" t="s">
         <v>290</v>
       </c>
       <c r="F10" s="193">
         <f ca="1">Statement!AC166</f>
-        <v>9.5227271136469928E-3</v>
+        <v>9.315700960693998E-3</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13631,7 +13631,7 @@
       </c>
       <c r="F11" s="194">
         <f ca="1">Statement!AC165</f>
-        <v>2.0435271278226218E-4</v>
+        <v>1.9991004048178321E-4</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13640,7 +13640,7 @@
       </c>
       <c r="C12" s="210" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>149.26</v>
+        <v>151.49</v>
       </c>
       <c r="E12" s="186" t="s">
         <v>94</v>
@@ -13656,7 +13656,7 @@
       </c>
       <c r="C13" s="210" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.2078000000000002</v>
+        <v>2.2160000000000002</v>
       </c>
       <c r="E13" s="186" t="s">
         <v>96</v>
@@ -13672,7 +13672,7 @@
       </c>
       <c r="C14" s="211" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>170660038</v>
+        <v>168652596</v>
       </c>
       <c r="E14" s="187" t="s">
         <v>97</v>
@@ -13688,7 +13688,7 @@
       </c>
       <c r="F15" s="193">
         <f ca="1">Statement!AC178</f>
-        <v>1.5155563975546871E-2</v>
+        <v>1.4826078727440375E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13701,10 +13701,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="234" t="s">
+      <c r="B17" s="235" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="234"/>
+      <c r="C17" s="235"/>
       <c r="E17" s="185" t="s">
         <v>293</v>
       </c>
@@ -13777,14 +13777,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="234" t="s">
+      <c r="B25" s="235" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="234"/>
-      <c r="E25" s="232" t="s">
+      <c r="C25" s="235"/>
+      <c r="E25" s="233" t="s">
         <v>340</v>
       </c>
-      <c r="F25" s="233"/>
+      <c r="F25" s="234"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="185" t="s">
@@ -13798,7 +13798,7 @@
       </c>
       <c r="F26" s="220" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>43.92</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13813,7 +13813,7 @@
       </c>
       <c r="F27" s="221">
         <f ca="1">F26/1000</f>
-        <v>4.3920000000000001E-2</v>
+        <v>4.3740000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -13833,15 +13833,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="235" t="s">
+      <c r="B33" s="232" t="s">
         <v>335</v>
       </c>
-      <c r="C33" s="235"/>
-      <c r="D33" s="235"/>
-      <c r="E33" s="235"/>
-      <c r="F33" s="235"/>
-      <c r="G33" s="235"/>
-      <c r="H33" s="235"/>
+      <c r="C33" s="232"/>
+      <c r="D33" s="232"/>
+      <c r="E33" s="232"/>
+      <c r="F33" s="232"/>
+      <c r="G33" s="232"/>
+      <c r="H33" s="232"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -13860,24 +13860,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="235"/>
-      <c r="C39" s="235"/>
-      <c r="D39" s="235"/>
-      <c r="E39" s="235"/>
-      <c r="F39" s="235"/>
-      <c r="G39" s="235"/>
-      <c r="H39" s="235"/>
+      <c r="B39" s="232"/>
+      <c r="C39" s="232"/>
+      <c r="D39" s="232"/>
+      <c r="E39" s="232"/>
+      <c r="F39" s="232"/>
+      <c r="G39" s="232"/>
+      <c r="H39" s="232"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="235" t="s">
+      <c r="B42" s="232" t="s">
         <v>338</v>
       </c>
-      <c r="C42" s="235"/>
-      <c r="D42" s="235"/>
-      <c r="E42" s="235"/>
-      <c r="F42" s="235"/>
-      <c r="G42" s="235"/>
-      <c r="H42" s="235"/>
+      <c r="C42" s="232"/>
+      <c r="D42" s="232"/>
+      <c r="E42" s="232"/>
+      <c r="F42" s="232"/>
+      <c r="G42" s="232"/>
+      <c r="H42" s="232"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -13892,24 +13892,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="235"/>
-      <c r="C49" s="235"/>
-      <c r="D49" s="235"/>
-      <c r="E49" s="235"/>
-      <c r="F49" s="235"/>
-      <c r="G49" s="235"/>
-      <c r="H49" s="235"/>
+      <c r="B49" s="232"/>
+      <c r="C49" s="232"/>
+      <c r="D49" s="232"/>
+      <c r="E49" s="232"/>
+      <c r="F49" s="232"/>
+      <c r="G49" s="232"/>
+      <c r="H49" s="232"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="235" t="s">
+      <c r="B52" s="232" t="s">
         <v>101</v>
       </c>
-      <c r="C52" s="235"/>
-      <c r="D52" s="235"/>
-      <c r="E52" s="235"/>
-      <c r="F52" s="235"/>
-      <c r="G52" s="235"/>
-      <c r="H52" s="235"/>
+      <c r="C52" s="232"/>
+      <c r="D52" s="232"/>
+      <c r="E52" s="232"/>
+      <c r="F52" s="232"/>
+      <c r="G52" s="232"/>
+      <c r="H52" s="232"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -13924,28 +13924,28 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="235"/>
-      <c r="C59" s="235"/>
-      <c r="D59" s="235"/>
-      <c r="E59" s="235"/>
-      <c r="F59" s="235"/>
-      <c r="G59" s="235"/>
-      <c r="H59" s="235"/>
+      <c r="B59" s="232"/>
+      <c r="C59" s="232"/>
+      <c r="D59" s="232"/>
+      <c r="E59" s="232"/>
+      <c r="F59" s="232"/>
+      <c r="G59" s="232"/>
+      <c r="H59" s="232"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B52:H52"/>
     <mergeCell ref="B59:H59"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14015,36 +14015,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="232" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="235" t="s">
+      <c r="S2" s="232" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="235"/>
-      <c r="U2" s="235"/>
-      <c r="V2" s="235"/>
-      <c r="W2" s="235"/>
-      <c r="X2" s="235"/>
-      <c r="Y2" s="235"/>
-      <c r="Z2" s="235"/>
-      <c r="AA2" s="235" t="s">
+      <c r="T2" s="232"/>
+      <c r="U2" s="232"/>
+      <c r="V2" s="232"/>
+      <c r="W2" s="232"/>
+      <c r="X2" s="232"/>
+      <c r="Y2" s="232"/>
+      <c r="Z2" s="232"/>
+      <c r="AA2" s="232" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="235"/>
-      <c r="AC2" s="235"/>
+      <c r="AB2" s="232"/>
+      <c r="AC2" s="232"/>
       <c r="AE2" s="85" t="s">
         <v>107</v>
       </c>
@@ -15240,35 +15240,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="232" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
-      <c r="P2" s="235" t="s">
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
+      <c r="P2" s="232" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="235"/>
-      <c r="R2" s="235"/>
-      <c r="S2" s="235"/>
-      <c r="T2" s="235"/>
-      <c r="U2" s="235"/>
-      <c r="V2" s="235"/>
-      <c r="W2" s="235"/>
-      <c r="X2" s="235" t="s">
+      <c r="Q2" s="232"/>
+      <c r="R2" s="232"/>
+      <c r="S2" s="232"/>
+      <c r="T2" s="232"/>
+      <c r="U2" s="232"/>
+      <c r="V2" s="232"/>
+      <c r="W2" s="232"/>
+      <c r="X2" s="232" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="235"/>
-      <c r="Z2" s="235"/>
+      <c r="Y2" s="232"/>
+      <c r="Z2" s="232"/>
       <c r="AB2" s="85" t="s">
         <v>107</v>
       </c>
@@ -16499,20 +16499,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="232" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
+      <c r="D3" s="232"/>
+      <c r="E3" s="232"/>
+      <c r="F3" s="232"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="232"/>
+      <c r="J3" s="232"/>
+      <c r="K3" s="232"/>
+      <c r="L3" s="232"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -17905,12 +17905,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -17918,6 +17912,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -17955,20 +17955,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="232" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
       <c r="S2" s="246"/>
       <c r="T2" s="246"/>
       <c r="U2" s="246"/>
@@ -18977,16 +18977,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19049,10 +19049,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="232" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="235"/>
+      <c r="C4" s="232"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19069,7 +19069,7 @@
       </c>
       <c r="C6" s="134">
         <f ca="1">Overview!C5</f>
-        <v>195.74</v>
+        <v>200.09</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19078,7 +19078,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">C5*C6</f>
-        <v>4757460.7</v>
+        <v>4863187.45</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19096,7 +19096,7 @@
       </c>
       <c r="C9" s="136">
         <f ca="1">Overview!F27</f>
-        <v>4.3920000000000001E-2</v>
+        <v>4.3740000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19105,7 +19105,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C13</f>
-        <v>2.2078000000000002</v>
+        <v>2.2160000000000002</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19137,10 +19137,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="235" t="s">
+      <c r="B15" s="232" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="235"/>
+      <c r="C15" s="232"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19148,7 +19148,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>1.7771974737274296E-3</v>
+        <v>1.7386279899462142E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19157,7 +19157,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.9982228025262726</v>
+        <v>0.99826137201005383</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19175,7 +19175,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14327100000000001</v>
+        <v>0.14346</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19184,7 +19184,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14308798242695808</v>
+        <v>0.14328062575027725</v>
       </c>
     </row>
   </sheetData>
@@ -19229,20 +19229,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="232" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
+      <c r="D3" s="232"/>
+      <c r="E3" s="232"/>
+      <c r="F3" s="232"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="232"/>
+      <c r="J3" s="232"/>
+      <c r="K3" s="232"/>
+      <c r="L3" s="232"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -19528,10 +19528,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="235" t="s">
+      <c r="B13" s="232" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="235"/>
+      <c r="C13" s="232"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -19551,10 +19551,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="235" t="s">
+      <c r="B18" s="232" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="235"/>
+      <c r="C18" s="232"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -19668,20 +19668,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="232" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -20613,10 +20613,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="235" t="s">
+      <c r="B37" s="232" t="s">
         <v>197</v>
       </c>
-      <c r="C37" s="235"/>
+      <c r="C37" s="232"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -20682,10 +20682,10 @@
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="235" t="s">
+      <c r="B46" s="232" t="s">
         <v>202</v>
       </c>
-      <c r="C46" s="235"/>
+      <c r="C46" s="232"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
@@ -20741,10 +20741,10 @@
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="235" t="s">
+      <c r="B54" s="232" t="s">
         <v>319</v>
       </c>
-      <c r="C54" s="235"/>
+      <c r="C54" s="232"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
@@ -20857,10 +20857,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="232" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="235"/>
+      <c r="C4" s="232"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -20914,7 +20914,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C5</f>
-        <v>195.74</v>
+        <v>200.09</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -20923,7 +20923,7 @@
       </c>
       <c r="C11" s="155">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.51605676731682315</v>
+        <v>0.48309736435901329</v>
       </c>
     </row>
   </sheetData>
@@ -20988,20 +20988,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="232" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
+      <c r="D3" s="232"/>
+      <c r="E3" s="232"/>
+      <c r="F3" s="232"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="232"/>
+      <c r="J3" s="232"/>
+      <c r="K3" s="232"/>
+      <c r="L3" s="232"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -21281,7 +21281,7 @@
       </c>
       <c r="C15" s="157">
         <f ca="1">Overview!C5</f>
-        <v>195.74</v>
+        <v>200.09</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -21347,7 +21347,7 @@
       </c>
       <c r="C23" s="162">
         <f ca="1">C15*C22</f>
-        <v>4736908</v>
+        <v>4842178</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -21374,7 +21374,7 @@
       </c>
       <c r="C26" s="163">
         <f ca="1">C23+C25-C24</f>
-        <v>4664806</v>
+        <v>4770076</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -21900,17 +21900,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -28408,7 +28408,7 @@
       <c r="AA114" s="68"/>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>195.74</v>
+        <v>200.09</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -28455,7 +28455,7 @@
       <c r="AA115" s="68"/>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>195.74</v>
+        <v>200.09</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29957,7 +29957,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>29.975497702909653</v>
+        <v>30.641653905053602</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -29994,7 +29994,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>18.887071059722043</v>
+        <v>19.306805192294796</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30031,7 +30031,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>24.232931233821382</v>
+        <v>24.771468328268725</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30068,7 +30068,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="144">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>4757460.7</v>
+        <v>4863187.45</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30105,7 +30105,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="144">
         <f ca="1">AC155+AC106-AC105+AC47+AC44</f>
-        <v>4685358.7</v>
+        <v>4791085.45</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -30142,7 +30142,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="184">
         <f ca="1">AC156/AC5</f>
-        <v>18.483333530578996</v>
+        <v>18.900416385591601</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -30179,7 +30179,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="184">
         <f ca="1">AC156/AC11</f>
-        <v>28.871175401300182</v>
+        <v>29.522663524047204</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -30314,7 +30314,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="72">
         <f t="shared" ref="AC161:AC162" ca="1" si="96">AC155/AC159</f>
-        <v>42.387632420681236</v>
+        <v>43.329627930183456</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -30351,7 +30351,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ca="1" si="96"/>
-        <v>36.946097718662905</v>
+        <v>37.779799274314691</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -30388,7 +30388,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="74">
         <f t="shared" ref="AC163" ca="1" si="99">AC159/AC155</f>
-        <v>2.3591787106092121E-2</v>
+        <v>2.3078896537290578E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -30425,7 +30425,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>3.3360580361704299E-2</v>
+        <v>3.2635314108651101E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -30462,7 +30462,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="155">
         <f ca="1">AC81/AC115</f>
-        <v>2.0435271278226218E-4</v>
+        <v>1.9991004048178321E-4</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -30499,7 +30499,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="155">
         <f ca="1">-AC62/AC155</f>
-        <v>9.5227271136469928E-3</v>
+        <v>9.315700960693998E-3</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -30536,7 +30536,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="155">
         <f ca="1">-(AC62+AC63)/AC155</f>
-        <v>9.7272479833622159E-3</v>
+        <v>9.5157755023405483E-3</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31039,7 +31039,7 @@
       <c r="AA178" s="49"/>
       <c r="AC178" s="155">
         <f ca="1">(AC105-AC106)/AC155</f>
-        <v>1.5155563975546871E-2</v>
+        <v>1.4826078727440375E-2</v>
       </c>
     </row>
     <row r="179" spans="1:31" x14ac:dyDescent="0.2">
@@ -32204,15 +32204,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="232" t="s">
         <v>230</v>
       </c>
-      <c r="C4" s="235"/>
-      <c r="E4" s="235" t="s">
+      <c r="C4" s="232"/>
+      <c r="E4" s="232" t="s">
         <v>237</v>
       </c>
-      <c r="F4" s="235"/>
-      <c r="G4" s="235"/>
+      <c r="F4" s="232"/>
+      <c r="G4" s="232"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -32220,7 +32220,7 @@
       </c>
       <c r="C5" s="173">
         <f ca="1">Overview!C5</f>
-        <v>195.74</v>
+        <v>200.09</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="133" t="s">
@@ -32236,7 +32236,7 @@
       </c>
       <c r="C6" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>4757460.7</v>
+        <v>4863187.45</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -32256,7 +32256,7 @@
       </c>
       <c r="C7" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>4685358.7</v>
+        <v>4791085.45</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -32276,7 +32276,7 @@
       </c>
       <c r="C8" s="175">
         <f ca="1">Statement!AC152</f>
-        <v>29.975497702909653</v>
+        <v>30.641653905053602</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>240</v>
@@ -32296,7 +32296,7 @@
       </c>
       <c r="C9" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>18.887071059722043</v>
+        <v>19.306805192294796</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>241</v>
@@ -32316,7 +32316,7 @@
       </c>
       <c r="C10" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>24.232931233821382</v>
+        <v>24.771468328268725</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -32336,7 +32336,7 @@
       </c>
       <c r="C11" s="175">
         <f ca="1">Statement!AC157</f>
-        <v>18.483333530578996</v>
+        <v>18.900416385591601</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -32345,18 +32345,18 @@
       </c>
       <c r="C12" s="175">
         <f ca="1">Statement!AC158</f>
-        <v>28.871175401300182</v>
+        <v>29.522663524047204</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="235" t="s">
+      <c r="B15" s="232" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="235"/>
-      <c r="E15" s="235" t="s">
+      <c r="C15" s="232"/>
+      <c r="E15" s="232" t="s">
         <v>243</v>
       </c>
-      <c r="F15" s="235"/>
+      <c r="F15" s="232"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -32407,14 +32407,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="235" t="s">
+      <c r="B21" s="232" t="s">
         <v>242</v>
       </c>
-      <c r="C21" s="235"/>
-      <c r="E21" s="235" t="s">
+      <c r="C21" s="232"/>
+      <c r="E21" s="232" t="s">
         <v>246</v>
       </c>
-      <c r="F21" s="235"/>
+      <c r="F21" s="232"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -32483,14 +32483,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="235" t="s">
+      <c r="B29" s="232" t="s">
         <v>247</v>
       </c>
-      <c r="C29" s="235"/>
-      <c r="E29" s="235" t="s">
+      <c r="C29" s="232"/>
+      <c r="E29" s="232" t="s">
         <v>253</v>
       </c>
-      <c r="F29" s="235"/>
+      <c r="F29" s="232"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -32566,14 +32566,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="235" t="s">
+      <c r="B37" s="232" t="s">
         <v>265</v>
       </c>
-      <c r="C37" s="235"/>
-      <c r="E37" s="235" t="s">
+      <c r="C37" s="232"/>
+      <c r="E37" s="232" t="s">
         <v>268</v>
       </c>
-      <c r="F37" s="235"/>
+      <c r="F37" s="232"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -32581,7 +32581,7 @@
       </c>
       <c r="C38" s="176">
         <f ca="1">Statement!AC164</f>
-        <v>3.3360580361704299E-2</v>
+        <v>3.2635314108651101E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>267</v>
@@ -32597,7 +32597,7 @@
       </c>
       <c r="C39" s="216">
         <f ca="1">Statement!AC163</f>
-        <v>2.3591787106092121E-2</v>
+        <v>2.3078896537290578E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>269</v>
@@ -32613,7 +32613,7 @@
       </c>
       <c r="C40" s="176">
         <f ca="1">Statement!AC165</f>
-        <v>2.0435271278226218E-4</v>
+        <v>1.9991004048178321E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>270</v>
@@ -32629,7 +32629,7 @@
       </c>
       <c r="C41" s="176">
         <f ca="1">Statement!AC166</f>
-        <v>9.5227271136469928E-3</v>
+        <v>9.315700960693998E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -32638,18 +32638,18 @@
       </c>
       <c r="C42" s="176">
         <f ca="1">Statement!AC167</f>
-        <v>9.7272479833622159E-3</v>
+        <v>9.5157755023405483E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="235" t="s">
+      <c r="B45" s="232" t="s">
         <v>276</v>
       </c>
-      <c r="C45" s="235"/>
-      <c r="E45" s="235" t="s">
+      <c r="C45" s="232"/>
+      <c r="E45" s="232" t="s">
         <v>282</v>
       </c>
-      <c r="F45" s="235"/>
+      <c r="F45" s="232"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -32682,18 +32682,18 @@
       </c>
       <c r="F48" s="176">
         <f ca="1">Statement!AC178</f>
-        <v>1.5155563975546871E-2</v>
+        <v>1.4826078727440375E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="235" t="s">
+      <c r="B51" s="232" t="s">
         <v>279</v>
       </c>
-      <c r="C51" s="235"/>
-      <c r="E51" s="235" t="s">
+      <c r="C51" s="232"/>
+      <c r="E51" s="232" t="s">
         <v>300</v>
       </c>
-      <c r="F51" s="235"/>
+      <c r="F51" s="232"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -32862,7 +32862,7 @@
       </c>
       <c r="I6" s="173">
         <f ca="1">Statement!AC114</f>
-        <v>195.74</v>
+        <v>200.09</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -32891,7 +32891,7 @@
       </c>
       <c r="I7" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>4757460.7</v>
+        <v>4863187.45</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -32920,7 +32920,7 @@
       </c>
       <c r="I8" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>4685358.7</v>
+        <v>4791085.45</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -32949,7 +32949,7 @@
       </c>
       <c r="I9" s="175">
         <f ca="1">Statement!AC152</f>
-        <v>29.975497702909653</v>
+        <v>30.641653905053602</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -32978,7 +32978,7 @@
       </c>
       <c r="I10" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>18.887071059722043</v>
+        <v>19.306805192294796</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33007,7 +33007,7 @@
       </c>
       <c r="I11" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>24.232931233821382</v>
+        <v>24.771468328268725</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33036,7 +33036,7 @@
       </c>
       <c r="I12" s="175">
         <f ca="1">Statement!AC157</f>
-        <v>18.483333530578996</v>
+        <v>18.900416385591601</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33065,7 +33065,7 @@
       </c>
       <c r="I13" s="175">
         <f ca="1">Statement!AC158</f>
-        <v>28.871175401300182</v>
+        <v>29.522663524047204</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -33838,7 +33838,7 @@
       </c>
       <c r="I51" s="176">
         <f ca="1">Statement!AC164</f>
-        <v>3.3360580361704299E-2</v>
+        <v>3.2635314108651101E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -33867,7 +33867,7 @@
       </c>
       <c r="I52" s="176">
         <f ca="1">Statement!AC163</f>
-        <v>2.3591787106092121E-2</v>
+        <v>2.3078896537290578E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -33896,7 +33896,7 @@
       </c>
       <c r="I53" s="176">
         <f ca="1">Statement!AC165</f>
-        <v>2.0435271278226218E-4</v>
+        <v>1.9991004048178321E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -33925,7 +33925,7 @@
       </c>
       <c r="I54" s="176">
         <f ca="1">Statement!AC166</f>
-        <v>9.5227271136469928E-3</v>
+        <v>9.315700960693998E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -33954,7 +33954,7 @@
       </c>
       <c r="I55" s="176">
         <f ca="1">Statement!AC167</f>
-        <v>9.7272479833622159E-3</v>
+        <v>9.5157755023405483E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34190,7 +34190,7 @@
       </c>
       <c r="I68" s="197">
         <f ca="1">Statement!AC178</f>
-        <v>1.5155563975546871E-2</v>
+        <v>1.4826078727440375E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34702,14 +34702,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="238" t="s">
+      <c r="C3" s="236" t="s">
         <v>310</v>
       </c>
-      <c r="D3" s="239"/>
-      <c r="F3" s="240" t="s">
+      <c r="D3" s="237"/>
+      <c r="F3" s="238" t="s">
         <v>311</v>
       </c>
-      <c r="G3" s="239"/>
+      <c r="G3" s="237"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -34776,19 +34776,19 @@
       <c r="B7" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C7" s="236">
+      <c r="C7" s="239">
         <f>Statement!AA88</f>
         <v>0.19798317847549429</v>
       </c>
-      <c r="D7" s="237"/>
-      <c r="F7" s="236">
+      <c r="D7" s="240"/>
+      <c r="F7" s="239">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.85227633788752211</v>
       </c>
-      <c r="G7" s="237"/>
+      <c r="G7" s="240"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="208" t="s">
@@ -34815,19 +34815,19 @@
       <c r="B9" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C9" s="236">
+      <c r="C9" s="239">
         <f>Statement!AA89</f>
         <v>0.20100974521545145</v>
       </c>
-      <c r="D9" s="237"/>
-      <c r="F9" s="236">
+      <c r="D9" s="240"/>
+      <c r="F9" s="239">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.17615269633206854</v>
       </c>
-      <c r="G9" s="237"/>
+      <c r="G9" s="240"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="208" t="s">
@@ -34854,19 +34854,19 @@
       <c r="B11" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C11" s="236">
+      <c r="C11" s="239">
         <f>Statement!AA90</f>
         <v>0.19697414518622902</v>
       </c>
-      <c r="D11" s="237"/>
-      <c r="F11" s="236">
+      <c r="D11" s="240"/>
+      <c r="F11" s="239">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.293272836358182</v>
       </c>
-      <c r="G11" s="237"/>
+      <c r="G11" s="240"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="208" t="s">
@@ -34893,19 +34893,19 @@
       <c r="B13" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C13" s="236">
+      <c r="C13" s="239">
         <f>Statement!AA93</f>
         <v>0.12172505151604357</v>
       </c>
-      <c r="D13" s="237"/>
-      <c r="F13" s="236">
+      <c r="D13" s="240"/>
+      <c r="F13" s="239">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.51510934393638175</v>
       </c>
-      <c r="G13" s="237"/>
+      <c r="G13" s="240"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="208" t="s">
@@ -34932,19 +34932,19 @@
       <c r="B15" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C15" s="236">
+      <c r="C15" s="239">
         <f>Statement!AA94</f>
         <v>0.20851486489537011</v>
       </c>
-      <c r="D15" s="237"/>
-      <c r="F15" s="236">
+      <c r="D15" s="240"/>
+      <c r="F15" s="239">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.4741658193918108</v>
       </c>
-      <c r="G15" s="237"/>
+      <c r="G15" s="240"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="208" t="s">
@@ -34971,19 +34971,19 @@
       <c r="B17" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C17" s="236">
+      <c r="C17" s="239">
         <f>Statement!AA96</f>
         <v>0.35756517690875234</v>
       </c>
-      <c r="D17" s="237"/>
-      <c r="F17" s="236">
+      <c r="D17" s="240"/>
+      <c r="F17" s="239">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>2.1063115845539282</v>
       </c>
-      <c r="G17" s="237"/>
+      <c r="G17" s="240"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="208" t="s">
@@ -35010,22 +35010,22 @@
       <c r="B19" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C19" s="236">
+      <c r="C19" s="239">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-1.6781270464963983E-3</v>
       </c>
-      <c r="D19" s="237"/>
-      <c r="F19" s="236">
+      <c r="D19" s="240"/>
+      <c r="F19" s="239">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-8.9390922758116297E-3</v>
       </c>
-      <c r="G19" s="237"/>
+      <c r="G19" s="240"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="208" t="s">
@@ -35052,22 +35052,22 @@
       <c r="B21" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C21" s="236">
+      <c r="C21" s="239">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.35795454545454553</v>
       </c>
-      <c r="D21" s="237"/>
-      <c r="F21" s="236">
+      <c r="D21" s="240"/>
+      <c r="F21" s="239">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>2.1447368421052633</v>
       </c>
-      <c r="G21" s="237"/>
+      <c r="G21" s="240"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -35115,22 +35115,22 @@
       <c r="B25" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C25" s="236">
+      <c r="C25" s="239">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.11992074288756137</v>
       </c>
-      <c r="D25" s="237"/>
-      <c r="F25" s="236">
+      <c r="D25" s="240"/>
+      <c r="F25" s="239">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>1.1517699869310756</v>
       </c>
-      <c r="G25" s="237"/>
+      <c r="G25" s="240"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="224" t="s">
@@ -35157,22 +35157,22 @@
       <c r="B27" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C27" s="236">
+      <c r="C27" s="239">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.31147368421052629</v>
       </c>
-      <c r="D27" s="237"/>
-      <c r="F27" s="236">
+      <c r="D27" s="240"/>
+      <c r="F27" s="239">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.73741458652907543</v>
       </c>
-      <c r="G27" s="237"/>
+      <c r="G27" s="240"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -35199,22 +35199,22 @@
       <c r="B29" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C29" s="236">
+      <c r="C29" s="239">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.20752960811374652</v>
       </c>
-      <c r="D29" s="237"/>
-      <c r="F29" s="236">
+      <c r="D29" s="240"/>
+      <c r="F29" s="239">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.92385968500715898</v>
       </c>
-      <c r="G29" s="237"/>
+      <c r="G29" s="240"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35241,43 +35241,25 @@
       <c r="B31" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C31" s="236">
+      <c r="C31" s="239">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>9.5647686220540165E-2</v>
       </c>
-      <c r="D31" s="237"/>
-      <c r="F31" s="236">
+      <c r="D31" s="240"/>
+      <c r="F31" s="239">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.28666666666666668</v>
       </c>
-      <c r="G31" s="237"/>
+      <c r="G31" s="240"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C25:D25"/>
@@ -35286,6 +35268,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{273E88C5-7449-0446-9008-592BD9067F14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD18DC50-58F8-7346-A967-A810846FE4E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="3" activeTab="12" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2261,9 +2261,6 @@
     </xf>
     <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2273,6 +2270,15 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2280,12 +2286,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12569,12 +12569,12 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>236.54</v>
-    <v>151.49</v>
-    <v>2.2160000000000002</v>
-    <v>5.12</v>
-    <v>2.6259999999999999E-2</v>
-    <v>-0.84</v>
-    <v>-4.1980000000000003E-3</v>
+    <v>152.97</v>
+    <v>2.2262</v>
+    <v>-2.75</v>
+    <v>-1.3918E-2</v>
+    <v>-0.4</v>
+    <v>-2.0530000000000001E-3</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -12582,25 +12582,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2788 San Tomas Expressway, SANTA CLARA, CA, 95051 US</v>
-    <v>200.63</v>
+    <v>200.05500000000001</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46203.950696596876</v>
+    <v>46205.999998460153</v>
     <v>0</v>
-    <v>195.11</v>
-    <v>4842178000000</v>
+    <v>192.35</v>
+    <v>4714886000000</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
-    <v>197.24</v>
-    <v>30.6417</v>
-    <v>194.97</v>
-    <v>200.09</v>
-    <v>199.25</v>
+    <v>197.14</v>
+    <v>30.257400000000001</v>
+    <v>197.58</v>
+    <v>194.83</v>
+    <v>194.43</v>
     <v>24200000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>166082238</v>
-    <v>168652596</v>
+    <v>142385548</v>
+    <v>166898435</v>
     <v>1998</v>
   </rv>
   <rv s="2">
@@ -12624,17 +12624,17 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>0.02</v>
-    <v>4.5750000000000001E-4</v>
+    <v>0.1</v>
+    <v>2.235E-3</v>
     <v>US</v>
-    <v>43.9</v>
+    <v>45.05</v>
     <v>Index</v>
     <v>3</v>
-    <v>43.67</v>
+    <v>44.53</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>43.78</v>
-    <v>43.72</v>
-    <v>43.74</v>
+    <v>45.03</v>
+    <v>44.75</v>
+    <v>44.85</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -12856,9 +12856,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13429,18 +13429,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="233" t="s">
+      <c r="B2" s="232" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="234"/>
-      <c r="E2" s="233" t="s">
+      <c r="C2" s="233"/>
+      <c r="E2" s="232" t="s">
         <v>284</v>
       </c>
-      <c r="F2" s="234"/>
-      <c r="H2" s="233" t="s">
+      <c r="F2" s="233"/>
+      <c r="H2" s="232" t="s">
         <v>325</v>
       </c>
-      <c r="I2" s="234"/>
+      <c r="I2" s="233"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="186" t="s">
@@ -13455,7 +13455,7 @@
       </c>
       <c r="F3" s="188">
         <f ca="1">Statement!AC155</f>
-        <v>4863187.45</v>
+        <v>4735343.1500000004</v>
       </c>
       <c r="H3" s="186" t="str">
         <f>'AVG target price'!B5</f>
@@ -13479,7 +13479,7 @@
       </c>
       <c r="F4" s="189">
         <f ca="1">Statement!AC156</f>
-        <v>4791085.45</v>
+        <v>4663241.1500000004</v>
       </c>
       <c r="H4" s="186" t="str">
         <f>'AVG target price'!B6</f>
@@ -13496,7 +13496,7 @@
       </c>
       <c r="C5" s="209" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>200.09</v>
+        <v>194.83</v>
       </c>
       <c r="E5" s="186" t="s">
         <v>240</v>
@@ -13520,14 +13520,14 @@
       </c>
       <c r="C6" s="209" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>199.25</v>
+        <v>194.43</v>
       </c>
       <c r="E6" s="186" t="s">
         <v>234</v>
       </c>
       <c r="F6" s="191">
         <f ca="1">Statement!AC152</f>
-        <v>30.641653905053602</v>
+        <v>29.836140888208273</v>
       </c>
       <c r="H6" s="186" t="str">
         <f>'AVG target price'!B8</f>
@@ -13544,14 +13544,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>5.12</v>
+        <v>-2.75</v>
       </c>
       <c r="E7" s="187" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="192">
         <f ca="1">Statement!AC153</f>
-        <v>19.306805192294796</v>
+        <v>18.799264608999927</v>
       </c>
       <c r="H7" s="185" t="str">
         <f>'AVG target price'!B9</f>
@@ -13568,14 +13568,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.84</v>
+        <v>-0.4</v>
       </c>
       <c r="E8" s="186" t="s">
         <v>262</v>
       </c>
       <c r="F8" s="193">
         <f ca="1">Statement!AC163</f>
-        <v>2.3078896537290578E-2</v>
+        <v>2.3701978176597402E-2</v>
       </c>
       <c r="H8" s="185" t="str">
         <f>'AVG target price'!B11</f>
@@ -13583,7 +13583,7 @@
       </c>
       <c r="I8" s="214">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.48309736435901329</v>
+        <v>0.52313787216853136</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13592,14 +13592,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>2.6259999999999999E-2</v>
+        <v>-1.3918E-2</v>
       </c>
       <c r="E9" s="186" t="s">
         <v>285</v>
       </c>
       <c r="F9" s="193">
         <f ca="1">Statement!AC164</f>
-        <v>3.2635314108651101E-2</v>
+        <v>3.3516398911871879E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13608,14 +13608,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-4.1980000000000003E-3</v>
+        <v>-2.0530000000000001E-3</v>
       </c>
       <c r="E10" s="186" t="s">
         <v>290</v>
       </c>
       <c r="F10" s="193">
         <f ca="1">Statement!AC166</f>
-        <v>9.315700960693998E-3</v>
+        <v>9.5672052826836843E-3</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13631,7 +13631,7 @@
       </c>
       <c r="F11" s="194">
         <f ca="1">Statement!AC165</f>
-        <v>1.9991004048178321E-4</v>
+        <v>2.053071908843607E-4</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13640,7 +13640,7 @@
       </c>
       <c r="C12" s="210" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>151.49</v>
+        <v>152.97</v>
       </c>
       <c r="E12" s="186" t="s">
         <v>94</v>
@@ -13656,7 +13656,7 @@
       </c>
       <c r="C13" s="210" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.2160000000000002</v>
+        <v>2.2262</v>
       </c>
       <c r="E13" s="186" t="s">
         <v>96</v>
@@ -13672,7 +13672,7 @@
       </c>
       <c r="C14" s="211" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>168652596</v>
+        <v>166898435</v>
       </c>
       <c r="E14" s="187" t="s">
         <v>97</v>
@@ -13688,7 +13688,7 @@
       </c>
       <c r="F15" s="193">
         <f ca="1">Statement!AC178</f>
-        <v>1.4826078727440375E-2</v>
+        <v>1.5226351653100366E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13701,10 +13701,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="235" t="s">
+      <c r="B17" s="234" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="235"/>
+      <c r="C17" s="234"/>
       <c r="E17" s="185" t="s">
         <v>293</v>
       </c>
@@ -13777,14 +13777,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="235" t="s">
+      <c r="B25" s="234" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="235"/>
-      <c r="E25" s="233" t="s">
+      <c r="C25" s="234"/>
+      <c r="E25" s="232" t="s">
         <v>340</v>
       </c>
-      <c r="F25" s="234"/>
+      <c r="F25" s="233"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="185" t="s">
@@ -13798,7 +13798,7 @@
       </c>
       <c r="F26" s="220" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>43.74</v>
+        <v>44.85</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13813,7 +13813,7 @@
       </c>
       <c r="F27" s="221">
         <f ca="1">F26/1000</f>
-        <v>4.3740000000000001E-2</v>
+        <v>4.4850000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -13833,15 +13833,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="232" t="s">
+      <c r="B33" s="235" t="s">
         <v>335</v>
       </c>
-      <c r="C33" s="232"/>
-      <c r="D33" s="232"/>
-      <c r="E33" s="232"/>
-      <c r="F33" s="232"/>
-      <c r="G33" s="232"/>
-      <c r="H33" s="232"/>
+      <c r="C33" s="235"/>
+      <c r="D33" s="235"/>
+      <c r="E33" s="235"/>
+      <c r="F33" s="235"/>
+      <c r="G33" s="235"/>
+      <c r="H33" s="235"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -13860,24 +13860,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="232"/>
-      <c r="C39" s="232"/>
-      <c r="D39" s="232"/>
-      <c r="E39" s="232"/>
-      <c r="F39" s="232"/>
-      <c r="G39" s="232"/>
-      <c r="H39" s="232"/>
+      <c r="B39" s="235"/>
+      <c r="C39" s="235"/>
+      <c r="D39" s="235"/>
+      <c r="E39" s="235"/>
+      <c r="F39" s="235"/>
+      <c r="G39" s="235"/>
+      <c r="H39" s="235"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="232" t="s">
+      <c r="B42" s="235" t="s">
         <v>338</v>
       </c>
-      <c r="C42" s="232"/>
-      <c r="D42" s="232"/>
-      <c r="E42" s="232"/>
-      <c r="F42" s="232"/>
-      <c r="G42" s="232"/>
-      <c r="H42" s="232"/>
+      <c r="C42" s="235"/>
+      <c r="D42" s="235"/>
+      <c r="E42" s="235"/>
+      <c r="F42" s="235"/>
+      <c r="G42" s="235"/>
+      <c r="H42" s="235"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -13892,24 +13892,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="232"/>
-      <c r="C49" s="232"/>
-      <c r="D49" s="232"/>
-      <c r="E49" s="232"/>
-      <c r="F49" s="232"/>
-      <c r="G49" s="232"/>
-      <c r="H49" s="232"/>
+      <c r="B49" s="235"/>
+      <c r="C49" s="235"/>
+      <c r="D49" s="235"/>
+      <c r="E49" s="235"/>
+      <c r="F49" s="235"/>
+      <c r="G49" s="235"/>
+      <c r="H49" s="235"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="232" t="s">
+      <c r="B52" s="235" t="s">
         <v>101</v>
       </c>
-      <c r="C52" s="232"/>
-      <c r="D52" s="232"/>
-      <c r="E52" s="232"/>
-      <c r="F52" s="232"/>
-      <c r="G52" s="232"/>
-      <c r="H52" s="232"/>
+      <c r="C52" s="235"/>
+      <c r="D52" s="235"/>
+      <c r="E52" s="235"/>
+      <c r="F52" s="235"/>
+      <c r="G52" s="235"/>
+      <c r="H52" s="235"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -13924,28 +13924,28 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="232"/>
-      <c r="C59" s="232"/>
-      <c r="D59" s="232"/>
-      <c r="E59" s="232"/>
-      <c r="F59" s="232"/>
-      <c r="G59" s="232"/>
-      <c r="H59" s="232"/>
+      <c r="B59" s="235"/>
+      <c r="C59" s="235"/>
+      <c r="D59" s="235"/>
+      <c r="E59" s="235"/>
+      <c r="F59" s="235"/>
+      <c r="G59" s="235"/>
+      <c r="H59" s="235"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B49:H49"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B52:H52"/>
-    <mergeCell ref="B59:H59"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B49:H49"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14015,36 +14015,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="232" t="s">
+      <c r="S2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="232"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="232"/>
-      <c r="W2" s="232"/>
-      <c r="X2" s="232"/>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="232"/>
-      <c r="AA2" s="232" t="s">
+      <c r="T2" s="235"/>
+      <c r="U2" s="235"/>
+      <c r="V2" s="235"/>
+      <c r="W2" s="235"/>
+      <c r="X2" s="235"/>
+      <c r="Y2" s="235"/>
+      <c r="Z2" s="235"/>
+      <c r="AA2" s="235" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="232"/>
-      <c r="AC2" s="232"/>
+      <c r="AB2" s="235"/>
+      <c r="AC2" s="235"/>
       <c r="AE2" s="85" t="s">
         <v>107</v>
       </c>
@@ -15240,35 +15240,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
-      <c r="P2" s="232" t="s">
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
+      <c r="P2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="232"/>
-      <c r="R2" s="232"/>
-      <c r="S2" s="232"/>
-      <c r="T2" s="232"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="232"/>
-      <c r="W2" s="232"/>
-      <c r="X2" s="232" t="s">
+      <c r="Q2" s="235"/>
+      <c r="R2" s="235"/>
+      <c r="S2" s="235"/>
+      <c r="T2" s="235"/>
+      <c r="U2" s="235"/>
+      <c r="V2" s="235"/>
+      <c r="W2" s="235"/>
+      <c r="X2" s="235" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="232"/>
+      <c r="Y2" s="235"/>
+      <c r="Z2" s="235"/>
       <c r="AB2" s="85" t="s">
         <v>107</v>
       </c>
@@ -16499,20 +16499,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -17823,23 +17823,23 @@
         <v>58</v>
       </c>
       <c r="C45" s="115">
-        <f>-Statement!M59</f>
+        <f>-Statement!M108</f>
         <v>976</v>
       </c>
       <c r="D45" s="115">
-        <f>-Statement!N59</f>
+        <f>-Statement!N108</f>
         <v>1833</v>
       </c>
       <c r="E45" s="115">
-        <f>-Statement!O59</f>
+        <f>-Statement!O108</f>
         <v>1069</v>
       </c>
       <c r="F45" s="115">
-        <f>-Statement!P59</f>
+        <f>-Statement!P108</f>
         <v>3236</v>
       </c>
       <c r="G45" s="116">
-        <f>-Statement!Q59</f>
+        <f>-Statement!Q108</f>
         <v>6042</v>
       </c>
       <c r="H45" s="25">
@@ -17905,6 +17905,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -17912,12 +17918,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -17955,20 +17955,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
       <c r="S2" s="246"/>
       <c r="T2" s="246"/>
       <c r="U2" s="246"/>
@@ -18977,16 +18977,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19049,10 +19049,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="235" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="232"/>
+      <c r="C4" s="235"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19069,7 +19069,7 @@
       </c>
       <c r="C6" s="134">
         <f ca="1">Overview!C5</f>
-        <v>200.09</v>
+        <v>194.83</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19078,7 +19078,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">C5*C6</f>
-        <v>4863187.45</v>
+        <v>4735343.1500000004</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19096,7 +19096,7 @@
       </c>
       <c r="C9" s="136">
         <f ca="1">Overview!F27</f>
-        <v>4.3740000000000001E-2</v>
+        <v>4.4850000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19105,7 +19105,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C13</f>
-        <v>2.2160000000000002</v>
+        <v>2.2262</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19137,10 +19137,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="232" t="s">
+      <c r="B15" s="235" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="232"/>
+      <c r="C15" s="235"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19148,7 +19148,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>1.7386279899462142E-3</v>
+        <v>1.7854834775690943E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19157,7 +19157,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99826137201005383</v>
+        <v>0.99821451652243087</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19175,7 +19175,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14346</v>
+        <v>0.14502899999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19184,7 +19184,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14328062575027725</v>
+        <v>0.14484199024604286</v>
       </c>
     </row>
   </sheetData>
@@ -19229,20 +19229,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -19528,10 +19528,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="232" t="s">
+      <c r="B13" s="235" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="232"/>
+      <c r="C13" s="235"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -19551,10 +19551,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="232" t="s">
+      <c r="B18" s="235" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="232"/>
+      <c r="C18" s="235"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -19668,20 +19668,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -20613,10 +20613,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="232" t="s">
+      <c r="B37" s="235" t="s">
         <v>197</v>
       </c>
-      <c r="C37" s="232"/>
+      <c r="C37" s="235"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -20682,10 +20682,10 @@
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="232" t="s">
+      <c r="B46" s="235" t="s">
         <v>202</v>
       </c>
-      <c r="C46" s="232"/>
+      <c r="C46" s="235"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
@@ -20741,10 +20741,10 @@
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="232" t="s">
+      <c r="B54" s="235" t="s">
         <v>319</v>
       </c>
-      <c r="C54" s="232"/>
+      <c r="C54" s="235"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
@@ -20857,10 +20857,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="235" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="232"/>
+      <c r="C4" s="235"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -20914,7 +20914,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C5</f>
-        <v>200.09</v>
+        <v>194.83</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -20923,7 +20923,7 @@
       </c>
       <c r="C11" s="155">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.48309736435901329</v>
+        <v>0.52313787216853136</v>
       </c>
     </row>
   </sheetData>
@@ -20988,20 +20988,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -21281,7 +21281,7 @@
       </c>
       <c r="C15" s="157">
         <f ca="1">Overview!C5</f>
-        <v>200.09</v>
+        <v>194.83</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -21347,7 +21347,7 @@
       </c>
       <c r="C23" s="162">
         <f ca="1">C15*C22</f>
-        <v>4842178</v>
+        <v>4714886</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -21374,7 +21374,7 @@
       </c>
       <c r="C26" s="163">
         <f ca="1">C23+C25-C24</f>
-        <v>4770076</v>
+        <v>4642784</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -21900,17 +21900,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -28408,7 +28408,7 @@
       <c r="AA114" s="68"/>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>200.09</v>
+        <v>194.83</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -28455,7 +28455,7 @@
       <c r="AA115" s="68"/>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>200.09</v>
+        <v>194.83</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29957,7 +29957,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>30.641653905053602</v>
+        <v>29.836140888208273</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -29994,7 +29994,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>19.306805192294796</v>
+        <v>18.799264608999927</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30031,7 +30031,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>24.771468328268725</v>
+        <v>24.120271749695615</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30068,7 +30068,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="144">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>4863187.45</v>
+        <v>4735343.1500000004</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30105,7 +30105,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="144">
         <f ca="1">AC155+AC106-AC105+AC47+AC44</f>
-        <v>4791085.45</v>
+        <v>4663241.1500000004</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -30142,7 +30142,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="184">
         <f ca="1">AC156/AC5</f>
-        <v>18.900416385591601</v>
+        <v>18.396081714932681</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -30179,7 +30179,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="184">
         <f ca="1">AC156/AC11</f>
-        <v>29.522663524047204</v>
+        <v>28.734887081369198</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -30314,7 +30314,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="72">
         <f t="shared" ref="AC161:AC162" ca="1" si="96">AC155/AC159</f>
-        <v>43.329627930183456</v>
+        <v>42.190571291107211</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -30351,7 +30351,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ca="1" si="96"/>
-        <v>37.779799274314691</v>
+        <v>36.771691186331154</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -30388,7 +30388,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="74">
         <f t="shared" ref="AC163" ca="1" si="99">AC159/AC155</f>
-        <v>2.3078896537290578E-2</v>
+        <v>2.3701978176597402E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -30425,7 +30425,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>3.2635314108651101E-2</v>
+        <v>3.3516398911871879E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -30462,7 +30462,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="155">
         <f ca="1">AC81/AC115</f>
-        <v>1.9991004048178321E-4</v>
+        <v>2.053071908843607E-4</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -30499,7 +30499,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="155">
         <f ca="1">-AC62/AC155</f>
-        <v>9.315700960693998E-3</v>
+        <v>9.5672052826836843E-3</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -30536,7 +30536,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="155">
         <f ca="1">-(AC62+AC63)/AC155</f>
-        <v>9.5157755023405483E-3</v>
+        <v>9.772681415918083E-3</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31039,7 +31039,7 @@
       <c r="AA178" s="49"/>
       <c r="AC178" s="155">
         <f ca="1">(AC105-AC106)/AC155</f>
-        <v>1.4826078727440375E-2</v>
+        <v>1.5226351653100366E-2</v>
       </c>
     </row>
     <row r="179" spans="1:31" x14ac:dyDescent="0.2">
@@ -32204,15 +32204,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="235" t="s">
         <v>230</v>
       </c>
-      <c r="C4" s="232"/>
-      <c r="E4" s="232" t="s">
+      <c r="C4" s="235"/>
+      <c r="E4" s="235" t="s">
         <v>237</v>
       </c>
-      <c r="F4" s="232"/>
-      <c r="G4" s="232"/>
+      <c r="F4" s="235"/>
+      <c r="G4" s="235"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -32220,7 +32220,7 @@
       </c>
       <c r="C5" s="173">
         <f ca="1">Overview!C5</f>
-        <v>200.09</v>
+        <v>194.83</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="133" t="s">
@@ -32236,7 +32236,7 @@
       </c>
       <c r="C6" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>4863187.45</v>
+        <v>4735343.1500000004</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -32256,7 +32256,7 @@
       </c>
       <c r="C7" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>4791085.45</v>
+        <v>4663241.1500000004</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -32276,7 +32276,7 @@
       </c>
       <c r="C8" s="175">
         <f ca="1">Statement!AC152</f>
-        <v>30.641653905053602</v>
+        <v>29.836140888208273</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>240</v>
@@ -32296,7 +32296,7 @@
       </c>
       <c r="C9" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>19.306805192294796</v>
+        <v>18.799264608999927</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>241</v>
@@ -32316,7 +32316,7 @@
       </c>
       <c r="C10" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>24.771468328268725</v>
+        <v>24.120271749695615</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -32336,7 +32336,7 @@
       </c>
       <c r="C11" s="175">
         <f ca="1">Statement!AC157</f>
-        <v>18.900416385591601</v>
+        <v>18.396081714932681</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -32345,18 +32345,18 @@
       </c>
       <c r="C12" s="175">
         <f ca="1">Statement!AC158</f>
-        <v>29.522663524047204</v>
+        <v>28.734887081369198</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="232" t="s">
+      <c r="B15" s="235" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="232"/>
-      <c r="E15" s="232" t="s">
+      <c r="C15" s="235"/>
+      <c r="E15" s="235" t="s">
         <v>243</v>
       </c>
-      <c r="F15" s="232"/>
+      <c r="F15" s="235"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -32407,14 +32407,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="232" t="s">
+      <c r="B21" s="235" t="s">
         <v>242</v>
       </c>
-      <c r="C21" s="232"/>
-      <c r="E21" s="232" t="s">
+      <c r="C21" s="235"/>
+      <c r="E21" s="235" t="s">
         <v>246</v>
       </c>
-      <c r="F21" s="232"/>
+      <c r="F21" s="235"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -32483,14 +32483,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="232" t="s">
+      <c r="B29" s="235" t="s">
         <v>247</v>
       </c>
-      <c r="C29" s="232"/>
-      <c r="E29" s="232" t="s">
+      <c r="C29" s="235"/>
+      <c r="E29" s="235" t="s">
         <v>253</v>
       </c>
-      <c r="F29" s="232"/>
+      <c r="F29" s="235"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -32566,14 +32566,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="232" t="s">
+      <c r="B37" s="235" t="s">
         <v>265</v>
       </c>
-      <c r="C37" s="232"/>
-      <c r="E37" s="232" t="s">
+      <c r="C37" s="235"/>
+      <c r="E37" s="235" t="s">
         <v>268</v>
       </c>
-      <c r="F37" s="232"/>
+      <c r="F37" s="235"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -32581,7 +32581,7 @@
       </c>
       <c r="C38" s="176">
         <f ca="1">Statement!AC164</f>
-        <v>3.2635314108651101E-2</v>
+        <v>3.3516398911871879E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>267</v>
@@ -32597,7 +32597,7 @@
       </c>
       <c r="C39" s="216">
         <f ca="1">Statement!AC163</f>
-        <v>2.3078896537290578E-2</v>
+        <v>2.3701978176597402E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>269</v>
@@ -32613,7 +32613,7 @@
       </c>
       <c r="C40" s="176">
         <f ca="1">Statement!AC165</f>
-        <v>1.9991004048178321E-4</v>
+        <v>2.053071908843607E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>270</v>
@@ -32629,7 +32629,7 @@
       </c>
       <c r="C41" s="176">
         <f ca="1">Statement!AC166</f>
-        <v>9.315700960693998E-3</v>
+        <v>9.5672052826836843E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -32638,18 +32638,18 @@
       </c>
       <c r="C42" s="176">
         <f ca="1">Statement!AC167</f>
-        <v>9.5157755023405483E-3</v>
+        <v>9.772681415918083E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="232" t="s">
+      <c r="B45" s="235" t="s">
         <v>276</v>
       </c>
-      <c r="C45" s="232"/>
-      <c r="E45" s="232" t="s">
+      <c r="C45" s="235"/>
+      <c r="E45" s="235" t="s">
         <v>282</v>
       </c>
-      <c r="F45" s="232"/>
+      <c r="F45" s="235"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -32682,18 +32682,18 @@
       </c>
       <c r="F48" s="176">
         <f ca="1">Statement!AC178</f>
-        <v>1.4826078727440375E-2</v>
+        <v>1.5226351653100366E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="232" t="s">
+      <c r="B51" s="235" t="s">
         <v>279</v>
       </c>
-      <c r="C51" s="232"/>
-      <c r="E51" s="232" t="s">
+      <c r="C51" s="235"/>
+      <c r="E51" s="235" t="s">
         <v>300</v>
       </c>
-      <c r="F51" s="232"/>
+      <c r="F51" s="235"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -32862,7 +32862,7 @@
       </c>
       <c r="I6" s="173">
         <f ca="1">Statement!AC114</f>
-        <v>200.09</v>
+        <v>194.83</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -32891,7 +32891,7 @@
       </c>
       <c r="I7" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>4863187.45</v>
+        <v>4735343.1500000004</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -32920,7 +32920,7 @@
       </c>
       <c r="I8" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>4791085.45</v>
+        <v>4663241.1500000004</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -32949,7 +32949,7 @@
       </c>
       <c r="I9" s="175">
         <f ca="1">Statement!AC152</f>
-        <v>30.641653905053602</v>
+        <v>29.836140888208273</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -32978,7 +32978,7 @@
       </c>
       <c r="I10" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>19.306805192294796</v>
+        <v>18.799264608999927</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33007,7 +33007,7 @@
       </c>
       <c r="I11" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>24.771468328268725</v>
+        <v>24.120271749695615</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33036,7 +33036,7 @@
       </c>
       <c r="I12" s="175">
         <f ca="1">Statement!AC157</f>
-        <v>18.900416385591601</v>
+        <v>18.396081714932681</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33065,7 +33065,7 @@
       </c>
       <c r="I13" s="175">
         <f ca="1">Statement!AC158</f>
-        <v>29.522663524047204</v>
+        <v>28.734887081369198</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -33838,7 +33838,7 @@
       </c>
       <c r="I51" s="176">
         <f ca="1">Statement!AC164</f>
-        <v>3.2635314108651101E-2</v>
+        <v>3.3516398911871879E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -33867,7 +33867,7 @@
       </c>
       <c r="I52" s="176">
         <f ca="1">Statement!AC163</f>
-        <v>2.3078896537290578E-2</v>
+        <v>2.3701978176597402E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -33896,7 +33896,7 @@
       </c>
       <c r="I53" s="176">
         <f ca="1">Statement!AC165</f>
-        <v>1.9991004048178321E-4</v>
+        <v>2.053071908843607E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -33925,7 +33925,7 @@
       </c>
       <c r="I54" s="176">
         <f ca="1">Statement!AC166</f>
-        <v>9.315700960693998E-3</v>
+        <v>9.5672052826836843E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -33954,7 +33954,7 @@
       </c>
       <c r="I55" s="176">
         <f ca="1">Statement!AC167</f>
-        <v>9.5157755023405483E-3</v>
+        <v>9.772681415918083E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34190,7 +34190,7 @@
       </c>
       <c r="I68" s="197">
         <f ca="1">Statement!AC178</f>
-        <v>1.4826078727440375E-2</v>
+        <v>1.5226351653100366E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34702,14 +34702,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="236" t="s">
+      <c r="C3" s="238" t="s">
         <v>310</v>
       </c>
-      <c r="D3" s="237"/>
-      <c r="F3" s="238" t="s">
+      <c r="D3" s="239"/>
+      <c r="F3" s="240" t="s">
         <v>311</v>
       </c>
-      <c r="G3" s="237"/>
+      <c r="G3" s="239"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -34776,19 +34776,19 @@
       <c r="B7" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C7" s="239">
+      <c r="C7" s="236">
         <f>Statement!AA88</f>
         <v>0.19798317847549429</v>
       </c>
-      <c r="D7" s="240"/>
-      <c r="F7" s="239">
+      <c r="D7" s="237"/>
+      <c r="F7" s="236">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.85227633788752211</v>
       </c>
-      <c r="G7" s="240"/>
+      <c r="G7" s="237"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="208" t="s">
@@ -34815,19 +34815,19 @@
       <c r="B9" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C9" s="239">
+      <c r="C9" s="236">
         <f>Statement!AA89</f>
         <v>0.20100974521545145</v>
       </c>
-      <c r="D9" s="240"/>
-      <c r="F9" s="239">
+      <c r="D9" s="237"/>
+      <c r="F9" s="236">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.17615269633206854</v>
       </c>
-      <c r="G9" s="240"/>
+      <c r="G9" s="237"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="208" t="s">
@@ -34854,19 +34854,19 @@
       <c r="B11" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C11" s="239">
+      <c r="C11" s="236">
         <f>Statement!AA90</f>
         <v>0.19697414518622902</v>
       </c>
-      <c r="D11" s="240"/>
-      <c r="F11" s="239">
+      <c r="D11" s="237"/>
+      <c r="F11" s="236">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.293272836358182</v>
       </c>
-      <c r="G11" s="240"/>
+      <c r="G11" s="237"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="208" t="s">
@@ -34893,19 +34893,19 @@
       <c r="B13" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C13" s="239">
+      <c r="C13" s="236">
         <f>Statement!AA93</f>
         <v>0.12172505151604357</v>
       </c>
-      <c r="D13" s="240"/>
-      <c r="F13" s="239">
+      <c r="D13" s="237"/>
+      <c r="F13" s="236">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.51510934393638175</v>
       </c>
-      <c r="G13" s="240"/>
+      <c r="G13" s="237"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="208" t="s">
@@ -34932,19 +34932,19 @@
       <c r="B15" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C15" s="239">
+      <c r="C15" s="236">
         <f>Statement!AA94</f>
         <v>0.20851486489537011</v>
       </c>
-      <c r="D15" s="240"/>
-      <c r="F15" s="239">
+      <c r="D15" s="237"/>
+      <c r="F15" s="236">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.4741658193918108</v>
       </c>
-      <c r="G15" s="240"/>
+      <c r="G15" s="237"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="208" t="s">
@@ -34971,19 +34971,19 @@
       <c r="B17" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C17" s="239">
+      <c r="C17" s="236">
         <f>Statement!AA96</f>
         <v>0.35756517690875234</v>
       </c>
-      <c r="D17" s="240"/>
-      <c r="F17" s="239">
+      <c r="D17" s="237"/>
+      <c r="F17" s="236">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>2.1063115845539282</v>
       </c>
-      <c r="G17" s="240"/>
+      <c r="G17" s="237"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="208" t="s">
@@ -35010,22 +35010,22 @@
       <c r="B19" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C19" s="239">
+      <c r="C19" s="236">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-1.6781270464963983E-3</v>
       </c>
-      <c r="D19" s="240"/>
-      <c r="F19" s="239">
+      <c r="D19" s="237"/>
+      <c r="F19" s="236">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-8.9390922758116297E-3</v>
       </c>
-      <c r="G19" s="240"/>
+      <c r="G19" s="237"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="208" t="s">
@@ -35052,22 +35052,22 @@
       <c r="B21" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C21" s="239">
+      <c r="C21" s="236">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.35795454545454553</v>
       </c>
-      <c r="D21" s="240"/>
-      <c r="F21" s="239">
+      <c r="D21" s="237"/>
+      <c r="F21" s="236">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>2.1447368421052633</v>
       </c>
-      <c r="G21" s="240"/>
+      <c r="G21" s="237"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -35115,22 +35115,22 @@
       <c r="B25" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C25" s="239">
+      <c r="C25" s="236">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.11992074288756137</v>
       </c>
-      <c r="D25" s="240"/>
-      <c r="F25" s="239">
+      <c r="D25" s="237"/>
+      <c r="F25" s="236">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>1.1517699869310756</v>
       </c>
-      <c r="G25" s="240"/>
+      <c r="G25" s="237"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="224" t="s">
@@ -35157,22 +35157,22 @@
       <c r="B27" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C27" s="239">
+      <c r="C27" s="236">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.31147368421052629</v>
       </c>
-      <c r="D27" s="240"/>
-      <c r="F27" s="239">
+      <c r="D27" s="237"/>
+      <c r="F27" s="236">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.73741458652907543</v>
       </c>
-      <c r="G27" s="240"/>
+      <c r="G27" s="237"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -35199,22 +35199,22 @@
       <c r="B29" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C29" s="239">
+      <c r="C29" s="236">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.20752960811374652</v>
       </c>
-      <c r="D29" s="240"/>
-      <c r="F29" s="239">
+      <c r="D29" s="237"/>
+      <c r="F29" s="236">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.92385968500715898</v>
       </c>
-      <c r="G29" s="240"/>
+      <c r="G29" s="237"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35241,25 +35241,43 @@
       <c r="B31" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C31" s="239">
+      <c r="C31" s="236">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>9.5647686220540165E-2</v>
       </c>
-      <c r="D31" s="240"/>
-      <c r="F31" s="239">
+      <c r="D31" s="237"/>
+      <c r="F31" s="236">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.28666666666666668</v>
       </c>
-      <c r="G31" s="240"/>
+      <c r="G31" s="237"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C25:D25"/>
@@ -35268,24 +35286,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD18DC50-58F8-7346-A967-A810846FE4E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AEB880D-5739-184D-A679-75D587E12678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="3" activeTab="12" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="8" activeTab="17" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -117,7 +117,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -128,7 +128,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -138,19 +159,28 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
     </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="399">
   <si>
     <t>Ticker</t>
   </si>
@@ -2261,6 +2291,9 @@
     </xf>
     <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2268,9 +2301,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12551,7 +12581,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1yv52&amp;q=XNAS%3aNVDA&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12569,12 +12599,10 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>236.54</v>
-    <v>152.97</v>
-    <v>2.2262</v>
-    <v>-2.75</v>
-    <v>-1.3918E-2</v>
-    <v>-0.4</v>
-    <v>-2.0530000000000001E-3</v>
+    <v>157.34200000000001</v>
+    <v>2.2239</v>
+    <v>2.0994999999999999</v>
+    <v>1.0736000000000001E-2</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -12582,35 +12610,49 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2788 San Tomas Expressway, SANTA CLARA, CA, 95051 US</v>
-    <v>200.05500000000001</v>
+    <v>198.41</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46205.999998460153</v>
+    <v>46210.766732164062</v>
     <v>0</v>
-    <v>192.35</v>
-    <v>4714886000000</v>
+    <v>191.15</v>
+    <v>4783117900000</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
-    <v>197.14</v>
-    <v>30.257400000000001</v>
-    <v>197.58</v>
-    <v>194.83</v>
-    <v>194.43</v>
+    <v>192.27</v>
+    <v>30.267900000000001</v>
+    <v>195.55</v>
+    <v>197.64949999999999</v>
     <v>24200000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>142385548</v>
-    <v>166898435</v>
+    <v>84756134</v>
+    <v>164489929</v>
     <v>1998</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -12624,28 +12666,28 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>0.1</v>
-    <v>2.235E-3</v>
+    <v>-0.06</v>
+    <v>-1.338E-3</v>
     <v>US</v>
-    <v>45.05</v>
+    <v>44.91</v>
     <v>Index</v>
-    <v>3</v>
-    <v>44.53</v>
+    <v>6</v>
+    <v>44.57</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>45.03</v>
-    <v>44.75</v>
+    <v>44.57</v>
     <v>44.85</v>
+    <v>44.79</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>4</v>
+    <v>7</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12667,8 +12709,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12689,7 +12729,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12699,6 +12738,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12734,7 +12778,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="45">
+    <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12745,16 +12789,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -12848,19 +12889,13 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="4">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -12932,9 +12967,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -12942,9 +12974,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13429,18 +13458,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="232" t="s">
+      <c r="B2" s="233" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="233"/>
-      <c r="E2" s="232" t="s">
+      <c r="C2" s="234"/>
+      <c r="E2" s="233" t="s">
         <v>284</v>
       </c>
-      <c r="F2" s="233"/>
-      <c r="H2" s="232" t="s">
+      <c r="F2" s="234"/>
+      <c r="H2" s="233" t="s">
         <v>325</v>
       </c>
-      <c r="I2" s="233"/>
+      <c r="I2" s="234"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="186" t="s">
@@ -13455,7 +13484,7 @@
       </c>
       <c r="F3" s="188">
         <f ca="1">Statement!AC155</f>
-        <v>4735343.1500000004</v>
+        <v>4803871.0975000001</v>
       </c>
       <c r="H3" s="186" t="str">
         <f>'AVG target price'!B5</f>
@@ -13479,7 +13508,7 @@
       </c>
       <c r="F4" s="189">
         <f ca="1">Statement!AC156</f>
-        <v>4663241.1500000004</v>
+        <v>4731769.0975000001</v>
       </c>
       <c r="H4" s="186" t="str">
         <f>'AVG target price'!B6</f>
@@ -13487,7 +13516,7 @@
       </c>
       <c r="I4" s="212">
         <f>'AVG target price'!C6</f>
-        <v>364.31185306105914</v>
+        <v>367.27840315363267</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13496,7 +13525,7 @@
       </c>
       <c r="C5" s="209" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>194.83</v>
+        <v>197.64949999999999</v>
       </c>
       <c r="E5" s="186" t="s">
         <v>240</v>
@@ -13518,16 +13547,16 @@
       <c r="B6" s="186" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="209" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>194.43</v>
+      <c r="C6" s="209" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="186" t="s">
         <v>234</v>
       </c>
       <c r="F6" s="191">
         <f ca="1">Statement!AC152</f>
-        <v>29.836140888208273</v>
+        <v>30.267917304747321</v>
       </c>
       <c r="H6" s="186" t="str">
         <f>'AVG target price'!B8</f>
@@ -13535,7 +13564,7 @@
       </c>
       <c r="I6" s="212">
         <f>'AVG target price'!C8</f>
-        <v>350.07748183234139</v>
+        <v>353.04403192491492</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13544,14 +13573,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-2.75</v>
+        <v>2.0994999999999999</v>
       </c>
       <c r="E7" s="187" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="192">
         <f ca="1">Statement!AC153</f>
-        <v>18.799264608999927</v>
+        <v>19.071319870330704</v>
       </c>
       <c r="H7" s="185" t="str">
         <f>'AVG target price'!B9</f>
@@ -13559,23 +13588,23 @@
       </c>
       <c r="I7" s="213">
         <f>'AVG target price'!C9</f>
-        <v>296.75295163459498</v>
+        <v>298.23622668088177</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="186" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.4</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="186" t="s">
         <v>262</v>
       </c>
       <c r="F8" s="193">
         <f ca="1">Statement!AC163</f>
-        <v>2.3701978176597402E-2</v>
+        <v>2.3363865874421498E-2</v>
       </c>
       <c r="H8" s="185" t="str">
         <f>'AVG target price'!B11</f>
@@ -13583,7 +13612,7 @@
       </c>
       <c r="I8" s="214">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.52313787216853136</v>
+        <v>0.50891465286217163</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13592,30 +13621,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-1.3918E-2</v>
+        <v>1.0736000000000001E-2</v>
       </c>
       <c r="E9" s="186" t="s">
         <v>285</v>
       </c>
       <c r="F9" s="193">
         <f ca="1">Statement!AC164</f>
-        <v>3.3516398911871879E-2</v>
+        <v>3.303828241407137E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="186" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-2.0530000000000001E-3</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="186" t="s">
         <v>290</v>
       </c>
       <c r="F10" s="193">
         <f ca="1">Statement!AC166</f>
-        <v>9.5672052826836843E-3</v>
+        <v>9.4307276528666269E-3</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13631,7 +13660,7 @@
       </c>
       <c r="F11" s="194">
         <f ca="1">Statement!AC165</f>
-        <v>2.053071908843607E-4</v>
+        <v>2.0237845276613401E-4</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13640,7 +13669,7 @@
       </c>
       <c r="C12" s="210" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>152.97</v>
+        <v>157.34200000000001</v>
       </c>
       <c r="E12" s="186" t="s">
         <v>94</v>
@@ -13656,7 +13685,7 @@
       </c>
       <c r="C13" s="210" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.2262</v>
+        <v>2.2239</v>
       </c>
       <c r="E13" s="186" t="s">
         <v>96</v>
@@ -13672,7 +13701,7 @@
       </c>
       <c r="C14" s="211" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>166898435</v>
+        <v>164489929</v>
       </c>
       <c r="E14" s="187" t="s">
         <v>97</v>
@@ -13688,7 +13717,7 @@
       </c>
       <c r="F15" s="193">
         <f ca="1">Statement!AC178</f>
-        <v>1.5226351653100366E-2</v>
+        <v>1.5009145444706638E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13701,10 +13730,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="234" t="s">
+      <c r="B17" s="235" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="234"/>
+      <c r="C17" s="235"/>
       <c r="E17" s="185" t="s">
         <v>293</v>
       </c>
@@ -13777,14 +13806,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="234" t="s">
+      <c r="B25" s="235" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="234"/>
-      <c r="E25" s="232" t="s">
+      <c r="C25" s="235"/>
+      <c r="E25" s="233" t="s">
         <v>340</v>
       </c>
-      <c r="F25" s="233"/>
+      <c r="F25" s="234"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="185" t="s">
@@ -13793,12 +13822,12 @@
       <c r="C26" s="171">
         <v>0.21</v>
       </c>
-      <c r="E26" s="186" t="e" vm="2">
+      <c r="E26" s="186" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="220" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>44.85</v>
+        <v>44.79</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13813,7 +13842,7 @@
       </c>
       <c r="F27" s="221">
         <f ca="1">F26/1000</f>
-        <v>4.4850000000000001E-2</v>
+        <v>4.4789999999999996E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -13833,15 +13862,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="235" t="s">
+      <c r="B33" s="232" t="s">
         <v>335</v>
       </c>
-      <c r="C33" s="235"/>
-      <c r="D33" s="235"/>
-      <c r="E33" s="235"/>
-      <c r="F33" s="235"/>
-      <c r="G33" s="235"/>
-      <c r="H33" s="235"/>
+      <c r="C33" s="232"/>
+      <c r="D33" s="232"/>
+      <c r="E33" s="232"/>
+      <c r="F33" s="232"/>
+      <c r="G33" s="232"/>
+      <c r="H33" s="232"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -13860,24 +13889,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="235"/>
-      <c r="C39" s="235"/>
-      <c r="D39" s="235"/>
-      <c r="E39" s="235"/>
-      <c r="F39" s="235"/>
-      <c r="G39" s="235"/>
-      <c r="H39" s="235"/>
+      <c r="B39" s="232"/>
+      <c r="C39" s="232"/>
+      <c r="D39" s="232"/>
+      <c r="E39" s="232"/>
+      <c r="F39" s="232"/>
+      <c r="G39" s="232"/>
+      <c r="H39" s="232"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="235" t="s">
+      <c r="B42" s="232" t="s">
         <v>338</v>
       </c>
-      <c r="C42" s="235"/>
-      <c r="D42" s="235"/>
-      <c r="E42" s="235"/>
-      <c r="F42" s="235"/>
-      <c r="G42" s="235"/>
-      <c r="H42" s="235"/>
+      <c r="C42" s="232"/>
+      <c r="D42" s="232"/>
+      <c r="E42" s="232"/>
+      <c r="F42" s="232"/>
+      <c r="G42" s="232"/>
+      <c r="H42" s="232"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -13892,24 +13921,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="235"/>
-      <c r="C49" s="235"/>
-      <c r="D49" s="235"/>
-      <c r="E49" s="235"/>
-      <c r="F49" s="235"/>
-      <c r="G49" s="235"/>
-      <c r="H49" s="235"/>
+      <c r="B49" s="232"/>
+      <c r="C49" s="232"/>
+      <c r="D49" s="232"/>
+      <c r="E49" s="232"/>
+      <c r="F49" s="232"/>
+      <c r="G49" s="232"/>
+      <c r="H49" s="232"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="235" t="s">
+      <c r="B52" s="232" t="s">
         <v>101</v>
       </c>
-      <c r="C52" s="235"/>
-      <c r="D52" s="235"/>
-      <c r="E52" s="235"/>
-      <c r="F52" s="235"/>
-      <c r="G52" s="235"/>
-      <c r="H52" s="235"/>
+      <c r="C52" s="232"/>
+      <c r="D52" s="232"/>
+      <c r="E52" s="232"/>
+      <c r="F52" s="232"/>
+      <c r="G52" s="232"/>
+      <c r="H52" s="232"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -13924,13 +13953,13 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="235"/>
-      <c r="C59" s="235"/>
-      <c r="D59" s="235"/>
-      <c r="E59" s="235"/>
-      <c r="F59" s="235"/>
-      <c r="G59" s="235"/>
-      <c r="H59" s="235"/>
+      <c r="B59" s="232"/>
+      <c r="C59" s="232"/>
+      <c r="D59" s="232"/>
+      <c r="E59" s="232"/>
+      <c r="F59" s="232"/>
+      <c r="G59" s="232"/>
+      <c r="H59" s="232"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -14015,36 +14044,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="232" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="235" t="s">
+      <c r="S2" s="232" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="235"/>
-      <c r="U2" s="235"/>
-      <c r="V2" s="235"/>
-      <c r="W2" s="235"/>
-      <c r="X2" s="235"/>
-      <c r="Y2" s="235"/>
-      <c r="Z2" s="235"/>
-      <c r="AA2" s="235" t="s">
+      <c r="T2" s="232"/>
+      <c r="U2" s="232"/>
+      <c r="V2" s="232"/>
+      <c r="W2" s="232"/>
+      <c r="X2" s="232"/>
+      <c r="Y2" s="232"/>
+      <c r="Z2" s="232"/>
+      <c r="AA2" s="232" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="235"/>
-      <c r="AC2" s="235"/>
+      <c r="AB2" s="232"/>
+      <c r="AC2" s="232"/>
       <c r="AE2" s="85" t="s">
         <v>107</v>
       </c>
@@ -15240,35 +15269,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="232" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
-      <c r="P2" s="235" t="s">
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
+      <c r="P2" s="232" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="235"/>
-      <c r="R2" s="235"/>
-      <c r="S2" s="235"/>
-      <c r="T2" s="235"/>
-      <c r="U2" s="235"/>
-      <c r="V2" s="235"/>
-      <c r="W2" s="235"/>
-      <c r="X2" s="235" t="s">
+      <c r="Q2" s="232"/>
+      <c r="R2" s="232"/>
+      <c r="S2" s="232"/>
+      <c r="T2" s="232"/>
+      <c r="U2" s="232"/>
+      <c r="V2" s="232"/>
+      <c r="W2" s="232"/>
+      <c r="X2" s="232" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="235"/>
-      <c r="Z2" s="235"/>
+      <c r="Y2" s="232"/>
+      <c r="Z2" s="232"/>
       <c r="AB2" s="85" t="s">
         <v>107</v>
       </c>
@@ -16499,20 +16528,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="232" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
+      <c r="D3" s="232"/>
+      <c r="E3" s="232"/>
+      <c r="F3" s="232"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="232"/>
+      <c r="J3" s="232"/>
+      <c r="K3" s="232"/>
+      <c r="L3" s="232"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -17955,20 +17984,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="232" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
       <c r="S2" s="246"/>
       <c r="T2" s="246"/>
       <c r="U2" s="246"/>
@@ -19049,10 +19078,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="232" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="235"/>
+      <c r="C4" s="232"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19069,7 +19098,7 @@
       </c>
       <c r="C6" s="134">
         <f ca="1">Overview!C5</f>
-        <v>194.83</v>
+        <v>197.64949999999999</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19078,7 +19107,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">C5*C6</f>
-        <v>4735343.1500000004</v>
+        <v>4803871.0975000001</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19096,7 +19125,7 @@
       </c>
       <c r="C9" s="136">
         <f ca="1">Overview!F27</f>
-        <v>4.4850000000000001E-2</v>
+        <v>4.4789999999999996E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19105,7 +19134,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C13</f>
-        <v>2.2262</v>
+        <v>2.2239</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19137,10 +19166,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="235" t="s">
+      <c r="B15" s="232" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="235"/>
+      <c r="C15" s="232"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19148,7 +19177,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>1.7854834775690943E-3</v>
+        <v>1.760058114833162E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19157,7 +19186,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99821451652243087</v>
+        <v>0.99823994188516685</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19175,7 +19204,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14502899999999999</v>
+        <v>0.14486549999999998</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19184,7 +19213,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14484199024604286</v>
+        <v>0.14468144104261224</v>
       </c>
     </row>
   </sheetData>
@@ -19229,20 +19258,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="232" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
+      <c r="D3" s="232"/>
+      <c r="E3" s="232"/>
+      <c r="F3" s="232"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="232"/>
+      <c r="J3" s="232"/>
+      <c r="K3" s="232"/>
+      <c r="L3" s="232"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -19528,10 +19557,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="235" t="s">
+      <c r="B13" s="232" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="235"/>
+      <c r="C13" s="232"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -19551,10 +19580,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="235" t="s">
+      <c r="B18" s="232" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="235"/>
+      <c r="C18" s="232"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -19646,7 +19675,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D33819-10E3-B843-9B8A-30FFCAB234A7}">
-  <dimension ref="A1:N61"/>
+  <dimension ref="A1:N67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="83" customWidth="1"/>
@@ -19668,20 +19697,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="232" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -20613,10 +20642,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="235" t="s">
+      <c r="B37" s="232" t="s">
         <v>197</v>
       </c>
-      <c r="C37" s="235"/>
+      <c r="C37" s="232"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -20665,155 +20694,209 @@
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C43" s="137">
+        <f>Statement!AC105</f>
+        <v>80572</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B44" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C44" s="137">
+        <f>Statement!AC106</f>
+        <v>8470</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B45" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C45" s="24">
+        <f>C42+C43-C44</f>
+        <v>8926701.588649042</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B46" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C43" s="88">
+      <c r="C46" s="88">
         <f>Statement!AC77</f>
         <v>24305</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B44" s="142" t="s">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B47" s="142" t="s">
         <v>201</v>
       </c>
-      <c r="C44" s="143">
-        <f>C42/C43</f>
-        <v>364.31185306105914</v>
-      </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="235" t="s">
+      <c r="C47" s="143">
+        <f>C45/C46</f>
+        <v>367.27840315363267</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B49" s="232" t="s">
         <v>202</v>
       </c>
-      <c r="C46" s="235"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B47" s="1" t="s">
+      <c r="C49" s="232"/>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B50" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="C47" s="64">
+      <c r="C50" s="64">
         <f>L6</f>
         <v>1256848.3311313502</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B48" s="1" t="s">
+    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B51" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C48" s="136">
+      <c r="C51" s="136">
         <f>Overview!C29</f>
         <v>0.12</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="39" t="s">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B52" s="39" t="s">
         <v>204</v>
       </c>
-      <c r="C49" s="105">
+      <c r="C52" s="105">
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B50" s="1" t="s">
+    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B53" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C50" s="24">
+      <c r="C53" s="24">
         <f>L18</f>
         <v>23429.712685180726</v>
       </c>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B51" s="1" t="s">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B54" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C51" s="24">
-        <f>(C47*C49)/C50</f>
+      <c r="C54" s="24">
+        <f>(C50*C52)/C53</f>
         <v>536.4335226894633</v>
       </c>
     </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="142" t="s">
+    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B55" s="142" t="s">
         <v>201</v>
       </c>
-      <c r="C52" s="143">
-        <f>C51/(1+C48)^5</f>
+      <c r="C55" s="143">
+        <f>C54/(1+C51)^5</f>
         <v>304.38678708173404</v>
       </c>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="235" t="s">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B57" s="232" t="s">
         <v>319</v>
       </c>
-      <c r="C54" s="235"/>
-    </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55" s="1" t="s">
+      <c r="C57" s="232"/>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B58" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="C55" s="64">
+      <c r="C58" s="64">
         <f>L8</f>
         <v>496659.91370982229</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B56" s="1" t="s">
+    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B59" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C56" s="136">
+      <c r="C59" s="136">
         <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
         <v>0.12</v>
       </c>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="39" t="s">
+    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B60" s="39" t="s">
         <v>387</v>
       </c>
-      <c r="C57" s="105">
+      <c r="C60" s="105">
         <v>30</v>
       </c>
     </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B58" s="1" t="s">
+    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B61" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="C58" s="24">
-        <f>(C55*C57)</f>
+      <c r="C61" s="24">
+        <f>(C58*C60)</f>
         <v>14899797.411294669</v>
       </c>
     </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B59" s="1" t="s">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B62" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="C59" s="24">
-        <f>C58/(1+C56)^5-G30+G31</f>
+      <c r="C62" s="24">
+        <f>C61/(1+C59)^5-G30+G31</f>
         <v>8508633.1959350575</v>
       </c>
     </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="1" t="s">
+    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B63" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C63" s="137">
+        <f>Statement!AC105</f>
+        <v>80572</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B64" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C64" s="137">
+        <f>Statement!AC106</f>
+        <v>8470</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B65" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C65" s="24">
+        <f>C62+C63-C64</f>
+        <v>8580735.1959350575</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B66" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C60" s="88">
+      <c r="C66" s="88">
         <f>Statement!AC77</f>
         <v>24305</v>
       </c>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B61" s="142" t="s">
+    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B67" s="142" t="s">
         <v>201</v>
       </c>
-      <c r="C61" s="143">
-        <f>C59/C60</f>
-        <v>350.07748183234139</v>
+      <c r="C67" s="143">
+        <f>C65/C66</f>
+        <v>353.04403192491492</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B57:C57"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
@@ -20857,10 +20940,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="232" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="235"/>
+      <c r="C4" s="232"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -20877,8 +20960,8 @@
         <v>209</v>
       </c>
       <c r="C6" s="134">
-        <f>Multiples!C44</f>
-        <v>364.31185306105914</v>
+        <f>Multiples!C47</f>
+        <v>367.27840315363267</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -20886,7 +20969,7 @@
         <v>210</v>
       </c>
       <c r="C7" s="134">
-        <f>Multiples!C52</f>
+        <f>Multiples!C55</f>
         <v>304.38678708173404</v>
       </c>
     </row>
@@ -20895,8 +20978,8 @@
         <v>320</v>
       </c>
       <c r="C8" s="134">
-        <f>Multiples!C61</f>
-        <v>350.07748183234139</v>
+        <f>Multiples!C67</f>
+        <v>353.04403192491492</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -20905,7 +20988,7 @@
       </c>
       <c r="C9" s="143">
         <f>AVERAGE(C5:C8)</f>
-        <v>296.75295163459498</v>
+        <v>298.23622668088177</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -20914,7 +20997,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C5</f>
-        <v>194.83</v>
+        <v>197.64949999999999</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -20923,7 +21006,7 @@
       </c>
       <c r="C11" s="155">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.52313787216853136</v>
+        <v>0.50891465286217163</v>
       </c>
     </row>
   </sheetData>
@@ -20988,20 +21071,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="232" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
+      <c r="D3" s="232"/>
+      <c r="E3" s="232"/>
+      <c r="F3" s="232"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="232"/>
+      <c r="J3" s="232"/>
+      <c r="K3" s="232"/>
+      <c r="L3" s="232"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -21281,7 +21364,7 @@
       </c>
       <c r="C15" s="157">
         <f ca="1">Overview!C5</f>
-        <v>194.83</v>
+        <v>197.64949999999999</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -21347,7 +21430,7 @@
       </c>
       <c r="C23" s="162">
         <f ca="1">C15*C22</f>
-        <v>4714886</v>
+        <v>4783117.8999999994</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -21374,7 +21457,7 @@
       </c>
       <c r="C26" s="163">
         <f ca="1">C23+C25-C24</f>
-        <v>4642784</v>
+        <v>4711015.8999999994</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -28408,7 +28491,7 @@
       <c r="AA114" s="68"/>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>194.83</v>
+        <v>197.64949999999999</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -28455,7 +28538,7 @@
       <c r="AA115" s="68"/>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>194.83</v>
+        <v>197.64949999999999</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29957,7 +30040,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>29.836140888208273</v>
+        <v>30.267917304747321</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -29994,7 +30077,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>18.799264608999927</v>
+        <v>19.071319870330704</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30031,7 +30114,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>24.120271749695615</v>
+        <v>24.469330448039127</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30068,7 +30151,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="144">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>4735343.1500000004</v>
+        <v>4803871.0975000001</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30105,7 +30188,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="144">
         <f ca="1">AC155+AC106-AC105+AC47+AC44</f>
-        <v>4663241.1500000004</v>
+        <v>4731769.0975000001</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -30142,7 +30225,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="184">
         <f ca="1">AC156/AC5</f>
-        <v>18.396081714932681</v>
+        <v>18.666418521762115</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -30179,7 +30262,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="184">
         <f ca="1">AC156/AC11</f>
-        <v>28.734887081369198</v>
+        <v>29.157156222078441</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -30314,7 +30397,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="72">
         <f t="shared" ref="AC161:AC162" ca="1" si="96">AC155/AC159</f>
-        <v>42.190571291107211</v>
+        <v>42.801135966748937</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -30351,7 +30434,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ca="1" si="96"/>
-        <v>36.771691186331154</v>
+        <v>37.312063953264534</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -30388,7 +30471,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="74">
         <f t="shared" ref="AC163" ca="1" si="99">AC159/AC155</f>
-        <v>2.3701978176597402E-2</v>
+        <v>2.3363865874421498E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -30425,7 +30508,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>3.3516398911871879E-2</v>
+        <v>3.303828241407137E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -30462,7 +30545,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="155">
         <f ca="1">AC81/AC115</f>
-        <v>2.053071908843607E-4</v>
+        <v>2.0237845276613401E-4</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -30499,7 +30582,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="155">
         <f ca="1">-AC62/AC155</f>
-        <v>9.5672052826836843E-3</v>
+        <v>9.4307276528666269E-3</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -30536,7 +30619,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="155">
         <f ca="1">-(AC62+AC63)/AC155</f>
-        <v>9.772681415918083E-3</v>
+        <v>9.6332726379946328E-3</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31039,7 +31122,7 @@
       <c r="AA178" s="49"/>
       <c r="AC178" s="155">
         <f ca="1">(AC105-AC106)/AC155</f>
-        <v>1.5226351653100366E-2</v>
+        <v>1.5009145444706638E-2</v>
       </c>
     </row>
     <row r="179" spans="1:31" x14ac:dyDescent="0.2">
@@ -32204,15 +32287,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="232" t="s">
         <v>230</v>
       </c>
-      <c r="C4" s="235"/>
-      <c r="E4" s="235" t="s">
+      <c r="C4" s="232"/>
+      <c r="E4" s="232" t="s">
         <v>237</v>
       </c>
-      <c r="F4" s="235"/>
-      <c r="G4" s="235"/>
+      <c r="F4" s="232"/>
+      <c r="G4" s="232"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -32220,7 +32303,7 @@
       </c>
       <c r="C5" s="173">
         <f ca="1">Overview!C5</f>
-        <v>194.83</v>
+        <v>197.64949999999999</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="133" t="s">
@@ -32236,7 +32319,7 @@
       </c>
       <c r="C6" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>4735343.1500000004</v>
+        <v>4803871.0975000001</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -32256,7 +32339,7 @@
       </c>
       <c r="C7" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>4663241.1500000004</v>
+        <v>4731769.0975000001</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -32276,7 +32359,7 @@
       </c>
       <c r="C8" s="175">
         <f ca="1">Statement!AC152</f>
-        <v>29.836140888208273</v>
+        <v>30.267917304747321</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>240</v>
@@ -32296,7 +32379,7 @@
       </c>
       <c r="C9" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>18.799264608999927</v>
+        <v>19.071319870330704</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>241</v>
@@ -32316,7 +32399,7 @@
       </c>
       <c r="C10" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>24.120271749695615</v>
+        <v>24.469330448039127</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -32336,7 +32419,7 @@
       </c>
       <c r="C11" s="175">
         <f ca="1">Statement!AC157</f>
-        <v>18.396081714932681</v>
+        <v>18.666418521762115</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -32345,18 +32428,18 @@
       </c>
       <c r="C12" s="175">
         <f ca="1">Statement!AC158</f>
-        <v>28.734887081369198</v>
+        <v>29.157156222078441</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="235" t="s">
+      <c r="B15" s="232" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="235"/>
-      <c r="E15" s="235" t="s">
+      <c r="C15" s="232"/>
+      <c r="E15" s="232" t="s">
         <v>243</v>
       </c>
-      <c r="F15" s="235"/>
+      <c r="F15" s="232"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -32407,14 +32490,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="235" t="s">
+      <c r="B21" s="232" t="s">
         <v>242</v>
       </c>
-      <c r="C21" s="235"/>
-      <c r="E21" s="235" t="s">
+      <c r="C21" s="232"/>
+      <c r="E21" s="232" t="s">
         <v>246</v>
       </c>
-      <c r="F21" s="235"/>
+      <c r="F21" s="232"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -32483,14 +32566,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="235" t="s">
+      <c r="B29" s="232" t="s">
         <v>247</v>
       </c>
-      <c r="C29" s="235"/>
-      <c r="E29" s="235" t="s">
+      <c r="C29" s="232"/>
+      <c r="E29" s="232" t="s">
         <v>253</v>
       </c>
-      <c r="F29" s="235"/>
+      <c r="F29" s="232"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -32566,14 +32649,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="235" t="s">
+      <c r="B37" s="232" t="s">
         <v>265</v>
       </c>
-      <c r="C37" s="235"/>
-      <c r="E37" s="235" t="s">
+      <c r="C37" s="232"/>
+      <c r="E37" s="232" t="s">
         <v>268</v>
       </c>
-      <c r="F37" s="235"/>
+      <c r="F37" s="232"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -32581,7 +32664,7 @@
       </c>
       <c r="C38" s="176">
         <f ca="1">Statement!AC164</f>
-        <v>3.3516398911871879E-2</v>
+        <v>3.303828241407137E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>267</v>
@@ -32597,7 +32680,7 @@
       </c>
       <c r="C39" s="216">
         <f ca="1">Statement!AC163</f>
-        <v>2.3701978176597402E-2</v>
+        <v>2.3363865874421498E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>269</v>
@@ -32613,7 +32696,7 @@
       </c>
       <c r="C40" s="176">
         <f ca="1">Statement!AC165</f>
-        <v>2.053071908843607E-4</v>
+        <v>2.0237845276613401E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>270</v>
@@ -32629,7 +32712,7 @@
       </c>
       <c r="C41" s="176">
         <f ca="1">Statement!AC166</f>
-        <v>9.5672052826836843E-3</v>
+        <v>9.4307276528666269E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -32638,18 +32721,18 @@
       </c>
       <c r="C42" s="176">
         <f ca="1">Statement!AC167</f>
-        <v>9.772681415918083E-3</v>
+        <v>9.6332726379946328E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="235" t="s">
+      <c r="B45" s="232" t="s">
         <v>276</v>
       </c>
-      <c r="C45" s="235"/>
-      <c r="E45" s="235" t="s">
+      <c r="C45" s="232"/>
+      <c r="E45" s="232" t="s">
         <v>282</v>
       </c>
-      <c r="F45" s="235"/>
+      <c r="F45" s="232"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -32682,18 +32765,18 @@
       </c>
       <c r="F48" s="176">
         <f ca="1">Statement!AC178</f>
-        <v>1.5226351653100366E-2</v>
+        <v>1.5009145444706638E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="235" t="s">
+      <c r="B51" s="232" t="s">
         <v>279</v>
       </c>
-      <c r="C51" s="235"/>
-      <c r="E51" s="235" t="s">
+      <c r="C51" s="232"/>
+      <c r="E51" s="232" t="s">
         <v>300</v>
       </c>
-      <c r="F51" s="235"/>
+      <c r="F51" s="232"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -32862,7 +32945,7 @@
       </c>
       <c r="I6" s="173">
         <f ca="1">Statement!AC114</f>
-        <v>194.83</v>
+        <v>197.64949999999999</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -32891,7 +32974,7 @@
       </c>
       <c r="I7" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>4735343.1500000004</v>
+        <v>4803871.0975000001</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -32920,7 +33003,7 @@
       </c>
       <c r="I8" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>4663241.1500000004</v>
+        <v>4731769.0975000001</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -32949,7 +33032,7 @@
       </c>
       <c r="I9" s="175">
         <f ca="1">Statement!AC152</f>
-        <v>29.836140888208273</v>
+        <v>30.267917304747321</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -32978,7 +33061,7 @@
       </c>
       <c r="I10" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>18.799264608999927</v>
+        <v>19.071319870330704</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33007,7 +33090,7 @@
       </c>
       <c r="I11" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>24.120271749695615</v>
+        <v>24.469330448039127</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33036,7 +33119,7 @@
       </c>
       <c r="I12" s="175">
         <f ca="1">Statement!AC157</f>
-        <v>18.396081714932681</v>
+        <v>18.666418521762115</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33065,7 +33148,7 @@
       </c>
       <c r="I13" s="175">
         <f ca="1">Statement!AC158</f>
-        <v>28.734887081369198</v>
+        <v>29.157156222078441</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -33838,7 +33921,7 @@
       </c>
       <c r="I51" s="176">
         <f ca="1">Statement!AC164</f>
-        <v>3.3516398911871879E-2</v>
+        <v>3.303828241407137E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -33867,7 +33950,7 @@
       </c>
       <c r="I52" s="176">
         <f ca="1">Statement!AC163</f>
-        <v>2.3701978176597402E-2</v>
+        <v>2.3363865874421498E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -33896,7 +33979,7 @@
       </c>
       <c r="I53" s="176">
         <f ca="1">Statement!AC165</f>
-        <v>2.053071908843607E-4</v>
+        <v>2.0237845276613401E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -33925,7 +34008,7 @@
       </c>
       <c r="I54" s="176">
         <f ca="1">Statement!AC166</f>
-        <v>9.5672052826836843E-3</v>
+        <v>9.4307276528666269E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -33954,7 +34037,7 @@
       </c>
       <c r="I55" s="176">
         <f ca="1">Statement!AC167</f>
-        <v>9.772681415918083E-3</v>
+        <v>9.6332726379946328E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34190,7 +34273,7 @@
       </c>
       <c r="I68" s="197">
         <f ca="1">Statement!AC178</f>
-        <v>1.5226351653100366E-2</v>
+        <v>1.5009145444706638E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">

--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AEB880D-5739-184D-A679-75D587E12678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BBDB40E-135B-084E-B5B0-5F81F16110AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="8" activeTab="17" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -117,7 +117,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -128,28 +128,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -159,21 +138,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2291,9 +2261,6 @@
     </xf>
     <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2301,6 +2268,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12581,7 +12551,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1yv52&amp;q=XNAS%3aNVDA&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12599,10 +12569,12 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>236.54</v>
-    <v>157.34200000000001</v>
-    <v>2.2239</v>
-    <v>2.0994999999999999</v>
-    <v>1.0736000000000001E-2</v>
+    <v>161.61000000000001</v>
+    <v>2.2223000000000002</v>
+    <v>8.18</v>
+    <v>4.0339E-2</v>
+    <v>-0.59</v>
+    <v>-2.797E-3</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -12610,49 +12582,35 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2788 San Tomas Expressway, SANTA CLARA, CA, 95051 US</v>
-    <v>198.41</v>
+    <v>211</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46210.766732164062</v>
+    <v>46213.886782082809</v>
     <v>0</v>
-    <v>191.15</v>
-    <v>4783117900000</v>
+    <v>201.92</v>
+    <v>5105232000000</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
-    <v>192.27</v>
-    <v>30.267900000000001</v>
-    <v>195.55</v>
-    <v>197.64949999999999</v>
+    <v>202</v>
+    <v>32.3063</v>
+    <v>202.78</v>
+    <v>210.96</v>
+    <v>210.37</v>
     <v>24200000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>84756134</v>
-    <v>164489929</v>
+    <v>147771633</v>
+    <v>152809403</v>
     <v>1998</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -12666,28 +12624,28 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.06</v>
-    <v>-1.338E-3</v>
+    <v>-0.3</v>
+    <v>-6.5659999999999998E-3</v>
     <v>US</v>
-    <v>44.91</v>
+    <v>45.81</v>
     <v>Index</v>
-    <v>6</v>
-    <v>44.57</v>
+    <v>3</v>
+    <v>45.29</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>44.57</v>
-    <v>44.85</v>
-    <v>44.79</v>
+    <v>45.77</v>
+    <v>45.69</v>
+    <v>45.39</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12709,6 +12667,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12729,6 +12689,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12738,11 +12699,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12778,7 +12734,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12789,13 +12745,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -12889,13 +12848,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -12967,6 +12932,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -12974,6 +12942,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13458,18 +13429,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="233" t="s">
+      <c r="B2" s="232" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="234"/>
-      <c r="E2" s="233" t="s">
+      <c r="C2" s="233"/>
+      <c r="E2" s="232" t="s">
         <v>284</v>
       </c>
-      <c r="F2" s="234"/>
-      <c r="H2" s="233" t="s">
+      <c r="F2" s="233"/>
+      <c r="H2" s="232" t="s">
         <v>325</v>
       </c>
-      <c r="I2" s="234"/>
+      <c r="I2" s="233"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="186" t="s">
@@ -13484,7 +13455,7 @@
       </c>
       <c r="F3" s="188">
         <f ca="1">Statement!AC155</f>
-        <v>4803871.0975000001</v>
+        <v>5127382.8</v>
       </c>
       <c r="H3" s="186" t="str">
         <f>'AVG target price'!B5</f>
@@ -13508,7 +13479,7 @@
       </c>
       <c r="F4" s="189">
         <f ca="1">Statement!AC156</f>
-        <v>4731769.0975000001</v>
+        <v>5055280.8</v>
       </c>
       <c r="H4" s="186" t="str">
         <f>'AVG target price'!B6</f>
@@ -13525,7 +13496,7 @@
       </c>
       <c r="C5" s="209" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>197.64949999999999</v>
+        <v>210.96</v>
       </c>
       <c r="E5" s="186" t="s">
         <v>240</v>
@@ -13547,16 +13518,16 @@
       <c r="B6" s="186" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="209" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="209" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>210.37</v>
       </c>
       <c r="E6" s="186" t="s">
         <v>234</v>
       </c>
       <c r="F6" s="191">
         <f ca="1">Statement!AC152</f>
-        <v>30.267917304747321</v>
+        <v>32.306278713629411</v>
       </c>
       <c r="H6" s="186" t="str">
         <f>'AVG target price'!B8</f>
@@ -13573,14 +13544,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>2.0994999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="E7" s="187" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="192">
         <f ca="1">Statement!AC153</f>
-        <v>19.071319870330704</v>
+        <v>20.355658070700738</v>
       </c>
       <c r="H7" s="185" t="str">
         <f>'AVG target price'!B9</f>
@@ -13595,16 +13566,16 @@
       <c r="B8" s="186" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>-0.59</v>
       </c>
       <c r="E8" s="186" t="s">
         <v>262</v>
       </c>
       <c r="F8" s="193">
         <f ca="1">Statement!AC163</f>
-        <v>2.3363865874421498E-2</v>
+        <v>2.1889725104979486E-2</v>
       </c>
       <c r="H8" s="185" t="str">
         <f>'AVG target price'!B11</f>
@@ -13612,7 +13583,7 @@
       </c>
       <c r="I8" s="214">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.50891465286217163</v>
+        <v>0.41370983447516951</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13621,30 +13592,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>1.0736000000000001E-2</v>
+        <v>4.0339E-2</v>
       </c>
       <c r="E9" s="186" t="s">
         <v>285</v>
       </c>
       <c r="F9" s="193">
         <f ca="1">Statement!AC164</f>
-        <v>3.303828241407137E-2</v>
+        <v>3.0953735305271138E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="186" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>-2.797E-3</v>
       </c>
       <c r="E10" s="186" t="s">
         <v>290</v>
       </c>
       <c r="F10" s="193">
         <f ca="1">Statement!AC166</f>
-        <v>9.4307276528666269E-3</v>
+        <v>8.835696839330975E-3</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13660,7 +13631,7 @@
       </c>
       <c r="F11" s="194">
         <f ca="1">Statement!AC165</f>
-        <v>2.0237845276613401E-4</v>
+        <v>1.8960940462646946E-4</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13669,7 +13640,7 @@
       </c>
       <c r="C12" s="210" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>157.34200000000001</v>
+        <v>161.61000000000001</v>
       </c>
       <c r="E12" s="186" t="s">
         <v>94</v>
@@ -13685,7 +13656,7 @@
       </c>
       <c r="C13" s="210" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.2239</v>
+        <v>2.2223000000000002</v>
       </c>
       <c r="E13" s="186" t="s">
         <v>96</v>
@@ -13701,7 +13672,7 @@
       </c>
       <c r="C14" s="211" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>164489929</v>
+        <v>152809403</v>
       </c>
       <c r="E14" s="187" t="s">
         <v>97</v>
@@ -13717,7 +13688,7 @@
       </c>
       <c r="F15" s="193">
         <f ca="1">Statement!AC178</f>
-        <v>1.5009145444706638E-2</v>
+        <v>1.4062144921186693E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13730,10 +13701,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="235" t="s">
+      <c r="B17" s="234" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="235"/>
+      <c r="C17" s="234"/>
       <c r="E17" s="185" t="s">
         <v>293</v>
       </c>
@@ -13806,14 +13777,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="235" t="s">
+      <c r="B25" s="234" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="235"/>
-      <c r="E25" s="233" t="s">
+      <c r="C25" s="234"/>
+      <c r="E25" s="232" t="s">
         <v>340</v>
       </c>
-      <c r="F25" s="234"/>
+      <c r="F25" s="233"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="185" t="s">
@@ -13822,12 +13793,12 @@
       <c r="C26" s="171">
         <v>0.21</v>
       </c>
-      <c r="E26" s="186" t="e" vm="5">
+      <c r="E26" s="186" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="220" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>44.79</v>
+        <v>45.39</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13842,7 +13813,7 @@
       </c>
       <c r="F27" s="221">
         <f ca="1">F26/1000</f>
-        <v>4.4789999999999996E-2</v>
+        <v>4.539E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -13862,15 +13833,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="232" t="s">
+      <c r="B33" s="235" t="s">
         <v>335</v>
       </c>
-      <c r="C33" s="232"/>
-      <c r="D33" s="232"/>
-      <c r="E33" s="232"/>
-      <c r="F33" s="232"/>
-      <c r="G33" s="232"/>
-      <c r="H33" s="232"/>
+      <c r="C33" s="235"/>
+      <c r="D33" s="235"/>
+      <c r="E33" s="235"/>
+      <c r="F33" s="235"/>
+      <c r="G33" s="235"/>
+      <c r="H33" s="235"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -13889,24 +13860,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="232"/>
-      <c r="C39" s="232"/>
-      <c r="D39" s="232"/>
-      <c r="E39" s="232"/>
-      <c r="F39" s="232"/>
-      <c r="G39" s="232"/>
-      <c r="H39" s="232"/>
+      <c r="B39" s="235"/>
+      <c r="C39" s="235"/>
+      <c r="D39" s="235"/>
+      <c r="E39" s="235"/>
+      <c r="F39" s="235"/>
+      <c r="G39" s="235"/>
+      <c r="H39" s="235"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="232" t="s">
+      <c r="B42" s="235" t="s">
         <v>338</v>
       </c>
-      <c r="C42" s="232"/>
-      <c r="D42" s="232"/>
-      <c r="E42" s="232"/>
-      <c r="F42" s="232"/>
-      <c r="G42" s="232"/>
-      <c r="H42" s="232"/>
+      <c r="C42" s="235"/>
+      <c r="D42" s="235"/>
+      <c r="E42" s="235"/>
+      <c r="F42" s="235"/>
+      <c r="G42" s="235"/>
+      <c r="H42" s="235"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -13921,24 +13892,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="232"/>
-      <c r="C49" s="232"/>
-      <c r="D49" s="232"/>
-      <c r="E49" s="232"/>
-      <c r="F49" s="232"/>
-      <c r="G49" s="232"/>
-      <c r="H49" s="232"/>
+      <c r="B49" s="235"/>
+      <c r="C49" s="235"/>
+      <c r="D49" s="235"/>
+      <c r="E49" s="235"/>
+      <c r="F49" s="235"/>
+      <c r="G49" s="235"/>
+      <c r="H49" s="235"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="232" t="s">
+      <c r="B52" s="235" t="s">
         <v>101</v>
       </c>
-      <c r="C52" s="232"/>
-      <c r="D52" s="232"/>
-      <c r="E52" s="232"/>
-      <c r="F52" s="232"/>
-      <c r="G52" s="232"/>
-      <c r="H52" s="232"/>
+      <c r="C52" s="235"/>
+      <c r="D52" s="235"/>
+      <c r="E52" s="235"/>
+      <c r="F52" s="235"/>
+      <c r="G52" s="235"/>
+      <c r="H52" s="235"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -13953,13 +13924,13 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="232"/>
-      <c r="C59" s="232"/>
-      <c r="D59" s="232"/>
-      <c r="E59" s="232"/>
-      <c r="F59" s="232"/>
-      <c r="G59" s="232"/>
-      <c r="H59" s="232"/>
+      <c r="B59" s="235"/>
+      <c r="C59" s="235"/>
+      <c r="D59" s="235"/>
+      <c r="E59" s="235"/>
+      <c r="F59" s="235"/>
+      <c r="G59" s="235"/>
+      <c r="H59" s="235"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -14044,36 +14015,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="232" t="s">
+      <c r="S2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="232"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="232"/>
-      <c r="W2" s="232"/>
-      <c r="X2" s="232"/>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="232"/>
-      <c r="AA2" s="232" t="s">
+      <c r="T2" s="235"/>
+      <c r="U2" s="235"/>
+      <c r="V2" s="235"/>
+      <c r="W2" s="235"/>
+      <c r="X2" s="235"/>
+      <c r="Y2" s="235"/>
+      <c r="Z2" s="235"/>
+      <c r="AA2" s="235" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="232"/>
-      <c r="AC2" s="232"/>
+      <c r="AB2" s="235"/>
+      <c r="AC2" s="235"/>
       <c r="AE2" s="85" t="s">
         <v>107</v>
       </c>
@@ -15269,35 +15240,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
-      <c r="P2" s="232" t="s">
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
+      <c r="P2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="232"/>
-      <c r="R2" s="232"/>
-      <c r="S2" s="232"/>
-      <c r="T2" s="232"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="232"/>
-      <c r="W2" s="232"/>
-      <c r="X2" s="232" t="s">
+      <c r="Q2" s="235"/>
+      <c r="R2" s="235"/>
+      <c r="S2" s="235"/>
+      <c r="T2" s="235"/>
+      <c r="U2" s="235"/>
+      <c r="V2" s="235"/>
+      <c r="W2" s="235"/>
+      <c r="X2" s="235" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="232"/>
+      <c r="Y2" s="235"/>
+      <c r="Z2" s="235"/>
       <c r="AB2" s="85" t="s">
         <v>107</v>
       </c>
@@ -16528,20 +16499,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -17984,20 +17955,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
       <c r="S2" s="246"/>
       <c r="T2" s="246"/>
       <c r="U2" s="246"/>
@@ -19078,10 +19049,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="235" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="232"/>
+      <c r="C4" s="235"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19098,7 +19069,7 @@
       </c>
       <c r="C6" s="134">
         <f ca="1">Overview!C5</f>
-        <v>197.64949999999999</v>
+        <v>210.96</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19107,7 +19078,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">C5*C6</f>
-        <v>4803871.0975000001</v>
+        <v>5127382.8</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19125,7 +19096,7 @@
       </c>
       <c r="C9" s="136">
         <f ca="1">Overview!F27</f>
-        <v>4.4789999999999996E-2</v>
+        <v>4.539E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19134,7 +19105,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C13</f>
-        <v>2.2239</v>
+        <v>2.2223000000000002</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19166,10 +19137,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="232" t="s">
+      <c r="B15" s="235" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="232"/>
+      <c r="C15" s="235"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19177,7 +19148,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>1.760058114833162E-3</v>
+        <v>1.6491905687016576E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19186,7 +19157,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99823994188516685</v>
+        <v>0.99835080943129839</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19204,7 +19175,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14486549999999998</v>
+        <v>0.14539350000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19213,7 +19184,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14468144104261224</v>
+        <v>0.14522016429906248</v>
       </c>
     </row>
   </sheetData>
@@ -19258,20 +19229,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -19557,10 +19528,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="232" t="s">
+      <c r="B13" s="235" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="232"/>
+      <c r="C13" s="235"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -19580,10 +19551,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="232" t="s">
+      <c r="B18" s="235" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="232"/>
+      <c r="C18" s="235"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -19697,20 +19668,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -20642,10 +20613,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="232" t="s">
+      <c r="B37" s="235" t="s">
         <v>197</v>
       </c>
-      <c r="C37" s="232"/>
+      <c r="C37" s="235"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -20738,10 +20709,10 @@
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="232" t="s">
+      <c r="B49" s="235" t="s">
         <v>202</v>
       </c>
-      <c r="C49" s="232"/>
+      <c r="C49" s="235"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -20797,10 +20768,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="232" t="s">
+      <c r="B57" s="235" t="s">
         <v>319</v>
       </c>
-      <c r="C57" s="232"/>
+      <c r="C57" s="235"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -20940,10 +20911,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="235" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="232"/>
+      <c r="C4" s="235"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -20997,7 +20968,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C5</f>
-        <v>197.64949999999999</v>
+        <v>210.96</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21006,7 +20977,7 @@
       </c>
       <c r="C11" s="155">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.50891465286217163</v>
+        <v>0.41370983447516951</v>
       </c>
     </row>
   </sheetData>
@@ -21071,20 +21042,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -21364,7 +21335,7 @@
       </c>
       <c r="C15" s="157">
         <f ca="1">Overview!C5</f>
-        <v>197.64949999999999</v>
+        <v>210.96</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -21430,7 +21401,7 @@
       </c>
       <c r="C23" s="162">
         <f ca="1">C15*C22</f>
-        <v>4783117.8999999994</v>
+        <v>5105232</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -21457,7 +21428,7 @@
       </c>
       <c r="C26" s="163">
         <f ca="1">C23+C25-C24</f>
-        <v>4711015.8999999994</v>
+        <v>5033130</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -28491,7 +28462,7 @@
       <c r="AA114" s="68"/>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>197.64949999999999</v>
+        <v>210.96</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -28538,7 +28509,7 @@
       <c r="AA115" s="68"/>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>197.64949999999999</v>
+        <v>210.96</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30040,7 +30011,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>30.267917304747321</v>
+        <v>32.306278713629411</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -30077,7 +30048,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>19.071319870330704</v>
+        <v>20.355658070700738</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30114,7 +30085,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>24.469330448039127</v>
+        <v>26.117192056232547</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30151,7 +30122,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="144">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>4803871.0975000001</v>
+        <v>5127382.8</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30188,7 +30159,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="144">
         <f ca="1">AC155+AC106-AC105+AC47+AC44</f>
-        <v>4731769.0975000001</v>
+        <v>5055280.8</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -30225,7 +30196,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="184">
         <f ca="1">AC156/AC5</f>
-        <v>18.666418521762115</v>
+        <v>19.942644117542635</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -30262,7 +30233,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="184">
         <f ca="1">AC156/AC11</f>
-        <v>29.157156222078441</v>
+        <v>31.15063499399205</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -30397,7 +30368,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="72">
         <f t="shared" ref="AC161:AC162" ca="1" si="96">AC155/AC159</f>
-        <v>42.801135966748937</v>
+        <v>45.683533950479784</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -30434,7 +30405,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ca="1" si="96"/>
-        <v>37.312063953264534</v>
+        <v>39.863094885793984</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -30471,7 +30442,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="74">
         <f t="shared" ref="AC163" ca="1" si="99">AC159/AC155</f>
-        <v>2.3363865874421498E-2</v>
+        <v>2.1889725104979486E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -30508,7 +30479,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>3.303828241407137E-2</v>
+        <v>3.0953735305271138E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -30545,7 +30516,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="155">
         <f ca="1">AC81/AC115</f>
-        <v>2.0237845276613401E-4</v>
+        <v>1.8960940462646946E-4</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -30582,7 +30553,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="155">
         <f ca="1">-AC62/AC155</f>
-        <v>9.4307276528666269E-3</v>
+        <v>8.835696839330975E-3</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -30619,7 +30590,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="155">
         <f ca="1">-(AC62+AC63)/AC155</f>
-        <v>9.6332726379946328E-3</v>
+        <v>9.0254622689766792E-3</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31122,7 +31093,7 @@
       <c r="AA178" s="49"/>
       <c r="AC178" s="155">
         <f ca="1">(AC105-AC106)/AC155</f>
-        <v>1.5009145444706638E-2</v>
+        <v>1.4062144921186693E-2</v>
       </c>
     </row>
     <row r="179" spans="1:31" x14ac:dyDescent="0.2">
@@ -32287,15 +32258,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="235" t="s">
         <v>230</v>
       </c>
-      <c r="C4" s="232"/>
-      <c r="E4" s="232" t="s">
+      <c r="C4" s="235"/>
+      <c r="E4" s="235" t="s">
         <v>237</v>
       </c>
-      <c r="F4" s="232"/>
-      <c r="G4" s="232"/>
+      <c r="F4" s="235"/>
+      <c r="G4" s="235"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -32303,7 +32274,7 @@
       </c>
       <c r="C5" s="173">
         <f ca="1">Overview!C5</f>
-        <v>197.64949999999999</v>
+        <v>210.96</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="133" t="s">
@@ -32319,7 +32290,7 @@
       </c>
       <c r="C6" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>4803871.0975000001</v>
+        <v>5127382.8</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -32339,7 +32310,7 @@
       </c>
       <c r="C7" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>4731769.0975000001</v>
+        <v>5055280.8</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -32359,7 +32330,7 @@
       </c>
       <c r="C8" s="175">
         <f ca="1">Statement!AC152</f>
-        <v>30.267917304747321</v>
+        <v>32.306278713629411</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>240</v>
@@ -32379,7 +32350,7 @@
       </c>
       <c r="C9" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>19.071319870330704</v>
+        <v>20.355658070700738</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>241</v>
@@ -32399,7 +32370,7 @@
       </c>
       <c r="C10" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>24.469330448039127</v>
+        <v>26.117192056232547</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -32419,7 +32390,7 @@
       </c>
       <c r="C11" s="175">
         <f ca="1">Statement!AC157</f>
-        <v>18.666418521762115</v>
+        <v>19.942644117542635</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -32428,18 +32399,18 @@
       </c>
       <c r="C12" s="175">
         <f ca="1">Statement!AC158</f>
-        <v>29.157156222078441</v>
+        <v>31.15063499399205</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="232" t="s">
+      <c r="B15" s="235" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="232"/>
-      <c r="E15" s="232" t="s">
+      <c r="C15" s="235"/>
+      <c r="E15" s="235" t="s">
         <v>243</v>
       </c>
-      <c r="F15" s="232"/>
+      <c r="F15" s="235"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -32490,14 +32461,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="232" t="s">
+      <c r="B21" s="235" t="s">
         <v>242</v>
       </c>
-      <c r="C21" s="232"/>
-      <c r="E21" s="232" t="s">
+      <c r="C21" s="235"/>
+      <c r="E21" s="235" t="s">
         <v>246</v>
       </c>
-      <c r="F21" s="232"/>
+      <c r="F21" s="235"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -32566,14 +32537,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="232" t="s">
+      <c r="B29" s="235" t="s">
         <v>247</v>
       </c>
-      <c r="C29" s="232"/>
-      <c r="E29" s="232" t="s">
+      <c r="C29" s="235"/>
+      <c r="E29" s="235" t="s">
         <v>253</v>
       </c>
-      <c r="F29" s="232"/>
+      <c r="F29" s="235"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -32649,14 +32620,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="232" t="s">
+      <c r="B37" s="235" t="s">
         <v>265</v>
       </c>
-      <c r="C37" s="232"/>
-      <c r="E37" s="232" t="s">
+      <c r="C37" s="235"/>
+      <c r="E37" s="235" t="s">
         <v>268</v>
       </c>
-      <c r="F37" s="232"/>
+      <c r="F37" s="235"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -32664,7 +32635,7 @@
       </c>
       <c r="C38" s="176">
         <f ca="1">Statement!AC164</f>
-        <v>3.303828241407137E-2</v>
+        <v>3.0953735305271138E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>267</v>
@@ -32680,7 +32651,7 @@
       </c>
       <c r="C39" s="216">
         <f ca="1">Statement!AC163</f>
-        <v>2.3363865874421498E-2</v>
+        <v>2.1889725104979486E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>269</v>
@@ -32696,7 +32667,7 @@
       </c>
       <c r="C40" s="176">
         <f ca="1">Statement!AC165</f>
-        <v>2.0237845276613401E-4</v>
+        <v>1.8960940462646946E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>270</v>
@@ -32712,7 +32683,7 @@
       </c>
       <c r="C41" s="176">
         <f ca="1">Statement!AC166</f>
-        <v>9.4307276528666269E-3</v>
+        <v>8.835696839330975E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -32721,18 +32692,18 @@
       </c>
       <c r="C42" s="176">
         <f ca="1">Statement!AC167</f>
-        <v>9.6332726379946328E-3</v>
+        <v>9.0254622689766792E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="232" t="s">
+      <c r="B45" s="235" t="s">
         <v>276</v>
       </c>
-      <c r="C45" s="232"/>
-      <c r="E45" s="232" t="s">
+      <c r="C45" s="235"/>
+      <c r="E45" s="235" t="s">
         <v>282</v>
       </c>
-      <c r="F45" s="232"/>
+      <c r="F45" s="235"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -32765,18 +32736,18 @@
       </c>
       <c r="F48" s="176">
         <f ca="1">Statement!AC178</f>
-        <v>1.5009145444706638E-2</v>
+        <v>1.4062144921186693E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="232" t="s">
+      <c r="B51" s="235" t="s">
         <v>279</v>
       </c>
-      <c r="C51" s="232"/>
-      <c r="E51" s="232" t="s">
+      <c r="C51" s="235"/>
+      <c r="E51" s="235" t="s">
         <v>300</v>
       </c>
-      <c r="F51" s="232"/>
+      <c r="F51" s="235"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -32945,7 +32916,7 @@
       </c>
       <c r="I6" s="173">
         <f ca="1">Statement!AC114</f>
-        <v>197.64949999999999</v>
+        <v>210.96</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -32974,7 +32945,7 @@
       </c>
       <c r="I7" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>4803871.0975000001</v>
+        <v>5127382.8</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33003,7 +32974,7 @@
       </c>
       <c r="I8" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>4731769.0975000001</v>
+        <v>5055280.8</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33032,7 +33003,7 @@
       </c>
       <c r="I9" s="175">
         <f ca="1">Statement!AC152</f>
-        <v>30.267917304747321</v>
+        <v>32.306278713629411</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33061,7 +33032,7 @@
       </c>
       <c r="I10" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>19.071319870330704</v>
+        <v>20.355658070700738</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33090,7 +33061,7 @@
       </c>
       <c r="I11" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>24.469330448039127</v>
+        <v>26.117192056232547</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33119,7 +33090,7 @@
       </c>
       <c r="I12" s="175">
         <f ca="1">Statement!AC157</f>
-        <v>18.666418521762115</v>
+        <v>19.942644117542635</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33148,7 +33119,7 @@
       </c>
       <c r="I13" s="175">
         <f ca="1">Statement!AC158</f>
-        <v>29.157156222078441</v>
+        <v>31.15063499399205</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -33921,7 +33892,7 @@
       </c>
       <c r="I51" s="176">
         <f ca="1">Statement!AC164</f>
-        <v>3.303828241407137E-2</v>
+        <v>3.0953735305271138E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -33950,7 +33921,7 @@
       </c>
       <c r="I52" s="176">
         <f ca="1">Statement!AC163</f>
-        <v>2.3363865874421498E-2</v>
+        <v>2.1889725104979486E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -33979,7 +33950,7 @@
       </c>
       <c r="I53" s="176">
         <f ca="1">Statement!AC165</f>
-        <v>2.0237845276613401E-4</v>
+        <v>1.8960940462646946E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -34008,7 +33979,7 @@
       </c>
       <c r="I54" s="176">
         <f ca="1">Statement!AC166</f>
-        <v>9.4307276528666269E-3</v>
+        <v>8.835696839330975E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34037,7 +34008,7 @@
       </c>
       <c r="I55" s="176">
         <f ca="1">Statement!AC167</f>
-        <v>9.6332726379946328E-3</v>
+        <v>9.0254622689766792E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34273,7 +34244,7 @@
       </c>
       <c r="I68" s="197">
         <f ca="1">Statement!AC178</f>
-        <v>1.5009145444706638E-2</v>
+        <v>1.4062144921186693E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">

--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BBDB40E-135B-084E-B5B0-5F81F16110AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DC523E6-1ED8-DF4B-9688-6199A7F16521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -32,10 +32,12 @@
     <sheet name="DCF" sheetId="11" r:id="rId17"/>
     <sheet name="Multiples" sheetId="12" r:id="rId18"/>
     <sheet name="AVG target price" sheetId="13" r:id="rId19"/>
-    <sheet name="Reverse DCF" sheetId="14" r:id="rId20"/>
+    <sheet name="DDM" sheetId="21" r:id="rId20"/>
+    <sheet name="Reverse DCF" sheetId="14" r:id="rId21"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId21"/>
+    <externalReference r:id="rId22"/>
+    <externalReference r:id="rId23"/>
   </externalReferences>
   <calcPr calcId="191029" iterate="1"/>
   <extLst>
@@ -150,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="410">
   <si>
     <t>Ticker</t>
   </si>
@@ -1347,6 +1349,39 @@
   </si>
   <si>
     <t>Sales/Assets</t>
+  </si>
+  <si>
+    <t>Manual Cost of Equity</t>
+  </si>
+  <si>
+    <t>Dividend discount model</t>
+  </si>
+  <si>
+    <t>Dividend per share</t>
+  </si>
+  <si>
+    <t>Ratios</t>
+  </si>
+  <si>
+    <t>Payout</t>
+  </si>
+  <si>
+    <t>DDM valuation</t>
+  </si>
+  <si>
+    <t>Latest dividend</t>
+  </si>
+  <si>
+    <t>Year 1 growth rate</t>
+  </si>
+  <si>
+    <t>Year 1 dividend</t>
+  </si>
+  <si>
+    <t>Perpetual dividend growth</t>
+  </si>
+  <si>
+    <t>DDM price</t>
   </si>
 </sst>
 </file>
@@ -1950,7 +1985,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="250">
+  <cellXfs count="255">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2261,6 +2296,9 @@
     </xf>
     <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2270,15 +2308,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2286,6 +2315,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2315,6 +2350,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="39" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12441,6 +12481,95 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Overview"/>
+      <sheetName val="Financials -&gt;"/>
+      <sheetName val="Statement"/>
+      <sheetName val="Analysis -&gt;"/>
+      <sheetName val="Basic"/>
+      <sheetName val="Yearly Analysis"/>
+      <sheetName val="Quarter analysis"/>
+      <sheetName val="Graphs Year"/>
+      <sheetName val="Graphs Quarter"/>
+      <sheetName val="Forecast -&gt;"/>
+      <sheetName val="Revenue"/>
+      <sheetName val="COGS &amp; OpEx"/>
+      <sheetName val="WC &amp; Investments"/>
+      <sheetName val="FCF &amp; Other"/>
+      <sheetName val="Valuation -&gt;"/>
+      <sheetName val="WACC"/>
+      <sheetName val="DCF"/>
+      <sheetName val="Multiples"/>
+      <sheetName val="AVG target price"/>
+      <sheetName val="DDM"/>
+      <sheetName val="Reverse DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10">
+        <row r="5">
+          <cell r="C5">
+            <v>2021</v>
+          </cell>
+          <cell r="D5">
+            <v>2022</v>
+          </cell>
+          <cell r="E5">
+            <v>2023</v>
+          </cell>
+          <cell r="F5">
+            <v>2024</v>
+          </cell>
+          <cell r="G5">
+            <v>2025</v>
+          </cell>
+          <cell r="H5">
+            <v>2026</v>
+          </cell>
+          <cell r="I5">
+            <v>2027</v>
+          </cell>
+          <cell r="J5">
+            <v>2028</v>
+          </cell>
+          <cell r="K5">
+            <v>2029</v>
+          </cell>
+          <cell r="L5">
+            <v>2030</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="adi dumitras" id="{A0F62302-F8D3-B346-B5DF-839B413AE710}" userId="b24535bb88af1c42" providerId="Windows Live"/>
@@ -12569,12 +12698,12 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>236.54</v>
-    <v>161.61000000000001</v>
-    <v>2.2223000000000002</v>
+    <v>162.02000000000001</v>
+    <v>2.2214</v>
     <v>8.18</v>
     <v>4.0339E-2</v>
-    <v>-0.59</v>
-    <v>-2.797E-3</v>
+    <v>-0.39</v>
+    <v>-1.8490000000000002E-3</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -12585,21 +12714,21 @@
     <v>211</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46213.886782082809</v>
+    <v>46213.999999178122</v>
     <v>0</v>
     <v>201.92</v>
     <v>5105232000000</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
     <v>202</v>
-    <v>32.3063</v>
+    <v>31.053699999999999</v>
     <v>202.78</v>
     <v>210.96</v>
-    <v>210.37</v>
+    <v>210.57</v>
     <v>24200000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>147771633</v>
+    <v>148421001</v>
     <v>152809403</v>
     <v>1998</v>
   </rv>
@@ -12624,17 +12753,17 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.3</v>
-    <v>-6.5659999999999998E-3</v>
+    <v>0.3</v>
+    <v>6.6090000000000003E-3</v>
     <v>US</v>
-    <v>45.81</v>
+    <v>45.71</v>
     <v>Index</v>
     <v>3</v>
-    <v>45.29</v>
+    <v>45.39</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>45.77</v>
+    <v>45.41</v>
+    <v>45.39</v>
     <v>45.69</v>
-    <v>45.39</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -12856,9 +12985,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13429,18 +13558,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="232" t="s">
+      <c r="B2" s="233" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="233"/>
-      <c r="E2" s="232" t="s">
+      <c r="C2" s="234"/>
+      <c r="E2" s="233" t="s">
         <v>284</v>
       </c>
-      <c r="F2" s="233"/>
-      <c r="H2" s="232" t="s">
+      <c r="F2" s="234"/>
+      <c r="H2" s="233" t="s">
         <v>325</v>
       </c>
-      <c r="I2" s="233"/>
+      <c r="I2" s="234"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="186" t="s">
@@ -13520,7 +13649,7 @@
       </c>
       <c r="C6" s="209" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>210.37</v>
+        <v>210.57</v>
       </c>
       <c r="E6" s="186" t="s">
         <v>234</v>
@@ -13568,7 +13697,7 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.59</v>
+        <v>-0.39</v>
       </c>
       <c r="E8" s="186" t="s">
         <v>262</v>
@@ -13608,7 +13737,7 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-2.797E-3</v>
+        <v>-1.8490000000000002E-3</v>
       </c>
       <c r="E10" s="186" t="s">
         <v>290</v>
@@ -13617,6 +13746,13 @@
         <f ca="1">Statement!AC166</f>
         <v>8.835696839330975E-3</v>
       </c>
+      <c r="H10" s="185" t="s">
+        <v>409</v>
+      </c>
+      <c r="I10" s="213">
+        <f>DDM!C26</f>
+        <v>0.48421052631578948</v>
+      </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B11" s="186" t="s">
@@ -13640,7 +13776,7 @@
       </c>
       <c r="C12" s="210" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>161.61000000000001</v>
+        <v>162.02000000000001</v>
       </c>
       <c r="E12" s="186" t="s">
         <v>94</v>
@@ -13656,7 +13792,7 @@
       </c>
       <c r="C13" s="210" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.2223000000000002</v>
+        <v>2.2214</v>
       </c>
       <c r="E13" s="186" t="s">
         <v>96</v>
@@ -13701,10 +13837,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="234" t="s">
+      <c r="B17" s="235" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="234"/>
+      <c r="C17" s="235"/>
       <c r="E17" s="185" t="s">
         <v>293</v>
       </c>
@@ -13777,14 +13913,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="234" t="s">
+      <c r="B25" s="235" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="234"/>
-      <c r="E25" s="232" t="s">
+      <c r="C25" s="235"/>
+      <c r="E25" s="233" t="s">
         <v>340</v>
       </c>
-      <c r="F25" s="233"/>
+      <c r="F25" s="234"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="185" t="s">
@@ -13798,7 +13934,7 @@
       </c>
       <c r="F26" s="220" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>45.39</v>
+        <v>45.69</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13813,7 +13949,7 @@
       </c>
       <c r="F27" s="221">
         <f ca="1">F26/1000</f>
-        <v>4.539E-2</v>
+        <v>4.5689999999999995E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -13826,22 +13962,22 @@
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="185" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="C29" s="222">
         <v>0.12</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="235" t="s">
+      <c r="B33" s="232" t="s">
         <v>335</v>
       </c>
-      <c r="C33" s="235"/>
-      <c r="D33" s="235"/>
-      <c r="E33" s="235"/>
-      <c r="F33" s="235"/>
-      <c r="G33" s="235"/>
-      <c r="H33" s="235"/>
+      <c r="C33" s="232"/>
+      <c r="D33" s="232"/>
+      <c r="E33" s="232"/>
+      <c r="F33" s="232"/>
+      <c r="G33" s="232"/>
+      <c r="H33" s="232"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -13860,24 +13996,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="235"/>
-      <c r="C39" s="235"/>
-      <c r="D39" s="235"/>
-      <c r="E39" s="235"/>
-      <c r="F39" s="235"/>
-      <c r="G39" s="235"/>
-      <c r="H39" s="235"/>
+      <c r="B39" s="232"/>
+      <c r="C39" s="232"/>
+      <c r="D39" s="232"/>
+      <c r="E39" s="232"/>
+      <c r="F39" s="232"/>
+      <c r="G39" s="232"/>
+      <c r="H39" s="232"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="235" t="s">
+      <c r="B42" s="232" t="s">
         <v>338</v>
       </c>
-      <c r="C42" s="235"/>
-      <c r="D42" s="235"/>
-      <c r="E42" s="235"/>
-      <c r="F42" s="235"/>
-      <c r="G42" s="235"/>
-      <c r="H42" s="235"/>
+      <c r="C42" s="232"/>
+      <c r="D42" s="232"/>
+      <c r="E42" s="232"/>
+      <c r="F42" s="232"/>
+      <c r="G42" s="232"/>
+      <c r="H42" s="232"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -13892,24 +14028,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="235"/>
-      <c r="C49" s="235"/>
-      <c r="D49" s="235"/>
-      <c r="E49" s="235"/>
-      <c r="F49" s="235"/>
-      <c r="G49" s="235"/>
-      <c r="H49" s="235"/>
+      <c r="B49" s="232"/>
+      <c r="C49" s="232"/>
+      <c r="D49" s="232"/>
+      <c r="E49" s="232"/>
+      <c r="F49" s="232"/>
+      <c r="G49" s="232"/>
+      <c r="H49" s="232"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="235" t="s">
+      <c r="B52" s="232" t="s">
         <v>101</v>
       </c>
-      <c r="C52" s="235"/>
-      <c r="D52" s="235"/>
-      <c r="E52" s="235"/>
-      <c r="F52" s="235"/>
-      <c r="G52" s="235"/>
-      <c r="H52" s="235"/>
+      <c r="C52" s="232"/>
+      <c r="D52" s="232"/>
+      <c r="E52" s="232"/>
+      <c r="F52" s="232"/>
+      <c r="G52" s="232"/>
+      <c r="H52" s="232"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -13924,28 +14060,28 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="235"/>
-      <c r="C59" s="235"/>
-      <c r="D59" s="235"/>
-      <c r="E59" s="235"/>
-      <c r="F59" s="235"/>
-      <c r="G59" s="235"/>
-      <c r="H59" s="235"/>
+      <c r="B59" s="232"/>
+      <c r="C59" s="232"/>
+      <c r="D59" s="232"/>
+      <c r="E59" s="232"/>
+      <c r="F59" s="232"/>
+      <c r="G59" s="232"/>
+      <c r="H59" s="232"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B52:H52"/>
     <mergeCell ref="B59:H59"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14015,36 +14151,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="232" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="235" t="s">
+      <c r="S2" s="232" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="235"/>
-      <c r="U2" s="235"/>
-      <c r="V2" s="235"/>
-      <c r="W2" s="235"/>
-      <c r="X2" s="235"/>
-      <c r="Y2" s="235"/>
-      <c r="Z2" s="235"/>
-      <c r="AA2" s="235" t="s">
+      <c r="T2" s="232"/>
+      <c r="U2" s="232"/>
+      <c r="V2" s="232"/>
+      <c r="W2" s="232"/>
+      <c r="X2" s="232"/>
+      <c r="Y2" s="232"/>
+      <c r="Z2" s="232"/>
+      <c r="AA2" s="232" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="235"/>
-      <c r="AC2" s="235"/>
+      <c r="AB2" s="232"/>
+      <c r="AC2" s="232"/>
       <c r="AE2" s="85" t="s">
         <v>107</v>
       </c>
@@ -15240,35 +15376,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="232" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
-      <c r="P2" s="235" t="s">
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
+      <c r="P2" s="232" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="235"/>
-      <c r="R2" s="235"/>
-      <c r="S2" s="235"/>
-      <c r="T2" s="235"/>
-      <c r="U2" s="235"/>
-      <c r="V2" s="235"/>
-      <c r="W2" s="235"/>
-      <c r="X2" s="235" t="s">
+      <c r="Q2" s="232"/>
+      <c r="R2" s="232"/>
+      <c r="S2" s="232"/>
+      <c r="T2" s="232"/>
+      <c r="U2" s="232"/>
+      <c r="V2" s="232"/>
+      <c r="W2" s="232"/>
+      <c r="X2" s="232" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="235"/>
-      <c r="Z2" s="235"/>
+      <c r="Y2" s="232"/>
+      <c r="Z2" s="232"/>
       <c r="AB2" s="85" t="s">
         <v>107</v>
       </c>
@@ -16499,20 +16635,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="232" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
+      <c r="D3" s="232"/>
+      <c r="E3" s="232"/>
+      <c r="F3" s="232"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="232"/>
+      <c r="J3" s="232"/>
+      <c r="K3" s="232"/>
+      <c r="L3" s="232"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -17905,12 +18041,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -17918,6 +18048,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -17955,20 +18091,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="232" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
       <c r="S2" s="246"/>
       <c r="T2" s="246"/>
       <c r="U2" s="246"/>
@@ -18977,16 +19113,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19049,10 +19185,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="232" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="235"/>
+      <c r="C4" s="232"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19096,7 +19232,7 @@
       </c>
       <c r="C9" s="136">
         <f ca="1">Overview!F27</f>
-        <v>4.539E-2</v>
+        <v>4.5689999999999995E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19105,7 +19241,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C13</f>
-        <v>2.2223000000000002</v>
+        <v>2.2214</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19137,10 +19273,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="235" t="s">
+      <c r="B15" s="232" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="235"/>
+      <c r="C15" s="232"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19175,7 +19311,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14539350000000001</v>
+        <v>0.14565299999999998</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19184,7 +19320,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14522016429906248</v>
+        <v>0.14547923633410986</v>
       </c>
     </row>
   </sheetData>
@@ -19229,20 +19365,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="232" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
+      <c r="D3" s="232"/>
+      <c r="E3" s="232"/>
+      <c r="F3" s="232"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="232"/>
+      <c r="J3" s="232"/>
+      <c r="K3" s="232"/>
+      <c r="L3" s="232"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -19528,10 +19664,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="235" t="s">
+      <c r="B13" s="232" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="235"/>
+      <c r="C13" s="232"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -19551,10 +19687,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="235" t="s">
+      <c r="B18" s="232" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="235"/>
+      <c r="C18" s="232"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -19668,20 +19804,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="232" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -20613,10 +20749,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="235" t="s">
+      <c r="B37" s="232" t="s">
         <v>197</v>
       </c>
-      <c r="C37" s="235"/>
+      <c r="C37" s="232"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -20709,10 +20845,10 @@
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="235" t="s">
+      <c r="B49" s="232" t="s">
         <v>202</v>
       </c>
-      <c r="C49" s="235"/>
+      <c r="C49" s="232"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -20728,7 +20864,7 @@
         <v>388</v>
       </c>
       <c r="C51" s="136">
-        <f>Overview!C29</f>
+        <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
         <v>0.12</v>
       </c>
     </row>
@@ -20768,10 +20904,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="235" t="s">
+      <c r="B57" s="232" t="s">
         <v>319</v>
       </c>
-      <c r="C57" s="235"/>
+      <c r="C57" s="232"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -20911,10 +21047,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="232" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="235"/>
+      <c r="C4" s="232"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21010,6 +21146,477 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E9CEB08-E030-1045-9E9A-EAE6DBD05C9B}">
+  <dimension ref="A1:N26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="2" style="83" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="1"/>
+    <col min="4" max="4" width="10.83203125" style="1" customWidth="1"/>
+    <col min="5" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="10.83203125" style="1" customWidth="1"/>
+    <col min="9" max="12" width="10.83203125" style="1"/>
+    <col min="13" max="14" width="9.5" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="10.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="83" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="4"/>
+      <c r="B1" s="82" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" s="4"/>
+      <c r="C2" s="232" t="s">
+        <v>105</v>
+      </c>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="245" t="s">
+        <v>106</v>
+      </c>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
+    </row>
+    <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="86"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="241" t="s">
+        <v>186</v>
+      </c>
+      <c r="D4" s="241"/>
+      <c r="E4" s="241"/>
+      <c r="F4" s="241"/>
+      <c r="G4" s="241"/>
+      <c r="H4" s="241"/>
+      <c r="I4" s="241"/>
+      <c r="J4" s="241"/>
+      <c r="K4" s="241"/>
+      <c r="L4" s="241"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B5" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="12">
+        <f>[2]Revenue!C5</f>
+        <v>2021</v>
+      </c>
+      <c r="D5" s="12">
+        <f>[2]Revenue!D5</f>
+        <v>2022</v>
+      </c>
+      <c r="E5" s="12">
+        <f>[2]Revenue!E5</f>
+        <v>2023</v>
+      </c>
+      <c r="F5" s="12">
+        <f>[2]Revenue!F5</f>
+        <v>2024</v>
+      </c>
+      <c r="G5" s="12">
+        <f>[2]Revenue!G5</f>
+        <v>2025</v>
+      </c>
+      <c r="H5" s="12">
+        <f>[2]Revenue!H5</f>
+        <v>2026</v>
+      </c>
+      <c r="I5" s="12">
+        <f>[2]Revenue!I5</f>
+        <v>2027</v>
+      </c>
+      <c r="J5" s="12">
+        <f>[2]Revenue!J5</f>
+        <v>2028</v>
+      </c>
+      <c r="K5" s="12">
+        <f>[2]Revenue!K5</f>
+        <v>2029</v>
+      </c>
+      <c r="L5" s="12">
+        <f>[2]Revenue!L5</f>
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B6" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="C6" s="250">
+        <f>Statement!M25</f>
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="D6" s="250">
+        <f>Statement!N25</f>
+        <v>0.17399999999999999</v>
+      </c>
+      <c r="E6" s="250">
+        <f>Statement!O25</f>
+        <v>1.1930000000000001</v>
+      </c>
+      <c r="F6" s="250">
+        <f>Statement!P25</f>
+        <v>2.94</v>
+      </c>
+      <c r="G6" s="251">
+        <f>Statement!Q25</f>
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H6" s="138"/>
+      <c r="I6" s="138"/>
+      <c r="J6" s="138"/>
+      <c r="K6" s="138"/>
+      <c r="L6" s="138"/>
+      <c r="N6" s="91"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B7" s="16" t="s">
+        <v>401</v>
+      </c>
+      <c r="C7" s="250">
+        <f>Statement!M81</f>
+        <v>1.6E-2</v>
+      </c>
+      <c r="D7" s="250">
+        <f>Statement!N81</f>
+        <v>1.6E-2</v>
+      </c>
+      <c r="E7" s="250">
+        <f>Statement!O81</f>
+        <v>1.6E-2</v>
+      </c>
+      <c r="F7" s="250">
+        <f>Statement!P81</f>
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="G7" s="251">
+        <f>Statement!Q81</f>
+        <v>0.04</v>
+      </c>
+      <c r="H7" s="138"/>
+      <c r="I7" s="138"/>
+      <c r="J7" s="138"/>
+      <c r="K7" s="138"/>
+      <c r="L7" s="138"/>
+      <c r="N7" s="91"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N8" s="91"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C9" s="241" t="s">
+        <v>114</v>
+      </c>
+      <c r="D9" s="241"/>
+      <c r="E9" s="241"/>
+      <c r="F9" s="241"/>
+      <c r="G9" s="241"/>
+      <c r="H9" s="241"/>
+      <c r="I9" s="241"/>
+      <c r="J9" s="241"/>
+      <c r="K9" s="241"/>
+      <c r="L9" s="241"/>
+      <c r="N9" s="91"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B10" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="C10" s="12">
+        <f t="shared" ref="C10:L10" si="0">C5</f>
+        <v>2021</v>
+      </c>
+      <c r="D10" s="12">
+        <f t="shared" si="0"/>
+        <v>2022</v>
+      </c>
+      <c r="E10" s="12">
+        <f t="shared" si="0"/>
+        <v>2023</v>
+      </c>
+      <c r="F10" s="12">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
+      <c r="G10" s="12">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
+      <c r="H10" s="12">
+        <f t="shared" si="0"/>
+        <v>2026</v>
+      </c>
+      <c r="I10" s="12">
+        <f t="shared" si="0"/>
+        <v>2027</v>
+      </c>
+      <c r="J10" s="12">
+        <f t="shared" si="0"/>
+        <v>2028</v>
+      </c>
+      <c r="K10" s="12">
+        <f t="shared" si="0"/>
+        <v>2029</v>
+      </c>
+      <c r="L10" s="12">
+        <f t="shared" si="0"/>
+        <v>2030</v>
+      </c>
+      <c r="N10" s="91"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C11" s="138"/>
+      <c r="D11" s="95">
+        <f>(D6-C6)/C6</f>
+        <v>-0.54805194805194812</v>
+      </c>
+      <c r="E11" s="95">
+        <f>(E6-D6)/D6</f>
+        <v>5.8563218390804606</v>
+      </c>
+      <c r="F11" s="95">
+        <f>(F6-E6)/E6</f>
+        <v>1.4643755238893543</v>
+      </c>
+      <c r="G11" s="96">
+        <f>(G6-F6)/F6</f>
+        <v>0.66666666666666685</v>
+      </c>
+      <c r="H11" s="138"/>
+      <c r="I11" s="138"/>
+      <c r="J11" s="138"/>
+      <c r="K11" s="138"/>
+      <c r="L11" s="138"/>
+      <c r="N11" s="91"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B12" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C12" s="138"/>
+      <c r="D12" s="95">
+        <f>IF(C7=0,
+IF(D7=0,0,IF(D7&gt;0,1,-1)),
+(D7-C7)/ABS(C7)
+)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="95">
+        <f>IF(D7=0,
+IF(E7=0,0,IF(E7&gt;0,1,-1)),
+(E7-D7)/ABS(D7)
+)</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="95">
+        <f>IF(E7=0,
+IF(F7=0,0,IF(F7&gt;0,1,-1)),
+(F7-E7)/ABS(E7)
+)</f>
+        <v>1.125</v>
+      </c>
+      <c r="G12" s="96">
+        <f>IF(F7=0,
+IF(G7=0,0,IF(G7&gt;0,1,-1)),
+(G7-F7)/ABS(F7)
+)</f>
+        <v>0.17647058823529405</v>
+      </c>
+      <c r="H12" s="138"/>
+      <c r="I12" s="138"/>
+      <c r="J12" s="138"/>
+      <c r="K12" s="138"/>
+      <c r="L12" s="138"/>
+      <c r="N12" s="91"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="91"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C14" s="241" t="s">
+        <v>402</v>
+      </c>
+      <c r="D14" s="241"/>
+      <c r="E14" s="241"/>
+      <c r="F14" s="241"/>
+      <c r="G14" s="241"/>
+      <c r="H14" s="241"/>
+      <c r="I14" s="241"/>
+      <c r="J14" s="241"/>
+      <c r="K14" s="241"/>
+      <c r="L14" s="241"/>
+      <c r="N14" s="91"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B15" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="C15" s="12">
+        <f>C5</f>
+        <v>2021</v>
+      </c>
+      <c r="D15" s="12">
+        <f t="shared" ref="D15:L15" si="1">D5</f>
+        <v>2022</v>
+      </c>
+      <c r="E15" s="12">
+        <f t="shared" si="1"/>
+        <v>2023</v>
+      </c>
+      <c r="F15" s="12">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="G15" s="12">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="H15" s="12">
+        <f t="shared" si="1"/>
+        <v>2026</v>
+      </c>
+      <c r="I15" s="12">
+        <f t="shared" si="1"/>
+        <v>2027</v>
+      </c>
+      <c r="J15" s="12">
+        <f t="shared" si="1"/>
+        <v>2028</v>
+      </c>
+      <c r="K15" s="12">
+        <f t="shared" si="1"/>
+        <v>2029</v>
+      </c>
+      <c r="L15" s="12">
+        <f t="shared" si="1"/>
+        <v>2030</v>
+      </c>
+      <c r="N15" s="91"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B16" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C16" s="95">
+        <f>C7/C6</f>
+        <v>4.1558441558441558E-2</v>
+      </c>
+      <c r="D16" s="95">
+        <f t="shared" ref="D16:G16" si="2">D7/D6</f>
+        <v>9.195402298850576E-2</v>
+      </c>
+      <c r="E16" s="95">
+        <f t="shared" si="2"/>
+        <v>1.3411567476948869E-2</v>
+      </c>
+      <c r="F16" s="95">
+        <f t="shared" si="2"/>
+        <v>1.1564625850340137E-2</v>
+      </c>
+      <c r="G16" s="96">
+        <f t="shared" si="2"/>
+        <v>8.163265306122448E-3</v>
+      </c>
+      <c r="H16" s="138"/>
+      <c r="I16" s="138"/>
+      <c r="J16" s="138"/>
+      <c r="K16" s="138"/>
+      <c r="L16" s="138"/>
+      <c r="N16" s="91"/>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N17" s="91"/>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N18" s="91"/>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N19" s="91"/>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B20" s="232" t="s">
+        <v>404</v>
+      </c>
+      <c r="C20" s="232"/>
+      <c r="N20" s="91"/>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B21" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="C21" s="252">
+        <f>G7</f>
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B22" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C22" s="253">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B23" s="39" t="s">
+        <v>407</v>
+      </c>
+      <c r="C23" s="254">
+        <f>C21*(1+C22)</f>
+        <v>4.5999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B24" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C24" s="136">
+        <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B25" s="39" t="s">
+        <v>408</v>
+      </c>
+      <c r="C25" s="253">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B26" s="142" t="s">
+        <v>201</v>
+      </c>
+      <c r="C26" s="143">
+        <f>C23/(C24-C25)</f>
+        <v>0.48421052631578948</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="C9:L9"/>
+    <mergeCell ref="C14:L14"/>
+    <mergeCell ref="B20:C20"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0116CE1A-CCEC-514B-9208-A0DCC7740441}">
   <dimension ref="A1:AB49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -21042,20 +21649,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="232" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
+      <c r="D3" s="232"/>
+      <c r="E3" s="232"/>
+      <c r="F3" s="232"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="232"/>
+      <c r="J3" s="232"/>
+      <c r="K3" s="232"/>
+      <c r="L3" s="232"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -21954,17 +22561,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -32258,15 +32865,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="232" t="s">
         <v>230</v>
       </c>
-      <c r="C4" s="235"/>
-      <c r="E4" s="235" t="s">
+      <c r="C4" s="232"/>
+      <c r="E4" s="232" t="s">
         <v>237</v>
       </c>
-      <c r="F4" s="235"/>
-      <c r="G4" s="235"/>
+      <c r="F4" s="232"/>
+      <c r="G4" s="232"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -32403,14 +33010,14 @@
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="235" t="s">
+      <c r="B15" s="232" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="235"/>
-      <c r="E15" s="235" t="s">
+      <c r="C15" s="232"/>
+      <c r="E15" s="232" t="s">
         <v>243</v>
       </c>
-      <c r="F15" s="235"/>
+      <c r="F15" s="232"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -32461,14 +33068,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="235" t="s">
+      <c r="B21" s="232" t="s">
         <v>242</v>
       </c>
-      <c r="C21" s="235"/>
-      <c r="E21" s="235" t="s">
+      <c r="C21" s="232"/>
+      <c r="E21" s="232" t="s">
         <v>246</v>
       </c>
-      <c r="F21" s="235"/>
+      <c r="F21" s="232"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -32537,14 +33144,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="235" t="s">
+      <c r="B29" s="232" t="s">
         <v>247</v>
       </c>
-      <c r="C29" s="235"/>
-      <c r="E29" s="235" t="s">
+      <c r="C29" s="232"/>
+      <c r="E29" s="232" t="s">
         <v>253</v>
       </c>
-      <c r="F29" s="235"/>
+      <c r="F29" s="232"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -32620,14 +33227,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="235" t="s">
+      <c r="B37" s="232" t="s">
         <v>265</v>
       </c>
-      <c r="C37" s="235"/>
-      <c r="E37" s="235" t="s">
+      <c r="C37" s="232"/>
+      <c r="E37" s="232" t="s">
         <v>268</v>
       </c>
-      <c r="F37" s="235"/>
+      <c r="F37" s="232"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -32696,14 +33303,14 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="235" t="s">
+      <c r="B45" s="232" t="s">
         <v>276</v>
       </c>
-      <c r="C45" s="235"/>
-      <c r="E45" s="235" t="s">
+      <c r="C45" s="232"/>
+      <c r="E45" s="232" t="s">
         <v>282</v>
       </c>
-      <c r="F45" s="235"/>
+      <c r="F45" s="232"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -32740,14 +33347,14 @@
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="235" t="s">
+      <c r="B51" s="232" t="s">
         <v>279</v>
       </c>
-      <c r="C51" s="235"/>
-      <c r="E51" s="235" t="s">
+      <c r="C51" s="232"/>
+      <c r="E51" s="232" t="s">
         <v>300</v>
       </c>
-      <c r="F51" s="235"/>
+      <c r="F51" s="232"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34756,14 +35363,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="238" t="s">
+      <c r="C3" s="236" t="s">
         <v>310</v>
       </c>
-      <c r="D3" s="239"/>
-      <c r="F3" s="240" t="s">
+      <c r="D3" s="237"/>
+      <c r="F3" s="238" t="s">
         <v>311</v>
       </c>
-      <c r="G3" s="239"/>
+      <c r="G3" s="237"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -34830,19 +35437,19 @@
       <c r="B7" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C7" s="236">
+      <c r="C7" s="239">
         <f>Statement!AA88</f>
         <v>0.19798317847549429</v>
       </c>
-      <c r="D7" s="237"/>
-      <c r="F7" s="236">
+      <c r="D7" s="240"/>
+      <c r="F7" s="239">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.85227633788752211</v>
       </c>
-      <c r="G7" s="237"/>
+      <c r="G7" s="240"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="208" t="s">
@@ -34869,19 +35476,19 @@
       <c r="B9" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C9" s="236">
+      <c r="C9" s="239">
         <f>Statement!AA89</f>
         <v>0.20100974521545145</v>
       </c>
-      <c r="D9" s="237"/>
-      <c r="F9" s="236">
+      <c r="D9" s="240"/>
+      <c r="F9" s="239">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.17615269633206854</v>
       </c>
-      <c r="G9" s="237"/>
+      <c r="G9" s="240"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="208" t="s">
@@ -34908,19 +35515,19 @@
       <c r="B11" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C11" s="236">
+      <c r="C11" s="239">
         <f>Statement!AA90</f>
         <v>0.19697414518622902</v>
       </c>
-      <c r="D11" s="237"/>
-      <c r="F11" s="236">
+      <c r="D11" s="240"/>
+      <c r="F11" s="239">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.293272836358182</v>
       </c>
-      <c r="G11" s="237"/>
+      <c r="G11" s="240"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="208" t="s">
@@ -34947,19 +35554,19 @@
       <c r="B13" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C13" s="236">
+      <c r="C13" s="239">
         <f>Statement!AA93</f>
         <v>0.12172505151604357</v>
       </c>
-      <c r="D13" s="237"/>
-      <c r="F13" s="236">
+      <c r="D13" s="240"/>
+      <c r="F13" s="239">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.51510934393638175</v>
       </c>
-      <c r="G13" s="237"/>
+      <c r="G13" s="240"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="208" t="s">
@@ -34986,19 +35593,19 @@
       <c r="B15" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C15" s="236">
+      <c r="C15" s="239">
         <f>Statement!AA94</f>
         <v>0.20851486489537011</v>
       </c>
-      <c r="D15" s="237"/>
-      <c r="F15" s="236">
+      <c r="D15" s="240"/>
+      <c r="F15" s="239">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.4741658193918108</v>
       </c>
-      <c r="G15" s="237"/>
+      <c r="G15" s="240"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="208" t="s">
@@ -35025,19 +35632,19 @@
       <c r="B17" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C17" s="236">
+      <c r="C17" s="239">
         <f>Statement!AA96</f>
         <v>0.35756517690875234</v>
       </c>
-      <c r="D17" s="237"/>
-      <c r="F17" s="236">
+      <c r="D17" s="240"/>
+      <c r="F17" s="239">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>2.1063115845539282</v>
       </c>
-      <c r="G17" s="237"/>
+      <c r="G17" s="240"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="208" t="s">
@@ -35064,22 +35671,22 @@
       <c r="B19" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C19" s="236">
+      <c r="C19" s="239">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-1.6781270464963983E-3</v>
       </c>
-      <c r="D19" s="237"/>
-      <c r="F19" s="236">
+      <c r="D19" s="240"/>
+      <c r="F19" s="239">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-8.9390922758116297E-3</v>
       </c>
-      <c r="G19" s="237"/>
+      <c r="G19" s="240"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="208" t="s">
@@ -35106,22 +35713,22 @@
       <c r="B21" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C21" s="236">
+      <c r="C21" s="239">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.35795454545454553</v>
       </c>
-      <c r="D21" s="237"/>
-      <c r="F21" s="236">
+      <c r="D21" s="240"/>
+      <c r="F21" s="239">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>2.1447368421052633</v>
       </c>
-      <c r="G21" s="237"/>
+      <c r="G21" s="240"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -35169,22 +35776,22 @@
       <c r="B25" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C25" s="236">
+      <c r="C25" s="239">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.11992074288756137</v>
       </c>
-      <c r="D25" s="237"/>
-      <c r="F25" s="236">
+      <c r="D25" s="240"/>
+      <c r="F25" s="239">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>1.1517699869310756</v>
       </c>
-      <c r="G25" s="237"/>
+      <c r="G25" s="240"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="224" t="s">
@@ -35211,22 +35818,22 @@
       <c r="B27" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C27" s="236">
+      <c r="C27" s="239">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.31147368421052629</v>
       </c>
-      <c r="D27" s="237"/>
-      <c r="F27" s="236">
+      <c r="D27" s="240"/>
+      <c r="F27" s="239">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.73741458652907543</v>
       </c>
-      <c r="G27" s="237"/>
+      <c r="G27" s="240"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -35253,22 +35860,22 @@
       <c r="B29" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C29" s="236">
+      <c r="C29" s="239">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.20752960811374652</v>
       </c>
-      <c r="D29" s="237"/>
-      <c r="F29" s="236">
+      <c r="D29" s="240"/>
+      <c r="F29" s="239">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.92385968500715898</v>
       </c>
-      <c r="G29" s="237"/>
+      <c r="G29" s="240"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35295,43 +35902,25 @@
       <c r="B31" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C31" s="236">
+      <c r="C31" s="239">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>9.5647686220540165E-2</v>
       </c>
-      <c r="D31" s="237"/>
-      <c r="F31" s="236">
+      <c r="D31" s="240"/>
+      <c r="F31" s="239">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.28666666666666668</v>
       </c>
-      <c r="G31" s="237"/>
+      <c r="G31" s="240"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C25:D25"/>
@@ -35340,6 +35929,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DC523E6-1ED8-DF4B-9688-6199A7F16521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{506FA025-F08B-0C44-A7F5-D539158C42BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2296,9 +2296,11 @@
     </xf>
     <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="39" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2308,6 +2310,15 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2315,12 +2326,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2350,11 +2355,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="39" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="39" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12698,12 +12698,12 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>236.54</v>
-    <v>162.02000000000001</v>
-    <v>2.2214</v>
-    <v>8.18</v>
-    <v>4.0339E-2</v>
-    <v>-0.39</v>
-    <v>-1.8490000000000002E-3</v>
+    <v>164.07</v>
+    <v>2.2212999999999998</v>
+    <v>-5.0999999999999996</v>
+    <v>-2.4E-2</v>
+    <v>-1.4350000000000001</v>
+    <v>-6.9189999999999998E-3</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -12711,25 +12711,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2788 San Tomas Expressway, SANTA CLARA, CA, 95051 US</v>
-    <v>211</v>
+    <v>211.08</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46213.999999178122</v>
+    <v>46219.999965416406</v>
     <v>0</v>
-    <v>201.92</v>
-    <v>5105232000000</v>
+    <v>205.845</v>
+    <v>5019080000000</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
-    <v>202</v>
-    <v>31.053699999999999</v>
-    <v>202.78</v>
-    <v>210.96</v>
-    <v>210.57</v>
+    <v>210.17</v>
+    <v>31.761099999999999</v>
+    <v>212.5</v>
+    <v>207.4</v>
+    <v>205.965</v>
     <v>24200000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>148421001</v>
-    <v>152809403</v>
+    <v>122986074</v>
+    <v>146051455</v>
     <v>1998</v>
   </rv>
   <rv s="2">
@@ -12753,16 +12753,16 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>0.3</v>
-    <v>6.6090000000000003E-3</v>
+    <v>0.24</v>
+    <v>5.2810000000000001E-3</v>
     <v>US</v>
-    <v>45.71</v>
+    <v>45.96</v>
     <v>Index</v>
     <v>3</v>
-    <v>45.39</v>
+    <v>45.61</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>45.41</v>
-    <v>45.39</v>
+    <v>45.82</v>
+    <v>45.45</v>
     <v>45.69</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
@@ -13558,18 +13558,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="233" t="s">
+      <c r="B2" s="237" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="234"/>
-      <c r="E2" s="233" t="s">
+      <c r="C2" s="238"/>
+      <c r="E2" s="237" t="s">
         <v>284</v>
       </c>
-      <c r="F2" s="234"/>
-      <c r="H2" s="233" t="s">
+      <c r="F2" s="238"/>
+      <c r="H2" s="237" t="s">
         <v>325</v>
       </c>
-      <c r="I2" s="234"/>
+      <c r="I2" s="238"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="186" t="s">
@@ -13584,7 +13584,7 @@
       </c>
       <c r="F3" s="188">
         <f ca="1">Statement!AC155</f>
-        <v>5127382.8</v>
+        <v>5040857</v>
       </c>
       <c r="H3" s="186" t="str">
         <f>'AVG target price'!B5</f>
@@ -13608,7 +13608,7 @@
       </c>
       <c r="F4" s="189">
         <f ca="1">Statement!AC156</f>
-        <v>5055280.8</v>
+        <v>4968755</v>
       </c>
       <c r="H4" s="186" t="str">
         <f>'AVG target price'!B6</f>
@@ -13625,7 +13625,7 @@
       </c>
       <c r="C5" s="209" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>210.96</v>
+        <v>207.4</v>
       </c>
       <c r="E5" s="186" t="s">
         <v>240</v>
@@ -13649,14 +13649,14 @@
       </c>
       <c r="C6" s="209" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>210.57</v>
+        <v>205.965</v>
       </c>
       <c r="E6" s="186" t="s">
         <v>234</v>
       </c>
       <c r="F6" s="191">
         <f ca="1">Statement!AC152</f>
-        <v>32.306278713629411</v>
+        <v>31.761102603369071</v>
       </c>
       <c r="H6" s="186" t="str">
         <f>'AVG target price'!B8</f>
@@ -13673,14 +13673,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>8.18</v>
+        <v>-5.0999999999999996</v>
       </c>
       <c r="E7" s="187" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="192">
         <f ca="1">Statement!AC153</f>
-        <v>20.355658070700738</v>
+        <v>20.012151516227402</v>
       </c>
       <c r="H7" s="185" t="str">
         <f>'AVG target price'!B9</f>
@@ -13697,14 +13697,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.39</v>
+        <v>-1.4350000000000001</v>
       </c>
       <c r="E8" s="186" t="s">
         <v>262</v>
       </c>
       <c r="F8" s="193">
         <f ca="1">Statement!AC163</f>
-        <v>2.1889725104979486E-2</v>
+        <v>2.2265460019992633E-2</v>
       </c>
       <c r="H8" s="185" t="str">
         <f>'AVG target price'!B11</f>
@@ -13712,7 +13712,7 @@
       </c>
       <c r="I8" s="214">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.41370983447516951</v>
+        <v>0.43797602064070279</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13721,14 +13721,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>4.0339E-2</v>
+        <v>-2.4E-2</v>
       </c>
       <c r="E9" s="186" t="s">
         <v>285</v>
       </c>
       <c r="F9" s="193">
         <f ca="1">Statement!AC164</f>
-        <v>3.0953735305271138E-2</v>
+        <v>3.1485053037608485E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13737,14 +13737,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.8490000000000002E-3</v>
+        <v>-6.9189999999999998E-3</v>
       </c>
       <c r="E10" s="186" t="s">
         <v>290</v>
       </c>
       <c r="F10" s="193">
         <f ca="1">Statement!AC166</f>
-        <v>8.835696839330975E-3</v>
+        <v>8.9873606809318333E-3</v>
       </c>
       <c r="H10" s="185" t="s">
         <v>409</v>
@@ -13767,7 +13767,7 @@
       </c>
       <c r="F11" s="194">
         <f ca="1">Statement!AC165</f>
-        <v>1.8960940462646946E-4</v>
+        <v>1.9286403085824494E-4</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13776,7 +13776,7 @@
       </c>
       <c r="C12" s="210" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>162.02000000000001</v>
+        <v>164.07</v>
       </c>
       <c r="E12" s="186" t="s">
         <v>94</v>
@@ -13792,7 +13792,7 @@
       </c>
       <c r="C13" s="210" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.2214</v>
+        <v>2.2212999999999998</v>
       </c>
       <c r="E13" s="186" t="s">
         <v>96</v>
@@ -13808,7 +13808,7 @@
       </c>
       <c r="C14" s="211" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>152809403</v>
+        <v>146051455</v>
       </c>
       <c r="E14" s="187" t="s">
         <v>97</v>
@@ -13824,7 +13824,7 @@
       </c>
       <c r="F15" s="193">
         <f ca="1">Statement!AC178</f>
-        <v>1.4062144921186693E-2</v>
+        <v>1.4303520214915837E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13837,10 +13837,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="235" t="s">
+      <c r="B17" s="239" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="235"/>
+      <c r="C17" s="239"/>
       <c r="E17" s="185" t="s">
         <v>293</v>
       </c>
@@ -13913,14 +13913,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="235" t="s">
+      <c r="B25" s="239" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="235"/>
-      <c r="E25" s="233" t="s">
+      <c r="C25" s="239"/>
+      <c r="E25" s="237" t="s">
         <v>340</v>
       </c>
-      <c r="F25" s="234"/>
+      <c r="F25" s="238"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="185" t="s">
@@ -13969,15 +13969,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="232" t="s">
+      <c r="B33" s="240" t="s">
         <v>335</v>
       </c>
-      <c r="C33" s="232"/>
-      <c r="D33" s="232"/>
-      <c r="E33" s="232"/>
-      <c r="F33" s="232"/>
-      <c r="G33" s="232"/>
-      <c r="H33" s="232"/>
+      <c r="C33" s="240"/>
+      <c r="D33" s="240"/>
+      <c r="E33" s="240"/>
+      <c r="F33" s="240"/>
+      <c r="G33" s="240"/>
+      <c r="H33" s="240"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -13996,24 +13996,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="232"/>
-      <c r="C39" s="232"/>
-      <c r="D39" s="232"/>
-      <c r="E39" s="232"/>
-      <c r="F39" s="232"/>
-      <c r="G39" s="232"/>
-      <c r="H39" s="232"/>
+      <c r="B39" s="240"/>
+      <c r="C39" s="240"/>
+      <c r="D39" s="240"/>
+      <c r="E39" s="240"/>
+      <c r="F39" s="240"/>
+      <c r="G39" s="240"/>
+      <c r="H39" s="240"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="232" t="s">
+      <c r="B42" s="240" t="s">
         <v>338</v>
       </c>
-      <c r="C42" s="232"/>
-      <c r="D42" s="232"/>
-      <c r="E42" s="232"/>
-      <c r="F42" s="232"/>
-      <c r="G42" s="232"/>
-      <c r="H42" s="232"/>
+      <c r="C42" s="240"/>
+      <c r="D42" s="240"/>
+      <c r="E42" s="240"/>
+      <c r="F42" s="240"/>
+      <c r="G42" s="240"/>
+      <c r="H42" s="240"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14028,24 +14028,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="232"/>
-      <c r="C49" s="232"/>
-      <c r="D49" s="232"/>
-      <c r="E49" s="232"/>
-      <c r="F49" s="232"/>
-      <c r="G49" s="232"/>
-      <c r="H49" s="232"/>
+      <c r="B49" s="240"/>
+      <c r="C49" s="240"/>
+      <c r="D49" s="240"/>
+      <c r="E49" s="240"/>
+      <c r="F49" s="240"/>
+      <c r="G49" s="240"/>
+      <c r="H49" s="240"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="232" t="s">
+      <c r="B52" s="240" t="s">
         <v>101</v>
       </c>
-      <c r="C52" s="232"/>
-      <c r="D52" s="232"/>
-      <c r="E52" s="232"/>
-      <c r="F52" s="232"/>
-      <c r="G52" s="232"/>
-      <c r="H52" s="232"/>
+      <c r="C52" s="240"/>
+      <c r="D52" s="240"/>
+      <c r="E52" s="240"/>
+      <c r="F52" s="240"/>
+      <c r="G52" s="240"/>
+      <c r="H52" s="240"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14060,28 +14060,28 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="232"/>
-      <c r="C59" s="232"/>
-      <c r="D59" s="232"/>
-      <c r="E59" s="232"/>
-      <c r="F59" s="232"/>
-      <c r="G59" s="232"/>
-      <c r="H59" s="232"/>
+      <c r="B59" s="240"/>
+      <c r="C59" s="240"/>
+      <c r="D59" s="240"/>
+      <c r="E59" s="240"/>
+      <c r="F59" s="240"/>
+      <c r="G59" s="240"/>
+      <c r="H59" s="240"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B49:H49"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B52:H52"/>
-    <mergeCell ref="B59:H59"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B49:H49"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14151,36 +14151,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="240" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="232" t="s">
+      <c r="S2" s="240" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="232"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="232"/>
-      <c r="W2" s="232"/>
-      <c r="X2" s="232"/>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="232"/>
-      <c r="AA2" s="232" t="s">
+      <c r="T2" s="240"/>
+      <c r="U2" s="240"/>
+      <c r="V2" s="240"/>
+      <c r="W2" s="240"/>
+      <c r="X2" s="240"/>
+      <c r="Y2" s="240"/>
+      <c r="Z2" s="240"/>
+      <c r="AA2" s="240" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="232"/>
-      <c r="AC2" s="232"/>
+      <c r="AB2" s="240"/>
+      <c r="AC2" s="240"/>
       <c r="AE2" s="85" t="s">
         <v>107</v>
       </c>
@@ -14191,32 +14191,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="241" t="s">
+      <c r="C4" s="246" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="241"/>
-      <c r="E4" s="241"/>
-      <c r="F4" s="241"/>
-      <c r="G4" s="241"/>
-      <c r="H4" s="241"/>
-      <c r="I4" s="241"/>
-      <c r="J4" s="241"/>
-      <c r="K4" s="241"/>
-      <c r="L4" s="241"/>
+      <c r="D4" s="246"/>
+      <c r="E4" s="246"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
+      <c r="H4" s="246"/>
+      <c r="I4" s="246"/>
+      <c r="J4" s="246"/>
+      <c r="K4" s="246"/>
+      <c r="L4" s="246"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="242" t="s">
+      <c r="S4" s="247" t="s">
         <v>108</v>
       </c>
-      <c r="T4" s="243"/>
-      <c r="U4" s="243"/>
-      <c r="V4" s="243"/>
-      <c r="W4" s="243"/>
-      <c r="X4" s="243"/>
-      <c r="Y4" s="243"/>
-      <c r="Z4" s="243"/>
-      <c r="AA4" s="243"/>
-      <c r="AB4" s="243"/>
-      <c r="AC4" s="243"/>
+      <c r="T4" s="248"/>
+      <c r="U4" s="248"/>
+      <c r="V4" s="248"/>
+      <c r="W4" s="248"/>
+      <c r="X4" s="248"/>
+      <c r="Y4" s="248"/>
+      <c r="Z4" s="248"/>
+      <c r="AA4" s="248"/>
+      <c r="AB4" s="248"/>
+      <c r="AC4" s="248"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -14801,33 +14801,33 @@
       <c r="Q11" s="91"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C12" s="241" t="s">
+      <c r="C12" s="246" t="s">
         <v>114</v>
       </c>
-      <c r="D12" s="241"/>
-      <c r="E12" s="241"/>
-      <c r="F12" s="241"/>
-      <c r="G12" s="241"/>
-      <c r="H12" s="241"/>
-      <c r="I12" s="241"/>
-      <c r="J12" s="241"/>
-      <c r="K12" s="241"/>
-      <c r="L12" s="241"/>
+      <c r="D12" s="246"/>
+      <c r="E12" s="246"/>
+      <c r="F12" s="246"/>
+      <c r="G12" s="246"/>
+      <c r="H12" s="246"/>
+      <c r="I12" s="246"/>
+      <c r="J12" s="246"/>
+      <c r="K12" s="246"/>
+      <c r="L12" s="246"/>
       <c r="O12" s="5"/>
       <c r="Q12" s="91"/>
-      <c r="S12" s="242" t="s">
+      <c r="S12" s="247" t="s">
         <v>114</v>
       </c>
-      <c r="T12" s="243"/>
-      <c r="U12" s="243"/>
-      <c r="V12" s="243"/>
-      <c r="W12" s="243"/>
-      <c r="X12" s="243"/>
-      <c r="Y12" s="243"/>
-      <c r="Z12" s="243"/>
-      <c r="AA12" s="243"/>
-      <c r="AB12" s="243"/>
-      <c r="AC12" s="243"/>
+      <c r="T12" s="248"/>
+      <c r="U12" s="248"/>
+      <c r="V12" s="248"/>
+      <c r="W12" s="248"/>
+      <c r="X12" s="248"/>
+      <c r="Y12" s="248"/>
+      <c r="Z12" s="248"/>
+      <c r="AA12" s="248"/>
+      <c r="AB12" s="248"/>
+      <c r="AC12" s="248"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B13" s="16" t="s">
@@ -15376,35 +15376,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="240" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
-      <c r="P2" s="232" t="s">
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
+      <c r="P2" s="240" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="232"/>
-      <c r="R2" s="232"/>
-      <c r="S2" s="232"/>
-      <c r="T2" s="232"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="232"/>
-      <c r="W2" s="232"/>
-      <c r="X2" s="232" t="s">
+      <c r="Q2" s="240"/>
+      <c r="R2" s="240"/>
+      <c r="S2" s="240"/>
+      <c r="T2" s="240"/>
+      <c r="U2" s="240"/>
+      <c r="V2" s="240"/>
+      <c r="W2" s="240"/>
+      <c r="X2" s="240" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="232"/>
+      <c r="Y2" s="240"/>
+      <c r="Z2" s="240"/>
       <c r="AB2" s="85" t="s">
         <v>107</v>
       </c>
@@ -15413,31 +15413,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="241" t="s">
+      <c r="C4" s="246" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="241"/>
-      <c r="E4" s="241"/>
-      <c r="F4" s="241"/>
-      <c r="G4" s="241"/>
-      <c r="H4" s="241"/>
-      <c r="I4" s="241"/>
-      <c r="J4" s="241"/>
-      <c r="K4" s="241"/>
-      <c r="L4" s="241"/>
-      <c r="P4" s="243" t="s">
+      <c r="D4" s="246"/>
+      <c r="E4" s="246"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
+      <c r="H4" s="246"/>
+      <c r="I4" s="246"/>
+      <c r="J4" s="246"/>
+      <c r="K4" s="246"/>
+      <c r="L4" s="246"/>
+      <c r="P4" s="248" t="s">
         <v>108</v>
       </c>
-      <c r="Q4" s="243"/>
-      <c r="R4" s="243"/>
-      <c r="S4" s="243"/>
-      <c r="T4" s="243"/>
-      <c r="U4" s="243"/>
-      <c r="V4" s="243"/>
-      <c r="W4" s="243"/>
-      <c r="X4" s="243"/>
-      <c r="Y4" s="243"/>
-      <c r="Z4" s="243"/>
+      <c r="Q4" s="248"/>
+      <c r="R4" s="248"/>
+      <c r="S4" s="248"/>
+      <c r="T4" s="248"/>
+      <c r="U4" s="248"/>
+      <c r="V4" s="248"/>
+      <c r="W4" s="248"/>
+      <c r="X4" s="248"/>
+      <c r="Y4" s="248"/>
+      <c r="Z4" s="248"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -15632,32 +15632,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="241" t="s">
+      <c r="C9" s="246" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="241"/>
-      <c r="E9" s="241"/>
-      <c r="F9" s="241"/>
-      <c r="G9" s="241"/>
-      <c r="H9" s="241"/>
-      <c r="I9" s="241"/>
-      <c r="J9" s="241"/>
-      <c r="K9" s="241"/>
-      <c r="L9" s="241"/>
+      <c r="D9" s="246"/>
+      <c r="E9" s="246"/>
+      <c r="F9" s="246"/>
+      <c r="G9" s="246"/>
+      <c r="H9" s="246"/>
+      <c r="I9" s="246"/>
+      <c r="J9" s="246"/>
+      <c r="K9" s="246"/>
+      <c r="L9" s="246"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="243" t="s">
+      <c r="P9" s="248" t="s">
         <v>118</v>
       </c>
-      <c r="Q9" s="243"/>
-      <c r="R9" s="243"/>
-      <c r="S9" s="243"/>
-      <c r="T9" s="243"/>
-      <c r="U9" s="243"/>
-      <c r="V9" s="243"/>
-      <c r="W9" s="243"/>
-      <c r="X9" s="243"/>
-      <c r="Y9" s="243"/>
-      <c r="Z9" s="243"/>
+      <c r="Q9" s="248"/>
+      <c r="R9" s="248"/>
+      <c r="S9" s="248"/>
+      <c r="T9" s="248"/>
+      <c r="U9" s="248"/>
+      <c r="V9" s="248"/>
+      <c r="W9" s="248"/>
+      <c r="X9" s="248"/>
+      <c r="Y9" s="248"/>
+      <c r="Z9" s="248"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -16133,31 +16133,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="241" t="s">
+      <c r="C17" s="246" t="s">
         <v>120</v>
       </c>
-      <c r="D17" s="241"/>
-      <c r="E17" s="241"/>
-      <c r="F17" s="241"/>
-      <c r="G17" s="241"/>
-      <c r="H17" s="241"/>
-      <c r="I17" s="241"/>
-      <c r="J17" s="241"/>
-      <c r="K17" s="241"/>
-      <c r="L17" s="241"/>
-      <c r="P17" s="243" t="s">
+      <c r="D17" s="246"/>
+      <c r="E17" s="246"/>
+      <c r="F17" s="246"/>
+      <c r="G17" s="246"/>
+      <c r="H17" s="246"/>
+      <c r="I17" s="246"/>
+      <c r="J17" s="246"/>
+      <c r="K17" s="246"/>
+      <c r="L17" s="246"/>
+      <c r="P17" s="248" t="s">
         <v>120</v>
       </c>
-      <c r="Q17" s="243"/>
-      <c r="R17" s="243"/>
-      <c r="S17" s="243"/>
-      <c r="T17" s="243"/>
-      <c r="U17" s="243"/>
-      <c r="V17" s="243"/>
-      <c r="W17" s="243"/>
-      <c r="X17" s="243"/>
-      <c r="Y17" s="243"/>
-      <c r="Z17" s="243"/>
+      <c r="Q17" s="248"/>
+      <c r="R17" s="248"/>
+      <c r="S17" s="248"/>
+      <c r="T17" s="248"/>
+      <c r="U17" s="248"/>
+      <c r="V17" s="248"/>
+      <c r="W17" s="248"/>
+      <c r="X17" s="248"/>
+      <c r="Y17" s="248"/>
+      <c r="Z17" s="248"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="16" t="s">
@@ -16635,60 +16635,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="240" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
-      <c r="G3" s="244"/>
-      <c r="H3" s="245" t="s">
+      <c r="D3" s="240"/>
+      <c r="E3" s="240"/>
+      <c r="F3" s="240"/>
+      <c r="G3" s="249"/>
+      <c r="H3" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
-      <c r="P3" s="246"/>
-      <c r="Q3" s="246"/>
-      <c r="R3" s="246"/>
-      <c r="S3" s="246"/>
-      <c r="T3" s="246"/>
-      <c r="U3" s="246"/>
-      <c r="V3" s="246"/>
-      <c r="W3" s="246"/>
-      <c r="X3" s="246"/>
-      <c r="Y3" s="246"/>
-      <c r="Z3" s="246"/>
+      <c r="I3" s="240"/>
+      <c r="J3" s="240"/>
+      <c r="K3" s="240"/>
+      <c r="L3" s="240"/>
+      <c r="P3" s="251"/>
+      <c r="Q3" s="251"/>
+      <c r="R3" s="251"/>
+      <c r="S3" s="251"/>
+      <c r="T3" s="251"/>
+      <c r="U3" s="251"/>
+      <c r="V3" s="251"/>
+      <c r="W3" s="251"/>
+      <c r="X3" s="251"/>
+      <c r="Y3" s="251"/>
+      <c r="Z3" s="251"/>
       <c r="AB3" s="110"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="241" t="s">
+      <c r="C5" s="246" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="241"/>
-      <c r="E5" s="241"/>
-      <c r="F5" s="241"/>
-      <c r="G5" s="241"/>
-      <c r="H5" s="241"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="241"/>
-      <c r="K5" s="241"/>
-      <c r="L5" s="241"/>
-      <c r="P5" s="246"/>
-      <c r="Q5" s="246"/>
-      <c r="R5" s="246"/>
-      <c r="S5" s="246"/>
-      <c r="T5" s="246"/>
-      <c r="U5" s="246"/>
-      <c r="V5" s="246"/>
-      <c r="W5" s="246"/>
-      <c r="X5" s="246"/>
-      <c r="Y5" s="246"/>
-      <c r="Z5" s="246"/>
+      <c r="D5" s="246"/>
+      <c r="E5" s="246"/>
+      <c r="F5" s="246"/>
+      <c r="G5" s="246"/>
+      <c r="H5" s="246"/>
+      <c r="I5" s="246"/>
+      <c r="J5" s="246"/>
+      <c r="K5" s="246"/>
+      <c r="L5" s="246"/>
+      <c r="P5" s="251"/>
+      <c r="Q5" s="251"/>
+      <c r="R5" s="251"/>
+      <c r="S5" s="251"/>
+      <c r="T5" s="251"/>
+      <c r="U5" s="251"/>
+      <c r="V5" s="251"/>
+      <c r="W5" s="251"/>
+      <c r="X5" s="251"/>
+      <c r="Y5" s="251"/>
+      <c r="Z5" s="251"/>
       <c r="AB5" s="111"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -16874,30 +16874,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="241" t="s">
+      <c r="C11" s="246" t="s">
         <v>124</v>
       </c>
-      <c r="D11" s="241"/>
-      <c r="E11" s="241"/>
-      <c r="F11" s="241"/>
-      <c r="G11" s="241"/>
-      <c r="H11" s="241"/>
-      <c r="I11" s="241"/>
-      <c r="J11" s="241"/>
-      <c r="K11" s="241"/>
-      <c r="L11" s="241"/>
+      <c r="D11" s="246"/>
+      <c r="E11" s="246"/>
+      <c r="F11" s="246"/>
+      <c r="G11" s="246"/>
+      <c r="H11" s="246"/>
+      <c r="I11" s="246"/>
+      <c r="J11" s="246"/>
+      <c r="K11" s="246"/>
+      <c r="L11" s="246"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="246"/>
-      <c r="Q11" s="246"/>
-      <c r="R11" s="246"/>
-      <c r="S11" s="246"/>
-      <c r="T11" s="246"/>
-      <c r="U11" s="246"/>
-      <c r="V11" s="246"/>
-      <c r="W11" s="246"/>
-      <c r="X11" s="246"/>
-      <c r="Y11" s="246"/>
-      <c r="Z11" s="246"/>
+      <c r="P11" s="251"/>
+      <c r="Q11" s="251"/>
+      <c r="R11" s="251"/>
+      <c r="S11" s="251"/>
+      <c r="T11" s="251"/>
+      <c r="U11" s="251"/>
+      <c r="V11" s="251"/>
+      <c r="W11" s="251"/>
+      <c r="X11" s="251"/>
+      <c r="Y11" s="251"/>
+      <c r="Z11" s="251"/>
       <c r="AB11" s="111"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -17139,18 +17139,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="241" t="s">
+      <c r="C18" s="246" t="s">
         <v>129</v>
       </c>
-      <c r="D18" s="241"/>
-      <c r="E18" s="241"/>
-      <c r="F18" s="241"/>
-      <c r="G18" s="241"/>
-      <c r="H18" s="241"/>
-      <c r="I18" s="241"/>
-      <c r="J18" s="241"/>
-      <c r="K18" s="241"/>
-      <c r="L18" s="241"/>
+      <c r="D18" s="246"/>
+      <c r="E18" s="246"/>
+      <c r="F18" s="246"/>
+      <c r="G18" s="246"/>
+      <c r="H18" s="246"/>
+      <c r="I18" s="246"/>
+      <c r="J18" s="246"/>
+      <c r="K18" s="246"/>
+      <c r="L18" s="246"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17363,23 +17363,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="246"/>
-      <c r="C25" s="246"/>
+      <c r="B25" s="251"/>
+      <c r="C25" s="251"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="110"/>
-      <c r="C26" s="241" t="s">
+      <c r="C26" s="246" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="241"/>
-      <c r="E26" s="241"/>
-      <c r="F26" s="241"/>
-      <c r="G26" s="241"/>
-      <c r="H26" s="241"/>
-      <c r="I26" s="241"/>
-      <c r="J26" s="241"/>
-      <c r="K26" s="241"/>
-      <c r="L26" s="241"/>
+      <c r="D26" s="246"/>
+      <c r="E26" s="246"/>
+      <c r="F26" s="246"/>
+      <c r="G26" s="246"/>
+      <c r="H26" s="246"/>
+      <c r="I26" s="246"/>
+      <c r="J26" s="246"/>
+      <c r="K26" s="246"/>
+      <c r="L26" s="246"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -17571,18 +17571,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="110"/>
-      <c r="C33" s="241" t="s">
+      <c r="C33" s="246" t="s">
         <v>139</v>
       </c>
-      <c r="D33" s="241"/>
-      <c r="E33" s="241"/>
-      <c r="F33" s="241"/>
-      <c r="G33" s="241"/>
-      <c r="H33" s="241"/>
-      <c r="I33" s="241"/>
-      <c r="J33" s="241"/>
-      <c r="K33" s="241"/>
-      <c r="L33" s="241"/>
+      <c r="D33" s="246"/>
+      <c r="E33" s="246"/>
+      <c r="F33" s="246"/>
+      <c r="G33" s="246"/>
+      <c r="H33" s="246"/>
+      <c r="I33" s="246"/>
+      <c r="J33" s="246"/>
+      <c r="K33" s="246"/>
+      <c r="L33" s="246"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -17766,18 +17766,18 @@
       <c r="C39" s="126"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="241" t="s">
+      <c r="C40" s="246" t="s">
         <v>142</v>
       </c>
-      <c r="D40" s="241"/>
-      <c r="E40" s="241"/>
-      <c r="F40" s="241"/>
-      <c r="G40" s="241"/>
-      <c r="H40" s="241"/>
-      <c r="I40" s="241"/>
-      <c r="J40" s="241"/>
-      <c r="K40" s="241"/>
-      <c r="L40" s="241"/>
+      <c r="D40" s="246"/>
+      <c r="E40" s="246"/>
+      <c r="F40" s="246"/>
+      <c r="G40" s="246"/>
+      <c r="H40" s="246"/>
+      <c r="I40" s="246"/>
+      <c r="J40" s="246"/>
+      <c r="K40" s="246"/>
+      <c r="L40" s="246"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18041,6 +18041,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18048,12 +18054,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18091,60 +18091,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="240" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
-      <c r="S2" s="246"/>
-      <c r="T2" s="246"/>
-      <c r="U2" s="246"/>
-      <c r="V2" s="246"/>
-      <c r="W2" s="246"/>
-      <c r="X2" s="246"/>
-      <c r="Y2" s="246"/>
-      <c r="Z2" s="246"/>
-      <c r="AA2" s="246"/>
-      <c r="AB2" s="246"/>
-      <c r="AC2" s="246"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
+      <c r="S2" s="251"/>
+      <c r="T2" s="251"/>
+      <c r="U2" s="251"/>
+      <c r="V2" s="251"/>
+      <c r="W2" s="251"/>
+      <c r="X2" s="251"/>
+      <c r="Y2" s="251"/>
+      <c r="Z2" s="251"/>
+      <c r="AA2" s="251"/>
+      <c r="AB2" s="251"/>
+      <c r="AC2" s="251"/>
       <c r="AE2" s="110"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="241" t="s">
+      <c r="C4" s="246" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="241"/>
-      <c r="E4" s="241"/>
-      <c r="F4" s="241"/>
-      <c r="G4" s="241"/>
-      <c r="H4" s="241"/>
-      <c r="I4" s="241"/>
-      <c r="J4" s="241"/>
-      <c r="K4" s="241"/>
-      <c r="L4" s="241"/>
-      <c r="S4" s="246"/>
-      <c r="T4" s="246"/>
-      <c r="U4" s="246"/>
-      <c r="V4" s="246"/>
-      <c r="W4" s="246"/>
-      <c r="X4" s="246"/>
-      <c r="Y4" s="246"/>
-      <c r="Z4" s="246"/>
-      <c r="AA4" s="246"/>
-      <c r="AB4" s="246"/>
-      <c r="AC4" s="246"/>
+      <c r="D4" s="246"/>
+      <c r="E4" s="246"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
+      <c r="H4" s="246"/>
+      <c r="I4" s="246"/>
+      <c r="J4" s="246"/>
+      <c r="K4" s="246"/>
+      <c r="L4" s="246"/>
+      <c r="S4" s="251"/>
+      <c r="T4" s="251"/>
+      <c r="U4" s="251"/>
+      <c r="V4" s="251"/>
+      <c r="W4" s="251"/>
+      <c r="X4" s="251"/>
+      <c r="Y4" s="251"/>
+      <c r="Z4" s="251"/>
+      <c r="AA4" s="251"/>
+      <c r="AB4" s="251"/>
+      <c r="AC4" s="251"/>
       <c r="AE4" s="111"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -18507,18 +18507,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="241" t="s">
+      <c r="C13" s="246" t="s">
         <v>150</v>
       </c>
-      <c r="D13" s="241"/>
-      <c r="E13" s="241"/>
-      <c r="F13" s="241"/>
-      <c r="G13" s="241"/>
-      <c r="H13" s="241"/>
-      <c r="I13" s="241"/>
-      <c r="J13" s="241"/>
-      <c r="K13" s="241"/>
-      <c r="L13" s="241"/>
+      <c r="D13" s="246"/>
+      <c r="E13" s="246"/>
+      <c r="F13" s="246"/>
+      <c r="G13" s="246"/>
+      <c r="H13" s="246"/>
+      <c r="I13" s="246"/>
+      <c r="J13" s="246"/>
+      <c r="K13" s="246"/>
+      <c r="L13" s="246"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -18611,18 +18611,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="241" t="s">
+      <c r="C18" s="246" t="s">
         <v>151</v>
       </c>
-      <c r="D18" s="241"/>
-      <c r="E18" s="241"/>
-      <c r="F18" s="241"/>
-      <c r="G18" s="241"/>
-      <c r="H18" s="241"/>
-      <c r="I18" s="241"/>
-      <c r="J18" s="241"/>
-      <c r="K18" s="241"/>
-      <c r="L18" s="241"/>
+      <c r="D18" s="246"/>
+      <c r="E18" s="246"/>
+      <c r="F18" s="246"/>
+      <c r="G18" s="246"/>
+      <c r="H18" s="246"/>
+      <c r="I18" s="246"/>
+      <c r="J18" s="246"/>
+      <c r="K18" s="246"/>
+      <c r="L18" s="246"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -18814,18 +18814,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="241" t="s">
+      <c r="C25" s="246" t="s">
         <v>259</v>
       </c>
-      <c r="D25" s="241"/>
-      <c r="E25" s="241"/>
-      <c r="F25" s="241"/>
-      <c r="G25" s="241"/>
-      <c r="H25" s="241"/>
-      <c r="I25" s="241"/>
-      <c r="J25" s="241"/>
-      <c r="K25" s="241"/>
-      <c r="L25" s="241"/>
+      <c r="D25" s="246"/>
+      <c r="E25" s="246"/>
+      <c r="F25" s="246"/>
+      <c r="G25" s="246"/>
+      <c r="H25" s="246"/>
+      <c r="I25" s="246"/>
+      <c r="J25" s="246"/>
+      <c r="K25" s="246"/>
+      <c r="L25" s="246"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -18963,18 +18963,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="241" t="s">
+      <c r="C31" s="246" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="241"/>
-      <c r="E31" s="241"/>
-      <c r="F31" s="241"/>
-      <c r="G31" s="241"/>
-      <c r="H31" s="241"/>
-      <c r="I31" s="241"/>
-      <c r="J31" s="241"/>
-      <c r="K31" s="241"/>
-      <c r="L31" s="241"/>
+      <c r="D31" s="246"/>
+      <c r="E31" s="246"/>
+      <c r="F31" s="246"/>
+      <c r="G31" s="246"/>
+      <c r="H31" s="246"/>
+      <c r="I31" s="246"/>
+      <c r="J31" s="246"/>
+      <c r="K31" s="246"/>
+      <c r="L31" s="246"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19113,16 +19113,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19185,10 +19185,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="240" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="232"/>
+      <c r="C4" s="240"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19205,7 +19205,7 @@
       </c>
       <c r="C6" s="134">
         <f ca="1">Overview!C5</f>
-        <v>210.96</v>
+        <v>207.4</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19214,7 +19214,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">C5*C6</f>
-        <v>5127382.8</v>
+        <v>5040857</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19241,7 +19241,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C13</f>
-        <v>2.2214</v>
+        <v>2.2212999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19273,10 +19273,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="232" t="s">
+      <c r="B15" s="240" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="232"/>
+      <c r="C15" s="240"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19284,7 +19284,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>1.6491905687016576E-3</v>
+        <v>1.6774512722190502E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19293,7 +19293,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99835080943129839</v>
+        <v>0.99832254872778092</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19311,7 +19311,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14565299999999998</v>
+        <v>0.14564849999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19320,7 +19320,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14547923633410986</v>
+        <v>0.14547176625013589</v>
       </c>
     </row>
   </sheetData>
@@ -19365,60 +19365,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="240" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
-      <c r="G3" s="244"/>
-      <c r="H3" s="245" t="s">
+      <c r="D3" s="240"/>
+      <c r="E3" s="240"/>
+      <c r="F3" s="240"/>
+      <c r="G3" s="249"/>
+      <c r="H3" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
-      <c r="P3" s="246"/>
-      <c r="Q3" s="246"/>
-      <c r="R3" s="246"/>
-      <c r="S3" s="246"/>
-      <c r="T3" s="246"/>
-      <c r="U3" s="246"/>
-      <c r="V3" s="246"/>
-      <c r="W3" s="246"/>
-      <c r="X3" s="246"/>
-      <c r="Y3" s="246"/>
-      <c r="Z3" s="246"/>
+      <c r="I3" s="240"/>
+      <c r="J3" s="240"/>
+      <c r="K3" s="240"/>
+      <c r="L3" s="240"/>
+      <c r="P3" s="251"/>
+      <c r="Q3" s="251"/>
+      <c r="R3" s="251"/>
+      <c r="S3" s="251"/>
+      <c r="T3" s="251"/>
+      <c r="U3" s="251"/>
+      <c r="V3" s="251"/>
+      <c r="W3" s="251"/>
+      <c r="X3" s="251"/>
+      <c r="Y3" s="251"/>
+      <c r="Z3" s="251"/>
       <c r="AB3" s="110"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="241" t="s">
+      <c r="C5" s="246" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="241"/>
-      <c r="E5" s="241"/>
-      <c r="F5" s="241"/>
-      <c r="G5" s="241"/>
-      <c r="H5" s="241"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="241"/>
-      <c r="K5" s="241"/>
-      <c r="L5" s="241"/>
-      <c r="P5" s="246"/>
-      <c r="Q5" s="246"/>
-      <c r="R5" s="246"/>
-      <c r="S5" s="246"/>
-      <c r="T5" s="246"/>
-      <c r="U5" s="246"/>
-      <c r="V5" s="246"/>
-      <c r="W5" s="246"/>
-      <c r="X5" s="246"/>
-      <c r="Y5" s="246"/>
-      <c r="Z5" s="246"/>
+      <c r="D5" s="246"/>
+      <c r="E5" s="246"/>
+      <c r="F5" s="246"/>
+      <c r="G5" s="246"/>
+      <c r="H5" s="246"/>
+      <c r="I5" s="246"/>
+      <c r="J5" s="246"/>
+      <c r="K5" s="246"/>
+      <c r="L5" s="246"/>
+      <c r="P5" s="251"/>
+      <c r="Q5" s="251"/>
+      <c r="R5" s="251"/>
+      <c r="S5" s="251"/>
+      <c r="T5" s="251"/>
+      <c r="U5" s="251"/>
+      <c r="V5" s="251"/>
+      <c r="W5" s="251"/>
+      <c r="X5" s="251"/>
+      <c r="Y5" s="251"/>
+      <c r="Z5" s="251"/>
       <c r="AB5" s="111"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -19664,10 +19664,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="232" t="s">
+      <c r="B13" s="240" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="232"/>
+      <c r="C13" s="240"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -19687,10 +19687,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="232" t="s">
+      <c r="B18" s="240" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="232"/>
+      <c r="C18" s="240"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -19804,37 +19804,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="240" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="241" t="s">
+      <c r="C4" s="246" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="241"/>
-      <c r="E4" s="241"/>
-      <c r="F4" s="241"/>
-      <c r="G4" s="241"/>
-      <c r="H4" s="241"/>
-      <c r="I4" s="241"/>
-      <c r="J4" s="241"/>
-      <c r="K4" s="241"/>
-      <c r="L4" s="241"/>
+      <c r="D4" s="246"/>
+      <c r="E4" s="246"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
+      <c r="H4" s="246"/>
+      <c r="I4" s="246"/>
+      <c r="J4" s="246"/>
+      <c r="K4" s="246"/>
+      <c r="L4" s="246"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20023,18 +20023,18 @@
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="241" t="s">
+      <c r="C10" s="246" t="s">
         <v>114</v>
       </c>
-      <c r="D10" s="241"/>
-      <c r="E10" s="241"/>
-      <c r="F10" s="241"/>
-      <c r="G10" s="241"/>
-      <c r="H10" s="241"/>
-      <c r="I10" s="241"/>
-      <c r="J10" s="241"/>
-      <c r="K10" s="241"/>
-      <c r="L10" s="241"/>
+      <c r="D10" s="246"/>
+      <c r="E10" s="246"/>
+      <c r="F10" s="246"/>
+      <c r="G10" s="246"/>
+      <c r="H10" s="246"/>
+      <c r="I10" s="246"/>
+      <c r="J10" s="246"/>
+      <c r="K10" s="246"/>
+      <c r="L10" s="246"/>
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -20228,18 +20228,18 @@
       <c r="N15" s="91"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="241" t="s">
+      <c r="C16" s="246" t="s">
         <v>188</v>
       </c>
-      <c r="D16" s="241"/>
-      <c r="E16" s="241"/>
-      <c r="F16" s="241"/>
-      <c r="G16" s="241"/>
-      <c r="H16" s="241"/>
-      <c r="I16" s="241"/>
-      <c r="J16" s="241"/>
-      <c r="K16" s="241"/>
-      <c r="L16" s="241"/>
+      <c r="D16" s="246"/>
+      <c r="E16" s="246"/>
+      <c r="F16" s="246"/>
+      <c r="G16" s="246"/>
+      <c r="H16" s="246"/>
+      <c r="I16" s="246"/>
+      <c r="J16" s="246"/>
+      <c r="K16" s="246"/>
+      <c r="L16" s="246"/>
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -20373,18 +20373,18 @@
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="241" t="s">
+      <c r="C21" s="246" t="s">
         <v>191</v>
       </c>
-      <c r="D21" s="241"/>
-      <c r="E21" s="241"/>
-      <c r="F21" s="241"/>
-      <c r="G21" s="241"/>
-      <c r="H21" s="241"/>
-      <c r="I21" s="241"/>
-      <c r="J21" s="241"/>
-      <c r="K21" s="241"/>
-      <c r="L21" s="241"/>
+      <c r="D21" s="246"/>
+      <c r="E21" s="246"/>
+      <c r="F21" s="246"/>
+      <c r="G21" s="246"/>
+      <c r="H21" s="246"/>
+      <c r="I21" s="246"/>
+      <c r="J21" s="246"/>
+      <c r="K21" s="246"/>
+      <c r="L21" s="246"/>
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -20468,18 +20468,18 @@
       <c r="N25" s="91"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="241" t="s">
+      <c r="C26" s="246" t="s">
         <v>192</v>
       </c>
-      <c r="D26" s="241"/>
-      <c r="E26" s="241"/>
-      <c r="F26" s="241"/>
-      <c r="G26" s="241"/>
-      <c r="H26" s="241"/>
-      <c r="I26" s="241"/>
-      <c r="J26" s="241"/>
-      <c r="K26" s="241"/>
-      <c r="L26" s="241"/>
+      <c r="D26" s="246"/>
+      <c r="E26" s="246"/>
+      <c r="F26" s="246"/>
+      <c r="G26" s="246"/>
+      <c r="H26" s="246"/>
+      <c r="I26" s="246"/>
+      <c r="J26" s="246"/>
+      <c r="K26" s="246"/>
+      <c r="L26" s="246"/>
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -20749,10 +20749,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="232" t="s">
+      <c r="B37" s="240" t="s">
         <v>197</v>
       </c>
-      <c r="C37" s="232"/>
+      <c r="C37" s="240"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -20845,10 +20845,10 @@
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="232" t="s">
+      <c r="B49" s="240" t="s">
         <v>202</v>
       </c>
-      <c r="C49" s="232"/>
+      <c r="C49" s="240"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -20904,10 +20904,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="232" t="s">
+      <c r="B57" s="240" t="s">
         <v>319</v>
       </c>
-      <c r="C57" s="232"/>
+      <c r="C57" s="240"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -21047,10 +21047,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="240" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="232"/>
+      <c r="C4" s="240"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21104,7 +21104,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C5</f>
-        <v>210.96</v>
+        <v>207.4</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21113,7 +21113,7 @@
       </c>
       <c r="C11" s="155">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.41370983447516951</v>
+        <v>0.43797602064070279</v>
       </c>
     </row>
   </sheetData>
@@ -21169,37 +21169,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="240" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="241" t="s">
+      <c r="C4" s="246" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="241"/>
-      <c r="E4" s="241"/>
-      <c r="F4" s="241"/>
-      <c r="G4" s="241"/>
-      <c r="H4" s="241"/>
-      <c r="I4" s="241"/>
-      <c r="J4" s="241"/>
-      <c r="K4" s="241"/>
-      <c r="L4" s="241"/>
+      <c r="D4" s="246"/>
+      <c r="E4" s="246"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
+      <c r="H4" s="246"/>
+      <c r="I4" s="246"/>
+      <c r="J4" s="246"/>
+      <c r="K4" s="246"/>
+      <c r="L4" s="246"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21250,23 +21250,23 @@
       <c r="B6" s="16" t="s">
         <v>240</v>
       </c>
-      <c r="C6" s="250">
+      <c r="C6" s="232">
         <f>Statement!M25</f>
         <v>0.38500000000000001</v>
       </c>
-      <c r="D6" s="250">
+      <c r="D6" s="232">
         <f>Statement!N25</f>
         <v>0.17399999999999999</v>
       </c>
-      <c r="E6" s="250">
+      <c r="E6" s="232">
         <f>Statement!O25</f>
         <v>1.1930000000000001</v>
       </c>
-      <c r="F6" s="250">
+      <c r="F6" s="232">
         <f>Statement!P25</f>
         <v>2.94</v>
       </c>
-      <c r="G6" s="251">
+      <c r="G6" s="233">
         <f>Statement!Q25</f>
         <v>4.9000000000000004</v>
       </c>
@@ -21281,23 +21281,23 @@
       <c r="B7" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="C7" s="250">
+      <c r="C7" s="232">
         <f>Statement!M81</f>
         <v>1.6E-2</v>
       </c>
-      <c r="D7" s="250">
+      <c r="D7" s="232">
         <f>Statement!N81</f>
         <v>1.6E-2</v>
       </c>
-      <c r="E7" s="250">
+      <c r="E7" s="232">
         <f>Statement!O81</f>
         <v>1.6E-2</v>
       </c>
-      <c r="F7" s="250">
+      <c r="F7" s="232">
         <f>Statement!P81</f>
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="G7" s="251">
+      <c r="G7" s="233">
         <f>Statement!Q81</f>
         <v>0.04</v>
       </c>
@@ -21312,18 +21312,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="241" t="s">
+      <c r="C9" s="246" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="241"/>
-      <c r="E9" s="241"/>
-      <c r="F9" s="241"/>
-      <c r="G9" s="241"/>
-      <c r="H9" s="241"/>
-      <c r="I9" s="241"/>
-      <c r="J9" s="241"/>
-      <c r="K9" s="241"/>
-      <c r="L9" s="241"/>
+      <c r="D9" s="246"/>
+      <c r="E9" s="246"/>
+      <c r="F9" s="246"/>
+      <c r="G9" s="246"/>
+      <c r="H9" s="246"/>
+      <c r="I9" s="246"/>
+      <c r="J9" s="246"/>
+      <c r="K9" s="246"/>
+      <c r="L9" s="246"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21444,18 +21444,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="241" t="s">
+      <c r="C14" s="246" t="s">
         <v>402</v>
       </c>
-      <c r="D14" s="241"/>
-      <c r="E14" s="241"/>
-      <c r="F14" s="241"/>
-      <c r="G14" s="241"/>
-      <c r="H14" s="241"/>
-      <c r="I14" s="241"/>
-      <c r="J14" s="241"/>
-      <c r="K14" s="241"/>
-      <c r="L14" s="241"/>
+      <c r="D14" s="246"/>
+      <c r="E14" s="246"/>
+      <c r="F14" s="246"/>
+      <c r="G14" s="246"/>
+      <c r="H14" s="246"/>
+      <c r="I14" s="246"/>
+      <c r="J14" s="246"/>
+      <c r="K14" s="246"/>
+      <c r="L14" s="246"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -21545,17 +21545,17 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="232" t="s">
+      <c r="B20" s="240" t="s">
         <v>404</v>
       </c>
-      <c r="C20" s="232"/>
+      <c r="C20" s="240"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="C21" s="252">
+      <c r="C21" s="234">
         <f>G7</f>
         <v>0.04</v>
       </c>
@@ -21564,7 +21564,7 @@
       <c r="B22" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="C22" s="253">
+      <c r="C22" s="235">
         <v>0.15</v>
       </c>
     </row>
@@ -21572,7 +21572,7 @@
       <c r="B23" s="39" t="s">
         <v>407</v>
       </c>
-      <c r="C23" s="254">
+      <c r="C23" s="236">
         <f>C21*(1+C22)</f>
         <v>4.5999999999999999E-2</v>
       </c>
@@ -21590,7 +21590,7 @@
       <c r="B25" s="39" t="s">
         <v>408</v>
       </c>
-      <c r="C25" s="253">
+      <c r="C25" s="235">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
@@ -21605,12 +21605,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B20:C20"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C9:L9"/>
     <mergeCell ref="C14:L14"/>
-    <mergeCell ref="B20:C20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -21649,60 +21649,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="240" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
-      <c r="G3" s="244"/>
-      <c r="H3" s="245" t="s">
+      <c r="D3" s="240"/>
+      <c r="E3" s="240"/>
+      <c r="F3" s="240"/>
+      <c r="G3" s="249"/>
+      <c r="H3" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
-      <c r="P3" s="246"/>
-      <c r="Q3" s="246"/>
-      <c r="R3" s="246"/>
-      <c r="S3" s="246"/>
-      <c r="T3" s="246"/>
-      <c r="U3" s="246"/>
-      <c r="V3" s="246"/>
-      <c r="W3" s="246"/>
-      <c r="X3" s="246"/>
-      <c r="Y3" s="246"/>
-      <c r="Z3" s="246"/>
+      <c r="I3" s="240"/>
+      <c r="J3" s="240"/>
+      <c r="K3" s="240"/>
+      <c r="L3" s="240"/>
+      <c r="P3" s="251"/>
+      <c r="Q3" s="251"/>
+      <c r="R3" s="251"/>
+      <c r="S3" s="251"/>
+      <c r="T3" s="251"/>
+      <c r="U3" s="251"/>
+      <c r="V3" s="251"/>
+      <c r="W3" s="251"/>
+      <c r="X3" s="251"/>
+      <c r="Y3" s="251"/>
+      <c r="Z3" s="251"/>
       <c r="AB3" s="110"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="241" t="s">
+      <c r="C5" s="246" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="241"/>
-      <c r="E5" s="241"/>
-      <c r="F5" s="241"/>
-      <c r="G5" s="241"/>
-      <c r="H5" s="241"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="241"/>
-      <c r="K5" s="241"/>
-      <c r="L5" s="241"/>
-      <c r="P5" s="246"/>
-      <c r="Q5" s="246"/>
-      <c r="R5" s="246"/>
-      <c r="S5" s="246"/>
-      <c r="T5" s="246"/>
-      <c r="U5" s="246"/>
-      <c r="V5" s="246"/>
-      <c r="W5" s="246"/>
-      <c r="X5" s="246"/>
-      <c r="Y5" s="246"/>
-      <c r="Z5" s="246"/>
+      <c r="D5" s="246"/>
+      <c r="E5" s="246"/>
+      <c r="F5" s="246"/>
+      <c r="G5" s="246"/>
+      <c r="H5" s="246"/>
+      <c r="I5" s="246"/>
+      <c r="J5" s="246"/>
+      <c r="K5" s="246"/>
+      <c r="L5" s="246"/>
+      <c r="P5" s="251"/>
+      <c r="Q5" s="251"/>
+      <c r="R5" s="251"/>
+      <c r="S5" s="251"/>
+      <c r="T5" s="251"/>
+      <c r="U5" s="251"/>
+      <c r="V5" s="251"/>
+      <c r="W5" s="251"/>
+      <c r="X5" s="251"/>
+      <c r="Y5" s="251"/>
+      <c r="Z5" s="251"/>
       <c r="AB5" s="111"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -21931,10 +21931,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="247" t="s">
+      <c r="B14" s="252" t="s">
         <v>215</v>
       </c>
-      <c r="C14" s="248"/>
+      <c r="C14" s="253"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="156" t="s">
@@ -21942,7 +21942,7 @@
       </c>
       <c r="C15" s="157">
         <f ca="1">Overview!C5</f>
-        <v>210.96</v>
+        <v>207.4</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -21961,20 +21961,20 @@
       <c r="C17" s="159">
         <v>0.55000000000000004</v>
       </c>
-      <c r="E17" s="249" t="s">
+      <c r="E17" s="254" t="s">
         <v>218</v>
       </c>
-      <c r="F17" s="249"/>
-      <c r="G17" s="249"/>
-      <c r="H17" s="249"/>
-      <c r="I17" s="249"/>
+      <c r="F17" s="254"/>
+      <c r="G17" s="254"/>
+      <c r="H17" s="254"/>
+      <c r="I17" s="254"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="247" t="s">
+      <c r="B19" s="252" t="s">
         <v>176</v>
       </c>
-      <c r="C19" s="248"/>
+      <c r="C19" s="253"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="160" t="s">
@@ -22008,7 +22008,7 @@
       </c>
       <c r="C23" s="162">
         <f ca="1">C15*C22</f>
-        <v>5105232</v>
+        <v>5019080</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22035,15 +22035,15 @@
       </c>
       <c r="C26" s="163">
         <f ca="1">C23+C25-C24</f>
-        <v>5033130</v>
+        <v>4946978</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="247" t="s">
+      <c r="B28" s="252" t="s">
         <v>178</v>
       </c>
-      <c r="C28" s="248"/>
+      <c r="C28" s="253"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="160" t="s">
@@ -22118,18 +22118,18 @@
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="241" t="s">
+      <c r="C39" s="246" t="s">
         <v>221</v>
       </c>
-      <c r="D39" s="241"/>
-      <c r="E39" s="241"/>
-      <c r="F39" s="241"/>
-      <c r="G39" s="241"/>
-      <c r="H39" s="241"/>
-      <c r="I39" s="241"/>
-      <c r="J39" s="241"/>
-      <c r="K39" s="241"/>
-      <c r="L39" s="241"/>
+      <c r="D39" s="246"/>
+      <c r="E39" s="246"/>
+      <c r="F39" s="246"/>
+      <c r="G39" s="246"/>
+      <c r="H39" s="246"/>
+      <c r="I39" s="246"/>
+      <c r="J39" s="246"/>
+      <c r="K39" s="246"/>
+      <c r="L39" s="246"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -22561,17 +22561,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29069,7 +29069,7 @@
       <c r="AA114" s="68"/>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>210.96</v>
+        <v>207.4</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29116,7 +29116,7 @@
       <c r="AA115" s="68"/>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>210.96</v>
+        <v>207.4</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30618,7 +30618,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>32.306278713629411</v>
+        <v>31.761102603369071</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -30655,7 +30655,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>20.355658070700738</v>
+        <v>20.012151516227402</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30692,7 +30692,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>26.117192056232547</v>
+        <v>25.676458250202078</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30729,7 +30729,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="144">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>5127382.8</v>
+        <v>5040857</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30766,7 +30766,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="144">
         <f ca="1">AC155+AC106-AC105+AC47+AC44</f>
-        <v>5055280.8</v>
+        <v>4968755</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -30803,7 +30803,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="184">
         <f ca="1">AC156/AC5</f>
-        <v>19.942644117542635</v>
+        <v>19.601307344244962</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -30840,7 +30840,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="184">
         <f ca="1">AC156/AC11</f>
-        <v>31.15063499399205</v>
+        <v>30.617463105031273</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -30975,7 +30975,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="72">
         <f t="shared" ref="AC161:AC162" ca="1" si="96">AC155/AC159</f>
-        <v>45.683533950479784</v>
+        <v>44.912613487530848</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31012,7 +31012,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ca="1" si="96"/>
-        <v>39.863094885793984</v>
+        <v>39.180801198869766</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31049,7 +31049,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="74">
         <f t="shared" ref="AC163" ca="1" si="99">AC159/AC155</f>
-        <v>2.1889725104979486E-2</v>
+        <v>2.2265460019992633E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31086,7 +31086,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>3.0953735305271138E-2</v>
+        <v>3.1485053037608485E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31123,7 +31123,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="155">
         <f ca="1">AC81/AC115</f>
-        <v>1.8960940462646946E-4</v>
+        <v>1.9286403085824494E-4</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31160,7 +31160,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="155">
         <f ca="1">-AC62/AC155</f>
-        <v>8.835696839330975E-3</v>
+        <v>8.9873606809318333E-3</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -31197,7 +31197,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="155">
         <f ca="1">-(AC62+AC63)/AC155</f>
-        <v>9.0254622689766792E-3</v>
+        <v>9.1803834149629723E-3</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31700,7 +31700,7 @@
       <c r="AA178" s="49"/>
       <c r="AC178" s="155">
         <f ca="1">(AC105-AC106)/AC155</f>
-        <v>1.4062144921186693E-2</v>
+        <v>1.4303520214915837E-2</v>
       </c>
     </row>
     <row r="179" spans="1:31" x14ac:dyDescent="0.2">
@@ -32865,15 +32865,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="240" t="s">
         <v>230</v>
       </c>
-      <c r="C4" s="232"/>
-      <c r="E4" s="232" t="s">
+      <c r="C4" s="240"/>
+      <c r="E4" s="240" t="s">
         <v>237</v>
       </c>
-      <c r="F4" s="232"/>
-      <c r="G4" s="232"/>
+      <c r="F4" s="240"/>
+      <c r="G4" s="240"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -32881,7 +32881,7 @@
       </c>
       <c r="C5" s="173">
         <f ca="1">Overview!C5</f>
-        <v>210.96</v>
+        <v>207.4</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="133" t="s">
@@ -32897,7 +32897,7 @@
       </c>
       <c r="C6" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>5127382.8</v>
+        <v>5040857</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -32917,7 +32917,7 @@
       </c>
       <c r="C7" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>5055280.8</v>
+        <v>4968755</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -32937,7 +32937,7 @@
       </c>
       <c r="C8" s="175">
         <f ca="1">Statement!AC152</f>
-        <v>32.306278713629411</v>
+        <v>31.761102603369071</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>240</v>
@@ -32957,7 +32957,7 @@
       </c>
       <c r="C9" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>20.355658070700738</v>
+        <v>20.012151516227402</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>241</v>
@@ -32977,7 +32977,7 @@
       </c>
       <c r="C10" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>26.117192056232547</v>
+        <v>25.676458250202078</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -32997,7 +32997,7 @@
       </c>
       <c r="C11" s="175">
         <f ca="1">Statement!AC157</f>
-        <v>19.942644117542635</v>
+        <v>19.601307344244962</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33006,18 +33006,18 @@
       </c>
       <c r="C12" s="175">
         <f ca="1">Statement!AC158</f>
-        <v>31.15063499399205</v>
+        <v>30.617463105031273</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="232" t="s">
+      <c r="B15" s="240" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="232"/>
-      <c r="E15" s="232" t="s">
+      <c r="C15" s="240"/>
+      <c r="E15" s="240" t="s">
         <v>243</v>
       </c>
-      <c r="F15" s="232"/>
+      <c r="F15" s="240"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33068,14 +33068,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="232" t="s">
+      <c r="B21" s="240" t="s">
         <v>242</v>
       </c>
-      <c r="C21" s="232"/>
-      <c r="E21" s="232" t="s">
+      <c r="C21" s="240"/>
+      <c r="E21" s="240" t="s">
         <v>246</v>
       </c>
-      <c r="F21" s="232"/>
+      <c r="F21" s="240"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33144,14 +33144,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="232" t="s">
+      <c r="B29" s="240" t="s">
         <v>247</v>
       </c>
-      <c r="C29" s="232"/>
-      <c r="E29" s="232" t="s">
+      <c r="C29" s="240"/>
+      <c r="E29" s="240" t="s">
         <v>253</v>
       </c>
-      <c r="F29" s="232"/>
+      <c r="F29" s="240"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33227,14 +33227,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="232" t="s">
+      <c r="B37" s="240" t="s">
         <v>265</v>
       </c>
-      <c r="C37" s="232"/>
-      <c r="E37" s="232" t="s">
+      <c r="C37" s="240"/>
+      <c r="E37" s="240" t="s">
         <v>268</v>
       </c>
-      <c r="F37" s="232"/>
+      <c r="F37" s="240"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33242,7 +33242,7 @@
       </c>
       <c r="C38" s="176">
         <f ca="1">Statement!AC164</f>
-        <v>3.0953735305271138E-2</v>
+        <v>3.1485053037608485E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>267</v>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C39" s="216">
         <f ca="1">Statement!AC163</f>
-        <v>2.1889725104979486E-2</v>
+        <v>2.2265460019992633E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>269</v>
@@ -33274,7 +33274,7 @@
       </c>
       <c r="C40" s="176">
         <f ca="1">Statement!AC165</f>
-        <v>1.8960940462646946E-4</v>
+        <v>1.9286403085824494E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>270</v>
@@ -33290,7 +33290,7 @@
       </c>
       <c r="C41" s="176">
         <f ca="1">Statement!AC166</f>
-        <v>8.835696839330975E-3</v>
+        <v>8.9873606809318333E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33299,18 +33299,18 @@
       </c>
       <c r="C42" s="176">
         <f ca="1">Statement!AC167</f>
-        <v>9.0254622689766792E-3</v>
+        <v>9.1803834149629723E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="232" t="s">
+      <c r="B45" s="240" t="s">
         <v>276</v>
       </c>
-      <c r="C45" s="232"/>
-      <c r="E45" s="232" t="s">
+      <c r="C45" s="240"/>
+      <c r="E45" s="240" t="s">
         <v>282</v>
       </c>
-      <c r="F45" s="232"/>
+      <c r="F45" s="240"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33343,18 +33343,18 @@
       </c>
       <c r="F48" s="176">
         <f ca="1">Statement!AC178</f>
-        <v>1.4062144921186693E-2</v>
+        <v>1.4303520214915837E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="232" t="s">
+      <c r="B51" s="240" t="s">
         <v>279</v>
       </c>
-      <c r="C51" s="232"/>
-      <c r="E51" s="232" t="s">
+      <c r="C51" s="240"/>
+      <c r="E51" s="240" t="s">
         <v>300</v>
       </c>
-      <c r="F51" s="232"/>
+      <c r="F51" s="240"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -33523,7 +33523,7 @@
       </c>
       <c r="I6" s="173">
         <f ca="1">Statement!AC114</f>
-        <v>210.96</v>
+        <v>207.4</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33552,7 +33552,7 @@
       </c>
       <c r="I7" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>5127382.8</v>
+        <v>5040857</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33581,7 +33581,7 @@
       </c>
       <c r="I8" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>5055280.8</v>
+        <v>4968755</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33610,7 +33610,7 @@
       </c>
       <c r="I9" s="175">
         <f ca="1">Statement!AC152</f>
-        <v>32.306278713629411</v>
+        <v>31.761102603369071</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33639,7 +33639,7 @@
       </c>
       <c r="I10" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>20.355658070700738</v>
+        <v>20.012151516227402</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33668,7 +33668,7 @@
       </c>
       <c r="I11" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>26.117192056232547</v>
+        <v>25.676458250202078</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33697,7 +33697,7 @@
       </c>
       <c r="I12" s="175">
         <f ca="1">Statement!AC157</f>
-        <v>19.942644117542635</v>
+        <v>19.601307344244962</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33726,7 +33726,7 @@
       </c>
       <c r="I13" s="175">
         <f ca="1">Statement!AC158</f>
-        <v>31.15063499399205</v>
+        <v>30.617463105031273</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34499,7 +34499,7 @@
       </c>
       <c r="I51" s="176">
         <f ca="1">Statement!AC164</f>
-        <v>3.0953735305271138E-2</v>
+        <v>3.1485053037608485E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34528,7 +34528,7 @@
       </c>
       <c r="I52" s="176">
         <f ca="1">Statement!AC163</f>
-        <v>2.1889725104979486E-2</v>
+        <v>2.2265460019992633E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34557,7 +34557,7 @@
       </c>
       <c r="I53" s="176">
         <f ca="1">Statement!AC165</f>
-        <v>1.8960940462646946E-4</v>
+        <v>1.9286403085824494E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -34586,7 +34586,7 @@
       </c>
       <c r="I54" s="176">
         <f ca="1">Statement!AC166</f>
-        <v>8.835696839330975E-3</v>
+        <v>8.9873606809318333E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34615,7 +34615,7 @@
       </c>
       <c r="I55" s="176">
         <f ca="1">Statement!AC167</f>
-        <v>9.0254622689766792E-3</v>
+        <v>9.1803834149629723E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34851,7 +34851,7 @@
       </c>
       <c r="I68" s="197">
         <f ca="1">Statement!AC178</f>
-        <v>1.4062144921186693E-2</v>
+        <v>1.4303520214915837E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35363,14 +35363,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="236" t="s">
+      <c r="C3" s="243" t="s">
         <v>310</v>
       </c>
-      <c r="D3" s="237"/>
-      <c r="F3" s="238" t="s">
+      <c r="D3" s="244"/>
+      <c r="F3" s="245" t="s">
         <v>311</v>
       </c>
-      <c r="G3" s="237"/>
+      <c r="G3" s="244"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35437,19 +35437,19 @@
       <c r="B7" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C7" s="239">
+      <c r="C7" s="241">
         <f>Statement!AA88</f>
         <v>0.19798317847549429</v>
       </c>
-      <c r="D7" s="240"/>
-      <c r="F7" s="239">
+      <c r="D7" s="242"/>
+      <c r="F7" s="241">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.85227633788752211</v>
       </c>
-      <c r="G7" s="240"/>
+      <c r="G7" s="242"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="208" t="s">
@@ -35476,19 +35476,19 @@
       <c r="B9" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C9" s="239">
+      <c r="C9" s="241">
         <f>Statement!AA89</f>
         <v>0.20100974521545145</v>
       </c>
-      <c r="D9" s="240"/>
-      <c r="F9" s="239">
+      <c r="D9" s="242"/>
+      <c r="F9" s="241">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.17615269633206854</v>
       </c>
-      <c r="G9" s="240"/>
+      <c r="G9" s="242"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="208" t="s">
@@ -35515,19 +35515,19 @@
       <c r="B11" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C11" s="239">
+      <c r="C11" s="241">
         <f>Statement!AA90</f>
         <v>0.19697414518622902</v>
       </c>
-      <c r="D11" s="240"/>
-      <c r="F11" s="239">
+      <c r="D11" s="242"/>
+      <c r="F11" s="241">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.293272836358182</v>
       </c>
-      <c r="G11" s="240"/>
+      <c r="G11" s="242"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="208" t="s">
@@ -35554,19 +35554,19 @@
       <c r="B13" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C13" s="239">
+      <c r="C13" s="241">
         <f>Statement!AA93</f>
         <v>0.12172505151604357</v>
       </c>
-      <c r="D13" s="240"/>
-      <c r="F13" s="239">
+      <c r="D13" s="242"/>
+      <c r="F13" s="241">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.51510934393638175</v>
       </c>
-      <c r="G13" s="240"/>
+      <c r="G13" s="242"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="208" t="s">
@@ -35593,19 +35593,19 @@
       <c r="B15" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C15" s="239">
+      <c r="C15" s="241">
         <f>Statement!AA94</f>
         <v>0.20851486489537011</v>
       </c>
-      <c r="D15" s="240"/>
-      <c r="F15" s="239">
+      <c r="D15" s="242"/>
+      <c r="F15" s="241">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.4741658193918108</v>
       </c>
-      <c r="G15" s="240"/>
+      <c r="G15" s="242"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="208" t="s">
@@ -35632,19 +35632,19 @@
       <c r="B17" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C17" s="239">
+      <c r="C17" s="241">
         <f>Statement!AA96</f>
         <v>0.35756517690875234</v>
       </c>
-      <c r="D17" s="240"/>
-      <c r="F17" s="239">
+      <c r="D17" s="242"/>
+      <c r="F17" s="241">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>2.1063115845539282</v>
       </c>
-      <c r="G17" s="240"/>
+      <c r="G17" s="242"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="208" t="s">
@@ -35671,22 +35671,22 @@
       <c r="B19" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C19" s="239">
+      <c r="C19" s="241">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-1.6781270464963983E-3</v>
       </c>
-      <c r="D19" s="240"/>
-      <c r="F19" s="239">
+      <c r="D19" s="242"/>
+      <c r="F19" s="241">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-8.9390922758116297E-3</v>
       </c>
-      <c r="G19" s="240"/>
+      <c r="G19" s="242"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="208" t="s">
@@ -35713,22 +35713,22 @@
       <c r="B21" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C21" s="239">
+      <c r="C21" s="241">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.35795454545454553</v>
       </c>
-      <c r="D21" s="240"/>
-      <c r="F21" s="239">
+      <c r="D21" s="242"/>
+      <c r="F21" s="241">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>2.1447368421052633</v>
       </c>
-      <c r="G21" s="240"/>
+      <c r="G21" s="242"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -35776,22 +35776,22 @@
       <c r="B25" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C25" s="239">
+      <c r="C25" s="241">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.11992074288756137</v>
       </c>
-      <c r="D25" s="240"/>
-      <c r="F25" s="239">
+      <c r="D25" s="242"/>
+      <c r="F25" s="241">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>1.1517699869310756</v>
       </c>
-      <c r="G25" s="240"/>
+      <c r="G25" s="242"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="224" t="s">
@@ -35818,22 +35818,22 @@
       <c r="B27" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C27" s="239">
+      <c r="C27" s="241">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.31147368421052629</v>
       </c>
-      <c r="D27" s="240"/>
-      <c r="F27" s="239">
+      <c r="D27" s="242"/>
+      <c r="F27" s="241">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.73741458652907543</v>
       </c>
-      <c r="G27" s="240"/>
+      <c r="G27" s="242"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -35860,22 +35860,22 @@
       <c r="B29" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C29" s="239">
+      <c r="C29" s="241">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.20752960811374652</v>
       </c>
-      <c r="D29" s="240"/>
-      <c r="F29" s="239">
+      <c r="D29" s="242"/>
+      <c r="F29" s="241">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.92385968500715898</v>
       </c>
-      <c r="G29" s="240"/>
+      <c r="G29" s="242"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35902,25 +35902,43 @@
       <c r="B31" s="207" t="s">
         <v>312</v>
       </c>
-      <c r="C31" s="239">
+      <c r="C31" s="241">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>9.5647686220540165E-2</v>
       </c>
-      <c r="D31" s="240"/>
-      <c r="F31" s="239">
+      <c r="D31" s="242"/>
+      <c r="F31" s="241">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.28666666666666668</v>
       </c>
-      <c r="G31" s="240"/>
+      <c r="G31" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C25:D25"/>
@@ -35929,24 +35947,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{506FA025-F08B-0C44-A7F5-D539158C42BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{043E2811-2544-E341-B252-F395DC083D7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -119,7 +119,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -130,7 +130,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -140,12 +161,21 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
+    </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -12680,7 +12710,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1yv52&amp;q=XNAS%3aNVDA&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12699,11 +12729,9 @@
     <v>Powered by Refinitiv</v>
     <v>236.54</v>
     <v>164.07</v>
-    <v>2.2212999999999998</v>
-    <v>-5.0999999999999996</v>
-    <v>-2.4E-2</v>
-    <v>-1.4350000000000001</v>
-    <v>-6.9189999999999998E-3</v>
+    <v>2.2280000000000002</v>
+    <v>3.9338000000000002</v>
+    <v>2.0169000000000003E-2</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -12711,35 +12739,49 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2788 San Tomas Expressway, SANTA CLARA, CA, 95051 US</v>
-    <v>211.08</v>
+    <v>200.09</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46219.999965416406</v>
+    <v>46234.719659200782</v>
     <v>0</v>
-    <v>205.845</v>
-    <v>5019080000000</v>
+    <v>194.95</v>
+    <v>4815165960000</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
-    <v>210.17</v>
-    <v>31.761099999999999</v>
-    <v>212.5</v>
-    <v>207.4</v>
-    <v>205.965</v>
+    <v>198.49</v>
+    <v>30.470700000000001</v>
+    <v>195.04</v>
+    <v>198.97380000000001</v>
     <v>24200000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>122986074</v>
-    <v>146051455</v>
+    <v>61716561</v>
+    <v>134310928</v>
     <v>1998</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -12751,30 +12793,30 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>46.87</v>
+    <v>47.14</v>
     <v>39.47</v>
-    <v>0.24</v>
-    <v>5.2810000000000001E-3</v>
+    <v>0.41</v>
+    <v>8.8710000000000004E-3</v>
     <v>US</v>
-    <v>45.96</v>
+    <v>46.86</v>
     <v>Index</v>
-    <v>3</v>
-    <v>45.61</v>
+    <v>6</v>
+    <v>46.51</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>45.82</v>
-    <v>45.45</v>
-    <v>45.69</v>
+    <v>46.69</v>
+    <v>46.22</v>
+    <v>46.63</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>4</v>
+    <v>7</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12796,8 +12838,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12818,7 +12858,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12828,6 +12867,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12863,7 +12907,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="45">
+    <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12874,16 +12918,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -12977,19 +13018,13 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="4">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13061,9 +13096,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13071,9 +13103,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13584,7 +13613,7 @@
       </c>
       <c r="F3" s="188">
         <f ca="1">Statement!AC155</f>
-        <v>5040857</v>
+        <v>4836058.2090000007</v>
       </c>
       <c r="H3" s="186" t="str">
         <f>'AVG target price'!B5</f>
@@ -13608,7 +13637,7 @@
       </c>
       <c r="F4" s="189">
         <f ca="1">Statement!AC156</f>
-        <v>4968755</v>
+        <v>4763956.2090000007</v>
       </c>
       <c r="H4" s="186" t="str">
         <f>'AVG target price'!B6</f>
@@ -13625,7 +13654,7 @@
       </c>
       <c r="C5" s="209" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>207.4</v>
+        <v>198.97380000000001</v>
       </c>
       <c r="E5" s="186" t="s">
         <v>240</v>
@@ -13647,16 +13676,16 @@
       <c r="B6" s="186" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="209" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>205.965</v>
+      <c r="C6" s="209" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="186" t="s">
         <v>234</v>
       </c>
       <c r="F6" s="191">
         <f ca="1">Statement!AC152</f>
-        <v>31.761102603369071</v>
+        <v>30.470719754977033</v>
       </c>
       <c r="H6" s="186" t="str">
         <f>'AVG target price'!B8</f>
@@ -13673,14 +13702,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-5.0999999999999996</v>
+        <v>3.9338000000000002</v>
       </c>
       <c r="E7" s="187" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="192">
         <f ca="1">Statement!AC153</f>
-        <v>20.012151516227402</v>
+        <v>19.19910237878268</v>
       </c>
       <c r="H7" s="185" t="str">
         <f>'AVG target price'!B9</f>
@@ -13695,16 +13724,16 @@
       <c r="B8" s="186" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-1.4350000000000001</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="186" t="s">
         <v>262</v>
       </c>
       <c r="F8" s="193">
         <f ca="1">Statement!AC163</f>
-        <v>2.2265460019992633E-2</v>
+        <v>2.3208364157223067E-2</v>
       </c>
       <c r="H8" s="185" t="str">
         <f>'AVG target price'!B11</f>
@@ -13712,7 +13741,7 @@
       </c>
       <c r="I8" s="214">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.43797602064070279</v>
+        <v>0.4988718448402843</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13721,30 +13750,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-2.4E-2</v>
+        <v>2.0169000000000003E-2</v>
       </c>
       <c r="E9" s="186" t="s">
         <v>285</v>
       </c>
       <c r="F9" s="193">
         <f ca="1">Statement!AC164</f>
-        <v>3.1485053037608485E-2</v>
+        <v>3.2818391165067962E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="186" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-6.9189999999999998E-3</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="186" t="s">
         <v>290</v>
       </c>
       <c r="F10" s="193">
         <f ca="1">Statement!AC166</f>
-        <v>8.9873606809318333E-3</v>
+        <v>9.3679600290352896E-3</v>
       </c>
       <c r="H10" s="185" t="s">
         <v>409</v>
@@ -13767,7 +13796,7 @@
       </c>
       <c r="F11" s="194">
         <f ca="1">Statement!AC165</f>
-        <v>1.9286403085824494E-4</v>
+        <v>2.0103149258847143E-4</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13792,7 +13821,7 @@
       </c>
       <c r="C13" s="210" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.2212999999999998</v>
+        <v>2.2280000000000002</v>
       </c>
       <c r="E13" s="186" t="s">
         <v>96</v>
@@ -13808,7 +13837,7 @@
       </c>
       <c r="C14" s="211" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>146051455</v>
+        <v>134310928</v>
       </c>
       <c r="E14" s="187" t="s">
         <v>97</v>
@@ -13824,7 +13853,7 @@
       </c>
       <c r="F15" s="193">
         <f ca="1">Statement!AC178</f>
-        <v>1.4303520214915837E-2</v>
+        <v>1.4909249823713193E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13929,12 +13958,12 @@
       <c r="C26" s="171">
         <v>0.21</v>
       </c>
-      <c r="E26" s="186" t="e" vm="2">
+      <c r="E26" s="186" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="220" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>45.69</v>
+        <v>46.63</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13949,7 +13978,7 @@
       </c>
       <c r="F27" s="221">
         <f ca="1">F26/1000</f>
-        <v>4.5689999999999995E-2</v>
+        <v>4.6630000000000005E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -19205,7 +19234,7 @@
       </c>
       <c r="C6" s="134">
         <f ca="1">Overview!C5</f>
-        <v>207.4</v>
+        <v>198.97380000000001</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19214,7 +19243,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">C5*C6</f>
-        <v>5040857</v>
+        <v>4836058.2090000007</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19232,7 +19261,7 @@
       </c>
       <c r="C9" s="136">
         <f ca="1">Overview!F27</f>
-        <v>4.5689999999999995E-2</v>
+        <v>4.6630000000000005E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19241,7 +19270,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C13</f>
-        <v>2.2212999999999998</v>
+        <v>2.2280000000000002</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19284,7 +19313,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>1.6774512722190502E-3</v>
+        <v>1.7483642647110032E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19293,7 +19322,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99832254872778092</v>
+        <v>0.99825163573528897</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19311,7 +19340,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14564849999999999</v>
+        <v>0.14689000000000002</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19320,7 +19349,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14547176625013589</v>
+        <v>0.14670362436938184</v>
       </c>
     </row>
   </sheetData>
@@ -21104,7 +21133,7 @@
       </c>
       <c r="C10" s="134">
         <f ca="1">Overview!C5</f>
-        <v>207.4</v>
+        <v>198.97380000000001</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21113,7 +21142,7 @@
       </c>
       <c r="C11" s="155">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.43797602064070279</v>
+        <v>0.4988718448402843</v>
       </c>
     </row>
   </sheetData>
@@ -21942,7 +21971,7 @@
       </c>
       <c r="C15" s="157">
         <f ca="1">Overview!C5</f>
-        <v>207.4</v>
+        <v>198.97380000000001</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22008,7 +22037,7 @@
       </c>
       <c r="C23" s="162">
         <f ca="1">C15*C22</f>
-        <v>5019080</v>
+        <v>4815165.96</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22035,7 +22064,7 @@
       </c>
       <c r="C26" s="163">
         <f ca="1">C23+C25-C24</f>
-        <v>4946978</v>
+        <v>4743063.96</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -29059,17 +29088,33 @@
       <c r="Q114" s="63">
         <v>187.67</v>
       </c>
-      <c r="T114" s="68"/>
-      <c r="U114" s="68"/>
-      <c r="V114" s="68"/>
-      <c r="W114" s="68"/>
-      <c r="X114" s="68"/>
-      <c r="Y114" s="68"/>
-      <c r="Z114" s="68"/>
-      <c r="AA114" s="68"/>
+      <c r="T114" s="63">
+        <v>112.87</v>
+      </c>
+      <c r="U114" s="63">
+        <v>141.32</v>
+      </c>
+      <c r="V114" s="63">
+        <v>142.62</v>
+      </c>
+      <c r="W114" s="63">
+        <v>110.85</v>
+      </c>
+      <c r="X114" s="63">
+        <v>173.27</v>
+      </c>
+      <c r="Y114" s="63">
+        <v>186.02</v>
+      </c>
+      <c r="Z114" s="63">
+        <v>187.67</v>
+      </c>
+      <c r="AA114" s="63">
+        <v>208.27</v>
+      </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>207.4</v>
+        <v>198.97380000000001</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29106,17 +29151,41 @@
         <f>Q114/Q84</f>
         <v>187.67</v>
       </c>
-      <c r="T115" s="68"/>
-      <c r="U115" s="68"/>
-      <c r="V115" s="68"/>
-      <c r="W115" s="68"/>
-      <c r="X115" s="68"/>
-      <c r="Y115" s="68"/>
-      <c r="Z115" s="68"/>
-      <c r="AA115" s="68"/>
+      <c r="T115" s="65">
+        <f t="shared" ref="T115:AA115" si="68">T114/T84</f>
+        <v>112.87</v>
+      </c>
+      <c r="U115" s="65">
+        <f t="shared" si="68"/>
+        <v>141.32</v>
+      </c>
+      <c r="V115" s="65">
+        <f t="shared" si="68"/>
+        <v>142.62</v>
+      </c>
+      <c r="W115" s="65">
+        <f t="shared" si="68"/>
+        <v>110.85</v>
+      </c>
+      <c r="X115" s="65">
+        <f t="shared" si="68"/>
+        <v>173.27</v>
+      </c>
+      <c r="Y115" s="65">
+        <f t="shared" si="68"/>
+        <v>186.02</v>
+      </c>
+      <c r="Z115" s="65">
+        <f t="shared" si="68"/>
+        <v>187.67</v>
+      </c>
+      <c r="AA115" s="65">
+        <f t="shared" si="68"/>
+        <v>208.27</v>
+      </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>207.4</v>
+        <v>198.97380000000001</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29230,19 +29299,19 @@
         <v>94</v>
       </c>
       <c r="M121" s="76">
-        <f t="shared" ref="M121:P121" si="68">M119*M120</f>
+        <f t="shared" ref="M121:P121" si="69">M119*M120</f>
         <v>0.22069839545567699</v>
       </c>
       <c r="N121" s="76">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0.10606575688407557</v>
       </c>
       <c r="O121" s="76">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0.45277507302823755</v>
       </c>
       <c r="P121" s="76">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0.65304074336251472</v>
       </c>
       <c r="Q121" s="76">
@@ -29304,19 +29373,19 @@
         <v>96</v>
       </c>
       <c r="M123" s="76">
-        <f t="shared" ref="M123:P123" si="69">M121*M122</f>
+        <f t="shared" ref="M123:P123" si="70">M121*M122</f>
         <v>0.36645122501127303</v>
       </c>
       <c r="N123" s="76">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.19763811592235647</v>
       </c>
       <c r="O123" s="76">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.69244729861789756</v>
       </c>
       <c r="P123" s="76">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.91872880608115781</v>
       </c>
       <c r="Q123" s="76">
@@ -29478,35 +29547,35 @@
       <c r="P129" s="49"/>
       <c r="Q129" s="49"/>
       <c r="T129" s="25">
-        <f t="shared" ref="T129:AA129" si="70">U5</f>
+        <f t="shared" ref="T129:AA129" si="71">U5</f>
         <v>35082</v>
       </c>
       <c r="U129" s="25">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>39331</v>
       </c>
       <c r="V129" s="25">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>44062</v>
       </c>
       <c r="W129" s="25">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>46743</v>
       </c>
       <c r="X129" s="25">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>57006</v>
       </c>
       <c r="Y129" s="25">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>68127</v>
       </c>
       <c r="Z129" s="25">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>81615</v>
       </c>
       <c r="AA129" s="25">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="AC129" s="49"/>
@@ -29531,35 +29600,35 @@
       <c r="P130" s="49"/>
       <c r="Q130" s="49"/>
       <c r="T130" s="229" t="str">
-        <f t="shared" ref="T130:AA130" si="71">IF(T129&gt;T128, "BEAT", IF(T129&lt;T127, "MISSED", "MET"))</f>
+        <f t="shared" ref="T130:AA130" si="72">IF(T129&gt;T128, "BEAT", IF(T129&lt;T127, "MISSED", "MET"))</f>
         <v>BEAT</v>
       </c>
       <c r="U130" s="229" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>BEAT</v>
       </c>
       <c r="V130" s="229" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>BEAT</v>
       </c>
       <c r="W130" s="229" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>BEAT</v>
       </c>
       <c r="X130" s="229" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>BEAT</v>
       </c>
       <c r="Y130" s="229" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>BEAT</v>
       </c>
       <c r="Z130" s="229" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>BEAT</v>
       </c>
       <c r="AA130" s="229" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>MISSED</v>
       </c>
       <c r="AC130" s="49"/>
@@ -29674,35 +29743,35 @@
       <c r="P133" s="49"/>
       <c r="Q133" s="49"/>
       <c r="T133" s="81">
-        <f t="shared" ref="T133:AA133" si="72">U99</f>
+        <f t="shared" ref="T133:AA133" si="73">U99</f>
         <v>0.74556752750698363</v>
       </c>
       <c r="U133" s="81">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0.73028908494571709</v>
       </c>
       <c r="V133" s="81">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0.60523807362353044</v>
       </c>
       <c r="W133" s="81">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0.72423678411740799</v>
       </c>
       <c r="X133" s="81">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0.7341157071185489</v>
       </c>
       <c r="Y133" s="81">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0.74996697344665109</v>
       </c>
       <c r="Z133" s="81">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0.74933529375727503</v>
       </c>
       <c r="AA133" s="81">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="AC133" s="49"/>
@@ -29727,35 +29796,35 @@
       <c r="P134" s="49"/>
       <c r="Q134" s="49"/>
       <c r="T134" s="229" t="str">
-        <f t="shared" ref="T134:AA134" si="73">IF(T133&gt;T132, "BEAT", IF(T133&lt;T131, "MISSED", "MET"))</f>
+        <f t="shared" ref="T134:AA134" si="74">IF(T133&gt;T132, "BEAT", IF(T133&lt;T131, "MISSED", "MET"))</f>
         <v>MET</v>
       </c>
       <c r="U134" s="229" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>MET</v>
       </c>
       <c r="V134" s="229" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>MISSED</v>
       </c>
       <c r="W134" s="229" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>BEAT</v>
       </c>
       <c r="X134" s="229" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>MET</v>
       </c>
       <c r="Y134" s="229" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>MET</v>
       </c>
       <c r="Z134" s="229" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>MET</v>
       </c>
       <c r="AA134" s="229" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>MISSED</v>
       </c>
       <c r="AC134" s="49"/>
@@ -29870,35 +29939,35 @@
       <c r="P137" s="49"/>
       <c r="Q137" s="49"/>
       <c r="T137" s="25">
-        <f t="shared" ref="T137:AA137" si="74">U10</f>
+        <f t="shared" ref="T137:AA137" si="75">U10</f>
         <v>4287</v>
       </c>
       <c r="U137" s="25">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>4689</v>
       </c>
       <c r="V137" s="25">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>5030</v>
       </c>
       <c r="W137" s="25">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>5413</v>
       </c>
       <c r="X137" s="25">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>5839</v>
       </c>
       <c r="Y137" s="25">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>6794</v>
       </c>
       <c r="Z137" s="25">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>7621</v>
       </c>
       <c r="AA137" s="25">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="AC137" s="49"/>
@@ -29923,35 +29992,35 @@
       <c r="P138" s="49"/>
       <c r="Q138" s="49"/>
       <c r="T138" s="229" t="str">
-        <f t="shared" ref="T138:AA138" si="75">IF(T137&gt;T136, "BEAT", IF(T137&lt;T135, "MISSED", "MET"))</f>
+        <f t="shared" ref="T138:AA138" si="76">IF(T137&gt;T136, "BEAT", IF(T137&lt;T135, "MISSED", "MET"))</f>
         <v>MISSED</v>
       </c>
       <c r="U138" s="229" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>MISSED</v>
       </c>
       <c r="V138" s="229" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>MISSED</v>
       </c>
       <c r="W138" s="229" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>MISSED</v>
       </c>
       <c r="X138" s="229" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>MISSED</v>
       </c>
       <c r="Y138" s="229" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>BEAT</v>
       </c>
       <c r="Z138" s="229" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>MISSED</v>
       </c>
       <c r="AA138" s="229" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>MISSED</v>
       </c>
       <c r="AC138" s="49"/>
@@ -30040,55 +30109,55 @@
         <v>131</v>
       </c>
       <c r="M143" s="119">
-        <f t="shared" ref="M143:Q144" si="76">M29/M5*365</f>
+        <f t="shared" ref="M143:Q144" si="77">M29/M5*365</f>
         <v>63.061975180203611</v>
       </c>
       <c r="N143" s="119">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>51.785237636242307</v>
       </c>
       <c r="O143" s="119">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>59.906683956534586</v>
       </c>
       <c r="P143" s="119">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>64.512785734537957</v>
       </c>
       <c r="Q143" s="119">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>65.01907955061175</v>
       </c>
       <c r="T143" s="119">
-        <f t="shared" ref="T143:AA143" si="77">T29/T5*90</f>
+        <f t="shared" ref="T143:AA143" si="78">T29/T5*90</f>
         <v>42.339547270306255</v>
       </c>
       <c r="U143" s="119">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>45.389943560800411</v>
       </c>
       <c r="V143" s="119">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>52.778978413973704</v>
       </c>
       <c r="W143" s="119">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>45.206300213335751</v>
       </c>
       <c r="X143" s="119">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>53.542134651177712</v>
       </c>
       <c r="Y143" s="119">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>52.71708241237765</v>
       </c>
       <c r="Z143" s="119">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>50.815976044739969</v>
       </c>
       <c r="AA143" s="119">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>44.892482999448632</v>
       </c>
       <c r="AC143" s="119">
@@ -30101,55 +30170,55 @@
         <v>132</v>
       </c>
       <c r="M144" s="119">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>100.73365822650703</v>
       </c>
       <c r="N144" s="119">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>162.079101394388</v>
       </c>
       <c r="O144" s="119">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>115.99362252572048</v>
       </c>
       <c r="P144" s="119">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>112.72404179049603</v>
       </c>
       <c r="Q144" s="119">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>125.043537414966</v>
       </c>
       <c r="T144" s="119">
-        <f t="shared" ref="T144:AA144" si="78">T30/T6*365</f>
+        <f t="shared" ref="T144:AA144" si="79">T30/T6*365</f>
         <v>326.32935976426467</v>
       </c>
       <c r="U144" s="119">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>312.98565987004258</v>
       </c>
       <c r="V144" s="119">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>346.83257918552033</v>
       </c>
       <c r="W144" s="119">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>237.81447625618031</v>
       </c>
       <c r="X144" s="119">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>423.67183863460048</v>
       </c>
       <c r="Y144" s="119">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>476.42409447779909</v>
       </c>
       <c r="Z144" s="119">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>458.61776447105791</v>
       </c>
       <c r="AA144" s="119">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>460.25540131000093</v>
       </c>
       <c r="AC144" s="119">
@@ -30182,35 +30251,35 @@
         <v>57.325010004001605</v>
       </c>
       <c r="T145" s="119">
-        <f t="shared" ref="T145:AA145" si="79">T37/T6*90</f>
+        <f t="shared" ref="T145:AA145" si="80">T37/T6*90</f>
         <v>44.361103669970532</v>
       </c>
       <c r="U145" s="119">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>53.973784449921581</v>
       </c>
       <c r="V145" s="119">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>53.53506787330317</v>
       </c>
       <c r="W145" s="119">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>37.932045532942396</v>
       </c>
       <c r="X145" s="119">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>63.286268425135759</v>
       </c>
       <c r="Y145" s="119">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>51.208022695784123</v>
       </c>
       <c r="Z145" s="119">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>51.842197957027118</v>
       </c>
       <c r="AA145" s="119">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>57.617069117215763</v>
       </c>
       <c r="AC145" s="119">
@@ -30227,55 +30296,55 @@
         <v>94.848181346110991</v>
       </c>
       <c r="N146" s="119">
-        <f t="shared" ref="N146:Q146" si="80">N143+N144-N145</f>
+        <f t="shared" ref="N146:Q146" si="81">N143+N144-N145</f>
         <v>176.38413589756092</v>
       </c>
       <c r="O146" s="119">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>116.62980530904048</v>
       </c>
       <c r="P146" s="119">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>106.67247199943577</v>
       </c>
       <c r="Q146" s="119">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>132.73760696157615</v>
       </c>
       <c r="T146" s="119">
-        <f t="shared" ref="T146" si="81">T143+T144-T145</f>
+        <f t="shared" ref="T146" si="82">T143+T144-T145</f>
         <v>324.30780336460037</v>
       </c>
       <c r="U146" s="119">
-        <f t="shared" ref="U146" si="82">U143+U144-U145</f>
+        <f t="shared" ref="U146" si="83">U143+U144-U145</f>
         <v>304.40181898092141</v>
       </c>
       <c r="V146" s="119">
-        <f t="shared" ref="V146" si="83">V143+V144-V145</f>
+        <f t="shared" ref="V146" si="84">V143+V144-V145</f>
         <v>346.07648972619091</v>
       </c>
       <c r="W146" s="119">
-        <f t="shared" ref="W146" si="84">W143+W144-W145</f>
+        <f t="shared" ref="W146" si="85">W143+W144-W145</f>
         <v>245.08873093657368</v>
       </c>
       <c r="X146" s="119">
-        <f t="shared" ref="X146" si="85">X143+X144-X145</f>
+        <f t="shared" ref="X146" si="86">X143+X144-X145</f>
         <v>413.92770486064245</v>
       </c>
       <c r="Y146" s="119">
-        <f t="shared" ref="Y146" si="86">Y143+Y144-Y145</f>
+        <f t="shared" ref="Y146" si="87">Y143+Y144-Y145</f>
         <v>477.93315419439267</v>
       </c>
       <c r="Z146" s="119">
-        <f t="shared" ref="Z146:AA146" si="87">Z143+Z144-Z145</f>
+        <f t="shared" ref="Z146:AA146" si="88">Z143+Z144-Z145</f>
         <v>457.59154255877075</v>
       </c>
       <c r="AA146" s="119">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>447.53081519223383</v>
       </c>
       <c r="AC146" s="119">
-        <f t="shared" ref="AC146" si="88">AC143+AC144-AC145</f>
+        <f t="shared" ref="AC146" si="89">AC143+AC144-AC145</f>
         <v>129.34693643390989</v>
       </c>
     </row>
@@ -30304,35 +30373,35 @@
         <v>5.3835835033981171E-2</v>
       </c>
       <c r="T147" s="119">
-        <f t="shared" ref="T147:AA147" si="89">T106/T48</f>
+        <f t="shared" ref="T147:AA147" si="90">T106/T48</f>
         <v>0.14548549615695444</v>
       </c>
       <c r="U147" s="119">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0.12840862532056632</v>
       </c>
       <c r="V147" s="119">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0.10668498745698186</v>
       </c>
       <c r="W147" s="119">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0.10095058621471083</v>
       </c>
       <c r="X147" s="119">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>8.4549240494951619E-2</v>
       </c>
       <c r="Y147" s="119">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>7.1212898559257179E-2</v>
       </c>
       <c r="Z147" s="119">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>5.4471591234193512E-2</v>
       </c>
       <c r="AA147" s="119">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>4.3330570817602339E-2</v>
       </c>
       <c r="AC147" s="119">
@@ -30365,35 +30434,35 @@
         <v>-0.34386781357085183</v>
       </c>
       <c r="T148" s="180">
-        <f t="shared" ref="T148:AA148" si="90">(T106-T105)/T48</f>
+        <f t="shared" ref="T148:AA148" si="91">(T106-T105)/T48</f>
         <v>-0.45289475041697475</v>
       </c>
       <c r="U148" s="180">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>-0.45562148135783548</v>
       </c>
       <c r="V148" s="180">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>-0.43802236312982967</v>
       </c>
       <c r="W148" s="180">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>-0.53942487744951872</v>
       </c>
       <c r="X148" s="180">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>-0.48261777072035633</v>
       </c>
       <c r="Y148" s="180">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>-0.43853923984625348</v>
       </c>
       <c r="Z148" s="180">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>-0.3432320573706395</v>
       </c>
       <c r="AA148" s="180">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>-0.36885723932594616</v>
       </c>
       <c r="AC148" s="180">
@@ -30426,35 +30495,35 @@
         <v>3.1409383453036099</v>
       </c>
       <c r="T149" s="119">
-        <f t="shared" ref="T149:AA149" si="91">(T105+T29)/T39</f>
+        <f t="shared" ref="T149:AA149" si="92">(T105+T29)/T39</f>
         <v>3.5028992769704344</v>
       </c>
       <c r="U149" s="119">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>3.4091874506948239</v>
       </c>
       <c r="V149" s="119">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>3.672355516152269</v>
       </c>
       <c r="W149" s="119">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>2.8567176550372992</v>
       </c>
       <c r="X149" s="119">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>3.4876118233911861</v>
       </c>
       <c r="Y149" s="119">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>3.6049472674976029</v>
       </c>
       <c r="Z149" s="119">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>3.1409383453036099</v>
       </c>
       <c r="AA149" s="119">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>2.7636951964269438</v>
       </c>
       <c r="AC149" s="119">
@@ -30487,35 +30556,35 @@
         <v>3.9052638124553058</v>
       </c>
       <c r="T150" s="119">
-        <f t="shared" ref="T150:AA150" si="92">T31/T39</f>
+        <f t="shared" ref="T150:AA150" si="93">T31/T39</f>
         <v>4.2689526809363594</v>
       </c>
       <c r="U150" s="119">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>4.1046179986649678</v>
       </c>
       <c r="V150" s="119">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>4.4398514988640772</v>
       </c>
       <c r="W150" s="119">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>3.3884032853590536</v>
       </c>
       <c r="X150" s="119">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>4.2140000824504265</v>
       </c>
       <c r="Y150" s="119">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>4.4675743048897409</v>
       </c>
       <c r="Z150" s="119">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>3.9052638124553058</v>
       </c>
       <c r="AA150" s="119">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>3.440775681341719</v>
       </c>
       <c r="AC150" s="119">
@@ -30548,35 +30617,35 @@
         <v>N/A</v>
       </c>
       <c r="T151" s="182" t="str">
-        <f t="shared" ref="T151:AA151" si="93">IF(T12&gt;=0,"N/A",IF(T11&lt;=0,"N/A",T11/-T12))</f>
+        <f t="shared" ref="T151:AA151" si="94">IF(T12&gt;=0,"N/A",IF(T11&lt;=0,"N/A",T11/-T12))</f>
         <v>N/A</v>
       </c>
       <c r="U151" s="182" t="str">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>N/A</v>
       </c>
       <c r="V151" s="182" t="str">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>N/A</v>
       </c>
       <c r="W151" s="182" t="str">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>N/A</v>
       </c>
       <c r="X151" s="182" t="str">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>N/A</v>
       </c>
       <c r="Y151" s="182" t="str">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>N/A</v>
       </c>
       <c r="Z151" s="182" t="str">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>N/A</v>
       </c>
       <c r="AA151" s="182" t="str">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>N/A</v>
       </c>
       <c r="AC151" s="182" t="str">
@@ -30618,7 +30687,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>31.761102603369071</v>
+        <v>30.470719754977033</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -30655,7 +30724,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>20.012151516227402</v>
+        <v>19.19910237878268</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30682,17 +30751,41 @@
         <f>Q115/(Statement!Q48/Statement!Q74)</f>
         <v>28.992904960805632</v>
       </c>
-      <c r="T154" s="49"/>
-      <c r="U154" s="49"/>
-      <c r="V154" s="49"/>
-      <c r="W154" s="49"/>
-      <c r="X154" s="49"/>
-      <c r="Y154" s="49"/>
-      <c r="Z154" s="49"/>
-      <c r="AA154" s="49"/>
+      <c r="T154" s="72">
+        <f>T115/(Statement!T48/Statement!T74)</f>
+        <v>47.607357669756006</v>
+      </c>
+      <c r="U154" s="72">
+        <f>U115/(Statement!U48/Statement!U74)</f>
+        <v>52.518654304314175</v>
+      </c>
+      <c r="V154" s="72">
+        <f>V115/(Statement!V48/Statement!V74)</f>
+        <v>43.868140733924143</v>
+      </c>
+      <c r="W154" s="72">
+        <f>W115/(Statement!W48/Statement!W74)</f>
+        <v>32.259580406235465</v>
+      </c>
+      <c r="X154" s="72">
+        <f>X115/(Statement!X48/Statement!X74)</f>
+        <v>42.049525122090067</v>
+      </c>
+      <c r="Y154" s="72">
+        <f>Y115/(Statement!Y48/Statement!Y74)</f>
+        <v>38.018503410514988</v>
+      </c>
+      <c r="Z154" s="72">
+        <f>Z115/(Statement!Z48/Statement!Z74)</f>
+        <v>28.992904960805632</v>
+      </c>
+      <c r="AA154" s="72">
+        <f>AA115/(Statement!AA48/Statement!AA74)</f>
+        <v>25.784165669091546</v>
+      </c>
       <c r="AC154" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>25.676458250202078</v>
+        <v>24.633280947849848</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30719,17 +30812,41 @@
         <f>Statement!Q115*Statement!Q77</f>
         <v>4589469.8499999996</v>
       </c>
-      <c r="T155" s="49"/>
-      <c r="U155" s="49"/>
-      <c r="V155" s="49"/>
-      <c r="W155" s="49"/>
-      <c r="X155" s="49"/>
-      <c r="Y155" s="49"/>
-      <c r="Z155" s="49"/>
-      <c r="AA155" s="49"/>
+      <c r="T155" s="144">
+        <f>Statement!T115*Statement!T77</f>
+        <v>2799176</v>
+      </c>
+      <c r="U155" s="144">
+        <f>Statement!U115*Statement!U77</f>
+        <v>3494984.92</v>
+      </c>
+      <c r="V155" s="144">
+        <f>Statement!V115*Statement!V77</f>
+        <v>3515440.38</v>
+      </c>
+      <c r="W155" s="144">
+        <f>Statement!W115*Statement!W77</f>
+        <v>2723584.5</v>
+      </c>
+      <c r="X155" s="144">
+        <f>Statement!X115*Statement!X77</f>
+        <v>4239223.82</v>
+      </c>
+      <c r="Y155" s="144">
+        <f>Statement!Y115*Statement!Y77</f>
+        <v>4549305.12</v>
+      </c>
+      <c r="Z155" s="144">
+        <f>Statement!Z115*Statement!Z77</f>
+        <v>4589469.8499999996</v>
+      </c>
+      <c r="AA155" s="144">
+        <f>Statement!AA115*Statement!AA77</f>
+        <v>5062002.3500000006</v>
+      </c>
       <c r="AC155" s="144">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>5040857</v>
+        <v>4836058.2090000007</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30756,17 +30873,41 @@
         <f>Q155+Q106-Q105+Q47+Q44</f>
         <v>4535381.8499999996</v>
       </c>
-      <c r="T156" s="49"/>
-      <c r="U156" s="49"/>
-      <c r="V156" s="49"/>
-      <c r="W156" s="49"/>
-      <c r="X156" s="49"/>
-      <c r="Y156" s="49"/>
-      <c r="Z156" s="49"/>
-      <c r="AA156" s="49"/>
+      <c r="T156" s="144">
+        <f t="shared" ref="T156:AA156" si="95">T155+T106-T105+T47+T44</f>
+        <v>2772837</v>
+      </c>
+      <c r="U156" s="144">
+        <f t="shared" si="95"/>
+        <v>3464959.92</v>
+      </c>
+      <c r="V156" s="144">
+        <f t="shared" si="95"/>
+        <v>3480693.38</v>
+      </c>
+      <c r="W156" s="144">
+        <f t="shared" si="95"/>
+        <v>2678357.5</v>
+      </c>
+      <c r="X156" s="144">
+        <f t="shared" si="95"/>
+        <v>4190898.8200000003</v>
+      </c>
+      <c r="Y156" s="144">
+        <f t="shared" si="95"/>
+        <v>4497164.12</v>
+      </c>
+      <c r="Z156" s="144">
+        <f t="shared" si="95"/>
+        <v>4535481.8499999996</v>
+      </c>
+      <c r="AA156" s="144">
+        <f t="shared" si="95"/>
+        <v>4989900.3500000006</v>
+      </c>
       <c r="AC156" s="144">
         <f ca="1">AC155+AC106-AC105+AC47+AC44</f>
-        <v>4968755</v>
+        <v>4763956.2090000007</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -30803,7 +30944,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="184">
         <f ca="1">AC156/AC5</f>
-        <v>19.601307344244962</v>
+        <v>18.79339388380653</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -30840,7 +30981,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="184">
         <f ca="1">AC156/AC11</f>
-        <v>30.617463105031273</v>
+        <v>29.355493169424165</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -30868,35 +31009,35 @@
         <v>90290</v>
       </c>
       <c r="T159" s="64">
-        <f t="shared" ref="T159:AA159" si="94">T58-T53+T108+T64</f>
+        <f t="shared" ref="T159:AA159" si="96">T58-T53+T108+T64</f>
         <v>12358</v>
       </c>
       <c r="U159" s="64">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>15564</v>
       </c>
       <c r="V159" s="64">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>14230</v>
       </c>
       <c r="W159" s="64">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>24713</v>
       </c>
       <c r="X159" s="64">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>11847</v>
       </c>
       <c r="Y159" s="64">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>20458</v>
       </c>
       <c r="Z159" s="64">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>33273</v>
       </c>
       <c r="AA159" s="64">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>46659</v>
       </c>
       <c r="AC159" s="64">
@@ -30950,19 +31091,19 @@
         <v>95.00515665796344</v>
       </c>
       <c r="N161" s="72">
-        <f t="shared" ref="N161:Q161" si="95">N155/N159</f>
+        <f t="shared" ref="N161:Q161" si="97">N155/N159</f>
         <v>461.29572338489538</v>
       </c>
       <c r="O161" s="72">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>65.653012099522826</v>
       </c>
       <c r="P161" s="72">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>62.645954451493331</v>
       </c>
       <c r="Q161" s="72">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>50.830322848598954</v>
       </c>
       <c r="T161" s="49"/>
@@ -30974,8 +31115,8 @@
       <c r="Z161" s="49"/>
       <c r="AA161" s="49"/>
       <c r="AC161" s="72">
-        <f t="shared" ref="AC161:AC162" ca="1" si="96">AC155/AC159</f>
-        <v>44.912613487530848</v>
+        <f t="shared" ref="AC161:AC162" ca="1" si="98">AC155/AC159</f>
+        <v>43.087914047952111</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -30987,19 +31128,19 @@
         <v>85.552901846404438</v>
       </c>
       <c r="N162" s="72">
-        <f t="shared" ref="N162:Q162" si="97">N156/N160</f>
+        <f t="shared" ref="N162:Q162" si="99">N156/N160</f>
         <v>292.02604166666669</v>
       </c>
       <c r="O162" s="72">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>59.253144937486333</v>
       </c>
       <c r="P162" s="72">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>58.114897258120507</v>
       </c>
       <c r="Q162" s="72">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>49.56625962229554</v>
       </c>
       <c r="T162" s="49"/>
@@ -31011,8 +31152,8 @@
       <c r="Z162" s="49"/>
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
-        <f t="shared" ca="1" si="96"/>
-        <v>39.180801198869766</v>
+        <f t="shared" ca="1" si="98"/>
+        <v>37.565873371689747</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31024,19 +31165,19 @@
         <v>1.0525744445642981E-2</v>
       </c>
       <c r="N163" s="74">
-        <f t="shared" ref="N163:Q163" si="98">N159/N155</f>
+        <f t="shared" ref="N163:Q163" si="100">N159/N155</f>
         <v>2.1678067870696933E-3</v>
       </c>
       <c r="O163" s="74">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>1.5231593616513875E-2</v>
       </c>
       <c r="P163" s="74">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>1.5962722712993357E-2</v>
       </c>
       <c r="Q163" s="74">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>1.9673296252289359E-2</v>
       </c>
       <c r="T163" s="49"/>
@@ -31048,8 +31189,8 @@
       <c r="Z163" s="49"/>
       <c r="AA163" s="49"/>
       <c r="AC163" s="74">
-        <f t="shared" ref="AC163" ca="1" si="99">AC159/AC155</f>
-        <v>2.2265460019992633E-2</v>
+        <f t="shared" ref="AC163" ca="1" si="101">AC159/AC155</f>
+        <v>2.3208364157223067E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31086,7 +31227,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>3.1485053037608485E-2</v>
+        <v>3.2818391165067962E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31123,7 +31264,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="155">
         <f ca="1">AC81/AC115</f>
-        <v>1.9286403085824494E-4</v>
+        <v>2.0103149258847143E-4</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31160,7 +31301,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="155">
         <f ca="1">-AC62/AC155</f>
-        <v>8.9873606809318333E-3</v>
+        <v>9.3679600290352896E-3</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -31197,7 +31338,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="155">
         <f ca="1">-(AC62+AC63)/AC155</f>
-        <v>9.1803834149629723E-3</v>
+        <v>9.5691569456044963E-3</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31447,35 +31588,35 @@
         <v>2.5743209876543212</v>
       </c>
       <c r="T174" s="72">
-        <f t="shared" ref="T174:AA174" si="100">T105/T74</f>
+        <f t="shared" ref="T174:AA174" si="102">T105/T74</f>
         <v>1.4186710150835711</v>
       </c>
       <c r="U174" s="72">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>1.5715394038383013</v>
       </c>
       <c r="V174" s="72">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>1.7709016393442623</v>
       </c>
       <c r="W174" s="72">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>2.2004508196721311</v>
       </c>
       <c r="X174" s="72">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>2.3370781893004113</v>
       </c>
       <c r="Y174" s="72">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>2.494156378600823</v>
       </c>
       <c r="Z174" s="72">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>2.5743209876543212</v>
       </c>
       <c r="AA174" s="72">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>3.3294214876033057</v>
       </c>
       <c r="AC174" s="72">
@@ -31508,35 +31649,35 @@
         <v>6.217021359450145E-2</v>
       </c>
       <c r="T175" s="155">
-        <f t="shared" ref="T175:AA175" si="101">T53/T58</f>
+        <f t="shared" ref="T175:AA175" si="103">T53/T58</f>
         <v>7.9646628476775491E-2</v>
       </c>
       <c r="U175" s="155">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>7.1019343127800783E-2</v>
       </c>
       <c r="V175" s="155">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>7.944431080105846E-2</v>
       </c>
       <c r="W175" s="155">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>5.3768147661778655E-2</v>
       </c>
       <c r="X175" s="155">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>0.10569476082004556</v>
       </c>
       <c r="Y175" s="155">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>6.9684210526315793E-2</v>
       </c>
       <c r="Z175" s="155">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>4.5122962144238742E-2</v>
       </c>
       <c r="AA175" s="155">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>3.829651994279358E-2</v>
       </c>
       <c r="AC175" s="155">
@@ -31569,35 +31710,35 @@
         <v>2.9573303448211987E-2</v>
       </c>
       <c r="T176" s="155">
-        <f t="shared" ref="T176:AA176" si="102">T53/T5</f>
+        <f t="shared" ref="T176:AA176" si="104">T53/T5</f>
         <v>3.8415446071904127E-2</v>
       </c>
       <c r="U176" s="155">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>3.5687817114189613E-2</v>
       </c>
       <c r="V176" s="155">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>3.3586738196333683E-2</v>
       </c>
       <c r="W176" s="155">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>3.3452861876446825E-2</v>
       </c>
       <c r="X176" s="155">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>3.4743170100335882E-2</v>
       </c>
       <c r="Y176" s="155">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>2.9032031715959722E-2</v>
       </c>
       <c r="Z176" s="155">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>2.3969938497218429E-2</v>
       </c>
       <c r="AA176" s="155">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>2.3623108497212521E-2</v>
       </c>
       <c r="AC176" s="155">
@@ -31630,35 +31771,35 @@
         <v>2.2258436213991768</v>
       </c>
       <c r="T177" s="72">
-        <f t="shared" ref="T177:AA177" si="103">(T105-T106)/T74</f>
+        <f t="shared" ref="T177:AA177" si="105">(T105-T106)/T74</f>
         <v>1.0737464329392581</v>
       </c>
       <c r="U177" s="72">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>1.2260106165781952</v>
       </c>
       <c r="V177" s="72">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>1.4240573770491802</v>
       </c>
       <c r="W177" s="72">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>1.8535655737704917</v>
       </c>
       <c r="X177" s="72">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>1.9886831275720165</v>
       </c>
       <c r="Y177" s="72">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>2.1457201646090533</v>
       </c>
       <c r="Z177" s="72">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>2.2217283950617284</v>
       </c>
       <c r="AA177" s="72">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>2.9794214876033056</v>
       </c>
       <c r="AC177" s="72">
@@ -31700,7 +31841,7 @@
       <c r="AA178" s="49"/>
       <c r="AC178" s="155">
         <f ca="1">(AC105-AC106)/AC155</f>
-        <v>1.4303520214915837E-2</v>
+        <v>1.4909249823713193E-2</v>
       </c>
     </row>
     <row r="179" spans="1:31" x14ac:dyDescent="0.2">
@@ -31728,35 +31869,35 @@
         <v>2.7980253591308617E-2</v>
       </c>
       <c r="T179" s="155">
-        <f t="shared" ref="T179:AA179" si="104">-T108/T5</f>
+        <f t="shared" ref="T179:AA179" si="106">-T108/T5</f>
         <v>3.2523302263648468E-2</v>
       </c>
       <c r="U179" s="155">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>2.3174277407217378E-2</v>
       </c>
       <c r="V179" s="155">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>2.7382980346291729E-2</v>
       </c>
       <c r="W179" s="155">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>2.7847124506377378E-2</v>
       </c>
       <c r="X179" s="155">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>4.05194360652932E-2</v>
       </c>
       <c r="Y179" s="155">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>2.871627547977406E-2</v>
       </c>
       <c r="Z179" s="155">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>1.8847153111101324E-2</v>
       </c>
       <c r="AA179" s="155">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>2.1527905409544815E-2</v>
       </c>
       <c r="AC179" s="155">
@@ -31789,35 +31930,35 @@
         <v>5.8821238731283712E-2</v>
       </c>
       <c r="T180" s="155">
-        <f t="shared" ref="T180:AA180" si="105">-(T108/T58)</f>
+        <f t="shared" ref="T180:AA180" si="107">-(T108/T58)</f>
         <v>6.7430464490302988E-2</v>
       </c>
       <c r="U180" s="155">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>4.6117193261103862E-2</v>
       </c>
       <c r="V180" s="155">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>6.4770267019485211E-2</v>
       </c>
       <c r="W180" s="155">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>4.4758152768658348E-2</v>
       </c>
       <c r="X180" s="155">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.12326716563618614</v>
       </c>
       <c r="Y180" s="155">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>6.8926315789473683E-2</v>
       </c>
       <c r="Z180" s="155">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>3.5479414202818457E-2</v>
       </c>
       <c r="AA180" s="155">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>3.4899888765294769E-2</v>
       </c>
       <c r="AC180" s="155">
@@ -31850,35 +31991,35 @@
         <v>2.1252198381990857</v>
       </c>
       <c r="T181" s="155">
-        <f t="shared" ref="T181:AA181" si="106">-T108/T52</f>
+        <f t="shared" ref="T181:AA181" si="108">-T108/T52</f>
         <v>2.25635103926097</v>
       </c>
       <c r="U181" s="155">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>1.7008368200836821</v>
       </c>
       <c r="V181" s="155">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>1.9834254143646408</v>
       </c>
       <c r="W181" s="155">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>2.0081833060556464</v>
       </c>
       <c r="X181" s="155">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>2.8353293413173652</v>
       </c>
       <c r="Y181" s="155">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>2.1768617021276597</v>
       </c>
       <c r="Z181" s="155">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>1.5832305795314427</v>
       </c>
       <c r="AA181" s="155">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>1.7622868605817452</v>
       </c>
       <c r="AC181" s="155">
@@ -31895,19 +32036,19 @@
         <v>0.60909317219996828</v>
       </c>
       <c r="N182" s="72">
-        <f t="shared" ref="N182:Q182" si="107">N5/N36</f>
+        <f t="shared" ref="N182:Q182" si="109">N5/N36</f>
         <v>0.65499490068476518</v>
       </c>
       <c r="O182" s="72">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>0.92688047711781885</v>
       </c>
       <c r="P182" s="72">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>1.169317479234057</v>
       </c>
       <c r="Q182" s="72">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>1.0441724733200195</v>
       </c>
       <c r="T182" s="49"/>
@@ -31919,7 +32060,7 @@
       <c r="Z182" s="49"/>
       <c r="AA182" s="49"/>
       <c r="AC182" s="72">
-        <f t="shared" ref="AC182" si="108">AC5/AC36</f>
+        <f t="shared" ref="AC182" si="110">AC5/AC36</f>
         <v>0.97694181305256023</v>
       </c>
     </row>
@@ -31932,19 +32073,19 @@
         <v>1.0901304650931183</v>
       </c>
       <c r="N183" s="72">
-        <f t="shared" ref="N183:Q183" si="109">IF(AND(N11&gt;0,N106&gt;0),N106/N11,"N/A")</f>
+        <f t="shared" ref="N183:Q183" si="111">IF(AND(N11&gt;0,N106&gt;0),N106/N11,"N/A")</f>
         <v>2.5930397727272729</v>
       </c>
       <c r="O183" s="72">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>0.29446196773019534</v>
       </c>
       <c r="P183" s="72">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>0.103900408824721</v>
       </c>
       <c r="Q183" s="72">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>6.4945124897420756E-2</v>
       </c>
       <c r="T183" s="49"/>
@@ -31956,7 +32097,7 @@
       <c r="Z183" s="49"/>
       <c r="AA183" s="49"/>
       <c r="AC183" s="72">
-        <f t="shared" ref="AC183" si="110">IF(AND(AC11&gt;0,AC106&gt;0),AC106/AC11,"N/A")</f>
+        <f t="shared" ref="AC183" si="112">IF(AND(AC11&gt;0,AC106&gt;0),AC106/AC11,"N/A")</f>
         <v>5.2192131127337706E-2</v>
       </c>
     </row>
@@ -31969,19 +32110,19 @@
         <v>-1.0220097599840654</v>
       </c>
       <c r="N184" s="230">
-        <f t="shared" ref="N184:Q184" si="111">IF(AND(N11&gt;0,N106&gt;0),(N106-N105)/N11,"N/A")</f>
+        <f t="shared" ref="N184:Q184" si="113">IF(AND(N11&gt;0,N106&gt;0),(N106-N105)/N11,"N/A")</f>
         <v>-0.5546875</v>
       </c>
       <c r="O184" s="230">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>-0.49360063083828704</v>
       </c>
       <c r="P184" s="230">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>-0.42658956698955225</v>
       </c>
       <c r="Q184" s="230">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>-0.41482663148933557</v>
       </c>
       <c r="T184" s="49"/>
@@ -31993,7 +32134,7 @@
       <c r="Z184" s="49"/>
       <c r="AA184" s="49"/>
       <c r="AC184" s="230">
-        <f t="shared" ref="AC184" si="112">IF(AND(AC11&gt;0,AC106&gt;0),(AC106-AC105)/AC11,"N/A")</f>
+        <f t="shared" ref="AC184" si="114">IF(AND(AC11&gt;0,AC106&gt;0),(AC106-AC105)/AC11,"N/A")</f>
         <v>-0.44429244847028376</v>
       </c>
     </row>
@@ -32006,19 +32147,19 @@
         <v>1.6461162079510703</v>
       </c>
       <c r="N185" s="230">
-        <f t="shared" ref="N185:Q185" si="113">N5/(N106+N110-N105)</f>
+        <f t="shared" ref="N185:Q185" si="115">N5/(N106+N110-N105)</f>
         <v>1.3652191517360057</v>
       </c>
       <c r="O185" s="230">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>2.2814665018911731</v>
       </c>
       <c r="P185" s="230">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>2.9272543741588155</v>
       </c>
       <c r="Q185" s="230">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>2.0923211084734268</v>
       </c>
       <c r="T185" s="49"/>
@@ -32030,7 +32171,7 @@
       <c r="Z185" s="49"/>
       <c r="AA185" s="49"/>
       <c r="AC185" s="230">
-        <f t="shared" ref="AC185" si="114">AC5/(AC106+AC110-AC105)</f>
+        <f t="shared" ref="AC185" si="116">AC5/(AC106+AC110-AC105)</f>
         <v>2.0546882598968974</v>
       </c>
     </row>
@@ -32160,7 +32301,7 @@
         <v>37377</v>
       </c>
       <c r="AC190" s="62">
-        <f t="shared" ref="AC190:AC192" si="115">SUM(X190:AA190)</f>
+        <f t="shared" ref="AC190:AC192" si="117">SUM(X190:AA190)</f>
         <v>103965</v>
       </c>
     </row>
@@ -32218,7 +32359,7 @@
         <v>75246</v>
       </c>
       <c r="AC191" s="62">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>229871</v>
       </c>
     </row>
@@ -32278,7 +32419,7 @@
         <v>6369</v>
       </c>
       <c r="AC192" s="62">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>23620</v>
       </c>
     </row>
@@ -32342,61 +32483,61 @@
       <c r="K196" s="81"/>
       <c r="L196" s="81"/>
       <c r="M196" s="81">
-        <f t="shared" ref="M196:Q199" si="116">IF(L189=0,
+        <f t="shared" ref="M196:Q199" si="118">IF(L189=0,
 IF(M189=0,0,IF(M189&gt;0,1,-1)),
 (M189-L189)/ABS(L189)
 )</f>
         <v>0</v>
       </c>
       <c r="N196" s="81">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="O196" s="81">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="P196" s="81">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>1</v>
       </c>
       <c r="Q196" s="81">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>0.96364041936203437</v>
       </c>
       <c r="T196" s="81">
-        <f t="shared" ref="T196:AA199" si="117">IF(S189=0,
+        <f t="shared" ref="T196:AA199" si="119">IF(S189=0,
 IF(T189=0,0,IF(T189&gt;0,1,-1)),
 (T189-S189)/ABS(S189)
 )</f>
         <v>1</v>
       </c>
       <c r="U196" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>0.26059122575786103</v>
       </c>
       <c r="V196" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>0.42598954443614639</v>
       </c>
       <c r="W196" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>-7.8296847177123707E-2</v>
       </c>
       <c r="X196" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>0.35706574237172567</v>
       </c>
       <c r="Y196" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>0.27035967005820039</v>
       </c>
       <c r="Z196" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>0.11450230718523402</v>
       </c>
       <c r="AA196" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>0.11992074288756137</v>
       </c>
       <c r="AC196" s="49"/>
@@ -32406,55 +32547,55 @@
         <v>371</v>
       </c>
       <c r="M197" s="81">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="N197" s="81">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="O197" s="81">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="P197" s="81">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>1</v>
       </c>
       <c r="Q197" s="81">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>0.43510343704186349</v>
       </c>
       <c r="T197" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>1</v>
       </c>
       <c r="U197" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>0.11060702875399361</v>
       </c>
       <c r="V197" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>-5.1493009608192856E-2</v>
       </c>
       <c r="W197" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>0.304925391241053</v>
       </c>
       <c r="X197" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>-0.19987914284386185</v>
       </c>
       <c r="Y197" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>0.21274618021262998</v>
       </c>
       <c r="Z197" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>0.3652694610778443</v>
       </c>
       <c r="AA197" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>0.31147368421052629</v>
       </c>
       <c r="AC197" s="49"/>
@@ -32464,55 +32605,55 @@
         <v>372</v>
       </c>
       <c r="M198" s="81">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="N198" s="81">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="O198" s="81">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="P198" s="81">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>1</v>
       </c>
       <c r="Q198" s="81">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>0.68194919521469621</v>
       </c>
       <c r="T198" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>1</v>
       </c>
       <c r="U198" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>0.17124695493300854</v>
       </c>
       <c r="V198" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>0.15628351369796237</v>
       </c>
       <c r="W198" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>9.9269252388982571E-2</v>
       </c>
       <c r="X198" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>5.0726119860912251E-2</v>
       </c>
       <c r="Y198" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>0.24622834339108429</v>
       </c>
       <c r="Z198" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>0.21671385336327248</v>
       </c>
       <c r="AA198" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>0.20752960811374652</v>
       </c>
       <c r="AC198" s="49"/>
@@ -32522,55 +32663,55 @@
         <v>373</v>
       </c>
       <c r="M199" s="81">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="N199" s="81">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="O199" s="81">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="P199" s="81">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>1</v>
       </c>
       <c r="Q199" s="81">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>0.4500032656260205</v>
       </c>
       <c r="T199" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>1</v>
       </c>
       <c r="U199" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>0.14410828025477707</v>
       </c>
       <c r="V199" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>-0.12990025516121551</v>
       </c>
       <c r="W199" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>0.31964809384164222</v>
       </c>
       <c r="X199" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>0.1408080808080808</v>
       </c>
       <c r="Y199" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>2.5500265627766958E-2</v>
       </c>
       <c r="Z199" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>3.7989984458642722E-3</v>
       </c>
       <c r="AA199" s="81">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>9.5647686220540165E-2</v>
       </c>
       <c r="AC199" s="49"/>
@@ -32710,15 +32851,15 @@
         <v>89.141856392294216</v>
       </c>
       <c r="O207" s="144">
-        <f t="shared" ref="O207:Q207" si="118">100*(1+((O115-$M115)/ABS($M115)))</f>
+        <f t="shared" ref="O207:Q207" si="120">100*(1+((O115-$M115)/ABS($M115)))</f>
         <v>267.20665499124345</v>
       </c>
       <c r="P207" s="144">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>624.43082311733804</v>
       </c>
       <c r="Q207" s="144">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>821.67250437828375</v>
       </c>
       <c r="T207" s="49"/>
@@ -32743,15 +32884,15 @@
         <v>100.2229323028907</v>
       </c>
       <c r="O208" s="144">
-        <f t="shared" ref="O208:Q208" si="119">100*(1+((O5-$M5)/ABS($M5)))</f>
+        <f t="shared" ref="O208:Q208" si="121">100*(1+((O5-$M5)/ABS($M5)))</f>
         <v>226.35802927844244</v>
       </c>
       <c r="P208" s="144">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>484.86661217210371</v>
       </c>
       <c r="Q208" s="144">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>802.32592702682621</v>
       </c>
       <c r="T208" s="49"/>
@@ -32776,15 +32917,15 @@
         <v>45.194805194805184</v>
       </c>
       <c r="O209" s="144">
-        <f t="shared" ref="O209:Q209" si="120">100*(1+((O25-$M25)/ABS($M25)))</f>
+        <f t="shared" ref="O209:Q209" si="122">100*(1+((O25-$M25)/ABS($M25)))</f>
         <v>309.87012987012992</v>
       </c>
       <c r="P209" s="144">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>763.63636363636363</v>
       </c>
       <c r="Q209" s="144">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>1272.7272727272727</v>
       </c>
       <c r="T209" s="49"/>
@@ -32881,7 +33022,7 @@
       </c>
       <c r="C5" s="173">
         <f ca="1">Overview!C5</f>
-        <v>207.4</v>
+        <v>198.97380000000001</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="133" t="s">
@@ -32897,7 +33038,7 @@
       </c>
       <c r="C6" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>5040857</v>
+        <v>4836058.2090000007</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -32917,7 +33058,7 @@
       </c>
       <c r="C7" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>4968755</v>
+        <v>4763956.2090000007</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -32937,7 +33078,7 @@
       </c>
       <c r="C8" s="175">
         <f ca="1">Statement!AC152</f>
-        <v>31.761102603369071</v>
+        <v>30.470719754977033</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>240</v>
@@ -32957,7 +33098,7 @@
       </c>
       <c r="C9" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>20.012151516227402</v>
+        <v>19.19910237878268</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>241</v>
@@ -32977,7 +33118,7 @@
       </c>
       <c r="C10" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>25.676458250202078</v>
+        <v>24.633280947849848</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -32997,7 +33138,7 @@
       </c>
       <c r="C11" s="175">
         <f ca="1">Statement!AC157</f>
-        <v>19.601307344244962</v>
+        <v>18.79339388380653</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33006,7 +33147,7 @@
       </c>
       <c r="C12" s="175">
         <f ca="1">Statement!AC158</f>
-        <v>30.617463105031273</v>
+        <v>29.355493169424165</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -33242,7 +33383,7 @@
       </c>
       <c r="C38" s="176">
         <f ca="1">Statement!AC164</f>
-        <v>3.1485053037608485E-2</v>
+        <v>3.2818391165067962E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>267</v>
@@ -33258,7 +33399,7 @@
       </c>
       <c r="C39" s="216">
         <f ca="1">Statement!AC163</f>
-        <v>2.2265460019992633E-2</v>
+        <v>2.3208364157223067E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>269</v>
@@ -33274,7 +33415,7 @@
       </c>
       <c r="C40" s="176">
         <f ca="1">Statement!AC165</f>
-        <v>1.9286403085824494E-4</v>
+        <v>2.0103149258847143E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>270</v>
@@ -33290,7 +33431,7 @@
       </c>
       <c r="C41" s="176">
         <f ca="1">Statement!AC166</f>
-        <v>8.9873606809318333E-3</v>
+        <v>9.3679600290352896E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33299,7 +33440,7 @@
       </c>
       <c r="C42" s="176">
         <f ca="1">Statement!AC167</f>
-        <v>9.1803834149629723E-3</v>
+        <v>9.5691569456044963E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -33343,7 +33484,7 @@
       </c>
       <c r="F48" s="176">
         <f ca="1">Statement!AC178</f>
-        <v>1.4303520214915837E-2</v>
+        <v>1.4909249823713193E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -33523,7 +33664,7 @@
       </c>
       <c r="I6" s="173">
         <f ca="1">Statement!AC114</f>
-        <v>207.4</v>
+        <v>198.97380000000001</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33552,7 +33693,7 @@
       </c>
       <c r="I7" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>5040857</v>
+        <v>4836058.2090000007</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33581,7 +33722,7 @@
       </c>
       <c r="I8" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>4968755</v>
+        <v>4763956.2090000007</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33610,7 +33751,7 @@
       </c>
       <c r="I9" s="175">
         <f ca="1">Statement!AC152</f>
-        <v>31.761102603369071</v>
+        <v>30.470719754977033</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33639,7 +33780,7 @@
       </c>
       <c r="I10" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>20.012151516227402</v>
+        <v>19.19910237878268</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33668,7 +33809,7 @@
       </c>
       <c r="I11" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>25.676458250202078</v>
+        <v>24.633280947849848</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33697,7 +33838,7 @@
       </c>
       <c r="I12" s="175">
         <f ca="1">Statement!AC157</f>
-        <v>19.601307344244962</v>
+        <v>18.79339388380653</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33726,7 +33867,7 @@
       </c>
       <c r="I13" s="175">
         <f ca="1">Statement!AC158</f>
-        <v>30.617463105031273</v>
+        <v>29.355493169424165</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34499,7 +34640,7 @@
       </c>
       <c r="I51" s="176">
         <f ca="1">Statement!AC164</f>
-        <v>3.1485053037608485E-2</v>
+        <v>3.2818391165067962E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34528,7 +34669,7 @@
       </c>
       <c r="I52" s="176">
         <f ca="1">Statement!AC163</f>
-        <v>2.2265460019992633E-2</v>
+        <v>2.3208364157223067E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34557,7 +34698,7 @@
       </c>
       <c r="I53" s="176">
         <f ca="1">Statement!AC165</f>
-        <v>1.9286403085824494E-4</v>
+        <v>2.0103149258847143E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -34586,7 +34727,7 @@
       </c>
       <c r="I54" s="176">
         <f ca="1">Statement!AC166</f>
-        <v>8.9873606809318333E-3</v>
+        <v>9.3679600290352896E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34615,7 +34756,7 @@
       </c>
       <c r="I55" s="176">
         <f ca="1">Statement!AC167</f>
-        <v>9.1803834149629723E-3</v>
+        <v>9.5691569456044963E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34851,7 +34992,7 @@
       </c>
       <c r="I68" s="197">
         <f ca="1">Statement!AC178</f>
-        <v>1.4303520214915837E-2</v>
+        <v>1.4909249823713193E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
